--- a/documents/ExperimentData.xlsx
+++ b/documents/ExperimentData.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ostatemailokstate-my.sharepoint.com/personal/lucius_vo_okstate_edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1b2bcfbbb34c0c/Documents/GitHub/meliso/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="155" documentId="8_{D7059BC8-D0E2-41E7-A566-DBD48656E1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED452C8B-D082-BF46-ABC4-901F1A87DDE0}"/>
+  <xr:revisionPtr revIDLastSave="403" documentId="8_{D7059BC8-D0E2-41E7-A566-DBD48656E1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E185A334-D7E8-418E-B917-3C8B74B4AEE2}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
   </bookViews>
   <sheets>
-    <sheet name="Experiment 1" sheetId="1" r:id="rId1"/>
+    <sheet name="DataExp1" sheetId="2" r:id="rId1"/>
+    <sheet name="Experiment 1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
   <si>
     <t>MCA Rows</t>
   </si>
@@ -68,9 +69,6 @@
     <t>L-infty Norm Error</t>
   </si>
   <si>
-    <t xml:space="preserve">L-2 Norm Error </t>
-  </si>
-  <si>
     <t>Acc. Write Latency (Mean)</t>
   </si>
   <si>
@@ -93,12 +91,36 @@
   </si>
   <si>
     <t>TaOx-HfOx</t>
+  </si>
+  <si>
+    <t>N = 10</t>
+  </si>
+  <si>
+    <t>L-2 Norm Error (Mean)</t>
+  </si>
+  <si>
+    <t>L-infty Norm Error (Mean)</t>
+  </si>
+  <si>
+    <t>N=1</t>
+  </si>
+  <si>
+    <t>L-2 Norm Error</t>
+  </si>
+  <si>
+    <t>N=3</t>
+  </si>
+  <si>
+    <t>N = 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -115,15 +137,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -131,14 +159,93 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -146,11 +253,38 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -167,10 +301,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -489,560 +619,1238 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB6579EC-3EC3-439D-9B94-319298E6C78E}">
+  <dimension ref="B1:R34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="K1" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+    </row>
+    <row r="2" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="19"/>
+      <c r="K2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="8"/>
+      <c r="O2" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="R2" s="19"/>
+    </row>
+    <row r="3" spans="2:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q3" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" s="18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B4" s="11">
+        <v>24.443761142859401</v>
+      </c>
+      <c r="C4" s="11">
+        <v>3.3744526857264301</v>
+      </c>
+      <c r="D4" s="12">
+        <v>11.146140000613499</v>
+      </c>
+      <c r="E4" s="12">
+        <v>1.68778800506088</v>
+      </c>
+      <c r="F4" s="11">
+        <v>5.0263956831744903</v>
+      </c>
+      <c r="G4" s="11">
+        <v>0.90170831675261998</v>
+      </c>
+      <c r="H4" s="12">
+        <v>1.0386527872326301</v>
+      </c>
+      <c r="I4" s="12">
+        <v>0.281035172507479</v>
+      </c>
+      <c r="K4" s="11">
+        <v>50.189180557709498</v>
+      </c>
+      <c r="L4" s="11">
+        <v>6.8272041826728298</v>
+      </c>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B5" s="11">
+        <v>21.768763521560601</v>
+      </c>
+      <c r="C5" s="11">
+        <v>3.1865062401780699</v>
+      </c>
+      <c r="D5" s="12">
+        <v>10.978647285226099</v>
+      </c>
+      <c r="E5" s="12">
+        <v>1.7065269254956801</v>
+      </c>
+      <c r="F5" s="11">
+        <v>4.85409002254627</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0.80897913982258796</v>
+      </c>
+      <c r="H5" s="12">
+        <v>0.89008783875792397</v>
+      </c>
+      <c r="I5" s="12">
+        <v>0.27529653142885502</v>
+      </c>
+      <c r="K5" s="11">
+        <v>49.008992449178898</v>
+      </c>
+      <c r="L5" s="11">
+        <v>6.5588284593994697</v>
+      </c>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B6" s="11">
+        <v>24.272210690591301</v>
+      </c>
+      <c r="C6" s="11">
+        <v>3.3054398403598002</v>
+      </c>
+      <c r="D6" s="12">
+        <v>11.131989491819301</v>
+      </c>
+      <c r="E6" s="12">
+        <v>1.68616441676978</v>
+      </c>
+      <c r="F6" s="11">
+        <v>4.9373714864782201</v>
+      </c>
+      <c r="G6" s="11">
+        <v>0.89188987256264995</v>
+      </c>
+      <c r="H6" s="12">
+        <v>1.0114258900419599</v>
+      </c>
+      <c r="I6" s="12">
+        <v>0.29627600535638898</v>
+      </c>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B7" s="11">
+        <v>24.404174573572501</v>
+      </c>
+      <c r="C7" s="11">
+        <v>3.3186837088307102</v>
+      </c>
+      <c r="D7" s="12">
+        <v>10.9557705531107</v>
+      </c>
+      <c r="E7" s="12">
+        <v>1.57213037578915</v>
+      </c>
+      <c r="F7" s="11">
+        <v>4.7911793814388997</v>
+      </c>
+      <c r="G7" s="11">
+        <v>0.81751166683242105</v>
+      </c>
+      <c r="H7" s="12">
+        <v>0.95254623904054903</v>
+      </c>
+      <c r="I7" s="12">
+        <v>0.26236662864990901</v>
+      </c>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B8" s="11">
+        <v>24.519392747918499</v>
+      </c>
+      <c r="C8" s="11">
+        <v>3.3765146340410901</v>
+      </c>
+      <c r="D8" s="12">
+        <v>11.084394304570299</v>
+      </c>
+      <c r="E8" s="12">
+        <v>1.71086338931697</v>
+      </c>
+      <c r="F8" s="11">
+        <v>4.5716851890135404</v>
+      </c>
+      <c r="G8" s="11">
+        <v>0.78488713802412502</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0.59342344244794798</v>
+      </c>
+      <c r="I8" s="12">
+        <v>0.17203410846221501</v>
+      </c>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B9" s="11">
+        <v>24.310600989632899</v>
+      </c>
+      <c r="C9" s="11">
+        <v>3.3225698262557399</v>
+      </c>
+      <c r="D9" s="12">
+        <v>11.078199731004901</v>
+      </c>
+      <c r="E9" s="12">
+        <v>1.65069524058359</v>
+      </c>
+      <c r="F9" s="11">
+        <v>4.9807010405869097</v>
+      </c>
+      <c r="G9" s="11">
+        <v>0.92921451381373998</v>
+      </c>
+      <c r="H9" s="12">
+        <v>0.56505155768495896</v>
+      </c>
+      <c r="I9" s="12">
+        <v>0.16474922791581201</v>
+      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B10" s="11">
+        <v>24.519392747918499</v>
+      </c>
+      <c r="C10" s="11">
+        <v>3.3765146340410901</v>
+      </c>
+      <c r="D10" s="12">
+        <v>11.3283064247616</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1.75667635216019</v>
+      </c>
+      <c r="F10" s="11">
+        <v>4.3655684894788598</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0.72256847111010403</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0.89008783875792397</v>
+      </c>
+      <c r="I10" s="12">
+        <v>0.27529653142885502</v>
+      </c>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B11" s="11">
+        <v>21.996905724856099</v>
+      </c>
+      <c r="C11" s="11">
+        <v>2.9856415262303599</v>
+      </c>
+      <c r="D11" s="12">
+        <v>11.0671269081706</v>
+      </c>
+      <c r="E11" s="12">
+        <v>1.68567829653259</v>
+      </c>
+      <c r="F11" s="11">
+        <v>4.9579210625189001</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0.89091012676741499</v>
+      </c>
+      <c r="H11" s="12">
+        <v>0.95254623904054903</v>
+      </c>
+      <c r="I11" s="12">
+        <v>0.26236662864990901</v>
+      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B12" s="11">
+        <v>24.073944136969398</v>
+      </c>
+      <c r="C12" s="11">
+        <v>3.2906045777064898</v>
+      </c>
+      <c r="D12" s="12">
+        <v>10.871081688695201</v>
+      </c>
+      <c r="E12" s="12">
+        <v>1.5456538017913899</v>
+      </c>
+      <c r="F12" s="11">
+        <v>4.5042629003538499</v>
+      </c>
+      <c r="G12" s="11">
+        <v>0.75565867825603805</v>
+      </c>
+      <c r="H12" s="12">
+        <v>0.98179762818361005</v>
+      </c>
+      <c r="I12" s="12">
+        <v>0.28993726071696102</v>
+      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B13" s="11">
+        <v>24.073944136969398</v>
+      </c>
+      <c r="C13" s="11">
+        <v>3.2906045777064898</v>
+      </c>
+      <c r="D13" s="12">
+        <v>11.065870149418</v>
+      </c>
+      <c r="E13" s="12">
+        <v>1.7106619694696501</v>
+      </c>
+      <c r="F13" s="11">
+        <v>4.4913411407632298</v>
+      </c>
+      <c r="G13" s="11">
+        <v>0.764781871349272</v>
+      </c>
+      <c r="H13" s="12">
+        <v>0.61764700512757498</v>
+      </c>
+      <c r="I13" s="12">
+        <v>0.17697658502358601</v>
+      </c>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="J15" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="K1:R1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB2F127C-15E6-41A0-94B0-FA50F057125C}">
   <dimension ref="A1:AA35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+    </row>
+    <row r="2" spans="1:27" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-    </row>
-    <row r="2" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:27" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="B4" s="13">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="8">
+        <v>66</v>
+      </c>
+      <c r="E4" s="8">
+        <v>66</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1</v>
+      </c>
+      <c r="G4" s="8">
+        <v>1</v>
+      </c>
+      <c r="H4" s="8">
+        <v>66</v>
+      </c>
+      <c r="I4" s="8">
+        <v>66</v>
+      </c>
+      <c r="J4" s="12">
+        <f>AVERAGE(DataExp1!B4:B13)</f>
+        <v>23.838309041284862</v>
+      </c>
+      <c r="K4" s="12">
+        <f>AVERAGE(DataExp1!C4:C13)</f>
+        <v>3.2827532251076272</v>
+      </c>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="14"/>
+      <c r="B5" s="13">
         <v>3</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="12">
+        <f>AVERAGE(DataExp1!D4:D13)</f>
+        <v>11.070752653739017</v>
+      </c>
+      <c r="K5" s="12">
+        <f>AVERAGE(DataExp1!E4:E13)</f>
+        <v>1.6712838772969871</v>
+      </c>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="13">
+        <v>5</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="12">
+        <f>AVERAGE(DataExp1!F4:F13)</f>
+        <v>4.7480516396353174</v>
+      </c>
+      <c r="K6" s="12">
+        <f>AVERAGE(DataExp1!G4:G13)</f>
+        <v>0.82681097952909732</v>
+      </c>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="14"/>
+      <c r="B7" s="13">
+        <v>10</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="12">
+        <f>AVERAGE(DataExp1!H4:H13)</f>
+        <v>0.84932664663156276</v>
+      </c>
+      <c r="K7" s="12">
+        <f>AVERAGE(DataExp1!I4:I13)</f>
+        <v>0.24563346801399702</v>
+      </c>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="9">
         <v>1</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="15">
+        <v>2.45597546770956</v>
+      </c>
+      <c r="K8" s="15">
+        <v>0.47959805829178598</v>
+      </c>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9">
+        <v>3</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="8"/>
+      <c r="B10" s="9">
+        <v>5</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="8"/>
+      <c r="B11" s="9">
         <v>10</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="13">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="12">
+        <v>2.0124832402399999</v>
+      </c>
+      <c r="K12" s="12">
+        <v>0.37754673426285001</v>
+      </c>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="14"/>
+      <c r="B13" s="13">
+        <v>3</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="14"/>
+      <c r="B14" s="13">
         <v>5</v>
       </c>
-      <c r="D4" s="2">
-        <v>66</v>
-      </c>
-      <c r="E4" s="2">
-        <v>66</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="14"/>
+      <c r="B15" s="13">
+        <v>10</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="9">
         <v>1</v>
       </c>
-      <c r="G4" s="2">
-        <v>1</v>
-      </c>
-      <c r="H4" s="2">
-        <v>66</v>
-      </c>
-      <c r="I4" s="2">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
-      <c r="B5">
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="8"/>
+      <c r="B17" s="9">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
-      <c r="B6">
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9">
         <v>5</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
-      <c r="B7">
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9">
         <v>10</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="B9">
-        <v>3</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-      <c r="B10">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-      <c r="B15">
-        <v>10</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17">
-        <v>3</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18">
-        <v>5</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="B19">
-        <v>10</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>15</v>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="3">
         <v>66</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="3">
         <v>66</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="3">
         <v>3</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="3">
         <v>3</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="3">
         <v>22</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
       <c r="B21">
         <v>3</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
       <c r="B22">
         <v>5</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
       <c r="B23">
         <v>10</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>16</v>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
       <c r="B25">
         <v>3</v>
       </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
       <c r="B26">
         <v>5</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="2"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
       <c r="B27">
         <v>10</v>
       </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
-        <v>17</v>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
       <c r="B29">
         <v>3</v>
       </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="2"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
       <c r="B30">
         <v>5</v>
       </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="2"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="3"/>
       <c r="B31">
         <v>10</v>
       </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
-        <v>18</v>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A33" s="2"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="3"/>
       <c r="B33">
         <v>3</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" s="2"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
       <c r="B34">
         <v>5</v>
       </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="2"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="3"/>
       <c r="B35">
         <v>10</v>
       </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="C4:C19"/>
+    <mergeCell ref="D4:D19"/>
+    <mergeCell ref="E4:E19"/>
+    <mergeCell ref="F4:F19"/>
+    <mergeCell ref="G4:G19"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A32:A35"/>
@@ -1056,36 +1864,26 @@
     <mergeCell ref="G20:G35"/>
     <mergeCell ref="H20:H35"/>
     <mergeCell ref="I20:I35"/>
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="C4:C19"/>
-    <mergeCell ref="D4:D19"/>
-    <mergeCell ref="E4:E19"/>
-    <mergeCell ref="F4:F19"/>
-    <mergeCell ref="G4:G19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1314,6 +2112,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58C277AC-42DD-4338-BD2A-AF7ECB0689E8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -1326,14 +2132,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/documents/ExperimentData.xlsx
+++ b/documents/ExperimentData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1b2bcfbbb34c0c/Documents/GitHub/meliso/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="403" documentId="8_{D7059BC8-D0E2-41E7-A566-DBD48656E1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E185A334-D7E8-418E-B917-3C8B74B4AEE2}"/>
+  <xr:revisionPtr revIDLastSave="562" documentId="8_{D7059BC8-D0E2-41E7-A566-DBD48656E1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60FDD0E8-883E-44EC-AD0B-A9187D86735E}"/>
   <bookViews>
     <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="25">
   <si>
     <t>MCA Rows</t>
   </si>
@@ -119,7 +119,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -239,16 +239,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -262,29 +256,34 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -301,6 +300,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -620,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB6579EC-3EC3-439D-9B94-319298E6C78E}">
-  <dimension ref="B1:R34"/>
+  <dimension ref="B1:AJ34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
@@ -629,562 +632,1098 @@
     <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B1" s="17" t="s">
+    <row r="1" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="K1" s="17" t="s">
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="K1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-    </row>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B2" s="8" t="s">
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="T1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AC1" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+    </row>
+    <row r="2" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8" t="s">
+      <c r="C2" s="14"/>
+      <c r="D2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="19" t="s">
+      <c r="E2" s="14"/>
+      <c r="F2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19" t="s">
+      <c r="G2" s="13"/>
+      <c r="H2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="19"/>
-      <c r="K2" s="8" t="s">
+      <c r="I2" s="13"/>
+      <c r="K2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8" t="s">
+      <c r="L2" s="14"/>
+      <c r="M2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="8"/>
-      <c r="O2" s="19" t="s">
+      <c r="N2" s="14"/>
+      <c r="O2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="19" t="s">
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="19"/>
-    </row>
-    <row r="3" spans="2:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
+      <c r="R2" s="13"/>
+      <c r="T2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="W2" s="14"/>
+      <c r="X2" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA2" s="13"/>
+      <c r="AC2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH2" s="13"/>
+      <c r="AI2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ2" s="13"/>
+    </row>
+    <row r="3" spans="2:36" ht="45" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="O3" s="18" t="s">
+      <c r="O3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="P3" s="18" t="s">
+      <c r="P3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="18" t="s">
+      <c r="Q3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="R3" s="18" t="s">
+      <c r="R3" s="12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B4" s="11">
+      <c r="T3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="X3" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG3" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AH3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI3" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AJ3" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B4" s="8">
         <v>24.443761142859401</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="8">
         <v>3.3744526857264301</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="9">
         <v>11.146140000613499</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="9">
         <v>1.68778800506088</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="8">
         <v>5.0263956831744903</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="8">
         <v>0.90170831675261998</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="9">
         <v>1.0386527872326301</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="9">
         <v>0.281035172507479</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="8">
         <v>50.189180557709498</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="8">
         <v>6.8272041826728298</v>
       </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B5" s="11">
+      <c r="M4" s="9">
+        <v>2.40398255283031</v>
+      </c>
+      <c r="N4" s="9">
+        <v>0.494699860082361</v>
+      </c>
+      <c r="O4" s="8">
+        <v>2.5208897211674199</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0.47344483768397699</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>1.34621453385329</v>
+      </c>
+      <c r="R4" s="9">
+        <v>0.35832775281353502</v>
+      </c>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
+      <c r="Z4" s="9"/>
+      <c r="AA4" s="9"/>
+      <c r="AC4" s="8"/>
+      <c r="AD4" s="8"/>
+      <c r="AE4" s="9">
+        <v>1.8250170991933701</v>
+      </c>
+      <c r="AF4" s="9">
+        <v>0.33633033357449799</v>
+      </c>
+      <c r="AG4" s="8">
+        <v>1.8523706039791701</v>
+      </c>
+      <c r="AH4" s="8">
+        <v>0.34156715764353801</v>
+      </c>
+      <c r="AI4" s="9">
+        <v>1.8795419666048101</v>
+      </c>
+      <c r="AJ4" s="9">
+        <v>0.34574964955663201</v>
+      </c>
+    </row>
+    <row r="5" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B5" s="8">
         <v>21.768763521560601</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="8">
         <v>3.1865062401780699</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="9">
         <v>10.978647285226099</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="9">
         <v>1.7065269254956801</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="8">
         <v>4.85409002254627</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="8">
         <v>0.80897913982258796</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="9">
         <v>0.89008783875792397</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="9">
         <v>0.27529653142885502</v>
       </c>
-      <c r="K5" s="11">
+      <c r="K5" s="8">
         <v>49.008992449178898</v>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="8">
         <v>6.5588284593994697</v>
       </c>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B6" s="11">
+      <c r="M5" s="9">
+        <v>1.6098328308093</v>
+      </c>
+      <c r="N5" s="9">
+        <v>0.35390275267126498</v>
+      </c>
+      <c r="O5" s="8">
+        <v>2.6847186811052599</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0.49866574556051502</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>2.7075638424040802</v>
+      </c>
+      <c r="R5" s="9">
+        <v>0.55112744515069301</v>
+      </c>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AC5" s="8"/>
+      <c r="AD5" s="8"/>
+      <c r="AE5" s="9">
+        <v>1.96093445188255</v>
+      </c>
+      <c r="AF5" s="9">
+        <v>0.35374707690719498</v>
+      </c>
+      <c r="AG5" s="8">
+        <v>1.9641721709049</v>
+      </c>
+      <c r="AH5" s="8">
+        <v>0.36261738420721501</v>
+      </c>
+      <c r="AI5" s="9">
+        <v>1.91781862598536</v>
+      </c>
+      <c r="AJ5" s="9">
+        <v>0.35301643444209602</v>
+      </c>
+    </row>
+    <row r="6" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B6" s="8">
         <v>24.272210690591301</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="8">
         <v>3.3054398403598002</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="9">
         <v>11.131989491819301</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="9">
         <v>1.68616441676978</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="8">
         <v>4.9373714864782201</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="8">
         <v>0.89188987256264995</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="9">
         <v>1.0114258900419599</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="9">
         <v>0.29627600535638898</v>
       </c>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B7" s="11">
+      <c r="K6" s="8">
+        <v>50.370043311847297</v>
+      </c>
+      <c r="L6" s="8">
+        <v>6.8266682265390397</v>
+      </c>
+      <c r="M6" s="9">
+        <v>3.31366070223083</v>
+      </c>
+      <c r="N6" s="9">
+        <v>0.59823315379531405</v>
+      </c>
+      <c r="O6" s="8">
+        <v>1.8698821640777401</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0.36723080126573698</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>2.4706305240653101</v>
+      </c>
+      <c r="R6" s="9">
+        <v>0.47413541013360899</v>
+      </c>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AC6" s="8"/>
+      <c r="AD6" s="8"/>
+      <c r="AE6" s="9">
+        <v>1.88217908842425</v>
+      </c>
+      <c r="AF6" s="9">
+        <v>0.35140505638671998</v>
+      </c>
+      <c r="AG6" s="8">
+        <v>1.8959378968298899</v>
+      </c>
+      <c r="AH6" s="8">
+        <v>0.34943432354470599</v>
+      </c>
+      <c r="AI6" s="9">
+        <v>1.96427586073906</v>
+      </c>
+      <c r="AJ6" s="9">
+        <v>0.35731335216903298</v>
+      </c>
+    </row>
+    <row r="7" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B7" s="8">
         <v>24.404174573572501</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="8">
         <v>3.3186837088307102</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="9">
         <v>10.9557705531107</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="9">
         <v>1.57213037578915</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="8">
         <v>4.7911793814388997</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="8">
         <v>0.81751166683242105</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="9">
         <v>0.95254623904054903</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="9">
         <v>0.26236662864990901</v>
       </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B8" s="11">
+      <c r="K7" s="8">
+        <v>48.5283966162228</v>
+      </c>
+      <c r="L7" s="8">
+        <v>6.39532451008645</v>
+      </c>
+      <c r="M7" s="9">
+        <v>2.3974738662768198</v>
+      </c>
+      <c r="N7" s="9">
+        <v>0.49437600947429899</v>
+      </c>
+      <c r="O7" s="8">
+        <v>2.8090651842160401</v>
+      </c>
+      <c r="P7" s="8">
+        <v>0.55561814716228497</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>1.9235703445824599</v>
+      </c>
+      <c r="R7" s="9">
+        <v>0.37579443485147102</v>
+      </c>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AC7" s="8"/>
+      <c r="AD7" s="8"/>
+      <c r="AE7" s="9">
+        <v>1.88221703832479</v>
+      </c>
+      <c r="AF7" s="9">
+        <v>0.35140505652889598</v>
+      </c>
+      <c r="AG7" s="8">
+        <v>1.8654391378277699</v>
+      </c>
+      <c r="AH7" s="8">
+        <v>0.35136993223547403</v>
+      </c>
+      <c r="AI7" s="9">
+        <v>1.9178899634194899</v>
+      </c>
+      <c r="AJ7" s="9">
+        <v>0.35300853576487501</v>
+      </c>
+    </row>
+    <row r="8" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B8" s="8">
         <v>24.519392747918499</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="8">
         <v>3.3765146340410901</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="9">
         <v>11.084394304570299</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="9">
         <v>1.71086338931697</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="8">
         <v>4.5716851890135404</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="8">
         <v>0.78488713802412502</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="9">
         <v>0.59342344244794798</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="9">
         <v>0.17203410846221501</v>
       </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="11">
+      <c r="K8" s="8">
+        <v>50.189180557709498</v>
+      </c>
+      <c r="L8" s="8">
+        <v>6.8272041826728298</v>
+      </c>
+      <c r="M8" s="9">
+        <v>2.3363436265518498</v>
+      </c>
+      <c r="N8" s="9">
+        <v>0.49525277741667301</v>
+      </c>
+      <c r="O8" s="8">
+        <v>3.2921811589554202</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0.61038119286221504</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>2.39747268966476</v>
+      </c>
+      <c r="R8" s="9">
+        <v>0.479906115601407</v>
+      </c>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AC8" s="8"/>
+      <c r="AD8" s="8"/>
+      <c r="AE8" s="9">
+        <v>1.8315258657560201</v>
+      </c>
+      <c r="AF8" s="9">
+        <v>0.34577767622515698</v>
+      </c>
+      <c r="AG8" s="8">
+        <v>1.8523461079911401</v>
+      </c>
+      <c r="AH8" s="8">
+        <v>0.34156715758035</v>
+      </c>
+      <c r="AI8" s="9">
+        <v>1.94458113911453</v>
+      </c>
+      <c r="AJ8" s="9">
+        <v>0.36071379860479102</v>
+      </c>
+    </row>
+    <row r="9" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B9" s="8">
         <v>24.310600989632899</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="8">
         <v>3.3225698262557399</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="9">
         <v>11.078199731004901</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="9">
         <v>1.65069524058359</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="8">
         <v>4.9807010405869097</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="8">
         <v>0.92921451381373998</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="9">
         <v>0.56505155768495896</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="9">
         <v>0.16474922791581201</v>
       </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="11">
+      <c r="K9" s="8">
+        <v>49.619431099961197</v>
+      </c>
+      <c r="L9" s="8">
+        <v>6.6224281863214802</v>
+      </c>
+      <c r="M9" s="9">
+        <v>2.06027858560702</v>
+      </c>
+      <c r="N9" s="9">
+        <v>0.41902119187009701</v>
+      </c>
+      <c r="O9" s="8">
+        <v>2.1176598714663699</v>
+      </c>
+      <c r="P9" s="8">
+        <v>0.420783326797598</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>1.05066650115089</v>
+      </c>
+      <c r="R9" s="9">
+        <v>0.25434177251207701</v>
+      </c>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9"/>
+      <c r="AC9" s="8"/>
+      <c r="AD9" s="8"/>
+      <c r="AE9" s="9">
+        <v>1.86147110489288</v>
+      </c>
+      <c r="AF9" s="9">
+        <v>0.34558367107705801</v>
+      </c>
+      <c r="AG9" s="8">
+        <v>1.96362562254665</v>
+      </c>
+      <c r="AH9" s="8">
+        <v>0.36222639562867198</v>
+      </c>
+      <c r="AI9" s="9">
+        <v>1.9642715242957101</v>
+      </c>
+      <c r="AJ9" s="9">
+        <v>0.35731730151554097</v>
+      </c>
+    </row>
+    <row r="10" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B10" s="8">
         <v>24.519392747918499</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="8">
         <v>3.3765146340410901</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="9">
         <v>11.3283064247616</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="9">
         <v>1.75667635216019</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="8">
         <v>4.3655684894788598</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="8">
         <v>0.72256847111010403</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="9">
         <v>0.89008783875792397</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="9">
         <v>0.27529653142885502</v>
       </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="11">
+      <c r="K10" s="8">
+        <v>50.370043311847297</v>
+      </c>
+      <c r="L10" s="8">
+        <v>6.8266682265390397</v>
+      </c>
+      <c r="M10" s="9">
+        <v>1.1013427759766601</v>
+      </c>
+      <c r="N10" s="9">
+        <v>0.279195398098668</v>
+      </c>
+      <c r="O10" s="8">
+        <v>1.8886807440369899</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0.41993899419076303</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>1.08014977882427</v>
+      </c>
+      <c r="R10" s="9">
+        <v>0.28419236315363</v>
+      </c>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="9"/>
+      <c r="AC10" s="8"/>
+      <c r="AD10" s="8"/>
+      <c r="AE10" s="9">
+        <v>1.86657481807766</v>
+      </c>
+      <c r="AF10" s="9">
+        <v>0.34383410086548399</v>
+      </c>
+      <c r="AG10" s="8">
+        <v>1.90028400803589</v>
+      </c>
+      <c r="AH10" s="8">
+        <v>0.34945012130988901</v>
+      </c>
+      <c r="AI10" s="9">
+        <v>1.90928027610508</v>
+      </c>
+      <c r="AJ10" s="9">
+        <v>0.34945018620593998</v>
+      </c>
+    </row>
+    <row r="11" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B11" s="8">
         <v>21.996905724856099</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="8">
         <v>2.9856415262303599</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="9">
         <v>11.0671269081706</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="9">
         <v>1.68567829653259</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="8">
         <v>4.9579210625189001</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="8">
         <v>0.89091012676741499</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="9">
         <v>0.95254623904054903</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="9">
         <v>0.26236662864990901</v>
       </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="11">
+      <c r="K11" s="8">
+        <v>50.6021835670551</v>
+      </c>
+      <c r="L11" s="8">
+        <v>6.8159615936773701</v>
+      </c>
+      <c r="M11" s="9">
+        <v>2.4294044850569798</v>
+      </c>
+      <c r="N11" s="9">
+        <v>0.491532450674801</v>
+      </c>
+      <c r="O11" s="8">
+        <v>2.4929016378617299</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0.47851192255269298</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>2.3570848611973498</v>
+      </c>
+      <c r="R11" s="9">
+        <v>0.47000785524292399</v>
+      </c>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="8"/>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="9"/>
+      <c r="AC11" s="8"/>
+      <c r="AD11" s="8"/>
+      <c r="AE11" s="9">
+        <v>1.81268296370352</v>
+      </c>
+      <c r="AF11" s="9">
+        <v>0.33337223640394198</v>
+      </c>
+      <c r="AG11" s="8">
+        <v>1.96429126731902</v>
+      </c>
+      <c r="AH11" s="8">
+        <v>0.35731730156293201</v>
+      </c>
+      <c r="AI11" s="9">
+        <v>1.8795069801762501</v>
+      </c>
+      <c r="AJ11" s="9">
+        <v>0.34575359895052998</v>
+      </c>
+    </row>
+    <row r="12" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B12" s="8">
         <v>24.073944136969398</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="8">
         <v>3.2906045777064898</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="9">
         <v>10.871081688695201</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="9">
         <v>1.5456538017913899</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="8">
         <v>4.5042629003538499</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="8">
         <v>0.75565867825603805</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="9">
         <v>0.98179762818361005</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="9">
         <v>0.28993726071696102</v>
       </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="11">
+      <c r="K12" s="8">
+        <v>48.5283966162228</v>
+      </c>
+      <c r="L12" s="8">
+        <v>6.39532451008645</v>
+      </c>
+      <c r="M12" s="9">
+        <v>2.8583793701106899</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0.57377303940268798</v>
+      </c>
+      <c r="O12" s="8">
+        <v>2.2571410688804598</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0.46259787093209498</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>2.4566723216903199</v>
+      </c>
+      <c r="R12" s="9">
+        <v>0.46852708080793398</v>
+      </c>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AC12" s="8"/>
+      <c r="AD12" s="8"/>
+      <c r="AE12" s="9">
+        <v>1.8125561645361601</v>
+      </c>
+      <c r="AF12" s="9">
+        <v>0.33334854013531301</v>
+      </c>
+      <c r="AG12" s="8">
+        <v>1.96488011670068</v>
+      </c>
+      <c r="AH12" s="8">
+        <v>0.36261343482516201</v>
+      </c>
+      <c r="AI12" s="9">
+        <v>1.9178899634194899</v>
+      </c>
+      <c r="AJ12" s="9">
+        <v>0.35300853576487501</v>
+      </c>
+    </row>
+    <row r="13" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B13" s="8">
         <v>24.073944136969398</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="8">
         <v>3.2906045777064898</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="9">
         <v>11.065870149418</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="9">
         <v>1.7106619694696501</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="8">
         <v>4.4913411407632298</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="8">
         <v>0.764781871349272</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="9">
         <v>0.61764700512757498</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="9">
         <v>0.17697658502358601</v>
       </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="J15" t="s">
-        <v>16</v>
-      </c>
-      <c r="K15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
+      <c r="K13" s="8">
+        <v>50.813193764563998</v>
+      </c>
+      <c r="L13" s="8">
+        <v>6.8053931798874796</v>
+      </c>
+      <c r="M13" s="9">
+        <v>2.07438188382043</v>
+      </c>
+      <c r="N13" s="9">
+        <v>0.43125921121579203</v>
+      </c>
+      <c r="O13" s="8">
+        <v>2.5100936022216298</v>
+      </c>
+      <c r="P13" s="8">
+        <v>2.5100936022216298</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>2.6805114554649099</v>
+      </c>
+      <c r="R13" s="9">
+        <v>0.50105033491431605</v>
+      </c>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="9"/>
+      <c r="AC13" s="8"/>
+      <c r="AD13" s="8"/>
+      <c r="AE13" s="9">
+        <v>1.8250318583902301</v>
+      </c>
+      <c r="AF13" s="9">
+        <v>0.33629873874712601</v>
+      </c>
+      <c r="AG13" s="8">
+        <v>1.9040866582123299</v>
+      </c>
+      <c r="AH13" s="8">
+        <v>0.35445006159312697</v>
+      </c>
+      <c r="AI13" s="9">
+        <v>1.96429126731902</v>
+      </c>
+      <c r="AJ13" s="9">
+        <v>0.35731730156293201</v>
+      </c>
+    </row>
+    <row r="14" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+    </row>
+    <row r="15" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+    </row>
+    <row r="16" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="20">
+    <mergeCell ref="AC1:AJ1"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="AG2:AH2"/>
+    <mergeCell ref="AI2:AJ2"/>
+    <mergeCell ref="T1:AA1"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="K1:R1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="B1:I1"/>
-    <mergeCell ref="K1:R1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1211,646 +1750,658 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
-      <c r="Z1" s="4"/>
-      <c r="AA1" s="4"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
     </row>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:27" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="10">
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="14">
         <v>66</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="14">
         <v>66</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="14">
         <v>1</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="14">
         <v>1</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="14">
         <v>66</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="14">
         <v>66</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="9">
         <f>AVERAGE(DataExp1!B4:B13)</f>
         <v>23.838309041284862</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="9">
         <f>AVERAGE(DataExp1!C4:C13)</f>
         <v>3.2827532251076272</v>
       </c>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="13">
+      <c r="A5" s="17"/>
+      <c r="B5" s="10">
         <v>3</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="12">
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="9">
         <f>AVERAGE(DataExp1!D4:D13)</f>
         <v>11.070752653739017</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="9">
         <f>AVERAGE(DataExp1!E4:E13)</f>
         <v>1.6712838772969871</v>
       </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
-      <c r="B6" s="13">
+      <c r="A6" s="17"/>
+      <c r="B6" s="10">
         <v>5</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="12">
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="9">
         <f>AVERAGE(DataExp1!F4:F13)</f>
         <v>4.7480516396353174</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="9">
         <f>AVERAGE(DataExp1!G4:G13)</f>
         <v>0.82681097952909732</v>
       </c>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="13">
+      <c r="A7" s="17"/>
+      <c r="B7" s="10">
         <v>10</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="12">
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="9">
         <f>AVERAGE(DataExp1!H4:H13)</f>
         <v>0.84932664663156276</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="9">
         <f>AVERAGE(DataExp1!I4:I13)</f>
         <v>0.24563346801399702</v>
       </c>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="6">
         <v>1</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="15">
-        <v>2.45597546770956</v>
-      </c>
-      <c r="K8" s="15">
-        <v>0.47959805829178598</v>
-      </c>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="8">
+        <f>AVERAGE(DataExp1!K4:K13)</f>
+        <v>49.821904185231844</v>
+      </c>
+      <c r="K8" s="8">
+        <f>AVERAGE(DataExp1!L4:L13)</f>
+        <v>6.6901005257882433</v>
+      </c>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9">
+      <c r="A9" s="14"/>
+      <c r="B9" s="6">
         <v>3</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="8">
+        <f>AVERAGE(DataExp1!M4:M13)</f>
+        <v>2.2585080679270888</v>
+      </c>
+      <c r="K9" s="8">
+        <f>AVERAGE(DataExp1!N4:N13)</f>
+        <v>0.46312458447019578</v>
+      </c>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9">
+      <c r="A10" s="14"/>
+      <c r="B10" s="6">
         <v>5</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="8">
+        <f>AVERAGE(DataExp1!O4:O13)</f>
+        <v>2.4443213833989064</v>
+      </c>
+      <c r="K10" s="8">
+        <f>AVERAGE(DataExp1!P4:P13)</f>
+        <v>0.67972664412295081</v>
+      </c>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9">
+      <c r="A11" s="14"/>
+      <c r="B11" s="6">
         <v>10</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="8">
+        <f>AVERAGE(DataExp1!Q4:Q13)</f>
+        <v>2.0470536852897636</v>
+      </c>
+      <c r="K11" s="8">
+        <f>AVERAGE(DataExp1!R4:R13)</f>
+        <v>0.42174105651815957</v>
+      </c>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="10">
         <v>1</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="12">
-        <v>2.0124832402399999</v>
-      </c>
-      <c r="K12" s="12">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
-      <c r="B13" s="13">
+      <c r="A13" s="17"/>
+      <c r="B13" s="10">
         <v>3</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="13">
+      <c r="A14" s="17"/>
+      <c r="B14" s="10">
         <v>5</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
-      <c r="B15" s="13">
+      <c r="A15" s="17"/>
+      <c r="B15" s="10">
         <v>10</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="6">
         <v>1</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9">
+      <c r="A17" s="14"/>
+      <c r="B17" s="6">
         <v>3</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9">
+      <c r="A18" s="14"/>
+      <c r="B18" s="6">
         <v>5</v>
       </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9">
+      <c r="A19" s="14"/>
+      <c r="B19" s="6">
         <v>10</v>
       </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="8">
+        <f>AVERAGE(DataExp1!AI4:AI13)</f>
+        <v>1.9259347567178799</v>
+      </c>
+      <c r="K19" s="8">
+        <f>AVERAGE(DataExp1!AJ4:AJ13)</f>
+        <v>0.35326486945372448</v>
+      </c>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="18" t="s">
         <v>14</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="18">
         <v>66</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="18">
         <v>66</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="18">
         <v>3</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="18">
         <v>3</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="18">
         <v>22</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="18">
         <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
+      <c r="A21" s="18"/>
       <c r="B21">
         <v>3</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
+      <c r="A22" s="18"/>
       <c r="B22">
         <v>5</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
+      <c r="A23" s="18"/>
       <c r="B23">
         <v>10</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="18" t="s">
         <v>15</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
+      <c r="A25" s="18"/>
       <c r="B25">
         <v>3</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
+      <c r="A26" s="18"/>
       <c r="B26">
         <v>5</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
+      <c r="A27" s="18"/>
       <c r="B27">
         <v>10</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="18" t="s">
         <v>16</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
+      <c r="A29" s="18"/>
       <c r="B29">
         <v>3</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="3"/>
+      <c r="A30" s="18"/>
       <c r="B30">
         <v>5</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="3"/>
+      <c r="A31" s="18"/>
       <c r="B31">
         <v>10</v>
       </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="3"/>
+      <c r="A33" s="18"/>
       <c r="B33">
         <v>3</v>
       </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="3"/>
+      <c r="A34" s="18"/>
       <c r="B34">
         <v>5</v>
       </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
+      <c r="A35" s="18"/>
       <c r="B35">
         <v>10</v>
       </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="C4:C19"/>
-    <mergeCell ref="D4:D19"/>
-    <mergeCell ref="E4:E19"/>
-    <mergeCell ref="F4:F19"/>
-    <mergeCell ref="G4:G19"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A32:A35"/>
@@ -1864,29 +2415,22 @@
     <mergeCell ref="G20:G35"/>
     <mergeCell ref="H20:H35"/>
     <mergeCell ref="I20:I35"/>
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="C4:C19"/>
+    <mergeCell ref="D4:D19"/>
+    <mergeCell ref="E4:E19"/>
+    <mergeCell ref="F4:F19"/>
+    <mergeCell ref="G4:G19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A16C87A6682E6E4295773DFF29EAB41B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a3213889016ec1ec7c5b45183b07d2a5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xmlns:ns4="c7f849e2-0a63-4d53-be53-fb9d39becd19" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39cf848dedf08b05fa72a945c282372c" ns3:_="" ns4:_="">
     <xsd:import namespace="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
@@ -2111,10 +2655,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
+    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2137,20 +2709,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
-    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/documents/ExperimentData.xlsx
+++ b/documents/ExperimentData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1b2bcfbbb34c0c/Documents/GitHub/meliso/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="562" documentId="8_{D7059BC8-D0E2-41E7-A566-DBD48656E1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60FDD0E8-883E-44EC-AD0B-A9187D86735E}"/>
+  <xr:revisionPtr revIDLastSave="672" documentId="8_{D7059BC8-D0E2-41E7-A566-DBD48656E1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E31E596D-74E4-4418-9A58-7D1D2B4DBBCB}"/>
   <bookViews>
     <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
   </bookViews>
@@ -137,7 +137,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -150,8 +150,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -235,11 +241,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -267,14 +286,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -282,7 +304,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -633,46 +657,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="K1" s="15" t="s">
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="K1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="T1" s="15" t="s">
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="T1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
-      <c r="AC1" s="15" t="s">
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AC1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="AD1" s="15"/>
-      <c r="AE1" s="15"/>
-      <c r="AF1" s="15"/>
-      <c r="AG1" s="15"/>
-      <c r="AH1" s="15"/>
-      <c r="AI1" s="15"/>
-      <c r="AJ1" s="15"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="13"/>
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
     </row>
     <row r="2" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
@@ -683,14 +707,14 @@
         <v>23</v>
       </c>
       <c r="E2" s="14"/>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13" t="s">
+      <c r="G2" s="15"/>
+      <c r="H2" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="13"/>
+      <c r="I2" s="15"/>
       <c r="K2" s="14" t="s">
         <v>21</v>
       </c>
@@ -699,14 +723,14 @@
         <v>23</v>
       </c>
       <c r="N2" s="14"/>
-      <c r="O2" s="13" t="s">
+      <c r="O2" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13" t="s">
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="13"/>
+      <c r="R2" s="15"/>
       <c r="T2" s="14" t="s">
         <v>21</v>
       </c>
@@ -715,14 +739,14 @@
         <v>23</v>
       </c>
       <c r="W2" s="14"/>
-      <c r="X2" s="13" t="s">
+      <c r="X2" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="13" t="s">
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="AA2" s="13"/>
+      <c r="AA2" s="15"/>
       <c r="AC2" s="14" t="s">
         <v>21</v>
       </c>
@@ -731,14 +755,14 @@
         <v>23</v>
       </c>
       <c r="AF2" s="14"/>
-      <c r="AG2" s="13" t="s">
+      <c r="AG2" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="AH2" s="13"/>
-      <c r="AI2" s="13" t="s">
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="AJ2" s="13"/>
+      <c r="AJ2" s="15"/>
     </row>
     <row r="3" spans="2:36" ht="45" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -887,16 +911,36 @@
       <c r="R4" s="9">
         <v>0.35832775281353502</v>
       </c>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="9"/>
-      <c r="AA4" s="9"/>
-      <c r="AC4" s="8"/>
-      <c r="AD4" s="8"/>
+      <c r="T4" s="8">
+        <v>2.0282019718480502</v>
+      </c>
+      <c r="U4" s="8">
+        <v>0.37754673426285001</v>
+      </c>
+      <c r="V4" s="9">
+        <v>2.93314349751103</v>
+      </c>
+      <c r="W4" s="9">
+        <v>0.65213375302212495</v>
+      </c>
+      <c r="X4" s="8">
+        <v>3.1835707328913601</v>
+      </c>
+      <c r="Y4" s="8">
+        <v>0.65565129784223597</v>
+      </c>
+      <c r="Z4" s="9">
+        <v>3.0446059739842699</v>
+      </c>
+      <c r="AA4" s="9">
+        <v>0.65226013362701096</v>
+      </c>
+      <c r="AC4" s="8">
+        <v>34.570056762068198</v>
+      </c>
+      <c r="AD4" s="8">
+        <v>4.5778664577056496</v>
+      </c>
       <c r="AE4" s="9">
         <v>1.8250170991933701</v>
       </c>
@@ -965,16 +1009,36 @@
       <c r="R5" s="9">
         <v>0.55112744515069301</v>
       </c>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="8"/>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="9"/>
-      <c r="AC5" s="8"/>
-      <c r="AD5" s="8"/>
+      <c r="T5" s="8">
+        <v>2.0576101229880499</v>
+      </c>
+      <c r="U5" s="8">
+        <v>0.37754673426285001</v>
+      </c>
+      <c r="V5" s="9">
+        <v>3.0231717517272201</v>
+      </c>
+      <c r="W5" s="9">
+        <v>0.65213375302212495</v>
+      </c>
+      <c r="X5" s="8">
+        <v>3.0014742636059601</v>
+      </c>
+      <c r="Y5" s="8">
+        <v>0.65213375302212495</v>
+      </c>
+      <c r="Z5" s="9">
+        <v>3.0732721507638598</v>
+      </c>
+      <c r="AA5" s="9">
+        <v>0.65213375302212495</v>
+      </c>
+      <c r="AC5" s="8">
+        <v>34.554127832915199</v>
+      </c>
+      <c r="AD5" s="8">
+        <v>4.5660618080018196</v>
+      </c>
       <c r="AE5" s="9">
         <v>1.96093445188255</v>
       </c>
@@ -1043,16 +1107,36 @@
       <c r="R6" s="9">
         <v>0.47413541013360899</v>
       </c>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
+      <c r="T6" s="8">
+        <v>2.0124832402399999</v>
+      </c>
+      <c r="U6" s="8">
+        <v>0.37754673426285001</v>
+      </c>
+      <c r="V6" s="9">
+        <v>3.1835707328913601</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0.65565129784223597</v>
+      </c>
+      <c r="X6" s="8">
+        <v>3.0052609093097602</v>
+      </c>
+      <c r="Y6" s="8">
+        <v>0.65213375302212495</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>2.9332438502332301</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.65213375302212495</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>34.586395368105499</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>4.5775860505016004</v>
+      </c>
       <c r="AE6" s="9">
         <v>1.88217908842425</v>
       </c>
@@ -1121,16 +1205,32 @@
       <c r="R7" s="9">
         <v>0.37579443485147102</v>
       </c>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
+      <c r="T7" s="8">
+        <v>1.98733133553576</v>
+      </c>
+      <c r="U7" s="8">
+        <v>0.37754673426285001</v>
+      </c>
+      <c r="V7" s="9">
+        <v>2.9709094694099698</v>
+      </c>
+      <c r="W7" s="9">
+        <v>0.65213375302212495</v>
+      </c>
+      <c r="X7" s="8">
+        <v>3.1234714223794802</v>
+      </c>
+      <c r="Y7" s="8">
+        <v>0.65226013362701096</v>
+      </c>
       <c r="Z7" s="9"/>
       <c r="AA7" s="9"/>
-      <c r="AC7" s="8"/>
-      <c r="AD7" s="8"/>
+      <c r="AC7" s="8">
+        <v>34.474323231873001</v>
+      </c>
+      <c r="AD7" s="8">
+        <v>4.5812551646225703</v>
+      </c>
       <c r="AE7" s="9">
         <v>1.88221703832479</v>
       </c>
@@ -1199,16 +1299,32 @@
       <c r="R8" s="9">
         <v>0.479906115601407</v>
       </c>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
+      <c r="T8" s="8">
+        <v>2.0045866890630801</v>
+      </c>
+      <c r="U8" s="8">
+        <v>0.37754673426285001</v>
+      </c>
+      <c r="V8" s="9">
+        <v>2.8887491003138202</v>
+      </c>
+      <c r="W8" s="9">
+        <v>0.65213375302212495</v>
+      </c>
+      <c r="X8" s="8">
+        <v>3.1300087680066402</v>
+      </c>
+      <c r="Y8" s="8">
+        <v>0.65226013362701096</v>
+      </c>
       <c r="Z8" s="9"/>
       <c r="AA8" s="9"/>
-      <c r="AC8" s="8"/>
-      <c r="AD8" s="8"/>
+      <c r="AC8" s="8">
+        <v>34.482423779545499</v>
+      </c>
+      <c r="AD8" s="8">
+        <v>4.5801967278307698</v>
+      </c>
       <c r="AE8" s="9">
         <v>1.8315258657560201</v>
       </c>
@@ -1277,16 +1393,32 @@
       <c r="R9" s="9">
         <v>0.25434177251207701</v>
       </c>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
+      <c r="T9" s="8">
+        <v>2.03035231561176</v>
+      </c>
+      <c r="U9" s="8">
+        <v>0.37754673426285001</v>
+      </c>
+      <c r="V9" s="9">
+        <v>3.0233946110574101</v>
+      </c>
+      <c r="W9" s="9">
+        <v>0.65226013362701096</v>
+      </c>
+      <c r="X9" s="8">
+        <v>3.0222659675151302</v>
+      </c>
+      <c r="Y9" s="8">
+        <v>0.65226013362701096</v>
+      </c>
       <c r="Z9" s="9"/>
       <c r="AA9" s="9"/>
-      <c r="AC9" s="8"/>
-      <c r="AD9" s="8"/>
+      <c r="AC9" s="8">
+        <v>34.570056762068198</v>
+      </c>
+      <c r="AD9" s="8">
+        <v>4.5778664577056496</v>
+      </c>
       <c r="AE9" s="9">
         <v>1.86147110489288</v>
       </c>
@@ -1355,16 +1487,32 @@
       <c r="R10" s="9">
         <v>0.28419236315363</v>
       </c>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
+      <c r="T10" s="8">
+        <v>2.0282019718480502</v>
+      </c>
+      <c r="U10" s="8">
+        <v>0.37754673426285001</v>
+      </c>
+      <c r="V10" s="9">
+        <v>3.0233946110574101</v>
+      </c>
+      <c r="W10" s="9">
+        <v>0.65226013362701096</v>
+      </c>
+      <c r="X10" s="8">
+        <v>3.0769912027266599</v>
+      </c>
+      <c r="Y10" s="8">
+        <v>0.65226013362701096</v>
+      </c>
       <c r="Z10" s="9"/>
       <c r="AA10" s="9"/>
-      <c r="AC10" s="8"/>
-      <c r="AD10" s="8"/>
+      <c r="AC10" s="8">
+        <v>34.498810594745102</v>
+      </c>
+      <c r="AD10" s="8">
+        <v>4.5805798233599297</v>
+      </c>
       <c r="AE10" s="9">
         <v>1.86657481807766</v>
       </c>
@@ -1433,16 +1581,32 @@
       <c r="R11" s="9">
         <v>0.47000785524292399</v>
       </c>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="8"/>
+      <c r="T11" s="8">
+        <v>2.0045866890630801</v>
+      </c>
+      <c r="U11" s="8">
+        <v>0.37754673426285001</v>
+      </c>
+      <c r="V11" s="9">
+        <v>3.1856421504299002</v>
+      </c>
+      <c r="W11" s="9">
+        <v>0.65565129784223597</v>
+      </c>
+      <c r="X11" s="8">
+        <v>3.1856421504299002</v>
+      </c>
+      <c r="Y11" s="8">
+        <v>0.65565129784223597</v>
+      </c>
       <c r="Z11" s="9"/>
       <c r="AA11" s="9"/>
-      <c r="AC11" s="8"/>
-      <c r="AD11" s="8"/>
+      <c r="AC11" s="8">
+        <v>34.554127832915199</v>
+      </c>
+      <c r="AD11" s="8">
+        <v>4.5660618080018196</v>
+      </c>
       <c r="AE11" s="9">
         <v>1.81268296370352</v>
       </c>
@@ -1511,16 +1675,32 @@
       <c r="R12" s="9">
         <v>0.46852708080793398</v>
       </c>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="8"/>
+      <c r="T12" s="8">
+        <v>2.0124832402399999</v>
+      </c>
+      <c r="U12" s="8">
+        <v>0.37754673426285001</v>
+      </c>
+      <c r="V12" s="9">
+        <v>2.9469306504008701</v>
+      </c>
+      <c r="W12" s="9">
+        <v>0.65213375302212495</v>
+      </c>
+      <c r="X12" s="8">
+        <v>3.1524446068305201</v>
+      </c>
+      <c r="Y12" s="8">
+        <v>0.65226013362701096</v>
+      </c>
       <c r="Z12" s="9"/>
       <c r="AA12" s="9"/>
-      <c r="AC12" s="8"/>
-      <c r="AD12" s="8"/>
+      <c r="AC12" s="8">
+        <v>34.6014705772876</v>
+      </c>
+      <c r="AD12" s="8">
+        <v>4.5785181060921998</v>
+      </c>
       <c r="AE12" s="9">
         <v>1.8125561645361601</v>
       </c>
@@ -1589,16 +1769,32 @@
       <c r="R13" s="9">
         <v>0.50105033491431605</v>
       </c>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="8"/>
+      <c r="T13" s="8">
+        <v>2.0282019718480502</v>
+      </c>
+      <c r="U13" s="8">
+        <v>0.37754673426285001</v>
+      </c>
+      <c r="V13" s="9">
+        <v>3.1450098960334101</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0.65226013362701096</v>
+      </c>
+      <c r="X13" s="8">
+        <v>3.0895272691364801</v>
+      </c>
+      <c r="Y13" s="8">
+        <v>0.65226013362701096</v>
+      </c>
       <c r="Z13" s="9"/>
       <c r="AA13" s="9"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
+      <c r="AC13" s="8">
+        <v>34.63132536506</v>
+      </c>
+      <c r="AD13" s="8">
+        <v>4.5643280255556196</v>
+      </c>
       <c r="AE13" s="9">
         <v>1.8250318583902301</v>
       </c>
@@ -1704,26 +1900,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="K1:R1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="T1:AA1"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
     <mergeCell ref="AC1:AJ1"/>
     <mergeCell ref="AC2:AD2"/>
     <mergeCell ref="AE2:AF2"/>
     <mergeCell ref="AG2:AH2"/>
     <mergeCell ref="AI2:AJ2"/>
-    <mergeCell ref="T1:AA1"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="K1:R1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1750,35 +1946,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16"/>
-      <c r="AA1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
+      <c r="X1" s="17"/>
+      <c r="Y1" s="17"/>
+      <c r="Z1" s="17"/>
+      <c r="AA1" s="17"/>
     </row>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:27" ht="45" x14ac:dyDescent="0.25">
@@ -1823,7 +2019,7 @@
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="10">
@@ -1862,7 +2058,7 @@
       <c r="M4" s="10"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="10">
         <v>3</v>
       </c>
@@ -1885,7 +2081,7 @@
       <c r="M5" s="10"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
+      <c r="A6" s="18"/>
       <c r="B6" s="10">
         <v>5</v>
       </c>
@@ -1908,7 +2104,7 @@
       <c r="M6" s="10"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
+      <c r="A7" s="18"/>
       <c r="B7" s="10">
         <v>10</v>
       </c>
@@ -2025,7 +2221,7 @@
       <c r="M11" s="6"/>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="10">
@@ -2038,13 +2234,19 @@
       <c r="G12" s="14"/>
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
+      <c r="J12" s="9">
+        <f>AVERAGE(DataExp1!T4:T13)</f>
+        <v>2.0194039548285878</v>
+      </c>
+      <c r="K12" s="9">
+        <f>AVERAGE(DataExp1!U4:U13)</f>
+        <v>0.37754673426285007</v>
+      </c>
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="10">
         <v>3</v>
       </c>
@@ -2055,13 +2257,19 @@
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
+      <c r="J13" s="9">
+        <f>AVERAGE(DataExp1!V4:V13)</f>
+        <v>3.0323916470832399</v>
+      </c>
+      <c r="K13" s="9">
+        <f>AVERAGE(DataExp1!W4:W13)</f>
+        <v>0.65287517616761293</v>
+      </c>
       <c r="L13" s="10"/>
       <c r="M13" s="10"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="10">
         <v>5</v>
       </c>
@@ -2072,13 +2280,19 @@
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
+      <c r="J14" s="9">
+        <f>AVERAGE(DataExp1!X4:X13)</f>
+        <v>3.0970657292831891</v>
+      </c>
+      <c r="K14" s="9">
+        <f>AVERAGE(DataExp1!Y4:Y13)</f>
+        <v>0.65291309034907874</v>
+      </c>
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
+      <c r="A15" s="18"/>
       <c r="B15" s="10">
         <v>10</v>
       </c>
@@ -2108,8 +2322,14 @@
       <c r="G16" s="14"/>
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
+      <c r="J16" s="8">
+        <f>AVERAGE(DataExp1!AC4:AC13)</f>
+        <v>34.552311810658352</v>
+      </c>
+      <c r="K16" s="8">
+        <f>AVERAGE(DataExp1!AD4:AD13)</f>
+        <v>4.575032042937762</v>
+      </c>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
     </row>
@@ -2125,8 +2345,14 @@
       <c r="G17" s="14"/>
       <c r="H17" s="14"/>
       <c r="I17" s="14"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
+      <c r="J17" s="8">
+        <f>AVERAGE(DataExp1!AE4:AE14)</f>
+        <v>1.8560190453181431</v>
+      </c>
+      <c r="K17" s="8">
+        <f>AVERAGE(DataExp1!AF5:AF14)</f>
+        <v>0.34386357258632122</v>
+      </c>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
     </row>
@@ -2142,8 +2368,14 @@
       <c r="G18" s="14"/>
       <c r="H18" s="14"/>
       <c r="I18" s="14"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
+      <c r="J18" s="8">
+        <f>AVERAGE(DataExp1!AG4:AG13)</f>
+        <v>1.9127433590347436</v>
+      </c>
+      <c r="K18" s="8">
+        <f>AVERAGE(DataExp1!AH5:AH6)</f>
+        <v>0.35602585387596053</v>
+      </c>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
     </row>
@@ -2171,237 +2403,311 @@
       <c r="M19" s="6"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="6">
         <v>1</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="14">
         <v>66</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="14">
         <v>66</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="14">
         <v>3</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="14">
         <v>3</v>
       </c>
-      <c r="H20" s="18">
+      <c r="H20" s="14">
         <v>22</v>
       </c>
-      <c r="I20" s="18">
+      <c r="I20" s="14">
         <v>22</v>
       </c>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
-      <c r="B21">
+      <c r="A21" s="16"/>
+      <c r="B21" s="6">
         <v>3</v>
       </c>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
-      <c r="B22">
+      <c r="A22" s="16"/>
+      <c r="B22" s="6">
         <v>5</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
-      <c r="B23">
+      <c r="A23" s="16"/>
+      <c r="B23" s="6">
         <v>10</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="19">
         <v>1</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="18"/>
-      <c r="B25">
+      <c r="A25" s="21"/>
+      <c r="B25" s="19">
         <v>3</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="18"/>
-      <c r="B26">
+      <c r="A26" s="21"/>
+      <c r="B26" s="19">
         <v>5</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="18"/>
-      <c r="B27">
+      <c r="A27" s="21"/>
+      <c r="B27" s="19">
         <v>10</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="6">
         <v>1</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="18"/>
-      <c r="B29">
+      <c r="A29" s="16"/>
+      <c r="B29" s="6">
         <v>3</v>
       </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="18"/>
-      <c r="B30">
+      <c r="A30" s="16"/>
+      <c r="B30" s="6">
         <v>5</v>
       </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
-      <c r="B31">
+      <c r="A31" s="16"/>
+      <c r="B31" s="20">
         <v>10</v>
       </c>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="19">
         <v>1</v>
       </c>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
-      <c r="B33">
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="19"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="21"/>
+      <c r="B33" s="19">
         <v>3</v>
       </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
-      <c r="B34">
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="21"/>
+      <c r="B34" s="19">
         <v>5</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="18"/>
-      <c r="B35">
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="21"/>
+      <c r="B35" s="19">
         <v>10</v>
       </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="18"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="C4:C19"/>
+    <mergeCell ref="D4:D19"/>
+    <mergeCell ref="E4:E19"/>
+    <mergeCell ref="F4:F19"/>
+    <mergeCell ref="G4:G19"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A32:A35"/>
@@ -2415,22 +2721,29 @@
     <mergeCell ref="G20:G35"/>
     <mergeCell ref="H20:H35"/>
     <mergeCell ref="I20:I35"/>
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="C4:C19"/>
-    <mergeCell ref="D4:D19"/>
-    <mergeCell ref="E4:E19"/>
-    <mergeCell ref="F4:F19"/>
-    <mergeCell ref="G4:G19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A16C87A6682E6E4295773DFF29EAB41B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a3213889016ec1ec7c5b45183b07d2a5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xmlns:ns4="c7f849e2-0a63-4d53-be53-fb9d39becd19" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39cf848dedf08b05fa72a945c282372c" ns3:_="" ns4:_="">
     <xsd:import namespace="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
@@ -2655,38 +2968,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
-    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2709,9 +2994,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
+    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/documents/ExperimentData.xlsx
+++ b/documents/ExperimentData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1b2bcfbbb34c0c/Documents/GitHub/meliso/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="672" documentId="8_{D7059BC8-D0E2-41E7-A566-DBD48656E1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E31E596D-74E4-4418-9A58-7D1D2B4DBBCB}"/>
+  <xr:revisionPtr revIDLastSave="738" documentId="8_{D7059BC8-D0E2-41E7-A566-DBD48656E1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D523FF4C-3D2A-48EE-99C9-FAABFE3C05D8}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
   </bookViews>
   <sheets>
     <sheet name="DataExp1" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="27">
   <si>
     <t>MCA Rows</t>
   </si>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t>Acc. Write Latency (Mean)</t>
-  </si>
-  <si>
-    <t>Acc. Write Latency (Stdev)</t>
   </si>
   <si>
     <t>No. iteration</t>
@@ -112,6 +109,15 @@
   </si>
   <si>
     <t>N = 5</t>
+  </si>
+  <si>
+    <t>Write Latency</t>
+  </si>
+  <si>
+    <t>Write Energy</t>
+  </si>
+  <si>
+    <t>Acc. Write Energy (Mean)</t>
   </si>
 </sst>
 </file>
@@ -157,7 +163,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -190,45 +196,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -254,11 +221,59 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -269,34 +284,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -304,11 +309,51 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -647,1279 +692,1448 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB6579EC-3EC3-439D-9B94-319298E6C78E}">
-  <dimension ref="B1:AJ34"/>
+  <dimension ref="B1:AR34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B1" s="13" t="s">
+    <row r="1" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="B1" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="S1" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="K1" s="13" t="s">
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AB1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="T1" s="13" t="s">
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14"/>
+      <c r="AG1" s="14"/>
+      <c r="AH1" s="14"/>
+      <c r="AI1" s="14"/>
+      <c r="AK1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13"/>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AC1" s="13" t="s">
+      <c r="AL1" s="14"/>
+      <c r="AM1" s="14"/>
+      <c r="AN1" s="14"/>
+      <c r="AO1" s="14"/>
+      <c r="AP1" s="14"/>
+      <c r="AQ1" s="14"/>
+      <c r="AR1" s="14"/>
+    </row>
+    <row r="2" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="B2" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="AD1" s="13"/>
-      <c r="AE1" s="13"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="13"/>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
-      <c r="AJ1" s="13"/>
-    </row>
-    <row r="2" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="s">
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="S2" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="V2" s="13"/>
+      <c r="W2" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z2" s="12"/>
+      <c r="AB2" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC2" s="13"/>
+      <c r="AD2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AG2" s="12"/>
+      <c r="AH2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI2" s="12"/>
+      <c r="AK2" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="AN2" s="13"/>
+      <c r="AO2" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP2" s="12"/>
+      <c r="AQ2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="AR2" s="12"/>
+    </row>
+    <row r="3" spans="2:44" ht="45" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="15"/>
-      <c r="K2" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="14"/>
-      <c r="O2" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="R2" s="15"/>
-      <c r="T2" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="W2" s="14"/>
-      <c r="X2" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA2" s="15"/>
-      <c r="AC2" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD2" s="14"/>
-      <c r="AE2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="AF2" s="14"/>
-      <c r="AG2" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AJ2" s="15"/>
-    </row>
-    <row r="3" spans="2:36" ht="45" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="12" t="s">
+      <c r="H3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="12" t="s">
+      <c r="L3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="P3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" s="3" t="s">
+      <c r="U3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="V3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="O3" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" s="12" t="s">
+      <c r="W3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="X3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="R3" s="12" t="s">
+      <c r="Y3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="U3" s="3" t="s">
+      <c r="AB3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="V3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="W3" s="3" t="s">
+      <c r="AD3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="X3" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y3" s="12" t="s">
+      <c r="AF3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="Z3" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA3" s="12" t="s">
+      <c r="AH3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="AC3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AK3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AE3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="AF3" s="3" t="s">
+      <c r="AM3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AG3" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AH3" s="12" t="s">
+      <c r="AO3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AP3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="AI3" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AJ3" s="12" t="s">
+      <c r="AQ3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AR3" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B4" s="8">
+    <row r="4" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="B4" s="5">
         <v>24.443761142859401</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="5">
         <v>3.3744526857264301</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6">
         <v>11.146140000613499</v>
       </c>
-      <c r="E4" s="9">
+      <c r="G4" s="6">
         <v>1.68778800506088</v>
       </c>
-      <c r="F4" s="8">
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="5">
         <v>5.0263956831744903</v>
       </c>
-      <c r="G4" s="8">
+      <c r="K4" s="5">
         <v>0.90170831675261998</v>
       </c>
-      <c r="H4" s="9">
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="6">
         <v>1.0386527872326301</v>
       </c>
-      <c r="I4" s="9">
+      <c r="O4" s="6">
         <v>0.281035172507479</v>
       </c>
-      <c r="K4" s="8">
+      <c r="P4" s="23">
+        <v>427.43972841419099</v>
+      </c>
+      <c r="Q4" s="23">
+        <v>1.90857404909223E-3</v>
+      </c>
+      <c r="S4" s="5">
         <v>50.189180557709498</v>
       </c>
-      <c r="L4" s="8">
+      <c r="T4" s="5">
         <v>6.8272041826728298</v>
       </c>
-      <c r="M4" s="9">
+      <c r="U4" s="6">
         <v>2.40398255283031</v>
       </c>
-      <c r="N4" s="9">
+      <c r="V4" s="6">
         <v>0.494699860082361</v>
       </c>
-      <c r="O4" s="8">
+      <c r="W4" s="5">
         <v>2.5208897211674199</v>
       </c>
-      <c r="P4" s="8">
+      <c r="X4" s="5">
         <v>0.47344483768397699</v>
       </c>
-      <c r="Q4" s="9">
+      <c r="Y4" s="6">
         <v>1.34621453385329</v>
       </c>
-      <c r="R4" s="9">
+      <c r="Z4" s="6">
         <v>0.35832775281353502</v>
       </c>
-      <c r="T4" s="8">
+      <c r="AB4" s="5">
         <v>2.0282019718480502</v>
       </c>
-      <c r="U4" s="8">
+      <c r="AC4" s="5">
         <v>0.37754673426285001</v>
       </c>
-      <c r="V4" s="9">
+      <c r="AD4" s="6">
         <v>2.93314349751103</v>
       </c>
-      <c r="W4" s="9">
+      <c r="AE4" s="6">
         <v>0.65213375302212495</v>
       </c>
-      <c r="X4" s="8">
+      <c r="AF4" s="5">
         <v>3.1835707328913601</v>
       </c>
-      <c r="Y4" s="8">
+      <c r="AG4" s="5">
         <v>0.65565129784223597</v>
       </c>
-      <c r="Z4" s="9">
+      <c r="AH4" s="6">
         <v>3.0446059739842699</v>
       </c>
-      <c r="AA4" s="9">
+      <c r="AI4" s="6">
         <v>0.65226013362701096</v>
       </c>
-      <c r="AC4" s="8">
+      <c r="AK4" s="5">
         <v>34.570056762068198</v>
       </c>
-      <c r="AD4" s="8">
+      <c r="AL4" s="5">
         <v>4.5778664577056496</v>
       </c>
-      <c r="AE4" s="9">
+      <c r="AM4" s="6">
         <v>1.8250170991933701</v>
       </c>
-      <c r="AF4" s="9">
+      <c r="AN4" s="6">
         <v>0.33633033357449799</v>
       </c>
-      <c r="AG4" s="8">
+      <c r="AO4" s="5">
         <v>1.8523706039791701</v>
       </c>
-      <c r="AH4" s="8">
+      <c r="AP4" s="5">
         <v>0.34156715764353801</v>
       </c>
-      <c r="AI4" s="9">
+      <c r="AQ4" s="6">
         <v>1.8795419666048101</v>
       </c>
-      <c r="AJ4" s="9">
+      <c r="AR4" s="6">
         <v>0.34574964955663201</v>
       </c>
     </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B5" s="8">
+    <row r="5" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="B5" s="5">
         <v>21.768763521560601</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="5">
         <v>3.1865062401780699</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6">
         <v>10.978647285226099</v>
       </c>
-      <c r="E5" s="9">
+      <c r="G5" s="6">
         <v>1.7065269254956801</v>
       </c>
-      <c r="F5" s="8">
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="5">
         <v>4.85409002254627</v>
       </c>
-      <c r="G5" s="8">
+      <c r="K5" s="5">
         <v>0.80897913982258796</v>
       </c>
-      <c r="H5" s="9">
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="6">
         <v>0.89008783875792397</v>
       </c>
-      <c r="I5" s="9">
+      <c r="O5" s="6">
         <v>0.27529653142885502</v>
       </c>
-      <c r="K5" s="8">
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="S5" s="5">
         <v>49.008992449178898</v>
       </c>
-      <c r="L5" s="8">
+      <c r="T5" s="5">
         <v>6.5588284593994697</v>
       </c>
-      <c r="M5" s="9">
+      <c r="U5" s="6">
         <v>1.6098328308093</v>
       </c>
-      <c r="N5" s="9">
+      <c r="V5" s="6">
         <v>0.35390275267126498</v>
       </c>
-      <c r="O5" s="8">
+      <c r="W5" s="5">
         <v>2.6847186811052599</v>
       </c>
-      <c r="P5" s="8">
+      <c r="X5" s="5">
         <v>0.49866574556051502</v>
       </c>
-      <c r="Q5" s="9">
+      <c r="Y5" s="6">
         <v>2.7075638424040802</v>
       </c>
-      <c r="R5" s="9">
+      <c r="Z5" s="6">
         <v>0.55112744515069301</v>
       </c>
-      <c r="T5" s="8">
+      <c r="AB5" s="5">
         <v>2.0576101229880499</v>
       </c>
-      <c r="U5" s="8">
+      <c r="AC5" s="5">
         <v>0.37754673426285001</v>
       </c>
-      <c r="V5" s="9">
+      <c r="AD5" s="6">
         <v>3.0231717517272201</v>
       </c>
-      <c r="W5" s="9">
+      <c r="AE5" s="6">
         <v>0.65213375302212495</v>
       </c>
-      <c r="X5" s="8">
+      <c r="AF5" s="5">
         <v>3.0014742636059601</v>
       </c>
-      <c r="Y5" s="8">
+      <c r="AG5" s="5">
         <v>0.65213375302212495</v>
       </c>
-      <c r="Z5" s="9">
+      <c r="AH5" s="6">
         <v>3.0732721507638598</v>
       </c>
-      <c r="AA5" s="9">
+      <c r="AI5" s="6">
         <v>0.65213375302212495</v>
       </c>
-      <c r="AC5" s="8">
+      <c r="AK5" s="5">
         <v>34.554127832915199</v>
       </c>
-      <c r="AD5" s="8">
+      <c r="AL5" s="5">
         <v>4.5660618080018196</v>
       </c>
-      <c r="AE5" s="9">
+      <c r="AM5" s="6">
         <v>1.96093445188255</v>
       </c>
-      <c r="AF5" s="9">
+      <c r="AN5" s="6">
         <v>0.35374707690719498</v>
       </c>
-      <c r="AG5" s="8">
+      <c r="AO5" s="5">
         <v>1.9641721709049</v>
       </c>
-      <c r="AH5" s="8">
+      <c r="AP5" s="5">
         <v>0.36261738420721501</v>
       </c>
-      <c r="AI5" s="9">
+      <c r="AQ5" s="6">
         <v>1.91781862598536</v>
       </c>
-      <c r="AJ5" s="9">
+      <c r="AR5" s="6">
         <v>0.35301643444209602</v>
       </c>
     </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B6" s="8">
+    <row r="6" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="B6" s="5">
         <v>24.272210690591301</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="5">
         <v>3.3054398403598002</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6">
         <v>11.131989491819301</v>
       </c>
-      <c r="E6" s="9">
+      <c r="G6" s="6">
         <v>1.68616441676978</v>
       </c>
-      <c r="F6" s="8">
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="5">
         <v>4.9373714864782201</v>
       </c>
-      <c r="G6" s="8">
+      <c r="K6" s="5">
         <v>0.89188987256264995</v>
       </c>
-      <c r="H6" s="9">
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="6">
         <v>1.0114258900419599</v>
       </c>
-      <c r="I6" s="9">
+      <c r="O6" s="6">
         <v>0.29627600535638898</v>
       </c>
-      <c r="K6" s="8">
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="S6" s="5">
         <v>50.370043311847297</v>
       </c>
-      <c r="L6" s="8">
+      <c r="T6" s="5">
         <v>6.8266682265390397</v>
       </c>
-      <c r="M6" s="9">
+      <c r="U6" s="6">
         <v>3.31366070223083</v>
       </c>
-      <c r="N6" s="9">
+      <c r="V6" s="6">
         <v>0.59823315379531405</v>
       </c>
-      <c r="O6" s="8">
+      <c r="W6" s="5">
         <v>1.8698821640777401</v>
       </c>
-      <c r="P6" s="8">
+      <c r="X6" s="5">
         <v>0.36723080126573698</v>
       </c>
-      <c r="Q6" s="9">
+      <c r="Y6" s="6">
         <v>2.4706305240653101</v>
       </c>
-      <c r="R6" s="9">
+      <c r="Z6" s="6">
         <v>0.47413541013360899</v>
       </c>
-      <c r="T6" s="8">
+      <c r="AB6" s="5">
         <v>2.0124832402399999</v>
       </c>
-      <c r="U6" s="8">
+      <c r="AC6" s="5">
         <v>0.37754673426285001</v>
       </c>
-      <c r="V6" s="9">
+      <c r="AD6" s="6">
         <v>3.1835707328913601</v>
       </c>
-      <c r="W6" s="9">
+      <c r="AE6" s="6">
         <v>0.65565129784223597</v>
       </c>
-      <c r="X6" s="8">
+      <c r="AF6" s="5">
         <v>3.0052609093097602</v>
       </c>
-      <c r="Y6" s="8">
+      <c r="AG6" s="5">
         <v>0.65213375302212495</v>
       </c>
-      <c r="Z6" s="9">
+      <c r="AH6" s="6">
         <v>2.9332438502332301</v>
       </c>
-      <c r="AA6" s="9">
+      <c r="AI6" s="6">
         <v>0.65213375302212495</v>
       </c>
-      <c r="AC6" s="8">
+      <c r="AK6" s="5">
         <v>34.586395368105499</v>
       </c>
-      <c r="AD6" s="8">
+      <c r="AL6" s="5">
         <v>4.5775860505016004</v>
       </c>
-      <c r="AE6" s="9">
+      <c r="AM6" s="6">
         <v>1.88217908842425</v>
       </c>
-      <c r="AF6" s="9">
+      <c r="AN6" s="6">
         <v>0.35140505638671998</v>
       </c>
-      <c r="AG6" s="8">
+      <c r="AO6" s="5">
         <v>1.8959378968298899</v>
       </c>
-      <c r="AH6" s="8">
+      <c r="AP6" s="5">
         <v>0.34943432354470599</v>
       </c>
-      <c r="AI6" s="9">
+      <c r="AQ6" s="6">
         <v>1.96427586073906</v>
       </c>
-      <c r="AJ6" s="9">
+      <c r="AR6" s="6">
         <v>0.35731335216903298</v>
       </c>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B7" s="8">
+    <row r="7" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="B7" s="5">
         <v>24.404174573572501</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="5">
         <v>3.3186837088307102</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6">
         <v>10.9557705531107</v>
       </c>
-      <c r="E7" s="9">
+      <c r="G7" s="6">
         <v>1.57213037578915</v>
       </c>
-      <c r="F7" s="8">
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="5">
         <v>4.7911793814388997</v>
       </c>
-      <c r="G7" s="8">
+      <c r="K7" s="5">
         <v>0.81751166683242105</v>
       </c>
-      <c r="H7" s="9">
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="6">
         <v>0.95254623904054903</v>
       </c>
-      <c r="I7" s="9">
+      <c r="O7" s="6">
         <v>0.26236662864990901</v>
       </c>
-      <c r="K7" s="8">
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="S7" s="5">
         <v>48.5283966162228</v>
       </c>
-      <c r="L7" s="8">
+      <c r="T7" s="5">
         <v>6.39532451008645</v>
       </c>
-      <c r="M7" s="9">
+      <c r="U7" s="6">
         <v>2.3974738662768198</v>
       </c>
-      <c r="N7" s="9">
+      <c r="V7" s="6">
         <v>0.49437600947429899</v>
       </c>
-      <c r="O7" s="8">
+      <c r="W7" s="5">
         <v>2.8090651842160401</v>
       </c>
-      <c r="P7" s="8">
+      <c r="X7" s="5">
         <v>0.55561814716228497</v>
       </c>
-      <c r="Q7" s="9">
+      <c r="Y7" s="6">
         <v>1.9235703445824599</v>
       </c>
-      <c r="R7" s="9">
+      <c r="Z7" s="6">
         <v>0.37579443485147102</v>
       </c>
-      <c r="T7" s="8">
+      <c r="AB7" s="5">
         <v>1.98733133553576</v>
       </c>
-      <c r="U7" s="8">
+      <c r="AC7" s="5">
         <v>0.37754673426285001</v>
       </c>
-      <c r="V7" s="9">
+      <c r="AD7" s="6">
         <v>2.9709094694099698</v>
       </c>
-      <c r="W7" s="9">
+      <c r="AE7" s="6">
         <v>0.65213375302212495</v>
       </c>
-      <c r="X7" s="8">
+      <c r="AF7" s="5">
         <v>3.1234714223794802</v>
       </c>
-      <c r="Y7" s="8">
+      <c r="AG7" s="5">
         <v>0.65226013362701096</v>
       </c>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="9"/>
-      <c r="AC7" s="8">
+      <c r="AH7" s="6"/>
+      <c r="AI7" s="6"/>
+      <c r="AK7" s="5">
         <v>34.474323231873001</v>
       </c>
-      <c r="AD7" s="8">
+      <c r="AL7" s="5">
         <v>4.5812551646225703</v>
       </c>
-      <c r="AE7" s="9">
+      <c r="AM7" s="6">
         <v>1.88221703832479</v>
       </c>
-      <c r="AF7" s="9">
+      <c r="AN7" s="6">
         <v>0.35140505652889598</v>
       </c>
-      <c r="AG7" s="8">
+      <c r="AO7" s="5">
         <v>1.8654391378277699</v>
       </c>
-      <c r="AH7" s="8">
+      <c r="AP7" s="5">
         <v>0.35136993223547403</v>
       </c>
-      <c r="AI7" s="9">
+      <c r="AQ7" s="6">
         <v>1.9178899634194899</v>
       </c>
-      <c r="AJ7" s="9">
+      <c r="AR7" s="6">
         <v>0.35300853576487501</v>
       </c>
     </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B8" s="8">
+    <row r="8" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="B8" s="5">
         <v>24.519392747918499</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="5">
         <v>3.3765146340410901</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6">
         <v>11.084394304570299</v>
       </c>
-      <c r="E8" s="9">
+      <c r="G8" s="6">
         <v>1.71086338931697</v>
       </c>
-      <c r="F8" s="8">
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="5">
         <v>4.5716851890135404</v>
       </c>
-      <c r="G8" s="8">
+      <c r="K8" s="5">
         <v>0.78488713802412502</v>
       </c>
-      <c r="H8" s="9">
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="6">
         <v>0.59342344244794798</v>
       </c>
-      <c r="I8" s="9">
+      <c r="O8" s="6">
         <v>0.17203410846221501</v>
       </c>
-      <c r="K8" s="8">
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="S8" s="5">
         <v>50.189180557709498</v>
       </c>
-      <c r="L8" s="8">
+      <c r="T8" s="5">
         <v>6.8272041826728298</v>
       </c>
-      <c r="M8" s="9">
+      <c r="U8" s="6">
         <v>2.3363436265518498</v>
       </c>
-      <c r="N8" s="9">
+      <c r="V8" s="6">
         <v>0.49525277741667301</v>
       </c>
-      <c r="O8" s="8">
+      <c r="W8" s="5">
         <v>3.2921811589554202</v>
       </c>
-      <c r="P8" s="8">
+      <c r="X8" s="5">
         <v>0.61038119286221504</v>
       </c>
-      <c r="Q8" s="9">
+      <c r="Y8" s="6">
         <v>2.39747268966476</v>
       </c>
-      <c r="R8" s="9">
+      <c r="Z8" s="6">
         <v>0.479906115601407</v>
       </c>
-      <c r="T8" s="8">
+      <c r="AB8" s="5">
         <v>2.0045866890630801</v>
       </c>
-      <c r="U8" s="8">
+      <c r="AC8" s="5">
         <v>0.37754673426285001</v>
       </c>
-      <c r="V8" s="9">
+      <c r="AD8" s="6">
         <v>2.8887491003138202</v>
       </c>
-      <c r="W8" s="9">
+      <c r="AE8" s="6">
         <v>0.65213375302212495</v>
       </c>
-      <c r="X8" s="8">
+      <c r="AF8" s="5">
         <v>3.1300087680066402</v>
       </c>
-      <c r="Y8" s="8">
+      <c r="AG8" s="5">
         <v>0.65226013362701096</v>
       </c>
-      <c r="Z8" s="9"/>
-      <c r="AA8" s="9"/>
-      <c r="AC8" s="8">
+      <c r="AH8" s="6"/>
+      <c r="AI8" s="6"/>
+      <c r="AK8" s="5">
         <v>34.482423779545499</v>
       </c>
-      <c r="AD8" s="8">
+      <c r="AL8" s="5">
         <v>4.5801967278307698</v>
       </c>
-      <c r="AE8" s="9">
+      <c r="AM8" s="6">
         <v>1.8315258657560201</v>
       </c>
-      <c r="AF8" s="9">
+      <c r="AN8" s="6">
         <v>0.34577767622515698</v>
       </c>
-      <c r="AG8" s="8">
+      <c r="AO8" s="5">
         <v>1.8523461079911401</v>
       </c>
-      <c r="AH8" s="8">
+      <c r="AP8" s="5">
         <v>0.34156715758035</v>
       </c>
-      <c r="AI8" s="9">
+      <c r="AQ8" s="6">
         <v>1.94458113911453</v>
       </c>
-      <c r="AJ8" s="9">
+      <c r="AR8" s="6">
         <v>0.36071379860479102</v>
       </c>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B9" s="8">
+    <row r="9" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="B9" s="5">
         <v>24.310600989632899</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="5">
         <v>3.3225698262557399</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6">
         <v>11.078199731004901</v>
       </c>
-      <c r="E9" s="9">
+      <c r="G9" s="6">
         <v>1.65069524058359</v>
       </c>
-      <c r="F9" s="8">
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="5">
         <v>4.9807010405869097</v>
       </c>
-      <c r="G9" s="8">
+      <c r="K9" s="5">
         <v>0.92921451381373998</v>
       </c>
-      <c r="H9" s="9">
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="6">
         <v>0.56505155768495896</v>
       </c>
-      <c r="I9" s="9">
+      <c r="O9" s="6">
         <v>0.16474922791581201</v>
       </c>
-      <c r="K9" s="8">
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="S9" s="5">
         <v>49.619431099961197</v>
       </c>
-      <c r="L9" s="8">
+      <c r="T9" s="5">
         <v>6.6224281863214802</v>
       </c>
-      <c r="M9" s="9">
+      <c r="U9" s="6">
         <v>2.06027858560702</v>
       </c>
-      <c r="N9" s="9">
+      <c r="V9" s="6">
         <v>0.41902119187009701</v>
       </c>
-      <c r="O9" s="8">
+      <c r="W9" s="5">
         <v>2.1176598714663699</v>
       </c>
-      <c r="P9" s="8">
+      <c r="X9" s="5">
         <v>0.420783326797598</v>
       </c>
-      <c r="Q9" s="9">
+      <c r="Y9" s="6">
         <v>1.05066650115089</v>
       </c>
-      <c r="R9" s="9">
+      <c r="Z9" s="6">
         <v>0.25434177251207701</v>
       </c>
-      <c r="T9" s="8">
+      <c r="AB9" s="5">
         <v>2.03035231561176</v>
       </c>
-      <c r="U9" s="8">
+      <c r="AC9" s="5">
         <v>0.37754673426285001</v>
       </c>
-      <c r="V9" s="9">
+      <c r="AD9" s="6">
         <v>3.0233946110574101</v>
       </c>
-      <c r="W9" s="9">
+      <c r="AE9" s="6">
         <v>0.65226013362701096</v>
       </c>
-      <c r="X9" s="8">
+      <c r="AF9" s="5">
         <v>3.0222659675151302</v>
       </c>
-      <c r="Y9" s="8">
+      <c r="AG9" s="5">
         <v>0.65226013362701096</v>
       </c>
-      <c r="Z9" s="9"/>
-      <c r="AA9" s="9"/>
-      <c r="AC9" s="8">
+      <c r="AH9" s="6"/>
+      <c r="AI9" s="6"/>
+      <c r="AK9" s="5">
         <v>34.570056762068198</v>
       </c>
-      <c r="AD9" s="8">
+      <c r="AL9" s="5">
         <v>4.5778664577056496</v>
       </c>
-      <c r="AE9" s="9">
+      <c r="AM9" s="6">
         <v>1.86147110489288</v>
       </c>
-      <c r="AF9" s="9">
+      <c r="AN9" s="6">
         <v>0.34558367107705801</v>
       </c>
-      <c r="AG9" s="8">
+      <c r="AO9" s="5">
         <v>1.96362562254665</v>
       </c>
-      <c r="AH9" s="8">
+      <c r="AP9" s="5">
         <v>0.36222639562867198</v>
       </c>
-      <c r="AI9" s="9">
+      <c r="AQ9" s="6">
         <v>1.9642715242957101</v>
       </c>
-      <c r="AJ9" s="9">
+      <c r="AR9" s="6">
         <v>0.35731730151554097</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B10" s="8">
+    <row r="10" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="B10" s="5">
         <v>24.519392747918499</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="5">
         <v>3.3765146340410901</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6">
         <v>11.3283064247616</v>
       </c>
-      <c r="E10" s="9">
+      <c r="G10" s="6">
         <v>1.75667635216019</v>
       </c>
-      <c r="F10" s="8">
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="5">
         <v>4.3655684894788598</v>
       </c>
-      <c r="G10" s="8">
+      <c r="K10" s="5">
         <v>0.72256847111010403</v>
       </c>
-      <c r="H10" s="9">
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="6">
         <v>0.89008783875792397</v>
       </c>
-      <c r="I10" s="9">
+      <c r="O10" s="6">
         <v>0.27529653142885502</v>
       </c>
-      <c r="K10" s="8">
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="S10" s="5">
         <v>50.370043311847297</v>
       </c>
-      <c r="L10" s="8">
+      <c r="T10" s="5">
         <v>6.8266682265390397</v>
       </c>
-      <c r="M10" s="9">
+      <c r="U10" s="6">
         <v>1.1013427759766601</v>
       </c>
-      <c r="N10" s="9">
+      <c r="V10" s="6">
         <v>0.279195398098668</v>
       </c>
-      <c r="O10" s="8">
+      <c r="W10" s="5">
         <v>1.8886807440369899</v>
       </c>
-      <c r="P10" s="8">
+      <c r="X10" s="5">
         <v>0.41993899419076303</v>
       </c>
-      <c r="Q10" s="9">
+      <c r="Y10" s="6">
         <v>1.08014977882427</v>
       </c>
-      <c r="R10" s="9">
+      <c r="Z10" s="6">
         <v>0.28419236315363</v>
       </c>
-      <c r="T10" s="8">
+      <c r="AB10" s="5">
         <v>2.0282019718480502</v>
       </c>
-      <c r="U10" s="8">
+      <c r="AC10" s="5">
         <v>0.37754673426285001</v>
       </c>
-      <c r="V10" s="9">
+      <c r="AD10" s="6">
         <v>3.0233946110574101</v>
       </c>
-      <c r="W10" s="9">
+      <c r="AE10" s="6">
         <v>0.65226013362701096</v>
       </c>
-      <c r="X10" s="8">
+      <c r="AF10" s="5">
         <v>3.0769912027266599</v>
       </c>
-      <c r="Y10" s="8">
+      <c r="AG10" s="5">
         <v>0.65226013362701096</v>
       </c>
-      <c r="Z10" s="9"/>
-      <c r="AA10" s="9"/>
-      <c r="AC10" s="8">
+      <c r="AH10" s="6"/>
+      <c r="AI10" s="6"/>
+      <c r="AK10" s="5">
         <v>34.498810594745102</v>
       </c>
-      <c r="AD10" s="8">
+      <c r="AL10" s="5">
         <v>4.5805798233599297</v>
       </c>
-      <c r="AE10" s="9">
+      <c r="AM10" s="6">
         <v>1.86657481807766</v>
       </c>
-      <c r="AF10" s="9">
+      <c r="AN10" s="6">
         <v>0.34383410086548399</v>
       </c>
-      <c r="AG10" s="8">
+      <c r="AO10" s="5">
         <v>1.90028400803589</v>
       </c>
-      <c r="AH10" s="8">
+      <c r="AP10" s="5">
         <v>0.34945012130988901</v>
       </c>
-      <c r="AI10" s="9">
+      <c r="AQ10" s="6">
         <v>1.90928027610508</v>
       </c>
-      <c r="AJ10" s="9">
+      <c r="AR10" s="6">
         <v>0.34945018620593998</v>
       </c>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B11" s="8">
+    <row r="11" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="B11" s="5">
         <v>21.996905724856099</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="5">
         <v>2.9856415262303599</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6">
         <v>11.0671269081706</v>
       </c>
-      <c r="E11" s="9">
+      <c r="G11" s="6">
         <v>1.68567829653259</v>
       </c>
-      <c r="F11" s="8">
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="5">
         <v>4.9579210625189001</v>
       </c>
-      <c r="G11" s="8">
+      <c r="K11" s="5">
         <v>0.89091012676741499</v>
       </c>
-      <c r="H11" s="9">
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="6">
         <v>0.95254623904054903</v>
       </c>
-      <c r="I11" s="9">
+      <c r="O11" s="6">
         <v>0.26236662864990901</v>
       </c>
-      <c r="K11" s="8">
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="S11" s="5">
         <v>50.6021835670551</v>
       </c>
-      <c r="L11" s="8">
+      <c r="T11" s="5">
         <v>6.8159615936773701</v>
       </c>
-      <c r="M11" s="9">
+      <c r="U11" s="6">
         <v>2.4294044850569798</v>
       </c>
-      <c r="N11" s="9">
+      <c r="V11" s="6">
         <v>0.491532450674801</v>
       </c>
-      <c r="O11" s="8">
+      <c r="W11" s="5">
         <v>2.4929016378617299</v>
       </c>
-      <c r="P11" s="8">
+      <c r="X11" s="5">
         <v>0.47851192255269298</v>
       </c>
-      <c r="Q11" s="9">
+      <c r="Y11" s="6">
         <v>2.3570848611973498</v>
       </c>
-      <c r="R11" s="9">
+      <c r="Z11" s="6">
         <v>0.47000785524292399</v>
       </c>
-      <c r="T11" s="8">
+      <c r="AB11" s="5">
         <v>2.0045866890630801</v>
       </c>
-      <c r="U11" s="8">
+      <c r="AC11" s="5">
         <v>0.37754673426285001</v>
       </c>
-      <c r="V11" s="9">
+      <c r="AD11" s="6">
         <v>3.1856421504299002</v>
       </c>
-      <c r="W11" s="9">
+      <c r="AE11" s="6">
         <v>0.65565129784223597</v>
       </c>
-      <c r="X11" s="8">
+      <c r="AF11" s="5">
         <v>3.1856421504299002</v>
       </c>
-      <c r="Y11" s="8">
+      <c r="AG11" s="5">
         <v>0.65565129784223597</v>
       </c>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
-      <c r="AC11" s="8">
+      <c r="AH11" s="6"/>
+      <c r="AI11" s="6"/>
+      <c r="AK11" s="5">
         <v>34.554127832915199</v>
       </c>
-      <c r="AD11" s="8">
+      <c r="AL11" s="5">
         <v>4.5660618080018196</v>
       </c>
-      <c r="AE11" s="9">
+      <c r="AM11" s="6">
         <v>1.81268296370352</v>
       </c>
-      <c r="AF11" s="9">
+      <c r="AN11" s="6">
         <v>0.33337223640394198</v>
       </c>
-      <c r="AG11" s="8">
+      <c r="AO11" s="5">
         <v>1.96429126731902</v>
       </c>
-      <c r="AH11" s="8">
+      <c r="AP11" s="5">
         <v>0.35731730156293201</v>
       </c>
-      <c r="AI11" s="9">
+      <c r="AQ11" s="6">
         <v>1.8795069801762501</v>
       </c>
-      <c r="AJ11" s="9">
+      <c r="AR11" s="6">
         <v>0.34575359895052998</v>
       </c>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B12" s="8">
+    <row r="12" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="B12" s="5">
         <v>24.073944136969398</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="5">
         <v>3.2906045777064898</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6">
         <v>10.871081688695201</v>
       </c>
-      <c r="E12" s="9">
+      <c r="G12" s="6">
         <v>1.5456538017913899</v>
       </c>
-      <c r="F12" s="8">
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="5">
         <v>4.5042629003538499</v>
       </c>
-      <c r="G12" s="8">
+      <c r="K12" s="5">
         <v>0.75565867825603805</v>
       </c>
-      <c r="H12" s="9">
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="6">
         <v>0.98179762818361005</v>
       </c>
-      <c r="I12" s="9">
+      <c r="O12" s="6">
         <v>0.28993726071696102</v>
       </c>
-      <c r="K12" s="8">
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="S12" s="5">
         <v>48.5283966162228</v>
       </c>
-      <c r="L12" s="8">
+      <c r="T12" s="5">
         <v>6.39532451008645</v>
       </c>
-      <c r="M12" s="9">
+      <c r="U12" s="6">
         <v>2.8583793701106899</v>
       </c>
-      <c r="N12" s="9">
+      <c r="V12" s="6">
         <v>0.57377303940268798</v>
       </c>
-      <c r="O12" s="8">
+      <c r="W12" s="5">
         <v>2.2571410688804598</v>
       </c>
-      <c r="P12" s="8">
+      <c r="X12" s="5">
         <v>0.46259787093209498</v>
       </c>
-      <c r="Q12" s="9">
+      <c r="Y12" s="6">
         <v>2.4566723216903199</v>
       </c>
-      <c r="R12" s="9">
+      <c r="Z12" s="6">
         <v>0.46852708080793398</v>
       </c>
-      <c r="T12" s="8">
+      <c r="AB12" s="5">
         <v>2.0124832402399999</v>
       </c>
-      <c r="U12" s="8">
+      <c r="AC12" s="5">
         <v>0.37754673426285001</v>
       </c>
-      <c r="V12" s="9">
+      <c r="AD12" s="6">
         <v>2.9469306504008701</v>
       </c>
-      <c r="W12" s="9">
+      <c r="AE12" s="6">
         <v>0.65213375302212495</v>
       </c>
-      <c r="X12" s="8">
+      <c r="AF12" s="5">
         <v>3.1524446068305201</v>
       </c>
-      <c r="Y12" s="8">
+      <c r="AG12" s="5">
         <v>0.65226013362701096</v>
       </c>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-      <c r="AC12" s="8">
+      <c r="AH12" s="6"/>
+      <c r="AI12" s="6"/>
+      <c r="AK12" s="5">
         <v>34.6014705772876</v>
       </c>
-      <c r="AD12" s="8">
+      <c r="AL12" s="5">
         <v>4.5785181060921998</v>
       </c>
-      <c r="AE12" s="9">
+      <c r="AM12" s="6">
         <v>1.8125561645361601</v>
       </c>
-      <c r="AF12" s="9">
+      <c r="AN12" s="6">
         <v>0.33334854013531301</v>
       </c>
-      <c r="AG12" s="8">
+      <c r="AO12" s="5">
         <v>1.96488011670068</v>
       </c>
-      <c r="AH12" s="8">
+      <c r="AP12" s="5">
         <v>0.36261343482516201</v>
       </c>
-      <c r="AI12" s="9">
+      <c r="AQ12" s="6">
         <v>1.9178899634194899</v>
       </c>
-      <c r="AJ12" s="9">
+      <c r="AR12" s="6">
         <v>0.35300853576487501</v>
       </c>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B13" s="8">
+    <row r="13" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="B13" s="5">
         <v>24.073944136969398</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="5">
         <v>3.2906045777064898</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6">
         <v>11.065870149418</v>
       </c>
-      <c r="E13" s="9">
+      <c r="G13" s="6">
         <v>1.7106619694696501</v>
       </c>
-      <c r="F13" s="8">
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="5">
         <v>4.4913411407632298</v>
       </c>
-      <c r="G13" s="8">
+      <c r="K13" s="5">
         <v>0.764781871349272</v>
       </c>
-      <c r="H13" s="9">
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="6">
         <v>0.61764700512757498</v>
       </c>
-      <c r="I13" s="9">
+      <c r="O13" s="6">
         <v>0.17697658502358601</v>
       </c>
-      <c r="K13" s="8">
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="S13" s="5">
         <v>50.813193764563998</v>
       </c>
-      <c r="L13" s="8">
+      <c r="T13" s="5">
         <v>6.8053931798874796</v>
       </c>
-      <c r="M13" s="9">
+      <c r="U13" s="6">
         <v>2.07438188382043</v>
       </c>
-      <c r="N13" s="9">
+      <c r="V13" s="6">
         <v>0.43125921121579203</v>
       </c>
-      <c r="O13" s="8">
+      <c r="W13" s="5">
         <v>2.5100936022216298</v>
       </c>
-      <c r="P13" s="8">
+      <c r="X13" s="5">
         <v>2.5100936022216298</v>
       </c>
-      <c r="Q13" s="9">
+      <c r="Y13" s="6">
         <v>2.6805114554649099</v>
       </c>
-      <c r="R13" s="9">
+      <c r="Z13" s="6">
         <v>0.50105033491431605</v>
       </c>
-      <c r="T13" s="8">
+      <c r="AB13" s="5">
         <v>2.0282019718480502</v>
       </c>
-      <c r="U13" s="8">
+      <c r="AC13" s="5">
         <v>0.37754673426285001</v>
       </c>
-      <c r="V13" s="9">
+      <c r="AD13" s="6">
         <v>3.1450098960334101</v>
       </c>
-      <c r="W13" s="9">
+      <c r="AE13" s="6">
         <v>0.65226013362701096</v>
       </c>
-      <c r="X13" s="8">
+      <c r="AF13" s="5">
         <v>3.0895272691364801</v>
       </c>
-      <c r="Y13" s="8">
+      <c r="AG13" s="5">
         <v>0.65226013362701096</v>
       </c>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AC13" s="8">
+      <c r="AH13" s="6"/>
+      <c r="AI13" s="6"/>
+      <c r="AK13" s="5">
         <v>34.63132536506</v>
       </c>
-      <c r="AD13" s="8">
+      <c r="AL13" s="5">
         <v>4.5643280255556196</v>
       </c>
-      <c r="AE13" s="9">
+      <c r="AM13" s="6">
         <v>1.8250318583902301</v>
       </c>
-      <c r="AF13" s="9">
+      <c r="AN13" s="6">
         <v>0.33629873874712601</v>
       </c>
-      <c r="AG13" s="8">
+      <c r="AO13" s="5">
         <v>1.9040866582123299</v>
       </c>
-      <c r="AH13" s="8">
+      <c r="AP13" s="5">
         <v>0.35445006159312697</v>
       </c>
-      <c r="AI13" s="9">
+      <c r="AQ13" s="6">
         <v>1.96429126731902</v>
       </c>
-      <c r="AJ13" s="9">
+      <c r="AR13" s="6">
         <v>0.35731730156293201</v>
       </c>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-    </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-    </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
+    <row r="14" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="2:44" x14ac:dyDescent="0.25">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="K1:R1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="T1:AA1"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="AC1:AJ1"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="AG2:AH2"/>
-    <mergeCell ref="AI2:AJ2"/>
+    <mergeCell ref="AK1:AR1"/>
+    <mergeCell ref="AK2:AL2"/>
+    <mergeCell ref="AM2:AN2"/>
+    <mergeCell ref="AO2:AP2"/>
+    <mergeCell ref="AQ2:AR2"/>
+    <mergeCell ref="AB1:AI1"/>
+    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="AF2:AG2"/>
+    <mergeCell ref="AH2:AI2"/>
+    <mergeCell ref="S1:Z1"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="B1:O1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="N2:Q2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1941,773 +2155,806 @@
     <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="12" max="12" width="18" style="8" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+    </row>
+    <row r="2" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+    </row>
+    <row r="3" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="32" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17"/>
-    </row>
-    <row r="2" spans="1:27" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:27" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="B4" s="29">
         <v>1</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="10">
+      <c r="C4" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="30">
+        <v>66</v>
+      </c>
+      <c r="E4" s="30">
+        <v>66</v>
+      </c>
+      <c r="F4" s="30">
         <v>1</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="14">
+      <c r="G4" s="30">
+        <v>1</v>
+      </c>
+      <c r="H4" s="30">
         <v>66</v>
       </c>
-      <c r="E4" s="14">
+      <c r="I4" s="30">
         <v>66</v>
       </c>
-      <c r="F4" s="14">
-        <v>1</v>
-      </c>
-      <c r="G4" s="14">
-        <v>1</v>
-      </c>
-      <c r="H4" s="14">
-        <v>66</v>
-      </c>
-      <c r="I4" s="14">
-        <v>66</v>
-      </c>
-      <c r="J4" s="9">
+      <c r="J4" s="6">
         <f>AVERAGE(DataExp1!B4:B13)</f>
         <v>23.838309041284862</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="6">
         <f>AVERAGE(DataExp1!C4:C13)</f>
         <v>3.2827532251076272</v>
       </c>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="L4" s="8">
+        <v>280.77705301382201</v>
+      </c>
+      <c r="M4" s="8">
+        <v>1.24324175218449E-3</v>
+      </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="10">
+      <c r="A5" s="16"/>
+      <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="9">
-        <f>AVERAGE(DataExp1!D4:D13)</f>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="6">
+        <f>AVERAGE(DataExp1!F4:F13)</f>
         <v>11.070752653739017</v>
       </c>
-      <c r="K5" s="9">
-        <f>AVERAGE(DataExp1!E4:E13)</f>
+      <c r="K5" s="6">
+        <f>AVERAGE(DataExp1!G4:G13)</f>
         <v>1.6712838772969871</v>
       </c>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+      <c r="L5" s="6">
+        <v>391.23075904146799</v>
+      </c>
+      <c r="M5" s="6">
+        <v>1.8368430572894799E-3</v>
+      </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="10">
+      <c r="A6" s="16"/>
+      <c r="B6" s="7">
         <v>5</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="9">
-        <f>AVERAGE(DataExp1!F4:F13)</f>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="6">
+        <f>AVERAGE(DataExp1!J4:J13)</f>
         <v>4.7480516396353174</v>
       </c>
-      <c r="K6" s="9">
-        <f>AVERAGE(DataExp1!G4:G13)</f>
+      <c r="K6" s="6">
+        <f>AVERAGE(DataExp1!K4:K13)</f>
         <v>0.82681097952909732</v>
       </c>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
+      <c r="L6" s="6">
+        <v>417.59086506911302</v>
+      </c>
+      <c r="M6" s="6">
+        <v>1.8680991323063701E-3</v>
+      </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
-      <c r="B7" s="10">
+      <c r="A7" s="16"/>
+      <c r="B7" s="7">
         <v>10</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="9">
-        <f>AVERAGE(DataExp1!H4:H13)</f>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="6">
+        <f>AVERAGE(DataExp1!N4:N13)</f>
         <v>0.84932664663156276</v>
       </c>
-      <c r="K7" s="9">
-        <f>AVERAGE(DataExp1!I4:I13)</f>
+      <c r="K7" s="6">
+        <f>AVERAGE(DataExp1!O4:O13)</f>
         <v>0.24563346801399702</v>
       </c>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="L7" s="6">
+        <v>427.43972841419099</v>
+      </c>
+      <c r="M7" s="6">
+        <v>1.90857404909223E-3</v>
+      </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="4">
+        <v>1</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="5">
+        <f>AVERAGE(DataExp1!S4:S13)</f>
+        <v>49.821904185231844</v>
+      </c>
+      <c r="K8" s="5">
+        <f>AVERAGE(DataExp1!T4:T13)</f>
+        <v>6.6901005257882433</v>
+      </c>
+      <c r="L8" s="5">
+        <v>38.8018530138228</v>
+      </c>
+      <c r="M8" s="5">
+        <v>1.8341564911519399E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="13"/>
+      <c r="B9" s="4">
+        <v>3</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="5">
+        <f>AVERAGE(DataExp1!U4:U13)</f>
+        <v>2.2585080679270888</v>
+      </c>
+      <c r="K9" s="5">
+        <f>AVERAGE(DataExp1!V4:V13)</f>
+        <v>0.46312458447019578</v>
+      </c>
+      <c r="L9" s="5">
+        <v>73.281259041468303</v>
+      </c>
+      <c r="M9" s="5">
+        <v>3.8957965924184199E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="13"/>
+      <c r="B10" s="4">
+        <v>5</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="5">
+        <f>AVERAGE(DataExp1!W4:W13)</f>
+        <v>2.4443213833989064</v>
+      </c>
+      <c r="K10" s="5">
+        <f>AVERAGE(DataExp1!X4:X13)</f>
+        <v>0.67972664412295081</v>
+      </c>
+      <c r="L10" s="5">
+        <v>77.092715069113893</v>
+      </c>
+      <c r="M10" s="5">
+        <v>4.1758142847234302E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="B11" s="4">
+        <v>10</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="5">
+        <f>AVERAGE(DataExp1!Y4:Y13)</f>
+        <v>2.0470536852897636</v>
+      </c>
+      <c r="K11" s="5">
+        <f>AVERAGE(DataExp1!Z4:Z13)</f>
+        <v>0.42174105651815957</v>
+      </c>
+      <c r="L11" s="5">
+        <v>76.300224110581993</v>
+      </c>
+      <c r="M11" s="5">
+        <v>4.0673431385843499E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B12" s="7">
         <v>1</v>
       </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="8">
-        <f>AVERAGE(DataExp1!K4:K13)</f>
-        <v>49.821904185231844</v>
-      </c>
-      <c r="K8" s="8">
-        <f>AVERAGE(DataExp1!L4:L13)</f>
-        <v>6.6901005257882433</v>
-      </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="6">
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="6">
+        <f>AVERAGE(DataExp1!AB4:AB13)</f>
+        <v>2.0194039548285878</v>
+      </c>
+      <c r="K12" s="6">
+        <f>AVERAGE(DataExp1!AC4:AC13)</f>
+        <v>0.37754673426285007</v>
+      </c>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="16"/>
+      <c r="B13" s="7">
         <v>3</v>
       </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="8">
-        <f>AVERAGE(DataExp1!M4:M13)</f>
-        <v>2.2585080679270888</v>
-      </c>
-      <c r="K9" s="8">
-        <f>AVERAGE(DataExp1!N4:N13)</f>
-        <v>0.46312458447019578</v>
-      </c>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
-      <c r="B10" s="6">
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="6">
+        <f>AVERAGE(DataExp1!AD4:AD13)</f>
+        <v>3.0323916470832399</v>
+      </c>
+      <c r="K13" s="6">
+        <f>AVERAGE(DataExp1!AE4:AE13)</f>
+        <v>0.65287517616761293</v>
+      </c>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="16"/>
+      <c r="B14" s="7">
         <v>5</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="8">
-        <f>AVERAGE(DataExp1!O4:O13)</f>
-        <v>2.4443213833989064</v>
-      </c>
-      <c r="K10" s="8">
-        <f>AVERAGE(DataExp1!P4:P13)</f>
-        <v>0.67972664412295081</v>
-      </c>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
-      <c r="B11" s="6">
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="6">
+        <f>AVERAGE(DataExp1!AF4:AF13)</f>
+        <v>3.0970657292831891</v>
+      </c>
+      <c r="K14" s="6">
+        <f>AVERAGE(DataExp1!AG4:AG13)</f>
+        <v>0.65291309034907874</v>
+      </c>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="16"/>
+      <c r="B15" s="7">
         <v>10</v>
       </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="8">
-        <f>AVERAGE(DataExp1!Q4:Q13)</f>
-        <v>2.0470536852897636</v>
-      </c>
-      <c r="K11" s="8">
-        <f>AVERAGE(DataExp1!R4:R13)</f>
-        <v>0.42174105651815957</v>
-      </c>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B16" s="4">
         <v>1</v>
       </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="9">
-        <f>AVERAGE(DataExp1!T4:T13)</f>
-        <v>2.0194039548285878</v>
-      </c>
-      <c r="K12" s="9">
-        <f>AVERAGE(DataExp1!U4:U13)</f>
-        <v>0.37754673426285007</v>
-      </c>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
-      <c r="B13" s="10">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="5">
+        <f>AVERAGE(DataExp1!AK4:AK13)</f>
+        <v>34.552311810658352</v>
+      </c>
+      <c r="K16" s="5">
+        <f>AVERAGE(DataExp1!AL4:AL13)</f>
+        <v>4.575032042937762</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="13"/>
+      <c r="B17" s="4">
         <v>3</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="9">
-        <f>AVERAGE(DataExp1!V4:V13)</f>
-        <v>3.0323916470832399</v>
-      </c>
-      <c r="K13" s="9">
-        <f>AVERAGE(DataExp1!W4:W13)</f>
-        <v>0.65287517616761293</v>
-      </c>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
-      <c r="B14" s="10">
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="5">
+        <f>AVERAGE(DataExp1!AM4:AM14)</f>
+        <v>1.8560190453181431</v>
+      </c>
+      <c r="K17" s="5">
+        <f>AVERAGE(DataExp1!AN5:AN14)</f>
+        <v>0.34386357258632122</v>
+      </c>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
+      <c r="B18" s="4">
         <v>5</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="9">
-        <f>AVERAGE(DataExp1!X4:X13)</f>
-        <v>3.0970657292831891</v>
-      </c>
-      <c r="K14" s="9">
-        <f>AVERAGE(DataExp1!Y4:Y13)</f>
-        <v>0.65291309034907874</v>
-      </c>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
-      <c r="B15" s="10">
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="5">
+        <f>AVERAGE(DataExp1!AO4:AO13)</f>
+        <v>1.9127433590347436</v>
+      </c>
+      <c r="K18" s="5">
+        <f>AVERAGE(DataExp1!AP5:AP6)</f>
+        <v>0.35602585387596053</v>
+      </c>
+      <c r="L18" s="5">
+        <v>8.8376119113808799E-2</v>
+      </c>
+      <c r="M18" s="5">
+        <v>2.8023187480955202E-5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="4">
         <v>10</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="6">
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="5">
+        <f>AVERAGE(DataExp1!AQ4:AQ13)</f>
+        <v>1.9259347567178799</v>
+      </c>
+      <c r="K19" s="5">
+        <f>AVERAGE(DataExp1!AR4:AR13)</f>
+        <v>0.35326486945372448</v>
+      </c>
+      <c r="L19" s="5">
+        <v>8.81585941138084E-2</v>
+      </c>
+      <c r="M19" s="5">
+        <v>2.7971865110220399E-5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="8">
-        <f>AVERAGE(DataExp1!AC4:AC13)</f>
-        <v>34.552311810658352</v>
-      </c>
-      <c r="K16" s="8">
-        <f>AVERAGE(DataExp1!AD4:AD13)</f>
-        <v>4.575032042937762</v>
-      </c>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="6">
+      <c r="C20" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="13">
+        <v>66</v>
+      </c>
+      <c r="E20" s="13">
+        <v>66</v>
+      </c>
+      <c r="F20" s="13">
         <v>3</v>
       </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="8">
-        <f>AVERAGE(DataExp1!AE4:AE14)</f>
-        <v>1.8560190453181431</v>
-      </c>
-      <c r="K17" s="8">
-        <f>AVERAGE(DataExp1!AF5:AF14)</f>
-        <v>0.34386357258632122</v>
-      </c>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
-      <c r="B18" s="6">
+      <c r="G20" s="13">
+        <v>3</v>
+      </c>
+      <c r="H20" s="13">
+        <v>22</v>
+      </c>
+      <c r="I20" s="13">
+        <v>22</v>
+      </c>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="18"/>
+      <c r="B21" s="4">
+        <v>3</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="18"/>
+      <c r="B22" s="4">
         <v>5</v>
       </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="8">
-        <f>AVERAGE(DataExp1!AG4:AG13)</f>
-        <v>1.9127433590347436</v>
-      </c>
-      <c r="K18" s="8">
-        <f>AVERAGE(DataExp1!AH5:AH6)</f>
-        <v>0.35602585387596053</v>
-      </c>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="6">
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="18"/>
+      <c r="B23" s="4">
         <v>10</v>
       </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="8">
-        <f>AVERAGE(DataExp1!AI4:AI13)</f>
-        <v>1.9259347567178799</v>
-      </c>
-      <c r="K19" s="8">
-        <f>AVERAGE(DataExp1!AJ4:AJ13)</f>
-        <v>0.35326486945372448</v>
-      </c>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B24" s="10">
         <v>1</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="17"/>
+      <c r="B25" s="10">
+        <v>3</v>
+      </c>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="B26" s="10">
         <v>5</v>
       </c>
-      <c r="D20" s="14">
-        <v>66</v>
-      </c>
-      <c r="E20" s="14">
-        <v>66</v>
-      </c>
-      <c r="F20" s="14">
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="17"/>
+      <c r="B27" s="10">
+        <v>10</v>
+      </c>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="4">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="18"/>
+      <c r="B29" s="4">
         <v>3</v>
       </c>
-      <c r="G20" s="14">
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="18"/>
+      <c r="B30" s="4">
+        <v>5</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="18"/>
+      <c r="B31" s="11">
+        <v>10</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="10">
+        <v>1</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="33"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="10">
         <v>3</v>
       </c>
-      <c r="H20" s="14">
-        <v>22</v>
-      </c>
-      <c r="I20" s="14">
-        <v>22</v>
-      </c>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="16"/>
-      <c r="B21" s="6">
-        <v>3</v>
-      </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="16"/>
-      <c r="B22" s="6">
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="33"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="17"/>
+      <c r="B34" s="10">
         <v>5</v>
       </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="16"/>
-      <c r="B23" s="6">
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="33"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="17"/>
+      <c r="B35" s="10">
         <v>10</v>
       </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="19">
-        <v>1</v>
-      </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="21"/>
-      <c r="B25" s="19">
-        <v>3</v>
-      </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="21"/>
-      <c r="B26" s="19">
-        <v>5</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="21"/>
-      <c r="B27" s="19">
-        <v>10</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28" s="6">
-        <v>1</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="16"/>
-      <c r="B29" s="6">
-        <v>3</v>
-      </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="16"/>
-      <c r="B30" s="6">
-        <v>5</v>
-      </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="16"/>
-      <c r="B31" s="20">
-        <v>10</v>
-      </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" s="19">
-        <v>1</v>
-      </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="19"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="21"/>
-      <c r="B33" s="19">
-        <v>3</v>
-      </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="21"/>
-      <c r="B34" s="19">
-        <v>5</v>
-      </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="21"/>
-      <c r="B35" s="19">
-        <v>10</v>
-      </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="C4:C19"/>
-    <mergeCell ref="D4:D19"/>
-    <mergeCell ref="E4:E19"/>
-    <mergeCell ref="F4:F19"/>
-    <mergeCell ref="G4:G19"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A32:A35"/>
@@ -2721,29 +2968,22 @@
     <mergeCell ref="G20:G35"/>
     <mergeCell ref="H20:H35"/>
     <mergeCell ref="I20:I35"/>
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="C4:C19"/>
+    <mergeCell ref="D4:D19"/>
+    <mergeCell ref="E4:E19"/>
+    <mergeCell ref="F4:F19"/>
+    <mergeCell ref="G4:G19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A16C87A6682E6E4295773DFF29EAB41B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a3213889016ec1ec7c5b45183b07d2a5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xmlns:ns4="c7f849e2-0a63-4d53-be53-fb9d39becd19" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39cf848dedf08b05fa72a945c282372c" ns3:_="" ns4:_="">
     <xsd:import namespace="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
@@ -2968,10 +3208,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
+    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2994,20 +3262,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
-    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/documents/ExperimentData.xlsx
+++ b/documents/ExperimentData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1b2bcfbbb34c0c/Documents/GitHub/meliso/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="738" documentId="8_{D7059BC8-D0E2-41E7-A566-DBD48656E1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D523FF4C-3D2A-48EE-99C9-FAABFE3C05D8}"/>
+  <xr:revisionPtr revIDLastSave="740" documentId="8_{D7059BC8-D0E2-41E7-A566-DBD48656E1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E593162-A419-4081-AE2B-96F2A16DFCA5}"/>
   <bookViews>
     <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
   </bookViews>
@@ -294,26 +294,26 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -324,10 +324,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -340,20 +336,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -369,10 +369,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -705,68 +701,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="S1" s="14" t="s">
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="S1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AB1" s="14" t="s">
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="18"/>
+      <c r="Z1" s="18"/>
+      <c r="AB1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="AC1" s="14"/>
-      <c r="AD1" s="14"/>
-      <c r="AE1" s="14"/>
-      <c r="AF1" s="14"/>
-      <c r="AG1" s="14"/>
-      <c r="AH1" s="14"/>
-      <c r="AI1" s="14"/>
-      <c r="AK1" s="14" t="s">
+      <c r="AC1" s="18"/>
+      <c r="AD1" s="18"/>
+      <c r="AE1" s="18"/>
+      <c r="AF1" s="18"/>
+      <c r="AG1" s="18"/>
+      <c r="AH1" s="18"/>
+      <c r="AI1" s="18"/>
+      <c r="AK1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="AL1" s="14"/>
-      <c r="AM1" s="14"/>
-      <c r="AN1" s="14"/>
-      <c r="AO1" s="14"/>
-      <c r="AP1" s="14"/>
-      <c r="AQ1" s="14"/>
-      <c r="AR1" s="14"/>
+      <c r="AL1" s="18"/>
+      <c r="AM1" s="18"/>
+      <c r="AN1" s="18"/>
+      <c r="AO1" s="18"/>
+      <c r="AP1" s="18"/>
+      <c r="AQ1" s="18"/>
+      <c r="AR1" s="18"/>
     </row>
     <row r="2" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="19" t="s">
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="21"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="23"/>
       <c r="J2" s="24" t="s">
         <v>23</v>
       </c>
@@ -776,57 +772,57 @@
       <c r="N2" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="14"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="S2" s="13" t="s">
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+      <c r="S2" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13" t="s">
+      <c r="T2" s="19"/>
+      <c r="U2" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="13"/>
-      <c r="W2" s="12" t="s">
+      <c r="V2" s="19"/>
+      <c r="W2" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12" t="s">
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="Z2" s="12"/>
-      <c r="AB2" s="13" t="s">
+      <c r="Z2" s="20"/>
+      <c r="AB2" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="AC2" s="13"/>
-      <c r="AD2" s="13" t="s">
+      <c r="AC2" s="19"/>
+      <c r="AD2" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="AE2" s="13"/>
-      <c r="AF2" s="12" t="s">
+      <c r="AE2" s="19"/>
+      <c r="AF2" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="AG2" s="12"/>
-      <c r="AH2" s="12" t="s">
+      <c r="AG2" s="20"/>
+      <c r="AH2" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="AI2" s="12"/>
-      <c r="AK2" s="13" t="s">
+      <c r="AI2" s="20"/>
+      <c r="AK2" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="AL2" s="13"/>
-      <c r="AM2" s="13" t="s">
+      <c r="AL2" s="19"/>
+      <c r="AM2" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="AN2" s="13"/>
-      <c r="AO2" s="12" t="s">
+      <c r="AN2" s="19"/>
+      <c r="AO2" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="AP2" s="12"/>
-      <c r="AQ2" s="12" t="s">
+      <c r="AP2" s="20"/>
+      <c r="AQ2" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="AR2" s="12"/>
+      <c r="AR2" s="20"/>
     </row>
     <row r="3" spans="2:44" ht="45" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -981,10 +977,10 @@
       <c r="O4" s="6">
         <v>0.281035172507479</v>
       </c>
-      <c r="P4" s="23">
+      <c r="P4" s="13">
         <v>427.43972841419099</v>
       </c>
-      <c r="Q4" s="23">
+      <c r="Q4" s="13">
         <v>1.90857404909223E-3</v>
       </c>
       <c r="S4" s="5">
@@ -1091,8 +1087,8 @@
       <c r="O5" s="6">
         <v>0.27529653142885502</v>
       </c>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
       <c r="S5" s="5">
         <v>49.008992449178898</v>
       </c>
@@ -1197,8 +1193,8 @@
       <c r="O6" s="6">
         <v>0.29627600535638898</v>
       </c>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
       <c r="S6" s="5">
         <v>50.370043311847297</v>
       </c>
@@ -1303,8 +1299,8 @@
       <c r="O7" s="6">
         <v>0.26236662864990901</v>
       </c>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
       <c r="S7" s="5">
         <v>48.5283966162228</v>
       </c>
@@ -1405,8 +1401,8 @@
       <c r="O8" s="6">
         <v>0.17203410846221501</v>
       </c>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
       <c r="S8" s="5">
         <v>50.189180557709498</v>
       </c>
@@ -1507,8 +1503,8 @@
       <c r="O9" s="6">
         <v>0.16474922791581201</v>
       </c>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
       <c r="S9" s="5">
         <v>49.619431099961197</v>
       </c>
@@ -1609,8 +1605,8 @@
       <c r="O10" s="6">
         <v>0.27529653142885502</v>
       </c>
-      <c r="P10" s="23"/>
-      <c r="Q10" s="23"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
       <c r="S10" s="5">
         <v>50.370043311847297</v>
       </c>
@@ -1711,8 +1707,8 @@
       <c r="O11" s="6">
         <v>0.26236662864990901</v>
       </c>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
       <c r="S11" s="5">
         <v>50.6021835670551</v>
       </c>
@@ -1813,8 +1809,8 @@
       <c r="O12" s="6">
         <v>0.28993726071696102</v>
       </c>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
       <c r="S12" s="5">
         <v>48.5283966162228</v>
       </c>
@@ -1915,8 +1911,8 @@
       <c r="O13" s="6">
         <v>0.17697658502358601</v>
       </c>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
       <c r="S13" s="5">
         <v>50.813193764563998</v>
       </c>
@@ -2114,26 +2110,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B1:O1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="S1:Z1"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AB1:AI1"/>
+    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="AF2:AG2"/>
+    <mergeCell ref="AH2:AI2"/>
     <mergeCell ref="AK1:AR1"/>
     <mergeCell ref="AK2:AL2"/>
     <mergeCell ref="AM2:AN2"/>
     <mergeCell ref="AO2:AP2"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="AB1:AI1"/>
-    <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="AF2:AG2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="S1:Z1"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="B1:O1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="N2:Q2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2160,39 +2156,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="31"/>
     </row>
     <row r="2" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
     </row>
     <row r="3" spans="1:27" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -2228,18 +2224,18 @@
       <c r="K3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="L3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="M3" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="14">
         <v>1</v>
       </c>
       <c r="C4" s="30" t="s">
@@ -2279,17 +2275,17 @@
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
+      <c r="A5" s="33"/>
       <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
       <c r="J5" s="6">
         <f>AVERAGE(DataExp1!F4:F13)</f>
         <v>11.070752653739017</v>
@@ -2306,17 +2302,17 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
+      <c r="A6" s="33"/>
       <c r="B6" s="7">
         <v>5</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
       <c r="J6" s="6">
         <f>AVERAGE(DataExp1!J4:J13)</f>
         <v>4.7480516396353174</v>
@@ -2333,17 +2329,17 @@
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
+      <c r="A7" s="33"/>
       <c r="B7" s="7">
         <v>10</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
       <c r="J7" s="6">
         <f>AVERAGE(DataExp1!N4:N13)</f>
         <v>0.84932664663156276</v>
@@ -2360,19 +2356,19 @@
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="19" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="4">
         <v>1</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
       <c r="J8" s="5">
         <f>AVERAGE(DataExp1!S4:S13)</f>
         <v>49.821904185231844</v>
@@ -2389,17 +2385,17 @@
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
       <c r="J9" s="5">
         <f>AVERAGE(DataExp1!U4:U13)</f>
         <v>2.2585080679270888</v>
@@ -2416,17 +2412,17 @@
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
+      <c r="A10" s="19"/>
       <c r="B10" s="4">
         <v>5</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
       <c r="J10" s="5">
         <f>AVERAGE(DataExp1!W4:W13)</f>
         <v>2.4443213833989064</v>
@@ -2443,17 +2439,17 @@
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
+      <c r="A11" s="19"/>
       <c r="B11" s="4">
         <v>10</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
       <c r="J11" s="5">
         <f>AVERAGE(DataExp1!Y4:Y13)</f>
         <v>2.0470536852897636</v>
@@ -2470,19 +2466,19 @@
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
         <v>1</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
       <c r="J12" s="6">
         <f>AVERAGE(DataExp1!AB4:AB13)</f>
         <v>2.0194039548285878</v>
@@ -2495,17 +2491,17 @@
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
+      <c r="A13" s="33"/>
       <c r="B13" s="7">
         <v>3</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
       <c r="J13" s="6">
         <f>AVERAGE(DataExp1!AD4:AD13)</f>
         <v>3.0323916470832399</v>
@@ -2518,17 +2514,17 @@
       <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="16"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="7">
         <v>5</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
       <c r="J14" s="6">
         <f>AVERAGE(DataExp1!AF4:AF13)</f>
         <v>3.0970657292831891</v>
@@ -2541,36 +2537,36 @@
       <c r="M14" s="6"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
+      <c r="A15" s="33"/>
       <c r="B15" s="7">
         <v>10</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="19" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="4">
         <v>1</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
       <c r="J16" s="5">
         <f>AVERAGE(DataExp1!AK4:AK13)</f>
         <v>34.552311810658352</v>
@@ -2583,17 +2579,17 @@
       <c r="M16" s="5"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
+      <c r="A17" s="19"/>
       <c r="B17" s="4">
         <v>3</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
       <c r="J17" s="5">
         <f>AVERAGE(DataExp1!AM4:AM14)</f>
         <v>1.8560190453181431</v>
@@ -2602,21 +2598,25 @@
         <f>AVERAGE(DataExp1!AN5:AN14)</f>
         <v>0.34386357258632122</v>
       </c>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
+      <c r="L17" s="5">
+        <v>8.8175866468285097E-2</v>
+      </c>
+      <c r="M17" s="5">
+        <v>2.79669169855113E-5</v>
+      </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
+      <c r="A18" s="19"/>
       <c r="B18" s="4">
         <v>5</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
       <c r="J18" s="5">
         <f>AVERAGE(DataExp1!AO4:AO13)</f>
         <v>1.9127433590347436</v>
@@ -2633,17 +2633,17 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
+      <c r="A19" s="19"/>
       <c r="B19" s="4">
         <v>10</v>
       </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
       <c r="J19" s="5">
         <f>AVERAGE(DataExp1!AQ4:AQ13)</f>
         <v>1.9259347567178799</v>
@@ -2660,31 +2660,31 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="29" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="19">
         <v>66</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="19">
         <v>66</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="19">
         <v>3</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="19">
         <v>3</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="19">
         <v>22</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="19">
         <v>22</v>
       </c>
       <c r="J20" s="4"/>
@@ -2693,268 +2693,278 @@
       <c r="M20" s="5"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
+      <c r="A21" s="29"/>
       <c r="B21" s="4">
         <v>3</v>
       </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
+      <c r="A22" s="29"/>
       <c r="B22" s="4">
         <v>5</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="4">
         <v>10</v>
       </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="28" t="s">
         <v>14</v>
       </c>
       <c r="B24" s="10">
         <v>1</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="17"/>
+      <c r="A25" s="28"/>
       <c r="B25" s="10">
         <v>3</v>
       </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="33"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="17"/>
+      <c r="A26" s="28"/>
       <c r="B26" s="10">
         <v>5</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
+      <c r="A27" s="28"/>
       <c r="B27" s="10">
         <v>10</v>
       </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="17"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="29" t="s">
         <v>15</v>
       </c>
       <c r="B28" s="4">
         <v>1</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="18"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="4">
         <v>3</v>
       </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="18"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="4">
         <v>5</v>
       </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="11">
         <v>10</v>
       </c>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="28" t="s">
         <v>16</v>
       </c>
       <c r="B32" s="10">
         <v>1</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
-      <c r="L32" s="33"/>
-      <c r="M32" s="33"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="17"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
+      <c r="A33" s="28"/>
       <c r="B33" s="10">
         <v>3</v>
       </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
+      <c r="L33" s="17"/>
+      <c r="M33" s="17"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
+      <c r="A34" s="28"/>
       <c r="B34" s="10">
         <v>5</v>
       </c>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="33"/>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="17"/>
+      <c r="A35" s="28"/>
       <c r="B35" s="10">
         <v>10</v>
       </c>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
-      <c r="L35" s="33"/>
-      <c r="M35" s="33"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="C4:C19"/>
+    <mergeCell ref="D4:D19"/>
+    <mergeCell ref="E4:E19"/>
+    <mergeCell ref="F4:F19"/>
+    <mergeCell ref="G4:G19"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A32:A35"/>
@@ -2968,22 +2978,29 @@
     <mergeCell ref="G20:G35"/>
     <mergeCell ref="H20:H35"/>
     <mergeCell ref="I20:I35"/>
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="C4:C19"/>
-    <mergeCell ref="D4:D19"/>
-    <mergeCell ref="E4:E19"/>
-    <mergeCell ref="F4:F19"/>
-    <mergeCell ref="G4:G19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A16C87A6682E6E4295773DFF29EAB41B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a3213889016ec1ec7c5b45183b07d2a5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xmlns:ns4="c7f849e2-0a63-4d53-be53-fb9d39becd19" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39cf848dedf08b05fa72a945c282372c" ns3:_="" ns4:_="">
     <xsd:import namespace="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
@@ -3208,38 +3225,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
-    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3262,9 +3251,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
+    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/documents/ExperimentData.xlsx
+++ b/documents/ExperimentData.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1b2bcfbbb34c0c/Documents/GitHub/meliso/documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciusvo/Documents/GitHub/meliso/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="740" documentId="8_{D7059BC8-D0E2-41E7-A566-DBD48656E1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E593162-A419-4081-AE2B-96F2A16DFCA5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="1" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
   </bookViews>
   <sheets>
     <sheet name="DataExp1" sheetId="2" r:id="rId1"/>
     <sheet name="Experiment 1" sheetId="1" r:id="rId2"/>
+    <sheet name="Experiment 2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="28">
   <si>
     <t>MCA Rows</t>
   </si>
@@ -118,6 +119,9 @@
   </si>
   <si>
     <t>Acc. Write Energy (Mean)</t>
+  </si>
+  <si>
+    <t>Ag-aSi/TaOx-HfOx</t>
   </si>
 </sst>
 </file>
@@ -309,12 +313,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -336,14 +334,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -352,6 +347,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -689,18 +693,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB6579EC-3EC3-439D-9B94-319298E6C78E}">
   <dimension ref="B1:AR34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.42578125" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.5" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B1" s="18" t="s">
         <v>13</v>
       </c>
@@ -750,81 +754,81 @@
       <c r="AQ1" s="18"/>
       <c r="AR1" s="18"/>
     </row>
-    <row r="2" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B2" s="21" t="s">
+    <row r="2" spans="2:44" x14ac:dyDescent="0.2">
+      <c r="B2" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="21" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="24" t="s">
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="27" t="s">
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="25" t="s">
         <v>17</v>
       </c>
       <c r="O2" s="18"/>
       <c r="P2" s="18"/>
       <c r="Q2" s="18"/>
-      <c r="S2" s="19" t="s">
+      <c r="S2" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="T2" s="19"/>
-      <c r="U2" s="19" t="s">
+      <c r="T2" s="26"/>
+      <c r="U2" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="19"/>
-      <c r="W2" s="20" t="s">
+      <c r="V2" s="26"/>
+      <c r="W2" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20" t="s">
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="Z2" s="20"/>
-      <c r="AB2" s="19" t="s">
+      <c r="Z2" s="27"/>
+      <c r="AB2" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="AC2" s="19"/>
-      <c r="AD2" s="19" t="s">
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="AE2" s="19"/>
-      <c r="AF2" s="20" t="s">
+      <c r="AE2" s="26"/>
+      <c r="AF2" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="AG2" s="20"/>
-      <c r="AH2" s="20" t="s">
+      <c r="AG2" s="27"/>
+      <c r="AH2" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="AI2" s="20"/>
-      <c r="AK2" s="19" t="s">
+      <c r="AI2" s="27"/>
+      <c r="AK2" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="AL2" s="19"/>
-      <c r="AM2" s="19" t="s">
+      <c r="AL2" s="26"/>
+      <c r="AM2" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="AN2" s="19"/>
-      <c r="AO2" s="20" t="s">
+      <c r="AN2" s="26"/>
+      <c r="AO2" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="AP2" s="20"/>
-      <c r="AQ2" s="20" t="s">
+      <c r="AP2" s="27"/>
+      <c r="AQ2" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="AR2" s="20"/>
-    </row>
-    <row r="3" spans="2:44" ht="45" x14ac:dyDescent="0.25">
+      <c r="AR2" s="27"/>
+    </row>
+    <row r="3" spans="2:44" ht="48" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
         <v>21</v>
       </c>
@@ -946,7 +950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B4" s="5">
         <v>24.443761142859401</v>
       </c>
@@ -1056,7 +1060,7 @@
         <v>0.34574964955663201</v>
       </c>
     </row>
-    <row r="5" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B5" s="5">
         <v>21.768763521560601</v>
       </c>
@@ -1162,7 +1166,7 @@
         <v>0.35301643444209602</v>
       </c>
     </row>
-    <row r="6" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B6" s="5">
         <v>24.272210690591301</v>
       </c>
@@ -1268,7 +1272,7 @@
         <v>0.35731335216903298</v>
       </c>
     </row>
-    <row r="7" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B7" s="5">
         <v>24.404174573572501</v>
       </c>
@@ -1370,7 +1374,7 @@
         <v>0.35300853576487501</v>
       </c>
     </row>
-    <row r="8" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B8" s="5">
         <v>24.519392747918499</v>
       </c>
@@ -1472,7 +1476,7 @@
         <v>0.36071379860479102</v>
       </c>
     </row>
-    <row r="9" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B9" s="5">
         <v>24.310600989632899</v>
       </c>
@@ -1574,7 +1578,7 @@
         <v>0.35731730151554097</v>
       </c>
     </row>
-    <row r="10" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B10" s="5">
         <v>24.519392747918499</v>
       </c>
@@ -1676,7 +1680,7 @@
         <v>0.34945018620593998</v>
       </c>
     </row>
-    <row r="11" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B11" s="5">
         <v>21.996905724856099</v>
       </c>
@@ -1778,7 +1782,7 @@
         <v>0.34575359895052998</v>
       </c>
     </row>
-    <row r="12" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B12" s="5">
         <v>24.073944136969398</v>
       </c>
@@ -1880,7 +1884,7 @@
         <v>0.35300853576487501</v>
       </c>
     </row>
-    <row r="13" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B13" s="5">
         <v>24.073944136969398</v>
       </c>
@@ -1982,127 +1986,127 @@
         <v>0.35731730156293201</v>
       </c>
     </row>
-    <row r="14" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
     </row>
-    <row r="15" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
     </row>
-    <row r="16" spans="2:44" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -2110,26 +2114,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AK1:AR1"/>
+    <mergeCell ref="AK2:AL2"/>
+    <mergeCell ref="AM2:AN2"/>
+    <mergeCell ref="AO2:AP2"/>
+    <mergeCell ref="AQ2:AR2"/>
+    <mergeCell ref="AB1:AI1"/>
+    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="AF2:AG2"/>
+    <mergeCell ref="AH2:AI2"/>
+    <mergeCell ref="S1:Z1"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="Y2:Z2"/>
     <mergeCell ref="B1:O1"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="S1:Z1"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AB1:AI1"/>
-    <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="AF2:AG2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="AK1:AR1"/>
-    <mergeCell ref="AK2:AL2"/>
-    <mergeCell ref="AM2:AN2"/>
-    <mergeCell ref="AO2:AP2"/>
-    <mergeCell ref="AQ2:AR2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2138,59 +2142,60 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB2F127C-15E6-41A0-94B0-FA50F057125C}">
   <dimension ref="A1:AA35"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" style="8" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" style="8" customWidth="1"/>
+    <col min="13" max="13" width="16.1640625" style="8" customWidth="1"/>
+    <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="31"/>
-      <c r="Z1" s="31"/>
-      <c r="AA1" s="31"/>
-    </row>
-    <row r="2" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+    </row>
+    <row r="2" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="L2" s="15"/>
       <c r="M2" s="15"/>
     </row>
-    <row r="3" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -2231,32 +2236,32 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A4" s="29" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="14">
         <v>1</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="31">
         <v>66</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <v>66</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="31">
         <v>1</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="31">
         <v>1</v>
       </c>
-      <c r="H4" s="30">
+      <c r="H4" s="31">
         <v>66</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="31">
         <v>66</v>
       </c>
       <c r="J4" s="6">
@@ -2273,19 +2278,23 @@
       <c r="M4" s="8">
         <v>1.24324175218449E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
+      <c r="O4">
+        <f>L7/L19</f>
+        <v>4848.5315891311448</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A5" s="30"/>
       <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
       <c r="J5" s="6">
         <f>AVERAGE(DataExp1!F4:F13)</f>
         <v>11.070752653739017</v>
@@ -2300,19 +2309,23 @@
       <c r="M5" s="6">
         <v>1.8368430572894799E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="33"/>
+      <c r="O5">
+        <f>L7/L11</f>
+        <v>5.6020769715525622</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A6" s="30"/>
       <c r="B6" s="7">
         <v>5</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
       <c r="J6" s="6">
         <f>AVERAGE(DataExp1!J4:J13)</f>
         <v>4.7480516396353174</v>
@@ -2328,18 +2341,18 @@
         <v>1.8680991323063701E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="33"/>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A7" s="30"/>
       <c r="B7" s="7">
         <v>10</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
       <c r="J7" s="6">
         <f>AVERAGE(DataExp1!N4:N13)</f>
         <v>0.84932664663156276</v>
@@ -2355,20 +2368,20 @@
         <v>1.90857404909223E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A8" s="26" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="4">
         <v>1</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="26"/>
       <c r="J8" s="5">
         <f>AVERAGE(DataExp1!S4:S13)</f>
         <v>49.821904185231844</v>
@@ -2384,18 +2397,18 @@
         <v>1.8341564911519399E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="19"/>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A9" s="26"/>
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
       <c r="J9" s="5">
         <f>AVERAGE(DataExp1!U4:U13)</f>
         <v>2.2585080679270888</v>
@@ -2411,18 +2424,18 @@
         <v>3.8957965924184199E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="19"/>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A10" s="26"/>
       <c r="B10" s="4">
         <v>5</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
       <c r="J10" s="5">
         <f>AVERAGE(DataExp1!W4:W13)</f>
         <v>2.4443213833989064</v>
@@ -2438,18 +2451,18 @@
         <v>4.1758142847234302E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="19"/>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A11" s="26"/>
       <c r="B11" s="4">
         <v>10</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
       <c r="J11" s="5">
         <f>AVERAGE(DataExp1!Y4:Y13)</f>
         <v>2.0470536852897636</v>
@@ -2465,20 +2478,20 @@
         <v>4.0673431385843499E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="33" t="s">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A12" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
         <v>1</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
       <c r="J12" s="6">
         <f>AVERAGE(DataExp1!AB4:AB13)</f>
         <v>2.0194039548285878</v>
@@ -2490,18 +2503,18 @@
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A13" s="30"/>
       <c r="B13" s="7">
         <v>3</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
       <c r="J13" s="6">
         <f>AVERAGE(DataExp1!AD4:AD13)</f>
         <v>3.0323916470832399</v>
@@ -2513,18 +2526,18 @@
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="33"/>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A14" s="30"/>
       <c r="B14" s="7">
         <v>5</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
       <c r="J14" s="6">
         <f>AVERAGE(DataExp1!AF4:AF13)</f>
         <v>3.0970657292831891</v>
@@ -2536,37 +2549,37 @@
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="33"/>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A15" s="30"/>
       <c r="B15" s="7">
         <v>10</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A16" s="26" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="4">
         <v>1</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
       <c r="J16" s="5">
         <f>AVERAGE(DataExp1!AK4:AK13)</f>
         <v>34.552311810658352</v>
@@ -2577,19 +2590,23 @@
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="19"/>
+      <c r="P16">
+        <f>14.81/0.17</f>
+        <v>87.117647058823522</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17" s="26"/>
       <c r="B17" s="4">
         <v>3</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
       <c r="J17" s="5">
         <f>AVERAGE(DataExp1!AM4:AM14)</f>
         <v>1.8560190453181431</v>
@@ -2604,19 +2621,26 @@
       <c r="M17" s="5">
         <v>2.79669169855113E-5</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="19"/>
+      <c r="O17" t="s">
+        <v>27</v>
+      </c>
+      <c r="P17">
+        <f>M7/M19</f>
+        <v>68.231919522408703</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A18" s="26"/>
       <c r="B18" s="4">
         <v>5</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
       <c r="J18" s="5">
         <f>AVERAGE(DataExp1!AO4:AO13)</f>
         <v>1.9127433590347436</v>
@@ -2632,18 +2656,18 @@
         <v>2.8023187480955202E-5</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A19" s="26"/>
       <c r="B19" s="4">
         <v>10</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
       <c r="J19" s="5">
         <f>AVERAGE(DataExp1!AQ4:AQ13)</f>
         <v>1.9259347567178799</v>
@@ -2659,32 +2683,32 @@
         <v>2.7971865110220399E-5</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="29" t="s">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20" s="33" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="26">
         <v>66</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="26">
         <v>66</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="26">
         <v>3</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="26">
         <v>3</v>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="26">
         <v>22</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="26">
         <v>22</v>
       </c>
       <c r="J20" s="4"/>
@@ -2692,262 +2716,262 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="29"/>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21" s="33"/>
       <c r="B21" s="4">
         <v>3</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="29"/>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" s="33"/>
       <c r="B22" s="4">
         <v>5</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="29"/>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23" s="33"/>
       <c r="B23" s="4">
         <v>10</v>
       </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="28" t="s">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" s="32" t="s">
         <v>14</v>
       </c>
       <c r="B24" s="10">
         <v>1</v>
       </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="28"/>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A25" s="32"/>
       <c r="B25" s="10">
         <v>3</v>
       </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="28"/>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A26" s="32"/>
       <c r="B26" s="10">
         <v>5</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="28"/>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A27" s="32"/>
       <c r="B27" s="10">
         <v>10</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="29" t="s">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A28" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B28" s="4">
         <v>1</v>
       </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="29"/>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A29" s="33"/>
       <c r="B29" s="4">
         <v>3</v>
       </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="29"/>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A30" s="33"/>
       <c r="B30" s="4">
         <v>5</v>
       </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="29"/>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A31" s="33"/>
       <c r="B31" s="11">
         <v>10</v>
       </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="5"/>
       <c r="M31" s="5"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="28" t="s">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32" s="32" t="s">
         <v>16</v>
       </c>
       <c r="B32" s="10">
         <v>1</v>
       </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="28"/>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A33" s="32"/>
       <c r="B33" s="10">
         <v>3</v>
       </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="28"/>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34" s="32"/>
       <c r="B34" s="10">
         <v>5</v>
       </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="28"/>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A35" s="32"/>
       <c r="B35" s="10">
         <v>10</v>
       </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
       <c r="L35" s="17"/>
@@ -2955,16 +2979,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="C4:C19"/>
-    <mergeCell ref="D4:D19"/>
-    <mergeCell ref="E4:E19"/>
-    <mergeCell ref="F4:F19"/>
-    <mergeCell ref="G4:G19"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A32:A35"/>
@@ -2978,29 +2992,64 @@
     <mergeCell ref="G20:G35"/>
     <mergeCell ref="H20:H35"/>
     <mergeCell ref="I20:I35"/>
+    <mergeCell ref="A1:AA1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="C4:C19"/>
+    <mergeCell ref="D4:D19"/>
+    <mergeCell ref="E4:E19"/>
+    <mergeCell ref="F4:F19"/>
+    <mergeCell ref="G4:G19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E80E6C9-07DF-4341-ACF2-5E614276889D}">
+  <dimension ref="A1:AA1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="28"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:AA1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A16C87A6682E6E4295773DFF29EAB41B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a3213889016ec1ec7c5b45183b07d2a5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xmlns:ns4="c7f849e2-0a63-4d53-be53-fb9d39becd19" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39cf848dedf08b05fa72a945c282372c" ns3:_="" ns4:_="">
     <xsd:import namespace="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
@@ -3225,10 +3274,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
+    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3251,20 +3328,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
-    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/documents/ExperimentData.xlsx
+++ b/documents/ExperimentData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luciusvo/Documents/GitHub/meliso/documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1b2bcfbbb34c0c/Documents/GitHub/meliso/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CD4EDAE-911B-4936-956E-33EFF2ADA7C1}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="1" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
   </bookViews>
   <sheets>
     <sheet name="DataExp1" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="25">
   <si>
     <t>MCA Rows</t>
   </si>
@@ -112,16 +112,7 @@
     <t>N = 5</t>
   </si>
   <si>
-    <t>Write Latency</t>
-  </si>
-  <si>
-    <t>Write Energy</t>
-  </si>
-  <si>
     <t>Acc. Write Energy (Mean)</t>
-  </si>
-  <si>
-    <t>Ag-aSi/TaOx-HfOx</t>
   </si>
 </sst>
 </file>
@@ -167,7 +158,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -225,59 +216,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -298,10 +241,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -313,32 +252,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -349,15 +276,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -692,143 +623,124 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB6579EC-3EC3-439D-9B94-319298E6C78E}">
-  <dimension ref="B1:AR34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:AJ34"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.5" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:44" x14ac:dyDescent="0.2">
-      <c r="B1" s="18" t="s">
+    <row r="1" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B1" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="S1" s="18" t="s">
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="K1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="18"/>
-      <c r="Z1" s="18"/>
-      <c r="AB1" s="18" t="s">
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="T1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="AC1" s="18"/>
-      <c r="AD1" s="18"/>
-      <c r="AE1" s="18"/>
-      <c r="AF1" s="18"/>
-      <c r="AG1" s="18"/>
-      <c r="AH1" s="18"/>
-      <c r="AI1" s="18"/>
-      <c r="AK1" s="18" t="s">
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AC1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="AL1" s="18"/>
-      <c r="AM1" s="18"/>
-      <c r="AN1" s="18"/>
-      <c r="AO1" s="18"/>
-      <c r="AP1" s="18"/>
-      <c r="AQ1" s="18"/>
-      <c r="AR1" s="18"/>
-    </row>
-    <row r="2" spans="2:44" x14ac:dyDescent="0.2">
-      <c r="B2" s="19" t="s">
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="16"/>
+      <c r="AF1" s="16"/>
+      <c r="AG1" s="16"/>
+      <c r="AH1" s="16"/>
+      <c r="AI1" s="16"/>
+      <c r="AJ1" s="16"/>
+    </row>
+    <row r="2" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="19" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="22" t="s">
+      <c r="E2" s="17"/>
+      <c r="F2" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="25" t="s">
+      <c r="G2" s="18"/>
+      <c r="H2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="K2" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="17"/>
+      <c r="O2" s="18" t="s">
+        <v>23</v>
+      </c>
       <c r="P2" s="18"/>
-      <c r="Q2" s="18"/>
-      <c r="S2" s="26" t="s">
+      <c r="Q2" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="18"/>
+      <c r="T2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26" t="s">
+      <c r="U2" s="17"/>
+      <c r="V2" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="26"/>
-      <c r="W2" s="27" t="s">
+      <c r="W2" s="17"/>
+      <c r="X2" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="27"/>
-      <c r="Y2" s="27" t="s">
+      <c r="Y2" s="18"/>
+      <c r="Z2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="Z2" s="27"/>
-      <c r="AB2" s="26" t="s">
+      <c r="AA2" s="18"/>
+      <c r="AC2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="AC2" s="26"/>
-      <c r="AD2" s="26" t="s">
+      <c r="AD2" s="17"/>
+      <c r="AE2" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="AE2" s="26"/>
-      <c r="AF2" s="27" t="s">
+      <c r="AF2" s="17"/>
+      <c r="AG2" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="AG2" s="27"/>
-      <c r="AH2" s="27" t="s">
+      <c r="AH2" s="18"/>
+      <c r="AI2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="AI2" s="27"/>
-      <c r="AK2" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="AL2" s="26"/>
-      <c r="AM2" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="AN2" s="26"/>
-      <c r="AO2" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="AP2" s="27"/>
-      <c r="AQ2" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="AR2" s="27"/>
-    </row>
-    <row r="3" spans="2:44" ht="48" x14ac:dyDescent="0.2">
+      <c r="AJ2" s="18"/>
+    </row>
+    <row r="3" spans="2:36" ht="45" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>21</v>
       </c>
@@ -836,1304 +748,1182 @@
         <v>9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="I3" s="9" t="s">
         <v>9</v>
       </c>
+      <c r="K3" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="L3" s="3" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="9" t="s">
         <v>21</v>
       </c>
+      <c r="N3" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="O3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="S3" s="3" t="s">
+      <c r="Q3" s="9" t="s">
         <v>21</v>
       </c>
+      <c r="R3" s="9" t="s">
+        <v>9</v>
+      </c>
       <c r="T3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="U3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="V3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="W3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="W3" s="9" t="s">
+      <c r="X3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="Y3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="Y3" s="9" t="s">
+      <c r="Z3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="9" t="s">
+      <c r="AA3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AC3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AC3" s="3" t="s">
+      <c r="AD3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AE3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AF3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AF3" s="9" t="s">
+      <c r="AG3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="AG3" s="9" t="s">
+      <c r="AH3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="AH3" s="9" t="s">
+      <c r="AI3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="AI3" s="9" t="s">
+      <c r="AJ3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="AK3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AL3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AM3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="AN3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AP3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AQ3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="AR3" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="2:44" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B4" s="5">
         <v>24.443761142859401</v>
       </c>
       <c r="C4" s="5">
         <v>3.3744526857264301</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6">
+      <c r="D4" s="6">
         <v>11.146140000613499</v>
       </c>
-      <c r="G4" s="6">
+      <c r="E4" s="6">
         <v>1.68778800506088</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="5">
+      <c r="F4" s="5">
         <v>5.0263956831744903</v>
       </c>
+      <c r="G4" s="5">
+        <v>0.90170831675261998</v>
+      </c>
+      <c r="H4" s="6">
+        <v>1.0386527872326301</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0.281035172507479</v>
+      </c>
       <c r="K4" s="5">
-        <v>0.90170831675261998</v>
-      </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
+        <v>50.189180557709498</v>
+      </c>
+      <c r="L4" s="5">
+        <v>6.8272041826728298</v>
+      </c>
+      <c r="M4" s="6">
+        <v>2.40398255283031</v>
+      </c>
       <c r="N4" s="6">
-        <v>1.0386527872326301</v>
-      </c>
-      <c r="O4" s="6">
-        <v>0.281035172507479</v>
-      </c>
-      <c r="P4" s="13">
-        <v>427.43972841419099</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>1.90857404909223E-3</v>
-      </c>
-      <c r="S4" s="5">
-        <v>50.189180557709498</v>
+        <v>0.494699860082361</v>
+      </c>
+      <c r="O4" s="5">
+        <v>2.5208897211674199</v>
+      </c>
+      <c r="P4" s="5">
+        <v>0.47344483768397699</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>1.34621453385329</v>
+      </c>
+      <c r="R4" s="6">
+        <v>0.35832775281353502</v>
       </c>
       <c r="T4" s="5">
-        <v>6.8272041826728298</v>
-      </c>
-      <c r="U4" s="6">
-        <v>2.40398255283031</v>
+        <v>2.0282019718480502</v>
+      </c>
+      <c r="U4" s="5">
+        <v>0.37754673426285001</v>
       </c>
       <c r="V4" s="6">
-        <v>0.494699860082361</v>
-      </c>
-      <c r="W4" s="5">
-        <v>2.5208897211674199</v>
+        <v>2.93314349751103</v>
+      </c>
+      <c r="W4" s="6">
+        <v>0.65213375302212495</v>
       </c>
       <c r="X4" s="5">
-        <v>0.47344483768397699</v>
-      </c>
-      <c r="Y4" s="6">
-        <v>1.34621453385329</v>
+        <v>3.1835707328913601</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>0.65565129784223597</v>
       </c>
       <c r="Z4" s="6">
-        <v>0.35832775281353502</v>
-      </c>
-      <c r="AB4" s="5">
-        <v>2.0282019718480502</v>
+        <v>3.0446059739842699</v>
+      </c>
+      <c r="AA4" s="6">
+        <v>0.65226013362701096</v>
       </c>
       <c r="AC4" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD4" s="6">
-        <v>2.93314349751103</v>
+        <v>34.570056762068198</v>
+      </c>
+      <c r="AD4" s="5">
+        <v>4.5778664577056496</v>
       </c>
       <c r="AE4" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AF4" s="5">
-        <v>3.1835707328913601</v>
+        <v>1.8250170991933701</v>
+      </c>
+      <c r="AF4" s="6">
+        <v>0.33633033357449799</v>
       </c>
       <c r="AG4" s="5">
-        <v>0.65565129784223597</v>
-      </c>
-      <c r="AH4" s="6">
-        <v>3.0446059739842699</v>
+        <v>1.8523706039791701</v>
+      </c>
+      <c r="AH4" s="5">
+        <v>0.34156715764353801</v>
       </c>
       <c r="AI4" s="6">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AK4" s="5">
-        <v>34.570056762068198</v>
-      </c>
-      <c r="AL4" s="5">
-        <v>4.5778664577056496</v>
-      </c>
-      <c r="AM4" s="6">
-        <v>1.8250170991933701</v>
-      </c>
-      <c r="AN4" s="6">
-        <v>0.33633033357449799</v>
-      </c>
-      <c r="AO4" s="5">
-        <v>1.8523706039791701</v>
-      </c>
-      <c r="AP4" s="5">
-        <v>0.34156715764353801</v>
-      </c>
-      <c r="AQ4" s="6">
         <v>1.8795419666048101</v>
       </c>
-      <c r="AR4" s="6">
+      <c r="AJ4" s="6">
         <v>0.34574964955663201</v>
       </c>
     </row>
-    <row r="5" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B5" s="5">
         <v>21.768763521560601</v>
       </c>
       <c r="C5" s="5">
         <v>3.1865062401780699</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="6">
+      <c r="D5" s="6">
         <v>10.978647285226099</v>
       </c>
-      <c r="G5" s="6">
+      <c r="E5" s="6">
         <v>1.7065269254956801</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="5">
+      <c r="F5" s="5">
         <v>4.85409002254627</v>
       </c>
+      <c r="G5" s="5">
+        <v>0.80897913982258796</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0.89008783875792397</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0.27529653142885502</v>
+      </c>
       <c r="K5" s="5">
-        <v>0.80897913982258796</v>
-      </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+        <v>49.008992449178898</v>
+      </c>
+      <c r="L5" s="5">
+        <v>6.5588284593994697</v>
+      </c>
+      <c r="M5" s="6">
+        <v>1.6098328308093</v>
+      </c>
       <c r="N5" s="6">
-        <v>0.89008783875792397</v>
-      </c>
-      <c r="O5" s="6">
-        <v>0.27529653142885502</v>
-      </c>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="S5" s="5">
-        <v>49.008992449178898</v>
+        <v>0.35390275267126498</v>
+      </c>
+      <c r="O5" s="5">
+        <v>2.6847186811052599</v>
+      </c>
+      <c r="P5" s="5">
+        <v>0.49866574556051502</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>2.7075638424040802</v>
+      </c>
+      <c r="R5" s="6">
+        <v>0.55112744515069301</v>
       </c>
       <c r="T5" s="5">
-        <v>6.5588284593994697</v>
-      </c>
-      <c r="U5" s="6">
-        <v>1.6098328308093</v>
+        <v>2.0576101229880499</v>
+      </c>
+      <c r="U5" s="5">
+        <v>0.37754673426285001</v>
       </c>
       <c r="V5" s="6">
-        <v>0.35390275267126498</v>
-      </c>
-      <c r="W5" s="5">
-        <v>2.6847186811052599</v>
+        <v>3.0231717517272201</v>
+      </c>
+      <c r="W5" s="6">
+        <v>0.65213375302212495</v>
       </c>
       <c r="X5" s="5">
-        <v>0.49866574556051502</v>
-      </c>
-      <c r="Y5" s="6">
-        <v>2.7075638424040802</v>
+        <v>3.0014742636059601</v>
+      </c>
+      <c r="Y5" s="5">
+        <v>0.65213375302212495</v>
       </c>
       <c r="Z5" s="6">
-        <v>0.55112744515069301</v>
-      </c>
-      <c r="AB5" s="5">
-        <v>2.0576101229880499</v>
+        <v>3.0732721507638598</v>
+      </c>
+      <c r="AA5" s="6">
+        <v>0.65213375302212495</v>
       </c>
       <c r="AC5" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD5" s="6">
-        <v>3.0231717517272201</v>
+        <v>34.554127832915199</v>
+      </c>
+      <c r="AD5" s="5">
+        <v>4.5660618080018196</v>
       </c>
       <c r="AE5" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AF5" s="5">
-        <v>3.0014742636059601</v>
+        <v>1.96093445188255</v>
+      </c>
+      <c r="AF5" s="6">
+        <v>0.35374707690719498</v>
       </c>
       <c r="AG5" s="5">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AH5" s="6">
-        <v>3.0732721507638598</v>
+        <v>1.9641721709049</v>
+      </c>
+      <c r="AH5" s="5">
+        <v>0.36261738420721501</v>
       </c>
       <c r="AI5" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AK5" s="5">
-        <v>34.554127832915199</v>
-      </c>
-      <c r="AL5" s="5">
-        <v>4.5660618080018196</v>
-      </c>
-      <c r="AM5" s="6">
-        <v>1.96093445188255</v>
-      </c>
-      <c r="AN5" s="6">
-        <v>0.35374707690719498</v>
-      </c>
-      <c r="AO5" s="5">
-        <v>1.9641721709049</v>
-      </c>
-      <c r="AP5" s="5">
-        <v>0.36261738420721501</v>
-      </c>
-      <c r="AQ5" s="6">
         <v>1.91781862598536</v>
       </c>
-      <c r="AR5" s="6">
+      <c r="AJ5" s="6">
         <v>0.35301643444209602</v>
       </c>
     </row>
-    <row r="6" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B6" s="5">
         <v>24.272210690591301</v>
       </c>
       <c r="C6" s="5">
         <v>3.3054398403598002</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="6">
+      <c r="D6" s="6">
         <v>11.131989491819301</v>
       </c>
-      <c r="G6" s="6">
+      <c r="E6" s="6">
         <v>1.68616441676978</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="5">
+      <c r="F6" s="5">
         <v>4.9373714864782201</v>
       </c>
+      <c r="G6" s="5">
+        <v>0.89188987256264995</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1.0114258900419599</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0.29627600535638898</v>
+      </c>
       <c r="K6" s="5">
-        <v>0.89188987256264995</v>
-      </c>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
+        <v>50.370043311847297</v>
+      </c>
+      <c r="L6" s="5">
+        <v>6.8266682265390397</v>
+      </c>
+      <c r="M6" s="6">
+        <v>3.31366070223083</v>
+      </c>
       <c r="N6" s="6">
-        <v>1.0114258900419599</v>
-      </c>
-      <c r="O6" s="6">
-        <v>0.29627600535638898</v>
-      </c>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="S6" s="5">
-        <v>50.370043311847297</v>
+        <v>0.59823315379531405</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1.8698821640777401</v>
+      </c>
+      <c r="P6" s="5">
+        <v>0.36723080126573698</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>2.4706305240653101</v>
+      </c>
+      <c r="R6" s="6">
+        <v>0.47413541013360899</v>
       </c>
       <c r="T6" s="5">
-        <v>6.8266682265390397</v>
-      </c>
-      <c r="U6" s="6">
-        <v>3.31366070223083</v>
+        <v>2.0124832402399999</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0.37754673426285001</v>
       </c>
       <c r="V6" s="6">
-        <v>0.59823315379531405</v>
-      </c>
-      <c r="W6" s="5">
-        <v>1.8698821640777401</v>
+        <v>3.1835707328913601</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.65565129784223597</v>
       </c>
       <c r="X6" s="5">
-        <v>0.36723080126573698</v>
-      </c>
-      <c r="Y6" s="6">
-        <v>2.4706305240653101</v>
+        <v>3.0052609093097602</v>
+      </c>
+      <c r="Y6" s="5">
+        <v>0.65213375302212495</v>
       </c>
       <c r="Z6" s="6">
-        <v>0.47413541013360899</v>
-      </c>
-      <c r="AB6" s="5">
-        <v>2.0124832402399999</v>
+        <v>2.9332438502332301</v>
+      </c>
+      <c r="AA6" s="6">
+        <v>0.65213375302212495</v>
       </c>
       <c r="AC6" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD6" s="6">
-        <v>3.1835707328913601</v>
+        <v>34.586395368105499</v>
+      </c>
+      <c r="AD6" s="5">
+        <v>4.5775860505016004</v>
       </c>
       <c r="AE6" s="6">
-        <v>0.65565129784223597</v>
-      </c>
-      <c r="AF6" s="5">
-        <v>3.0052609093097602</v>
+        <v>1.88217908842425</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0.35140505638671998</v>
       </c>
       <c r="AG6" s="5">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AH6" s="6">
-        <v>2.9332438502332301</v>
+        <v>1.8959378968298899</v>
+      </c>
+      <c r="AH6" s="5">
+        <v>0.34943432354470599</v>
       </c>
       <c r="AI6" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AK6" s="5">
-        <v>34.586395368105499</v>
-      </c>
-      <c r="AL6" s="5">
-        <v>4.5775860505016004</v>
-      </c>
-      <c r="AM6" s="6">
-        <v>1.88217908842425</v>
-      </c>
-      <c r="AN6" s="6">
-        <v>0.35140505638671998</v>
-      </c>
-      <c r="AO6" s="5">
-        <v>1.8959378968298899</v>
-      </c>
-      <c r="AP6" s="5">
-        <v>0.34943432354470599</v>
-      </c>
-      <c r="AQ6" s="6">
         <v>1.96427586073906</v>
       </c>
-      <c r="AR6" s="6">
+      <c r="AJ6" s="6">
         <v>0.35731335216903298</v>
       </c>
     </row>
-    <row r="7" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>24.404174573572501</v>
       </c>
       <c r="C7" s="5">
         <v>3.3186837088307102</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6">
+      <c r="D7" s="6">
         <v>10.9557705531107</v>
       </c>
-      <c r="G7" s="6">
+      <c r="E7" s="6">
         <v>1.57213037578915</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="5">
+      <c r="F7" s="5">
         <v>4.7911793814388997</v>
       </c>
+      <c r="G7" s="5">
+        <v>0.81751166683242105</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0.95254623904054903</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.26236662864990901</v>
+      </c>
       <c r="K7" s="5">
-        <v>0.81751166683242105</v>
-      </c>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
+        <v>48.5283966162228</v>
+      </c>
+      <c r="L7" s="5">
+        <v>6.39532451008645</v>
+      </c>
+      <c r="M7" s="6">
+        <v>2.3974738662768198</v>
+      </c>
       <c r="N7" s="6">
-        <v>0.95254623904054903</v>
-      </c>
-      <c r="O7" s="6">
-        <v>0.26236662864990901</v>
-      </c>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="S7" s="5">
-        <v>48.5283966162228</v>
+        <v>0.49437600947429899</v>
+      </c>
+      <c r="O7" s="5">
+        <v>2.8090651842160401</v>
+      </c>
+      <c r="P7" s="5">
+        <v>0.55561814716228497</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>1.9235703445824599</v>
+      </c>
+      <c r="R7" s="6">
+        <v>0.37579443485147102</v>
       </c>
       <c r="T7" s="5">
-        <v>6.39532451008645</v>
-      </c>
-      <c r="U7" s="6">
-        <v>2.3974738662768198</v>
+        <v>1.98733133553576</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0.37754673426285001</v>
       </c>
       <c r="V7" s="6">
-        <v>0.49437600947429899</v>
-      </c>
-      <c r="W7" s="5">
-        <v>2.8090651842160401</v>
+        <v>2.9709094694099698</v>
+      </c>
+      <c r="W7" s="6">
+        <v>0.65213375302212495</v>
       </c>
       <c r="X7" s="5">
-        <v>0.55561814716228497</v>
-      </c>
-      <c r="Y7" s="6">
-        <v>1.9235703445824599</v>
+        <v>3.1234714223794802</v>
+      </c>
+      <c r="Y7" s="5">
+        <v>0.65226013362701096</v>
       </c>
       <c r="Z7" s="6">
-        <v>0.37579443485147102</v>
-      </c>
-      <c r="AB7" s="5">
-        <v>1.98733133553576</v>
+        <v>2.9332438502332301</v>
+      </c>
+      <c r="AA7" s="6">
+        <v>0.65213375302212495</v>
       </c>
       <c r="AC7" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD7" s="6">
-        <v>2.9709094694099698</v>
+        <v>34.474323231873001</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>4.5812551646225703</v>
       </c>
       <c r="AE7" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AF7" s="5">
-        <v>3.1234714223794802</v>
+        <v>1.88221703832479</v>
+      </c>
+      <c r="AF7" s="6">
+        <v>0.35140505652889598</v>
       </c>
       <c r="AG7" s="5">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AH7" s="6"/>
-      <c r="AI7" s="6"/>
-      <c r="AK7" s="5">
-        <v>34.474323231873001</v>
-      </c>
-      <c r="AL7" s="5">
-        <v>4.5812551646225703</v>
-      </c>
-      <c r="AM7" s="6">
-        <v>1.88221703832479</v>
-      </c>
-      <c r="AN7" s="6">
-        <v>0.35140505652889598</v>
-      </c>
-      <c r="AO7" s="5">
         <v>1.8654391378277699</v>
       </c>
-      <c r="AP7" s="5">
+      <c r="AH7" s="5">
         <v>0.35136993223547403</v>
       </c>
-      <c r="AQ7" s="6">
+      <c r="AI7" s="6">
         <v>1.9178899634194899</v>
       </c>
-      <c r="AR7" s="6">
+      <c r="AJ7" s="6">
         <v>0.35300853576487501</v>
       </c>
     </row>
-    <row r="8" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>24.519392747918499</v>
       </c>
       <c r="C8" s="5">
         <v>3.3765146340410901</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="6">
+      <c r="D8" s="6">
         <v>11.084394304570299</v>
       </c>
-      <c r="G8" s="6">
+      <c r="E8" s="6">
         <v>1.71086338931697</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="5">
+      <c r="F8" s="5">
         <v>4.5716851890135404</v>
       </c>
+      <c r="G8" s="5">
+        <v>0.78488713802412502</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.59342344244794798</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.17203410846221501</v>
+      </c>
       <c r="K8" s="5">
-        <v>0.78488713802412502</v>
-      </c>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
+        <v>50.189180557709498</v>
+      </c>
+      <c r="L8" s="5">
+        <v>6.8272041826728298</v>
+      </c>
+      <c r="M8" s="6">
+        <v>2.3363436265518498</v>
+      </c>
       <c r="N8" s="6">
-        <v>0.59342344244794798</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0.17203410846221501</v>
-      </c>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="S8" s="5">
-        <v>50.189180557709498</v>
+        <v>0.49525277741667301</v>
+      </c>
+      <c r="O8" s="5">
+        <v>3.2921811589554202</v>
+      </c>
+      <c r="P8" s="5">
+        <v>0.61038119286221504</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>2.39747268966476</v>
+      </c>
+      <c r="R8" s="6">
+        <v>0.479906115601407</v>
       </c>
       <c r="T8" s="5">
-        <v>6.8272041826728298</v>
-      </c>
-      <c r="U8" s="6">
-        <v>2.3363436265518498</v>
+        <v>2.0045866890630801</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0.37754673426285001</v>
       </c>
       <c r="V8" s="6">
-        <v>0.49525277741667301</v>
-      </c>
-      <c r="W8" s="5">
-        <v>3.2921811589554202</v>
+        <v>2.8887491003138202</v>
+      </c>
+      <c r="W8" s="6">
+        <v>0.65213375302212495</v>
       </c>
       <c r="X8" s="5">
-        <v>0.61038119286221504</v>
-      </c>
-      <c r="Y8" s="6">
-        <v>2.39747268966476</v>
+        <v>3.1300087680066402</v>
+      </c>
+      <c r="Y8" s="5">
+        <v>0.65226013362701096</v>
       </c>
       <c r="Z8" s="6">
-        <v>0.479906115601407</v>
-      </c>
-      <c r="AB8" s="5">
-        <v>2.0045866890630801</v>
+        <v>3.0895272691364801</v>
+      </c>
+      <c r="AA8" s="6">
+        <v>0.65226013362701096</v>
       </c>
       <c r="AC8" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD8" s="6">
-        <v>2.8887491003138202</v>
+        <v>34.482423779545499</v>
+      </c>
+      <c r="AD8" s="5">
+        <v>4.5801967278307698</v>
       </c>
       <c r="AE8" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AF8" s="5">
-        <v>3.1300087680066402</v>
+        <v>1.8315258657560201</v>
+      </c>
+      <c r="AF8" s="6">
+        <v>0.34577767622515698</v>
       </c>
       <c r="AG8" s="5">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AH8" s="6"/>
-      <c r="AI8" s="6"/>
-      <c r="AK8" s="5">
-        <v>34.482423779545499</v>
-      </c>
-      <c r="AL8" s="5">
-        <v>4.5801967278307698</v>
-      </c>
-      <c r="AM8" s="6">
-        <v>1.8315258657560201</v>
-      </c>
-      <c r="AN8" s="6">
-        <v>0.34577767622515698</v>
-      </c>
-      <c r="AO8" s="5">
         <v>1.8523461079911401</v>
       </c>
-      <c r="AP8" s="5">
+      <c r="AH8" s="5">
         <v>0.34156715758035</v>
       </c>
-      <c r="AQ8" s="6">
+      <c r="AI8" s="6">
         <v>1.94458113911453</v>
       </c>
-      <c r="AR8" s="6">
+      <c r="AJ8" s="6">
         <v>0.36071379860479102</v>
       </c>
     </row>
-    <row r="9" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>24.310600989632899</v>
       </c>
       <c r="C9" s="5">
         <v>3.3225698262557399</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6">
+      <c r="D9" s="6">
         <v>11.078199731004901</v>
       </c>
-      <c r="G9" s="6">
+      <c r="E9" s="6">
         <v>1.65069524058359</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="5">
+      <c r="F9" s="5">
         <v>4.9807010405869097</v>
       </c>
+      <c r="G9" s="5">
+        <v>0.92921451381373998</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.56505155768495896</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0.16474922791581201</v>
+      </c>
       <c r="K9" s="5">
-        <v>0.92921451381373998</v>
-      </c>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
+        <v>49.619431099961197</v>
+      </c>
+      <c r="L9" s="5">
+        <v>6.6224281863214802</v>
+      </c>
+      <c r="M9" s="6">
+        <v>2.06027858560702</v>
+      </c>
       <c r="N9" s="6">
-        <v>0.56505155768495896</v>
-      </c>
-      <c r="O9" s="6">
-        <v>0.16474922791581201</v>
-      </c>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="S9" s="5">
-        <v>49.619431099961197</v>
+        <v>0.41902119187009701</v>
+      </c>
+      <c r="O9" s="5">
+        <v>2.1176598714663699</v>
+      </c>
+      <c r="P9" s="5">
+        <v>0.420783326797598</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>1.05066650115089</v>
+      </c>
+      <c r="R9" s="6">
+        <v>0.25434177251207701</v>
       </c>
       <c r="T9" s="5">
-        <v>6.6224281863214802</v>
-      </c>
-      <c r="U9" s="6">
-        <v>2.06027858560702</v>
+        <v>2.03035231561176</v>
+      </c>
+      <c r="U9" s="5">
+        <v>0.37754673426285001</v>
       </c>
       <c r="V9" s="6">
-        <v>0.41902119187009701</v>
-      </c>
-      <c r="W9" s="5">
-        <v>2.1176598714663699</v>
+        <v>3.0233946110574101</v>
+      </c>
+      <c r="W9" s="6">
+        <v>0.65226013362701096</v>
       </c>
       <c r="X9" s="5">
-        <v>0.420783326797598</v>
-      </c>
-      <c r="Y9" s="6">
-        <v>1.05066650115089</v>
+        <v>3.0222659675151302</v>
+      </c>
+      <c r="Y9" s="5">
+        <v>0.65226013362701096</v>
       </c>
       <c r="Z9" s="6">
-        <v>0.25434177251207701</v>
-      </c>
-      <c r="AB9" s="5">
-        <v>2.03035231561176</v>
+        <v>3.0231717517272201</v>
+      </c>
+      <c r="AA9" s="6">
+        <v>0.65213375302212495</v>
       </c>
       <c r="AC9" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD9" s="6">
-        <v>3.0233946110574101</v>
+        <v>34.570056762068198</v>
+      </c>
+      <c r="AD9" s="5">
+        <v>4.5778664577056496</v>
       </c>
       <c r="AE9" s="6">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AF9" s="5">
-        <v>3.0222659675151302</v>
+        <v>1.86147110489288</v>
+      </c>
+      <c r="AF9" s="6">
+        <v>0.34558367107705801</v>
       </c>
       <c r="AG9" s="5">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AH9" s="6"/>
-      <c r="AI9" s="6"/>
-      <c r="AK9" s="5">
-        <v>34.570056762068198</v>
-      </c>
-      <c r="AL9" s="5">
-        <v>4.5778664577056496</v>
-      </c>
-      <c r="AM9" s="6">
-        <v>1.86147110489288</v>
-      </c>
-      <c r="AN9" s="6">
-        <v>0.34558367107705801</v>
-      </c>
-      <c r="AO9" s="5">
         <v>1.96362562254665</v>
       </c>
-      <c r="AP9" s="5">
+      <c r="AH9" s="5">
         <v>0.36222639562867198</v>
       </c>
-      <c r="AQ9" s="6">
+      <c r="AI9" s="6">
         <v>1.9642715242957101</v>
       </c>
-      <c r="AR9" s="6">
+      <c r="AJ9" s="6">
         <v>0.35731730151554097</v>
       </c>
     </row>
-    <row r="10" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B10" s="5">
         <v>24.519392747918499</v>
       </c>
       <c r="C10" s="5">
         <v>3.3765146340410901</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="6">
+      <c r="D10" s="6">
         <v>11.3283064247616</v>
       </c>
-      <c r="G10" s="6">
+      <c r="E10" s="6">
         <v>1.75667635216019</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="5">
+      <c r="F10" s="5">
         <v>4.3655684894788598</v>
       </c>
+      <c r="G10" s="5">
+        <v>0.72256847111010403</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.89008783875792397</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0.27529653142885502</v>
+      </c>
       <c r="K10" s="5">
-        <v>0.72256847111010403</v>
-      </c>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
+        <v>50.370043311847297</v>
+      </c>
+      <c r="L10" s="5">
+        <v>6.8266682265390397</v>
+      </c>
+      <c r="M10" s="6">
+        <v>1.1013427759766601</v>
+      </c>
       <c r="N10" s="6">
-        <v>0.89008783875792397</v>
-      </c>
-      <c r="O10" s="6">
-        <v>0.27529653142885502</v>
-      </c>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="S10" s="5">
-        <v>50.370043311847297</v>
+        <v>0.279195398098668</v>
+      </c>
+      <c r="O10" s="5">
+        <v>1.8886807440369899</v>
+      </c>
+      <c r="P10" s="5">
+        <v>0.41993899419076303</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>1.08014977882427</v>
+      </c>
+      <c r="R10" s="6">
+        <v>0.28419236315363</v>
       </c>
       <c r="T10" s="5">
-        <v>6.8266682265390397</v>
-      </c>
-      <c r="U10" s="6">
-        <v>1.1013427759766601</v>
+        <v>2.0282019718480502</v>
+      </c>
+      <c r="U10" s="5">
+        <v>0.37754673426285001</v>
       </c>
       <c r="V10" s="6">
-        <v>0.279195398098668</v>
-      </c>
-      <c r="W10" s="5">
-        <v>1.8886807440369899</v>
+        <v>3.0233946110574101</v>
+      </c>
+      <c r="W10" s="6">
+        <v>0.65226013362701096</v>
       </c>
       <c r="X10" s="5">
-        <v>0.41993899419076303</v>
-      </c>
-      <c r="Y10" s="6">
-        <v>1.08014977882427</v>
+        <v>3.0769912027266599</v>
+      </c>
+      <c r="Y10" s="5">
+        <v>0.65226013362701096</v>
       </c>
       <c r="Z10" s="6">
-        <v>0.28419236315363</v>
-      </c>
-      <c r="AB10" s="5">
-        <v>2.0282019718480502</v>
+        <v>2.9681463342075101</v>
+      </c>
+      <c r="AA10" s="6">
+        <v>0.65213375302212495</v>
       </c>
       <c r="AC10" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD10" s="6">
-        <v>3.0233946110574101</v>
+        <v>34.498810594745102</v>
+      </c>
+      <c r="AD10" s="5">
+        <v>4.5805798233599297</v>
       </c>
       <c r="AE10" s="6">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AF10" s="5">
-        <v>3.0769912027266599</v>
+        <v>1.86657481807766</v>
+      </c>
+      <c r="AF10" s="6">
+        <v>0.34383410086548399</v>
       </c>
       <c r="AG10" s="5">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AH10" s="6"/>
-      <c r="AI10" s="6"/>
-      <c r="AK10" s="5">
-        <v>34.498810594745102</v>
-      </c>
-      <c r="AL10" s="5">
-        <v>4.5805798233599297</v>
-      </c>
-      <c r="AM10" s="6">
-        <v>1.86657481807766</v>
-      </c>
-      <c r="AN10" s="6">
-        <v>0.34383410086548399</v>
-      </c>
-      <c r="AO10" s="5">
         <v>1.90028400803589</v>
       </c>
-      <c r="AP10" s="5">
+      <c r="AH10" s="5">
         <v>0.34945012130988901</v>
       </c>
-      <c r="AQ10" s="6">
+      <c r="AI10" s="6">
         <v>1.90928027610508</v>
       </c>
-      <c r="AR10" s="6">
+      <c r="AJ10" s="6">
         <v>0.34945018620593998</v>
       </c>
     </row>
-    <row r="11" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B11" s="5">
         <v>21.996905724856099</v>
       </c>
       <c r="C11" s="5">
         <v>2.9856415262303599</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6">
+      <c r="D11" s="6">
         <v>11.0671269081706</v>
       </c>
-      <c r="G11" s="6">
+      <c r="E11" s="6">
         <v>1.68567829653259</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="5">
+      <c r="F11" s="5">
         <v>4.9579210625189001</v>
       </c>
+      <c r="G11" s="5">
+        <v>0.89091012676741499</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0.95254623904054903</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0.26236662864990901</v>
+      </c>
       <c r="K11" s="5">
-        <v>0.89091012676741499</v>
-      </c>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
+        <v>50.6021835670551</v>
+      </c>
+      <c r="L11" s="5">
+        <v>6.8159615936773701</v>
+      </c>
+      <c r="M11" s="6">
+        <v>2.4294044850569798</v>
+      </c>
       <c r="N11" s="6">
-        <v>0.95254623904054903</v>
-      </c>
-      <c r="O11" s="6">
-        <v>0.26236662864990901</v>
-      </c>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="S11" s="5">
-        <v>50.6021835670551</v>
+        <v>0.491532450674801</v>
+      </c>
+      <c r="O11" s="5">
+        <v>2.4929016378617299</v>
+      </c>
+      <c r="P11" s="5">
+        <v>0.47851192255269298</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>2.3570848611973498</v>
+      </c>
+      <c r="R11" s="6">
+        <v>0.47000785524292399</v>
       </c>
       <c r="T11" s="5">
-        <v>6.8159615936773701</v>
-      </c>
-      <c r="U11" s="6">
-        <v>2.4294044850569798</v>
+        <v>2.0045866890630801</v>
+      </c>
+      <c r="U11" s="5">
+        <v>0.37754673426285001</v>
       </c>
       <c r="V11" s="6">
-        <v>0.491532450674801</v>
-      </c>
-      <c r="W11" s="5">
-        <v>2.4929016378617299</v>
+        <v>3.1856421504299002</v>
+      </c>
+      <c r="W11" s="6">
+        <v>0.65565129784223597</v>
       </c>
       <c r="X11" s="5">
-        <v>0.47851192255269298</v>
-      </c>
-      <c r="Y11" s="6">
-        <v>2.3570848611973498</v>
+        <v>3.1856421504299002</v>
+      </c>
+      <c r="Y11" s="5">
+        <v>0.65565129784223597</v>
       </c>
       <c r="Z11" s="6">
-        <v>0.47000785524292399</v>
-      </c>
-      <c r="AB11" s="5">
-        <v>2.0045866890630801</v>
+        <v>3.1450098960334101</v>
+      </c>
+      <c r="AA11" s="6">
+        <v>0.65226013362701096</v>
       </c>
       <c r="AC11" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD11" s="6">
-        <v>3.1856421504299002</v>
+        <v>34.554127832915199</v>
+      </c>
+      <c r="AD11" s="5">
+        <v>4.5660618080018196</v>
       </c>
       <c r="AE11" s="6">
-        <v>0.65565129784223597</v>
-      </c>
-      <c r="AF11" s="5">
-        <v>3.1856421504299002</v>
+        <v>1.81268296370352</v>
+      </c>
+      <c r="AF11" s="6">
+        <v>0.33337223640394198</v>
       </c>
       <c r="AG11" s="5">
-        <v>0.65565129784223597</v>
-      </c>
-      <c r="AH11" s="6"/>
-      <c r="AI11" s="6"/>
-      <c r="AK11" s="5">
-        <v>34.554127832915199</v>
-      </c>
-      <c r="AL11" s="5">
-        <v>4.5660618080018196</v>
-      </c>
-      <c r="AM11" s="6">
-        <v>1.81268296370352</v>
-      </c>
-      <c r="AN11" s="6">
-        <v>0.33337223640394198</v>
-      </c>
-      <c r="AO11" s="5">
         <v>1.96429126731902</v>
       </c>
-      <c r="AP11" s="5">
+      <c r="AH11" s="5">
         <v>0.35731730156293201</v>
       </c>
-      <c r="AQ11" s="6">
+      <c r="AI11" s="6">
         <v>1.8795069801762501</v>
       </c>
-      <c r="AR11" s="6">
+      <c r="AJ11" s="6">
         <v>0.34575359895052998</v>
       </c>
     </row>
-    <row r="12" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>24.073944136969398</v>
       </c>
       <c r="C12" s="5">
         <v>3.2906045777064898</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6">
+      <c r="D12" s="6">
         <v>10.871081688695201</v>
       </c>
-      <c r="G12" s="6">
+      <c r="E12" s="6">
         <v>1.5456538017913899</v>
       </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="5">
+      <c r="F12" s="5">
         <v>4.5042629003538499</v>
       </c>
+      <c r="G12" s="5">
+        <v>0.75565867825603805</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0.98179762818361005</v>
+      </c>
+      <c r="I12" s="6">
+        <v>0.28993726071696102</v>
+      </c>
       <c r="K12" s="5">
-        <v>0.75565867825603805</v>
-      </c>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
+        <v>48.5283966162228</v>
+      </c>
+      <c r="L12" s="5">
+        <v>6.39532451008645</v>
+      </c>
+      <c r="M12" s="6">
+        <v>2.8583793701106899</v>
+      </c>
       <c r="N12" s="6">
-        <v>0.98179762818361005</v>
-      </c>
-      <c r="O12" s="6">
-        <v>0.28993726071696102</v>
-      </c>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="S12" s="5">
-        <v>48.5283966162228</v>
+        <v>0.57377303940268798</v>
+      </c>
+      <c r="O12" s="5">
+        <v>2.2571410688804598</v>
+      </c>
+      <c r="P12" s="5">
+        <v>0.46259787093209498</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>2.4566723216903199</v>
+      </c>
+      <c r="R12" s="6">
+        <v>0.46852708080793398</v>
       </c>
       <c r="T12" s="5">
-        <v>6.39532451008645</v>
-      </c>
-      <c r="U12" s="6">
-        <v>2.8583793701106899</v>
+        <v>2.0124832402399999</v>
+      </c>
+      <c r="U12" s="5">
+        <v>0.37754673426285001</v>
       </c>
       <c r="V12" s="6">
-        <v>0.57377303940268798</v>
-      </c>
-      <c r="W12" s="5">
-        <v>2.2571410688804598</v>
+        <v>2.9469306504008701</v>
+      </c>
+      <c r="W12" s="6">
+        <v>0.65213375302212495</v>
       </c>
       <c r="X12" s="5">
-        <v>0.46259787093209498</v>
-      </c>
-      <c r="Y12" s="6">
-        <v>2.4566723216903199</v>
+        <v>3.1524446068305201</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>0.65226013362701096</v>
       </c>
       <c r="Z12" s="6">
-        <v>0.46852708080793398</v>
-      </c>
-      <c r="AB12" s="5">
-        <v>2.0124832402399999</v>
+        <v>2.9709094694099698</v>
+      </c>
+      <c r="AA12" s="6">
+        <v>0.65213375302212495</v>
       </c>
       <c r="AC12" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD12" s="6">
-        <v>2.9469306504008701</v>
+        <v>34.6014705772876</v>
+      </c>
+      <c r="AD12" s="5">
+        <v>4.5785181060921998</v>
       </c>
       <c r="AE12" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AF12" s="5">
-        <v>3.1524446068305201</v>
+        <v>1.8125561645361601</v>
+      </c>
+      <c r="AF12" s="6">
+        <v>0.33334854013531301</v>
       </c>
       <c r="AG12" s="5">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AH12" s="6"/>
-      <c r="AI12" s="6"/>
-      <c r="AK12" s="5">
-        <v>34.6014705772876</v>
-      </c>
-      <c r="AL12" s="5">
-        <v>4.5785181060921998</v>
-      </c>
-      <c r="AM12" s="6">
-        <v>1.8125561645361601</v>
-      </c>
-      <c r="AN12" s="6">
-        <v>0.33334854013531301</v>
-      </c>
-      <c r="AO12" s="5">
         <v>1.96488011670068</v>
       </c>
-      <c r="AP12" s="5">
+      <c r="AH12" s="5">
         <v>0.36261343482516201</v>
       </c>
-      <c r="AQ12" s="6">
+      <c r="AI12" s="6">
         <v>1.9178899634194899</v>
       </c>
-      <c r="AR12" s="6">
+      <c r="AJ12" s="6">
         <v>0.35300853576487501</v>
       </c>
     </row>
-    <row r="13" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>24.073944136969398</v>
       </c>
       <c r="C13" s="5">
         <v>3.2906045777064898</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6">
+      <c r="D13" s="6">
         <v>11.065870149418</v>
       </c>
-      <c r="G13" s="6">
+      <c r="E13" s="6">
         <v>1.7106619694696501</v>
       </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="5">
+      <c r="F13" s="5">
         <v>4.4913411407632298</v>
       </c>
+      <c r="G13" s="5">
+        <v>0.764781871349272</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0.61764700512757498</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0.17697658502358601</v>
+      </c>
       <c r="K13" s="5">
-        <v>0.764781871349272</v>
-      </c>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
+        <v>50.813193764563998</v>
+      </c>
+      <c r="L13" s="5">
+        <v>6.8053931798874796</v>
+      </c>
+      <c r="M13" s="6">
+        <v>2.07438188382043</v>
+      </c>
       <c r="N13" s="6">
-        <v>0.61764700512757498</v>
-      </c>
-      <c r="O13" s="6">
-        <v>0.17697658502358601</v>
-      </c>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
-      <c r="S13" s="5">
-        <v>50.813193764563998</v>
+        <v>0.43125921121579203</v>
+      </c>
+      <c r="O13" s="5">
+        <v>2.5100936022216298</v>
+      </c>
+      <c r="P13" s="5">
+        <v>2.5100936022216298</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>2.6805114554649099</v>
+      </c>
+      <c r="R13" s="6">
+        <v>0.50105033491431605</v>
       </c>
       <c r="T13" s="5">
-        <v>6.8053931798874796</v>
-      </c>
-      <c r="U13" s="6">
-        <v>2.07438188382043</v>
+        <v>2.0282019718480502</v>
+      </c>
+      <c r="U13" s="5">
+        <v>0.37754673426285001</v>
       </c>
       <c r="V13" s="6">
-        <v>0.43125921121579203</v>
-      </c>
-      <c r="W13" s="5">
-        <v>2.5100936022216298</v>
+        <v>3.1450098960334101</v>
+      </c>
+      <c r="W13" s="6">
+        <v>0.65226013362701096</v>
       </c>
       <c r="X13" s="5">
-        <v>2.5100936022216298</v>
-      </c>
-      <c r="Y13" s="6">
-        <v>2.6805114554649099</v>
+        <v>3.0895272691364801</v>
+      </c>
+      <c r="Y13" s="5">
+        <v>0.65226013362701096</v>
       </c>
       <c r="Z13" s="6">
-        <v>0.50105033491431605</v>
-      </c>
-      <c r="AB13" s="5">
-        <v>2.0282019718480502</v>
+        <v>3.1234714223794802</v>
+      </c>
+      <c r="AA13" s="6">
+        <v>0.65226013362701096</v>
       </c>
       <c r="AC13" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD13" s="6">
-        <v>3.1450098960334101</v>
+        <v>34.63132536506</v>
+      </c>
+      <c r="AD13" s="5">
+        <v>4.5643280255556196</v>
       </c>
       <c r="AE13" s="6">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AF13" s="5">
-        <v>3.0895272691364801</v>
+        <v>1.8250318583902301</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>0.33629873874712601</v>
       </c>
       <c r="AG13" s="5">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AK13" s="5">
-        <v>34.63132536506</v>
-      </c>
-      <c r="AL13" s="5">
-        <v>4.5643280255556196</v>
-      </c>
-      <c r="AM13" s="6">
-        <v>1.8250318583902301</v>
-      </c>
-      <c r="AN13" s="6">
-        <v>0.33629873874712601</v>
-      </c>
-      <c r="AO13" s="5">
         <v>1.9040866582123299</v>
       </c>
-      <c r="AP13" s="5">
+      <c r="AH13" s="5">
         <v>0.35445006159312697</v>
       </c>
-      <c r="AQ13" s="6">
+      <c r="AI13" s="6">
         <v>1.96429126731902</v>
       </c>
-      <c r="AR13" s="6">
+      <c r="AJ13" s="6">
         <v>0.35731730156293201</v>
       </c>
     </row>
-    <row r="14" spans="2:44" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-    </row>
-    <row r="15" spans="2:44" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-    </row>
-    <row r="16" spans="2:44" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AK1:AR1"/>
-    <mergeCell ref="AK2:AL2"/>
-    <mergeCell ref="AM2:AN2"/>
-    <mergeCell ref="AO2:AP2"/>
-    <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="AB1:AI1"/>
-    <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="AF2:AG2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="S1:Z1"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="B1:O1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K1:R1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="T1:AA1"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="AC1:AJ1"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="AG2:AH2"/>
+    <mergeCell ref="AI2:AJ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2141,61 +1931,58 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB2F127C-15E6-41A0-94B0-FA50F057125C}">
-  <dimension ref="A1:AA35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" style="8" customWidth="1"/>
-    <col min="13" max="13" width="16.1640625" style="8" customWidth="1"/>
-    <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" style="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-    </row>
-    <row r="2" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:27" ht="32" x14ac:dyDescent="0.2">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+    </row>
+    <row r="2" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L2" s="13"/>
+      <c r="M2" s="26"/>
+    </row>
+    <row r="3" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -2229,39 +2016,39 @@
       <c r="K3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="L3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="29" t="s">
+      <c r="M3" s="27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="12">
         <v>1</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="21">
         <v>66</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="21">
         <v>66</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="21">
         <v>1</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="21">
         <v>1</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="21">
         <v>66</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="21">
         <v>66</v>
       </c>
       <c r="J4" s="6">
@@ -2272,713 +2059,730 @@
         <f>AVERAGE(DataExp1!C4:C13)</f>
         <v>3.2827532251076272</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="6">
         <v>280.77705301382201</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="28">
         <v>1.24324175218449E-3</v>
       </c>
-      <c r="O4">
-        <f>L7/L19</f>
-        <v>4848.5315891311448</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A5" s="30"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
       <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
       <c r="J5" s="6">
-        <f>AVERAGE(DataExp1!F4:F13)</f>
+        <f>AVERAGE(DataExp1!D4:D13)</f>
         <v>11.070752653739017</v>
       </c>
       <c r="K5" s="6">
-        <f>AVERAGE(DataExp1!G4:G13)</f>
+        <f>AVERAGE(DataExp1!E4:E13)</f>
         <v>1.6712838772969871</v>
       </c>
       <c r="L5" s="6">
         <v>391.23075904146799</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="28">
         <v>1.8368430572894799E-3</v>
       </c>
-      <c r="O5">
-        <f>L7/L11</f>
-        <v>5.6020769715525622</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A6" s="30"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A6" s="24"/>
       <c r="B6" s="7">
         <v>5</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
       <c r="J6" s="6">
-        <f>AVERAGE(DataExp1!J4:J13)</f>
+        <f>AVERAGE(DataExp1!F4:F13)</f>
         <v>4.7480516396353174</v>
       </c>
       <c r="K6" s="6">
-        <f>AVERAGE(DataExp1!K4:K13)</f>
+        <f>AVERAGE(DataExp1!G4:G13)</f>
         <v>0.82681097952909732</v>
       </c>
       <c r="L6" s="6">
         <v>417.59086506911302</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="28">
         <v>1.8680991323063701E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A7" s="30"/>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A7" s="24"/>
       <c r="B7" s="7">
         <v>10</v>
       </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
       <c r="J7" s="6">
-        <f>AVERAGE(DataExp1!N4:N13)</f>
+        <f>AVERAGE(DataExp1!H4:H13)</f>
         <v>0.84932664663156276</v>
       </c>
       <c r="K7" s="6">
-        <f>AVERAGE(DataExp1!O4:O13)</f>
+        <f>AVERAGE(DataExp1!I4:I13)</f>
         <v>0.24563346801399702</v>
       </c>
       <c r="L7" s="6">
         <v>427.43972841419099</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="28">
         <v>1.90857404909223E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A8" s="26" t="s">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="4">
         <v>1</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
       <c r="J8" s="5">
-        <f>AVERAGE(DataExp1!S4:S13)</f>
+        <f>AVERAGE(DataExp1!K4:K13)</f>
         <v>49.821904185231844</v>
       </c>
       <c r="K8" s="5">
-        <f>AVERAGE(DataExp1!T4:T13)</f>
+        <f>AVERAGE(DataExp1!L4:L13)</f>
         <v>6.6901005257882433</v>
       </c>
       <c r="L8" s="5">
         <v>38.8018530138228</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="29">
         <v>1.8341564911519399E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A9" s="26"/>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
       <c r="J9" s="5">
-        <f>AVERAGE(DataExp1!U4:U13)</f>
+        <f>AVERAGE(DataExp1!M4:M13)</f>
         <v>2.2585080679270888</v>
       </c>
       <c r="K9" s="5">
-        <f>AVERAGE(DataExp1!V4:V13)</f>
+        <f>AVERAGE(DataExp1!N4:N13)</f>
         <v>0.46312458447019578</v>
       </c>
       <c r="L9" s="5">
         <v>73.281259041468303</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="29">
         <v>3.8957965924184199E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A10" s="26"/>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A10" s="17"/>
       <c r="B10" s="4">
         <v>5</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
       <c r="J10" s="5">
-        <f>AVERAGE(DataExp1!W4:W13)</f>
+        <f>AVERAGE(DataExp1!O4:O13)</f>
         <v>2.4443213833989064</v>
       </c>
       <c r="K10" s="5">
-        <f>AVERAGE(DataExp1!X4:X13)</f>
+        <f>AVERAGE(DataExp1!P4:P13)</f>
         <v>0.67972664412295081</v>
       </c>
       <c r="L10" s="5">
         <v>77.092715069113893</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="29">
         <v>4.1758142847234302E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A11" s="26"/>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
       <c r="B11" s="4">
         <v>10</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
       <c r="J11" s="5">
-        <f>AVERAGE(DataExp1!Y4:Y13)</f>
+        <f>AVERAGE(DataExp1!Q4:Q13)</f>
         <v>2.0470536852897636</v>
       </c>
       <c r="K11" s="5">
-        <f>AVERAGE(DataExp1!Z4:Z13)</f>
+        <f>AVERAGE(DataExp1!R4:R13)</f>
         <v>0.42174105651815957</v>
       </c>
       <c r="L11" s="5">
         <v>76.300224110581993</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="29">
         <v>4.0673431385843499E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A12" s="30" t="s">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A12" s="24" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
         <v>1</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
       <c r="J12" s="6">
-        <f>AVERAGE(DataExp1!AB4:AB13)</f>
+        <f>AVERAGE(DataExp1!T4:T13)</f>
         <v>2.0194039548285878</v>
       </c>
       <c r="K12" s="6">
-        <f>AVERAGE(DataExp1!AC4:AC13)</f>
+        <f>AVERAGE(DataExp1!U4:U13)</f>
         <v>0.37754673426285007</v>
       </c>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A13" s="30"/>
+      <c r="L12" s="6">
+        <v>4.4845012962678503E-2</v>
+      </c>
+      <c r="M12" s="28">
+        <v>1.32241661098872E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A13" s="24"/>
       <c r="B13" s="7">
         <v>3</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
       <c r="J13" s="6">
-        <f>AVERAGE(DataExp1!AD4:AD13)</f>
+        <f>AVERAGE(DataExp1!V4:V13)</f>
         <v>3.0323916470832399</v>
       </c>
       <c r="K13" s="6">
-        <f>AVERAGE(DataExp1!AE4:AE13)</f>
+        <f>AVERAGE(DataExp1!W4:W13)</f>
         <v>0.65287517616761293</v>
       </c>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A14" s="30"/>
+      <c r="L13" s="6">
+        <v>4.4845012962678503E-2</v>
+      </c>
+      <c r="M13" s="28">
+        <v>1.3223489288371801E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A14" s="24"/>
       <c r="B14" s="7">
         <v>5</v>
       </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
       <c r="J14" s="6">
-        <f>AVERAGE(DataExp1!AF4:AF13)</f>
+        <f>AVERAGE(DataExp1!X4:X13)</f>
         <v>3.0970657292831891</v>
       </c>
       <c r="K14" s="6">
-        <f>AVERAGE(DataExp1!AG4:AG13)</f>
+        <f>AVERAGE(DataExp1!Y4:Y13)</f>
         <v>0.65291309034907874</v>
       </c>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A15" s="30"/>
+      <c r="L14" s="6">
+        <v>4.78425388880356E-2</v>
+      </c>
+      <c r="M14" s="28">
+        <v>1.33917051049755E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A15" s="24"/>
       <c r="B15" s="7">
         <v>10</v>
       </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A16" s="26" t="s">
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="6">
+        <f>AVERAGE(DataExp1!Z4:Z13)</f>
+        <v>3.0304601968108664</v>
+      </c>
+      <c r="K15" s="6">
+        <f>AVERAGE(DataExp1!AA4:AA13)</f>
+        <v>0.65218430526407922</v>
+      </c>
+      <c r="L15" s="6">
+        <v>4.7875038888035598E-2</v>
+      </c>
+      <c r="M15" s="28">
+        <v>1.33921911090507E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="4">
         <v>1</v>
       </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
       <c r="J16" s="5">
-        <f>AVERAGE(DataExp1!AK4:AK13)</f>
+        <f>AVERAGE(DataExp1!AC4:AC13)</f>
         <v>34.552311810658352</v>
       </c>
       <c r="K16" s="5">
-        <f>AVERAGE(DataExp1!AL4:AL13)</f>
+        <f>AVERAGE(DataExp1!AD4:AD13)</f>
         <v>4.575032042937762</v>
       </c>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="P16">
-        <f>14.81/0.17</f>
-        <v>87.117647058823522</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A17" s="26"/>
+      <c r="L16" s="5">
+        <v>6.2164238822761397E-2</v>
+      </c>
+      <c r="M16" s="29">
+        <v>1.8093373899484099E-5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="17"/>
       <c r="B17" s="4">
         <v>3</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
       <c r="J17" s="5">
-        <f>AVERAGE(DataExp1!AM4:AM14)</f>
+        <f>AVERAGE(DataExp1!AE4:AE14)</f>
         <v>1.8560190453181431</v>
       </c>
       <c r="K17" s="5">
-        <f>AVERAGE(DataExp1!AN5:AN14)</f>
+        <f>AVERAGE(DataExp1!AF5:AF14)</f>
         <v>0.34386357258632122</v>
       </c>
       <c r="L17" s="5">
         <v>8.8175866468285097E-2</v>
       </c>
-      <c r="M17" s="5">
+      <c r="M17" s="29">
         <v>2.79669169855113E-5</v>
       </c>
-      <c r="O17" t="s">
-        <v>27</v>
-      </c>
-      <c r="P17">
-        <f>M7/M19</f>
-        <v>68.231919522408703</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A18" s="26"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="17"/>
       <c r="B18" s="4">
         <v>5</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
       <c r="J18" s="5">
-        <f>AVERAGE(DataExp1!AO4:AO13)</f>
+        <f>AVERAGE(DataExp1!AG4:AG13)</f>
         <v>1.9127433590347436</v>
       </c>
       <c r="K18" s="5">
-        <f>AVERAGE(DataExp1!AP5:AP6)</f>
+        <f>AVERAGE(DataExp1!AH5:AH6)</f>
         <v>0.35602585387596053</v>
       </c>
       <c r="L18" s="5">
         <v>8.8376119113808799E-2</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M18" s="29">
         <v>2.8023187480955202E-5</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A19" s="26"/>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="17"/>
       <c r="B19" s="4">
         <v>10</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
       <c r="J19" s="5">
-        <f>AVERAGE(DataExp1!AQ4:AQ13)</f>
+        <f>AVERAGE(DataExp1!AI4:AI13)</f>
         <v>1.9259347567178799</v>
       </c>
       <c r="K19" s="5">
-        <f>AVERAGE(DataExp1!AR4:AR13)</f>
+        <f>AVERAGE(DataExp1!AJ4:AJ13)</f>
         <v>0.35326486945372448</v>
       </c>
       <c r="L19" s="5">
         <v>8.81585941138084E-2</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M19" s="29">
         <v>2.7971865110220399E-5</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A20" s="33" t="s">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="17">
         <v>66</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="17">
         <v>66</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="17">
         <v>3</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="17">
         <v>3</v>
       </c>
-      <c r="H20" s="26">
+      <c r="H20" s="17">
         <v>22</v>
       </c>
-      <c r="I20" s="26">
+      <c r="I20" s="17">
         <v>22</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A21" s="33"/>
+      <c r="M20" s="29"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
       <c r="B21" s="4">
         <v>3</v>
       </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A22" s="33"/>
+      <c r="M21" s="29"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
       <c r="B22" s="4">
         <v>5</v>
       </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A23" s="33"/>
+      <c r="M22" s="29"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="20"/>
       <c r="B23" s="4">
         <v>10</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A24" s="32" t="s">
+      <c r="M23" s="29"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
         <v>14</v>
       </c>
       <c r="B24" s="10">
         <v>1</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A25" s="32"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="30"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="19"/>
       <c r="B25" s="10">
         <v>3</v>
       </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A26" s="32"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="30"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="19"/>
       <c r="B26" s="10">
         <v>5</v>
       </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A27" s="32"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="30"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="19"/>
       <c r="B27" s="10">
         <v>10</v>
       </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A28" s="33" t="s">
+      <c r="L27" s="15"/>
+      <c r="M27" s="30"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B28" s="4">
         <v>1</v>
       </c>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A29" s="33"/>
+      <c r="M28" s="29"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="20"/>
       <c r="B29" s="4">
         <v>3</v>
       </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A30" s="33"/>
+      <c r="M29" s="29"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="20"/>
       <c r="B30" s="4">
         <v>5</v>
       </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A31" s="33"/>
+      <c r="M30" s="29"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="20"/>
       <c r="B31" s="11">
         <v>10</v>
       </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A32" s="32" t="s">
+      <c r="M31" s="29"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="19" t="s">
         <v>16</v>
       </c>
       <c r="B32" s="10">
         <v>1</v>
       </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A33" s="32"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="30"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="19"/>
       <c r="B33" s="10">
         <v>3</v>
       </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34" s="32"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="30"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="19"/>
       <c r="B34" s="10">
         <v>5</v>
       </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A35" s="32"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="30"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="19"/>
       <c r="B35" s="10">
         <v>10</v>
       </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="C4:C19"/>
+    <mergeCell ref="D4:D19"/>
+    <mergeCell ref="E4:E19"/>
+    <mergeCell ref="F4:F19"/>
+    <mergeCell ref="G4:G19"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A32:A35"/>
@@ -2992,16 +2796,6 @@
     <mergeCell ref="G20:G35"/>
     <mergeCell ref="H20:H35"/>
     <mergeCell ref="I20:I35"/>
-    <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="C4:C19"/>
-    <mergeCell ref="D4:D19"/>
-    <mergeCell ref="E4:E19"/>
-    <mergeCell ref="F4:F19"/>
-    <mergeCell ref="G4:G19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3010,36 +2804,36 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E80E6C9-07DF-4341-ACF2-5E614276889D}">
   <dimension ref="A1:AA1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28"/>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
+    <row r="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3050,6 +2844,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A16C87A6682E6E4295773DFF29EAB41B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a3213889016ec1ec7c5b45183b07d2a5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xmlns:ns4="c7f849e2-0a63-4d53-be53-fb9d39becd19" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39cf848dedf08b05fa72a945c282372c" ns3:_="" ns4:_="">
     <xsd:import namespace="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
@@ -3274,38 +3085,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
-    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3328,9 +3111,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
+    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/documents/ExperimentData.xlsx
+++ b/documents/ExperimentData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1b2bcfbbb34c0c/Documents/GitHub/meliso/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CD4EDAE-911B-4936-956E-33EFF2ADA7C1}"/>
+  <xr:revisionPtr revIDLastSave="456" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6D7F665-00B4-4BD5-A422-A17DCD1497C4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
+    <workbookView xWindow="-12890" yWindow="0" windowWidth="12980" windowHeight="15370" activeTab="1" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
   </bookViews>
   <sheets>
     <sheet name="DataExp1" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="34">
   <si>
     <t>MCA Rows</t>
   </si>
@@ -114,6 +114,33 @@
   <si>
     <t>Acc. Write Energy (Mean)</t>
   </si>
+  <si>
+    <t>Ipertubed</t>
+  </si>
+  <si>
+    <t>Ag-aSi (bcsstk02)</t>
+  </si>
+  <si>
+    <t>Ag-aSi (Ipertubed)</t>
+  </si>
+  <si>
+    <t>Elapsed Time for VMM</t>
+  </si>
+  <si>
+    <t>AlOx-HfO2 (bcsstk02)</t>
+  </si>
+  <si>
+    <t>AlOx-HfO2 (Ipertubed)</t>
+  </si>
+  <si>
+    <t>TaOx-HfOx (Ipertub)</t>
+  </si>
+  <si>
+    <t>EpiRAM (Ipertub)</t>
+  </si>
+  <si>
+    <t>EpiRAM (bcsstk02)</t>
+  </si>
 </sst>
 </file>
 
@@ -138,7 +165,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,6 +181,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -220,7 +253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -249,7 +282,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -258,14 +301,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -276,19 +313,21 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -304,6 +343,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -630,115 +673,116 @@
     <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B1" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="K1" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="T1" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16"/>
-      <c r="AA1" s="16"/>
-      <c r="AC1" s="16" t="s">
+      <c r="B1" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="K1" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="T1" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AC1" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="AD1" s="16"/>
-      <c r="AE1" s="16"/>
-      <c r="AF1" s="16"/>
-      <c r="AG1" s="16"/>
-      <c r="AH1" s="16"/>
-      <c r="AI1" s="16"/>
-      <c r="AJ1" s="16"/>
+      <c r="AD1" s="25"/>
+      <c r="AE1" s="25"/>
+      <c r="AF1" s="25"/>
+      <c r="AG1" s="25"/>
+      <c r="AH1" s="25"/>
+      <c r="AI1" s="25"/>
+      <c r="AJ1" s="25"/>
     </row>
     <row r="2" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17" t="s">
+      <c r="C2" s="23"/>
+      <c r="D2" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="18" t="s">
+      <c r="E2" s="23"/>
+      <c r="F2" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18" t="s">
+      <c r="G2" s="24"/>
+      <c r="H2" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="18"/>
-      <c r="K2" s="17" t="s">
+      <c r="I2" s="24"/>
+      <c r="K2" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17" t="s">
+      <c r="L2" s="23"/>
+      <c r="M2" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18" t="s">
+      <c r="N2" s="23"/>
+      <c r="O2" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18" t="s">
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="18"/>
-      <c r="T2" s="17" t="s">
+      <c r="R2" s="24"/>
+      <c r="T2" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="17"/>
-      <c r="V2" s="17" t="s">
+      <c r="U2" s="23"/>
+      <c r="V2" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="17"/>
-      <c r="X2" s="18" t="s">
+      <c r="W2" s="23"/>
+      <c r="X2" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="18"/>
-      <c r="Z2" s="18" t="s">
+      <c r="Y2" s="24"/>
+      <c r="Z2" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="AA2" s="18"/>
-      <c r="AC2" s="17" t="s">
+      <c r="AA2" s="24"/>
+      <c r="AC2" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="AD2" s="17"/>
-      <c r="AE2" s="17" t="s">
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="AF2" s="17"/>
-      <c r="AG2" s="18" t="s">
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="AH2" s="18"/>
-      <c r="AI2" s="18" t="s">
+      <c r="AH2" s="24"/>
+      <c r="AI2" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="AJ2" s="18"/>
+      <c r="AJ2" s="24"/>
     </row>
     <row r="3" spans="2:36" ht="45" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -1823,74 +1867,1108 @@
       <c r="C14" s="8"/>
     </row>
     <row r="15" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+      <c r="B15" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="K15" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="T15" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="25"/>
+      <c r="AA15" s="25"/>
+      <c r="AC15" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD15" s="25"/>
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="25"/>
+      <c r="AH15" s="25"/>
+      <c r="AI15" s="25"/>
+      <c r="AJ15" s="25"/>
     </row>
     <row r="16" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="23"/>
+      <c r="F16" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="24"/>
+      <c r="K16" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" s="23"/>
+      <c r="O16" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="R16" s="24"/>
+      <c r="T16" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="U16" s="23"/>
+      <c r="V16" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="W16" s="23"/>
+      <c r="X16" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y16" s="24"/>
+      <c r="Z16" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA16" s="24"/>
+      <c r="AC16" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD16" s="23"/>
+      <c r="AE16" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="AF16" s="23"/>
+      <c r="AG16" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH16" s="24"/>
+      <c r="AI16" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ16" s="24"/>
+    </row>
+    <row r="17" spans="2:36" ht="45" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="R17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="X17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ17" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B18" s="5">
+        <v>63.099979779433802</v>
+      </c>
+      <c r="C18" s="5">
+        <v>6.1914618829412298</v>
+      </c>
+      <c r="D18" s="6">
+        <v>38.709515333735297</v>
+      </c>
+      <c r="E18" s="6">
+        <v>3.8325863905188302</v>
+      </c>
+      <c r="F18" s="5">
+        <v>19.3125609083041</v>
+      </c>
+      <c r="G18" s="5">
+        <v>2.3699129682412501</v>
+      </c>
+      <c r="H18" s="6">
+        <v>5.11904383725365</v>
+      </c>
+      <c r="I18" s="6">
+        <v>0.73005812699544603</v>
+      </c>
+      <c r="K18" s="5">
+        <v>157.491792122156</v>
+      </c>
+      <c r="L18" s="5">
+        <v>14.514140074457901</v>
+      </c>
+      <c r="M18" s="6">
+        <v>2.3286845435735199</v>
+      </c>
+      <c r="N18" s="6">
+        <v>0.39920932369799</v>
+      </c>
+      <c r="O18" s="5">
+        <v>8.1717884699325491</v>
+      </c>
+      <c r="P18" s="5">
+        <v>1.0129108861659399</v>
+      </c>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="T18" s="5">
+        <v>13.236245367749699</v>
+      </c>
+      <c r="U18" s="5">
+        <v>1.57146153421673</v>
+      </c>
+      <c r="V18" s="6">
+        <v>1.90493440038017</v>
+      </c>
+      <c r="W18" s="6">
+        <v>0.45806793222847902</v>
+      </c>
+      <c r="X18" s="5">
+        <v>1.9321830134050899</v>
+      </c>
+      <c r="Y18" s="5">
+        <v>0.473754446095489</v>
+      </c>
+      <c r="Z18" s="6"/>
+      <c r="AA18" s="6"/>
+      <c r="AC18" s="5">
+        <v>59.705630088686199</v>
+      </c>
+      <c r="AD18" s="5">
+        <v>5.6586034268060601</v>
+      </c>
+      <c r="AE18" s="6">
+        <v>4.2657953513727804</v>
+      </c>
+      <c r="AF18" s="6">
+        <v>0.73609280545728795</v>
+      </c>
+      <c r="AG18" s="5">
+        <v>4.3067382375590597</v>
+      </c>
+      <c r="AH18" s="5">
+        <v>0.78876787017055605</v>
+      </c>
+      <c r="AI18" s="6">
+        <v>4.5961418368911104</v>
+      </c>
+      <c r="AJ18" s="6">
+        <v>0.77049022674415901</v>
+      </c>
+    </row>
+    <row r="19" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B19" s="5">
+        <v>63.042735492357899</v>
+      </c>
+      <c r="C19" s="5">
+        <v>6.1856100787064499</v>
+      </c>
+      <c r="D19" s="6">
+        <v>39.095490109684498</v>
+      </c>
+      <c r="E19" s="6">
+        <v>4.2537857712330602</v>
+      </c>
+      <c r="F19" s="5">
+        <v>20.411768203387801</v>
+      </c>
+      <c r="G19" s="5">
+        <v>2.4708117784551198</v>
+      </c>
+      <c r="H19" s="6">
+        <v>5.6384534247001596</v>
+      </c>
+      <c r="I19" s="6">
+        <v>0.86446282869091995</v>
+      </c>
+      <c r="K19" s="5">
+        <v>157.29900707611901</v>
+      </c>
+      <c r="L19" s="5">
+        <v>14.4931915247916</v>
+      </c>
+      <c r="M19" s="6">
+        <v>7.8733419303139298</v>
+      </c>
+      <c r="N19" s="6">
+        <v>1.00388575257059</v>
+      </c>
+      <c r="O19" s="5">
+        <v>6.2307112245394896</v>
+      </c>
+      <c r="P19" s="5">
+        <v>0.945277006207351</v>
+      </c>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
+      <c r="T19" s="5">
+        <v>13.236245367749699</v>
+      </c>
+      <c r="U19" s="5">
+        <v>1.57146153421673</v>
+      </c>
+      <c r="V19" s="6">
+        <v>1.9004171801880201</v>
+      </c>
+      <c r="W19" s="6">
+        <v>0.45806793222847902</v>
+      </c>
+      <c r="X19" s="5">
+        <v>1.90072564987806</v>
+      </c>
+      <c r="Y19" s="5">
+        <v>0.473754446095489</v>
+      </c>
+      <c r="Z19" s="6"/>
+      <c r="AA19" s="6"/>
+      <c r="AC19" s="5">
+        <v>60.177890822449797</v>
+      </c>
+      <c r="AD19" s="5">
+        <v>5.7023692293553001</v>
+      </c>
+      <c r="AE19" s="6">
+        <v>3.9426046524217799</v>
+      </c>
+      <c r="AF19" s="6">
+        <v>0.82754599084641001</v>
+      </c>
+      <c r="AG19" s="5">
+        <v>4.3359389837744198</v>
+      </c>
+      <c r="AH19" s="5">
+        <v>0.78875255111021403</v>
+      </c>
+      <c r="AI19" s="6">
+        <v>4.1287261615403503</v>
+      </c>
+      <c r="AJ19" s="6">
+        <v>0.74457174085613997</v>
+      </c>
+    </row>
+    <row r="20" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B20" s="5">
+        <v>72.908948571677797</v>
+      </c>
+      <c r="C20" s="5">
+        <v>7.1074838375327802</v>
+      </c>
+      <c r="D20" s="6">
+        <v>36.801848784197297</v>
+      </c>
+      <c r="E20" s="6">
+        <v>3.8240526776722201</v>
+      </c>
+      <c r="F20" s="5">
+        <v>20.914445133886598</v>
+      </c>
+      <c r="G20" s="5">
+        <v>2.3923524354409</v>
+      </c>
+      <c r="H20" s="6">
+        <v>4.1229650041350698</v>
+      </c>
+      <c r="I20" s="6">
+        <v>0.61635383312902503</v>
+      </c>
+      <c r="K20" s="5">
+        <v>159.352853227227</v>
+      </c>
+      <c r="L20" s="5">
+        <v>14.678664624417801</v>
+      </c>
+      <c r="M20" s="6">
+        <v>5.3107040461542097</v>
+      </c>
+      <c r="N20" s="6">
+        <v>0.93572788648500804</v>
+      </c>
+      <c r="O20" s="5">
+        <v>8.8419317184422397</v>
+      </c>
+      <c r="P20" s="5">
+        <v>1.0105737421724099</v>
+      </c>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="T20" s="5">
+        <v>13.2496111916915</v>
+      </c>
+      <c r="U20" s="5">
+        <v>1.57146153421673</v>
+      </c>
+      <c r="V20" s="6">
+        <v>1.8928704695040199</v>
+      </c>
+      <c r="W20" s="6">
+        <v>0.45806793222847902</v>
+      </c>
+      <c r="X20" s="5">
+        <v>1.9254081019906799</v>
+      </c>
+      <c r="Y20" s="5">
+        <v>0.473754446095489</v>
+      </c>
+      <c r="Z20" s="6"/>
+      <c r="AA20" s="6"/>
+      <c r="AC20" s="5">
+        <v>59.800266675023899</v>
+      </c>
+      <c r="AD20" s="5">
+        <v>5.6589098186134796</v>
+      </c>
+      <c r="AE20" s="6">
+        <v>4.0062601639211897</v>
+      </c>
+      <c r="AF20" s="6">
+        <v>0.73795381895044299</v>
+      </c>
+      <c r="AG20" s="5">
+        <v>4.6177380245423496</v>
+      </c>
+      <c r="AH20" s="5">
+        <v>0.76894302136484705</v>
+      </c>
+      <c r="AI20" s="6">
+        <v>4.16152269917868</v>
+      </c>
+      <c r="AJ20" s="6">
+        <v>0.74186796986636905</v>
+      </c>
+    </row>
+    <row r="21" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B21" s="5">
+        <v>70.511895936223198</v>
+      </c>
+      <c r="C21" s="5">
+        <v>6.8951414417694101</v>
+      </c>
+      <c r="D21" s="6">
+        <v>39.467779525017903</v>
+      </c>
+      <c r="E21" s="6">
+        <v>4.2341015047491899</v>
+      </c>
+      <c r="F21" s="5">
+        <v>18.750581694913599</v>
+      </c>
+      <c r="G21" s="5">
+        <v>2.4296486890765299</v>
+      </c>
+      <c r="H21" s="6">
+        <v>5.1094258927303402</v>
+      </c>
+      <c r="I21" s="6">
+        <v>0.72984480789211603</v>
+      </c>
+      <c r="K21" s="5">
+        <v>157.29900707611901</v>
+      </c>
+      <c r="L21" s="5">
+        <v>14.4931915247916</v>
+      </c>
+      <c r="M21" s="6">
+        <v>8.1890386233641905</v>
+      </c>
+      <c r="N21" s="6">
+        <v>0.972966699771316</v>
+      </c>
+      <c r="O21" s="5">
+        <v>2.5979047772938402</v>
+      </c>
+      <c r="P21" s="5">
+        <v>0.49508952439015402</v>
+      </c>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
+      <c r="T21" s="5">
+        <v>13.308572250548099</v>
+      </c>
+      <c r="U21" s="5">
+        <v>1.57146153421673</v>
+      </c>
+      <c r="V21" s="6">
+        <v>1.89579470823163</v>
+      </c>
+      <c r="W21" s="6">
+        <v>0.45806793222847902</v>
+      </c>
+      <c r="X21" s="5">
+        <v>1.92809473746348</v>
+      </c>
+      <c r="Y21" s="5">
+        <v>0.473754446095489</v>
+      </c>
+      <c r="Z21" s="6"/>
+      <c r="AA21" s="6"/>
+      <c r="AC21" s="5">
+        <v>59.763577152087599</v>
+      </c>
+      <c r="AD21" s="5">
+        <v>5.6605565868401699</v>
+      </c>
+      <c r="AE21" s="6">
+        <v>4.0965064780371803</v>
+      </c>
+      <c r="AF21" s="6">
+        <v>0.74199230991249299</v>
+      </c>
+      <c r="AG21" s="5">
+        <v>5.0523507457567902</v>
+      </c>
+      <c r="AH21" s="5">
+        <v>0.82059037677546498</v>
+      </c>
+      <c r="AI21" s="6">
+        <v>4.5857896450893199</v>
+      </c>
+      <c r="AJ21" s="6">
+        <v>0.77052852380524195</v>
+      </c>
+    </row>
+    <row r="22" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B22" s="5">
+        <v>63.110926462975499</v>
+      </c>
+      <c r="C22" s="5">
+        <v>6.1958200918135802</v>
+      </c>
+      <c r="D22" s="6">
+        <v>39.008448280288803</v>
+      </c>
+      <c r="E22" s="6">
+        <v>4.1939352765130602</v>
+      </c>
+      <c r="F22" s="5">
+        <v>18.643327675462999</v>
+      </c>
+      <c r="G22" s="5">
+        <v>2.3640932751286399</v>
+      </c>
+      <c r="H22" s="6">
+        <v>4.1024572901030796</v>
+      </c>
+      <c r="I22" s="6">
+        <v>0.66684968307617798</v>
+      </c>
+      <c r="K22" s="5">
+        <v>156.63177221391601</v>
+      </c>
+      <c r="L22" s="5">
+        <v>14.552850092942499</v>
+      </c>
+      <c r="M22" s="6">
+        <v>1.5954382843530299</v>
+      </c>
+      <c r="N22" s="6">
+        <v>0.34093122957817401</v>
+      </c>
+      <c r="O22" s="5">
+        <v>5.2511580596295104</v>
+      </c>
+      <c r="P22" s="5">
+        <v>0.95645330203096601</v>
+      </c>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="T22" s="5">
+        <v>13.2363942457426</v>
+      </c>
+      <c r="U22" s="5">
+        <v>1.57146153421673</v>
+      </c>
+      <c r="V22" s="6">
+        <v>1.84677639533975</v>
+      </c>
+      <c r="W22" s="6">
+        <v>0.40847846441090702</v>
+      </c>
+      <c r="X22" s="5">
+        <v>1.9129533293466101</v>
+      </c>
+      <c r="Y22" s="5">
+        <v>0.473754446095489</v>
+      </c>
+      <c r="Z22" s="6"/>
+      <c r="AA22" s="6"/>
+      <c r="AC22" s="5">
+        <v>59.788459460005697</v>
+      </c>
+      <c r="AD22" s="5">
+        <v>5.6563668900060096</v>
+      </c>
+      <c r="AE22" s="6">
+        <v>4.7948084662286998</v>
+      </c>
+      <c r="AF22" s="6">
+        <v>0.78044091788651704</v>
+      </c>
+      <c r="AG22" s="5">
+        <v>4.67808128757747</v>
+      </c>
+      <c r="AH22" s="5">
+        <v>0.78459048978145696</v>
+      </c>
+      <c r="AI22" s="6">
+        <v>4.8692804147897402</v>
+      </c>
+      <c r="AJ22" s="6">
+        <v>0.79097844961616104</v>
+      </c>
+    </row>
+    <row r="23" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B23" s="5">
+        <v>62.8215712107041</v>
+      </c>
+      <c r="C23" s="5">
+        <v>6.1644623938783498</v>
+      </c>
+      <c r="D23" s="6">
+        <v>40.482494792718498</v>
+      </c>
+      <c r="E23" s="6">
+        <v>4.2282882529463404</v>
+      </c>
+      <c r="F23" s="5">
+        <v>20.0793381879792</v>
+      </c>
+      <c r="G23" s="5">
+        <v>2.1635460449911998</v>
+      </c>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="K23" s="5">
+        <v>156.986009517112</v>
+      </c>
+      <c r="L23" s="5">
+        <v>14.467486922240001</v>
+      </c>
+      <c r="M23" s="6">
+        <v>1.88753858403897</v>
+      </c>
+      <c r="N23" s="6">
+        <v>0.42837619544093197</v>
+      </c>
+      <c r="O23" s="5">
+        <v>7.1603524175097304</v>
+      </c>
+      <c r="P23" s="5">
+        <v>1.00026650116511</v>
+      </c>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+      <c r="T23" s="5">
+        <v>13.308674501574901</v>
+      </c>
+      <c r="U23" s="5">
+        <v>1.57146153421673</v>
+      </c>
+      <c r="V23" s="6">
+        <v>1.84679124914915</v>
+      </c>
+      <c r="W23" s="6">
+        <v>0.40847846441090702</v>
+      </c>
+      <c r="X23" s="5">
+        <v>1.90072564987806</v>
+      </c>
+      <c r="Y23" s="5">
+        <v>0.473754446095489</v>
+      </c>
+      <c r="Z23" s="6"/>
+      <c r="AA23" s="6"/>
+      <c r="AC23" s="5">
+        <v>59.704796494574303</v>
+      </c>
+      <c r="AD23" s="5">
+        <v>5.65854215154509</v>
+      </c>
+      <c r="AE23" s="6">
+        <v>4.2657953513727804</v>
+      </c>
+      <c r="AF23" s="6">
+        <v>0.73609280545728795</v>
+      </c>
+      <c r="AG23" s="5">
+        <v>4.6146231262904296</v>
+      </c>
+      <c r="AH23" s="5">
+        <v>0.77049022674415901</v>
+      </c>
+      <c r="AI23" s="6">
+        <v>3.16447739831071</v>
+      </c>
+      <c r="AJ23" s="6">
+        <v>0.654757088945225</v>
+      </c>
+    </row>
+    <row r="24" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B24" s="5">
+        <v>63.110926462975499</v>
+      </c>
+      <c r="C24" s="5">
+        <v>6.1958200918135802</v>
+      </c>
+      <c r="D24" s="6">
+        <v>38.007488630184902</v>
+      </c>
+      <c r="E24" s="6">
+        <v>3.9127982684980802</v>
+      </c>
+      <c r="F24" s="5">
+        <v>16.411368520801499</v>
+      </c>
+      <c r="G24" s="5">
+        <v>1.9866453743771599</v>
+      </c>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="K24" s="5">
+        <v>158.196014729155</v>
+      </c>
+      <c r="L24" s="5">
+        <v>14.575139783219001</v>
+      </c>
+      <c r="M24" s="6">
+        <v>8.2933809227974091</v>
+      </c>
+      <c r="N24" s="6">
+        <v>1.08744489439875</v>
+      </c>
+      <c r="O24" s="5">
+        <v>8.3113921906864903</v>
+      </c>
+      <c r="P24" s="5">
+        <v>1.00724186950316</v>
+      </c>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="T24" s="5">
+        <v>13.308572250548099</v>
+      </c>
+      <c r="U24" s="5">
+        <v>1.57146153421673</v>
+      </c>
+      <c r="V24" s="6">
+        <v>1.8928399139471399</v>
+      </c>
+      <c r="W24" s="6">
+        <v>0.45806793222847902</v>
+      </c>
+      <c r="X24" s="5">
+        <v>1.92726370795321</v>
+      </c>
+      <c r="Y24" s="5">
+        <v>0.473754446095489</v>
+      </c>
+      <c r="Z24" s="6"/>
+      <c r="AA24" s="6"/>
+      <c r="AC24" s="5">
+        <v>59.763577152087599</v>
+      </c>
+      <c r="AD24" s="5">
+        <v>5.6605565868401699</v>
+      </c>
+      <c r="AE24" s="6">
+        <v>4.0062601639211897</v>
+      </c>
+      <c r="AF24" s="6">
+        <v>0.73795381895044299</v>
+      </c>
+      <c r="AG24" s="5">
+        <v>3.20141786716691</v>
+      </c>
+      <c r="AH24" s="5">
+        <v>0.654749429514626</v>
+      </c>
+      <c r="AI24" s="6">
+        <v>3.27705316310352</v>
+      </c>
+      <c r="AJ24" s="6">
+        <v>0.65983546495578804</v>
+      </c>
+    </row>
+    <row r="25" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B25" s="5">
+        <v>62.948412428098202</v>
+      </c>
+      <c r="C25" s="5">
+        <v>6.1773991708045601</v>
+      </c>
+      <c r="D25" s="6">
+        <v>38.424321998081503</v>
+      </c>
+      <c r="E25" s="6">
+        <v>3.7962006425224999</v>
+      </c>
+      <c r="F25" s="5">
+        <v>19.3437107481444</v>
+      </c>
+      <c r="G25" s="5">
+        <v>2.4587922053428302</v>
+      </c>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="K25" s="5">
+        <v>157.491792122156</v>
+      </c>
+      <c r="L25" s="5">
+        <v>14.514140074457901</v>
+      </c>
+      <c r="M25" s="6">
+        <v>7.9528826625526996</v>
+      </c>
+      <c r="N25" s="6">
+        <v>1.00403884516471</v>
+      </c>
+      <c r="O25" s="5">
+        <v>2.5901809467614498</v>
+      </c>
+      <c r="P25" s="5">
+        <v>0.71838880869329702</v>
+      </c>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
+      <c r="T25" s="5">
+        <v>13.2496111916915</v>
+      </c>
+      <c r="U25" s="5">
+        <v>1.57146153421673</v>
+      </c>
+      <c r="V25" s="6">
+        <v>1.88988196952168</v>
+      </c>
+      <c r="W25" s="6">
+        <v>0.45806793222847902</v>
+      </c>
+      <c r="X25" s="5">
+        <v>1.9000822249987701</v>
+      </c>
+      <c r="Y25" s="5">
+        <v>0.473754446095489</v>
+      </c>
+      <c r="Z25" s="6"/>
+      <c r="AA25" s="6"/>
+      <c r="AC25" s="5">
+        <v>59.780185400258901</v>
+      </c>
+      <c r="AD25" s="5">
+        <v>5.6572783626149601</v>
+      </c>
+      <c r="AE25" s="6">
+        <v>3.99030456835369</v>
+      </c>
+      <c r="AF25" s="6">
+        <v>0.73808402950040897</v>
+      </c>
+      <c r="AG25" s="5">
+        <v>4.4974089192370004</v>
+      </c>
+      <c r="AH25" s="5">
+        <v>0.76155164534629505</v>
+      </c>
+      <c r="AI25" s="6">
+        <v>4.7203610704798997</v>
+      </c>
+      <c r="AJ25" s="6">
+        <v>0.97485233337667998</v>
+      </c>
+    </row>
+    <row r="26" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B26" s="5">
+        <v>62.8215712107041</v>
+      </c>
+      <c r="C26" s="5">
+        <v>6.1644623938783498</v>
+      </c>
+      <c r="D26" s="6">
+        <v>37.969670161082703</v>
+      </c>
+      <c r="E26" s="6">
+        <v>3.82926654229257</v>
+      </c>
+      <c r="F26" s="5">
+        <v>19.3437107481444</v>
+      </c>
+      <c r="G26" s="5">
+        <v>2.4587922053428302</v>
+      </c>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="K26" s="5">
+        <v>156.87408337816299</v>
+      </c>
+      <c r="L26" s="5">
+        <v>14.5729484252851</v>
+      </c>
+      <c r="M26" s="6">
+        <v>2.2530507252529302</v>
+      </c>
+      <c r="N26" s="6">
+        <v>0.38723762689095498</v>
+      </c>
+      <c r="O26" s="5">
+        <v>4.3416457442441896</v>
+      </c>
+      <c r="P26" s="5">
+        <v>0.81790916195557295</v>
+      </c>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="T26" s="5">
+        <v>13.2958588107644</v>
+      </c>
+      <c r="U26" s="5">
+        <v>1.57146153421673</v>
+      </c>
+      <c r="V26" s="6">
+        <v>1.88577925752618</v>
+      </c>
+      <c r="W26" s="6">
+        <v>0.45806793222847902</v>
+      </c>
+      <c r="X26" s="5">
+        <v>1.9129598430242301</v>
+      </c>
+      <c r="Y26" s="5">
+        <v>0.473754446095489</v>
+      </c>
+      <c r="Z26" s="6"/>
+      <c r="AA26" s="6"/>
+      <c r="AC26" s="5">
+        <v>59.763577152087599</v>
+      </c>
+      <c r="AD26" s="5">
+        <v>5.6605565868401699</v>
+      </c>
+      <c r="AE26" s="6">
+        <v>4.7934652069475101</v>
+      </c>
+      <c r="AF26" s="6">
+        <v>0.78044091788651704</v>
+      </c>
+      <c r="AG26" s="5">
+        <v>4.62239210584959</v>
+      </c>
+      <c r="AH26" s="5">
+        <v>0.77049022674415901</v>
+      </c>
+      <c r="AI26" s="6">
+        <v>4.1992812511646704</v>
+      </c>
+      <c r="AJ26" s="6">
+        <v>0.74189860738961999</v>
+      </c>
+    </row>
+    <row r="27" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B27" s="5">
+        <v>73.290681754099893</v>
+      </c>
+      <c r="C27" s="5">
+        <v>7.1442031435740603</v>
+      </c>
+      <c r="D27" s="6">
+        <v>38.295022809888302</v>
+      </c>
+      <c r="E27" s="6">
+        <v>4.1806733869494197</v>
+      </c>
+      <c r="F27" s="5">
+        <v>17.592599412371602</v>
+      </c>
+      <c r="G27" s="5">
+        <v>2.29104900348994</v>
+      </c>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="K27" s="5">
+        <v>157.491792122156</v>
+      </c>
+      <c r="L27" s="5">
+        <v>14.514140074457901</v>
+      </c>
+      <c r="M27" s="6">
+        <v>8.0216212976691192</v>
+      </c>
+      <c r="N27" s="6">
+        <v>0.94819842453320702</v>
+      </c>
+      <c r="O27" s="5">
+        <v>7.8031301233212496</v>
+      </c>
+      <c r="P27" s="5">
+        <v>0.98052828629424604</v>
+      </c>
+      <c r="Q27" s="6"/>
+      <c r="R27" s="6"/>
+      <c r="T27" s="5">
+        <v>13.2496111916915</v>
+      </c>
+      <c r="U27" s="5">
+        <v>1.57146153421673</v>
+      </c>
+      <c r="V27" s="6">
+        <v>1.89142964942645</v>
+      </c>
+      <c r="W27" s="6">
+        <v>0.45806793222847902</v>
+      </c>
+      <c r="X27" s="5">
+        <v>1.9268909669221299</v>
+      </c>
+      <c r="Y27" s="5">
+        <v>0.473754446095489</v>
+      </c>
+      <c r="Z27" s="6"/>
+      <c r="AA27" s="6"/>
+      <c r="AC27" s="5">
+        <v>59.705630088686199</v>
+      </c>
+      <c r="AD27" s="5">
+        <v>5.6586034268060601</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>3.8324091847093902</v>
+      </c>
+      <c r="AF27" s="6">
+        <v>0.83666835893369396</v>
+      </c>
+      <c r="AG27" s="5">
+        <v>4.3195119947240102</v>
+      </c>
+      <c r="AH27" s="5">
+        <v>0.78874489201662801</v>
+      </c>
+      <c r="AI27" s="6">
+        <v>4.2361236162037104</v>
+      </c>
+      <c r="AJ27" s="6">
+        <v>0.77829603577231399</v>
+      </c>
+    </row>
+    <row r="28" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:36" x14ac:dyDescent="0.25">
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
     </row>
@@ -1903,27 +2981,47 @@
       <c r="C34" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="40">
+    <mergeCell ref="T15:AA15"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="Z16:AA16"/>
+    <mergeCell ref="AC15:AJ15"/>
+    <mergeCell ref="AC16:AD16"/>
+    <mergeCell ref="AE16:AF16"/>
+    <mergeCell ref="AG16:AH16"/>
+    <mergeCell ref="AI16:AJ16"/>
+    <mergeCell ref="K15:R15"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="AC1:AJ1"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="AG2:AH2"/>
+    <mergeCell ref="AI2:AJ2"/>
+    <mergeCell ref="T1:AA1"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="K1:R1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K1:R1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="T1:AA1"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="X2:Y2"/>
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="AC1:AJ1"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="AG2:AH2"/>
-    <mergeCell ref="AI2:AJ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1945,42 +3043,43 @@
     <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18" style="8" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" style="31" customWidth="1"/>
+    <col min="12" max="12" width="17.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" style="21" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
     </row>
     <row r="2" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="L2" s="13"/>
-      <c r="M2" s="26"/>
+      <c r="M2" s="16"/>
     </row>
     <row r="3" spans="1:25" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -2019,36 +3118,39 @@
       <c r="L3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="27" t="s">
+      <c r="M3" s="17" t="s">
         <v>24</v>
       </c>
+      <c r="N3" s="34" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="27" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="12">
         <v>1</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="29">
         <v>66</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="29">
         <v>66</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="29">
         <v>1</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="29">
         <v>1</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="29">
         <v>66</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="29">
         <v>66</v>
       </c>
       <c r="J4" s="6">
@@ -2062,22 +3164,23 @@
       <c r="L4" s="6">
         <v>280.77705301382201</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="18">
         <v>1.24324175218449E-3</v>
       </c>
+      <c r="N4" s="10"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
+      <c r="A5" s="28"/>
       <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
       <c r="J5" s="6">
         <f>AVERAGE(DataExp1!D4:D13)</f>
         <v>11.070752653739017</v>
@@ -2089,22 +3192,23 @@
       <c r="L5" s="6">
         <v>391.23075904146799</v>
       </c>
-      <c r="M5" s="28">
+      <c r="M5" s="18">
         <v>1.8368430572894799E-3</v>
       </c>
+      <c r="N5" s="10"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
+      <c r="A6" s="28"/>
       <c r="B6" s="7">
         <v>5</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
       <c r="J6" s="6">
         <f>AVERAGE(DataExp1!F4:F13)</f>
         <v>4.7480516396353174</v>
@@ -2116,22 +3220,23 @@
       <c r="L6" s="6">
         <v>417.59086506911302</v>
       </c>
-      <c r="M6" s="28">
+      <c r="M6" s="18">
         <v>1.8680991323063701E-3</v>
       </c>
+      <c r="N6" s="10"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
+      <c r="A7" s="28"/>
       <c r="B7" s="7">
         <v>10</v>
       </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
       <c r="J7" s="6">
         <f>AVERAGE(DataExp1!H4:H13)</f>
         <v>0.84932664663156276</v>
@@ -2143,24 +3248,25 @@
       <c r="L7" s="6">
         <v>427.43972841419099</v>
       </c>
-      <c r="M7" s="28">
+      <c r="M7" s="18">
         <v>1.90857404909223E-3</v>
       </c>
+      <c r="N7" s="10"/>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="23" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="4">
         <v>1</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
       <c r="J8" s="5">
         <f>AVERAGE(DataExp1!K4:K13)</f>
         <v>49.821904185231844</v>
@@ -2172,22 +3278,23 @@
       <c r="L8" s="5">
         <v>38.8018530138228</v>
       </c>
-      <c r="M8" s="29">
+      <c r="M8" s="19">
         <v>1.8341564911519399E-2</v>
       </c>
+      <c r="N8" s="4"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
+      <c r="A9" s="23"/>
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
       <c r="J9" s="5">
         <f>AVERAGE(DataExp1!M4:M13)</f>
         <v>2.2585080679270888</v>
@@ -2199,22 +3306,23 @@
       <c r="L9" s="5">
         <v>73.281259041468303</v>
       </c>
-      <c r="M9" s="29">
+      <c r="M9" s="19">
         <v>3.8957965924184199E-2</v>
       </c>
+      <c r="N9" s="4"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
+      <c r="A10" s="23"/>
       <c r="B10" s="4">
         <v>5</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
       <c r="J10" s="5">
         <f>AVERAGE(DataExp1!O4:O13)</f>
         <v>2.4443213833989064</v>
@@ -2226,22 +3334,23 @@
       <c r="L10" s="5">
         <v>77.092715069113893</v>
       </c>
-      <c r="M10" s="29">
+      <c r="M10" s="19">
         <v>4.1758142847234302E-2</v>
       </c>
+      <c r="N10" s="4"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
+      <c r="A11" s="23"/>
       <c r="B11" s="4">
         <v>10</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
       <c r="J11" s="5">
         <f>AVERAGE(DataExp1!Q4:Q13)</f>
         <v>2.0470536852897636</v>
@@ -2253,134 +3362,139 @@
       <c r="L11" s="5">
         <v>76.300224110581993</v>
       </c>
-      <c r="M11" s="29">
+      <c r="M11" s="19">
         <v>4.0673431385843499E-2</v>
       </c>
+      <c r="N11" s="4"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="28" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
         <v>1</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="6">
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="32">
         <f>AVERAGE(DataExp1!T4:T13)</f>
         <v>2.0194039548285878</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="32">
         <f>AVERAGE(DataExp1!U4:U13)</f>
         <v>0.37754673426285007</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="32">
         <v>4.4845012962678503E-2</v>
       </c>
-      <c r="M12" s="28">
+      <c r="M12" s="33">
         <v>1.32241661098872E-4</v>
       </c>
+      <c r="N12" s="35"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
+      <c r="A13" s="28"/>
       <c r="B13" s="7">
         <v>3</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="6">
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="32">
         <f>AVERAGE(DataExp1!V4:V13)</f>
         <v>3.0323916470832399</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="32">
         <f>AVERAGE(DataExp1!W4:W13)</f>
         <v>0.65287517616761293</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="32">
         <v>4.4845012962678503E-2</v>
       </c>
-      <c r="M13" s="28">
+      <c r="M13" s="33">
         <v>1.3223489288371801E-4</v>
       </c>
+      <c r="N13" s="35"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="24"/>
+      <c r="A14" s="28"/>
       <c r="B14" s="7">
         <v>5</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="6">
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="32">
         <f>AVERAGE(DataExp1!X4:X13)</f>
         <v>3.0970657292831891</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="32">
         <f>AVERAGE(DataExp1!Y4:Y13)</f>
         <v>0.65291309034907874</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="32">
         <v>4.78425388880356E-2</v>
       </c>
-      <c r="M14" s="28">
+      <c r="M14" s="33">
         <v>1.33917051049755E-4</v>
       </c>
+      <c r="N14" s="35"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
+      <c r="A15" s="28"/>
       <c r="B15" s="7">
         <v>10</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="6">
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="32">
         <f>AVERAGE(DataExp1!Z4:Z13)</f>
         <v>3.0304601968108664</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="32">
         <f>AVERAGE(DataExp1!AA4:AA13)</f>
         <v>0.65218430526407922</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="32">
         <v>4.7875038888035598E-2</v>
       </c>
-      <c r="M15" s="28">
+      <c r="M15" s="33">
         <v>1.33921911090507E-4</v>
       </c>
+      <c r="N15" s="35"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="23" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="4">
         <v>1</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
       <c r="J16" s="5">
         <f>AVERAGE(DataExp1!AC4:AC13)</f>
         <v>34.552311810658352</v>
@@ -2392,22 +3506,23 @@
       <c r="L16" s="5">
         <v>6.2164238822761397E-2</v>
       </c>
-      <c r="M16" s="29">
+      <c r="M16" s="19">
         <v>1.8093373899484099E-5</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
+      <c r="N16" s="4"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="23"/>
       <c r="B17" s="4">
         <v>3</v>
       </c>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
       <c r="J17" s="5">
         <f>AVERAGE(DataExp1!AE4:AE14)</f>
         <v>1.8560190453181431</v>
@@ -2419,22 +3534,23 @@
       <c r="L17" s="5">
         <v>8.8175866468285097E-2</v>
       </c>
-      <c r="M17" s="29">
+      <c r="M17" s="19">
         <v>2.79669169855113E-5</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
+      <c r="N17" s="4"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="23"/>
       <c r="B18" s="4">
         <v>5</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
       <c r="J18" s="5">
         <f>AVERAGE(DataExp1!AG4:AG13)</f>
         <v>1.9127433590347436</v>
@@ -2446,22 +3562,23 @@
       <c r="L18" s="5">
         <v>8.8376119113808799E-2</v>
       </c>
-      <c r="M18" s="29">
+      <c r="M18" s="19">
         <v>2.8023187480955202E-5</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
+      <c r="N18" s="4"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="23"/>
       <c r="B19" s="4">
         <v>10</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
       <c r="J19" s="5">
         <f>AVERAGE(DataExp1!AI4:AI13)</f>
         <v>1.9259347567178799</v>
@@ -2473,316 +3590,491 @@
       <c r="L19" s="5">
         <v>8.81585941138084E-2</v>
       </c>
-      <c r="M19" s="29">
+      <c r="M19" s="19">
         <v>2.7971865110220399E-5</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+      <c r="N19" s="4"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="31" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="C20" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="17">
-        <v>66</v>
-      </c>
-      <c r="E20" s="17">
-        <v>66</v>
-      </c>
-      <c r="F20" s="17">
-        <v>3</v>
-      </c>
-      <c r="G20" s="17">
-        <v>3</v>
-      </c>
-      <c r="H20" s="17">
-        <v>22</v>
-      </c>
-      <c r="I20" s="17">
-        <v>22</v>
-      </c>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="29"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="20"/>
+      <c r="C20" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="23">
+        <v>128</v>
+      </c>
+      <c r="E20" s="23">
+        <v>128</v>
+      </c>
+      <c r="F20" s="23">
+        <v>1</v>
+      </c>
+      <c r="G20" s="23">
+        <v>1</v>
+      </c>
+      <c r="H20" s="23">
+        <v>128</v>
+      </c>
+      <c r="I20" s="23">
+        <v>128</v>
+      </c>
+      <c r="J20" s="4">
+        <f>AVERAGE(DataExp1!B18:B27)</f>
+        <v>65.766764930924992</v>
+      </c>
+      <c r="K20" s="4">
+        <f>AVERAGE(DataExp1!C18:C27)</f>
+        <v>6.4421864526712369</v>
+      </c>
+      <c r="L20" s="5">
+        <v>1035.7896129462799</v>
+      </c>
+      <c r="M20" s="19">
+        <v>5.95739397649482E-3</v>
+      </c>
+      <c r="N20" s="5">
+        <v>12.759822845458901</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="31"/>
       <c r="B21" s="4">
         <v>3</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="29"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="20"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="4">
+        <f>AVERAGE(DataExp1!D18:D27)</f>
+        <v>38.626208042487967</v>
+      </c>
+      <c r="K21" s="4">
+        <f>AVERAGE(DataExp1!E18:E27)</f>
+        <v>4.0285688713895276</v>
+      </c>
+      <c r="L21" s="5">
+        <v>1685.75088883886</v>
+      </c>
+      <c r="M21" s="19">
+        <v>1.1219430173259401E-2</v>
+      </c>
+      <c r="N21" s="5">
+        <v>12.8247382640838</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="31"/>
       <c r="B22" s="4">
         <v>5</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="29"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="20"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="4">
+        <f>AVERAGE(DataExp1!F18:F27)</f>
+        <v>19.080341123339618</v>
+      </c>
+      <c r="K22" s="4">
+        <f>AVERAGE(DataExp1!G18:G27)</f>
+        <v>2.3385643979886401</v>
+      </c>
+      <c r="L22" s="5">
+        <v>1984.11291473147</v>
+      </c>
+      <c r="M22" s="19">
+        <v>1.31972764989438E-2</v>
+      </c>
+      <c r="N22" s="5">
+        <v>12.9234986305236</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="31"/>
       <c r="B23" s="4">
         <v>10</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="29"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="4">
+        <f>AVERAGE(DataExp1!H18:H27)</f>
+        <v>4.8184690897844593</v>
+      </c>
+      <c r="K23" s="4">
+        <f>AVERAGE(DataExp1!I18:I27)</f>
+        <v>0.721513855956737</v>
+      </c>
+      <c r="L23" s="5">
+        <v>2183.88837946289</v>
+      </c>
+      <c r="M23" s="19">
+        <v>1.4378549136786E-2</v>
+      </c>
+      <c r="N23" s="5">
+        <v>14.266155481338499</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="30" t="s">
         <v>14</v>
       </c>
       <c r="B24" s="10">
         <v>1</v>
       </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="30"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="10">
+        <f>AVERAGE(DataExp1!K18:K27)</f>
+        <v>157.51141235842792</v>
+      </c>
+      <c r="K24" s="10">
+        <f>AVERAGE(DataExp1!L18:L27)</f>
+        <v>14.53758931210613</v>
+      </c>
+      <c r="L24" s="15">
+        <v>140.34726294628899</v>
+      </c>
+      <c r="M24" s="20">
+        <v>8.6437071411442801E-2</v>
+      </c>
+      <c r="N24" s="15">
+        <v>12.795346260070801</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="30"/>
       <c r="B25" s="10">
         <v>3</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="30"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="19"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="10">
+        <f>AVERAGE(DataExp1!M18:M27)</f>
+        <v>5.370568162007002</v>
+      </c>
+      <c r="K25" s="10">
+        <f>AVERAGE(DataExp1!N18:N27)</f>
+        <v>0.75080168785316326</v>
+      </c>
+      <c r="L25" s="15">
+        <v>336.02303883887203</v>
+      </c>
+      <c r="M25" s="20">
+        <v>0.307117723102377</v>
+      </c>
+      <c r="N25" s="15">
+        <v>12.8078730106353</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="30"/>
       <c r="B26" s="10">
         <v>5</v>
       </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="30"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="19"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="10">
+        <f>AVERAGE(DataExp1!O18:O27)</f>
+        <v>6.130019567236074</v>
+      </c>
+      <c r="K26" s="10">
+        <f>AVERAGE(DataExp1!P18:P27)</f>
+        <v>0.89446390885782068</v>
+      </c>
+      <c r="L26" s="15">
+        <v>351.22411473145002</v>
+      </c>
+      <c r="M26" s="20">
+        <v>0.31561186164217703</v>
+      </c>
+      <c r="N26" s="15">
+        <v>26.1628239154815</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="30"/>
       <c r="B27" s="10">
         <v>10</v>
       </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
       <c r="L27" s="15"/>
-      <c r="M27" s="30"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
+      <c r="M27" s="20"/>
+      <c r="N27" s="15"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="31" t="s">
         <v>15</v>
       </c>
       <c r="B28" s="4">
         <v>1</v>
       </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="29"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="20"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="4">
+        <f>AVERAGE(DataExp1!T18:T27)</f>
+        <v>13.2679396369752</v>
+      </c>
+      <c r="K28" s="4">
+        <f>AVERAGE(DataExp1!U18:U27)</f>
+        <v>1.5714615342167302</v>
+      </c>
+      <c r="L28" s="5">
+        <v>8.3970028801535798E-2</v>
+      </c>
+      <c r="M28" s="19">
+        <v>3.6284487521842497E-5</v>
+      </c>
+      <c r="N28" s="5">
+        <v>0.30750107765197698</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="31"/>
       <c r="B29" s="4">
         <v>3</v>
       </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="17"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="29"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="20"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="4">
+        <f>AVERAGE(DataExp1!V18:V27)</f>
+        <v>1.8847515193214188</v>
+      </c>
+      <c r="K29" s="4">
+        <f>AVERAGE(DataExp1!W18:W27)</f>
+        <v>0.44815003866496461</v>
+      </c>
+      <c r="L29" s="5">
+        <v>9.5270057603071695E-2</v>
+      </c>
+      <c r="M29" s="19">
+        <v>4.9660843797880298E-5</v>
+      </c>
+      <c r="N29" s="5">
+        <v>0.36651349067687899</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="31"/>
       <c r="B30" s="4">
         <v>5</v>
       </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="29"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="20"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="4">
+        <f>AVERAGE(DataExp1!X18:X27)</f>
+        <v>1.9167287224860321</v>
+      </c>
+      <c r="K30" s="4">
+        <f>AVERAGE(DataExp1!Y18:Y27)</f>
+        <v>0.473754446095489</v>
+      </c>
+      <c r="L30" s="5">
+        <v>9.6327586404607604E-2</v>
+      </c>
+      <c r="M30" s="19">
+        <v>4.9897249721340198E-5</v>
+      </c>
+      <c r="N30" s="5">
+        <v>0.397212743759155</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="31"/>
       <c r="B31" s="11">
         <v>10</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="5"/>
-      <c r="M31" s="29"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
+      <c r="M31" s="19"/>
+      <c r="N31" s="5"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="30" t="s">
         <v>16</v>
       </c>
       <c r="B32" s="10">
         <v>1</v>
       </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="30"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="15">
+        <f>AVERAGE(DataExp1!AC18:AC27)</f>
+        <v>59.79535904859479</v>
+      </c>
+      <c r="K32" s="15">
+        <f>AVERAGE(DataExp1!AD18:AD27)</f>
+        <v>5.6632343066267472</v>
+      </c>
+      <c r="L32" s="15">
+        <v>0.22719339629037999</v>
+      </c>
+      <c r="M32" s="20">
+        <v>9.04054493084061E-5</v>
+      </c>
+      <c r="N32" s="15">
+        <v>12.858536243438699</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="30"/>
       <c r="B33" s="10">
         <v>3</v>
       </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="30"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="15">
+        <f>AVERAGE(DataExp1!AE18:AE27)</f>
+        <v>4.1994209587286191</v>
+      </c>
+      <c r="K33" s="15">
+        <f>AVERAGE(DataExp1!AF18:AF27)</f>
+        <v>0.76532657737815013</v>
+      </c>
+      <c r="L33" s="15">
+        <v>0.334194763871137</v>
+      </c>
+      <c r="M33" s="20">
+        <v>1.6040279311206501E-4</v>
+      </c>
+      <c r="N33" s="15">
+        <v>12.8858025074005</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="30"/>
       <c r="B34" s="10">
         <v>5</v>
       </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="30"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="19"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="23"/>
+      <c r="J34" s="15">
+        <f>AVERAGE(DataExp1!AG18:AG27)</f>
+        <v>4.4246201292478027</v>
+      </c>
+      <c r="K34" s="15">
+        <f>AVERAGE(DataExp1!AH18:AH27)</f>
+        <v>0.76976707295684066</v>
+      </c>
+      <c r="L34" s="15">
+        <v>0.33717530645189397</v>
+      </c>
+      <c r="M34" s="20">
+        <v>1.6153492724404301E-4</v>
+      </c>
+      <c r="N34" s="15">
+        <v>13.6702349185943</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" s="30"/>
       <c r="B35" s="10">
         <v>10</v>
       </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="30"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="15">
+        <f>AVERAGE(DataExp1!AI18:AI27)</f>
+        <v>4.1938757256751718</v>
+      </c>
+      <c r="K35" s="15">
+        <f>AVERAGE(DataExp1!AJ18:AJ27)</f>
+        <v>0.76280764413276991</v>
+      </c>
+      <c r="L35" s="15">
+        <v>0.33856701443077702</v>
+      </c>
+      <c r="M35" s="20">
+        <v>1.6191006940398199E-4</v>
+      </c>
+      <c r="N35" s="15">
+        <v>35.664546728134098</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="C4:C19"/>
-    <mergeCell ref="D4:D19"/>
-    <mergeCell ref="E4:E19"/>
-    <mergeCell ref="F4:F19"/>
-    <mergeCell ref="G4:G19"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A32:A35"/>
@@ -2796,6 +4088,16 @@
     <mergeCell ref="G20:G35"/>
     <mergeCell ref="H20:H35"/>
     <mergeCell ref="I20:I35"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="C4:C19"/>
+    <mergeCell ref="D4:D19"/>
+    <mergeCell ref="E4:E19"/>
+    <mergeCell ref="F4:F19"/>
+    <mergeCell ref="G4:G19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2807,33 +4109,33 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22"/>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
-      <c r="S1" s="22"/>
-      <c r="T1" s="22"/>
-      <c r="U1" s="22"/>
-      <c r="V1" s="22"/>
-      <c r="W1" s="22"/>
-      <c r="X1" s="22"/>
-      <c r="Y1" s="22"/>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
+      <c r="A1" s="26"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="Z1" s="26"/>
+      <c r="AA1" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2844,23 +4146,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A16C87A6682E6E4295773DFF29EAB41B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a3213889016ec1ec7c5b45183b07d2a5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xmlns:ns4="c7f849e2-0a63-4d53-be53-fb9d39becd19" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39cf848dedf08b05fa72a945c282372c" ns3:_="" ns4:_="">
     <xsd:import namespace="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
@@ -3085,10 +4370,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
+    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3111,20 +4424,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
-    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/documents/ExperimentData.xlsx
+++ b/documents/ExperimentData.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1b2bcfbbb34c0c/Documents/GitHub/meliso/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="775" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{138C2E5E-F7BA-45B7-BFEA-CFCD2D0AB987}"/>
+  <xr:revisionPtr revIDLastSave="783" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D07D5FA6-4BCD-4496-828A-B5364B503ACF}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
   </bookViews>
   <sheets>
     <sheet name="DataExp1" sheetId="2" r:id="rId1"/>
-    <sheet name="DataExp2" sheetId="4" r:id="rId2"/>
-    <sheet name="Experiment 1" sheetId="1" r:id="rId3"/>
+    <sheet name="Experiment 1" sheetId="1" r:id="rId2"/>
+    <sheet name="DataExp2" sheetId="4" r:id="rId3"/>
     <sheet name="Experiment 2" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -396,7 +396,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -440,29 +440,60 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -470,16 +501,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -490,74 +516,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -909,147 +894,146 @@
     <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.85546875" style="54"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
       <c r="M1" s="22"/>
-      <c r="O1" s="25" t="s">
+      <c r="O1" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="AB1" s="25" t="s">
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="AB1" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="AC1" s="25"/>
-      <c r="AD1" s="25"/>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
-      <c r="AH1" s="25"/>
-      <c r="AI1" s="25"/>
-      <c r="AJ1" s="25"/>
-      <c r="AK1" s="56"/>
-      <c r="AL1" s="56"/>
-      <c r="AM1" s="51"/>
-      <c r="AO1" s="25" t="s">
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="41"/>
+      <c r="AL1" s="41"/>
+      <c r="AM1" s="22"/>
+      <c r="AO1" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="AP1" s="25"/>
-      <c r="AQ1" s="25"/>
-      <c r="AR1" s="25"/>
-      <c r="AS1" s="25"/>
-      <c r="AT1" s="25"/>
-      <c r="AU1" s="25"/>
-      <c r="AV1" s="25"/>
-      <c r="AW1" s="25"/>
-      <c r="AX1" s="56"/>
-      <c r="AY1" s="56"/>
+      <c r="AP1" s="49"/>
+      <c r="AQ1" s="49"/>
+      <c r="AR1" s="49"/>
+      <c r="AS1" s="49"/>
+      <c r="AT1" s="49"/>
+      <c r="AU1" s="49"/>
+      <c r="AV1" s="49"/>
+      <c r="AW1" s="49"/>
+      <c r="AX1" s="41"/>
+      <c r="AY1" s="41"/>
     </row>
     <row r="2" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="44" t="s">
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="48" t="s">
+      <c r="F2" s="43"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="49"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="27" t="s">
+      <c r="I2" s="46"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="O2" s="44" t="s">
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="O2" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="44" t="s">
+      <c r="P2" s="43"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="S2" s="45"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="48" t="s">
+      <c r="S2" s="43"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="49"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="27" t="s">
+      <c r="V2" s="46"/>
+      <c r="W2" s="47"/>
+      <c r="X2" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="Y2" s="27"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="44" t="s">
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="AC2" s="45"/>
-      <c r="AD2" s="46"/>
-      <c r="AE2" s="44" t="s">
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="44"/>
+      <c r="AE2" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="AF2" s="45"/>
-      <c r="AG2" s="46"/>
-      <c r="AH2" s="48" t="s">
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="44"/>
+      <c r="AH2" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="AI2" s="49"/>
-      <c r="AJ2" s="50"/>
-      <c r="AK2" s="27" t="s">
+      <c r="AI2" s="46"/>
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="AL2" s="27"/>
-      <c r="AM2" s="27"/>
-      <c r="AO2" s="44" t="s">
+      <c r="AL2" s="48"/>
+      <c r="AM2" s="48"/>
+      <c r="AO2" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="AP2" s="45"/>
-      <c r="AQ2" s="46"/>
-      <c r="AR2" s="44" t="s">
+      <c r="AP2" s="43"/>
+      <c r="AQ2" s="44"/>
+      <c r="AR2" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="AS2" s="45"/>
-      <c r="AT2" s="46"/>
-      <c r="AU2" s="48" t="s">
+      <c r="AS2" s="43"/>
+      <c r="AT2" s="44"/>
+      <c r="AU2" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="AV2" s="49"/>
-      <c r="AW2" s="50"/>
-      <c r="AX2" s="27" t="s">
+      <c r="AV2" s="46"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="AY2" s="27"/>
-      <c r="AZ2" s="27"/>
+      <c r="AY2" s="48"/>
+      <c r="AZ2" s="48"/>
     </row>
     <row r="3" spans="2:52" ht="45" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -1058,7 +1042,7 @@
       <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="28" t="s">
         <v>35</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -1067,7 +1051,7 @@
       <c r="F3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="47" t="s">
+      <c r="G3" s="28" t="s">
         <v>35</v>
       </c>
       <c r="H3" s="9" t="s">
@@ -1076,7 +1060,7 @@
       <c r="I3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="47" t="s">
+      <c r="J3" s="28" t="s">
         <v>35</v>
       </c>
       <c r="K3" s="9" t="s">
@@ -1085,7 +1069,7 @@
       <c r="L3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="47" t="s">
+      <c r="M3" s="28" t="s">
         <v>35</v>
       </c>
       <c r="O3" s="3" t="s">
@@ -1094,7 +1078,7 @@
       <c r="P3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="47" t="s">
+      <c r="Q3" s="28" t="s">
         <v>35</v>
       </c>
       <c r="R3" s="3" t="s">
@@ -1103,7 +1087,7 @@
       <c r="S3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="47" t="s">
+      <c r="T3" s="28" t="s">
         <v>35</v>
       </c>
       <c r="U3" s="9" t="s">
@@ -1112,7 +1096,7 @@
       <c r="V3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="W3" s="47" t="s">
+      <c r="W3" s="28" t="s">
         <v>35</v>
       </c>
       <c r="X3" s="9" t="s">
@@ -1121,17 +1105,17 @@
       <c r="Y3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="Z3" s="47" t="s">
+      <c r="Z3" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="AA3" s="55"/>
-      <c r="AB3" s="47" t="s">
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="28" t="s">
         <v>20</v>
       </c>
       <c r="AC3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AD3" s="47" t="s">
+      <c r="AD3" s="28" t="s">
         <v>35</v>
       </c>
       <c r="AE3" s="3" t="s">
@@ -1140,7 +1124,7 @@
       <c r="AF3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AG3" s="47" t="s">
+      <c r="AG3" s="28" t="s">
         <v>35</v>
       </c>
       <c r="AH3" s="9" t="s">
@@ -1149,7 +1133,7 @@
       <c r="AI3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="AJ3" s="47" t="s">
+      <c r="AJ3" s="28" t="s">
         <v>35</v>
       </c>
       <c r="AK3" s="9" t="s">
@@ -1158,16 +1142,16 @@
       <c r="AL3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="AM3" s="47" t="s">
+      <c r="AM3" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="AO3" s="47" t="s">
+      <c r="AO3" s="28" t="s">
         <v>20</v>
       </c>
       <c r="AP3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AQ3" s="47" t="s">
+      <c r="AQ3" s="28" t="s">
         <v>35</v>
       </c>
       <c r="AR3" s="3" t="s">
@@ -1176,7 +1160,7 @@
       <c r="AS3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AT3" s="47" t="s">
+      <c r="AT3" s="28" t="s">
         <v>35</v>
       </c>
       <c r="AU3" s="9" t="s">
@@ -1185,7 +1169,7 @@
       <c r="AV3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="AW3" s="47" t="s">
+      <c r="AW3" s="28" t="s">
         <v>35</v>
       </c>
       <c r="AX3" s="9" t="s">
@@ -1194,7 +1178,7 @@
       <c r="AY3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="AZ3" s="47" t="s">
+      <c r="AZ3" s="28" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2538,143 +2522,143 @@
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
       <c r="M15" s="22"/>
-      <c r="O15" s="25" t="s">
+      <c r="O15" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
-      <c r="V15" s="25"/>
-      <c r="W15" s="25"/>
-      <c r="X15" s="25"/>
-      <c r="Y15" s="25"/>
-      <c r="AB15" s="25" t="s">
+      <c r="P15" s="49"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="49"/>
+      <c r="U15" s="49"/>
+      <c r="V15" s="49"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="49"/>
+      <c r="Y15" s="49"/>
+      <c r="AB15" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="AC15" s="25"/>
-      <c r="AD15" s="25"/>
-      <c r="AE15" s="25"/>
-      <c r="AF15" s="25"/>
-      <c r="AG15" s="25"/>
-      <c r="AH15" s="25"/>
-      <c r="AI15" s="25"/>
-      <c r="AJ15" s="25"/>
-      <c r="AK15" s="25"/>
-      <c r="AL15" s="25"/>
-      <c r="AM15" s="51"/>
-      <c r="AO15" s="25" t="s">
+      <c r="AC15" s="49"/>
+      <c r="AD15" s="49"/>
+      <c r="AE15" s="49"/>
+      <c r="AF15" s="49"/>
+      <c r="AG15" s="49"/>
+      <c r="AH15" s="49"/>
+      <c r="AI15" s="49"/>
+      <c r="AJ15" s="49"/>
+      <c r="AK15" s="49"/>
+      <c r="AL15" s="49"/>
+      <c r="AM15" s="22"/>
+      <c r="AO15" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="AP15" s="25"/>
-      <c r="AQ15" s="25"/>
-      <c r="AR15" s="25"/>
-      <c r="AS15" s="25"/>
-      <c r="AT15" s="25"/>
-      <c r="AU15" s="25"/>
-      <c r="AV15" s="25"/>
-      <c r="AW15" s="25"/>
-      <c r="AX15" s="25"/>
-      <c r="AY15" s="25"/>
+      <c r="AP15" s="49"/>
+      <c r="AQ15" s="49"/>
+      <c r="AR15" s="49"/>
+      <c r="AS15" s="49"/>
+      <c r="AT15" s="49"/>
+      <c r="AU15" s="49"/>
+      <c r="AV15" s="49"/>
+      <c r="AW15" s="49"/>
+      <c r="AX15" s="49"/>
+      <c r="AY15" s="49"/>
     </row>
     <row r="16" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="44" t="s">
+      <c r="C16" s="43"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="48" t="s">
+      <c r="F16" s="43"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="49"/>
-      <c r="J16" s="50"/>
-      <c r="K16" s="27" t="s">
+      <c r="I16" s="46"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-      <c r="O16" s="44" t="s">
+      <c r="L16" s="48"/>
+      <c r="M16" s="48"/>
+      <c r="O16" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="46"/>
-      <c r="R16" s="44" t="s">
+      <c r="P16" s="43"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="S16" s="45"/>
-      <c r="T16" s="46"/>
-      <c r="U16" s="48" t="s">
+      <c r="S16" s="43"/>
+      <c r="T16" s="44"/>
+      <c r="U16" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="V16" s="49"/>
-      <c r="W16" s="50"/>
-      <c r="X16" s="27" t="s">
+      <c r="V16" s="46"/>
+      <c r="W16" s="47"/>
+      <c r="X16" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="Y16" s="27"/>
-      <c r="Z16" s="27"/>
-      <c r="AA16" s="51"/>
-      <c r="AB16" s="44" t="s">
+      <c r="Y16" s="48"/>
+      <c r="Z16" s="48"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="AC16" s="45"/>
-      <c r="AD16" s="46"/>
-      <c r="AE16" s="44" t="s">
+      <c r="AC16" s="43"/>
+      <c r="AD16" s="44"/>
+      <c r="AE16" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="AF16" s="45"/>
-      <c r="AG16" s="46"/>
-      <c r="AH16" s="48" t="s">
+      <c r="AF16" s="43"/>
+      <c r="AG16" s="44"/>
+      <c r="AH16" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="AI16" s="49"/>
-      <c r="AJ16" s="50"/>
-      <c r="AK16" s="27" t="s">
+      <c r="AI16" s="46"/>
+      <c r="AJ16" s="47"/>
+      <c r="AK16" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="AL16" s="27"/>
-      <c r="AM16" s="27"/>
-      <c r="AO16" s="44" t="s">
+      <c r="AL16" s="48"/>
+      <c r="AM16" s="48"/>
+      <c r="AO16" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="AP16" s="45"/>
-      <c r="AQ16" s="46"/>
-      <c r="AR16" s="44" t="s">
+      <c r="AP16" s="43"/>
+      <c r="AQ16" s="44"/>
+      <c r="AR16" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="AS16" s="45"/>
-      <c r="AT16" s="46"/>
-      <c r="AU16" s="48" t="s">
+      <c r="AS16" s="43"/>
+      <c r="AT16" s="44"/>
+      <c r="AU16" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="AV16" s="49"/>
-      <c r="AW16" s="50"/>
-      <c r="AX16" s="27" t="s">
+      <c r="AV16" s="46"/>
+      <c r="AW16" s="47"/>
+      <c r="AX16" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="AY16" s="27"/>
-      <c r="AZ16" s="27"/>
+      <c r="AY16" s="48"/>
+      <c r="AZ16" s="48"/>
     </row>
     <row r="17" spans="2:52" ht="45" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
@@ -2683,7 +2667,7 @@
       <c r="C17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="47" t="s">
+      <c r="D17" s="28" t="s">
         <v>35</v>
       </c>
       <c r="E17" s="3" t="s">
@@ -2692,7 +2676,7 @@
       <c r="F17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="47" t="s">
+      <c r="G17" s="28" t="s">
         <v>35</v>
       </c>
       <c r="H17" s="9" t="s">
@@ -2701,7 +2685,7 @@
       <c r="I17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="J17" s="47" t="s">
+      <c r="J17" s="28" t="s">
         <v>35</v>
       </c>
       <c r="K17" s="9" t="s">
@@ -2710,7 +2694,7 @@
       <c r="L17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="M17" s="47" t="s">
+      <c r="M17" s="28" t="s">
         <v>35</v>
       </c>
       <c r="O17" s="3" t="s">
@@ -2719,7 +2703,7 @@
       <c r="P17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="Q17" s="47" t="s">
+      <c r="Q17" s="28" t="s">
         <v>35</v>
       </c>
       <c r="R17" s="3" t="s">
@@ -2728,7 +2712,7 @@
       <c r="S17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="T17" s="47" t="s">
+      <c r="T17" s="28" t="s">
         <v>35</v>
       </c>
       <c r="U17" s="9" t="s">
@@ -2737,7 +2721,7 @@
       <c r="V17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="W17" s="47" t="s">
+      <c r="W17" s="28" t="s">
         <v>35</v>
       </c>
       <c r="X17" s="9" t="s">
@@ -2746,17 +2730,17 @@
       <c r="Y17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="Z17" s="47" t="s">
+      <c r="Z17" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="AA17" s="55"/>
-      <c r="AB17" s="47" t="s">
+      <c r="AA17" s="31"/>
+      <c r="AB17" s="28" t="s">
         <v>20</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AD17" s="47" t="s">
+      <c r="AD17" s="28" t="s">
         <v>35</v>
       </c>
       <c r="AE17" s="3" t="s">
@@ -2765,7 +2749,7 @@
       <c r="AF17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AG17" s="47" t="s">
+      <c r="AG17" s="28" t="s">
         <v>35</v>
       </c>
       <c r="AH17" s="9" t="s">
@@ -2774,7 +2758,7 @@
       <c r="AI17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="AJ17" s="47" t="s">
+      <c r="AJ17" s="28" t="s">
         <v>35</v>
       </c>
       <c r="AK17" s="9" t="s">
@@ -2783,16 +2767,16 @@
       <c r="AL17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="AM17" s="47" t="s">
+      <c r="AM17" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="AO17" s="47" t="s">
+      <c r="AO17" s="28" t="s">
         <v>20</v>
       </c>
       <c r="AP17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AQ17" s="47" t="s">
+      <c r="AQ17" s="28" t="s">
         <v>35</v>
       </c>
       <c r="AR17" s="3" t="s">
@@ -2801,7 +2785,7 @@
       <c r="AS17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="AT17" s="47" t="s">
+      <c r="AT17" s="28" t="s">
         <v>35</v>
       </c>
       <c r="AU17" s="9" t="s">
@@ -2810,7 +2794,7 @@
       <c r="AV17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="AW17" s="47" t="s">
+      <c r="AW17" s="28" t="s">
         <v>35</v>
       </c>
       <c r="AX17" s="9" t="s">
@@ -2819,7 +2803,7 @@
       <c r="AY17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="AZ17" s="47" t="s">
+      <c r="AZ17" s="28" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2851,7 +2835,7 @@
       <c r="L18" s="6">
         <v>0.73005812699544603</v>
       </c>
-      <c r="M18" s="52"/>
+      <c r="M18" s="29"/>
       <c r="O18" s="5">
         <v>157.491792122156</v>
       </c>
@@ -2879,7 +2863,7 @@
       <c r="Y18" s="6">
         <v>1.00475359299919</v>
       </c>
-      <c r="AB18" s="53">
+      <c r="AB18" s="30">
         <v>13.236245367749699</v>
       </c>
       <c r="AC18" s="5">
@@ -2964,7 +2948,7 @@
       <c r="L19" s="6">
         <v>0.86446282869091995</v>
       </c>
-      <c r="M19" s="52"/>
+      <c r="M19" s="29"/>
       <c r="O19" s="5">
         <v>157.29900707611901</v>
       </c>
@@ -2992,7 +2976,7 @@
       <c r="Y19" s="6">
         <v>0.46057620855832399</v>
       </c>
-      <c r="AB19" s="53">
+      <c r="AB19" s="30">
         <v>13.236245367749699</v>
       </c>
       <c r="AC19" s="5">
@@ -3077,7 +3061,7 @@
       <c r="L20" s="6">
         <v>0.61635383312902503</v>
       </c>
-      <c r="M20" s="52"/>
+      <c r="M20" s="29"/>
       <c r="O20" s="5">
         <v>159.352853227227</v>
       </c>
@@ -3105,7 +3089,7 @@
       <c r="Y20" s="6">
         <v>1.0174902634114</v>
       </c>
-      <c r="AB20" s="53">
+      <c r="AB20" s="30">
         <v>13.2496111916915</v>
       </c>
       <c r="AC20" s="5">
@@ -3190,7 +3174,7 @@
       <c r="L21" s="6">
         <v>0.72984480789211603</v>
       </c>
-      <c r="M21" s="52"/>
+      <c r="M21" s="29"/>
       <c r="O21" s="5">
         <v>157.29900707611901</v>
       </c>
@@ -3218,7 +3202,7 @@
       <c r="Y21" s="6">
         <v>0.97220188931186902</v>
       </c>
-      <c r="AB21" s="53">
+      <c r="AB21" s="30">
         <v>13.308572250548099</v>
       </c>
       <c r="AC21" s="5">
@@ -3303,7 +3287,7 @@
       <c r="L22" s="6">
         <v>0.66684968307617798</v>
       </c>
-      <c r="M22" s="52"/>
+      <c r="M22" s="29"/>
       <c r="O22" s="5">
         <v>156.63177221391601</v>
       </c>
@@ -3331,7 +3315,7 @@
       <c r="Y22" s="6">
         <v>0.98780444655659705</v>
       </c>
-      <c r="AB22" s="53">
+      <c r="AB22" s="30">
         <v>13.2363942457426</v>
       </c>
       <c r="AC22" s="5">
@@ -3416,7 +3400,7 @@
       <c r="L23" s="6">
         <v>0.52390907977896095</v>
       </c>
-      <c r="M23" s="52"/>
+      <c r="M23" s="29"/>
       <c r="O23" s="5">
         <v>156.986009517112</v>
       </c>
@@ -3444,7 +3428,7 @@
       <c r="Y23" s="6">
         <v>0.73135202091426998</v>
       </c>
-      <c r="AB23" s="53">
+      <c r="AB23" s="30">
         <v>13.308674501574901</v>
       </c>
       <c r="AC23" s="5">
@@ -3529,7 +3513,7 @@
       <c r="L24" s="6">
         <v>0.85510723023493096</v>
       </c>
-      <c r="M24" s="52"/>
+      <c r="M24" s="29"/>
       <c r="O24" s="5">
         <v>158.196014729155</v>
       </c>
@@ -3557,7 +3541,7 @@
       <c r="Y24" s="6">
         <v>1.0147213122487999</v>
       </c>
-      <c r="AB24" s="53">
+      <c r="AB24" s="30">
         <v>13.308572250548099</v>
       </c>
       <c r="AC24" s="5">
@@ -3642,7 +3626,7 @@
       <c r="L25" s="6">
         <v>0.661985006820213</v>
       </c>
-      <c r="M25" s="52"/>
+      <c r="M25" s="29"/>
       <c r="O25" s="5">
         <v>157.491792122156</v>
       </c>
@@ -3670,7 +3654,7 @@
       <c r="Y25" s="6">
         <v>0.731352021572787</v>
       </c>
-      <c r="AB25" s="53">
+      <c r="AB25" s="30">
         <v>13.2496111916915</v>
       </c>
       <c r="AC25" s="5">
@@ -3755,7 +3739,7 @@
       <c r="L26" s="6">
         <v>0.61961678721450797</v>
       </c>
-      <c r="M26" s="52"/>
+      <c r="M26" s="29"/>
       <c r="O26" s="5">
         <v>156.87408337816299</v>
       </c>
@@ -3783,7 +3767,7 @@
       <c r="Y26" s="6">
         <v>0.86006578658153399</v>
       </c>
-      <c r="AB26" s="53">
+      <c r="AB26" s="30">
         <v>13.2958588107644</v>
       </c>
       <c r="AC26" s="5">
@@ -3868,7 +3852,7 @@
       <c r="L27" s="6">
         <v>0.95989886174272399</v>
       </c>
-      <c r="M27" s="52"/>
+      <c r="M27" s="29"/>
       <c r="O27" s="5">
         <v>157.491792122156</v>
       </c>
@@ -3896,7 +3880,7 @@
       <c r="Y27" s="6">
         <v>0.99652077413521101</v>
       </c>
-      <c r="AB27" s="53">
+      <c r="AB27" s="30">
         <v>13.2496111916915</v>
       </c>
       <c r="AC27" s="5">
@@ -3990,2843 +3974,52 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="AB15:AL15"/>
+    <mergeCell ref="AB16:AD16"/>
+    <mergeCell ref="AE16:AG16"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AK16:AM16"/>
+    <mergeCell ref="AO15:AY15"/>
+    <mergeCell ref="AO16:AQ16"/>
+    <mergeCell ref="AR16:AT16"/>
+    <mergeCell ref="AU16:AW16"/>
+    <mergeCell ref="AX16:AZ16"/>
+    <mergeCell ref="O15:Y15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="U16:W16"/>
+    <mergeCell ref="X16:Z16"/>
+    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="AO1:AY1"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="AB1:AL1"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AK2:AM2"/>
+    <mergeCell ref="O1:Y1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="O1:Y1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AB1:AL1"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AK2:AM2"/>
-    <mergeCell ref="AO1:AY1"/>
-    <mergeCell ref="AO2:AQ2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="B15:L15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="O15:Y15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="U16:W16"/>
-    <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="AO15:AY15"/>
-    <mergeCell ref="AO16:AQ16"/>
-    <mergeCell ref="AR16:AT16"/>
-    <mergeCell ref="AU16:AW16"/>
-    <mergeCell ref="AX16:AZ16"/>
-    <mergeCell ref="AB15:AL15"/>
-    <mergeCell ref="AB16:AD16"/>
-    <mergeCell ref="AE16:AG16"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AK16:AM16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E02A095-16D7-4FBB-B206-8C2A6F2CFB60}">
-  <dimension ref="B1:AZ34"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.85546875" style="54"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B1" s="28" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="22"/>
-      <c r="O1" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
-      <c r="W1" s="25"/>
-      <c r="X1" s="25"/>
-      <c r="Y1" s="25"/>
-      <c r="AB1" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC1" s="25"/>
-      <c r="AD1" s="25"/>
-      <c r="AE1" s="25"/>
-      <c r="AF1" s="25"/>
-      <c r="AG1" s="25"/>
-      <c r="AH1" s="25"/>
-      <c r="AI1" s="25"/>
-      <c r="AJ1" s="25"/>
-      <c r="AK1" s="56"/>
-      <c r="AL1" s="56"/>
-      <c r="AM1" s="51"/>
-      <c r="AO1" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="AP1" s="25"/>
-      <c r="AQ1" s="25"/>
-      <c r="AR1" s="25"/>
-      <c r="AS1" s="25"/>
-      <c r="AT1" s="25"/>
-      <c r="AU1" s="25"/>
-      <c r="AV1" s="25"/>
-      <c r="AW1" s="25"/>
-      <c r="AX1" s="56"/>
-      <c r="AY1" s="56"/>
-    </row>
-    <row r="2" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B2" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="49"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="O2" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="S2" s="45"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V2" s="49"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y2" s="27"/>
-      <c r="Z2" s="27"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC2" s="45"/>
-      <c r="AD2" s="46"/>
-      <c r="AE2" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF2" s="45"/>
-      <c r="AG2" s="46"/>
-      <c r="AH2" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AI2" s="49"/>
-      <c r="AJ2" s="50"/>
-      <c r="AK2" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL2" s="27"/>
-      <c r="AM2" s="27"/>
-      <c r="AO2" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="AP2" s="45"/>
-      <c r="AQ2" s="46"/>
-      <c r="AR2" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="AS2" s="45"/>
-      <c r="AT2" s="46"/>
-      <c r="AU2" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AV2" s="49"/>
-      <c r="AW2" s="50"/>
-      <c r="AX2" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AY2" s="27"/>
-      <c r="AZ2" s="27"/>
-    </row>
-    <row r="3" spans="2:52" ht="45" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="T3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="U3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="V3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="W3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="X3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA3" s="55"/>
-      <c r="AB3" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="AL3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AM3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO3" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AQ3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AR3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AS3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AT3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AU3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AW3" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AX3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="AY3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AZ3" s="47" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="O4" s="5">
-        <v>50.189180557709498</v>
-      </c>
-      <c r="P4" s="5">
-        <v>6.8272041826728298</v>
-      </c>
-      <c r="Q4" s="5">
-        <v>1.66333055496215</v>
-      </c>
-      <c r="R4" s="6">
-        <v>2.40398255283031</v>
-      </c>
-      <c r="S4" s="6">
-        <v>0.494699860082361</v>
-      </c>
-      <c r="T4" s="6">
-        <v>1.6662456989288299</v>
-      </c>
-      <c r="U4" s="5">
-        <v>2.5208897211674199</v>
-      </c>
-      <c r="V4" s="5">
-        <v>0.47344483768397699</v>
-      </c>
-      <c r="W4" s="5">
-        <v>1.8126475811004601</v>
-      </c>
-      <c r="X4" s="6">
-        <v>1.34621453385329</v>
-      </c>
-      <c r="Y4" s="6">
-        <v>0.35832775281353502</v>
-      </c>
-      <c r="Z4" s="4">
-        <v>1.7666320800781199</v>
-      </c>
-      <c r="AB4" s="5">
-        <v>2.0282019718480502</v>
-      </c>
-      <c r="AC4" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD4" s="5">
-        <v>0.15384221076965299</v>
-      </c>
-      <c r="AE4" s="6">
-        <v>2.93314349751103</v>
-      </c>
-      <c r="AF4" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AG4" s="6">
-        <v>0.164636850357055</v>
-      </c>
-      <c r="AH4" s="5">
-        <v>3.1835707328913601</v>
-      </c>
-      <c r="AI4" s="5">
-        <v>0.65565129784223597</v>
-      </c>
-      <c r="AJ4" s="5">
-        <v>0.17476344108581501</v>
-      </c>
-      <c r="AK4" s="6">
-        <v>3.0446059739842699</v>
-      </c>
-      <c r="AL4" s="6">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AM4" s="6">
-        <v>0.16964745521545399</v>
-      </c>
-      <c r="AO4" s="5">
-        <v>34.570056762068198</v>
-      </c>
-      <c r="AP4" s="5">
-        <v>4.5778664577056496</v>
-      </c>
-      <c r="AQ4" s="5">
-        <v>1.67585968971252</v>
-      </c>
-      <c r="AR4" s="6">
-        <v>1.8250170991933701</v>
-      </c>
-      <c r="AS4" s="6">
-        <v>0.33633033357449799</v>
-      </c>
-      <c r="AT4" s="6">
-        <v>1.7158291339874201</v>
-      </c>
-      <c r="AU4" s="5">
-        <v>1.8523706039791701</v>
-      </c>
-      <c r="AV4" s="5">
-        <v>0.34156715764353801</v>
-      </c>
-      <c r="AW4" s="5">
-        <v>1.6030962467193599</v>
-      </c>
-      <c r="AX4" s="6">
-        <v>1.8795419666048101</v>
-      </c>
-      <c r="AY4" s="6">
-        <v>0.34574964955663201</v>
-      </c>
-      <c r="AZ4" s="4">
-        <v>1.69498038291931</v>
-      </c>
-    </row>
-    <row r="5" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="O5" s="5">
-        <v>49.008992449178898</v>
-      </c>
-      <c r="P5" s="5">
-        <v>6.5588284593994697</v>
-      </c>
-      <c r="Q5" s="5">
-        <v>1.6003003120422301</v>
-      </c>
-      <c r="R5" s="6">
-        <v>1.6098328308093</v>
-      </c>
-      <c r="S5" s="6">
-        <v>0.35390275267126498</v>
-      </c>
-      <c r="T5" s="6">
-        <v>1.63829588890075</v>
-      </c>
-      <c r="U5" s="5">
-        <v>2.6847186811052599</v>
-      </c>
-      <c r="V5" s="5">
-        <v>0.49866574556051502</v>
-      </c>
-      <c r="W5" s="5">
-        <v>1.63096380233764</v>
-      </c>
-      <c r="X5" s="6">
-        <v>2.7075638424040802</v>
-      </c>
-      <c r="Y5" s="6">
-        <v>0.55112744515069301</v>
-      </c>
-      <c r="Z5" s="4">
-        <v>1.6707100868225</v>
-      </c>
-      <c r="AB5" s="5">
-        <v>2.0576101229880499</v>
-      </c>
-      <c r="AC5" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD5" s="5">
-        <v>0.143673419952392</v>
-      </c>
-      <c r="AE5" s="6">
-        <v>3.0231717517272201</v>
-      </c>
-      <c r="AF5" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AG5" s="6">
-        <v>0.15351915359497001</v>
-      </c>
-      <c r="AH5" s="5">
-        <v>3.0014742636059601</v>
-      </c>
-      <c r="AI5" s="5">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AJ5" s="5">
-        <v>0.18802881240844699</v>
-      </c>
-      <c r="AK5" s="6">
-        <v>3.0732721507638598</v>
-      </c>
-      <c r="AL5" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AM5" s="6">
-        <v>0.164550065994262</v>
-      </c>
-      <c r="AO5" s="5">
-        <v>34.554127832915199</v>
-      </c>
-      <c r="AP5" s="5">
-        <v>4.5660618080018196</v>
-      </c>
-      <c r="AQ5" s="5">
-        <v>1.51645755767822</v>
-      </c>
-      <c r="AR5" s="6">
-        <v>1.96093445188255</v>
-      </c>
-      <c r="AS5" s="6">
-        <v>0.35374707690719498</v>
-      </c>
-      <c r="AT5" s="6">
-        <v>1.6856594085693299</v>
-      </c>
-      <c r="AU5" s="5">
-        <v>1.9641721709049</v>
-      </c>
-      <c r="AV5" s="5">
-        <v>0.36261738420721501</v>
-      </c>
-      <c r="AW5" s="5">
-        <v>1.7167608737945499</v>
-      </c>
-      <c r="AX5" s="6">
-        <v>1.91781862598536</v>
-      </c>
-      <c r="AY5" s="6">
-        <v>0.35301643444209602</v>
-      </c>
-      <c r="AZ5" s="4">
-        <v>1.7476181983947701</v>
-      </c>
-    </row>
-    <row r="6" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="O6" s="5">
-        <v>50.370043311847297</v>
-      </c>
-      <c r="P6" s="5">
-        <v>6.8266682265390397</v>
-      </c>
-      <c r="Q6" s="5">
-        <v>1.6202797889709399</v>
-      </c>
-      <c r="R6" s="6">
-        <v>3.31366070223083</v>
-      </c>
-      <c r="S6" s="6">
-        <v>0.59823315379531405</v>
-      </c>
-      <c r="T6" s="6">
-        <v>1.63130760192871</v>
-      </c>
-      <c r="U6" s="5">
-        <v>1.8698821640777401</v>
-      </c>
-      <c r="V6" s="5">
-        <v>0.36723080126573698</v>
-      </c>
-      <c r="W6" s="5">
-        <v>1.6870131492614699</v>
-      </c>
-      <c r="X6" s="6">
-        <v>2.4706305240653101</v>
-      </c>
-      <c r="Y6" s="6">
-        <v>0.47413541013360899</v>
-      </c>
-      <c r="Z6" s="4">
-        <v>1.6828861236572199</v>
-      </c>
-      <c r="AB6" s="5">
-        <v>2.0124832402399999</v>
-      </c>
-      <c r="AC6" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD6" s="5">
-        <v>0.15831112861633301</v>
-      </c>
-      <c r="AE6" s="6">
-        <v>3.1835707328913601</v>
-      </c>
-      <c r="AF6" s="6">
-        <v>0.65565129784223597</v>
-      </c>
-      <c r="AG6" s="6">
-        <v>0.15638685226440399</v>
-      </c>
-      <c r="AH6" s="5">
-        <v>3.0052609093097602</v>
-      </c>
-      <c r="AI6" s="5">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AJ6" s="5">
-        <v>0.1725754737854</v>
-      </c>
-      <c r="AK6" s="6">
-        <v>2.9332438502332301</v>
-      </c>
-      <c r="AL6" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AM6" s="6">
-        <v>0.17924475669860801</v>
-      </c>
-      <c r="AO6" s="5">
-        <v>34.586395368105499</v>
-      </c>
-      <c r="AP6" s="5">
-        <v>4.5775860505016004</v>
-      </c>
-      <c r="AQ6" s="5">
-        <v>1.56898593902587</v>
-      </c>
-      <c r="AR6" s="6">
-        <v>1.88217908842425</v>
-      </c>
-      <c r="AS6" s="6">
-        <v>0.35140505638671998</v>
-      </c>
-      <c r="AT6" s="6">
-        <v>1.71125292778015</v>
-      </c>
-      <c r="AU6" s="5">
-        <v>1.8959378968298899</v>
-      </c>
-      <c r="AV6" s="5">
-        <v>0.34943432354470599</v>
-      </c>
-      <c r="AW6" s="5">
-        <v>1.7259268760681099</v>
-      </c>
-      <c r="AX6" s="6">
-        <v>1.96427586073906</v>
-      </c>
-      <c r="AY6" s="6">
-        <v>0.35731335216903298</v>
-      </c>
-      <c r="AZ6" s="4">
-        <v>1.6857831478118801</v>
-      </c>
-    </row>
-    <row r="7" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="O7" s="5">
-        <v>48.5283966162228</v>
-      </c>
-      <c r="P7" s="5">
-        <v>6.39532451008645</v>
-      </c>
-      <c r="Q7" s="5">
-        <v>1.5867009162902801</v>
-      </c>
-      <c r="R7" s="6">
-        <v>2.3974738662768198</v>
-      </c>
-      <c r="S7" s="6">
-        <v>0.49437600947429899</v>
-      </c>
-      <c r="T7" s="6">
-        <v>1.67491650581359</v>
-      </c>
-      <c r="U7" s="5">
-        <v>2.8090651842160401</v>
-      </c>
-      <c r="V7" s="5">
-        <v>0.55561814716228497</v>
-      </c>
-      <c r="W7" s="5">
-        <v>1.6501393318176201</v>
-      </c>
-      <c r="X7" s="6">
-        <v>1.9235703445824599</v>
-      </c>
-      <c r="Y7" s="6">
-        <v>0.37579443485147102</v>
-      </c>
-      <c r="Z7" s="4">
-        <v>1.7136993408203101</v>
-      </c>
-      <c r="AB7" s="5">
-        <v>1.98733133553576</v>
-      </c>
-      <c r="AC7" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD7" s="5">
-        <v>0.150824069976806</v>
-      </c>
-      <c r="AE7" s="6">
-        <v>2.9709094694099698</v>
-      </c>
-      <c r="AF7" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AG7" s="6">
-        <v>0.156632900238037</v>
-      </c>
-      <c r="AH7" s="5">
-        <v>3.1234714223794802</v>
-      </c>
-      <c r="AI7" s="5">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AJ7" s="5">
-        <v>0.16536331176757799</v>
-      </c>
-      <c r="AK7" s="6">
-        <v>2.9332438502332301</v>
-      </c>
-      <c r="AL7" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AM7" s="6">
-        <v>0.16520929336547799</v>
-      </c>
-      <c r="AO7" s="5">
-        <v>34.474323231873001</v>
-      </c>
-      <c r="AP7" s="5">
-        <v>4.5812551646225703</v>
-      </c>
-      <c r="AQ7" s="5">
-        <v>1.63421034812927</v>
-      </c>
-      <c r="AR7" s="6">
-        <v>1.88221703832479</v>
-      </c>
-      <c r="AS7" s="6">
-        <v>0.35140505652889598</v>
-      </c>
-      <c r="AT7" s="6">
-        <v>1.74588942527771</v>
-      </c>
-      <c r="AU7" s="5">
-        <v>1.8654391378277699</v>
-      </c>
-      <c r="AV7" s="5">
-        <v>0.35136993223547403</v>
-      </c>
-      <c r="AW7" s="5">
-        <v>1.6497774124145499</v>
-      </c>
-      <c r="AX7" s="6">
-        <v>1.9178899634194899</v>
-      </c>
-      <c r="AY7" s="6">
-        <v>0.35300853576487501</v>
-      </c>
-      <c r="AZ7" s="4">
-        <v>1.6674399375915501</v>
-      </c>
-    </row>
-    <row r="8" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="O8" s="5">
-        <v>50.189180557709498</v>
-      </c>
-      <c r="P8" s="5">
-        <v>6.8272041826728298</v>
-      </c>
-      <c r="Q8" s="5">
-        <v>1.6410756111145</v>
-      </c>
-      <c r="R8" s="6">
-        <v>2.3363436265518498</v>
-      </c>
-      <c r="S8" s="6">
-        <v>0.49525277741667301</v>
-      </c>
-      <c r="T8" s="6">
-        <v>1.68248891830444</v>
-      </c>
-      <c r="U8" s="5">
-        <v>3.2921811589554202</v>
-      </c>
-      <c r="V8" s="5">
-        <v>0.61038119286221504</v>
-      </c>
-      <c r="W8" s="5">
-        <v>1.7693681716918901</v>
-      </c>
-      <c r="X8" s="6">
-        <v>2.39747268966476</v>
-      </c>
-      <c r="Y8" s="6">
-        <v>0.479906115601407</v>
-      </c>
-      <c r="Z8" s="4">
-        <v>1.80891561508178</v>
-      </c>
-      <c r="AB8" s="5">
-        <v>2.0045866890630801</v>
-      </c>
-      <c r="AC8" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD8" s="5">
-        <v>0.1446533203125</v>
-      </c>
-      <c r="AE8" s="6">
-        <v>2.8887491003138202</v>
-      </c>
-      <c r="AF8" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AG8" s="6">
-        <v>0.164668083190917</v>
-      </c>
-      <c r="AH8" s="5">
-        <v>3.1300087680066402</v>
-      </c>
-      <c r="AI8" s="5">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AJ8" s="5">
-        <v>0.20038580894470201</v>
-      </c>
-      <c r="AK8" s="6">
-        <v>3.0895272691364801</v>
-      </c>
-      <c r="AL8" s="6">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AM8" s="6">
-        <v>0.160871982574462</v>
-      </c>
-      <c r="AO8" s="5">
-        <v>34.482423779545499</v>
-      </c>
-      <c r="AP8" s="5">
-        <v>4.5801967278307698</v>
-      </c>
-      <c r="AQ8" s="5">
-        <v>1.68693852424621</v>
-      </c>
-      <c r="AR8" s="6">
-        <v>1.8315258657560201</v>
-      </c>
-      <c r="AS8" s="6">
-        <v>0.34577767622515698</v>
-      </c>
-      <c r="AT8" s="6">
-        <v>1.6904382705688401</v>
-      </c>
-      <c r="AU8" s="5">
-        <v>1.8523461079911401</v>
-      </c>
-      <c r="AV8" s="5">
-        <v>0.34156715758035</v>
-      </c>
-      <c r="AW8" s="5">
-        <v>1.6989877223968499</v>
-      </c>
-      <c r="AX8" s="6">
-        <v>1.94458113911453</v>
-      </c>
-      <c r="AY8" s="6">
-        <v>0.36071379860479102</v>
-      </c>
-      <c r="AZ8" s="4">
-        <v>1.66584968566894</v>
-      </c>
-    </row>
-    <row r="9" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="O9" s="5">
-        <v>49.619431099961197</v>
-      </c>
-      <c r="P9" s="5">
-        <v>6.6224281863214802</v>
-      </c>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="6">
-        <v>2.06027858560702</v>
-      </c>
-      <c r="S9" s="6">
-        <v>0.41902119187009701</v>
-      </c>
-      <c r="T9" s="6"/>
-      <c r="U9" s="5">
-        <v>2.1176598714663699</v>
-      </c>
-      <c r="V9" s="5">
-        <v>0.420783326797598</v>
-      </c>
-      <c r="W9" s="5"/>
-      <c r="X9" s="6">
-        <v>1.05066650115089</v>
-      </c>
-      <c r="Y9" s="6">
-        <v>0.25434177251207701</v>
-      </c>
-      <c r="Z9" s="4"/>
-      <c r="AB9" s="5">
-        <v>2.03035231561176</v>
-      </c>
-      <c r="AC9" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD9" s="5">
-        <v>0.142905473709106</v>
-      </c>
-      <c r="AE9" s="6">
-        <v>3.0233946110574101</v>
-      </c>
-      <c r="AF9" s="6">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AG9" s="6"/>
-      <c r="AH9" s="5">
-        <v>3.0222659675151302</v>
-      </c>
-      <c r="AI9" s="5">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AJ9" s="5"/>
-      <c r="AK9" s="6">
-        <v>3.0231717517272201</v>
-      </c>
-      <c r="AL9" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AM9" s="6"/>
-      <c r="AO9" s="5">
-        <v>34.570056762068198</v>
-      </c>
-      <c r="AP9" s="5">
-        <v>4.5778664577056496</v>
-      </c>
-      <c r="AQ9" s="5">
-        <v>1.62964344024658</v>
-      </c>
-      <c r="AR9" s="6">
-        <v>1.86147110489288</v>
-      </c>
-      <c r="AS9" s="6">
-        <v>0.34558367107705801</v>
-      </c>
-      <c r="AT9" s="6">
-        <v>1.6265385150909399</v>
-      </c>
-      <c r="AU9" s="5">
-        <v>1.96362562254665</v>
-      </c>
-      <c r="AV9" s="5">
-        <v>0.36222639562867198</v>
-      </c>
-      <c r="AW9" s="5">
-        <v>1.72279024124145</v>
-      </c>
-      <c r="AX9" s="6">
-        <v>1.9642715242957101</v>
-      </c>
-      <c r="AY9" s="6">
-        <v>0.35731730151554097</v>
-      </c>
-      <c r="AZ9" s="4"/>
-    </row>
-    <row r="10" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="O10" s="5">
-        <v>50.370043311847297</v>
-      </c>
-      <c r="P10" s="5">
-        <v>6.8266682265390397</v>
-      </c>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="6">
-        <v>1.1013427759766601</v>
-      </c>
-      <c r="S10" s="6">
-        <v>0.279195398098668</v>
-      </c>
-      <c r="T10" s="6"/>
-      <c r="U10" s="5">
-        <v>1.8886807440369899</v>
-      </c>
-      <c r="V10" s="5">
-        <v>0.41993899419076303</v>
-      </c>
-      <c r="W10" s="5"/>
-      <c r="X10" s="6">
-        <v>1.08014977882427</v>
-      </c>
-      <c r="Y10" s="6">
-        <v>0.28419236315363</v>
-      </c>
-      <c r="Z10" s="4"/>
-      <c r="AB10" s="5">
-        <v>2.0282019718480502</v>
-      </c>
-      <c r="AC10" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD10" s="5">
-        <v>0.151252746582031</v>
-      </c>
-      <c r="AE10" s="6">
-        <v>3.0233946110574101</v>
-      </c>
-      <c r="AF10" s="6">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AG10" s="6"/>
-      <c r="AH10" s="5">
-        <v>3.0769912027266599</v>
-      </c>
-      <c r="AI10" s="5">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AJ10" s="5"/>
-      <c r="AK10" s="6">
-        <v>2.9681463342075101</v>
-      </c>
-      <c r="AL10" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AM10" s="6"/>
-      <c r="AO10" s="5">
-        <v>34.498810594745102</v>
-      </c>
-      <c r="AP10" s="5">
-        <v>4.5805798233599297</v>
-      </c>
-      <c r="AQ10" s="5">
-        <v>1.5438361167907699</v>
-      </c>
-      <c r="AR10" s="6">
-        <v>1.86657481807766</v>
-      </c>
-      <c r="AS10" s="6">
-        <v>0.34383410086548399</v>
-      </c>
-      <c r="AT10" s="6">
-        <v>1.5724868774414</v>
-      </c>
-      <c r="AU10" s="5">
-        <v>1.90028400803589</v>
-      </c>
-      <c r="AV10" s="5">
-        <v>0.34945012130988901</v>
-      </c>
-      <c r="AW10" s="5">
-        <v>1.7850067615509</v>
-      </c>
-      <c r="AX10" s="6">
-        <v>1.90928027610508</v>
-      </c>
-      <c r="AY10" s="6">
-        <v>0.34945018620593998</v>
-      </c>
-      <c r="AZ10" s="4"/>
-    </row>
-    <row r="11" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="O11" s="5">
-        <v>50.6021835670551</v>
-      </c>
-      <c r="P11" s="5">
-        <v>6.8159615936773701</v>
-      </c>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="6">
-        <v>2.4294044850569798</v>
-      </c>
-      <c r="S11" s="6">
-        <v>0.491532450674801</v>
-      </c>
-      <c r="T11" s="6"/>
-      <c r="U11" s="5">
-        <v>2.4929016378617299</v>
-      </c>
-      <c r="V11" s="5">
-        <v>0.47851192255269298</v>
-      </c>
-      <c r="W11" s="5"/>
-      <c r="X11" s="6">
-        <v>2.3570848611973498</v>
-      </c>
-      <c r="Y11" s="6">
-        <v>0.47000785524292399</v>
-      </c>
-      <c r="Z11" s="4"/>
-      <c r="AB11" s="5">
-        <v>2.0045866890630801</v>
-      </c>
-      <c r="AC11" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD11" s="5">
-        <v>0.15222430229187001</v>
-      </c>
-      <c r="AE11" s="6">
-        <v>3.1856421504299002</v>
-      </c>
-      <c r="AF11" s="6">
-        <v>0.65565129784223597</v>
-      </c>
-      <c r="AG11" s="6"/>
-      <c r="AH11" s="5">
-        <v>3.1856421504299002</v>
-      </c>
-      <c r="AI11" s="5">
-        <v>0.65565129784223597</v>
-      </c>
-      <c r="AJ11" s="5"/>
-      <c r="AK11" s="6">
-        <v>3.1450098960334101</v>
-      </c>
-      <c r="AL11" s="6">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AM11" s="6"/>
-      <c r="AO11" s="5">
-        <v>34.554127832915199</v>
-      </c>
-      <c r="AP11" s="5">
-        <v>4.5660618080018196</v>
-      </c>
-      <c r="AQ11" s="5">
-        <v>1.5707144737243599</v>
-      </c>
-      <c r="AR11" s="6">
-        <v>1.81268296370352</v>
-      </c>
-      <c r="AS11" s="6">
-        <v>0.33337223640394198</v>
-      </c>
-      <c r="AT11" s="6">
-        <v>1.7173385620117101</v>
-      </c>
-      <c r="AU11" s="5">
-        <v>1.96429126731902</v>
-      </c>
-      <c r="AV11" s="5">
-        <v>0.35731730156293201</v>
-      </c>
-      <c r="AW11" s="5"/>
-      <c r="AX11" s="6">
-        <v>1.8795069801762501</v>
-      </c>
-      <c r="AY11" s="6">
-        <v>0.34575359895052998</v>
-      </c>
-      <c r="AZ11" s="4"/>
-    </row>
-    <row r="12" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="O12" s="5">
-        <v>48.5283966162228</v>
-      </c>
-      <c r="P12" s="5">
-        <v>6.39532451008645</v>
-      </c>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="6">
-        <v>2.8583793701106899</v>
-      </c>
-      <c r="S12" s="6">
-        <v>0.57377303940268798</v>
-      </c>
-      <c r="T12" s="6"/>
-      <c r="U12" s="5">
-        <v>2.2571410688804598</v>
-      </c>
-      <c r="V12" s="5">
-        <v>0.46259787093209498</v>
-      </c>
-      <c r="W12" s="5"/>
-      <c r="X12" s="6">
-        <v>2.4566723216903199</v>
-      </c>
-      <c r="Y12" s="6">
-        <v>0.46852708080793398</v>
-      </c>
-      <c r="Z12" s="4"/>
-      <c r="AB12" s="5">
-        <v>2.0124832402399999</v>
-      </c>
-      <c r="AC12" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD12" s="5">
-        <v>0.145009040832519</v>
-      </c>
-      <c r="AE12" s="6">
-        <v>2.9469306504008701</v>
-      </c>
-      <c r="AF12" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AG12" s="6"/>
-      <c r="AH12" s="5">
-        <v>3.1524446068305201</v>
-      </c>
-      <c r="AI12" s="5">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AJ12" s="5"/>
-      <c r="AK12" s="6">
-        <v>2.9709094694099698</v>
-      </c>
-      <c r="AL12" s="6">
-        <v>0.65213375302212495</v>
-      </c>
-      <c r="AM12" s="6"/>
-      <c r="AO12" s="5">
-        <v>34.6014705772876</v>
-      </c>
-      <c r="AP12" s="5">
-        <v>4.5785181060921998</v>
-      </c>
-      <c r="AQ12" s="5">
-        <v>1.55043768882751</v>
-      </c>
-      <c r="AR12" s="6">
-        <v>1.8125561645361601</v>
-      </c>
-      <c r="AS12" s="6">
-        <v>0.33334854013531301</v>
-      </c>
-      <c r="AT12" s="6">
-        <v>1.6649475097656199</v>
-      </c>
-      <c r="AU12" s="5">
-        <v>1.96488011670068</v>
-      </c>
-      <c r="AV12" s="5">
-        <v>0.36261343482516201</v>
-      </c>
-      <c r="AW12" s="5"/>
-      <c r="AX12" s="6">
-        <v>1.9178899634194899</v>
-      </c>
-      <c r="AY12" s="6">
-        <v>0.35300853576487501</v>
-      </c>
-      <c r="AZ12" s="4"/>
-    </row>
-    <row r="13" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="O13" s="5">
-        <v>50.813193764563998</v>
-      </c>
-      <c r="P13" s="5">
-        <v>6.8053931798874796</v>
-      </c>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="6">
-        <v>2.07438188382043</v>
-      </c>
-      <c r="S13" s="6">
-        <v>0.43125921121579203</v>
-      </c>
-      <c r="T13" s="6"/>
-      <c r="U13" s="5">
-        <v>2.5100936022216298</v>
-      </c>
-      <c r="V13" s="5">
-        <v>2.5100936022216298</v>
-      </c>
-      <c r="W13" s="5"/>
-      <c r="X13" s="6">
-        <v>2.6805114554649099</v>
-      </c>
-      <c r="Y13" s="6">
-        <v>0.50105033491431605</v>
-      </c>
-      <c r="Z13" s="4"/>
-      <c r="AB13" s="5">
-        <v>2.0282019718480502</v>
-      </c>
-      <c r="AC13" s="5">
-        <v>0.37754673426285001</v>
-      </c>
-      <c r="AD13" s="5">
-        <v>0.15650820732116699</v>
-      </c>
-      <c r="AE13" s="6">
-        <v>3.1450098960334101</v>
-      </c>
-      <c r="AF13" s="6">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="5">
-        <v>3.0895272691364801</v>
-      </c>
-      <c r="AI13" s="5">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AJ13" s="5"/>
-      <c r="AK13" s="6">
-        <v>3.1234714223794802</v>
-      </c>
-      <c r="AL13" s="6">
-        <v>0.65226013362701096</v>
-      </c>
-      <c r="AM13" s="6"/>
-      <c r="AO13" s="5">
-        <v>34.63132536506</v>
-      </c>
-      <c r="AP13" s="5">
-        <v>4.5643280255556196</v>
-      </c>
-      <c r="AQ13" s="5">
-        <v>1.64094710350036</v>
-      </c>
-      <c r="AR13" s="6">
-        <v>1.8250318583902301</v>
-      </c>
-      <c r="AS13" s="6">
-        <v>0.33629873874712601</v>
-      </c>
-      <c r="AT13" s="6">
-        <v>1.7591118812561</v>
-      </c>
-      <c r="AU13" s="5">
-        <v>1.9040866582123299</v>
-      </c>
-      <c r="AV13" s="5">
-        <v>0.35445006159312697</v>
-      </c>
-      <c r="AW13" s="5"/>
-      <c r="AX13" s="6">
-        <v>1.96429126731902</v>
-      </c>
-      <c r="AY13" s="6">
-        <v>0.35731730156293201</v>
-      </c>
-      <c r="AZ13" s="4"/>
-    </row>
-    <row r="14" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-    </row>
-    <row r="15" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B15" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-      <c r="M15" s="22"/>
-      <c r="O15" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
-      <c r="V15" s="25"/>
-      <c r="W15" s="25"/>
-      <c r="X15" s="25"/>
-      <c r="Y15" s="25"/>
-      <c r="AB15" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="AC15" s="25"/>
-      <c r="AD15" s="25"/>
-      <c r="AE15" s="25"/>
-      <c r="AF15" s="25"/>
-      <c r="AG15" s="25"/>
-      <c r="AH15" s="25"/>
-      <c r="AI15" s="25"/>
-      <c r="AJ15" s="25"/>
-      <c r="AK15" s="25"/>
-      <c r="AL15" s="25"/>
-      <c r="AM15" s="51"/>
-      <c r="AO15" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP15" s="25"/>
-      <c r="AQ15" s="25"/>
-      <c r="AR15" s="25"/>
-      <c r="AS15" s="25"/>
-      <c r="AT15" s="25"/>
-      <c r="AU15" s="25"/>
-      <c r="AV15" s="25"/>
-      <c r="AW15" s="25"/>
-      <c r="AX15" s="25"/>
-      <c r="AY15" s="25"/>
-    </row>
-    <row r="16" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B16" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="49"/>
-      <c r="J16" s="50"/>
-      <c r="K16" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-      <c r="O16" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="46"/>
-      <c r="R16" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="S16" s="45"/>
-      <c r="T16" s="46"/>
-      <c r="U16" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="V16" s="49"/>
-      <c r="W16" s="50"/>
-      <c r="X16" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y16" s="27"/>
-      <c r="Z16" s="27"/>
-      <c r="AA16" s="51"/>
-      <c r="AB16" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC16" s="45"/>
-      <c r="AD16" s="46"/>
-      <c r="AE16" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF16" s="45"/>
-      <c r="AG16" s="46"/>
-      <c r="AH16" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AI16" s="49"/>
-      <c r="AJ16" s="50"/>
-      <c r="AK16" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL16" s="27"/>
-      <c r="AM16" s="27"/>
-      <c r="AO16" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="AP16" s="45"/>
-      <c r="AQ16" s="46"/>
-      <c r="AR16" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="AS16" s="45"/>
-      <c r="AT16" s="46"/>
-      <c r="AU16" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="AV16" s="49"/>
-      <c r="AW16" s="50"/>
-      <c r="AX16" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="AY16" s="27"/>
-      <c r="AZ16" s="27"/>
-    </row>
-    <row r="17" spans="2:52" ht="45" x14ac:dyDescent="0.25">
-      <c r="B17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="M17" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q17" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="T17" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="U17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="V17" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="W17" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="X17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y17" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z17" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA17" s="55"/>
-      <c r="AB17" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD17" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AE17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG17" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI17" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ17" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="AL17" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AM17" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO17" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="AP17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AQ17" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AR17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AS17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AT17" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AU17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="AV17" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AW17" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="AX17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="AY17" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="AZ17" s="47" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="O18" s="5">
-        <v>157.491792122156</v>
-      </c>
-      <c r="P18" s="5">
-        <v>14.514140074457901</v>
-      </c>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="6">
-        <v>2.3286845435735199</v>
-      </c>
-      <c r="S18" s="6">
-        <v>0.39920932369799</v>
-      </c>
-      <c r="T18" s="6"/>
-      <c r="U18" s="5">
-        <v>8.1717884699325491</v>
-      </c>
-      <c r="V18" s="5">
-        <v>1.0129108861659399</v>
-      </c>
-      <c r="W18" s="5"/>
-      <c r="X18" s="6">
-        <v>8.3899543661545302</v>
-      </c>
-      <c r="Y18" s="6">
-        <v>1.00475359299919</v>
-      </c>
-      <c r="Z18" s="4"/>
-      <c r="AB18" s="53">
-        <v>13.236245367749699</v>
-      </c>
-      <c r="AC18" s="5">
-        <v>1.57146153421673</v>
-      </c>
-      <c r="AD18" s="5"/>
-      <c r="AE18" s="6">
-        <v>1.90493440038017</v>
-      </c>
-      <c r="AF18" s="6">
-        <v>0.45806793222847902</v>
-      </c>
-      <c r="AG18" s="6"/>
-      <c r="AH18" s="5">
-        <v>1.9321830134050899</v>
-      </c>
-      <c r="AI18" s="5">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AJ18" s="5"/>
-      <c r="AK18" s="6">
-        <v>1.92632846796436</v>
-      </c>
-      <c r="AL18" s="6">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AM18" s="6"/>
-      <c r="AO18" s="5">
-        <v>59.705630088686199</v>
-      </c>
-      <c r="AP18" s="5">
-        <v>5.6586034268060601</v>
-      </c>
-      <c r="AQ18" s="5"/>
-      <c r="AR18" s="6">
-        <v>4.2657953513727804</v>
-      </c>
-      <c r="AS18" s="6">
-        <v>0.73609280545728795</v>
-      </c>
-      <c r="AT18" s="6"/>
-      <c r="AU18" s="5">
-        <v>4.3067382375590597</v>
-      </c>
-      <c r="AV18" s="5">
-        <v>0.78876787017055605</v>
-      </c>
-      <c r="AW18" s="5"/>
-      <c r="AX18" s="6">
-        <v>4.5961418368911104</v>
-      </c>
-      <c r="AY18" s="6">
-        <v>0.77049022674415901</v>
-      </c>
-      <c r="AZ18" s="4"/>
-    </row>
-    <row r="19" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="O19" s="5">
-        <v>157.29900707611901</v>
-      </c>
-      <c r="P19" s="5">
-        <v>14.4931915247916</v>
-      </c>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="6">
-        <v>7.8733419303139298</v>
-      </c>
-      <c r="S19" s="6">
-        <v>1.00388575257059</v>
-      </c>
-      <c r="T19" s="6"/>
-      <c r="U19" s="5">
-        <v>6.2307112245394896</v>
-      </c>
-      <c r="V19" s="5">
-        <v>0.945277006207351</v>
-      </c>
-      <c r="W19" s="5"/>
-      <c r="X19" s="6">
-        <v>2.61612899501934</v>
-      </c>
-      <c r="Y19" s="6">
-        <v>0.46057620855832399</v>
-      </c>
-      <c r="Z19" s="4"/>
-      <c r="AB19" s="53">
-        <v>13.236245367749699</v>
-      </c>
-      <c r="AC19" s="5">
-        <v>1.57146153421673</v>
-      </c>
-      <c r="AD19" s="5"/>
-      <c r="AE19" s="6">
-        <v>1.9004171801880201</v>
-      </c>
-      <c r="AF19" s="6">
-        <v>0.45806793222847902</v>
-      </c>
-      <c r="AG19" s="6"/>
-      <c r="AH19" s="5">
-        <v>1.90072564987806</v>
-      </c>
-      <c r="AI19" s="5">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AJ19" s="5"/>
-      <c r="AK19" s="6">
-        <v>1.92872858661624</v>
-      </c>
-      <c r="AL19" s="6">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AM19" s="6"/>
-      <c r="AO19" s="5">
-        <v>60.177890822449797</v>
-      </c>
-      <c r="AP19" s="5">
-        <v>5.7023692293553001</v>
-      </c>
-      <c r="AQ19" s="5"/>
-      <c r="AR19" s="6">
-        <v>3.9426046524217799</v>
-      </c>
-      <c r="AS19" s="6">
-        <v>0.82754599084641001</v>
-      </c>
-      <c r="AT19" s="6"/>
-      <c r="AU19" s="5">
-        <v>4.3359389837744198</v>
-      </c>
-      <c r="AV19" s="5">
-        <v>0.78875255111021403</v>
-      </c>
-      <c r="AW19" s="5"/>
-      <c r="AX19" s="6">
-        <v>4.1287261615403503</v>
-      </c>
-      <c r="AY19" s="6">
-        <v>0.74457174085613997</v>
-      </c>
-      <c r="AZ19" s="4"/>
-    </row>
-    <row r="20" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="O20" s="5">
-        <v>159.352853227227</v>
-      </c>
-      <c r="P20" s="5">
-        <v>14.678664624417801</v>
-      </c>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="6">
-        <v>5.3107040461542097</v>
-      </c>
-      <c r="S20" s="6">
-        <v>0.93572788648500804</v>
-      </c>
-      <c r="T20" s="6"/>
-      <c r="U20" s="5">
-        <v>8.8419317184422397</v>
-      </c>
-      <c r="V20" s="5">
-        <v>1.0105737421724099</v>
-      </c>
-      <c r="W20" s="5"/>
-      <c r="X20" s="6">
-        <v>8.9036487278638106</v>
-      </c>
-      <c r="Y20" s="6">
-        <v>1.0174902634114</v>
-      </c>
-      <c r="Z20" s="4"/>
-      <c r="AB20" s="53">
-        <v>13.2496111916915</v>
-      </c>
-      <c r="AC20" s="5">
-        <v>1.57146153421673</v>
-      </c>
-      <c r="AD20" s="5"/>
-      <c r="AE20" s="6">
-        <v>1.8928704695040199</v>
-      </c>
-      <c r="AF20" s="6">
-        <v>0.45806793222847902</v>
-      </c>
-      <c r="AG20" s="6"/>
-      <c r="AH20" s="5">
-        <v>1.9254081019906799</v>
-      </c>
-      <c r="AI20" s="5">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AJ20" s="5"/>
-      <c r="AK20" s="6">
-        <v>1.9310103588079299</v>
-      </c>
-      <c r="AL20" s="6">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AM20" s="6"/>
-      <c r="AO20" s="5">
-        <v>59.800266675023899</v>
-      </c>
-      <c r="AP20" s="5">
-        <v>5.6589098186134796</v>
-      </c>
-      <c r="AQ20" s="5"/>
-      <c r="AR20" s="6">
-        <v>4.0062601639211897</v>
-      </c>
-      <c r="AS20" s="6">
-        <v>0.73795381895044299</v>
-      </c>
-      <c r="AT20" s="6"/>
-      <c r="AU20" s="5">
-        <v>4.6177380245423496</v>
-      </c>
-      <c r="AV20" s="5">
-        <v>0.76894302136484705</v>
-      </c>
-      <c r="AW20" s="5"/>
-      <c r="AX20" s="6">
-        <v>4.16152269917868</v>
-      </c>
-      <c r="AY20" s="6">
-        <v>0.74186796986636905</v>
-      </c>
-      <c r="AZ20" s="4"/>
-    </row>
-    <row r="21" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="O21" s="5">
-        <v>157.29900707611901</v>
-      </c>
-      <c r="P21" s="5">
-        <v>14.4931915247916</v>
-      </c>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="6">
-        <v>8.1890386233641905</v>
-      </c>
-      <c r="S21" s="6">
-        <v>0.972966699771316</v>
-      </c>
-      <c r="T21" s="6"/>
-      <c r="U21" s="5">
-        <v>2.5979047772938402</v>
-      </c>
-      <c r="V21" s="5">
-        <v>0.49508952439015402</v>
-      </c>
-      <c r="W21" s="5"/>
-      <c r="X21" s="6">
-        <v>5.7322415986417496</v>
-      </c>
-      <c r="Y21" s="6">
-        <v>0.97220188931186902</v>
-      </c>
-      <c r="Z21" s="4"/>
-      <c r="AB21" s="53">
-        <v>13.308572250548099</v>
-      </c>
-      <c r="AC21" s="5">
-        <v>1.57146153421673</v>
-      </c>
-      <c r="AD21" s="5"/>
-      <c r="AE21" s="6">
-        <v>1.89579470823163</v>
-      </c>
-      <c r="AF21" s="6">
-        <v>0.45806793222847902</v>
-      </c>
-      <c r="AG21" s="6"/>
-      <c r="AH21" s="5">
-        <v>1.92809473746348</v>
-      </c>
-      <c r="AI21" s="5">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AJ21" s="5"/>
-      <c r="AK21" s="6">
-        <v>1.9041536308450699</v>
-      </c>
-      <c r="AL21" s="6">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AM21" s="6"/>
-      <c r="AO21" s="5">
-        <v>59.763577152087599</v>
-      </c>
-      <c r="AP21" s="5">
-        <v>5.6605565868401699</v>
-      </c>
-      <c r="AQ21" s="5"/>
-      <c r="AR21" s="6">
-        <v>4.0965064780371803</v>
-      </c>
-      <c r="AS21" s="6">
-        <v>0.74199230991249299</v>
-      </c>
-      <c r="AT21" s="6"/>
-      <c r="AU21" s="5">
-        <v>5.0523507457567902</v>
-      </c>
-      <c r="AV21" s="5">
-        <v>0.82059037677546498</v>
-      </c>
-      <c r="AW21" s="5"/>
-      <c r="AX21" s="6">
-        <v>4.5857896450893199</v>
-      </c>
-      <c r="AY21" s="6">
-        <v>0.77052852380524195</v>
-      </c>
-      <c r="AZ21" s="4"/>
-    </row>
-    <row r="22" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="O22" s="5">
-        <v>156.63177221391601</v>
-      </c>
-      <c r="P22" s="5">
-        <v>14.552850092942499</v>
-      </c>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="6">
-        <v>1.5954382843530299</v>
-      </c>
-      <c r="S22" s="6">
-        <v>0.34093122957817401</v>
-      </c>
-      <c r="T22" s="6"/>
-      <c r="U22" s="5">
-        <v>5.2511580596295104</v>
-      </c>
-      <c r="V22" s="5">
-        <v>0.95645330203096601</v>
-      </c>
-      <c r="W22" s="5"/>
-      <c r="X22" s="6">
-        <v>7.8646628653608701</v>
-      </c>
-      <c r="Y22" s="6">
-        <v>0.98780444655659705</v>
-      </c>
-      <c r="Z22" s="4"/>
-      <c r="AB22" s="53">
-        <v>13.2363942457426</v>
-      </c>
-      <c r="AC22" s="5">
-        <v>1.57146153421673</v>
-      </c>
-      <c r="AD22" s="5"/>
-      <c r="AE22" s="6">
-        <v>1.84677639533975</v>
-      </c>
-      <c r="AF22" s="6">
-        <v>0.40847846441090702</v>
-      </c>
-      <c r="AG22" s="6"/>
-      <c r="AH22" s="5">
-        <v>1.9129533293466101</v>
-      </c>
-      <c r="AI22" s="5">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AJ22" s="5"/>
-      <c r="AK22" s="6">
-        <v>1.8932005458435199</v>
-      </c>
-      <c r="AL22" s="6">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AM22" s="6"/>
-      <c r="AO22" s="5">
-        <v>59.788459460005697</v>
-      </c>
-      <c r="AP22" s="5">
-        <v>5.6563668900060096</v>
-      </c>
-      <c r="AQ22" s="5"/>
-      <c r="AR22" s="6">
-        <v>4.7948084662286998</v>
-      </c>
-      <c r="AS22" s="6">
-        <v>0.78044091788651704</v>
-      </c>
-      <c r="AT22" s="6"/>
-      <c r="AU22" s="5">
-        <v>4.67808128757747</v>
-      </c>
-      <c r="AV22" s="5">
-        <v>0.78459048978145696</v>
-      </c>
-      <c r="AW22" s="5"/>
-      <c r="AX22" s="6">
-        <v>4.8692804147897402</v>
-      </c>
-      <c r="AY22" s="6">
-        <v>0.79097844961616104</v>
-      </c>
-      <c r="AZ22" s="4"/>
-    </row>
-    <row r="23" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="O23" s="5">
-        <v>156.986009517112</v>
-      </c>
-      <c r="P23" s="5">
-        <v>14.467486922240001</v>
-      </c>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="6">
-        <v>1.88753858403897</v>
-      </c>
-      <c r="S23" s="6">
-        <v>0.42837619544093197</v>
-      </c>
-      <c r="T23" s="6"/>
-      <c r="U23" s="5">
-        <v>7.1603524175097304</v>
-      </c>
-      <c r="V23" s="5">
-        <v>1.00026650116511</v>
-      </c>
-      <c r="W23" s="5"/>
-      <c r="X23" s="6">
-        <v>3.1299735370558799</v>
-      </c>
-      <c r="Y23" s="6">
-        <v>0.73135202091426998</v>
-      </c>
-      <c r="Z23" s="4"/>
-      <c r="AB23" s="53">
-        <v>13.308674501574901</v>
-      </c>
-      <c r="AC23" s="5">
-        <v>1.57146153421673</v>
-      </c>
-      <c r="AD23" s="5"/>
-      <c r="AE23" s="6">
-        <v>1.84679124914915</v>
-      </c>
-      <c r="AF23" s="6">
-        <v>0.40847846441090702</v>
-      </c>
-      <c r="AG23" s="6"/>
-      <c r="AH23" s="5">
-        <v>1.90072564987806</v>
-      </c>
-      <c r="AI23" s="5">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AJ23" s="5"/>
-      <c r="AK23" s="6">
-        <v>1.9321830134050899</v>
-      </c>
-      <c r="AL23" s="6">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AM23" s="6"/>
-      <c r="AO23" s="5">
-        <v>59.704796494574303</v>
-      </c>
-      <c r="AP23" s="5">
-        <v>5.65854215154509</v>
-      </c>
-      <c r="AQ23" s="5"/>
-      <c r="AR23" s="6">
-        <v>4.2657953513727804</v>
-      </c>
-      <c r="AS23" s="6">
-        <v>0.73609280545728795</v>
-      </c>
-      <c r="AT23" s="6"/>
-      <c r="AU23" s="5">
-        <v>4.6146231262904296</v>
-      </c>
-      <c r="AV23" s="5">
-        <v>0.77049022674415901</v>
-      </c>
-      <c r="AW23" s="5"/>
-      <c r="AX23" s="6">
-        <v>3.16447739831071</v>
-      </c>
-      <c r="AY23" s="6">
-        <v>0.654757088945225</v>
-      </c>
-      <c r="AZ23" s="4"/>
-    </row>
-    <row r="24" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="O24" s="5">
-        <v>158.196014729155</v>
-      </c>
-      <c r="P24" s="5">
-        <v>14.575139783219001</v>
-      </c>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="6">
-        <v>8.2933809227974091</v>
-      </c>
-      <c r="S24" s="6">
-        <v>1.08744489439875</v>
-      </c>
-      <c r="T24" s="6"/>
-      <c r="U24" s="5">
-        <v>8.3113921906864903</v>
-      </c>
-      <c r="V24" s="5">
-        <v>1.00724186950316</v>
-      </c>
-      <c r="W24" s="5"/>
-      <c r="X24" s="6">
-        <v>8.9040477791919201</v>
-      </c>
-      <c r="Y24" s="6">
-        <v>1.0147213122487999</v>
-      </c>
-      <c r="Z24" s="4"/>
-      <c r="AB24" s="53">
-        <v>13.308572250548099</v>
-      </c>
-      <c r="AC24" s="5">
-        <v>1.57146153421673</v>
-      </c>
-      <c r="AD24" s="5"/>
-      <c r="AE24" s="6">
-        <v>1.8928399139471399</v>
-      </c>
-      <c r="AF24" s="6">
-        <v>0.45806793222847902</v>
-      </c>
-      <c r="AG24" s="6"/>
-      <c r="AH24" s="5">
-        <v>1.92726370795321</v>
-      </c>
-      <c r="AI24" s="5">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AJ24" s="5"/>
-      <c r="AK24" s="6">
-        <v>1.90072564987806</v>
-      </c>
-      <c r="AL24" s="6">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AM24" s="6"/>
-      <c r="AO24" s="5">
-        <v>59.763577152087599</v>
-      </c>
-      <c r="AP24" s="5">
-        <v>5.6605565868401699</v>
-      </c>
-      <c r="AQ24" s="5"/>
-      <c r="AR24" s="6">
-        <v>4.0062601639211897</v>
-      </c>
-      <c r="AS24" s="6">
-        <v>0.73795381895044299</v>
-      </c>
-      <c r="AT24" s="6"/>
-      <c r="AU24" s="5">
-        <v>3.20141786716691</v>
-      </c>
-      <c r="AV24" s="5">
-        <v>0.654749429514626</v>
-      </c>
-      <c r="AW24" s="5"/>
-      <c r="AX24" s="6">
-        <v>3.27705316310352</v>
-      </c>
-      <c r="AY24" s="6">
-        <v>0.65983546495578804</v>
-      </c>
-      <c r="AZ24" s="4"/>
-    </row>
-    <row r="25" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="O25" s="5">
-        <v>157.491792122156</v>
-      </c>
-      <c r="P25" s="5">
-        <v>14.514140074457901</v>
-      </c>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="6">
-        <v>7.9528826625526996</v>
-      </c>
-      <c r="S25" s="6">
-        <v>1.00403884516471</v>
-      </c>
-      <c r="T25" s="6"/>
-      <c r="U25" s="5">
-        <v>2.5901809467614498</v>
-      </c>
-      <c r="V25" s="5">
-        <v>0.71838880869329702</v>
-      </c>
-      <c r="W25" s="5"/>
-      <c r="X25" s="6">
-        <v>2.8818765035072902</v>
-      </c>
-      <c r="Y25" s="6">
-        <v>0.731352021572787</v>
-      </c>
-      <c r="Z25" s="4"/>
-      <c r="AB25" s="53">
-        <v>13.2496111916915</v>
-      </c>
-      <c r="AC25" s="5">
-        <v>1.57146153421673</v>
-      </c>
-      <c r="AD25" s="5"/>
-      <c r="AE25" s="6">
-        <v>1.88988196952168</v>
-      </c>
-      <c r="AF25" s="6">
-        <v>0.45806793222847902</v>
-      </c>
-      <c r="AG25" s="6"/>
-      <c r="AH25" s="5">
-        <v>1.9000822249987701</v>
-      </c>
-      <c r="AI25" s="5">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AJ25" s="5"/>
-      <c r="AK25" s="6">
-        <v>1.9261561832388601</v>
-      </c>
-      <c r="AL25" s="6">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AM25" s="6"/>
-      <c r="AO25" s="5">
-        <v>59.780185400258901</v>
-      </c>
-      <c r="AP25" s="5">
-        <v>5.6572783626149601</v>
-      </c>
-      <c r="AQ25" s="5"/>
-      <c r="AR25" s="6">
-        <v>3.99030456835369</v>
-      </c>
-      <c r="AS25" s="6">
-        <v>0.73808402950040897</v>
-      </c>
-      <c r="AT25" s="6"/>
-      <c r="AU25" s="5">
-        <v>4.4974089192370004</v>
-      </c>
-      <c r="AV25" s="5">
-        <v>0.76155164534629505</v>
-      </c>
-      <c r="AW25" s="5"/>
-      <c r="AX25" s="6">
-        <v>4.7203610704798997</v>
-      </c>
-      <c r="AY25" s="6">
-        <v>0.97485233337667998</v>
-      </c>
-      <c r="AZ25" s="4"/>
-    </row>
-    <row r="26" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="O26" s="5">
-        <v>156.87408337816299</v>
-      </c>
-      <c r="P26" s="5">
-        <v>14.5729484252851</v>
-      </c>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="6">
-        <v>2.2530507252529302</v>
-      </c>
-      <c r="S26" s="6">
-        <v>0.38723762689095498</v>
-      </c>
-      <c r="T26" s="6"/>
-      <c r="U26" s="5">
-        <v>4.3416457442441896</v>
-      </c>
-      <c r="V26" s="5">
-        <v>0.81790916195557295</v>
-      </c>
-      <c r="W26" s="5"/>
-      <c r="X26" s="6">
-        <v>6.8467498165278498</v>
-      </c>
-      <c r="Y26" s="6">
-        <v>0.86006578658153399</v>
-      </c>
-      <c r="Z26" s="4"/>
-      <c r="AB26" s="53">
-        <v>13.2958588107644</v>
-      </c>
-      <c r="AC26" s="5">
-        <v>1.57146153421673</v>
-      </c>
-      <c r="AD26" s="5"/>
-      <c r="AE26" s="6">
-        <v>1.88577925752618</v>
-      </c>
-      <c r="AF26" s="6">
-        <v>0.45806793222847902</v>
-      </c>
-      <c r="AG26" s="6"/>
-      <c r="AH26" s="5">
-        <v>1.9129598430242301</v>
-      </c>
-      <c r="AI26" s="5">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AJ26" s="5"/>
-      <c r="AK26" s="6">
-        <v>1.90072564987806</v>
-      </c>
-      <c r="AL26" s="6">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AM26" s="6"/>
-      <c r="AO26" s="5">
-        <v>59.763577152087599</v>
-      </c>
-      <c r="AP26" s="5">
-        <v>5.6605565868401699</v>
-      </c>
-      <c r="AQ26" s="5"/>
-      <c r="AR26" s="6">
-        <v>4.7934652069475101</v>
-      </c>
-      <c r="AS26" s="6">
-        <v>0.78044091788651704</v>
-      </c>
-      <c r="AT26" s="6"/>
-      <c r="AU26" s="5">
-        <v>4.62239210584959</v>
-      </c>
-      <c r="AV26" s="5">
-        <v>0.77049022674415901</v>
-      </c>
-      <c r="AW26" s="5"/>
-      <c r="AX26" s="6">
-        <v>4.1992812511646704</v>
-      </c>
-      <c r="AY26" s="6">
-        <v>0.74189860738961999</v>
-      </c>
-      <c r="AZ26" s="4"/>
-    </row>
-    <row r="27" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="O27" s="5">
-        <v>157.491792122156</v>
-      </c>
-      <c r="P27" s="5">
-        <v>14.514140074457901</v>
-      </c>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="6">
-        <v>8.0216212976691192</v>
-      </c>
-      <c r="S27" s="6">
-        <v>0.94819842453320702</v>
-      </c>
-      <c r="T27" s="6"/>
-      <c r="U27" s="5">
-        <v>7.8031301233212496</v>
-      </c>
-      <c r="V27" s="5">
-        <v>0.98052828629424604</v>
-      </c>
-      <c r="W27" s="5"/>
-      <c r="X27" s="6">
-        <v>7.65752977429218</v>
-      </c>
-      <c r="Y27" s="6">
-        <v>0.99652077413521101</v>
-      </c>
-      <c r="Z27" s="4"/>
-      <c r="AB27" s="53">
-        <v>13.2496111916915</v>
-      </c>
-      <c r="AC27" s="5">
-        <v>1.57146153421673</v>
-      </c>
-      <c r="AD27" s="5"/>
-      <c r="AE27" s="6">
-        <v>1.89142964942645</v>
-      </c>
-      <c r="AF27" s="6">
-        <v>0.45806793222847902</v>
-      </c>
-      <c r="AG27" s="6"/>
-      <c r="AH27" s="5">
-        <v>1.9268909669221299</v>
-      </c>
-      <c r="AI27" s="5">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AJ27" s="5"/>
-      <c r="AK27" s="6">
-        <v>1.9090180403210999</v>
-      </c>
-      <c r="AL27" s="6">
-        <v>0.473754446095489</v>
-      </c>
-      <c r="AM27" s="6"/>
-      <c r="AO27" s="5">
-        <v>59.705630088686199</v>
-      </c>
-      <c r="AP27" s="5">
-        <v>5.6586034268060601</v>
-      </c>
-      <c r="AQ27" s="5"/>
-      <c r="AR27" s="6">
-        <v>3.8324091847093902</v>
-      </c>
-      <c r="AS27" s="6">
-        <v>0.83666835893369396</v>
-      </c>
-      <c r="AT27" s="6"/>
-      <c r="AU27" s="5">
-        <v>4.3195119947240102</v>
-      </c>
-      <c r="AV27" s="5">
-        <v>0.78874489201662801</v>
-      </c>
-      <c r="AW27" s="5"/>
-      <c r="AX27" s="6">
-        <v>4.2361236162037104</v>
-      </c>
-      <c r="AY27" s="6">
-        <v>0.77829603577231399</v>
-      </c>
-      <c r="AZ27" s="4"/>
-    </row>
-    <row r="28" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-    </row>
-    <row r="29" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-    </row>
-    <row r="30" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-    </row>
-    <row r="31" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-    </row>
-    <row r="32" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-    </row>
-  </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="AO16:AQ16"/>
-    <mergeCell ref="AR16:AT16"/>
-    <mergeCell ref="AU16:AW16"/>
-    <mergeCell ref="AX16:AZ16"/>
-    <mergeCell ref="U16:W16"/>
-    <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="AB16:AD16"/>
-    <mergeCell ref="AE16:AG16"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AK16:AM16"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="AO2:AQ2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="B15:L15"/>
-    <mergeCell ref="O15:Y15"/>
-    <mergeCell ref="AB15:AL15"/>
-    <mergeCell ref="AO15:AY15"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AK2:AM2"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="O1:Y1"/>
-    <mergeCell ref="AB1:AL1"/>
-    <mergeCell ref="AO1:AY1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB2F127C-15E6-41A0-94B0-FA50F057125C}">
   <dimension ref="A1:Z35"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6848,35 +4041,35 @@
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="38" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:26" s="27" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="51"/>
+      <c r="W1" s="51"/>
+      <c r="X1" s="51"/>
+      <c r="Y1" s="51"/>
+      <c r="Z1" s="51"/>
     </row>
     <row r="2" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M2" s="13"/>
@@ -6898,7 +4091,7 @@
       <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="3" t="s">
         <v>33</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -6930,32 +4123,32 @@
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="52" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="12">
         <v>1</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="55">
         <v>66</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="55">
         <v>66</v>
       </c>
-      <c r="F4" s="40"/>
-      <c r="G4" s="31">
+      <c r="F4" s="56"/>
+      <c r="G4" s="55">
         <v>1</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="55">
         <v>1</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="55">
         <v>66</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="55">
         <v>66</v>
       </c>
       <c r="K4" s="6">
@@ -6978,18 +4171,18 @@
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="34"/>
+      <c r="A5" s="53"/>
       <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
       <c r="K5" s="6">
         <f>AVERAGE(DataExp1!E4:E13)</f>
         <v>11.070752653739017</v>
@@ -7010,18 +4203,18 @@
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="34"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="7">
         <v>5</v>
       </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
       <c r="K6" s="6">
         <f>AVERAGE(DataExp1!H4:H13)</f>
         <v>4.7480516396353174</v>
@@ -7042,18 +4235,18 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="34"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="7">
         <v>10</v>
       </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
       <c r="K7" s="6">
         <f>AVERAGE(DataExp1!K4:K13)</f>
         <v>0.84932664663156276</v>
@@ -7074,20 +4267,20 @@
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="54" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="4">
         <v>1</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
       <c r="K8" s="5">
         <f>AVERAGE(DataExp1!O4:O13)</f>
         <v>49.821904185231844</v>
@@ -7108,18 +4301,18 @@
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="26"/>
+      <c r="A9" s="54"/>
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
       <c r="K9" s="5">
         <f>AVERAGE(DataExp1!R4:R13)</f>
         <v>2.2585080679270888</v>
@@ -7140,18 +4333,18 @@
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="26"/>
+      <c r="A10" s="54"/>
       <c r="B10" s="4">
         <v>5</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
       <c r="K10" s="5">
         <f>AVERAGE(DataExp1!U4:U13)</f>
         <v>2.4443213833989064</v>
@@ -7172,18 +4365,18 @@
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
+      <c r="A11" s="54"/>
       <c r="B11" s="4">
         <v>10</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
       <c r="K11" s="5">
         <f>AVERAGE(DataExp1!X4:X13)</f>
         <v>2.0470536852897636</v>
@@ -7204,20 +4397,20 @@
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="53" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="7">
         <v>1</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54"/>
       <c r="K12" s="23">
         <f>AVERAGE(DataExp1!AB4:AB13)</f>
         <v>2.0194039548285878</v>
@@ -7238,18 +4431,18 @@
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
+      <c r="A13" s="53"/>
       <c r="B13" s="7">
         <v>3</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
       <c r="K13" s="23">
         <f>AVERAGE(DataExp1!AE4:AE13)</f>
         <v>3.0323916470832399</v>
@@ -7270,18 +4463,18 @@
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="34"/>
+      <c r="A14" s="53"/>
       <c r="B14" s="7">
         <v>5</v>
       </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
       <c r="K14" s="23">
         <f>AVERAGE(DataExp1!AH4:AH13)</f>
         <v>3.0970657292831891</v>
@@ -7302,18 +4495,18 @@
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="34"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="7">
         <v>10</v>
       </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="54"/>
       <c r="K15" s="23">
         <f>AVERAGE(DataExp1!AK4:AK13)</f>
         <v>3.0304601968108664</v>
@@ -7334,20 +4527,20 @@
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="54" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="4">
         <v>1</v>
       </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="54"/>
       <c r="K16" s="5">
         <f>AVERAGE(DataExp1!AO4:AO13)</f>
         <v>34.552311810658352</v>
@@ -7368,18 +4561,18 @@
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="26"/>
+      <c r="A17" s="54"/>
       <c r="B17" s="4">
         <v>3</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="54"/>
       <c r="K17" s="5">
         <f>AVERAGE(DataExp1!AR4:AR14)</f>
         <v>1.8560190453181431</v>
@@ -7400,18 +4593,18 @@
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="26"/>
+      <c r="A18" s="54"/>
       <c r="B18" s="4">
         <v>5</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="54"/>
       <c r="K18" s="5">
         <f>AVERAGE(DataExp1!AU4:AU13)</f>
         <v>1.9127433590347436</v>
@@ -7432,18 +4625,18 @@
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="26"/>
+      <c r="A19" s="54"/>
       <c r="B19" s="4">
         <v>10</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="54"/>
       <c r="K19" s="5">
         <f>AVERAGE(DataExp1!AX4:AX13)</f>
         <v>1.9259347567178799</v>
@@ -7464,32 +4657,32 @@
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="60" t="s">
         <v>12</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="54">
         <v>128</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="54">
         <v>128</v>
       </c>
-      <c r="F20" s="40"/>
-      <c r="G20" s="26">
+      <c r="F20" s="56"/>
+      <c r="G20" s="54">
         <v>1</v>
       </c>
-      <c r="H20" s="26">
+      <c r="H20" s="54">
         <v>1</v>
       </c>
-      <c r="I20" s="26">
+      <c r="I20" s="54">
         <v>128</v>
       </c>
-      <c r="J20" s="26">
+      <c r="J20" s="54">
         <v>128</v>
       </c>
       <c r="K20" s="4">
@@ -7511,18 +4704,18 @@
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
+      <c r="A21" s="60"/>
       <c r="B21" s="4">
         <v>3</v>
       </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
       <c r="K21" s="4">
         <f>AVERAGE(DataExp1!E18:E27)</f>
         <v>38.626208042487967</v>
@@ -7542,18 +4735,18 @@
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="30"/>
+      <c r="A22" s="60"/>
       <c r="B22" s="4">
         <v>5</v>
       </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="26"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
       <c r="K22" s="4">
         <f>AVERAGE(DataExp1!H18:H27)</f>
         <v>19.080341123339618</v>
@@ -7573,18 +4766,18 @@
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
+      <c r="A23" s="60"/>
       <c r="B23" s="4">
         <v>10</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="26"/>
-      <c r="J23" s="26"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
       <c r="K23" s="4">
         <f>AVERAGE(DataExp1!K18:K27)</f>
         <v>4.4322830974230261</v>
@@ -7604,20 +4797,20 @@
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="59" t="s">
         <v>13</v>
       </c>
       <c r="B24" s="10">
         <v>1</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
       <c r="K24" s="10">
         <f>AVERAGE(DataExp1!O18:O27)</f>
         <v>157.51141235842792</v>
@@ -7637,18 +4830,18 @@
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="29"/>
+      <c r="A25" s="59"/>
       <c r="B25" s="10">
         <v>3</v>
       </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="54"/>
       <c r="K25" s="10">
         <f>AVERAGE(DataExp1!R18:R27)</f>
         <v>5.370568162007002</v>
@@ -7668,18 +4861,18 @@
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="29"/>
+      <c r="A26" s="59"/>
       <c r="B26" s="10">
         <v>5</v>
       </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
       <c r="K26" s="10">
         <f>AVERAGE(DataExp1!U18:U27)</f>
         <v>6.130019567236074</v>
@@ -7699,18 +4892,18 @@
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="29"/>
+      <c r="A27" s="59"/>
       <c r="B27" s="10">
         <v>10</v>
       </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="54"/>
       <c r="K27" s="10">
         <f>AVERAGE(DataExp1!X18:X27)</f>
         <v>6.2926813963615427</v>
@@ -7730,146 +4923,146 @@
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="60" t="s">
         <v>14</v>
       </c>
       <c r="B28" s="4">
         <v>1</v>
       </c>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="35">
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="54"/>
+      <c r="K28" s="25">
         <f>AVERAGE(DataExp1!AB18:AB27)</f>
         <v>13.2679396369752</v>
       </c>
-      <c r="L28" s="35">
+      <c r="L28" s="25">
         <f>AVERAGE(DataExp1!AC18:AC27)</f>
         <v>1.5714615342167302</v>
       </c>
-      <c r="M28" s="35">
+      <c r="M28" s="25">
         <v>8.3970028801535798E-2</v>
       </c>
-      <c r="N28" s="36">
+      <c r="N28" s="26">
         <v>3.6284487521842497E-5</v>
       </c>
-      <c r="O28" s="35">
+      <c r="O28" s="25">
         <v>0.30750107765197698</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="30"/>
+      <c r="A29" s="60"/>
       <c r="B29" s="4">
         <v>3</v>
       </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="35">
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="25">
         <f>AVERAGE(DataExp1!AE18:AE27)</f>
         <v>1.8847515193214188</v>
       </c>
-      <c r="L29" s="35">
+      <c r="L29" s="25">
         <f>AVERAGE(DataExp1!AF18:AF27)</f>
         <v>0.44815003866496461</v>
       </c>
-      <c r="M29" s="35">
+      <c r="M29" s="25">
         <v>9.5270057603071695E-2</v>
       </c>
-      <c r="N29" s="36">
+      <c r="N29" s="26">
         <v>4.9660843797880298E-5</v>
       </c>
-      <c r="O29" s="35">
+      <c r="O29" s="25">
         <v>0.36651349067687899</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="30"/>
+      <c r="A30" s="60"/>
       <c r="B30" s="4">
         <v>5</v>
       </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="35">
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="54"/>
+      <c r="K30" s="25">
         <f>AVERAGE(DataExp1!AH18:AH27)</f>
         <v>1.9167287224860321</v>
       </c>
-      <c r="L30" s="35">
+      <c r="L30" s="25">
         <f>AVERAGE(DataExp1!AI18:AI27)</f>
         <v>0.473754446095489</v>
       </c>
-      <c r="M30" s="35">
+      <c r="M30" s="25">
         <v>9.6327586404607604E-2</v>
       </c>
-      <c r="N30" s="36">
+      <c r="N30" s="26">
         <v>4.9897249721340198E-5</v>
       </c>
-      <c r="O30" s="35">
+      <c r="O30" s="25">
         <v>0.397212743759155</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="30"/>
+      <c r="A31" s="60"/>
       <c r="B31" s="11">
         <v>10</v>
       </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="35">
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="25">
         <f>AVERAGE(DataExp1!AK18:AK27)</f>
         <v>1.9152230126798291</v>
       </c>
-      <c r="L31" s="35">
+      <c r="L31" s="25">
         <f>AVERAGE(DataExp1!AL18:AL27)</f>
         <v>0.473754446095489</v>
       </c>
-      <c r="M31" s="35">
+      <c r="M31" s="25">
         <v>9.6205115206143499E-2</v>
       </c>
-      <c r="N31" s="36">
+      <c r="N31" s="26">
         <v>4.9853940035316602E-5</v>
       </c>
-      <c r="O31" s="35">
+      <c r="O31" s="25">
         <v>0.36162972450256298</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="59" t="s">
         <v>15</v>
       </c>
       <c r="B32" s="10">
         <v>1</v>
       </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
       <c r="K32" s="15">
         <f>AVERAGE(DataExp1!AO18:AO27)</f>
         <v>59.79535904859479</v>
@@ -7889,18 +5082,18 @@
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="29"/>
+      <c r="A33" s="59"/>
       <c r="B33" s="10">
         <v>3</v>
       </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="54"/>
       <c r="K33" s="15">
         <f>AVERAGE(DataExp1!AR18:AR27)</f>
         <v>4.1994209587286191</v>
@@ -7920,18 +5113,18 @@
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="29"/>
+      <c r="A34" s="59"/>
       <c r="B34" s="10">
         <v>5</v>
       </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="54"/>
       <c r="K34" s="15">
         <f>AVERAGE(DataExp1!AU18:AU27)</f>
         <v>4.4246201292478027</v>
@@ -7951,18 +5144,18 @@
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="29"/>
+      <c r="A35" s="59"/>
       <c r="B35" s="10">
         <v>10</v>
       </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
       <c r="K35" s="15">
         <f>AVERAGE(DataExp1!AX18:AX27)</f>
         <v>4.1938757256751718</v>
@@ -7983,17 +5176,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="C4:C19"/>
-    <mergeCell ref="D4:D19"/>
-    <mergeCell ref="E4:E19"/>
-    <mergeCell ref="G4:G19"/>
-    <mergeCell ref="H4:H19"/>
-    <mergeCell ref="F4:F19"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A32:A35"/>
@@ -8008,9 +5190,1696 @@
     <mergeCell ref="I20:I35"/>
     <mergeCell ref="J20:J35"/>
     <mergeCell ref="F20:F35"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="C4:C19"/>
+    <mergeCell ref="D4:D19"/>
+    <mergeCell ref="E4:E19"/>
+    <mergeCell ref="G4:G19"/>
+    <mergeCell ref="H4:H19"/>
+    <mergeCell ref="F4:F19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E02A095-16D7-4FBB-B206-8C2A6F2CFB60}">
+  <dimension ref="B1:AZ34"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B1" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="22"/>
+      <c r="O1" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="AB1" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC1" s="49"/>
+      <c r="AD1" s="49"/>
+      <c r="AE1" s="49"/>
+      <c r="AF1" s="49"/>
+      <c r="AG1" s="49"/>
+      <c r="AH1" s="49"/>
+      <c r="AI1" s="49"/>
+      <c r="AJ1" s="49"/>
+      <c r="AK1" s="41"/>
+      <c r="AL1" s="41"/>
+      <c r="AM1" s="22"/>
+      <c r="AO1" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP1" s="49"/>
+      <c r="AQ1" s="49"/>
+      <c r="AR1" s="49"/>
+      <c r="AS1" s="49"/>
+      <c r="AT1" s="49"/>
+      <c r="AU1" s="49"/>
+      <c r="AV1" s="49"/>
+      <c r="AW1" s="49"/>
+      <c r="AX1" s="41"/>
+      <c r="AY1" s="41"/>
+    </row>
+    <row r="2" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B2" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="43"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="46"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="O2" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" s="43"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="V2" s="46"/>
+      <c r="W2" s="47"/>
+      <c r="X2" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC2" s="43"/>
+      <c r="AD2" s="44"/>
+      <c r="AE2" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF2" s="43"/>
+      <c r="AG2" s="44"/>
+      <c r="AH2" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI2" s="46"/>
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL2" s="48"/>
+      <c r="AM2" s="48"/>
+      <c r="AO2" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="AP2" s="43"/>
+      <c r="AQ2" s="44"/>
+      <c r="AR2" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS2" s="43"/>
+      <c r="AT2" s="44"/>
+      <c r="AU2" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="AV2" s="46"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY2" s="48"/>
+      <c r="AZ2" s="48"/>
+    </row>
+    <row r="3" spans="2:52" ht="45" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="T3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="W3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AL3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO3" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AU3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AV3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="AW3" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AX3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ3" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="4"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="6"/>
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="6"/>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="5"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="6"/>
+      <c r="AL4" s="6"/>
+      <c r="AM4" s="6"/>
+      <c r="AO4" s="5"/>
+      <c r="AP4" s="5"/>
+      <c r="AQ4" s="5"/>
+      <c r="AR4" s="6"/>
+      <c r="AS4" s="6"/>
+      <c r="AT4" s="6"/>
+      <c r="AU4" s="5"/>
+      <c r="AV4" s="5"/>
+      <c r="AW4" s="5"/>
+      <c r="AX4" s="6"/>
+      <c r="AY4" s="6"/>
+      <c r="AZ4" s="4"/>
+    </row>
+    <row r="5" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="6"/>
+      <c r="Z5" s="4"/>
+      <c r="AB5" s="5"/>
+      <c r="AC5" s="5"/>
+      <c r="AD5" s="5"/>
+      <c r="AE5" s="6"/>
+      <c r="AF5" s="6"/>
+      <c r="AG5" s="6"/>
+      <c r="AH5" s="5"/>
+      <c r="AI5" s="5"/>
+      <c r="AJ5" s="5"/>
+      <c r="AK5" s="6"/>
+      <c r="AL5" s="6"/>
+      <c r="AM5" s="6"/>
+      <c r="AO5" s="5"/>
+      <c r="AP5" s="5"/>
+      <c r="AQ5" s="5"/>
+      <c r="AR5" s="6"/>
+      <c r="AS5" s="6"/>
+      <c r="AT5" s="6"/>
+      <c r="AU5" s="5"/>
+      <c r="AV5" s="5"/>
+      <c r="AW5" s="5"/>
+      <c r="AX5" s="6"/>
+      <c r="AY5" s="6"/>
+      <c r="AZ5" s="4"/>
+    </row>
+    <row r="6" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="4"/>
+      <c r="AB6" s="5"/>
+      <c r="AC6" s="5"/>
+      <c r="AD6" s="5"/>
+      <c r="AE6" s="6"/>
+      <c r="AF6" s="6"/>
+      <c r="AG6" s="6"/>
+      <c r="AH6" s="5"/>
+      <c r="AI6" s="5"/>
+      <c r="AJ6" s="5"/>
+      <c r="AK6" s="6"/>
+      <c r="AL6" s="6"/>
+      <c r="AM6" s="6"/>
+      <c r="AO6" s="5"/>
+      <c r="AP6" s="5"/>
+      <c r="AQ6" s="5"/>
+      <c r="AR6" s="6"/>
+      <c r="AS6" s="6"/>
+      <c r="AT6" s="6"/>
+      <c r="AU6" s="5"/>
+      <c r="AV6" s="5"/>
+      <c r="AW6" s="5"/>
+      <c r="AX6" s="6"/>
+      <c r="AY6" s="6"/>
+      <c r="AZ6" s="4"/>
+    </row>
+    <row r="7" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="4"/>
+      <c r="AB7" s="5"/>
+      <c r="AC7" s="5"/>
+      <c r="AD7" s="5"/>
+      <c r="AE7" s="6"/>
+      <c r="AF7" s="6"/>
+      <c r="AG7" s="6"/>
+      <c r="AH7" s="5"/>
+      <c r="AI7" s="5"/>
+      <c r="AJ7" s="5"/>
+      <c r="AK7" s="6"/>
+      <c r="AL7" s="6"/>
+      <c r="AM7" s="6"/>
+      <c r="AO7" s="5"/>
+      <c r="AP7" s="5"/>
+      <c r="AQ7" s="5"/>
+      <c r="AR7" s="6"/>
+      <c r="AS7" s="6"/>
+      <c r="AT7" s="6"/>
+      <c r="AU7" s="5"/>
+      <c r="AV7" s="5"/>
+      <c r="AW7" s="5"/>
+      <c r="AX7" s="6"/>
+      <c r="AY7" s="6"/>
+      <c r="AZ7" s="4"/>
+    </row>
+    <row r="8" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="4"/>
+      <c r="AB8" s="5"/>
+      <c r="AC8" s="5"/>
+      <c r="AD8" s="5"/>
+      <c r="AE8" s="6"/>
+      <c r="AF8" s="6"/>
+      <c r="AG8" s="6"/>
+      <c r="AH8" s="5"/>
+      <c r="AI8" s="5"/>
+      <c r="AJ8" s="5"/>
+      <c r="AK8" s="6"/>
+      <c r="AL8" s="6"/>
+      <c r="AM8" s="6"/>
+      <c r="AO8" s="5"/>
+      <c r="AP8" s="5"/>
+      <c r="AQ8" s="5"/>
+      <c r="AR8" s="6"/>
+      <c r="AS8" s="6"/>
+      <c r="AT8" s="6"/>
+      <c r="AU8" s="5"/>
+      <c r="AV8" s="5"/>
+      <c r="AW8" s="5"/>
+      <c r="AX8" s="6"/>
+      <c r="AY8" s="6"/>
+      <c r="AZ8" s="4"/>
+    </row>
+    <row r="9" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="4"/>
+      <c r="AB9" s="5"/>
+      <c r="AC9" s="5"/>
+      <c r="AD9" s="5"/>
+      <c r="AE9" s="6"/>
+      <c r="AF9" s="6"/>
+      <c r="AG9" s="6"/>
+      <c r="AH9" s="5"/>
+      <c r="AI9" s="5"/>
+      <c r="AJ9" s="5"/>
+      <c r="AK9" s="6"/>
+      <c r="AL9" s="6"/>
+      <c r="AM9" s="6"/>
+      <c r="AO9" s="5"/>
+      <c r="AP9" s="5"/>
+      <c r="AQ9" s="5"/>
+      <c r="AR9" s="6"/>
+      <c r="AS9" s="6"/>
+      <c r="AT9" s="6"/>
+      <c r="AU9" s="5"/>
+      <c r="AV9" s="5"/>
+      <c r="AW9" s="5"/>
+      <c r="AX9" s="6"/>
+      <c r="AY9" s="6"/>
+      <c r="AZ9" s="4"/>
+    </row>
+    <row r="10" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="4"/>
+      <c r="AB10" s="5"/>
+      <c r="AC10" s="5"/>
+      <c r="AD10" s="5"/>
+      <c r="AE10" s="6"/>
+      <c r="AF10" s="6"/>
+      <c r="AG10" s="6"/>
+      <c r="AH10" s="5"/>
+      <c r="AI10" s="5"/>
+      <c r="AJ10" s="5"/>
+      <c r="AK10" s="6"/>
+      <c r="AL10" s="6"/>
+      <c r="AM10" s="6"/>
+      <c r="AO10" s="5"/>
+      <c r="AP10" s="5"/>
+      <c r="AQ10" s="5"/>
+      <c r="AR10" s="6"/>
+      <c r="AS10" s="6"/>
+      <c r="AT10" s="6"/>
+      <c r="AU10" s="5"/>
+      <c r="AV10" s="5"/>
+      <c r="AW10" s="5"/>
+      <c r="AX10" s="6"/>
+      <c r="AY10" s="6"/>
+      <c r="AZ10" s="4"/>
+    </row>
+    <row r="11" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="4"/>
+      <c r="AB11" s="5"/>
+      <c r="AC11" s="5"/>
+      <c r="AD11" s="5"/>
+      <c r="AE11" s="6"/>
+      <c r="AF11" s="6"/>
+      <c r="AG11" s="6"/>
+      <c r="AH11" s="5"/>
+      <c r="AI11" s="5"/>
+      <c r="AJ11" s="5"/>
+      <c r="AK11" s="6"/>
+      <c r="AL11" s="6"/>
+      <c r="AM11" s="6"/>
+      <c r="AO11" s="5"/>
+      <c r="AP11" s="5"/>
+      <c r="AQ11" s="5"/>
+      <c r="AR11" s="6"/>
+      <c r="AS11" s="6"/>
+      <c r="AT11" s="6"/>
+      <c r="AU11" s="5"/>
+      <c r="AV11" s="5"/>
+      <c r="AW11" s="5"/>
+      <c r="AX11" s="6"/>
+      <c r="AY11" s="6"/>
+      <c r="AZ11" s="4"/>
+    </row>
+    <row r="12" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="4"/>
+      <c r="AB12" s="5"/>
+      <c r="AC12" s="5"/>
+      <c r="AD12" s="5"/>
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="6"/>
+      <c r="AG12" s="6"/>
+      <c r="AH12" s="5"/>
+      <c r="AI12" s="5"/>
+      <c r="AJ12" s="5"/>
+      <c r="AK12" s="6"/>
+      <c r="AL12" s="6"/>
+      <c r="AM12" s="6"/>
+      <c r="AO12" s="5"/>
+      <c r="AP12" s="5"/>
+      <c r="AQ12" s="5"/>
+      <c r="AR12" s="6"/>
+      <c r="AS12" s="6"/>
+      <c r="AT12" s="6"/>
+      <c r="AU12" s="5"/>
+      <c r="AV12" s="5"/>
+      <c r="AW12" s="5"/>
+      <c r="AX12" s="6"/>
+      <c r="AY12" s="6"/>
+      <c r="AZ12" s="4"/>
+    </row>
+    <row r="13" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="4"/>
+      <c r="AB13" s="5"/>
+      <c r="AC13" s="5"/>
+      <c r="AD13" s="5"/>
+      <c r="AE13" s="6"/>
+      <c r="AF13" s="6"/>
+      <c r="AG13" s="6"/>
+      <c r="AH13" s="5"/>
+      <c r="AI13" s="5"/>
+      <c r="AJ13" s="5"/>
+      <c r="AK13" s="6"/>
+      <c r="AL13" s="6"/>
+      <c r="AM13" s="6"/>
+      <c r="AO13" s="5"/>
+      <c r="AP13" s="5"/>
+      <c r="AQ13" s="5"/>
+      <c r="AR13" s="6"/>
+      <c r="AS13" s="6"/>
+      <c r="AT13" s="6"/>
+      <c r="AU13" s="5"/>
+      <c r="AV13" s="5"/>
+      <c r="AW13" s="5"/>
+      <c r="AX13" s="6"/>
+      <c r="AY13" s="6"/>
+      <c r="AZ13" s="4"/>
+    </row>
+    <row r="14" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B15" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="22"/>
+      <c r="O15" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="49"/>
+      <c r="U15" s="49"/>
+      <c r="V15" s="49"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="49"/>
+      <c r="Y15" s="49"/>
+      <c r="AB15" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC15" s="49"/>
+      <c r="AD15" s="49"/>
+      <c r="AE15" s="49"/>
+      <c r="AF15" s="49"/>
+      <c r="AG15" s="49"/>
+      <c r="AH15" s="49"/>
+      <c r="AI15" s="49"/>
+      <c r="AJ15" s="49"/>
+      <c r="AK15" s="49"/>
+      <c r="AL15" s="49"/>
+      <c r="AM15" s="22"/>
+      <c r="AO15" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP15" s="49"/>
+      <c r="AQ15" s="49"/>
+      <c r="AR15" s="49"/>
+      <c r="AS15" s="49"/>
+      <c r="AT15" s="49"/>
+      <c r="AU15" s="49"/>
+      <c r="AV15" s="49"/>
+      <c r="AW15" s="49"/>
+      <c r="AX15" s="49"/>
+      <c r="AY15" s="49"/>
+    </row>
+    <row r="16" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B16" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="43"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="43"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="46"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" s="48"/>
+      <c r="M16" s="48"/>
+      <c r="O16" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="44"/>
+      <c r="R16" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="S16" s="43"/>
+      <c r="T16" s="44"/>
+      <c r="U16" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="V16" s="46"/>
+      <c r="W16" s="47"/>
+      <c r="X16" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y16" s="48"/>
+      <c r="Z16" s="48"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC16" s="43"/>
+      <c r="AD16" s="44"/>
+      <c r="AE16" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF16" s="43"/>
+      <c r="AG16" s="44"/>
+      <c r="AH16" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI16" s="46"/>
+      <c r="AJ16" s="47"/>
+      <c r="AK16" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL16" s="48"/>
+      <c r="AM16" s="48"/>
+      <c r="AO16" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="AP16" s="43"/>
+      <c r="AQ16" s="44"/>
+      <c r="AR16" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS16" s="43"/>
+      <c r="AT16" s="44"/>
+      <c r="AU16" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="AV16" s="46"/>
+      <c r="AW16" s="47"/>
+      <c r="AX16" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY16" s="48"/>
+      <c r="AZ16" s="48"/>
+    </row>
+    <row r="17" spans="2:52" ht="45" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="M17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="T17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="U17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="V17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="W17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="X17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA17" s="31"/>
+      <c r="AB17" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AL17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO17" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="AP17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AR17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AS17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AU17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AV17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="AW17" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AX17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="AY17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ17" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="4"/>
+      <c r="AB18" s="5"/>
+      <c r="AC18" s="5"/>
+      <c r="AD18" s="5"/>
+      <c r="AE18" s="6"/>
+      <c r="AF18" s="6"/>
+      <c r="AG18" s="6"/>
+      <c r="AH18" s="5"/>
+      <c r="AI18" s="5"/>
+      <c r="AJ18" s="5"/>
+      <c r="AK18" s="6"/>
+      <c r="AL18" s="6"/>
+      <c r="AM18" s="6"/>
+      <c r="AO18" s="5"/>
+      <c r="AP18" s="5"/>
+      <c r="AQ18" s="5"/>
+      <c r="AR18" s="6"/>
+      <c r="AS18" s="6"/>
+      <c r="AT18" s="6"/>
+      <c r="AU18" s="5"/>
+      <c r="AV18" s="5"/>
+      <c r="AW18" s="5"/>
+      <c r="AX18" s="6"/>
+      <c r="AY18" s="6"/>
+      <c r="AZ18" s="4"/>
+    </row>
+    <row r="19" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="6"/>
+      <c r="T19" s="6"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="6"/>
+      <c r="Y19" s="6"/>
+      <c r="Z19" s="4"/>
+      <c r="AB19" s="5"/>
+      <c r="AC19" s="5"/>
+      <c r="AD19" s="5"/>
+      <c r="AE19" s="6"/>
+      <c r="AF19" s="6"/>
+      <c r="AG19" s="6"/>
+      <c r="AH19" s="5"/>
+      <c r="AI19" s="5"/>
+      <c r="AJ19" s="5"/>
+      <c r="AK19" s="6"/>
+      <c r="AL19" s="6"/>
+      <c r="AM19" s="6"/>
+      <c r="AO19" s="5"/>
+      <c r="AP19" s="5"/>
+      <c r="AQ19" s="5"/>
+      <c r="AR19" s="6"/>
+      <c r="AS19" s="6"/>
+      <c r="AT19" s="6"/>
+      <c r="AU19" s="5"/>
+      <c r="AV19" s="5"/>
+      <c r="AW19" s="5"/>
+      <c r="AX19" s="6"/>
+      <c r="AY19" s="6"/>
+      <c r="AZ19" s="4"/>
+    </row>
+    <row r="20" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="6"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="6"/>
+      <c r="Y20" s="6"/>
+      <c r="Z20" s="4"/>
+      <c r="AB20" s="5"/>
+      <c r="AC20" s="5"/>
+      <c r="AD20" s="5"/>
+      <c r="AE20" s="6"/>
+      <c r="AF20" s="6"/>
+      <c r="AG20" s="6"/>
+      <c r="AH20" s="5"/>
+      <c r="AI20" s="5"/>
+      <c r="AJ20" s="5"/>
+      <c r="AK20" s="6"/>
+      <c r="AL20" s="6"/>
+      <c r="AM20" s="6"/>
+      <c r="AO20" s="5"/>
+      <c r="AP20" s="5"/>
+      <c r="AQ20" s="5"/>
+      <c r="AR20" s="6"/>
+      <c r="AS20" s="6"/>
+      <c r="AT20" s="6"/>
+      <c r="AU20" s="5"/>
+      <c r="AV20" s="5"/>
+      <c r="AW20" s="5"/>
+      <c r="AX20" s="6"/>
+      <c r="AY20" s="6"/>
+      <c r="AZ20" s="4"/>
+    </row>
+    <row r="21" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="6"/>
+      <c r="T21" s="6"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="6"/>
+      <c r="Y21" s="6"/>
+      <c r="Z21" s="4"/>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="5"/>
+      <c r="AD21" s="5"/>
+      <c r="AE21" s="6"/>
+      <c r="AF21" s="6"/>
+      <c r="AG21" s="6"/>
+      <c r="AH21" s="5"/>
+      <c r="AI21" s="5"/>
+      <c r="AJ21" s="5"/>
+      <c r="AK21" s="6"/>
+      <c r="AL21" s="6"/>
+      <c r="AM21" s="6"/>
+      <c r="AO21" s="5"/>
+      <c r="AP21" s="5"/>
+      <c r="AQ21" s="5"/>
+      <c r="AR21" s="6"/>
+      <c r="AS21" s="6"/>
+      <c r="AT21" s="6"/>
+      <c r="AU21" s="5"/>
+      <c r="AV21" s="5"/>
+      <c r="AW21" s="5"/>
+      <c r="AX21" s="6"/>
+      <c r="AY21" s="6"/>
+      <c r="AZ21" s="4"/>
+    </row>
+    <row r="22" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="6"/>
+      <c r="Y22" s="6"/>
+      <c r="Z22" s="4"/>
+      <c r="AB22" s="5"/>
+      <c r="AC22" s="5"/>
+      <c r="AD22" s="5"/>
+      <c r="AE22" s="6"/>
+      <c r="AF22" s="6"/>
+      <c r="AG22" s="6"/>
+      <c r="AH22" s="5"/>
+      <c r="AI22" s="5"/>
+      <c r="AJ22" s="5"/>
+      <c r="AK22" s="6"/>
+      <c r="AL22" s="6"/>
+      <c r="AM22" s="6"/>
+      <c r="AO22" s="5"/>
+      <c r="AP22" s="5"/>
+      <c r="AQ22" s="5"/>
+      <c r="AR22" s="6"/>
+      <c r="AS22" s="6"/>
+      <c r="AT22" s="6"/>
+      <c r="AU22" s="5"/>
+      <c r="AV22" s="5"/>
+      <c r="AW22" s="5"/>
+      <c r="AX22" s="6"/>
+      <c r="AY22" s="6"/>
+      <c r="AZ22" s="4"/>
+    </row>
+    <row r="23" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+      <c r="W23" s="5"/>
+      <c r="X23" s="6"/>
+      <c r="Y23" s="6"/>
+      <c r="Z23" s="4"/>
+      <c r="AB23" s="5"/>
+      <c r="AC23" s="5"/>
+      <c r="AD23" s="5"/>
+      <c r="AE23" s="6"/>
+      <c r="AF23" s="6"/>
+      <c r="AG23" s="6"/>
+      <c r="AH23" s="5"/>
+      <c r="AI23" s="5"/>
+      <c r="AJ23" s="5"/>
+      <c r="AK23" s="6"/>
+      <c r="AL23" s="6"/>
+      <c r="AM23" s="6"/>
+      <c r="AO23" s="5"/>
+      <c r="AP23" s="5"/>
+      <c r="AQ23" s="5"/>
+      <c r="AR23" s="6"/>
+      <c r="AS23" s="6"/>
+      <c r="AT23" s="6"/>
+      <c r="AU23" s="5"/>
+      <c r="AV23" s="5"/>
+      <c r="AW23" s="5"/>
+      <c r="AX23" s="6"/>
+      <c r="AY23" s="6"/>
+      <c r="AZ23" s="4"/>
+    </row>
+    <row r="24" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="6"/>
+      <c r="T24" s="6"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
+      <c r="X24" s="6"/>
+      <c r="Y24" s="6"/>
+      <c r="Z24" s="4"/>
+      <c r="AB24" s="5"/>
+      <c r="AC24" s="5"/>
+      <c r="AD24" s="5"/>
+      <c r="AE24" s="6"/>
+      <c r="AF24" s="6"/>
+      <c r="AG24" s="6"/>
+      <c r="AH24" s="5"/>
+      <c r="AI24" s="5"/>
+      <c r="AJ24" s="5"/>
+      <c r="AK24" s="6"/>
+      <c r="AL24" s="6"/>
+      <c r="AM24" s="6"/>
+      <c r="AO24" s="5"/>
+      <c r="AP24" s="5"/>
+      <c r="AQ24" s="5"/>
+      <c r="AR24" s="6"/>
+      <c r="AS24" s="6"/>
+      <c r="AT24" s="6"/>
+      <c r="AU24" s="5"/>
+      <c r="AV24" s="5"/>
+      <c r="AW24" s="5"/>
+      <c r="AX24" s="6"/>
+      <c r="AY24" s="6"/>
+      <c r="AZ24" s="4"/>
+    </row>
+    <row r="25" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6"/>
+      <c r="U25" s="5"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="6"/>
+      <c r="Y25" s="6"/>
+      <c r="Z25" s="4"/>
+      <c r="AB25" s="5"/>
+      <c r="AC25" s="5"/>
+      <c r="AD25" s="5"/>
+      <c r="AE25" s="6"/>
+      <c r="AF25" s="6"/>
+      <c r="AG25" s="6"/>
+      <c r="AH25" s="5"/>
+      <c r="AI25" s="5"/>
+      <c r="AJ25" s="5"/>
+      <c r="AK25" s="6"/>
+      <c r="AL25" s="6"/>
+      <c r="AM25" s="6"/>
+      <c r="AO25" s="5"/>
+      <c r="AP25" s="5"/>
+      <c r="AQ25" s="5"/>
+      <c r="AR25" s="6"/>
+      <c r="AS25" s="6"/>
+      <c r="AT25" s="6"/>
+      <c r="AU25" s="5"/>
+      <c r="AV25" s="5"/>
+      <c r="AW25" s="5"/>
+      <c r="AX25" s="6"/>
+      <c r="AY25" s="6"/>
+      <c r="AZ25" s="4"/>
+    </row>
+    <row r="26" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="6"/>
+      <c r="T26" s="6"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+      <c r="W26" s="5"/>
+      <c r="X26" s="6"/>
+      <c r="Y26" s="6"/>
+      <c r="Z26" s="4"/>
+      <c r="AB26" s="5"/>
+      <c r="AC26" s="5"/>
+      <c r="AD26" s="5"/>
+      <c r="AE26" s="6"/>
+      <c r="AF26" s="6"/>
+      <c r="AG26" s="6"/>
+      <c r="AH26" s="5"/>
+      <c r="AI26" s="5"/>
+      <c r="AJ26" s="5"/>
+      <c r="AK26" s="6"/>
+      <c r="AL26" s="6"/>
+      <c r="AM26" s="6"/>
+      <c r="AO26" s="5"/>
+      <c r="AP26" s="5"/>
+      <c r="AQ26" s="5"/>
+      <c r="AR26" s="6"/>
+      <c r="AS26" s="6"/>
+      <c r="AT26" s="6"/>
+      <c r="AU26" s="5"/>
+      <c r="AV26" s="5"/>
+      <c r="AW26" s="5"/>
+      <c r="AX26" s="6"/>
+      <c r="AY26" s="6"/>
+      <c r="AZ26" s="4"/>
+    </row>
+    <row r="27" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="6"/>
+      <c r="S27" s="6"/>
+      <c r="T27" s="6"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+      <c r="W27" s="5"/>
+      <c r="X27" s="6"/>
+      <c r="Y27" s="6"/>
+      <c r="Z27" s="4"/>
+      <c r="AB27" s="5"/>
+      <c r="AC27" s="5"/>
+      <c r="AD27" s="5"/>
+      <c r="AE27" s="6"/>
+      <c r="AF27" s="6"/>
+      <c r="AG27" s="6"/>
+      <c r="AH27" s="5"/>
+      <c r="AI27" s="5"/>
+      <c r="AJ27" s="5"/>
+      <c r="AK27" s="6"/>
+      <c r="AL27" s="6"/>
+      <c r="AM27" s="6"/>
+      <c r="AO27" s="5"/>
+      <c r="AP27" s="5"/>
+      <c r="AQ27" s="5"/>
+      <c r="AR27" s="6"/>
+      <c r="AS27" s="6"/>
+      <c r="AT27" s="6"/>
+      <c r="AU27" s="5"/>
+      <c r="AV27" s="5"/>
+      <c r="AW27" s="5"/>
+      <c r="AX27" s="6"/>
+      <c r="AY27" s="6"/>
+      <c r="AZ27" s="4"/>
+    </row>
+    <row r="28" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+    </row>
+    <row r="31" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+    </row>
+    <row r="32" spans="2:52" x14ac:dyDescent="0.25">
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="40">
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="O1:Y1"/>
+    <mergeCell ref="AB1:AL1"/>
+    <mergeCell ref="AO1:AY1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="O15:Y15"/>
+    <mergeCell ref="AB15:AL15"/>
+    <mergeCell ref="AO15:AY15"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AK2:AM2"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="AO16:AQ16"/>
+    <mergeCell ref="AR16:AT16"/>
+    <mergeCell ref="AU16:AW16"/>
+    <mergeCell ref="AX16:AZ16"/>
+    <mergeCell ref="U16:W16"/>
+    <mergeCell ref="X16:Z16"/>
+    <mergeCell ref="AB16:AD16"/>
+    <mergeCell ref="AE16:AG16"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AK16:AM16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -8020,63 +6889,63 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32"/>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
+      <c r="A1" s="67"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="67"/>
+      <c r="T1" s="67"/>
+      <c r="U1" s="67"/>
+      <c r="V1" s="67"/>
+      <c r="W1" s="67"/>
+      <c r="X1" s="67"/>
+      <c r="Y1" s="67"/>
+      <c r="Z1" s="67"/>
+      <c r="AA1" s="67"/>
     </row>
     <row r="4" spans="1:29" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="37"/>
-      <c r="U4" s="37"/>
-      <c r="V4" s="37"/>
-      <c r="W4" s="37"/>
-      <c r="X4" s="37"/>
-      <c r="Y4" s="37"/>
-      <c r="Z4" s="37"/>
-      <c r="AA4" s="37"/>
-      <c r="AB4" s="37"/>
-      <c r="AC4" s="37"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
+      <c r="R4" s="51"/>
+      <c r="S4" s="51"/>
+      <c r="T4" s="51"/>
+      <c r="U4" s="51"/>
+      <c r="V4" s="51"/>
+      <c r="W4" s="51"/>
+      <c r="X4" s="51"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="51"/>
+      <c r="AB4" s="51"/>
+      <c r="AC4" s="51"/>
     </row>
     <row r="5" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M5" s="13"/>
@@ -8098,7 +6967,7 @@
       <c r="E6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="39" t="s">
+      <c r="F6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -8130,32 +6999,32 @@
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="53" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="7">
         <v>1</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="54">
         <v>66</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="54">
         <v>66</v>
       </c>
-      <c r="F7" s="40"/>
-      <c r="G7" s="26">
+      <c r="F7" s="56"/>
+      <c r="G7" s="54">
         <v>1</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="54">
         <v>1</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="54">
         <v>66</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="54">
         <v>66</v>
       </c>
       <c r="K7" s="6"/>
@@ -8165,18 +7034,18 @@
       <c r="O7" s="15"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A8" s="34"/>
+      <c r="A8" s="53"/>
       <c r="B8" s="7">
         <v>3</v>
       </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
@@ -8184,18 +7053,18 @@
       <c r="O8" s="15"/>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A9" s="34"/>
+      <c r="A9" s="53"/>
       <c r="B9" s="7">
         <v>5</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
@@ -8203,18 +7072,18 @@
       <c r="O9" s="15"/>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
+      <c r="A10" s="53"/>
       <c r="B10" s="7">
         <v>10</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
@@ -8222,20 +7091,20 @@
       <c r="O10" s="15"/>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="54" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="4">
         <v>1</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5"/>
@@ -8243,18 +7112,18 @@
       <c r="O11" s="5"/>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A12" s="26"/>
+      <c r="A12" s="54"/>
       <c r="B12" s="4">
         <v>3</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54"/>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
@@ -8262,18 +7131,18 @@
       <c r="O12" s="5"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="4">
         <v>5</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
@@ -8281,18 +7150,18 @@
       <c r="O13" s="5"/>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A14" s="26"/>
+      <c r="A14" s="54"/>
       <c r="B14" s="4">
         <v>10</v>
       </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
@@ -8300,20 +7169,20 @@
       <c r="O14" s="5"/>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="53" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="7">
         <v>1</v>
       </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="54"/>
       <c r="K15" s="15"/>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
@@ -8321,18 +7190,18 @@
       <c r="O15" s="15"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A16" s="34"/>
+      <c r="A16" s="53"/>
       <c r="B16" s="7">
         <v>3</v>
       </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="54"/>
       <c r="K16" s="15"/>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
@@ -8340,18 +7209,18 @@
       <c r="O16" s="15"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="34"/>
+      <c r="A17" s="53"/>
       <c r="B17" s="7">
         <v>5</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="54"/>
       <c r="K17" s="15"/>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
@@ -8359,18 +7228,18 @@
       <c r="O17" s="15"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="34"/>
+      <c r="A18" s="53"/>
       <c r="B18" s="7">
         <v>10</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="54"/>
       <c r="K18" s="15"/>
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
@@ -8378,20 +7247,20 @@
       <c r="O18" s="15"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="54" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="4">
         <v>1</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="54"/>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
@@ -8399,18 +7268,18 @@
       <c r="O19" s="5"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="26"/>
+      <c r="A20" s="54"/>
       <c r="B20" s="4">
         <v>3</v>
       </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
@@ -8418,18 +7287,18 @@
       <c r="O20" s="5"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="26"/>
+      <c r="A21" s="54"/>
       <c r="B21" s="4">
         <v>5</v>
       </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
@@ -8437,72 +7306,72 @@
       <c r="O21" s="5"/>
     </row>
     <row r="22" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59"/>
-      <c r="B22" s="70">
+      <c r="A22" s="62"/>
+      <c r="B22" s="39">
         <v>10</v>
       </c>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="61"/>
-      <c r="M22" s="61"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="61"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="32"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="71" t="s">
+      <c r="A23" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="65">
+      <c r="B23" s="34">
         <v>1</v>
       </c>
-      <c r="C23" s="63" t="s">
+      <c r="C23" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="63">
+      <c r="D23" s="61">
         <v>128</v>
       </c>
-      <c r="E23" s="63">
+      <c r="E23" s="61">
         <v>128</v>
       </c>
-      <c r="F23" s="64"/>
-      <c r="G23" s="63">
+      <c r="F23" s="65"/>
+      <c r="G23" s="61">
         <v>1</v>
       </c>
-      <c r="H23" s="63">
+      <c r="H23" s="61">
         <v>1</v>
       </c>
-      <c r="I23" s="63">
+      <c r="I23" s="61">
         <v>128</v>
       </c>
-      <c r="J23" s="63">
+      <c r="J23" s="61">
         <v>128</v>
       </c>
-      <c r="K23" s="65"/>
-      <c r="L23" s="65"/>
-      <c r="M23" s="66"/>
-      <c r="N23" s="67"/>
-      <c r="O23" s="66"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="34"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="35"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="72"/>
+      <c r="A24" s="60"/>
       <c r="B24" s="4">
         <v>3</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="26"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="5"/>
@@ -8510,18 +7379,18 @@
       <c r="O24" s="5"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="72"/>
+      <c r="A25" s="60"/>
       <c r="B25" s="4">
         <v>5</v>
       </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="54"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="5"/>
@@ -8529,18 +7398,18 @@
       <c r="O25" s="5"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="72"/>
+      <c r="A26" s="60"/>
       <c r="B26" s="4">
         <v>10</v>
       </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="5"/>
@@ -8548,20 +7417,20 @@
       <c r="O26" s="5"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="59" t="s">
         <v>13</v>
       </c>
       <c r="B27" s="10">
         <v>1</v>
       </c>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="54"/>
       <c r="K27" s="10"/>
       <c r="L27" s="10"/>
       <c r="M27" s="15"/>
@@ -8569,18 +7438,18 @@
       <c r="O27" s="15"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="29"/>
+      <c r="A28" s="59"/>
       <c r="B28" s="10">
         <v>3</v>
       </c>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="54"/>
       <c r="K28" s="10"/>
       <c r="L28" s="10"/>
       <c r="M28" s="15"/>
@@ -8588,18 +7457,18 @@
       <c r="O28" s="15"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="29"/>
+      <c r="A29" s="59"/>
       <c r="B29" s="10">
         <v>5</v>
       </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
       <c r="M29" s="15"/>
@@ -8607,18 +7476,18 @@
       <c r="O29" s="15"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="29"/>
+      <c r="A30" s="59"/>
       <c r="B30" s="10">
         <v>10</v>
       </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="54"/>
       <c r="K30" s="10"/>
       <c r="L30" s="10"/>
       <c r="M30" s="15"/>
@@ -8626,98 +7495,98 @@
       <c r="O30" s="15"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="72" t="s">
+      <c r="A31" s="60" t="s">
         <v>14</v>
       </c>
       <c r="B31" s="4">
         <v>1</v>
       </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="57"/>
-      <c r="L31" s="57"/>
-      <c r="M31" s="57"/>
-      <c r="N31" s="58"/>
-      <c r="O31" s="57"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="5"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="72"/>
+      <c r="A32" s="60"/>
       <c r="B32" s="4">
         <v>3</v>
       </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="57"/>
-      <c r="L32" s="57"/>
-      <c r="M32" s="57"/>
-      <c r="N32" s="58"/>
-      <c r="O32" s="57"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="5"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="72"/>
+      <c r="A33" s="60"/>
       <c r="B33" s="4">
         <v>5</v>
       </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="57"/>
-      <c r="L33" s="57"/>
-      <c r="M33" s="57"/>
-      <c r="N33" s="58"/>
-      <c r="O33" s="57"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="54"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="5"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="72"/>
+      <c r="A34" s="60"/>
       <c r="B34" s="11">
         <v>10</v>
       </c>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="57"/>
-      <c r="L34" s="57"/>
-      <c r="M34" s="57"/>
-      <c r="N34" s="58"/>
-      <c r="O34" s="57"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="54"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="5"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="59" t="s">
         <v>15</v>
       </c>
       <c r="B35" s="10">
         <v>1</v>
       </c>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
       <c r="K35" s="15"/>
       <c r="L35" s="15"/>
       <c r="M35" s="15"/>
@@ -8725,18 +7594,18 @@
       <c r="O35" s="15"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="29"/>
+      <c r="A36" s="59"/>
       <c r="B36" s="10">
         <v>3</v>
       </c>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="54"/>
       <c r="K36" s="15"/>
       <c r="L36" s="15"/>
       <c r="M36" s="15"/>
@@ -8744,18 +7613,18 @@
       <c r="O36" s="15"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="29"/>
+      <c r="A37" s="59"/>
       <c r="B37" s="10">
         <v>5</v>
       </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54"/>
+      <c r="E37" s="54"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="54"/>
+      <c r="H37" s="54"/>
+      <c r="I37" s="54"/>
+      <c r="J37" s="54"/>
       <c r="K37" s="15"/>
       <c r="L37" s="15"/>
       <c r="M37" s="15"/>
@@ -8763,38 +7632,26 @@
       <c r="O37" s="15"/>
     </row>
     <row r="38" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="73"/>
-      <c r="B38" s="74">
+      <c r="A38" s="63"/>
+      <c r="B38" s="40">
         <v>10</v>
       </c>
-      <c r="C38" s="59"/>
-      <c r="D38" s="59"/>
-      <c r="E38" s="59"/>
-      <c r="F38" s="60"/>
-      <c r="G38" s="59"/>
-      <c r="H38" s="59"/>
-      <c r="I38" s="59"/>
-      <c r="J38" s="59"/>
-      <c r="K38" s="68"/>
-      <c r="L38" s="68"/>
-      <c r="M38" s="68"/>
-      <c r="N38" s="69"/>
-      <c r="O38" s="68"/>
+      <c r="C38" s="62"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="62"/>
+      <c r="H38" s="62"/>
+      <c r="I38" s="62"/>
+      <c r="J38" s="62"/>
+      <c r="K38" s="37"/>
+      <c r="L38" s="37"/>
+      <c r="M38" s="37"/>
+      <c r="N38" s="38"/>
+      <c r="O38" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="G23:G38"/>
-    <mergeCell ref="H23:H38"/>
-    <mergeCell ref="I23:I38"/>
-    <mergeCell ref="J23:J38"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="C23:C38"/>
-    <mergeCell ref="D23:D38"/>
-    <mergeCell ref="E23:E38"/>
-    <mergeCell ref="F23:F38"/>
     <mergeCell ref="A1:AA1"/>
     <mergeCell ref="D4:AC4"/>
     <mergeCell ref="A7:A10"/>
@@ -8809,29 +7666,24 @@
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="A15:A18"/>
     <mergeCell ref="A19:A22"/>
+    <mergeCell ref="G23:G38"/>
+    <mergeCell ref="H23:H38"/>
+    <mergeCell ref="I23:I38"/>
+    <mergeCell ref="J23:J38"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="C23:C38"/>
+    <mergeCell ref="D23:D38"/>
+    <mergeCell ref="E23:E38"/>
+    <mergeCell ref="F23:F38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A16C87A6682E6E4295773DFF29EAB41B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a3213889016ec1ec7c5b45183b07d2a5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xmlns:ns4="c7f849e2-0a63-4d53-be53-fb9d39becd19" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39cf848dedf08b05fa72a945c282372c" ns3:_="" ns4:_="">
     <xsd:import namespace="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
@@ -9056,10 +7908,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
+    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9082,20 +7962,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
-    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/documents/ExperimentData.xlsx
+++ b/documents/ExperimentData.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1b2bcfbbb34c0c/Documents/GitHub/meliso/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1621" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{245B2FCF-5AE0-402D-9354-29DF10D5A247}"/>
+  <xr:revisionPtr revIDLastSave="1733" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3020F327-55BD-4FC8-8079-59A30095D32F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
   </bookViews>
   <sheets>
     <sheet name="DataExp1" sheetId="2" r:id="rId1"/>
-    <sheet name="Experiment 1" sheetId="1" r:id="rId2"/>
-    <sheet name="DataExp2" sheetId="4" r:id="rId3"/>
-    <sheet name="Experiment 2" sheetId="3" r:id="rId4"/>
-    <sheet name="Experiment 3" sheetId="5" r:id="rId5"/>
-    <sheet name="DataExp4" sheetId="6" r:id="rId6"/>
+    <sheet name="Experiment 1.1" sheetId="1" r:id="rId2"/>
+    <sheet name="Experiment 1.2" sheetId="7" r:id="rId3"/>
+    <sheet name="DataExp2" sheetId="4" r:id="rId4"/>
+    <sheet name="Experiment 2" sheetId="3" r:id="rId5"/>
+    <sheet name="Experiment 3" sheetId="5" r:id="rId6"/>
+    <sheet name="DataExp4" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="55">
   <si>
     <t>MCA Rows</t>
   </si>
@@ -145,12 +146,6 @@
     <t>Conditioning Number</t>
   </si>
   <si>
-    <t>Centralized Computation; 
-Fixed Number of Iterations for Error Correction; 
-Only applied Error Correction on Worst Device (a.k.a. excluding EpiRAM):
-Run 10 replications for each number of iterations</t>
-  </si>
-  <si>
     <t>Elapsed Time</t>
   </si>
   <si>
@@ -210,6 +205,18 @@
   <si>
     <t>Latency (V3.0)</t>
   </si>
+  <si>
+    <t>Centralized Computation (Small-scale); 
+Fixed Number of Iterations for Error Correction; 
+Only applied Error Correction on Worst Device (a.k.a. excluding EpiRAM):
+Run 10 replications for each number of iterations</t>
+  </si>
+  <si>
+    <t>Decentralized Computation (Large-scale); 
+Fixed Number of Iterations for Error Correction; 
+Aplied Error Correction to all devices
+Run 10 replications for each number of iterations</t>
+  </si>
 </sst>
 </file>
 
@@ -248,7 +255,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -270,12 +277,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -418,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -459,8 +460,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -474,7 +473,22 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -498,25 +512,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -531,17 +527,41 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -549,35 +569,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -932,143 +927,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
       <c r="M1" s="21"/>
-      <c r="O1" s="33" t="s">
+      <c r="O1" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="AB1" s="33" t="s">
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="AB1" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="AC1" s="33"/>
-      <c r="AD1" s="33"/>
-      <c r="AE1" s="33"/>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="33"/>
-      <c r="AI1" s="33"/>
-      <c r="AJ1" s="33"/>
-      <c r="AK1" s="41"/>
-      <c r="AL1" s="41"/>
+      <c r="AC1" s="46"/>
+      <c r="AD1" s="46"/>
+      <c r="AE1" s="46"/>
+      <c r="AF1" s="46"/>
+      <c r="AG1" s="46"/>
+      <c r="AH1" s="46"/>
+      <c r="AI1" s="46"/>
+      <c r="AJ1" s="46"/>
+      <c r="AK1" s="38"/>
+      <c r="AL1" s="38"/>
       <c r="AM1" s="21"/>
-      <c r="AO1" s="33" t="s">
+      <c r="AO1" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="AP1" s="33"/>
-      <c r="AQ1" s="33"/>
-      <c r="AR1" s="33"/>
-      <c r="AS1" s="33"/>
-      <c r="AT1" s="33"/>
-      <c r="AU1" s="33"/>
-      <c r="AV1" s="33"/>
-      <c r="AW1" s="33"/>
-      <c r="AX1" s="41"/>
-      <c r="AY1" s="41"/>
+      <c r="AP1" s="46"/>
+      <c r="AQ1" s="46"/>
+      <c r="AR1" s="46"/>
+      <c r="AS1" s="46"/>
+      <c r="AT1" s="46"/>
+      <c r="AU1" s="46"/>
+      <c r="AV1" s="46"/>
+      <c r="AW1" s="46"/>
+      <c r="AX1" s="38"/>
+      <c r="AY1" s="38"/>
     </row>
     <row r="2" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="34" t="s">
+      <c r="C2" s="40"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="35"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="37" t="s">
+      <c r="F2" s="40"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="38"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="40" t="s">
+      <c r="I2" s="43"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="O2" s="34" t="s">
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="O2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="34" t="s">
+      <c r="P2" s="40"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="S2" s="35"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="37" t="s">
+      <c r="S2" s="40"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="38"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="40" t="s">
+      <c r="V2" s="43"/>
+      <c r="W2" s="44"/>
+      <c r="X2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="45"/>
       <c r="AA2" s="21"/>
-      <c r="AB2" s="34" t="s">
+      <c r="AB2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="AC2" s="35"/>
-      <c r="AD2" s="36"/>
-      <c r="AE2" s="34" t="s">
+      <c r="AC2" s="40"/>
+      <c r="AD2" s="41"/>
+      <c r="AE2" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="36"/>
-      <c r="AH2" s="37" t="s">
+      <c r="AF2" s="40"/>
+      <c r="AG2" s="41"/>
+      <c r="AH2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="39"/>
-      <c r="AK2" s="40" t="s">
+      <c r="AI2" s="43"/>
+      <c r="AJ2" s="44"/>
+      <c r="AK2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="AL2" s="40"/>
-      <c r="AM2" s="40"/>
-      <c r="AO2" s="34" t="s">
+      <c r="AL2" s="45"/>
+      <c r="AM2" s="45"/>
+      <c r="AO2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="AP2" s="35"/>
-      <c r="AQ2" s="36"/>
-      <c r="AR2" s="34" t="s">
+      <c r="AP2" s="40"/>
+      <c r="AQ2" s="41"/>
+      <c r="AR2" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="AS2" s="35"/>
-      <c r="AT2" s="36"/>
-      <c r="AU2" s="37" t="s">
+      <c r="AS2" s="40"/>
+      <c r="AT2" s="41"/>
+      <c r="AU2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="AV2" s="38"/>
-      <c r="AW2" s="39"/>
-      <c r="AX2" s="40" t="s">
+      <c r="AV2" s="43"/>
+      <c r="AW2" s="44"/>
+      <c r="AX2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="AY2" s="40"/>
-      <c r="AZ2" s="40"/>
+      <c r="AY2" s="45"/>
+      <c r="AZ2" s="45"/>
     </row>
     <row r="3" spans="2:52" ht="45" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -1077,8 +1072,8 @@
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="27" t="s">
-        <v>35</v>
+      <c r="D3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>20</v>
@@ -1086,8 +1081,8 @@
       <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="27" t="s">
-        <v>35</v>
+      <c r="G3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>20</v>
@@ -1095,8 +1090,8 @@
       <c r="I3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="27" t="s">
-        <v>35</v>
+      <c r="J3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>20</v>
@@ -1104,8 +1099,8 @@
       <c r="L3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="27" t="s">
-        <v>35</v>
+      <c r="M3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>20</v>
@@ -1113,8 +1108,8 @@
       <c r="P3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="27" t="s">
-        <v>35</v>
+      <c r="Q3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>20</v>
@@ -1122,8 +1117,8 @@
       <c r="S3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="27" t="s">
-        <v>35</v>
+      <c r="T3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="U3" s="8" t="s">
         <v>20</v>
@@ -1131,8 +1126,8 @@
       <c r="V3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="W3" s="27" t="s">
-        <v>35</v>
+      <c r="W3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="X3" s="8" t="s">
         <v>20</v>
@@ -1140,18 +1135,18 @@
       <c r="Y3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="Z3" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="27" t="s">
+      <c r="Z3" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="25" t="s">
         <v>20</v>
       </c>
       <c r="AC3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AD3" s="27" t="s">
-        <v>35</v>
+      <c r="AD3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AE3" s="2" t="s">
         <v>20</v>
@@ -1159,8 +1154,8 @@
       <c r="AF3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AG3" s="27" t="s">
-        <v>35</v>
+      <c r="AG3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AH3" s="8" t="s">
         <v>20</v>
@@ -1168,8 +1163,8 @@
       <c r="AI3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AJ3" s="27" t="s">
-        <v>35</v>
+      <c r="AJ3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AK3" s="8" t="s">
         <v>20</v>
@@ -1177,17 +1172,17 @@
       <c r="AL3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AM3" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO3" s="27" t="s">
+      <c r="AM3" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AO3" s="25" t="s">
         <v>20</v>
       </c>
       <c r="AP3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AQ3" s="27" t="s">
-        <v>35</v>
+      <c r="AQ3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AR3" s="2" t="s">
         <v>20</v>
@@ -1195,8 +1190,8 @@
       <c r="AS3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AT3" s="27" t="s">
-        <v>35</v>
+      <c r="AT3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AU3" s="8" t="s">
         <v>20</v>
@@ -1204,8 +1199,8 @@
       <c r="AV3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AW3" s="27" t="s">
-        <v>35</v>
+      <c r="AW3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AX3" s="8" t="s">
         <v>20</v>
@@ -1213,8 +1208,8 @@
       <c r="AY3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AZ3" s="27" t="s">
-        <v>35</v>
+      <c r="AZ3" s="25" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="2:52" x14ac:dyDescent="0.25">
@@ -2557,143 +2552,143 @@
       <c r="D14" s="7"/>
     </row>
     <row r="15" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="41"/>
-      <c r="L15" s="41"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
       <c r="M15" s="21"/>
-      <c r="O15" s="33" t="s">
+      <c r="O15" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="33"/>
-      <c r="V15" s="33"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="33"/>
-      <c r="Y15" s="33"/>
-      <c r="AB15" s="33" t="s">
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="46"/>
+      <c r="S15" s="46"/>
+      <c r="T15" s="46"/>
+      <c r="U15" s="46"/>
+      <c r="V15" s="46"/>
+      <c r="W15" s="46"/>
+      <c r="X15" s="46"/>
+      <c r="Y15" s="46"/>
+      <c r="AB15" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="AC15" s="33"/>
-      <c r="AD15" s="33"/>
-      <c r="AE15" s="33"/>
-      <c r="AF15" s="33"/>
-      <c r="AG15" s="33"/>
-      <c r="AH15" s="33"/>
-      <c r="AI15" s="33"/>
-      <c r="AJ15" s="33"/>
-      <c r="AK15" s="33"/>
-      <c r="AL15" s="33"/>
+      <c r="AC15" s="46"/>
+      <c r="AD15" s="46"/>
+      <c r="AE15" s="46"/>
+      <c r="AF15" s="46"/>
+      <c r="AG15" s="46"/>
+      <c r="AH15" s="46"/>
+      <c r="AI15" s="46"/>
+      <c r="AJ15" s="46"/>
+      <c r="AK15" s="46"/>
+      <c r="AL15" s="46"/>
       <c r="AM15" s="21"/>
-      <c r="AO15" s="33" t="s">
+      <c r="AO15" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="AP15" s="33"/>
-      <c r="AQ15" s="33"/>
-      <c r="AR15" s="33"/>
-      <c r="AS15" s="33"/>
-      <c r="AT15" s="33"/>
-      <c r="AU15" s="33"/>
-      <c r="AV15" s="33"/>
-      <c r="AW15" s="33"/>
-      <c r="AX15" s="33"/>
-      <c r="AY15" s="33"/>
+      <c r="AP15" s="46"/>
+      <c r="AQ15" s="46"/>
+      <c r="AR15" s="46"/>
+      <c r="AS15" s="46"/>
+      <c r="AT15" s="46"/>
+      <c r="AU15" s="46"/>
+      <c r="AV15" s="46"/>
+      <c r="AW15" s="46"/>
+      <c r="AX15" s="46"/>
+      <c r="AY15" s="46"/>
     </row>
     <row r="16" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="34" t="s">
+      <c r="C16" s="40"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="35"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="37" t="s">
+      <c r="F16" s="40"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="38"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="40" t="s">
+      <c r="I16" s="43"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="O16" s="34" t="s">
+      <c r="L16" s="45"/>
+      <c r="M16" s="45"/>
+      <c r="O16" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="36"/>
-      <c r="R16" s="34" t="s">
+      <c r="P16" s="40"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="S16" s="35"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="37" t="s">
+      <c r="S16" s="40"/>
+      <c r="T16" s="41"/>
+      <c r="U16" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="V16" s="38"/>
-      <c r="W16" s="39"/>
-      <c r="X16" s="40" t="s">
+      <c r="V16" s="43"/>
+      <c r="W16" s="44"/>
+      <c r="X16" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="Y16" s="40"/>
-      <c r="Z16" s="40"/>
+      <c r="Y16" s="45"/>
+      <c r="Z16" s="45"/>
       <c r="AA16" s="21"/>
-      <c r="AB16" s="34" t="s">
+      <c r="AB16" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="AC16" s="35"/>
-      <c r="AD16" s="36"/>
-      <c r="AE16" s="34" t="s">
+      <c r="AC16" s="40"/>
+      <c r="AD16" s="41"/>
+      <c r="AE16" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="AF16" s="35"/>
-      <c r="AG16" s="36"/>
-      <c r="AH16" s="37" t="s">
+      <c r="AF16" s="40"/>
+      <c r="AG16" s="41"/>
+      <c r="AH16" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="AI16" s="38"/>
-      <c r="AJ16" s="39"/>
-      <c r="AK16" s="40" t="s">
+      <c r="AI16" s="43"/>
+      <c r="AJ16" s="44"/>
+      <c r="AK16" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="AL16" s="40"/>
-      <c r="AM16" s="40"/>
-      <c r="AO16" s="34" t="s">
+      <c r="AL16" s="45"/>
+      <c r="AM16" s="45"/>
+      <c r="AO16" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="AP16" s="35"/>
-      <c r="AQ16" s="36"/>
-      <c r="AR16" s="34" t="s">
+      <c r="AP16" s="40"/>
+      <c r="AQ16" s="41"/>
+      <c r="AR16" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="AS16" s="35"/>
-      <c r="AT16" s="36"/>
-      <c r="AU16" s="37" t="s">
+      <c r="AS16" s="40"/>
+      <c r="AT16" s="41"/>
+      <c r="AU16" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="AV16" s="38"/>
-      <c r="AW16" s="39"/>
-      <c r="AX16" s="40" t="s">
+      <c r="AV16" s="43"/>
+      <c r="AW16" s="44"/>
+      <c r="AX16" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="AY16" s="40"/>
-      <c r="AZ16" s="40"/>
+      <c r="AY16" s="45"/>
+      <c r="AZ16" s="45"/>
     </row>
     <row r="17" spans="2:52" ht="45" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
@@ -2702,8 +2697,8 @@
       <c r="C17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="27" t="s">
-        <v>35</v>
+      <c r="D17" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>20</v>
@@ -2711,8 +2706,8 @@
       <c r="F17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="27" t="s">
-        <v>35</v>
+      <c r="G17" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="H17" s="8" t="s">
         <v>20</v>
@@ -2720,8 +2715,8 @@
       <c r="I17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J17" s="27" t="s">
-        <v>35</v>
+      <c r="J17" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="K17" s="8" t="s">
         <v>20</v>
@@ -2729,8 +2724,8 @@
       <c r="L17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M17" s="27" t="s">
-        <v>35</v>
+      <c r="M17" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>20</v>
@@ -2738,8 +2733,8 @@
       <c r="P17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Q17" s="27" t="s">
-        <v>35</v>
+      <c r="Q17" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>20</v>
@@ -2747,8 +2742,8 @@
       <c r="S17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="T17" s="27" t="s">
-        <v>35</v>
+      <c r="T17" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="U17" s="8" t="s">
         <v>20</v>
@@ -2756,8 +2751,8 @@
       <c r="V17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="W17" s="27" t="s">
-        <v>35</v>
+      <c r="W17" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="X17" s="8" t="s">
         <v>20</v>
@@ -2765,18 +2760,18 @@
       <c r="Y17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="Z17" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA17" s="30"/>
-      <c r="AB17" s="27" t="s">
+      <c r="Z17" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA17" s="28"/>
+      <c r="AB17" s="25" t="s">
         <v>20</v>
       </c>
       <c r="AC17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AD17" s="27" t="s">
-        <v>35</v>
+      <c r="AD17" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AE17" s="2" t="s">
         <v>20</v>
@@ -2784,8 +2779,8 @@
       <c r="AF17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AG17" s="27" t="s">
-        <v>35</v>
+      <c r="AG17" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AH17" s="8" t="s">
         <v>20</v>
@@ -2793,8 +2788,8 @@
       <c r="AI17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AJ17" s="27" t="s">
-        <v>35</v>
+      <c r="AJ17" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AK17" s="8" t="s">
         <v>20</v>
@@ -2802,17 +2797,17 @@
       <c r="AL17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AM17" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO17" s="27" t="s">
+      <c r="AM17" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AO17" s="25" t="s">
         <v>20</v>
       </c>
       <c r="AP17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AQ17" s="27" t="s">
-        <v>35</v>
+      <c r="AQ17" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AR17" s="2" t="s">
         <v>20</v>
@@ -2820,8 +2815,8 @@
       <c r="AS17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AT17" s="27" t="s">
-        <v>35</v>
+      <c r="AT17" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AU17" s="8" t="s">
         <v>20</v>
@@ -2829,8 +2824,8 @@
       <c r="AV17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AW17" s="27" t="s">
-        <v>35</v>
+      <c r="AW17" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AX17" s="8" t="s">
         <v>20</v>
@@ -2838,8 +2833,8 @@
       <c r="AY17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AZ17" s="27" t="s">
-        <v>35</v>
+      <c r="AZ17" s="25" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="2:52" x14ac:dyDescent="0.25">
@@ -2870,7 +2865,7 @@
       <c r="L18" s="5">
         <v>0.73005812699544603</v>
       </c>
-      <c r="M18" s="28"/>
+      <c r="M18" s="26"/>
       <c r="O18" s="4">
         <v>157.491792122156</v>
       </c>
@@ -2898,7 +2893,7 @@
       <c r="Y18" s="5">
         <v>1.00475359299919</v>
       </c>
-      <c r="AB18" s="29">
+      <c r="AB18" s="27">
         <v>13.236245367749699</v>
       </c>
       <c r="AC18" s="4">
@@ -2983,7 +2978,7 @@
       <c r="L19" s="5">
         <v>0.86446282869091995</v>
       </c>
-      <c r="M19" s="28"/>
+      <c r="M19" s="26"/>
       <c r="O19" s="4">
         <v>157.29900707611901</v>
       </c>
@@ -3011,7 +3006,7 @@
       <c r="Y19" s="5">
         <v>0.46057620855832399</v>
       </c>
-      <c r="AB19" s="29">
+      <c r="AB19" s="27">
         <v>13.236245367749699</v>
       </c>
       <c r="AC19" s="4">
@@ -3096,7 +3091,7 @@
       <c r="L20" s="5">
         <v>0.61635383312902503</v>
       </c>
-      <c r="M20" s="28"/>
+      <c r="M20" s="26"/>
       <c r="O20" s="4">
         <v>159.352853227227</v>
       </c>
@@ -3124,7 +3119,7 @@
       <c r="Y20" s="5">
         <v>1.0174902634114</v>
       </c>
-      <c r="AB20" s="29">
+      <c r="AB20" s="27">
         <v>13.2496111916915</v>
       </c>
       <c r="AC20" s="4">
@@ -3209,7 +3204,7 @@
       <c r="L21" s="5">
         <v>0.72984480789211603</v>
       </c>
-      <c r="M21" s="28"/>
+      <c r="M21" s="26"/>
       <c r="O21" s="4">
         <v>157.29900707611901</v>
       </c>
@@ -3237,7 +3232,7 @@
       <c r="Y21" s="5">
         <v>0.97220188931186902</v>
       </c>
-      <c r="AB21" s="29">
+      <c r="AB21" s="27">
         <v>13.308572250548099</v>
       </c>
       <c r="AC21" s="4">
@@ -3322,7 +3317,7 @@
       <c r="L22" s="5">
         <v>0.66684968307617798</v>
       </c>
-      <c r="M22" s="28"/>
+      <c r="M22" s="26"/>
       <c r="O22" s="4">
         <v>156.63177221391601</v>
       </c>
@@ -3350,7 +3345,7 @@
       <c r="Y22" s="5">
         <v>0.98780444655659705</v>
       </c>
-      <c r="AB22" s="29">
+      <c r="AB22" s="27">
         <v>13.2363942457426</v>
       </c>
       <c r="AC22" s="4">
@@ -3435,7 +3430,7 @@
       <c r="L23" s="5">
         <v>0.52390907977896095</v>
       </c>
-      <c r="M23" s="28"/>
+      <c r="M23" s="26"/>
       <c r="O23" s="4">
         <v>156.986009517112</v>
       </c>
@@ -3463,7 +3458,7 @@
       <c r="Y23" s="5">
         <v>0.73135202091426998</v>
       </c>
-      <c r="AB23" s="29">
+      <c r="AB23" s="27">
         <v>13.308674501574901</v>
       </c>
       <c r="AC23" s="4">
@@ -3548,7 +3543,7 @@
       <c r="L24" s="5">
         <v>0.85510723023493096</v>
       </c>
-      <c r="M24" s="28"/>
+      <c r="M24" s="26"/>
       <c r="O24" s="4">
         <v>158.196014729155</v>
       </c>
@@ -3576,7 +3571,7 @@
       <c r="Y24" s="5">
         <v>1.0147213122487999</v>
       </c>
-      <c r="AB24" s="29">
+      <c r="AB24" s="27">
         <v>13.308572250548099</v>
       </c>
       <c r="AC24" s="4">
@@ -3661,7 +3656,7 @@
       <c r="L25" s="5">
         <v>0.661985006820213</v>
       </c>
-      <c r="M25" s="28"/>
+      <c r="M25" s="26"/>
       <c r="O25" s="4">
         <v>157.491792122156</v>
       </c>
@@ -3689,7 +3684,7 @@
       <c r="Y25" s="5">
         <v>0.731352021572787</v>
       </c>
-      <c r="AB25" s="29">
+      <c r="AB25" s="27">
         <v>13.2496111916915</v>
       </c>
       <c r="AC25" s="4">
@@ -3774,7 +3769,7 @@
       <c r="L26" s="5">
         <v>0.61961678721450797</v>
       </c>
-      <c r="M26" s="28"/>
+      <c r="M26" s="26"/>
       <c r="O26" s="4">
         <v>156.87408337816299</v>
       </c>
@@ -3802,7 +3797,7 @@
       <c r="Y26" s="5">
         <v>0.86006578658153399</v>
       </c>
-      <c r="AB26" s="29">
+      <c r="AB26" s="27">
         <v>13.2958588107644</v>
       </c>
       <c r="AC26" s="4">
@@ -3887,7 +3882,7 @@
       <c r="L27" s="5">
         <v>0.95989886174272399</v>
       </c>
-      <c r="M27" s="28"/>
+      <c r="M27" s="26"/>
       <c r="O27" s="4">
         <v>157.491792122156</v>
       </c>
@@ -3915,7 +3910,7 @@
       <c r="Y27" s="5">
         <v>0.99652077413521101</v>
       </c>
-      <c r="AB27" s="29">
+      <c r="AB27" s="27">
         <v>13.2496111916915</v>
       </c>
       <c r="AC27" s="4">
@@ -4009,46 +4004,46 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="AB15:AL15"/>
+    <mergeCell ref="AB16:AD16"/>
+    <mergeCell ref="AE16:AG16"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AK16:AM16"/>
+    <mergeCell ref="AO15:AY15"/>
+    <mergeCell ref="AO16:AQ16"/>
+    <mergeCell ref="AR16:AT16"/>
+    <mergeCell ref="AU16:AW16"/>
+    <mergeCell ref="AX16:AZ16"/>
+    <mergeCell ref="O15:Y15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="U16:W16"/>
+    <mergeCell ref="X16:Z16"/>
+    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="AO1:AY1"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="AB1:AL1"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AK2:AM2"/>
+    <mergeCell ref="O1:Y1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="O1:Y1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AB1:AL1"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AK2:AM2"/>
-    <mergeCell ref="AO1:AY1"/>
-    <mergeCell ref="AO2:AQ2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="B15:L15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="O15:Y15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="U16:W16"/>
-    <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="AO15:AY15"/>
-    <mergeCell ref="AO16:AQ16"/>
-    <mergeCell ref="AR16:AT16"/>
-    <mergeCell ref="AU16:AW16"/>
-    <mergeCell ref="AX16:AZ16"/>
-    <mergeCell ref="AB15:AL15"/>
-    <mergeCell ref="AB16:AD16"/>
-    <mergeCell ref="AE16:AG16"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AK16:AM16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4056,7 +4051,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB2F127C-15E6-41A0-94B0-FA50F057125C}">
-  <dimension ref="A1:Z35"/>
+  <dimension ref="A1:Z59"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -4076,47 +4071,47 @@
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12.28515625" customWidth="1"/>
-    <col min="19" max="19" width="10" style="68" customWidth="1"/>
+    <col min="19" max="19" width="10" style="35" customWidth="1"/>
     <col min="20" max="20" width="16.42578125" customWidth="1"/>
     <col min="21" max="21" width="16.7109375" customWidth="1"/>
     <col min="22" max="22" width="15.5703125" customWidth="1"/>
     <col min="23" max="23" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="26" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
+    <row r="1" spans="1:26" s="24" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
     </row>
     <row r="2" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M2" s="12"/>
       <c r="N2" s="15"/>
-      <c r="S2" s="67"/>
+      <c r="S2" s="34"/>
     </row>
     <row r="3" spans="1:26" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -4164,43 +4159,43 @@
       <c r="O3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Q3" s="66"/>
-      <c r="R3" s="69"/>
-      <c r="S3" s="70"/>
-      <c r="T3" s="69"/>
-      <c r="U3" s="69"/>
-      <c r="V3" s="69"/>
-      <c r="W3" s="69"/>
+      <c r="Q3" s="33"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
     </row>
     <row r="4" spans="1:26" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="49" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="44">
+      <c r="D4" s="53">
         <v>66</v>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="53">
         <v>66</v>
       </c>
-      <c r="F4" s="63">
+      <c r="F4" s="54">
         <v>13000</v>
       </c>
-      <c r="G4" s="44">
+      <c r="G4" s="53">
         <v>1</v>
       </c>
-      <c r="H4" s="44">
+      <c r="H4" s="53">
         <v>1</v>
       </c>
-      <c r="I4" s="44">
+      <c r="I4" s="53">
         <v>66</v>
       </c>
-      <c r="J4" s="44">
+      <c r="J4" s="53">
         <v>66</v>
       </c>
       <c r="K4" s="5">
@@ -4221,41 +4216,41 @@
         <f>AVERAGE(DataExp1!D4:D13)</f>
         <v>1.6688517570495538</v>
       </c>
-      <c r="Q4" s="66" t="s">
-        <v>39</v>
-      </c>
-      <c r="R4" s="69" t="s">
+      <c r="Q4" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="R4" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="S4" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="S4" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="T4" s="69" t="s">
+      <c r="T4" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="U4" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="V4" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="U4" s="69" t="s">
-        <v>46</v>
-      </c>
-      <c r="V4" s="69" t="s">
+      <c r="W4" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="W4" s="69" t="s">
-        <v>49</v>
-      </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="51"/>
+      <c r="A5" s="50"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
       <c r="K5" s="5">
         <f>AVERAGE(DataExp1!E4:E13)</f>
         <v>11.070752653739017</v>
@@ -4275,46 +4270,46 @@
         <v>1.6848387241363478</v>
       </c>
       <c r="Q5" t="s">
-        <v>40</v>
-      </c>
-      <c r="R5" s="68">
-        <f>M8/M12</f>
+        <v>39</v>
+      </c>
+      <c r="R5" s="35">
+        <f>M11/M18</f>
         <v>865.2434340049133</v>
       </c>
-      <c r="S5" s="68">
-        <f>N8/N12</f>
+      <c r="S5" s="35">
+        <f>N11/N18</f>
         <v>138.69732699293695</v>
       </c>
-      <c r="T5" s="68">
-        <f>$R$12/$S$12</f>
+      <c r="T5" s="35">
+        <f>$R$18/$S$18</f>
         <v>7.5</v>
       </c>
-      <c r="U5" s="68">
-        <f>$R$13/$S$13</f>
+      <c r="U5" s="35">
+        <f>$R$19/$S$19</f>
         <v>0.5862666666666666</v>
       </c>
-      <c r="V5" s="68">
-        <f>$R$14/$S$14</f>
+      <c r="V5" s="35">
+        <f>$R$20/$S$20</f>
         <v>68.017941414055528</v>
       </c>
-      <c r="W5" s="68">
-        <f>$R$15/$S$15</f>
+      <c r="W5" s="35">
+        <f>$R$24/$S$24</f>
         <v>0.88073394495412838</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
+      <c r="A6" s="50"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
       <c r="K6" s="5">
         <f>AVERAGE(DataExp1!H4:H13)</f>
         <v>4.7480516396353174</v>
@@ -4334,46 +4329,46 @@
         <v>1.7160061359405478</v>
       </c>
       <c r="Q6" t="s">
-        <v>41</v>
-      </c>
-      <c r="R6" s="68">
-        <f>M8/M16</f>
+        <v>40</v>
+      </c>
+      <c r="R6" s="35">
+        <f>M11/M25</f>
         <v>624.1828702262743</v>
       </c>
-      <c r="S6" s="68">
-        <f>N8/N16</f>
+      <c r="S6" s="35">
+        <f>N11/N25</f>
         <v>1013.7172322538682</v>
       </c>
-      <c r="T6" s="68">
-        <f>$R$12/$T$12</f>
+      <c r="T6" s="35">
+        <f>$R$18/$T$18</f>
         <v>93.75</v>
       </c>
-      <c r="U6" s="68">
-        <f>$R$13/$T$13</f>
+      <c r="U6" s="35">
+        <f>$R$19/$T$19</f>
         <v>0.47871529667936857</v>
       </c>
-      <c r="V6" s="68">
-        <f>$R$14/$T$14</f>
+      <c r="V6" s="35">
+        <f>$R$20/$T$20</f>
         <v>139.35975609756099</v>
       </c>
-      <c r="W6" s="68">
-        <f>$R$15/$T$15</f>
+      <c r="W6" s="35">
+        <f>$R$24/$T$24</f>
         <v>0.43340857787810377</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
+      <c r="A7" s="50"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
       <c r="K7" s="5">
         <f>AVERAGE(DataExp1!K4:K13)</f>
         <v>0.84932664663156276</v>
@@ -4389,1148 +4384,1574 @@
         <v>1.90857404909223E-3</v>
       </c>
       <c r="O7" s="14">
-        <f>AVERAGE(DataExp1!M4:M13)</f>
+        <f>AVERAGE(DataExp1!M1:M10)</f>
         <v>1.740799522399898</v>
       </c>
-      <c r="Q7" t="s">
-        <v>42</v>
-      </c>
-      <c r="R7" s="68">
-        <f>M8/M20</f>
+      <c r="R7" s="35"/>
+      <c r="T7" s="35"/>
+      <c r="U7" s="35"/>
+      <c r="V7" s="35"/>
+      <c r="W7" s="35"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="50"/>
+      <c r="B8" s="6">
+        <v>20</v>
+      </c>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="14"/>
+      <c r="R8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="35"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="50"/>
+      <c r="B9" s="6">
+        <v>50</v>
+      </c>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="14"/>
+      <c r="R9" s="35"/>
+      <c r="T9" s="35"/>
+      <c r="U9" s="35"/>
+      <c r="V9" s="35"/>
+      <c r="W9" s="35"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="50"/>
+      <c r="B10" s="6">
+        <v>100</v>
+      </c>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="14"/>
+      <c r="Q10" t="s">
+        <v>41</v>
+      </c>
+      <c r="R10" s="35">
+        <f>M11/M32</f>
         <v>3.7461133543762633E-2</v>
       </c>
-      <c r="S7" s="68">
-        <f>N8/N20</f>
+      <c r="S10" s="35">
+        <f>N11/N32</f>
         <v>3.0787899849979556</v>
       </c>
-      <c r="T7" s="68">
-        <f>$R$12/$U$12</f>
+      <c r="T10" s="35">
+        <f>$R$18/$U$18</f>
         <v>1.1764705882352941E-2</v>
       </c>
-      <c r="U7" s="68">
-        <f>$R$13/$U$13</f>
+      <c r="U10" s="35">
+        <f>$R$19/$U$19</f>
         <v>1.3352566049195262</v>
       </c>
-      <c r="V7" s="68">
-        <f>$R$14/$U$14</f>
+      <c r="V10" s="35">
+        <f>$R$20/$U$20</f>
         <v>3152.4137931034484</v>
       </c>
-      <c r="W7" s="68">
-        <f>$R$15/$U$15</f>
+      <c r="W10" s="35">
+        <f>$R$24/$U$24</f>
         <v>3.3516209476309227</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="45" t="s">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B11" s="3">
         <v>1</v>
       </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="4">
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="4">
         <f>AVERAGE(DataExp1!O4:O13)</f>
         <v>49.821904185231844</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L11" s="4">
         <f>AVERAGE(DataExp1!P4:P13)</f>
         <v>6.6901005257882433</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M11" s="4">
         <v>38.8018530138228</v>
       </c>
-      <c r="N8" s="18">
+      <c r="N11" s="18">
         <v>1.8341564911519399E-2</v>
       </c>
-      <c r="O8" s="4">
+      <c r="O11" s="4">
         <f>AVERAGE(DataExp1!Q4:Q13)</f>
         <v>1.6223374366760202</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="45"/>
-      <c r="B9" s="3">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="51"/>
+      <c r="B12" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="4">
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="4">
         <f>AVERAGE(DataExp1!R4:R13)</f>
         <v>2.2585080679270888</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L12" s="4">
         <f>AVERAGE(DataExp1!S4:S13)</f>
         <v>0.46312458447019578</v>
       </c>
-      <c r="M9" s="4">
+      <c r="M12" s="4">
         <v>73.281259041468303</v>
       </c>
-      <c r="N9" s="18">
+      <c r="N12" s="18">
         <v>3.8957965924184199E-2</v>
       </c>
-      <c r="O9" s="4">
+      <c r="O12" s="4">
         <f>AVERAGE(DataExp1!T4:T13)</f>
         <v>1.6586509227752639</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="45"/>
-      <c r="B10" s="3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="51"/>
+      <c r="B13" s="3">
         <v>5</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="4">
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="4">
         <f>AVERAGE(DataExp1!U4:U13)</f>
         <v>2.4443213833989064</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L13" s="4">
         <f>AVERAGE(DataExp1!V4:V13)</f>
         <v>0.67972664412295081</v>
       </c>
-      <c r="M10" s="4">
+      <c r="M13" s="4">
         <v>77.092715069113893</v>
       </c>
-      <c r="N10" s="18">
+      <c r="N13" s="18">
         <v>4.1758142847234302E-2</v>
       </c>
-      <c r="O10" s="4">
+      <c r="O13" s="4">
         <f>AVERAGE(DataExp1!W4:W13)</f>
         <v>1.7100264072418159</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="45"/>
-      <c r="B11" s="3">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="51"/>
+      <c r="B14" s="3">
         <v>10</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="4">
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="4">
         <f>AVERAGE(DataExp1!X4:X13)</f>
         <v>2.0470536852897636</v>
       </c>
-      <c r="L11" s="4">
+      <c r="L14" s="4">
         <f>AVERAGE(DataExp1!Y4:Y13)</f>
         <v>0.42174105651815957</v>
       </c>
-      <c r="M11" s="4">
+      <c r="M14" s="4">
         <v>76.300224110581993</v>
       </c>
-      <c r="N11" s="18">
+      <c r="N14" s="18">
         <v>4.0673431385843499E-2</v>
       </c>
-      <c r="O11" s="4">
+      <c r="O14" s="4">
         <f>AVERAGE(DataExp1!Z4:Z13)</f>
         <v>1.7285686492919858</v>
       </c>
-      <c r="R11" t="s">
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="51"/>
+      <c r="B15" s="3">
+        <v>20</v>
+      </c>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="51"/>
+      <c r="B16" s="3">
+        <v>50</v>
+      </c>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="4"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" s="51"/>
+      <c r="B17" s="3">
+        <v>100</v>
+      </c>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="4"/>
+      <c r="R17" t="s">
         <v>12</v>
       </c>
-      <c r="S11" s="68" t="s">
+      <c r="S17" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="T11" t="s">
+      <c r="T17" t="s">
         <v>14</v>
       </c>
-      <c r="U11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="64" t="s">
+      <c r="U17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A18" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="65">
+      <c r="B18" s="32">
         <v>1</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="22">
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="22">
         <f>AVERAGE(DataExp1!AB4:AB13)</f>
         <v>2.0194039548285878</v>
       </c>
-      <c r="L12" s="22">
+      <c r="L18" s="22">
         <f>AVERAGE(DataExp1!AC4:AC13)</f>
         <v>0.37754673426285007</v>
       </c>
-      <c r="M12" s="22">
+      <c r="M18" s="22">
         <v>4.4845012962678503E-2</v>
       </c>
-      <c r="N12" s="23">
+      <c r="N18" s="23">
         <v>1.32241661098872E-4</v>
       </c>
-      <c r="O12" s="22">
+      <c r="O18" s="22">
         <f>AVERAGE(DataExp1!AD4:AD13)</f>
         <v>0.14992039203643773</v>
       </c>
-      <c r="Q12" t="s">
-        <v>50</v>
-      </c>
-      <c r="R12" s="15">
+      <c r="Q18" t="s">
+        <v>49</v>
+      </c>
+      <c r="R18" s="15">
         <v>420000000</v>
       </c>
-      <c r="S12" s="15">
+      <c r="S18" s="15">
         <v>56000000</v>
       </c>
-      <c r="T12" s="20">
+      <c r="T18" s="20">
         <v>4480000</v>
       </c>
-      <c r="U12" s="20">
+      <c r="U18" s="20">
         <v>35700000000</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="64"/>
-      <c r="B13" s="65">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A19" s="52"/>
+      <c r="B19" s="32">
         <v>3</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="22">
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="22">
         <f>AVERAGE(DataExp1!AE4:AE13)</f>
         <v>3.0323916470832399</v>
       </c>
-      <c r="L13" s="22">
+      <c r="L19" s="22">
         <f>AVERAGE(DataExp1!AF4:AF13)</f>
         <v>0.65287517616761293</v>
       </c>
-      <c r="M13" s="22">
+      <c r="M19" s="22">
         <v>4.4845012962678503E-2</v>
       </c>
-      <c r="N13" s="23">
+      <c r="N19" s="23">
         <v>1.3223489288371801E-4</v>
       </c>
-      <c r="O13" s="22">
+      <c r="O19" s="22">
         <f>AVERAGE(DataExp1!AG4:AG13)</f>
         <v>0.15916876792907658</v>
       </c>
-      <c r="Q13" t="s">
-        <v>52</v>
-      </c>
-      <c r="R13">
+      <c r="Q19" t="s">
+        <v>51</v>
+      </c>
+      <c r="R19">
         <v>87.94</v>
       </c>
-      <c r="S13" s="68">
+      <c r="S19" s="35">
         <v>150</v>
       </c>
-      <c r="T13">
+      <c r="T19">
         <v>183.7</v>
       </c>
-      <c r="U13" s="68">
+      <c r="U19" s="35">
         <v>65.86</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="64"/>
-      <c r="B14" s="65">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A20" s="52"/>
+      <c r="B20" s="32">
         <v>5</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="22">
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="22">
         <f>AVERAGE(DataExp1!AH4:AH13)</f>
         <v>3.0970657292831891</v>
       </c>
-      <c r="L14" s="22">
+      <c r="L20" s="22">
         <f>AVERAGE(DataExp1!AI4:AI13)</f>
         <v>0.65291309034907874</v>
       </c>
-      <c r="M14" s="22">
+      <c r="M20" s="22">
         <v>4.78425388880356E-2</v>
       </c>
-      <c r="N14" s="23">
+      <c r="N20" s="23">
         <v>1.33917051049755E-4</v>
       </c>
-      <c r="O14" s="22">
+      <c r="O20" s="22">
         <f>AVERAGE(DataExp1!AJ4:AJ13)</f>
         <v>0.18022336959838842</v>
       </c>
-      <c r="Q14" t="s">
-        <v>53</v>
-      </c>
-      <c r="R14">
+      <c r="Q20" t="s">
+        <v>52</v>
+      </c>
+      <c r="R20">
         <v>31997</v>
       </c>
-      <c r="S14" s="68">
+      <c r="S20" s="35">
         <v>470.42</v>
       </c>
-      <c r="T14">
+      <c r="T20">
         <v>229.6</v>
       </c>
-      <c r="U14">
+      <c r="U20">
         <v>10.15</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="64"/>
-      <c r="B15" s="65">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A21" s="52"/>
+      <c r="B21" s="32">
         <v>10</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="22">
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="22">
         <f>AVERAGE(DataExp1!AK4:AK13)</f>
         <v>3.0304601968108664</v>
       </c>
-      <c r="L15" s="22">
+      <c r="L21" s="22">
         <f>AVERAGE(DataExp1!AL4:AL13)</f>
         <v>0.65218430526407922</v>
       </c>
-      <c r="M15" s="22">
+      <c r="M21" s="22">
         <v>4.7875038888035598E-2</v>
       </c>
-      <c r="N15" s="23">
+      <c r="N21" s="23">
         <v>1.33921911090507E-4</v>
       </c>
-      <c r="O15" s="22">
+      <c r="O21" s="22">
         <f>AVERAGE(DataExp1!AM4:AM13)</f>
         <v>0.1679047107696528</v>
       </c>
-      <c r="Q15" t="s">
-        <v>51</v>
-      </c>
-      <c r="R15">
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A22" s="52"/>
+      <c r="B22" s="32">
+        <v>20</v>
+      </c>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="22"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A23" s="52"/>
+      <c r="B23" s="32">
+        <v>50</v>
+      </c>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="22"/>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A24" s="52"/>
+      <c r="B24" s="32">
+        <v>100</v>
+      </c>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="22"/>
+      <c r="Q24" t="s">
+        <v>50</v>
+      </c>
+      <c r="R24">
         <v>13.44</v>
       </c>
-      <c r="S15" s="68">
+      <c r="S24" s="35">
         <v>15.26</v>
       </c>
-      <c r="T15">
+      <c r="T24">
         <v>31.01</v>
       </c>
-      <c r="U15">
+      <c r="U24">
         <v>4.01</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="45" t="s">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A25" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B25" s="3">
         <v>1</v>
       </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="4">
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="4">
         <f>AVERAGE(DataExp1!AO4:AO13)</f>
         <v>34.552311810658352</v>
       </c>
-      <c r="L16" s="4">
+      <c r="L25" s="4">
         <f>AVERAGE(DataExp1!AP4:AP13)</f>
         <v>4.575032042937762</v>
       </c>
-      <c r="M16" s="4">
+      <c r="M25" s="4">
         <v>6.2164238822761397E-2</v>
       </c>
-      <c r="N16" s="18">
+      <c r="N25" s="18">
         <v>1.8093373899484099E-5</v>
       </c>
-      <c r="O16" s="4">
+      <c r="O25" s="4">
         <f>AVERAGE(DataExp1!AQ4:AQ13)</f>
         <v>1.6018030881881669</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="45"/>
-      <c r="B17" s="3">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A26" s="51"/>
+      <c r="B26" s="3">
         <v>3</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="4">
+      <c r="C26" s="51"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="4">
         <f>AVERAGE(DataExp1!AR4:AR14)</f>
         <v>1.8560190453181431</v>
       </c>
-      <c r="L17" s="4">
+      <c r="L26" s="4">
         <f>AVERAGE(DataExp1!AS4:AS14)</f>
         <v>0.34311024868513884</v>
       </c>
-      <c r="M17" s="4">
+      <c r="M26" s="4">
         <v>8.8175866468285097E-2</v>
       </c>
-      <c r="N17" s="18">
+      <c r="N26" s="18">
         <v>2.79669169855113E-5</v>
       </c>
-      <c r="O17" s="4">
+      <c r="O26" s="4">
         <f>AVERAGE(DataExp1!AT4:AT13)</f>
         <v>1.6889492511749222</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="45"/>
-      <c r="B18" s="3">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A27" s="51"/>
+      <c r="B27" s="3">
         <v>5</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="4">
+      <c r="C27" s="51"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
+      <c r="K27" s="4">
         <f>AVERAGE(DataExp1!AU4:AU13)</f>
         <v>1.9127433590347436</v>
       </c>
-      <c r="L18" s="4">
+      <c r="L27" s="4">
         <f>AVERAGE(DataExp1!AV4:AV13)</f>
         <v>0.35326132701310653</v>
       </c>
-      <c r="M18" s="4">
+      <c r="M27" s="4">
         <v>8.8376119113808799E-2</v>
       </c>
-      <c r="N18" s="18">
+      <c r="N27" s="18">
         <v>2.8023187480955202E-5</v>
       </c>
-      <c r="O18" s="4">
+      <c r="O27" s="4">
         <f>AVERAGE(DataExp1!AW4:AW13)</f>
         <v>1.7003351620265386</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="45"/>
-      <c r="B19" s="3">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A28" s="51"/>
+      <c r="B28" s="3">
         <v>10</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="4">
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="51"/>
+      <c r="K28" s="4">
         <f>AVERAGE(DataExp1!AX4:AX13)</f>
         <v>1.9259347567178799</v>
       </c>
-      <c r="L19" s="4">
+      <c r="L28" s="4">
         <f>AVERAGE(DataExp1!AY4:AY13)</f>
         <v>0.35326486945372448</v>
       </c>
-      <c r="M19" s="4">
+      <c r="M28" s="4">
         <v>8.81585941138084E-2</v>
       </c>
-      <c r="N19" s="18">
+      <c r="N28" s="18">
         <v>2.7971865110220399E-5</v>
       </c>
-      <c r="O19" s="4">
+      <c r="O28" s="4">
         <f>AVERAGE(DataExp1!AZ4:AZ13)</f>
         <v>1.6923342704772899</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="43" t="s">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A29" s="51"/>
+      <c r="B29" s="3">
+        <v>20</v>
+      </c>
+      <c r="C29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="51"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="4"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A30" s="51"/>
+      <c r="B30" s="3">
+        <v>50</v>
+      </c>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="4"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A31" s="51"/>
+      <c r="B31" s="3">
+        <v>100</v>
+      </c>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="4"/>
+    </row>
+    <row r="32" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B32" s="3">
         <v>1</v>
       </c>
-      <c r="C20" s="45" t="s">
+      <c r="C32" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="45">
+      <c r="D32" s="51">
         <v>128</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E32" s="51">
         <v>128</v>
       </c>
-      <c r="F20" s="58">
+      <c r="F32" s="58">
         <v>1.1200000000000001</v>
       </c>
-      <c r="G20" s="45">
+      <c r="G32" s="51">
         <v>1</v>
       </c>
-      <c r="H20" s="45">
+      <c r="H32" s="51">
         <v>1</v>
       </c>
-      <c r="I20" s="45">
+      <c r="I32" s="51">
         <v>128</v>
       </c>
-      <c r="J20" s="45">
+      <c r="J32" s="51">
         <v>128</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K32" s="3">
         <f>AVERAGE(DataExp1!B18:B27)</f>
         <v>65.766764930924992</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L32" s="3">
         <f>AVERAGE(DataExp1!C18:C27)</f>
         <v>6.4421864526712369</v>
       </c>
-      <c r="M20" s="4">
+      <c r="M32" s="4">
         <v>1035.7896129462799</v>
       </c>
-      <c r="N20" s="18">
+      <c r="N32" s="18">
         <v>5.95739397649482E-3</v>
       </c>
-      <c r="O20" s="4">
+      <c r="O32" s="4">
         <v>12.759822845458901</v>
       </c>
-      <c r="Q20" s="66" t="s">
-        <v>39</v>
-      </c>
-      <c r="R20" s="69" t="s">
+      <c r="Q32" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="R32" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="S32" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="S20" s="70" t="s">
-        <v>44</v>
-      </c>
-      <c r="T20" s="69" t="s">
+      <c r="T32" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="U32" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="V32" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="U20" s="69" t="s">
-        <v>46</v>
-      </c>
-      <c r="V20" s="69" t="s">
+      <c r="W32" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="W20" s="69" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A21" s="43"/>
-      <c r="B21" s="3">
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" s="57"/>
+      <c r="B33" s="3">
         <v>3</v>
       </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="3">
+      <c r="C33" s="51"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="51"/>
+      <c r="K33" s="3">
         <f>AVERAGE(DataExp1!E18:E27)</f>
         <v>38.626208042487967</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L33" s="3">
         <f>AVERAGE(DataExp1!F18:F27)</f>
         <v>4.0285688713895276</v>
       </c>
-      <c r="M21" s="4">
+      <c r="M33" s="4">
         <v>1685.75088883886</v>
       </c>
-      <c r="N21" s="18">
+      <c r="N33" s="18">
         <v>1.1219430173259401E-2</v>
       </c>
-      <c r="O21" s="4">
+      <c r="O33" s="4">
         <v>12.8247382640838</v>
       </c>
-      <c r="Q21" t="s">
-        <v>40</v>
-      </c>
-      <c r="R21" s="7">
-        <f>M23/M27</f>
-        <v>6.1137183361576284</v>
-      </c>
-      <c r="S21" s="68">
-        <f>N23/N27</f>
-        <v>4.5301443779314346E-2</v>
-      </c>
-      <c r="T21" s="68">
-        <f>$R$12/$S$12</f>
-        <v>7.5</v>
-      </c>
-      <c r="U21" s="68">
-        <f>$R$13/$S$13</f>
-        <v>0.5862666666666666</v>
-      </c>
-      <c r="V21" s="68">
-        <f>$R$14/$S$14</f>
-        <v>68.017941414055528</v>
-      </c>
-      <c r="W21" s="68">
-        <f>$R$15/$S$15</f>
-        <v>0.88073394495412838</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="43"/>
-      <c r="B22" s="3">
+      <c r="Q33" t="s">
+        <v>39</v>
+      </c>
+      <c r="R33" s="7"/>
+      <c r="T33" s="35"/>
+      <c r="U33" s="35"/>
+      <c r="V33" s="35"/>
+      <c r="W33" s="35"/>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A34" s="57"/>
+      <c r="B34" s="3">
         <v>5</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
-      <c r="K22" s="3">
+      <c r="C34" s="51"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="51"/>
+      <c r="I34" s="51"/>
+      <c r="J34" s="51"/>
+      <c r="K34" s="3">
         <f>AVERAGE(DataExp1!H18:H27)</f>
         <v>19.080341123339618</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L34" s="3">
         <f>AVERAGE(DataExp1!I18:I27)</f>
         <v>2.3385643979886401</v>
       </c>
-      <c r="M22" s="4">
+      <c r="M34" s="4">
         <v>1984.11291473147</v>
       </c>
-      <c r="N22" s="18">
+      <c r="N34" s="18">
         <v>1.31972764989438E-2</v>
       </c>
-      <c r="O22" s="4">
+      <c r="O34" s="4">
         <v>12.9234986305236</v>
       </c>
-      <c r="Q22" t="s">
-        <v>41</v>
-      </c>
-      <c r="R22" s="7">
-        <f>M23/M31</f>
-        <v>22700.335369729182</v>
-      </c>
-      <c r="S22" s="68">
-        <f>N23/N31</f>
-        <v>288.4134960366265</v>
-      </c>
-      <c r="T22" s="68">
-        <f>$R$12/$T$12</f>
-        <v>93.75</v>
-      </c>
-      <c r="U22" s="68">
-        <f>$R$13/$T$13</f>
-        <v>0.47871529667936857</v>
-      </c>
-      <c r="V22" s="68">
-        <f>$R$14/$T$14</f>
-        <v>139.35975609756099</v>
-      </c>
-      <c r="W22" s="68">
-        <f>$R$15/$T$15</f>
-        <v>0.43340857787810377</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" s="43"/>
-      <c r="B23" s="3">
+      <c r="Q34" t="s">
+        <v>40</v>
+      </c>
+      <c r="R34" s="7"/>
+      <c r="T34" s="35"/>
+      <c r="U34" s="35"/>
+      <c r="V34" s="35"/>
+      <c r="W34" s="35"/>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A35" s="57"/>
+      <c r="B35" s="3">
         <v>10</v>
       </c>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="3">
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
+      <c r="J35" s="51"/>
+      <c r="K35" s="3">
         <f>AVERAGE(DataExp1!K18:K27)</f>
         <v>4.4322830974230261</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L35" s="3">
         <f>AVERAGE(DataExp1!L18:L27)</f>
         <v>0.72280862455750228</v>
       </c>
-      <c r="M23" s="4">
+      <c r="M35" s="4">
         <v>2183.88837946289</v>
       </c>
-      <c r="N23" s="18">
+      <c r="N35" s="18">
         <v>1.4378549136786E-2</v>
       </c>
-      <c r="O23" s="4">
+      <c r="O35" s="4">
         <v>14.266155481338499</v>
       </c>
-      <c r="Q23" t="s">
-        <v>42</v>
-      </c>
-      <c r="R23" s="7">
-        <f>M23/M35</f>
-        <v>6450.3873277040848</v>
-      </c>
-      <c r="S23" s="68">
-        <f>N23/N35</f>
-        <v>88.805774648333127</v>
-      </c>
-      <c r="T23" s="68">
-        <f>$R$12/$U$12</f>
-        <v>1.1764705882352941E-2</v>
-      </c>
-      <c r="U23" s="68">
-        <f>$R$13/$U$13</f>
-        <v>1.3352566049195262</v>
-      </c>
-      <c r="V23" s="68">
-        <f>$R$14/$U$14</f>
-        <v>3152.4137931034484</v>
-      </c>
-      <c r="W23" s="68">
-        <f>$R$15/$U$15</f>
-        <v>3.3516209476309227</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" s="42" t="s">
+      <c r="R35" s="7"/>
+      <c r="T35" s="35"/>
+      <c r="U35" s="35"/>
+      <c r="V35" s="35"/>
+      <c r="W35" s="35"/>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A36" s="57"/>
+      <c r="B36" s="3">
+        <v>20</v>
+      </c>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
+      <c r="J36" s="51"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="4"/>
+      <c r="R36" s="7"/>
+      <c r="T36" s="35"/>
+      <c r="U36" s="35"/>
+      <c r="V36" s="35"/>
+      <c r="W36" s="35"/>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A37" s="57"/>
+      <c r="B37" s="3">
+        <v>50</v>
+      </c>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="51"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="4"/>
+      <c r="R37" s="7"/>
+      <c r="T37" s="35"/>
+      <c r="U37" s="35"/>
+      <c r="V37" s="35"/>
+      <c r="W37" s="35"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A38" s="57"/>
+      <c r="B38" s="3">
+        <v>100</v>
+      </c>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="51"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="4"/>
+      <c r="R38" s="7"/>
+      <c r="T38" s="35"/>
+      <c r="U38" s="35"/>
+      <c r="V38" s="35"/>
+      <c r="W38" s="35"/>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A39" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B39" s="9">
         <v>1</v>
       </c>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="9">
+      <c r="C39" s="51"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="51"/>
+      <c r="J39" s="51"/>
+      <c r="K39" s="9">
         <f>AVERAGE(DataExp1!O18:O27)</f>
         <v>157.51141235842792</v>
       </c>
-      <c r="L24" s="9">
+      <c r="L39" s="9">
         <f>AVERAGE(DataExp1!P18:P27)</f>
         <v>14.53758931210613</v>
       </c>
-      <c r="M24" s="14">
+      <c r="M39" s="14">
         <v>140.34726294628899</v>
       </c>
-      <c r="N24" s="19">
+      <c r="N39" s="19">
         <v>8.6437071411442801E-2</v>
       </c>
-      <c r="O24" s="14">
+      <c r="O39" s="14">
         <v>12.795346260070801</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A25" s="42"/>
-      <c r="B25" s="9">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A40" s="56"/>
+      <c r="B40" s="9">
         <v>3</v>
       </c>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
-      <c r="K25" s="9">
+      <c r="C40" s="51"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="51"/>
+      <c r="I40" s="51"/>
+      <c r="J40" s="51"/>
+      <c r="K40" s="9">
         <f>AVERAGE(DataExp1!R18:R27)</f>
         <v>5.370568162007002</v>
       </c>
-      <c r="L25" s="9">
+      <c r="L40" s="9">
         <f>AVERAGE(DataExp1!S18:S27)</f>
         <v>0.75080168785316326</v>
       </c>
-      <c r="M25" s="14">
+      <c r="M40" s="14">
         <v>336.02303883887203</v>
       </c>
-      <c r="N25" s="19">
+      <c r="N40" s="19">
         <v>0.307117723102377</v>
       </c>
-      <c r="O25" s="14">
+      <c r="O40" s="14">
         <v>12.8078730106353</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A26" s="42"/>
-      <c r="B26" s="9">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A41" s="56"/>
+      <c r="B41" s="9">
         <v>5</v>
       </c>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="9">
+      <c r="C41" s="51"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="51"/>
+      <c r="K41" s="9">
         <f>AVERAGE(DataExp1!U18:U27)</f>
         <v>6.130019567236074</v>
       </c>
-      <c r="L26" s="9">
+      <c r="L41" s="9">
         <f>AVERAGE(DataExp1!V18:V27)</f>
         <v>0.89446390885782068</v>
       </c>
-      <c r="M26" s="14">
+      <c r="M41" s="14">
         <v>351.22411473145002</v>
       </c>
-      <c r="N26" s="19">
+      <c r="N41" s="19">
         <v>0.31561186164217703</v>
       </c>
-      <c r="O26" s="14">
+      <c r="O41" s="14">
         <v>26.1628239154815</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A27" s="42"/>
-      <c r="B27" s="9">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A42" s="56"/>
+      <c r="B42" s="9">
         <v>10</v>
       </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="9">
+      <c r="C42" s="51"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="55"/>
+      <c r="G42" s="51"/>
+      <c r="H42" s="51"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="51"/>
+      <c r="K42" s="9">
         <f>AVERAGE(DataExp1!X18:X27)</f>
         <v>6.2926813963615427</v>
       </c>
-      <c r="L27" s="9">
+      <c r="L42" s="9">
         <f>AVERAGE(DataExp1!Y18:Y27)</f>
         <v>0.87768383162899821</v>
       </c>
-      <c r="M27" s="14">
+      <c r="M42" s="14">
         <v>357.21115357032102</v>
       </c>
-      <c r="N27" s="19">
+      <c r="N42" s="19">
         <v>0.31739714978690298</v>
       </c>
-      <c r="O27" s="14">
+      <c r="O42" s="14">
         <v>26.592686176299999</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A28" s="43" t="s">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A43" s="56"/>
+      <c r="B43" s="9">
+        <v>20</v>
+      </c>
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="51"/>
+      <c r="J43" s="51"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="14"/>
+      <c r="N43" s="19"/>
+      <c r="O43" s="14"/>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A44" s="56"/>
+      <c r="B44" s="9">
+        <v>50</v>
+      </c>
+      <c r="C44" s="51"/>
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="51"/>
+      <c r="I44" s="51"/>
+      <c r="J44" s="51"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="14"/>
+      <c r="N44" s="19"/>
+      <c r="O44" s="14"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A45" s="56"/>
+      <c r="B45" s="9">
+        <v>100</v>
+      </c>
+      <c r="C45" s="51"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="51"/>
+      <c r="H45" s="51"/>
+      <c r="I45" s="51"/>
+      <c r="J45" s="51"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="14"/>
+      <c r="N45" s="19"/>
+      <c r="O45" s="9"/>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A46" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B46" s="32">
         <v>1</v>
       </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="24">
+      <c r="C46" s="51"/>
+      <c r="D46" s="51"/>
+      <c r="E46" s="51"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="51"/>
+      <c r="I46" s="51"/>
+      <c r="J46" s="51"/>
+      <c r="K46" s="22">
         <f>AVERAGE(DataExp1!AB18:AB27)</f>
         <v>13.2679396369752</v>
       </c>
-      <c r="L28" s="24">
+      <c r="L46" s="22">
         <f>AVERAGE(DataExp1!AC18:AC27)</f>
         <v>1.5714615342167302</v>
       </c>
-      <c r="M28" s="24">
+      <c r="M46" s="22">
         <v>8.3970028801535798E-2</v>
       </c>
-      <c r="N28" s="25">
+      <c r="N46" s="23">
         <v>3.6284487521842497E-5</v>
       </c>
-      <c r="O28" s="24">
+      <c r="O46" s="22">
         <v>0.30750107765197698</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A29" s="43"/>
-      <c r="B29" s="3">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A47" s="65"/>
+      <c r="B47" s="32">
         <v>3</v>
       </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="45"/>
-      <c r="K29" s="24">
+      <c r="C47" s="51"/>
+      <c r="D47" s="51"/>
+      <c r="E47" s="51"/>
+      <c r="F47" s="55"/>
+      <c r="G47" s="51"/>
+      <c r="H47" s="51"/>
+      <c r="I47" s="51"/>
+      <c r="J47" s="51"/>
+      <c r="K47" s="22">
         <f>AVERAGE(DataExp1!AE18:AE27)</f>
         <v>1.8847515193214188</v>
       </c>
-      <c r="L29" s="24">
+      <c r="L47" s="22">
         <f>AVERAGE(DataExp1!AF18:AF27)</f>
         <v>0.44815003866496461</v>
       </c>
-      <c r="M29" s="24">
+      <c r="M47" s="22">
         <v>9.5270057603071695E-2</v>
       </c>
-      <c r="N29" s="25">
+      <c r="N47" s="23">
         <v>4.9660843797880298E-5</v>
       </c>
-      <c r="O29" s="24">
+      <c r="O47" s="22">
         <v>0.36651349067687899</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A30" s="43"/>
-      <c r="B30" s="3">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A48" s="65"/>
+      <c r="B48" s="32">
         <v>5</v>
       </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45"/>
-      <c r="K30" s="24">
+      <c r="C48" s="51"/>
+      <c r="D48" s="51"/>
+      <c r="E48" s="51"/>
+      <c r="F48" s="55"/>
+      <c r="G48" s="51"/>
+      <c r="H48" s="51"/>
+      <c r="I48" s="51"/>
+      <c r="J48" s="51"/>
+      <c r="K48" s="22">
         <f>AVERAGE(DataExp1!AH18:AH27)</f>
         <v>1.9167287224860321</v>
       </c>
-      <c r="L30" s="24">
+      <c r="L48" s="22">
         <f>AVERAGE(DataExp1!AI18:AI27)</f>
         <v>0.473754446095489</v>
       </c>
-      <c r="M30" s="24">
+      <c r="M48" s="22">
         <v>9.6327586404607604E-2</v>
       </c>
-      <c r="N30" s="25">
+      <c r="N48" s="23">
         <v>4.9897249721340198E-5</v>
       </c>
-      <c r="O30" s="24">
+      <c r="O48" s="22">
         <v>0.397212743759155</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A31" s="43"/>
-      <c r="B31" s="10">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="65"/>
+      <c r="B49" s="66">
         <v>10</v>
       </c>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="45"/>
-      <c r="K31" s="24">
+      <c r="C49" s="51"/>
+      <c r="D49" s="51"/>
+      <c r="E49" s="51"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="51"/>
+      <c r="H49" s="51"/>
+      <c r="I49" s="51"/>
+      <c r="J49" s="51"/>
+      <c r="K49" s="22">
         <f>AVERAGE(DataExp1!AK18:AK27)</f>
         <v>1.9152230126798291</v>
       </c>
-      <c r="L31" s="24">
+      <c r="L49" s="22">
         <f>AVERAGE(DataExp1!AL18:AL27)</f>
         <v>0.473754446095489</v>
       </c>
-      <c r="M31" s="24">
+      <c r="M49" s="22">
         <v>9.6205115206143499E-2</v>
       </c>
-      <c r="N31" s="25">
+      <c r="N49" s="23">
         <v>4.9853940035316602E-5</v>
       </c>
-      <c r="O31" s="24">
+      <c r="O49" s="22">
         <v>0.36162972450256298</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A32" s="42" t="s">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="65"/>
+      <c r="B50" s="66">
+        <v>20</v>
+      </c>
+      <c r="C50" s="51"/>
+      <c r="D50" s="51"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="55"/>
+      <c r="G50" s="51"/>
+      <c r="H50" s="51"/>
+      <c r="I50" s="51"/>
+      <c r="J50" s="51"/>
+      <c r="K50" s="22"/>
+      <c r="L50" s="22"/>
+      <c r="M50" s="22"/>
+      <c r="N50" s="23"/>
+      <c r="O50" s="22"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="65"/>
+      <c r="B51" s="66">
+        <v>50</v>
+      </c>
+      <c r="C51" s="51"/>
+      <c r="D51" s="51"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="55"/>
+      <c r="G51" s="51"/>
+      <c r="H51" s="51"/>
+      <c r="I51" s="51"/>
+      <c r="J51" s="51"/>
+      <c r="K51" s="22"/>
+      <c r="L51" s="22"/>
+      <c r="M51" s="22"/>
+      <c r="N51" s="23"/>
+      <c r="O51" s="22"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="65"/>
+      <c r="B52" s="66">
+        <v>100</v>
+      </c>
+      <c r="C52" s="51"/>
+      <c r="D52" s="51"/>
+      <c r="E52" s="51"/>
+      <c r="F52" s="55"/>
+      <c r="G52" s="51"/>
+      <c r="H52" s="51"/>
+      <c r="I52" s="51"/>
+      <c r="J52" s="51"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="32"/>
+      <c r="M52" s="22"/>
+      <c r="N52" s="23"/>
+      <c r="O52" s="32"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B53" s="9">
         <v>1</v>
       </c>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="14">
+      <c r="C53" s="51"/>
+      <c r="D53" s="51"/>
+      <c r="E53" s="51"/>
+      <c r="F53" s="55"/>
+      <c r="G53" s="51"/>
+      <c r="H53" s="51"/>
+      <c r="I53" s="51"/>
+      <c r="J53" s="51"/>
+      <c r="K53" s="14">
         <f>AVERAGE(DataExp1!AO18:AO27)</f>
         <v>59.79535904859479</v>
       </c>
-      <c r="L32" s="14">
+      <c r="L53" s="14">
         <f>AVERAGE(DataExp1!AP18:AP27)</f>
         <v>5.6632343066267472</v>
       </c>
-      <c r="M32" s="14">
+      <c r="M53" s="14">
         <v>0.22719339629037999</v>
       </c>
-      <c r="N32" s="19">
+      <c r="N53" s="19">
         <v>9.04054493084061E-5</v>
       </c>
-      <c r="O32" s="14">
+      <c r="O53" s="14">
         <v>12.858536243438699</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="42"/>
-      <c r="B33" s="9">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="56"/>
+      <c r="B54" s="9">
         <v>3</v>
       </c>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="59"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="14">
+      <c r="C54" s="51"/>
+      <c r="D54" s="51"/>
+      <c r="E54" s="51"/>
+      <c r="F54" s="55"/>
+      <c r="G54" s="51"/>
+      <c r="H54" s="51"/>
+      <c r="I54" s="51"/>
+      <c r="J54" s="51"/>
+      <c r="K54" s="14">
         <f>AVERAGE(DataExp1!AR18:AR27)</f>
         <v>4.1994209587286191</v>
       </c>
-      <c r="L33" s="14">
+      <c r="L54" s="14">
         <f>AVERAGE(DataExp1!AS18:AS27)</f>
         <v>0.76532657737815013</v>
       </c>
-      <c r="M33" s="14">
+      <c r="M54" s="14">
         <v>0.334194763871137</v>
       </c>
-      <c r="N33" s="19">
+      <c r="N54" s="19">
         <v>1.6040279311206501E-4</v>
       </c>
-      <c r="O33" s="14">
+      <c r="O54" s="14">
         <v>12.8858025074005</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="42"/>
-      <c r="B34" s="9">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="56"/>
+      <c r="B55" s="9">
         <v>5</v>
       </c>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="59"/>
-      <c r="G34" s="45"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="14">
+      <c r="C55" s="51"/>
+      <c r="D55" s="51"/>
+      <c r="E55" s="51"/>
+      <c r="F55" s="55"/>
+      <c r="G55" s="51"/>
+      <c r="H55" s="51"/>
+      <c r="I55" s="51"/>
+      <c r="J55" s="51"/>
+      <c r="K55" s="14">
         <f>AVERAGE(DataExp1!AU18:AU27)</f>
         <v>4.4246201292478027</v>
       </c>
-      <c r="L34" s="14">
+      <c r="L55" s="14">
         <f>AVERAGE(DataExp1!AV18:AV27)</f>
         <v>0.76976707295684066</v>
       </c>
-      <c r="M34" s="14">
+      <c r="M55" s="14">
         <v>0.33717530645189397</v>
       </c>
-      <c r="N34" s="19">
+      <c r="N55" s="19">
         <v>1.6153492724404301E-4</v>
       </c>
-      <c r="O34" s="14">
+      <c r="O55" s="14">
         <v>13.6702349185943</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="42"/>
-      <c r="B35" s="9">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="56"/>
+      <c r="B56" s="9">
         <v>10</v>
       </c>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="45"/>
-      <c r="H35" s="45"/>
-      <c r="I35" s="45"/>
-      <c r="J35" s="45"/>
-      <c r="K35" s="14">
+      <c r="C56" s="51"/>
+      <c r="D56" s="51"/>
+      <c r="E56" s="51"/>
+      <c r="F56" s="55"/>
+      <c r="G56" s="51"/>
+      <c r="H56" s="51"/>
+      <c r="I56" s="51"/>
+      <c r="J56" s="51"/>
+      <c r="K56" s="14">
         <f>AVERAGE(DataExp1!AX18:AX27)</f>
         <v>4.1938757256751718</v>
       </c>
-      <c r="L35" s="14">
+      <c r="L56" s="14">
         <f>AVERAGE(DataExp1!AY18:AY27)</f>
         <v>0.76280764413276991</v>
       </c>
-      <c r="M35" s="14">
+      <c r="M56" s="14">
         <v>0.33856701443077702</v>
       </c>
-      <c r="N35" s="19">
+      <c r="N56" s="19">
         <v>1.6191006940398199E-4</v>
       </c>
-      <c r="O35" s="14">
+      <c r="O56" s="14">
         <v>35.664546728134098</v>
       </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="56"/>
+      <c r="B57" s="9">
+        <v>20</v>
+      </c>
+      <c r="C57" s="51"/>
+      <c r="D57" s="51"/>
+      <c r="E57" s="51"/>
+      <c r="F57" s="55"/>
+      <c r="G57" s="51"/>
+      <c r="H57" s="51"/>
+      <c r="I57" s="51"/>
+      <c r="J57" s="51"/>
+      <c r="K57" s="14"/>
+      <c r="L57" s="14"/>
+      <c r="M57" s="14"/>
+      <c r="N57" s="19"/>
+      <c r="O57" s="14"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="56"/>
+      <c r="B58" s="9">
+        <v>50</v>
+      </c>
+      <c r="C58" s="51"/>
+      <c r="D58" s="51"/>
+      <c r="E58" s="51"/>
+      <c r="F58" s="55"/>
+      <c r="G58" s="51"/>
+      <c r="H58" s="51"/>
+      <c r="I58" s="51"/>
+      <c r="J58" s="51"/>
+      <c r="K58" s="14"/>
+      <c r="L58" s="14"/>
+      <c r="M58" s="14"/>
+      <c r="N58" s="19"/>
+      <c r="O58" s="14"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="56"/>
+      <c r="B59" s="9">
+        <v>100</v>
+      </c>
+      <c r="C59" s="51"/>
+      <c r="D59" s="51"/>
+      <c r="E59" s="51"/>
+      <c r="F59" s="53"/>
+      <c r="G59" s="51"/>
+      <c r="H59" s="51"/>
+      <c r="I59" s="51"/>
+      <c r="J59" s="51"/>
+      <c r="K59" s="9"/>
+      <c r="L59" s="9"/>
+      <c r="M59" s="14"/>
+      <c r="N59" s="19"/>
+      <c r="O59" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A39:A45"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="I4:I31"/>
+    <mergeCell ref="J4:J31"/>
+    <mergeCell ref="A32:A38"/>
+    <mergeCell ref="C32:C59"/>
+    <mergeCell ref="D32:D59"/>
+    <mergeCell ref="E32:E59"/>
+    <mergeCell ref="G32:G59"/>
+    <mergeCell ref="H32:H59"/>
+    <mergeCell ref="I32:I59"/>
+    <mergeCell ref="J32:J59"/>
+    <mergeCell ref="F32:F59"/>
     <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="C4:C19"/>
-    <mergeCell ref="D4:D19"/>
-    <mergeCell ref="E4:E19"/>
-    <mergeCell ref="G4:G19"/>
-    <mergeCell ref="H4:H19"/>
-    <mergeCell ref="F4:F19"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A28:A31"/>
-    <mergeCell ref="A32:A35"/>
-    <mergeCell ref="I4:I19"/>
-    <mergeCell ref="J4:J19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="C20:C35"/>
-    <mergeCell ref="D20:D35"/>
-    <mergeCell ref="E20:E35"/>
-    <mergeCell ref="G20:G35"/>
-    <mergeCell ref="H20:H35"/>
-    <mergeCell ref="I20:I35"/>
-    <mergeCell ref="J20:J35"/>
-    <mergeCell ref="F20:F35"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="C4:C31"/>
+    <mergeCell ref="D4:D31"/>
+    <mergeCell ref="E4:E31"/>
+    <mergeCell ref="G4:G31"/>
+    <mergeCell ref="H4:H31"/>
+    <mergeCell ref="F4:F31"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5539,6 +5960,872 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CACBC33-D91B-42B9-AA21-9BA30A2BE58A}">
+  <dimension ref="A1:Z31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+    </row>
+    <row r="3" spans="1:26" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="11">
+        <v>1</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="53">
+        <v>66</v>
+      </c>
+      <c r="E4" s="53">
+        <v>66</v>
+      </c>
+      <c r="F4" s="54">
+        <v>13000</v>
+      </c>
+      <c r="G4" s="53">
+        <v>1</v>
+      </c>
+      <c r="H4" s="53">
+        <v>1</v>
+      </c>
+      <c r="I4" s="53">
+        <v>66</v>
+      </c>
+      <c r="J4" s="53">
+        <v>66</v>
+      </c>
+      <c r="K4" s="5">
+        <f>AVERAGE(DataExp1!B4:B13)</f>
+        <v>23.838309041284862</v>
+      </c>
+      <c r="L4" s="5">
+        <f>AVERAGE(DataExp1!C4:C13)</f>
+        <v>3.2827532251076272</v>
+      </c>
+      <c r="M4" s="5">
+        <v>280.77705301382201</v>
+      </c>
+      <c r="N4" s="17">
+        <v>1.24324175218449E-3</v>
+      </c>
+      <c r="O4" s="14">
+        <f>AVERAGE(DataExp1!D4:D13)</f>
+        <v>1.6688517570495538</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="50"/>
+      <c r="B5" s="6">
+        <v>3</v>
+      </c>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="5">
+        <f>AVERAGE(DataExp1!E4:E13)</f>
+        <v>11.070752653739017</v>
+      </c>
+      <c r="L5" s="5">
+        <f>AVERAGE(DataExp1!F4:F13)</f>
+        <v>1.6712838772969871</v>
+      </c>
+      <c r="M5" s="5">
+        <v>391.23075904146799</v>
+      </c>
+      <c r="N5" s="17">
+        <v>1.8368430572894799E-3</v>
+      </c>
+      <c r="O5" s="14">
+        <f>AVERAGE(DataExp1!G4:G13)</f>
+        <v>1.6848387241363478</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="50"/>
+      <c r="B6" s="6">
+        <v>5</v>
+      </c>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="5">
+        <f>AVERAGE(DataExp1!H4:H13)</f>
+        <v>4.7480516396353174</v>
+      </c>
+      <c r="L6" s="5">
+        <f>AVERAGE(DataExp1!I4:I13)</f>
+        <v>0.82681097952909732</v>
+      </c>
+      <c r="M6" s="5">
+        <v>417.59086506911302</v>
+      </c>
+      <c r="N6" s="17">
+        <v>1.8680991323063701E-3</v>
+      </c>
+      <c r="O6" s="14">
+        <f>AVERAGE(DataExp1!J4:J13)</f>
+        <v>1.7160061359405478</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="50"/>
+      <c r="B7" s="6">
+        <v>10</v>
+      </c>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="5">
+        <f>AVERAGE(DataExp1!K4:K13)</f>
+        <v>0.84932664663156276</v>
+      </c>
+      <c r="L7" s="5">
+        <f>AVERAGE(DataExp1!L4:L13)</f>
+        <v>0.24563346801399702</v>
+      </c>
+      <c r="M7" s="5">
+        <v>427.43972841419099</v>
+      </c>
+      <c r="N7" s="17">
+        <v>1.90857404909223E-3</v>
+      </c>
+      <c r="O7" s="14">
+        <f>AVERAGE(DataExp1!M1:M10)</f>
+        <v>1.740799522399898</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="50"/>
+      <c r="B8" s="6">
+        <v>20</v>
+      </c>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="14"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="50"/>
+      <c r="B9" s="6">
+        <v>50</v>
+      </c>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="14"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="50"/>
+      <c r="B10" s="6">
+        <v>100</v>
+      </c>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="14"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1</v>
+      </c>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="4">
+        <f>AVERAGE(DataExp1!O4:O13)</f>
+        <v>49.821904185231844</v>
+      </c>
+      <c r="L11" s="4">
+        <f>AVERAGE(DataExp1!P4:P13)</f>
+        <v>6.6901005257882433</v>
+      </c>
+      <c r="M11" s="4">
+        <v>38.8018530138228</v>
+      </c>
+      <c r="N11" s="18">
+        <v>1.8341564911519399E-2</v>
+      </c>
+      <c r="O11" s="4">
+        <f>AVERAGE(DataExp1!Q4:Q13)</f>
+        <v>1.6223374366760202</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="51"/>
+      <c r="B12" s="3">
+        <v>3</v>
+      </c>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="4">
+        <f>AVERAGE(DataExp1!R4:R13)</f>
+        <v>2.2585080679270888</v>
+      </c>
+      <c r="L12" s="4">
+        <f>AVERAGE(DataExp1!S4:S13)</f>
+        <v>0.46312458447019578</v>
+      </c>
+      <c r="M12" s="4">
+        <v>73.281259041468303</v>
+      </c>
+      <c r="N12" s="18">
+        <v>3.8957965924184199E-2</v>
+      </c>
+      <c r="O12" s="4">
+        <f>AVERAGE(DataExp1!T4:T13)</f>
+        <v>1.6586509227752639</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="51"/>
+      <c r="B13" s="3">
+        <v>5</v>
+      </c>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="4">
+        <f>AVERAGE(DataExp1!U4:U13)</f>
+        <v>2.4443213833989064</v>
+      </c>
+      <c r="L13" s="4">
+        <f>AVERAGE(DataExp1!V4:V13)</f>
+        <v>0.67972664412295081</v>
+      </c>
+      <c r="M13" s="4">
+        <v>77.092715069113893</v>
+      </c>
+      <c r="N13" s="18">
+        <v>4.1758142847234302E-2</v>
+      </c>
+      <c r="O13" s="4">
+        <f>AVERAGE(DataExp1!W4:W13)</f>
+        <v>1.7100264072418159</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="51"/>
+      <c r="B14" s="3">
+        <v>10</v>
+      </c>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="4">
+        <f>AVERAGE(DataExp1!X4:X13)</f>
+        <v>2.0470536852897636</v>
+      </c>
+      <c r="L14" s="4">
+        <f>AVERAGE(DataExp1!Y4:Y13)</f>
+        <v>0.42174105651815957</v>
+      </c>
+      <c r="M14" s="4">
+        <v>76.300224110581993</v>
+      </c>
+      <c r="N14" s="18">
+        <v>4.0673431385843499E-2</v>
+      </c>
+      <c r="O14" s="4">
+        <f>AVERAGE(DataExp1!Z4:Z13)</f>
+        <v>1.7285686492919858</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="51"/>
+      <c r="B15" s="3">
+        <v>20</v>
+      </c>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="51"/>
+      <c r="B16" s="3">
+        <v>50</v>
+      </c>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="4"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="51"/>
+      <c r="B17" s="3">
+        <v>100</v>
+      </c>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="4"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="32">
+        <v>1</v>
+      </c>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="22">
+        <f>AVERAGE(DataExp1!AB4:AB13)</f>
+        <v>2.0194039548285878</v>
+      </c>
+      <c r="L18" s="22">
+        <f>AVERAGE(DataExp1!AC4:AC13)</f>
+        <v>0.37754673426285007</v>
+      </c>
+      <c r="M18" s="22">
+        <v>4.4845012962678503E-2</v>
+      </c>
+      <c r="N18" s="23">
+        <v>1.32241661098872E-4</v>
+      </c>
+      <c r="O18" s="22">
+        <f>AVERAGE(DataExp1!AD4:AD13)</f>
+        <v>0.14992039203643773</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="52"/>
+      <c r="B19" s="32">
+        <v>3</v>
+      </c>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="22">
+        <f>AVERAGE(DataExp1!AE4:AE13)</f>
+        <v>3.0323916470832399</v>
+      </c>
+      <c r="L19" s="22">
+        <f>AVERAGE(DataExp1!AF4:AF13)</f>
+        <v>0.65287517616761293</v>
+      </c>
+      <c r="M19" s="22">
+        <v>4.4845012962678503E-2</v>
+      </c>
+      <c r="N19" s="23">
+        <v>1.3223489288371801E-4</v>
+      </c>
+      <c r="O19" s="22">
+        <f>AVERAGE(DataExp1!AG4:AG13)</f>
+        <v>0.15916876792907658</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="52"/>
+      <c r="B20" s="32">
+        <v>5</v>
+      </c>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="22">
+        <f>AVERAGE(DataExp1!AH4:AH13)</f>
+        <v>3.0970657292831891</v>
+      </c>
+      <c r="L20" s="22">
+        <f>AVERAGE(DataExp1!AI4:AI13)</f>
+        <v>0.65291309034907874</v>
+      </c>
+      <c r="M20" s="22">
+        <v>4.78425388880356E-2</v>
+      </c>
+      <c r="N20" s="23">
+        <v>1.33917051049755E-4</v>
+      </c>
+      <c r="O20" s="22">
+        <f>AVERAGE(DataExp1!AJ4:AJ13)</f>
+        <v>0.18022336959838842</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="52"/>
+      <c r="B21" s="32">
+        <v>10</v>
+      </c>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="22">
+        <f>AVERAGE(DataExp1!AK4:AK13)</f>
+        <v>3.0304601968108664</v>
+      </c>
+      <c r="L21" s="22">
+        <f>AVERAGE(DataExp1!AL4:AL13)</f>
+        <v>0.65218430526407922</v>
+      </c>
+      <c r="M21" s="22">
+        <v>4.7875038888035598E-2</v>
+      </c>
+      <c r="N21" s="23">
+        <v>1.33921911090507E-4</v>
+      </c>
+      <c r="O21" s="22">
+        <f>AVERAGE(DataExp1!AM4:AM13)</f>
+        <v>0.1679047107696528</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="52"/>
+      <c r="B22" s="32">
+        <v>20</v>
+      </c>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="22"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="52"/>
+      <c r="B23" s="32">
+        <v>50</v>
+      </c>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="22"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="52"/>
+      <c r="B24" s="32">
+        <v>100</v>
+      </c>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="22"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="3">
+        <v>1</v>
+      </c>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="4">
+        <f>AVERAGE(DataExp1!AO4:AO13)</f>
+        <v>34.552311810658352</v>
+      </c>
+      <c r="L25" s="4">
+        <f>AVERAGE(DataExp1!AP4:AP13)</f>
+        <v>4.575032042937762</v>
+      </c>
+      <c r="M25" s="4">
+        <v>6.2164238822761397E-2</v>
+      </c>
+      <c r="N25" s="18">
+        <v>1.8093373899484099E-5</v>
+      </c>
+      <c r="O25" s="4">
+        <f>AVERAGE(DataExp1!AQ4:AQ13)</f>
+        <v>1.6018030881881669</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="51"/>
+      <c r="B26" s="3">
+        <v>3</v>
+      </c>
+      <c r="C26" s="51"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="4">
+        <f>AVERAGE(DataExp1!AR4:AR14)</f>
+        <v>1.8560190453181431</v>
+      </c>
+      <c r="L26" s="4">
+        <f>AVERAGE(DataExp1!AS4:AS14)</f>
+        <v>0.34311024868513884</v>
+      </c>
+      <c r="M26" s="4">
+        <v>8.8175866468285097E-2</v>
+      </c>
+      <c r="N26" s="18">
+        <v>2.79669169855113E-5</v>
+      </c>
+      <c r="O26" s="4">
+        <f>AVERAGE(DataExp1!AT4:AT13)</f>
+        <v>1.6889492511749222</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="51"/>
+      <c r="B27" s="3">
+        <v>5</v>
+      </c>
+      <c r="C27" s="51"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
+      <c r="K27" s="4">
+        <f>AVERAGE(DataExp1!AU4:AU13)</f>
+        <v>1.9127433590347436</v>
+      </c>
+      <c r="L27" s="4">
+        <f>AVERAGE(DataExp1!AV4:AV13)</f>
+        <v>0.35326132701310653</v>
+      </c>
+      <c r="M27" s="4">
+        <v>8.8376119113808799E-2</v>
+      </c>
+      <c r="N27" s="18">
+        <v>2.8023187480955202E-5</v>
+      </c>
+      <c r="O27" s="4">
+        <f>AVERAGE(DataExp1!AW4:AW13)</f>
+        <v>1.7003351620265386</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="51"/>
+      <c r="B28" s="3">
+        <v>10</v>
+      </c>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="51"/>
+      <c r="K28" s="4">
+        <f>AVERAGE(DataExp1!AX4:AX13)</f>
+        <v>1.9259347567178799</v>
+      </c>
+      <c r="L28" s="4">
+        <f>AVERAGE(DataExp1!AY4:AY13)</f>
+        <v>0.35326486945372448</v>
+      </c>
+      <c r="M28" s="4">
+        <v>8.81585941138084E-2</v>
+      </c>
+      <c r="N28" s="18">
+        <v>2.7971865110220399E-5</v>
+      </c>
+      <c r="O28" s="4">
+        <f>AVERAGE(DataExp1!AZ4:AZ13)</f>
+        <v>1.6923342704772899</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="51"/>
+      <c r="B29" s="3">
+        <v>20</v>
+      </c>
+      <c r="C29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="51"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="4"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="51"/>
+      <c r="B30" s="3">
+        <v>50</v>
+      </c>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="4"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="51"/>
+      <c r="B31" s="3">
+        <v>100</v>
+      </c>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="C4:C31"/>
+    <mergeCell ref="D4:D31"/>
+    <mergeCell ref="E4:E31"/>
+    <mergeCell ref="F4:F31"/>
+    <mergeCell ref="G4:G31"/>
+    <mergeCell ref="H4:H31"/>
+    <mergeCell ref="I4:I31"/>
+    <mergeCell ref="J4:J31"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E02A095-16D7-4FBB-B206-8C2A6F2CFB60}">
   <dimension ref="B1:BM16"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5557,164 +6844,164 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:65" x14ac:dyDescent="0.25">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
       <c r="M1" s="21"/>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AI1" s="33" t="s">
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
+      <c r="AB1" s="46"/>
+      <c r="AI1" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="AJ1" s="33"/>
-      <c r="AK1" s="33"/>
-      <c r="AL1" s="33"/>
-      <c r="AM1" s="33"/>
-      <c r="AN1" s="33"/>
-      <c r="AO1" s="33"/>
-      <c r="AP1" s="33"/>
-      <c r="AQ1" s="33"/>
-      <c r="AR1" s="41"/>
-      <c r="AS1" s="41"/>
+      <c r="AJ1" s="46"/>
+      <c r="AK1" s="46"/>
+      <c r="AL1" s="46"/>
+      <c r="AM1" s="46"/>
+      <c r="AN1" s="46"/>
+      <c r="AO1" s="46"/>
+      <c r="AP1" s="46"/>
+      <c r="AQ1" s="46"/>
+      <c r="AR1" s="38"/>
+      <c r="AS1" s="38"/>
       <c r="AT1" s="21"/>
-      <c r="AY1" s="33" t="s">
+      <c r="AY1" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="AZ1" s="33"/>
-      <c r="BA1" s="33"/>
-      <c r="BB1" s="33"/>
-      <c r="BC1" s="33"/>
-      <c r="BD1" s="33"/>
-      <c r="BE1" s="33"/>
-      <c r="BF1" s="33"/>
-      <c r="BG1" s="33"/>
-      <c r="BH1" s="41"/>
-      <c r="BI1" s="41"/>
+      <c r="AZ1" s="46"/>
+      <c r="BA1" s="46"/>
+      <c r="BB1" s="46"/>
+      <c r="BC1" s="46"/>
+      <c r="BD1" s="46"/>
+      <c r="BE1" s="46"/>
+      <c r="BF1" s="46"/>
+      <c r="BG1" s="46"/>
+      <c r="BH1" s="38"/>
+      <c r="BI1" s="38"/>
     </row>
     <row r="2" spans="2:65" x14ac:dyDescent="0.25">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="34" t="s">
+      <c r="C2" s="40"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="35"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="37" t="s">
+      <c r="F2" s="40"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="38"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="40" t="s">
+      <c r="I2" s="43"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="R2" s="34" t="s">
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="R2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="35"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="34" t="s">
+      <c r="S2" s="40"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="35"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="37" t="s">
+      <c r="V2" s="40"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="40" t="s">
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="40"/>
-      <c r="AD2" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE2" s="40"/>
-      <c r="AF2" s="40"/>
-      <c r="AG2" s="54"/>
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="45"/>
+      <c r="AD2" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE2" s="45"/>
+      <c r="AF2" s="45"/>
+      <c r="AG2" s="21"/>
       <c r="AH2" s="21"/>
-      <c r="AI2" s="34" t="s">
+      <c r="AI2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="AJ2" s="35"/>
-      <c r="AK2" s="36"/>
-      <c r="AL2" s="34" t="s">
+      <c r="AJ2" s="40"/>
+      <c r="AK2" s="41"/>
+      <c r="AL2" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="AM2" s="35"/>
-      <c r="AN2" s="36"/>
-      <c r="AO2" s="37" t="s">
+      <c r="AM2" s="40"/>
+      <c r="AN2" s="41"/>
+      <c r="AO2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="AP2" s="38"/>
-      <c r="AQ2" s="39"/>
-      <c r="AR2" s="40" t="s">
+      <c r="AP2" s="43"/>
+      <c r="AQ2" s="44"/>
+      <c r="AR2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="AS2" s="40"/>
-      <c r="AT2" s="40"/>
-      <c r="AU2" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="AV2" s="40"/>
-      <c r="AW2" s="40"/>
-      <c r="AY2" s="34" t="s">
+      <c r="AS2" s="45"/>
+      <c r="AT2" s="45"/>
+      <c r="AU2" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="AV2" s="45"/>
+      <c r="AW2" s="45"/>
+      <c r="AY2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="AZ2" s="35"/>
-      <c r="BA2" s="36"/>
-      <c r="BB2" s="34" t="s">
+      <c r="AZ2" s="40"/>
+      <c r="BA2" s="41"/>
+      <c r="BB2" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="BC2" s="35"/>
-      <c r="BD2" s="36"/>
-      <c r="BE2" s="37" t="s">
+      <c r="BC2" s="40"/>
+      <c r="BD2" s="41"/>
+      <c r="BE2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="BF2" s="38"/>
-      <c r="BG2" s="39"/>
-      <c r="BH2" s="40" t="s">
+      <c r="BF2" s="43"/>
+      <c r="BG2" s="44"/>
+      <c r="BH2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="BI2" s="40"/>
-      <c r="BJ2" s="40"/>
-      <c r="BK2" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="BL2" s="40"/>
-      <c r="BM2" s="40"/>
+      <c r="BI2" s="45"/>
+      <c r="BJ2" s="45"/>
+      <c r="BK2" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="BL2" s="45"/>
+      <c r="BM2" s="45"/>
     </row>
     <row r="3" spans="2:65" ht="45" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -5723,8 +7010,8 @@
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="27" t="s">
-        <v>35</v>
+      <c r="D3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>20</v>
@@ -5732,8 +7019,8 @@
       <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="27" t="s">
-        <v>35</v>
+      <c r="G3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>20</v>
@@ -5741,8 +7028,8 @@
       <c r="I3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="27" t="s">
-        <v>35</v>
+      <c r="J3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>20</v>
@@ -5750,8 +7037,8 @@
       <c r="L3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="27" t="s">
-        <v>35</v>
+      <c r="M3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="N3" s="8" t="s">
         <v>20</v>
@@ -5759,8 +7046,8 @@
       <c r="O3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="27" t="s">
-        <v>35</v>
+      <c r="P3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>20</v>
@@ -5768,8 +7055,8 @@
       <c r="S3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="27" t="s">
-        <v>35</v>
+      <c r="T3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>20</v>
@@ -5777,8 +7064,8 @@
       <c r="V3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="W3" s="27" t="s">
-        <v>35</v>
+      <c r="W3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="X3" s="8" t="s">
         <v>20</v>
@@ -5786,8 +7073,8 @@
       <c r="Y3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="Z3" s="27" t="s">
-        <v>35</v>
+      <c r="Z3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AA3" s="8" t="s">
         <v>20</v>
@@ -5795,8 +7082,8 @@
       <c r="AB3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AC3" s="27" t="s">
-        <v>35</v>
+      <c r="AC3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AD3" s="8" t="s">
         <v>20</v>
@@ -5804,19 +7091,19 @@
       <c r="AE3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AF3" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG3" s="55"/>
-      <c r="AH3" s="30"/>
-      <c r="AI3" s="27" t="s">
+      <c r="AF3" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="25" t="s">
         <v>20</v>
       </c>
       <c r="AJ3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AK3" s="27" t="s">
-        <v>35</v>
+      <c r="AK3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AL3" s="2" t="s">
         <v>20</v>
@@ -5824,8 +7111,8 @@
       <c r="AM3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AN3" s="27" t="s">
-        <v>35</v>
+      <c r="AN3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AO3" s="8" t="s">
         <v>20</v>
@@ -5833,8 +7120,8 @@
       <c r="AP3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AQ3" s="27" t="s">
-        <v>35</v>
+      <c r="AQ3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AR3" s="8" t="s">
         <v>20</v>
@@ -5842,8 +7129,8 @@
       <c r="AS3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AT3" s="27" t="s">
-        <v>35</v>
+      <c r="AT3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AU3" s="8" t="s">
         <v>20</v>
@@ -5851,17 +7138,17 @@
       <c r="AV3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AW3" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="AY3" s="27" t="s">
+      <c r="AW3" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AY3" s="25" t="s">
         <v>20</v>
       </c>
       <c r="AZ3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="BA3" s="27" t="s">
-        <v>35</v>
+      <c r="BA3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="BB3" s="2" t="s">
         <v>20</v>
@@ -5869,8 +7156,8 @@
       <c r="BC3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="BD3" s="27" t="s">
-        <v>35</v>
+      <c r="BD3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="BE3" s="8" t="s">
         <v>20</v>
@@ -5878,8 +7165,8 @@
       <c r="BF3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="BG3" s="27" t="s">
-        <v>35</v>
+      <c r="BG3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="BH3" s="8" t="s">
         <v>20</v>
@@ -5887,8 +7174,8 @@
       <c r="BI3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="BJ3" s="27" t="s">
-        <v>35</v>
+      <c r="BJ3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="BK3" s="8" t="s">
         <v>20</v>
@@ -5896,8 +7183,8 @@
       <c r="BL3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="BM3" s="27" t="s">
-        <v>35</v>
+      <c r="BM3" s="25" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="2:65" x14ac:dyDescent="0.25">
@@ -5982,16 +7269,15 @@
       <c r="AC4" s="9">
         <v>0.16643857955932601</v>
       </c>
-      <c r="AD4" s="60">
+      <c r="AD4" s="4">
         <v>3.5110351294381599</v>
       </c>
-      <c r="AE4" s="60">
+      <c r="AE4" s="4">
         <v>0.73729848313939605</v>
       </c>
-      <c r="AF4" s="60">
+      <c r="AF4" s="4">
         <v>0.170168161392211</v>
       </c>
-      <c r="AG4" s="61"/>
       <c r="AI4" s="4">
         <v>2.0282019718480502</v>
       </c>
@@ -6028,13 +7314,13 @@
       <c r="AT4" s="5">
         <v>0.16964745521545399</v>
       </c>
-      <c r="AU4" s="60">
+      <c r="AU4" s="4">
         <v>3.02288650520053</v>
       </c>
-      <c r="AV4" s="60">
+      <c r="AV4" s="4">
         <v>0.65213375302212495</v>
       </c>
-      <c r="AW4" s="60">
+      <c r="AW4" s="4">
         <v>0.15408825874328599</v>
       </c>
       <c r="AY4" s="4">
@@ -6073,13 +7359,13 @@
       <c r="BJ4" s="3">
         <v>0.157181501388549</v>
       </c>
-      <c r="BK4" s="60">
+      <c r="BK4" s="4">
         <v>2.81576579443291</v>
       </c>
-      <c r="BL4" s="60">
+      <c r="BL4" s="4">
         <v>0.61912335363640203</v>
       </c>
-      <c r="BM4" s="60">
+      <c r="BM4" s="4">
         <v>0.15600681304931599</v>
       </c>
     </row>
@@ -6165,16 +7451,15 @@
       <c r="AC5" s="9">
         <v>0.162857770919799</v>
       </c>
-      <c r="AD5" s="60">
+      <c r="AD5" s="4">
         <v>3.7353311398727702</v>
       </c>
-      <c r="AE5" s="60">
+      <c r="AE5" s="4">
         <v>0.74867532182582797</v>
       </c>
-      <c r="AF5" s="60">
+      <c r="AF5" s="4">
         <v>0.16232037544250399</v>
       </c>
-      <c r="AG5" s="61"/>
       <c r="AI5" s="4">
         <v>2.0576101229880499</v>
       </c>
@@ -6211,13 +7496,13 @@
       <c r="AT5" s="5">
         <v>0.164550065994262</v>
       </c>
-      <c r="AU5" s="60">
+      <c r="AU5" s="4">
         <v>3.0836909556311598</v>
       </c>
-      <c r="AV5" s="60">
+      <c r="AV5" s="4">
         <v>0.65226013362701096</v>
       </c>
-      <c r="AW5" s="60">
+      <c r="AW5" s="4">
         <v>0.156248569488525</v>
       </c>
       <c r="AY5" s="4">
@@ -6256,13 +7541,13 @@
       <c r="BJ5" s="3">
         <v>0.15541315078735299</v>
       </c>
-      <c r="BK5" s="60">
+      <c r="BK5" s="4">
         <v>2.4319525791546099</v>
       </c>
-      <c r="BL5" s="60">
+      <c r="BL5" s="4">
         <v>0.61909175848517894</v>
       </c>
-      <c r="BM5" s="60">
+      <c r="BM5" s="4">
         <v>0.15285587310790999</v>
       </c>
     </row>
@@ -6348,16 +7633,15 @@
       <c r="AC6" s="9">
         <v>0.16499352455139099</v>
       </c>
-      <c r="AD6" s="60">
+      <c r="AD6" s="4">
         <v>0.91339993754753002</v>
       </c>
-      <c r="AE6" s="60">
+      <c r="AE6" s="4">
         <v>0.29765195389368498</v>
       </c>
-      <c r="AF6" s="60">
+      <c r="AF6" s="4">
         <v>0.163552045822143</v>
       </c>
-      <c r="AG6" s="61"/>
       <c r="AI6" s="4">
         <v>2.0124832402399999</v>
       </c>
@@ -6394,13 +7678,13 @@
       <c r="AT6" s="5">
         <v>0.17924475669860801</v>
       </c>
-      <c r="AU6" s="60">
+      <c r="AU6" s="4">
         <v>3.1405529779836701</v>
       </c>
-      <c r="AV6" s="60">
+      <c r="AV6" s="4">
         <v>0.65226013362701096</v>
       </c>
-      <c r="AW6" s="60">
+      <c r="AW6" s="4">
         <v>0.15193510055541901</v>
       </c>
       <c r="AY6" s="4">
@@ -6439,13 +7723,13 @@
       <c r="BJ6" s="3">
         <v>0.15583968162536599</v>
       </c>
-      <c r="BK6" s="60">
+      <c r="BK6" s="4">
         <v>2.6282612918328199</v>
       </c>
-      <c r="BL6" s="60">
+      <c r="BL6" s="4">
         <v>0.61909175848517894</v>
       </c>
-      <c r="BM6" s="60">
+      <c r="BM6" s="4">
         <v>0.15261030197143499</v>
       </c>
     </row>
@@ -6531,16 +7815,15 @@
       <c r="AC7" s="9">
         <v>0.16472458839416501</v>
       </c>
-      <c r="AD7" s="60">
+      <c r="AD7" s="4">
         <v>3.7362419552777202</v>
       </c>
-      <c r="AE7" s="60">
+      <c r="AE7" s="4">
         <v>0.74867532182582797</v>
       </c>
-      <c r="AF7" s="60">
+      <c r="AF7" s="4">
         <v>0.16232395172119099</v>
       </c>
-      <c r="AG7" s="61"/>
       <c r="AI7" s="4">
         <v>1.98733133553576</v>
       </c>
@@ -6577,13 +7860,13 @@
       <c r="AT7" s="5">
         <v>0.16520929336547799</v>
       </c>
-      <c r="AU7" s="60">
+      <c r="AU7" s="4">
         <v>3.1405529779836701</v>
       </c>
-      <c r="AV7" s="60">
+      <c r="AV7" s="4">
         <v>0.65226013362701096</v>
       </c>
-      <c r="AW7" s="60">
+      <c r="AW7" s="4">
         <v>0.15193510055541901</v>
       </c>
       <c r="AY7" s="4">
@@ -6622,13 +7905,13 @@
       <c r="BJ7" s="3">
         <v>0.149705410003662</v>
       </c>
-      <c r="BK7" s="60">
+      <c r="BK7" s="4">
         <v>2.81576579443291</v>
       </c>
-      <c r="BL7" s="60">
+      <c r="BL7" s="4">
         <v>0.61912335363640203</v>
       </c>
-      <c r="BM7" s="60">
+      <c r="BM7" s="4">
         <v>0.155811786651611</v>
       </c>
     </row>
@@ -6714,16 +7997,15 @@
       <c r="AC8" s="9">
         <v>0.161133527755737</v>
       </c>
-      <c r="AD8" s="60">
+      <c r="AD8" s="4">
         <v>3.6940440543667901</v>
       </c>
-      <c r="AE8" s="60">
+      <c r="AE8" s="4">
         <v>0.74867532182582797</v>
       </c>
-      <c r="AF8" s="60">
+      <c r="AF8" s="4">
         <v>0.163506984710693</v>
       </c>
-      <c r="AG8" s="61"/>
       <c r="AI8" s="4">
         <v>2.0045866890630801</v>
       </c>
@@ -6760,13 +8042,13 @@
       <c r="AT8" s="5">
         <v>0.160871982574462</v>
       </c>
-      <c r="AU8" s="60">
+      <c r="AU8" s="4">
         <v>3.1234714223794802</v>
       </c>
-      <c r="AV8" s="60">
+      <c r="AV8" s="4">
         <v>0.65226013362701096</v>
       </c>
-      <c r="AW8" s="60">
+      <c r="AW8" s="4">
         <v>0.15936398506164501</v>
       </c>
       <c r="AY8" s="4">
@@ -6805,13 +8087,13 @@
       <c r="BJ8" s="3">
         <v>0.15323472023010201</v>
       </c>
-      <c r="BK8" s="60">
+      <c r="BK8" s="4">
         <v>2.7916220620382401</v>
       </c>
-      <c r="BL8" s="60">
+      <c r="BL8" s="4">
         <v>0.61912335363640203</v>
       </c>
-      <c r="BM8" s="60">
+      <c r="BM8" s="4">
         <v>0.15216517448425201</v>
       </c>
     </row>
@@ -6857,23 +8139,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AD2:AF2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="AI2:AK2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="AO2:AQ2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="R1:AB1"/>
-    <mergeCell ref="AI1:AS1"/>
     <mergeCell ref="AY1:BI1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
@@ -6881,43 +8146,60 @@
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="U2:W2"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="R1:AB1"/>
+    <mergeCell ref="AI1:AS1"/>
+    <mergeCell ref="AD2:AF2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BH2:BJ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E80E6C9-07DF-4341-ACF2-5E614276889D}">
   <dimension ref="A1:AA23"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:27" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
+      <c r="D1" s="47" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="48"/>
+      <c r="V1" s="48"/>
+      <c r="W1" s="48"/>
+      <c r="X1" s="48"/>
+      <c r="Y1" s="48"/>
+      <c r="Z1" s="48"/>
+      <c r="AA1" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -6961,32 +8243,32 @@
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="50" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="6">
         <v>1</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="45">
+      <c r="D4" s="51">
         <v>66</v>
       </c>
-      <c r="E4" s="45">
+      <c r="E4" s="51">
         <v>66</v>
       </c>
-      <c r="F4" s="46"/>
-      <c r="G4" s="45">
+      <c r="F4" s="60"/>
+      <c r="G4" s="51">
         <v>1</v>
       </c>
-      <c r="H4" s="45">
+      <c r="H4" s="51">
         <v>1</v>
       </c>
-      <c r="I4" s="45">
+      <c r="I4" s="51">
         <v>66</v>
       </c>
-      <c r="J4" s="45">
+      <c r="J4" s="51">
         <v>66</v>
       </c>
       <c r="K4" s="5">
@@ -7003,18 +8285,18 @@
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="51"/>
+      <c r="A5" s="50"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
       <c r="K5" s="5">
         <f>AVERAGE(DataExp2!E4:E8)</f>
         <v>6.7273250931611468</v>
@@ -7029,18 +8311,18 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
+      <c r="A6" s="50"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
       <c r="K6" s="5">
         <f>AVERAGE(DataExp2!H4:H8)</f>
         <v>2.8757780700062598</v>
@@ -7055,18 +8337,18 @@
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
+      <c r="A7" s="50"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
       <c r="K7" s="5">
         <f>AVERAGE(DataExp2!K4:K8)</f>
         <v>2.5245777936554679</v>
@@ -7081,18 +8363,18 @@
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
+      <c r="A8" s="50"/>
       <c r="B8" s="6">
         <v>1000</v>
       </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
       <c r="K8" s="5">
         <f>AVERAGE(DataExp2!N4:N8)</f>
         <v>2.6210229749569218</v>
@@ -7107,20 +8389,20 @@
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="51" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
       <c r="K9" s="4">
         <f>AVERAGE(DataExp2!R4:R8)</f>
         <v>25.122901453825698</v>
@@ -7135,18 +8417,18 @@
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="45"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="3">
         <v>3</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
       <c r="K10" s="4">
         <f>AVERAGE(DataExp2!U4:U8)</f>
         <v>1.1978887514698182</v>
@@ -7161,18 +8443,18 @@
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="45"/>
+      <c r="A11" s="51"/>
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
       <c r="K11" s="4">
         <f>AVERAGE(DataExp2!X4:X8)</f>
         <v>2.7398509444970598</v>
@@ -7187,18 +8469,18 @@
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="45"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="3">
         <v>10</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
       <c r="K12" s="4">
         <f>AVERAGE(DataExp2!AA4:AA8)</f>
         <v>2.3904188069590249</v>
@@ -7213,18 +8495,18 @@
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="45"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="3">
         <v>1000</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
       <c r="K13" s="4">
         <f>AVERAGE(DataExp2!AD4:AD8)</f>
         <v>3.118010443300594</v>
@@ -7239,20 +8521,20 @@
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="50" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="6">
         <v>1</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
       <c r="K14" s="14">
         <f>AVERAGE(DataExp2!AI4:AI8)</f>
         <v>2.018042671934988</v>
@@ -7267,18 +8549,18 @@
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="51"/>
+      <c r="A15" s="50"/>
       <c r="B15" s="6">
         <v>3</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
       <c r="K15" s="14">
         <f>AVERAGE(DataExp2!AL4:AL8)</f>
         <v>2.9999089103706797</v>
@@ -7293,18 +8575,18 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="51"/>
+      <c r="A16" s="50"/>
       <c r="B16" s="6">
         <v>5</v>
       </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
       <c r="K16" s="14">
         <f>AVERAGE(DataExp2!AO4:AO8)</f>
         <v>3.0887572192386399</v>
@@ -7319,18 +8601,18 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="51"/>
+      <c r="A17" s="50"/>
       <c r="B17" s="6">
         <v>10</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="47"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
       <c r="K17" s="14">
         <f>AVERAGE(DataExp2!AR4:AR8)</f>
         <v>3.0147786188702144</v>
@@ -7345,18 +8627,18 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="51"/>
+      <c r="A18" s="50"/>
       <c r="B18" s="6">
         <v>1000</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
       <c r="K18" s="14">
         <f>AVERAGE(DataExp2!AU4:AU8)</f>
         <v>3.1022309678357018</v>
@@ -7371,20 +8653,20 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="45" t="s">
+      <c r="A19" s="51" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="3">
         <v>1</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
       <c r="K19" s="4">
         <f>AVERAGE(DataExp2!AY4:AY8)</f>
         <v>23.17734266838546</v>
@@ -7399,18 +8681,18 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="45"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
       <c r="K20" s="4">
         <f>AVERAGE(DataExp2!BB4:BB8)</f>
         <v>2.7741290185543344</v>
@@ -7425,18 +8707,18 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="45"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="3">
         <v>5</v>
       </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
       <c r="K21" s="4">
         <f>AVERAGE(DataExp2!BE4:BE8)</f>
         <v>2.776927957976338</v>
@@ -7458,46 +8740,46 @@
       <c r="C22" s="58"/>
       <c r="D22" s="58"/>
       <c r="E22" s="58"/>
-      <c r="F22" s="47"/>
+      <c r="F22" s="61"/>
       <c r="G22" s="58"/>
       <c r="H22" s="58"/>
       <c r="I22" s="58"/>
       <c r="J22" s="58"/>
-      <c r="K22" s="62">
+      <c r="K22" s="31">
         <f>AVERAGE(DataExp2!BH4:BH8)</f>
         <v>2.6552692879772497</v>
       </c>
-      <c r="L22" s="62">
+      <c r="L22" s="31">
         <f>AVERAGE(DataExp2!BI4:BI8)</f>
         <v>0.61909807751542356</v>
       </c>
-      <c r="M22" s="62">
+      <c r="M22" s="31">
         <f>AVERAGE(DataExp2!BJ4:BJ8)</f>
         <v>0.1542748928070064</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="52"/>
-      <c r="B23" s="32">
+      <c r="A23" s="59"/>
+      <c r="B23" s="30">
         <v>1000</v>
       </c>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="52"/>
-      <c r="K23" s="31">
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="29">
         <f>AVERAGE(DataExp2!BK4:BK8)</f>
         <v>2.6966735043782979</v>
       </c>
-      <c r="L23" s="31">
+      <c r="L23" s="29">
         <f>AVERAGE(DataExp2!BL4:BL8)</f>
         <v>0.6191107155759128</v>
       </c>
-      <c r="M23" s="31">
+      <c r="M23" s="29">
         <f>AVERAGE(DataExp2!BM4:BM8)</f>
         <v>0.15388998985290481</v>
       </c>
@@ -7522,7 +8804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{109AAA12-50B0-4DB2-B0E7-B06F76284A15}">
   <dimension ref="A2:L22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7569,32 +8851,32 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="63" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="6">
         <v>1</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="45">
+      <c r="D3" s="51">
         <v>66</v>
       </c>
-      <c r="E3" s="45">
+      <c r="E3" s="51">
         <v>66</v>
       </c>
-      <c r="F3" s="40"/>
-      <c r="G3" s="45">
+      <c r="F3" s="45"/>
+      <c r="G3" s="51">
         <v>1</v>
       </c>
-      <c r="H3" s="45">
+      <c r="H3" s="51">
         <v>1</v>
       </c>
-      <c r="I3" s="45">
+      <c r="I3" s="51">
         <v>66</v>
       </c>
-      <c r="J3" s="45">
+      <c r="J3" s="51">
         <v>66</v>
       </c>
       <c r="K3" s="9">
@@ -7605,18 +8887,18 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="57"/>
+      <c r="A4" s="64"/>
       <c r="B4" s="6">
         <v>3</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
       <c r="K4" s="14">
         <v>10.596633070539401</v>
       </c>
@@ -7625,18 +8907,18 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="57"/>
+      <c r="A5" s="64"/>
       <c r="B5" s="6">
         <v>5</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
       <c r="K5" s="14">
         <v>4.5624707313509596</v>
       </c>
@@ -7645,18 +8927,18 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="57"/>
+      <c r="A6" s="64"/>
       <c r="B6" s="6">
         <v>10</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
       <c r="K6" s="14">
         <v>0.610171518579538</v>
       </c>
@@ -7665,18 +8947,18 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="50"/>
+      <c r="A7" s="49"/>
       <c r="B7" s="6">
         <v>100</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
       <c r="K7" s="9">
         <v>0.56361848551125004</v>
       </c>
@@ -7691,116 +8973,116 @@
       <c r="B8" s="3">
         <v>1</v>
       </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="60">
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="4">
         <v>51.3708858392826</v>
       </c>
-      <c r="L8" s="60">
+      <c r="L8" s="4">
         <v>6.6885950561924696</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="59"/>
+      <c r="A9" s="55"/>
       <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="60">
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="4">
         <v>2.1067016984413098</v>
       </c>
-      <c r="L9" s="60">
+      <c r="L9" s="4">
         <v>0.40789971668138397</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="59"/>
+      <c r="A10" s="55"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="60">
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="4">
         <v>2.8064566058312099</v>
       </c>
-      <c r="L10" s="60">
+      <c r="L10" s="4">
         <v>0.67455402488281302</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="59"/>
+      <c r="A11" s="55"/>
       <c r="B11" s="3">
         <v>10</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="60">
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="4">
         <v>1.8870454425238199</v>
       </c>
-      <c r="L11" s="60">
+      <c r="L11" s="4">
         <v>0.37616173059733798</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="44"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="3">
         <v>100</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="60">
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="4">
         <v>1.6795645399372201</v>
       </c>
-      <c r="L12" s="60">
+      <c r="L12" s="4">
         <v>0.41984578161339797</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="56" t="s">
+      <c r="A13" s="63" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="6">
         <v>1</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
       <c r="K13" s="14">
         <v>1.97796965575553</v>
       </c>
@@ -7809,18 +9091,18 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="57"/>
+      <c r="A14" s="64"/>
       <c r="B14" s="6">
         <v>3</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
       <c r="K14" s="14">
         <v>3.1862607049915099</v>
       </c>
@@ -7829,18 +9111,18 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="57"/>
+      <c r="A15" s="64"/>
       <c r="B15" s="6">
         <v>5</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
       <c r="K15" s="14">
         <v>3.1662124268938201</v>
       </c>
@@ -7849,18 +9131,18 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="57"/>
+      <c r="A16" s="64"/>
       <c r="B16" s="6">
         <v>10</v>
       </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
       <c r="K16" s="14">
         <v>3.0769912027266599</v>
       </c>
@@ -7869,18 +9151,18 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="50"/>
+      <c r="A17" s="49"/>
       <c r="B17" s="6">
         <v>100</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
       <c r="K17" s="14">
         <v>3.1294599319079799</v>
       </c>
@@ -7889,20 +9171,20 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="51" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
       <c r="K18">
         <v>34.454845100484</v>
       </c>
@@ -7911,18 +9193,18 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="45"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="3">
         <v>3</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
       <c r="K19" s="4">
         <v>1.9521931441214699</v>
       </c>
@@ -7931,18 +9213,18 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="45"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="3">
         <v>5</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
       <c r="K20" s="3">
         <v>2.0043440401661101</v>
       </c>
@@ -7955,14 +9237,14 @@
       <c r="B21" s="10">
         <v>10</v>
       </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
       <c r="K21" s="3">
         <v>2.0041611367035599</v>
       </c>
@@ -7971,18 +9253,18 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="52"/>
-      <c r="B22" s="32">
+      <c r="A22" s="59"/>
+      <c r="B22" s="30">
         <v>100</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
       <c r="K22" s="3">
         <v>2.0126023888751998</v>
       </c>
@@ -7992,6 +9274,10 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A12"/>
     <mergeCell ref="J3:J22"/>
     <mergeCell ref="C3:C22"/>
     <mergeCell ref="D3:D22"/>
@@ -8000,17 +9286,13 @@
     <mergeCell ref="G3:G22"/>
     <mergeCell ref="H3:H22"/>
     <mergeCell ref="I3:I22"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A8:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88CF955-8A08-4606-BED9-523AEA531233}">
   <dimension ref="B1:BC21"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8028,148 +9310,148 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:55" x14ac:dyDescent="0.25">
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
       <c r="M1" s="21"/>
-      <c r="R1" s="33" t="s">
+      <c r="R1" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="33"/>
-      <c r="AA1" s="33"/>
-      <c r="AB1" s="33"/>
-      <c r="AE1" s="33" t="s">
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
+      <c r="AB1" s="46"/>
+      <c r="AE1" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" s="33"/>
-      <c r="AG1" s="33"/>
-      <c r="AH1" s="33"/>
-      <c r="AI1" s="33"/>
-      <c r="AJ1" s="33"/>
-      <c r="AK1" s="33"/>
-      <c r="AL1" s="33"/>
-      <c r="AM1" s="33"/>
-      <c r="AN1" s="41"/>
-      <c r="AO1" s="41"/>
+      <c r="AF1" s="46"/>
+      <c r="AG1" s="46"/>
+      <c r="AH1" s="46"/>
+      <c r="AI1" s="46"/>
+      <c r="AJ1" s="46"/>
+      <c r="AK1" s="46"/>
+      <c r="AL1" s="46"/>
+      <c r="AM1" s="46"/>
+      <c r="AN1" s="38"/>
+      <c r="AO1" s="38"/>
       <c r="AP1" s="21"/>
-      <c r="AR1" s="33" t="s">
+      <c r="AR1" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="AS1" s="33"/>
-      <c r="AT1" s="33"/>
-      <c r="AU1" s="33"/>
-      <c r="AV1" s="33"/>
-      <c r="AW1" s="33"/>
-      <c r="AX1" s="33"/>
-      <c r="AY1" s="33"/>
-      <c r="AZ1" s="33"/>
-      <c r="BA1" s="41"/>
-      <c r="BB1" s="41"/>
+      <c r="AS1" s="46"/>
+      <c r="AT1" s="46"/>
+      <c r="AU1" s="46"/>
+      <c r="AV1" s="46"/>
+      <c r="AW1" s="46"/>
+      <c r="AX1" s="46"/>
+      <c r="AY1" s="46"/>
+      <c r="AZ1" s="46"/>
+      <c r="BA1" s="38"/>
+      <c r="BB1" s="38"/>
     </row>
     <row r="2" spans="2:55" x14ac:dyDescent="0.25">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="34" t="s">
+      <c r="C2" s="40"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="35"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="37" t="s">
+      <c r="F2" s="40"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="38"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="40" t="s">
+      <c r="I2" s="43"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="R2" s="34" t="s">
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="O2" s="45"/>
+      <c r="P2" s="45"/>
+      <c r="R2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="35"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="34" t="s">
+      <c r="S2" s="40"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="35"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="37" t="s">
+      <c r="V2" s="40"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="40" t="s">
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="40"/>
+      <c r="AB2" s="45"/>
+      <c r="AC2" s="45"/>
       <c r="AD2" s="21"/>
-      <c r="AE2" s="34" t="s">
+      <c r="AE2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="36"/>
-      <c r="AH2" s="34" t="s">
+      <c r="AF2" s="40"/>
+      <c r="AG2" s="41"/>
+      <c r="AH2" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="AI2" s="35"/>
-      <c r="AJ2" s="36"/>
-      <c r="AK2" s="37" t="s">
+      <c r="AI2" s="40"/>
+      <c r="AJ2" s="41"/>
+      <c r="AK2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="AL2" s="38"/>
-      <c r="AM2" s="39"/>
-      <c r="AN2" s="40" t="s">
+      <c r="AL2" s="43"/>
+      <c r="AM2" s="44"/>
+      <c r="AN2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="AO2" s="40"/>
-      <c r="AP2" s="40"/>
-      <c r="AR2" s="34" t="s">
+      <c r="AO2" s="45"/>
+      <c r="AP2" s="45"/>
+      <c r="AR2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="AS2" s="35"/>
-      <c r="AT2" s="36"/>
-      <c r="AU2" s="34" t="s">
+      <c r="AS2" s="40"/>
+      <c r="AT2" s="41"/>
+      <c r="AU2" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="AV2" s="35"/>
-      <c r="AW2" s="36"/>
-      <c r="AX2" s="37" t="s">
+      <c r="AV2" s="40"/>
+      <c r="AW2" s="41"/>
+      <c r="AX2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="AY2" s="38"/>
-      <c r="AZ2" s="39"/>
-      <c r="BA2" s="40" t="s">
+      <c r="AY2" s="43"/>
+      <c r="AZ2" s="44"/>
+      <c r="BA2" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="BB2" s="40"/>
-      <c r="BC2" s="40"/>
+      <c r="BB2" s="45"/>
+      <c r="BC2" s="45"/>
     </row>
     <row r="3" spans="2:55" ht="45" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -8178,8 +9460,8 @@
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="27" t="s">
-        <v>35</v>
+      <c r="D3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>20</v>
@@ -8187,8 +9469,8 @@
       <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="27" t="s">
-        <v>35</v>
+      <c r="G3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>20</v>
@@ -8196,8 +9478,8 @@
       <c r="I3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="27" t="s">
-        <v>35</v>
+      <c r="J3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>20</v>
@@ -8205,8 +9487,8 @@
       <c r="L3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="27" t="s">
-        <v>35</v>
+      <c r="M3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="N3" s="8" t="s">
         <v>20</v>
@@ -8214,8 +9496,8 @@
       <c r="O3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="27" t="s">
-        <v>35</v>
+      <c r="P3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>20</v>
@@ -8223,8 +9505,8 @@
       <c r="S3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="27" t="s">
-        <v>35</v>
+      <c r="T3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>20</v>
@@ -8232,8 +9514,8 @@
       <c r="V3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="W3" s="27" t="s">
-        <v>35</v>
+      <c r="W3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="X3" s="8" t="s">
         <v>20</v>
@@ -8241,8 +9523,8 @@
       <c r="Y3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="Z3" s="27" t="s">
-        <v>35</v>
+      <c r="Z3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AA3" s="8" t="s">
         <v>20</v>
@@ -8250,18 +9532,18 @@
       <c r="AB3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AC3" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="27" t="s">
+      <c r="AC3" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="25" t="s">
         <v>20</v>
       </c>
       <c r="AF3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AG3" s="27" t="s">
-        <v>35</v>
+      <c r="AG3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AH3" s="2" t="s">
         <v>20</v>
@@ -8269,8 +9551,8 @@
       <c r="AI3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AJ3" s="27" t="s">
-        <v>35</v>
+      <c r="AJ3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AK3" s="8" t="s">
         <v>20</v>
@@ -8278,8 +9560,8 @@
       <c r="AL3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AM3" s="27" t="s">
-        <v>35</v>
+      <c r="AM3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AN3" s="8" t="s">
         <v>20</v>
@@ -8287,17 +9569,17 @@
       <c r="AO3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AP3" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="AR3" s="27" t="s">
+      <c r="AP3" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AR3" s="25" t="s">
         <v>20</v>
       </c>
       <c r="AS3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AT3" s="27" t="s">
-        <v>35</v>
+      <c r="AT3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AU3" s="2" t="s">
         <v>20</v>
@@ -8305,8 +9587,8 @@
       <c r="AV3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AW3" s="27" t="s">
-        <v>35</v>
+      <c r="AW3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="AX3" s="8" t="s">
         <v>20</v>
@@ -8314,8 +9596,8 @@
       <c r="AY3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AZ3" s="27" t="s">
-        <v>35</v>
+      <c r="AZ3" s="25" t="s">
+        <v>34</v>
       </c>
       <c r="BA3" s="8" t="s">
         <v>20</v>
@@ -8323,8 +9605,8 @@
       <c r="BB3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="BC3" s="27" t="s">
-        <v>35</v>
+      <c r="BC3" s="25" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="2:55" x14ac:dyDescent="0.25">
@@ -8899,16 +10181,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="AN2:AP2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="AH2:AJ2"/>
     <mergeCell ref="AK2:AM2"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="R1:AB1"/>
@@ -8920,26 +10192,36 @@
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AN2:AP2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9168,14 +10450,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58C277AC-42DD-4338-BD2A-AF7ECB0689E8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -9188,6 +10462,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/documents/ExperimentData.xlsx
+++ b/documents/ExperimentData.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1b2bcfbbb34c0c/Documents/GitHub/meliso/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1733" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3020F327-55BD-4FC8-8079-59A30095D32F}"/>
+  <xr:revisionPtr revIDLastSave="1943" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDC8AC79-796B-4BCF-B7F0-9A80331168E2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
   </bookViews>
   <sheets>
-    <sheet name="DataExp1" sheetId="2" r:id="rId1"/>
+    <sheet name="DataExp1.1" sheetId="2" r:id="rId1"/>
     <sheet name="Experiment 1.1" sheetId="1" r:id="rId2"/>
-    <sheet name="Experiment 1.2" sheetId="7" r:id="rId3"/>
-    <sheet name="DataExp2" sheetId="4" r:id="rId4"/>
-    <sheet name="Experiment 2" sheetId="3" r:id="rId5"/>
-    <sheet name="Experiment 3" sheetId="5" r:id="rId6"/>
-    <sheet name="DataExp4" sheetId="6" r:id="rId7"/>
+    <sheet name="DataExp1.2" sheetId="8" r:id="rId3"/>
+    <sheet name="Experiment 1.2" sheetId="7" r:id="rId4"/>
+    <sheet name="DataExp2" sheetId="4" r:id="rId5"/>
+    <sheet name="Experiment 2" sheetId="3" r:id="rId6"/>
+    <sheet name="Experiment 3" sheetId="5" r:id="rId7"/>
+    <sheet name="DataExp4" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="62">
   <si>
     <t>MCA Rows</t>
   </si>
@@ -216,6 +217,27 @@
 Fixed Number of Iterations for Error Correction; 
 Aplied Error Correction to all devices
 Run 10 replications for each number of iterations</t>
+  </si>
+  <si>
+    <t>email-Eu-core-temporal</t>
+  </si>
+  <si>
+    <t>Ag-aSi (email-Eu-core-temporal)</t>
+  </si>
+  <si>
+    <t>N = 20</t>
+  </si>
+  <si>
+    <t>N = 50</t>
+  </si>
+  <si>
+    <t>AlOx-HfO2 (email-Eu-core-temporal)</t>
+  </si>
+  <si>
+    <t>EpiRAM (email-Eu-core-temporal)</t>
+  </si>
+  <si>
+    <t>TaOx-HfOx (email-Eu-core-temporal)</t>
   </si>
 </sst>
 </file>
@@ -488,7 +510,8 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -512,8 +535,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -527,28 +571,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -569,10 +595,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -927,143 +949,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
       <c r="M1" s="21"/>
-      <c r="O1" s="46" t="s">
+      <c r="O1" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="AB1" s="46" t="s">
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="AB1" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="AC1" s="46"/>
-      <c r="AD1" s="46"/>
-      <c r="AE1" s="46"/>
-      <c r="AF1" s="46"/>
-      <c r="AG1" s="46"/>
-      <c r="AH1" s="46"/>
-      <c r="AI1" s="46"/>
-      <c r="AJ1" s="46"/>
-      <c r="AK1" s="38"/>
-      <c r="AL1" s="38"/>
+      <c r="AC1" s="39"/>
+      <c r="AD1" s="39"/>
+      <c r="AE1" s="39"/>
+      <c r="AF1" s="39"/>
+      <c r="AG1" s="39"/>
+      <c r="AH1" s="39"/>
+      <c r="AI1" s="39"/>
+      <c r="AJ1" s="39"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
       <c r="AM1" s="21"/>
-      <c r="AO1" s="46" t="s">
+      <c r="AO1" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AP1" s="46"/>
-      <c r="AQ1" s="46"/>
-      <c r="AR1" s="46"/>
-      <c r="AS1" s="46"/>
-      <c r="AT1" s="46"/>
-      <c r="AU1" s="46"/>
-      <c r="AV1" s="46"/>
-      <c r="AW1" s="46"/>
-      <c r="AX1" s="38"/>
-      <c r="AY1" s="38"/>
+      <c r="AP1" s="39"/>
+      <c r="AQ1" s="39"/>
+      <c r="AR1" s="39"/>
+      <c r="AS1" s="39"/>
+      <c r="AT1" s="39"/>
+      <c r="AU1" s="39"/>
+      <c r="AV1" s="39"/>
+      <c r="AW1" s="39"/>
+      <c r="AX1" s="47"/>
+      <c r="AY1" s="47"/>
     </row>
     <row r="2" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="39" t="s">
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="40"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="42" t="s">
+      <c r="F2" s="41"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="43"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="45" t="s">
+      <c r="I2" s="44"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="O2" s="39" t="s">
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="O2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="39" t="s">
+      <c r="P2" s="41"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="S2" s="40"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="42" t="s">
+      <c r="S2" s="41"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="43"/>
-      <c r="W2" s="44"/>
-      <c r="X2" s="45" t="s">
+      <c r="V2" s="44"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="Y2" s="45"/>
-      <c r="Z2" s="45"/>
+      <c r="Y2" s="46"/>
+      <c r="Z2" s="46"/>
       <c r="AA2" s="21"/>
-      <c r="AB2" s="39" t="s">
+      <c r="AB2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="AC2" s="40"/>
-      <c r="AD2" s="41"/>
-      <c r="AE2" s="39" t="s">
+      <c r="AC2" s="41"/>
+      <c r="AD2" s="42"/>
+      <c r="AE2" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="AF2" s="40"/>
-      <c r="AG2" s="41"/>
-      <c r="AH2" s="42" t="s">
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="42"/>
+      <c r="AH2" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="AI2" s="43"/>
-      <c r="AJ2" s="44"/>
-      <c r="AK2" s="45" t="s">
+      <c r="AI2" s="44"/>
+      <c r="AJ2" s="45"/>
+      <c r="AK2" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="AL2" s="45"/>
-      <c r="AM2" s="45"/>
-      <c r="AO2" s="39" t="s">
+      <c r="AL2" s="46"/>
+      <c r="AM2" s="46"/>
+      <c r="AO2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="AP2" s="40"/>
-      <c r="AQ2" s="41"/>
-      <c r="AR2" s="39" t="s">
+      <c r="AP2" s="41"/>
+      <c r="AQ2" s="42"/>
+      <c r="AR2" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="AS2" s="40"/>
-      <c r="AT2" s="41"/>
-      <c r="AU2" s="42" t="s">
+      <c r="AS2" s="41"/>
+      <c r="AT2" s="42"/>
+      <c r="AU2" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="AV2" s="43"/>
-      <c r="AW2" s="44"/>
-      <c r="AX2" s="45" t="s">
+      <c r="AV2" s="44"/>
+      <c r="AW2" s="45"/>
+      <c r="AX2" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="AY2" s="45"/>
-      <c r="AZ2" s="45"/>
+      <c r="AY2" s="46"/>
+      <c r="AZ2" s="46"/>
     </row>
     <row r="3" spans="2:52" ht="45" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -2552,143 +2574,143 @@
       <c r="D14" s="7"/>
     </row>
     <row r="15" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
       <c r="M15" s="21"/>
-      <c r="O15" s="46" t="s">
+      <c r="O15" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="P15" s="46"/>
-      <c r="Q15" s="46"/>
-      <c r="R15" s="46"/>
-      <c r="S15" s="46"/>
-      <c r="T15" s="46"/>
-      <c r="U15" s="46"/>
-      <c r="V15" s="46"/>
-      <c r="W15" s="46"/>
-      <c r="X15" s="46"/>
-      <c r="Y15" s="46"/>
-      <c r="AB15" s="46" t="s">
+      <c r="P15" s="39"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="39"/>
+      <c r="S15" s="39"/>
+      <c r="T15" s="39"/>
+      <c r="U15" s="39"/>
+      <c r="V15" s="39"/>
+      <c r="W15" s="39"/>
+      <c r="X15" s="39"/>
+      <c r="Y15" s="39"/>
+      <c r="AB15" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="AC15" s="46"/>
-      <c r="AD15" s="46"/>
-      <c r="AE15" s="46"/>
-      <c r="AF15" s="46"/>
-      <c r="AG15" s="46"/>
-      <c r="AH15" s="46"/>
-      <c r="AI15" s="46"/>
-      <c r="AJ15" s="46"/>
-      <c r="AK15" s="46"/>
-      <c r="AL15" s="46"/>
+      <c r="AC15" s="39"/>
+      <c r="AD15" s="39"/>
+      <c r="AE15" s="39"/>
+      <c r="AF15" s="39"/>
+      <c r="AG15" s="39"/>
+      <c r="AH15" s="39"/>
+      <c r="AI15" s="39"/>
+      <c r="AJ15" s="39"/>
+      <c r="AK15" s="39"/>
+      <c r="AL15" s="39"/>
       <c r="AM15" s="21"/>
-      <c r="AO15" s="46" t="s">
+      <c r="AO15" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="AP15" s="46"/>
-      <c r="AQ15" s="46"/>
-      <c r="AR15" s="46"/>
-      <c r="AS15" s="46"/>
-      <c r="AT15" s="46"/>
-      <c r="AU15" s="46"/>
-      <c r="AV15" s="46"/>
-      <c r="AW15" s="46"/>
-      <c r="AX15" s="46"/>
-      <c r="AY15" s="46"/>
+      <c r="AP15" s="39"/>
+      <c r="AQ15" s="39"/>
+      <c r="AR15" s="39"/>
+      <c r="AS15" s="39"/>
+      <c r="AT15" s="39"/>
+      <c r="AU15" s="39"/>
+      <c r="AV15" s="39"/>
+      <c r="AW15" s="39"/>
+      <c r="AX15" s="39"/>
+      <c r="AY15" s="39"/>
     </row>
     <row r="16" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="39" t="s">
+      <c r="C16" s="41"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="42" t="s">
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="43"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="45" t="s">
+      <c r="I16" s="44"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="L16" s="45"/>
-      <c r="M16" s="45"/>
-      <c r="O16" s="39" t="s">
+      <c r="L16" s="46"/>
+      <c r="M16" s="46"/>
+      <c r="O16" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="39" t="s">
+      <c r="P16" s="41"/>
+      <c r="Q16" s="42"/>
+      <c r="R16" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="S16" s="40"/>
-      <c r="T16" s="41"/>
-      <c r="U16" s="42" t="s">
+      <c r="S16" s="41"/>
+      <c r="T16" s="42"/>
+      <c r="U16" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="V16" s="43"/>
-      <c r="W16" s="44"/>
-      <c r="X16" s="45" t="s">
+      <c r="V16" s="44"/>
+      <c r="W16" s="45"/>
+      <c r="X16" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="Y16" s="45"/>
-      <c r="Z16" s="45"/>
+      <c r="Y16" s="46"/>
+      <c r="Z16" s="46"/>
       <c r="AA16" s="21"/>
-      <c r="AB16" s="39" t="s">
+      <c r="AB16" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="AC16" s="40"/>
-      <c r="AD16" s="41"/>
-      <c r="AE16" s="39" t="s">
+      <c r="AC16" s="41"/>
+      <c r="AD16" s="42"/>
+      <c r="AE16" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="AF16" s="40"/>
-      <c r="AG16" s="41"/>
-      <c r="AH16" s="42" t="s">
+      <c r="AF16" s="41"/>
+      <c r="AG16" s="42"/>
+      <c r="AH16" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="AI16" s="43"/>
-      <c r="AJ16" s="44"/>
-      <c r="AK16" s="45" t="s">
+      <c r="AI16" s="44"/>
+      <c r="AJ16" s="45"/>
+      <c r="AK16" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="AL16" s="45"/>
-      <c r="AM16" s="45"/>
-      <c r="AO16" s="39" t="s">
+      <c r="AL16" s="46"/>
+      <c r="AM16" s="46"/>
+      <c r="AO16" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="AP16" s="40"/>
-      <c r="AQ16" s="41"/>
-      <c r="AR16" s="39" t="s">
+      <c r="AP16" s="41"/>
+      <c r="AQ16" s="42"/>
+      <c r="AR16" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="AS16" s="40"/>
-      <c r="AT16" s="41"/>
-      <c r="AU16" s="42" t="s">
+      <c r="AS16" s="41"/>
+      <c r="AT16" s="42"/>
+      <c r="AU16" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="AV16" s="43"/>
-      <c r="AW16" s="44"/>
-      <c r="AX16" s="45" t="s">
+      <c r="AV16" s="44"/>
+      <c r="AW16" s="45"/>
+      <c r="AX16" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="AY16" s="45"/>
-      <c r="AZ16" s="45"/>
+      <c r="AY16" s="46"/>
+      <c r="AZ16" s="46"/>
     </row>
     <row r="17" spans="2:52" ht="45" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
@@ -4004,46 +4026,46 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="O1:Y1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AB1:AL1"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AK2:AM2"/>
+    <mergeCell ref="AO1:AY1"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="O15:Y15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="U16:W16"/>
+    <mergeCell ref="X16:Z16"/>
+    <mergeCell ref="AO15:AY15"/>
+    <mergeCell ref="AO16:AQ16"/>
+    <mergeCell ref="AR16:AT16"/>
+    <mergeCell ref="AU16:AW16"/>
+    <mergeCell ref="AX16:AZ16"/>
     <mergeCell ref="AB15:AL15"/>
     <mergeCell ref="AB16:AD16"/>
     <mergeCell ref="AE16:AG16"/>
     <mergeCell ref="AH16:AJ16"/>
     <mergeCell ref="AK16:AM16"/>
-    <mergeCell ref="AO15:AY15"/>
-    <mergeCell ref="AO16:AQ16"/>
-    <mergeCell ref="AR16:AT16"/>
-    <mergeCell ref="AU16:AW16"/>
-    <mergeCell ref="AX16:AZ16"/>
-    <mergeCell ref="O15:Y15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="U16:W16"/>
-    <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="B15:L15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="AO1:AY1"/>
-    <mergeCell ref="AO2:AQ2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="AB1:AL1"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AK2:AM2"/>
-    <mergeCell ref="O1:Y1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4079,34 +4101,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="24" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="48"/>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="48"/>
-      <c r="W1" s="48"/>
-      <c r="X1" s="48"/>
-      <c r="Y1" s="48"/>
-      <c r="Z1" s="48"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
     </row>
     <row r="2" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M2" s="12"/>
@@ -4168,42 +4190,42 @@
       <c r="W3" s="36"/>
     </row>
     <row r="4" spans="1:26" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="57" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="53">
+      <c r="D4" s="50">
         <v>66</v>
       </c>
-      <c r="E4" s="53">
+      <c r="E4" s="50">
         <v>66</v>
       </c>
-      <c r="F4" s="54">
+      <c r="F4" s="60">
         <v>13000</v>
       </c>
-      <c r="G4" s="53">
+      <c r="G4" s="50">
         <v>1</v>
       </c>
-      <c r="H4" s="53">
+      <c r="H4" s="50">
         <v>1</v>
       </c>
-      <c r="I4" s="53">
+      <c r="I4" s="50">
         <v>66</v>
       </c>
-      <c r="J4" s="53">
+      <c r="J4" s="50">
         <v>66</v>
       </c>
       <c r="K4" s="5">
-        <f>AVERAGE(DataExp1!B4:B13)</f>
+        <f>AVERAGE(DataExp1.1!B4:B13)</f>
         <v>23.838309041284862</v>
       </c>
       <c r="L4" s="5">
-        <f>AVERAGE(DataExp1!C4:C13)</f>
+        <f>AVERAGE(DataExp1.1!C4:C13)</f>
         <v>3.2827532251076272</v>
       </c>
       <c r="M4" s="5">
@@ -4213,7 +4235,7 @@
         <v>1.24324175218449E-3</v>
       </c>
       <c r="O4" s="14">
-        <f>AVERAGE(DataExp1!D4:D13)</f>
+        <f>AVERAGE(DataExp1.1!D4:D13)</f>
         <v>1.6688517570495538</v>
       </c>
       <c r="Q4" s="33" t="s">
@@ -4239,24 +4261,24 @@
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="50"/>
+      <c r="A5" s="58"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
       <c r="C5" s="51"/>
       <c r="D5" s="51"/>
       <c r="E5" s="51"/>
-      <c r="F5" s="55"/>
+      <c r="F5" s="54"/>
       <c r="G5" s="51"/>
       <c r="H5" s="51"/>
       <c r="I5" s="51"/>
       <c r="J5" s="51"/>
       <c r="K5" s="5">
-        <f>AVERAGE(DataExp1!E4:E13)</f>
+        <f>AVERAGE(DataExp1.1!E4:E13)</f>
         <v>11.070752653739017</v>
       </c>
       <c r="L5" s="5">
-        <f>AVERAGE(DataExp1!F4:F13)</f>
+        <f>AVERAGE(DataExp1.1!F4:F13)</f>
         <v>1.6712838772969871</v>
       </c>
       <c r="M5" s="5">
@@ -4266,7 +4288,7 @@
         <v>1.8368430572894799E-3</v>
       </c>
       <c r="O5" s="14">
-        <f>AVERAGE(DataExp1!G4:G13)</f>
+        <f>AVERAGE(DataExp1.1!G4:G13)</f>
         <v>1.6848387241363478</v>
       </c>
       <c r="Q5" t="s">
@@ -4298,24 +4320,24 @@
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="50"/>
+      <c r="A6" s="58"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
       <c r="C6" s="51"/>
       <c r="D6" s="51"/>
       <c r="E6" s="51"/>
-      <c r="F6" s="55"/>
+      <c r="F6" s="54"/>
       <c r="G6" s="51"/>
       <c r="H6" s="51"/>
       <c r="I6" s="51"/>
       <c r="J6" s="51"/>
       <c r="K6" s="5">
-        <f>AVERAGE(DataExp1!H4:H13)</f>
+        <f>AVERAGE(DataExp1.1!H4:H13)</f>
         <v>4.7480516396353174</v>
       </c>
       <c r="L6" s="5">
-        <f>AVERAGE(DataExp1!I4:I13)</f>
+        <f>AVERAGE(DataExp1.1!I4:I13)</f>
         <v>0.82681097952909732</v>
       </c>
       <c r="M6" s="5">
@@ -4325,7 +4347,7 @@
         <v>1.8680991323063701E-3</v>
       </c>
       <c r="O6" s="14">
-        <f>AVERAGE(DataExp1!J4:J13)</f>
+        <f>AVERAGE(DataExp1.1!J4:J13)</f>
         <v>1.7160061359405478</v>
       </c>
       <c r="Q6" t="s">
@@ -4357,24 +4379,24 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="50"/>
+      <c r="A7" s="58"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
       <c r="C7" s="51"/>
       <c r="D7" s="51"/>
       <c r="E7" s="51"/>
-      <c r="F7" s="55"/>
+      <c r="F7" s="54"/>
       <c r="G7" s="51"/>
       <c r="H7" s="51"/>
       <c r="I7" s="51"/>
       <c r="J7" s="51"/>
       <c r="K7" s="5">
-        <f>AVERAGE(DataExp1!K4:K13)</f>
+        <f>AVERAGE(DataExp1.1!K4:K13)</f>
         <v>0.84932664663156276</v>
       </c>
       <c r="L7" s="5">
-        <f>AVERAGE(DataExp1!L4:L13)</f>
+        <f>AVERAGE(DataExp1.1!L4:L13)</f>
         <v>0.24563346801399702</v>
       </c>
       <c r="M7" s="5">
@@ -4384,7 +4406,7 @@
         <v>1.90857404909223E-3</v>
       </c>
       <c r="O7" s="14">
-        <f>AVERAGE(DataExp1!M1:M10)</f>
+        <f>AVERAGE(DataExp1.1!M1:M10)</f>
         <v>1.740799522399898</v>
       </c>
       <c r="R7" s="35"/>
@@ -4394,14 +4416,14 @@
       <c r="W7" s="35"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="50"/>
+      <c r="A8" s="58"/>
       <c r="B8" s="6">
         <v>20</v>
       </c>
       <c r="C8" s="51"/>
       <c r="D8" s="51"/>
       <c r="E8" s="51"/>
-      <c r="F8" s="55"/>
+      <c r="F8" s="54"/>
       <c r="G8" s="51"/>
       <c r="H8" s="51"/>
       <c r="I8" s="51"/>
@@ -4418,14 +4440,14 @@
       <c r="W8" s="35"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="50"/>
+      <c r="A9" s="58"/>
       <c r="B9" s="6">
         <v>50</v>
       </c>
       <c r="C9" s="51"/>
       <c r="D9" s="51"/>
       <c r="E9" s="51"/>
-      <c r="F9" s="55"/>
+      <c r="F9" s="54"/>
       <c r="G9" s="51"/>
       <c r="H9" s="51"/>
       <c r="I9" s="51"/>
@@ -4442,14 +4464,14 @@
       <c r="W9" s="35"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="50"/>
+      <c r="A10" s="58"/>
       <c r="B10" s="6">
         <v>100</v>
       </c>
       <c r="C10" s="51"/>
       <c r="D10" s="51"/>
       <c r="E10" s="51"/>
-      <c r="F10" s="55"/>
+      <c r="F10" s="54"/>
       <c r="G10" s="51"/>
       <c r="H10" s="51"/>
       <c r="I10" s="51"/>
@@ -4497,17 +4519,17 @@
       <c r="C11" s="51"/>
       <c r="D11" s="51"/>
       <c r="E11" s="51"/>
-      <c r="F11" s="55"/>
+      <c r="F11" s="54"/>
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
       <c r="I11" s="51"/>
       <c r="J11" s="51"/>
       <c r="K11" s="4">
-        <f>AVERAGE(DataExp1!O4:O13)</f>
+        <f>AVERAGE(DataExp1.1!O4:O13)</f>
         <v>49.821904185231844</v>
       </c>
       <c r="L11" s="4">
-        <f>AVERAGE(DataExp1!P4:P13)</f>
+        <f>AVERAGE(DataExp1.1!P4:P13)</f>
         <v>6.6901005257882433</v>
       </c>
       <c r="M11" s="4">
@@ -4517,7 +4539,7 @@
         <v>1.8341564911519399E-2</v>
       </c>
       <c r="O11" s="4">
-        <f>AVERAGE(DataExp1!Q4:Q13)</f>
+        <f>AVERAGE(DataExp1.1!Q4:Q13)</f>
         <v>1.6223374366760202</v>
       </c>
     </row>
@@ -4529,17 +4551,17 @@
       <c r="C12" s="51"/>
       <c r="D12" s="51"/>
       <c r="E12" s="51"/>
-      <c r="F12" s="55"/>
+      <c r="F12" s="54"/>
       <c r="G12" s="51"/>
       <c r="H12" s="51"/>
       <c r="I12" s="51"/>
       <c r="J12" s="51"/>
       <c r="K12" s="4">
-        <f>AVERAGE(DataExp1!R4:R13)</f>
+        <f>AVERAGE(DataExp1.1!R4:R13)</f>
         <v>2.2585080679270888</v>
       </c>
       <c r="L12" s="4">
-        <f>AVERAGE(DataExp1!S4:S13)</f>
+        <f>AVERAGE(DataExp1.1!S4:S13)</f>
         <v>0.46312458447019578</v>
       </c>
       <c r="M12" s="4">
@@ -4549,7 +4571,7 @@
         <v>3.8957965924184199E-2</v>
       </c>
       <c r="O12" s="4">
-        <f>AVERAGE(DataExp1!T4:T13)</f>
+        <f>AVERAGE(DataExp1.1!T4:T13)</f>
         <v>1.6586509227752639</v>
       </c>
     </row>
@@ -4561,17 +4583,17 @@
       <c r="C13" s="51"/>
       <c r="D13" s="51"/>
       <c r="E13" s="51"/>
-      <c r="F13" s="55"/>
+      <c r="F13" s="54"/>
       <c r="G13" s="51"/>
       <c r="H13" s="51"/>
       <c r="I13" s="51"/>
       <c r="J13" s="51"/>
       <c r="K13" s="4">
-        <f>AVERAGE(DataExp1!U4:U13)</f>
+        <f>AVERAGE(DataExp1.1!U4:U13)</f>
         <v>2.4443213833989064</v>
       </c>
       <c r="L13" s="4">
-        <f>AVERAGE(DataExp1!V4:V13)</f>
+        <f>AVERAGE(DataExp1.1!V4:V13)</f>
         <v>0.67972664412295081</v>
       </c>
       <c r="M13" s="4">
@@ -4581,7 +4603,7 @@
         <v>4.1758142847234302E-2</v>
       </c>
       <c r="O13" s="4">
-        <f>AVERAGE(DataExp1!W4:W13)</f>
+        <f>AVERAGE(DataExp1.1!W4:W13)</f>
         <v>1.7100264072418159</v>
       </c>
     </row>
@@ -4593,17 +4615,17 @@
       <c r="C14" s="51"/>
       <c r="D14" s="51"/>
       <c r="E14" s="51"/>
-      <c r="F14" s="55"/>
+      <c r="F14" s="54"/>
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
       <c r="I14" s="51"/>
       <c r="J14" s="51"/>
       <c r="K14" s="4">
-        <f>AVERAGE(DataExp1!X4:X13)</f>
+        <f>AVERAGE(DataExp1.1!X4:X13)</f>
         <v>2.0470536852897636</v>
       </c>
       <c r="L14" s="4">
-        <f>AVERAGE(DataExp1!Y4:Y13)</f>
+        <f>AVERAGE(DataExp1.1!Y4:Y13)</f>
         <v>0.42174105651815957</v>
       </c>
       <c r="M14" s="4">
@@ -4613,7 +4635,7 @@
         <v>4.0673431385843499E-2</v>
       </c>
       <c r="O14" s="4">
-        <f>AVERAGE(DataExp1!Z4:Z13)</f>
+        <f>AVERAGE(DataExp1.1!Z4:Z13)</f>
         <v>1.7285686492919858</v>
       </c>
     </row>
@@ -4625,7 +4647,7 @@
       <c r="C15" s="51"/>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
-      <c r="F15" s="55"/>
+      <c r="F15" s="54"/>
       <c r="G15" s="51"/>
       <c r="H15" s="51"/>
       <c r="I15" s="51"/>
@@ -4644,7 +4666,7 @@
       <c r="C16" s="51"/>
       <c r="D16" s="51"/>
       <c r="E16" s="51"/>
-      <c r="F16" s="55"/>
+      <c r="F16" s="54"/>
       <c r="G16" s="51"/>
       <c r="H16" s="51"/>
       <c r="I16" s="51"/>
@@ -4663,7 +4685,7 @@
       <c r="C17" s="51"/>
       <c r="D17" s="51"/>
       <c r="E17" s="51"/>
-      <c r="F17" s="55"/>
+      <c r="F17" s="54"/>
       <c r="G17" s="51"/>
       <c r="H17" s="51"/>
       <c r="I17" s="51"/>
@@ -4687,7 +4709,7 @@
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="59" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="32">
@@ -4696,17 +4718,17 @@
       <c r="C18" s="51"/>
       <c r="D18" s="51"/>
       <c r="E18" s="51"/>
-      <c r="F18" s="55"/>
+      <c r="F18" s="54"/>
       <c r="G18" s="51"/>
       <c r="H18" s="51"/>
       <c r="I18" s="51"/>
       <c r="J18" s="51"/>
       <c r="K18" s="22">
-        <f>AVERAGE(DataExp1!AB4:AB13)</f>
+        <f>AVERAGE(DataExp1.1!AB4:AB13)</f>
         <v>2.0194039548285878</v>
       </c>
       <c r="L18" s="22">
-        <f>AVERAGE(DataExp1!AC4:AC13)</f>
+        <f>AVERAGE(DataExp1.1!AC4:AC13)</f>
         <v>0.37754673426285007</v>
       </c>
       <c r="M18" s="22">
@@ -4716,7 +4738,7 @@
         <v>1.32241661098872E-4</v>
       </c>
       <c r="O18" s="22">
-        <f>AVERAGE(DataExp1!AD4:AD13)</f>
+        <f>AVERAGE(DataExp1.1!AD4:AD13)</f>
         <v>0.14992039203643773</v>
       </c>
       <c r="Q18" t="s">
@@ -4736,24 +4758,24 @@
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="52"/>
+      <c r="A19" s="59"/>
       <c r="B19" s="32">
         <v>3</v>
       </c>
       <c r="C19" s="51"/>
       <c r="D19" s="51"/>
       <c r="E19" s="51"/>
-      <c r="F19" s="55"/>
+      <c r="F19" s="54"/>
       <c r="G19" s="51"/>
       <c r="H19" s="51"/>
       <c r="I19" s="51"/>
       <c r="J19" s="51"/>
       <c r="K19" s="22">
-        <f>AVERAGE(DataExp1!AE4:AE13)</f>
+        <f>AVERAGE(DataExp1.1!AE4:AE13)</f>
         <v>3.0323916470832399</v>
       </c>
       <c r="L19" s="22">
-        <f>AVERAGE(DataExp1!AF4:AF13)</f>
+        <f>AVERAGE(DataExp1.1!AF4:AF13)</f>
         <v>0.65287517616761293</v>
       </c>
       <c r="M19" s="22">
@@ -4763,7 +4785,7 @@
         <v>1.3223489288371801E-4</v>
       </c>
       <c r="O19" s="22">
-        <f>AVERAGE(DataExp1!AG4:AG13)</f>
+        <f>AVERAGE(DataExp1.1!AG4:AG13)</f>
         <v>0.15916876792907658</v>
       </c>
       <c r="Q19" t="s">
@@ -4783,24 +4805,24 @@
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A20" s="52"/>
+      <c r="A20" s="59"/>
       <c r="B20" s="32">
         <v>5</v>
       </c>
       <c r="C20" s="51"/>
       <c r="D20" s="51"/>
       <c r="E20" s="51"/>
-      <c r="F20" s="55"/>
+      <c r="F20" s="54"/>
       <c r="G20" s="51"/>
       <c r="H20" s="51"/>
       <c r="I20" s="51"/>
       <c r="J20" s="51"/>
       <c r="K20" s="22">
-        <f>AVERAGE(DataExp1!AH4:AH13)</f>
+        <f>AVERAGE(DataExp1.1!AH4:AH13)</f>
         <v>3.0970657292831891</v>
       </c>
       <c r="L20" s="22">
-        <f>AVERAGE(DataExp1!AI4:AI13)</f>
+        <f>AVERAGE(DataExp1.1!AI4:AI13)</f>
         <v>0.65291309034907874</v>
       </c>
       <c r="M20" s="22">
@@ -4810,7 +4832,7 @@
         <v>1.33917051049755E-4</v>
       </c>
       <c r="O20" s="22">
-        <f>AVERAGE(DataExp1!AJ4:AJ13)</f>
+        <f>AVERAGE(DataExp1.1!AJ4:AJ13)</f>
         <v>0.18022336959838842</v>
       </c>
       <c r="Q20" t="s">
@@ -4830,24 +4852,24 @@
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A21" s="52"/>
+      <c r="A21" s="59"/>
       <c r="B21" s="32">
         <v>10</v>
       </c>
       <c r="C21" s="51"/>
       <c r="D21" s="51"/>
       <c r="E21" s="51"/>
-      <c r="F21" s="55"/>
+      <c r="F21" s="54"/>
       <c r="G21" s="51"/>
       <c r="H21" s="51"/>
       <c r="I21" s="51"/>
       <c r="J21" s="51"/>
       <c r="K21" s="22">
-        <f>AVERAGE(DataExp1!AK4:AK13)</f>
+        <f>AVERAGE(DataExp1.1!AK4:AK13)</f>
         <v>3.0304601968108664</v>
       </c>
       <c r="L21" s="22">
-        <f>AVERAGE(DataExp1!AL4:AL13)</f>
+        <f>AVERAGE(DataExp1.1!AL4:AL13)</f>
         <v>0.65218430526407922</v>
       </c>
       <c r="M21" s="22">
@@ -4857,19 +4879,19 @@
         <v>1.33921911090507E-4</v>
       </c>
       <c r="O21" s="22">
-        <f>AVERAGE(DataExp1!AM4:AM13)</f>
+        <f>AVERAGE(DataExp1.1!AM4:AM13)</f>
         <v>0.1679047107696528</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="52"/>
+      <c r="A22" s="59"/>
       <c r="B22" s="32">
         <v>20</v>
       </c>
       <c r="C22" s="51"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
-      <c r="F22" s="55"/>
+      <c r="F22" s="54"/>
       <c r="G22" s="51"/>
       <c r="H22" s="51"/>
       <c r="I22" s="51"/>
@@ -4881,14 +4903,14 @@
       <c r="O22" s="22"/>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" s="52"/>
+      <c r="A23" s="59"/>
       <c r="B23" s="32">
         <v>50</v>
       </c>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
       <c r="E23" s="51"/>
-      <c r="F23" s="55"/>
+      <c r="F23" s="54"/>
       <c r="G23" s="51"/>
       <c r="H23" s="51"/>
       <c r="I23" s="51"/>
@@ -4900,14 +4922,14 @@
       <c r="O23" s="22"/>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" s="52"/>
+      <c r="A24" s="59"/>
       <c r="B24" s="32">
         <v>100</v>
       </c>
       <c r="C24" s="51"/>
       <c r="D24" s="51"/>
       <c r="E24" s="51"/>
-      <c r="F24" s="55"/>
+      <c r="F24" s="54"/>
       <c r="G24" s="51"/>
       <c r="H24" s="51"/>
       <c r="I24" s="51"/>
@@ -4943,17 +4965,17 @@
       <c r="C25" s="51"/>
       <c r="D25" s="51"/>
       <c r="E25" s="51"/>
-      <c r="F25" s="55"/>
+      <c r="F25" s="54"/>
       <c r="G25" s="51"/>
       <c r="H25" s="51"/>
       <c r="I25" s="51"/>
       <c r="J25" s="51"/>
       <c r="K25" s="4">
-        <f>AVERAGE(DataExp1!AO4:AO13)</f>
+        <f>AVERAGE(DataExp1.1!AO4:AO13)</f>
         <v>34.552311810658352</v>
       </c>
       <c r="L25" s="4">
-        <f>AVERAGE(DataExp1!AP4:AP13)</f>
+        <f>AVERAGE(DataExp1.1!AP4:AP13)</f>
         <v>4.575032042937762</v>
       </c>
       <c r="M25" s="4">
@@ -4963,7 +4985,7 @@
         <v>1.8093373899484099E-5</v>
       </c>
       <c r="O25" s="4">
-        <f>AVERAGE(DataExp1!AQ4:AQ13)</f>
+        <f>AVERAGE(DataExp1.1!AQ4:AQ13)</f>
         <v>1.6018030881881669</v>
       </c>
     </row>
@@ -4975,17 +4997,17 @@
       <c r="C26" s="51"/>
       <c r="D26" s="51"/>
       <c r="E26" s="51"/>
-      <c r="F26" s="55"/>
+      <c r="F26" s="54"/>
       <c r="G26" s="51"/>
       <c r="H26" s="51"/>
       <c r="I26" s="51"/>
       <c r="J26" s="51"/>
       <c r="K26" s="4">
-        <f>AVERAGE(DataExp1!AR4:AR14)</f>
+        <f>AVERAGE(DataExp1.1!AR4:AR14)</f>
         <v>1.8560190453181431</v>
       </c>
       <c r="L26" s="4">
-        <f>AVERAGE(DataExp1!AS4:AS14)</f>
+        <f>AVERAGE(DataExp1.1!AS4:AS14)</f>
         <v>0.34311024868513884</v>
       </c>
       <c r="M26" s="4">
@@ -4995,7 +5017,7 @@
         <v>2.79669169855113E-5</v>
       </c>
       <c r="O26" s="4">
-        <f>AVERAGE(DataExp1!AT4:AT13)</f>
+        <f>AVERAGE(DataExp1.1!AT4:AT13)</f>
         <v>1.6889492511749222</v>
       </c>
     </row>
@@ -5007,17 +5029,17 @@
       <c r="C27" s="51"/>
       <c r="D27" s="51"/>
       <c r="E27" s="51"/>
-      <c r="F27" s="55"/>
+      <c r="F27" s="54"/>
       <c r="G27" s="51"/>
       <c r="H27" s="51"/>
       <c r="I27" s="51"/>
       <c r="J27" s="51"/>
       <c r="K27" s="4">
-        <f>AVERAGE(DataExp1!AU4:AU13)</f>
+        <f>AVERAGE(DataExp1.1!AU4:AU13)</f>
         <v>1.9127433590347436</v>
       </c>
       <c r="L27" s="4">
-        <f>AVERAGE(DataExp1!AV4:AV13)</f>
+        <f>AVERAGE(DataExp1.1!AV4:AV13)</f>
         <v>0.35326132701310653</v>
       </c>
       <c r="M27" s="4">
@@ -5027,7 +5049,7 @@
         <v>2.8023187480955202E-5</v>
       </c>
       <c r="O27" s="4">
-        <f>AVERAGE(DataExp1!AW4:AW13)</f>
+        <f>AVERAGE(DataExp1.1!AW4:AW13)</f>
         <v>1.7003351620265386</v>
       </c>
     </row>
@@ -5039,17 +5061,17 @@
       <c r="C28" s="51"/>
       <c r="D28" s="51"/>
       <c r="E28" s="51"/>
-      <c r="F28" s="55"/>
+      <c r="F28" s="54"/>
       <c r="G28" s="51"/>
       <c r="H28" s="51"/>
       <c r="I28" s="51"/>
       <c r="J28" s="51"/>
       <c r="K28" s="4">
-        <f>AVERAGE(DataExp1!AX4:AX13)</f>
+        <f>AVERAGE(DataExp1.1!AX4:AX13)</f>
         <v>1.9259347567178799</v>
       </c>
       <c r="L28" s="4">
-        <f>AVERAGE(DataExp1!AY4:AY13)</f>
+        <f>AVERAGE(DataExp1.1!AY4:AY13)</f>
         <v>0.35326486945372448</v>
       </c>
       <c r="M28" s="4">
@@ -5059,7 +5081,7 @@
         <v>2.7971865110220399E-5</v>
       </c>
       <c r="O28" s="4">
-        <f>AVERAGE(DataExp1!AZ4:AZ13)</f>
+        <f>AVERAGE(DataExp1.1!AZ4:AZ13)</f>
         <v>1.6923342704772899</v>
       </c>
     </row>
@@ -5071,7 +5093,7 @@
       <c r="C29" s="51"/>
       <c r="D29" s="51"/>
       <c r="E29" s="51"/>
-      <c r="F29" s="55"/>
+      <c r="F29" s="54"/>
       <c r="G29" s="51"/>
       <c r="H29" s="51"/>
       <c r="I29" s="51"/>
@@ -5090,7 +5112,7 @@
       <c r="C30" s="51"/>
       <c r="D30" s="51"/>
       <c r="E30" s="51"/>
-      <c r="F30" s="55"/>
+      <c r="F30" s="54"/>
       <c r="G30" s="51"/>
       <c r="H30" s="51"/>
       <c r="I30" s="51"/>
@@ -5109,7 +5131,7 @@
       <c r="C31" s="51"/>
       <c r="D31" s="51"/>
       <c r="E31" s="51"/>
-      <c r="F31" s="53"/>
+      <c r="F31" s="50"/>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
       <c r="I31" s="51"/>
@@ -5121,7 +5143,7 @@
       <c r="O31" s="4"/>
     </row>
     <row r="32" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="57" t="s">
+      <c r="A32" s="52" t="s">
         <v>12</v>
       </c>
       <c r="B32" s="3">
@@ -5136,7 +5158,7 @@
       <c r="E32" s="51">
         <v>128</v>
       </c>
-      <c r="F32" s="58">
+      <c r="F32" s="53">
         <v>1.1200000000000001</v>
       </c>
       <c r="G32" s="51">
@@ -5152,11 +5174,11 @@
         <v>128</v>
       </c>
       <c r="K32" s="3">
-        <f>AVERAGE(DataExp1!B18:B27)</f>
+        <f>AVERAGE(DataExp1.1!B18:B27)</f>
         <v>65.766764930924992</v>
       </c>
       <c r="L32" s="3">
-        <f>AVERAGE(DataExp1!C18:C27)</f>
+        <f>AVERAGE(DataExp1.1!C18:C27)</f>
         <v>6.4421864526712369</v>
       </c>
       <c r="M32" s="4">
@@ -5191,24 +5213,24 @@
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A33" s="57"/>
+      <c r="A33" s="52"/>
       <c r="B33" s="3">
         <v>3</v>
       </c>
       <c r="C33" s="51"/>
       <c r="D33" s="51"/>
       <c r="E33" s="51"/>
-      <c r="F33" s="55"/>
+      <c r="F33" s="54"/>
       <c r="G33" s="51"/>
       <c r="H33" s="51"/>
       <c r="I33" s="51"/>
       <c r="J33" s="51"/>
       <c r="K33" s="3">
-        <f>AVERAGE(DataExp1!E18:E27)</f>
+        <f>AVERAGE(DataExp1.1!E18:E27)</f>
         <v>38.626208042487967</v>
       </c>
       <c r="L33" s="3">
-        <f>AVERAGE(DataExp1!F18:F27)</f>
+        <f>AVERAGE(DataExp1.1!F18:F27)</f>
         <v>4.0285688713895276</v>
       </c>
       <c r="M33" s="4">
@@ -5230,24 +5252,24 @@
       <c r="W33" s="35"/>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A34" s="57"/>
+      <c r="A34" s="52"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
       <c r="C34" s="51"/>
       <c r="D34" s="51"/>
       <c r="E34" s="51"/>
-      <c r="F34" s="55"/>
+      <c r="F34" s="54"/>
       <c r="G34" s="51"/>
       <c r="H34" s="51"/>
       <c r="I34" s="51"/>
       <c r="J34" s="51"/>
       <c r="K34" s="3">
-        <f>AVERAGE(DataExp1!H18:H27)</f>
+        <f>AVERAGE(DataExp1.1!H18:H27)</f>
         <v>19.080341123339618</v>
       </c>
       <c r="L34" s="3">
-        <f>AVERAGE(DataExp1!I18:I27)</f>
+        <f>AVERAGE(DataExp1.1!I18:I27)</f>
         <v>2.3385643979886401</v>
       </c>
       <c r="M34" s="4">
@@ -5269,24 +5291,24 @@
       <c r="W34" s="35"/>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A35" s="57"/>
+      <c r="A35" s="52"/>
       <c r="B35" s="3">
         <v>10</v>
       </c>
       <c r="C35" s="51"/>
       <c r="D35" s="51"/>
       <c r="E35" s="51"/>
-      <c r="F35" s="55"/>
+      <c r="F35" s="54"/>
       <c r="G35" s="51"/>
       <c r="H35" s="51"/>
       <c r="I35" s="51"/>
       <c r="J35" s="51"/>
       <c r="K35" s="3">
-        <f>AVERAGE(DataExp1!K18:K27)</f>
+        <f>AVERAGE(DataExp1.1!K18:K27)</f>
         <v>4.4322830974230261</v>
       </c>
       <c r="L35" s="3">
-        <f>AVERAGE(DataExp1!L18:L27)</f>
+        <f>AVERAGE(DataExp1.1!L18:L27)</f>
         <v>0.72280862455750228</v>
       </c>
       <c r="M35" s="4">
@@ -5305,14 +5327,14 @@
       <c r="W35" s="35"/>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A36" s="57"/>
+      <c r="A36" s="52"/>
       <c r="B36" s="3">
         <v>20</v>
       </c>
       <c r="C36" s="51"/>
       <c r="D36" s="51"/>
       <c r="E36" s="51"/>
-      <c r="F36" s="55"/>
+      <c r="F36" s="54"/>
       <c r="G36" s="51"/>
       <c r="H36" s="51"/>
       <c r="I36" s="51"/>
@@ -5329,14 +5351,14 @@
       <c r="W36" s="35"/>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A37" s="57"/>
+      <c r="A37" s="52"/>
       <c r="B37" s="3">
         <v>50</v>
       </c>
       <c r="C37" s="51"/>
       <c r="D37" s="51"/>
       <c r="E37" s="51"/>
-      <c r="F37" s="55"/>
+      <c r="F37" s="54"/>
       <c r="G37" s="51"/>
       <c r="H37" s="51"/>
       <c r="I37" s="51"/>
@@ -5353,14 +5375,14 @@
       <c r="W37" s="35"/>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="57"/>
+      <c r="A38" s="52"/>
       <c r="B38" s="3">
         <v>100</v>
       </c>
       <c r="C38" s="51"/>
       <c r="D38" s="51"/>
       <c r="E38" s="51"/>
-      <c r="F38" s="55"/>
+      <c r="F38" s="54"/>
       <c r="G38" s="51"/>
       <c r="H38" s="51"/>
       <c r="I38" s="51"/>
@@ -5377,7 +5399,7 @@
       <c r="W38" s="35"/>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A39" s="56" t="s">
+      <c r="A39" s="48" t="s">
         <v>13</v>
       </c>
       <c r="B39" s="9">
@@ -5386,17 +5408,17 @@
       <c r="C39" s="51"/>
       <c r="D39" s="51"/>
       <c r="E39" s="51"/>
-      <c r="F39" s="55"/>
+      <c r="F39" s="54"/>
       <c r="G39" s="51"/>
       <c r="H39" s="51"/>
       <c r="I39" s="51"/>
       <c r="J39" s="51"/>
       <c r="K39" s="9">
-        <f>AVERAGE(DataExp1!O18:O27)</f>
+        <f>AVERAGE(DataExp1.1!O18:O27)</f>
         <v>157.51141235842792</v>
       </c>
       <c r="L39" s="9">
-        <f>AVERAGE(DataExp1!P18:P27)</f>
+        <f>AVERAGE(DataExp1.1!P18:P27)</f>
         <v>14.53758931210613</v>
       </c>
       <c r="M39" s="14">
@@ -5410,24 +5432,24 @@
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A40" s="56"/>
+      <c r="A40" s="48"/>
       <c r="B40" s="9">
         <v>3</v>
       </c>
       <c r="C40" s="51"/>
       <c r="D40" s="51"/>
       <c r="E40" s="51"/>
-      <c r="F40" s="55"/>
+      <c r="F40" s="54"/>
       <c r="G40" s="51"/>
       <c r="H40" s="51"/>
       <c r="I40" s="51"/>
       <c r="J40" s="51"/>
       <c r="K40" s="9">
-        <f>AVERAGE(DataExp1!R18:R27)</f>
+        <f>AVERAGE(DataExp1.1!R18:R27)</f>
         <v>5.370568162007002</v>
       </c>
       <c r="L40" s="9">
-        <f>AVERAGE(DataExp1!S18:S27)</f>
+        <f>AVERAGE(DataExp1.1!S18:S27)</f>
         <v>0.75080168785316326</v>
       </c>
       <c r="M40" s="14">
@@ -5441,24 +5463,24 @@
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A41" s="56"/>
+      <c r="A41" s="48"/>
       <c r="B41" s="9">
         <v>5</v>
       </c>
       <c r="C41" s="51"/>
       <c r="D41" s="51"/>
       <c r="E41" s="51"/>
-      <c r="F41" s="55"/>
+      <c r="F41" s="54"/>
       <c r="G41" s="51"/>
       <c r="H41" s="51"/>
       <c r="I41" s="51"/>
       <c r="J41" s="51"/>
       <c r="K41" s="9">
-        <f>AVERAGE(DataExp1!U18:U27)</f>
+        <f>AVERAGE(DataExp1.1!U18:U27)</f>
         <v>6.130019567236074</v>
       </c>
       <c r="L41" s="9">
-        <f>AVERAGE(DataExp1!V18:V27)</f>
+        <f>AVERAGE(DataExp1.1!V18:V27)</f>
         <v>0.89446390885782068</v>
       </c>
       <c r="M41" s="14">
@@ -5472,24 +5494,24 @@
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A42" s="56"/>
+      <c r="A42" s="48"/>
       <c r="B42" s="9">
         <v>10</v>
       </c>
       <c r="C42" s="51"/>
       <c r="D42" s="51"/>
       <c r="E42" s="51"/>
-      <c r="F42" s="55"/>
+      <c r="F42" s="54"/>
       <c r="G42" s="51"/>
       <c r="H42" s="51"/>
       <c r="I42" s="51"/>
       <c r="J42" s="51"/>
       <c r="K42" s="9">
-        <f>AVERAGE(DataExp1!X18:X27)</f>
+        <f>AVERAGE(DataExp1.1!X18:X27)</f>
         <v>6.2926813963615427</v>
       </c>
       <c r="L42" s="9">
-        <f>AVERAGE(DataExp1!Y18:Y27)</f>
+        <f>AVERAGE(DataExp1.1!Y18:Y27)</f>
         <v>0.87768383162899821</v>
       </c>
       <c r="M42" s="14">
@@ -5503,14 +5525,14 @@
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A43" s="56"/>
+      <c r="A43" s="48"/>
       <c r="B43" s="9">
         <v>20</v>
       </c>
       <c r="C43" s="51"/>
       <c r="D43" s="51"/>
       <c r="E43" s="51"/>
-      <c r="F43" s="55"/>
+      <c r="F43" s="54"/>
       <c r="G43" s="51"/>
       <c r="H43" s="51"/>
       <c r="I43" s="51"/>
@@ -5522,14 +5544,14 @@
       <c r="O43" s="14"/>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A44" s="56"/>
+      <c r="A44" s="48"/>
       <c r="B44" s="9">
         <v>50</v>
       </c>
       <c r="C44" s="51"/>
       <c r="D44" s="51"/>
       <c r="E44" s="51"/>
-      <c r="F44" s="55"/>
+      <c r="F44" s="54"/>
       <c r="G44" s="51"/>
       <c r="H44" s="51"/>
       <c r="I44" s="51"/>
@@ -5541,14 +5563,14 @@
       <c r="O44" s="14"/>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A45" s="56"/>
+      <c r="A45" s="48"/>
       <c r="B45" s="9">
         <v>100</v>
       </c>
       <c r="C45" s="51"/>
       <c r="D45" s="51"/>
       <c r="E45" s="51"/>
-      <c r="F45" s="55"/>
+      <c r="F45" s="54"/>
       <c r="G45" s="51"/>
       <c r="H45" s="51"/>
       <c r="I45" s="51"/>
@@ -5560,7 +5582,7 @@
       <c r="O45" s="9"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A46" s="65" t="s">
+      <c r="A46" s="49" t="s">
         <v>14</v>
       </c>
       <c r="B46" s="32">
@@ -5569,17 +5591,17 @@
       <c r="C46" s="51"/>
       <c r="D46" s="51"/>
       <c r="E46" s="51"/>
-      <c r="F46" s="55"/>
+      <c r="F46" s="54"/>
       <c r="G46" s="51"/>
       <c r="H46" s="51"/>
       <c r="I46" s="51"/>
       <c r="J46" s="51"/>
       <c r="K46" s="22">
-        <f>AVERAGE(DataExp1!AB18:AB27)</f>
+        <f>AVERAGE(DataExp1.1!AB18:AB27)</f>
         <v>13.2679396369752</v>
       </c>
       <c r="L46" s="22">
-        <f>AVERAGE(DataExp1!AC18:AC27)</f>
+        <f>AVERAGE(DataExp1.1!AC18:AC27)</f>
         <v>1.5714615342167302</v>
       </c>
       <c r="M46" s="22">
@@ -5593,24 +5615,24 @@
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A47" s="65"/>
+      <c r="A47" s="49"/>
       <c r="B47" s="32">
         <v>3</v>
       </c>
       <c r="C47" s="51"/>
       <c r="D47" s="51"/>
       <c r="E47" s="51"/>
-      <c r="F47" s="55"/>
+      <c r="F47" s="54"/>
       <c r="G47" s="51"/>
       <c r="H47" s="51"/>
       <c r="I47" s="51"/>
       <c r="J47" s="51"/>
       <c r="K47" s="22">
-        <f>AVERAGE(DataExp1!AE18:AE27)</f>
+        <f>AVERAGE(DataExp1.1!AE18:AE27)</f>
         <v>1.8847515193214188</v>
       </c>
       <c r="L47" s="22">
-        <f>AVERAGE(DataExp1!AF18:AF27)</f>
+        <f>AVERAGE(DataExp1.1!AF18:AF27)</f>
         <v>0.44815003866496461</v>
       </c>
       <c r="M47" s="22">
@@ -5624,24 +5646,24 @@
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="65"/>
+      <c r="A48" s="49"/>
       <c r="B48" s="32">
         <v>5</v>
       </c>
       <c r="C48" s="51"/>
       <c r="D48" s="51"/>
       <c r="E48" s="51"/>
-      <c r="F48" s="55"/>
+      <c r="F48" s="54"/>
       <c r="G48" s="51"/>
       <c r="H48" s="51"/>
       <c r="I48" s="51"/>
       <c r="J48" s="51"/>
       <c r="K48" s="22">
-        <f>AVERAGE(DataExp1!AH18:AH27)</f>
+        <f>AVERAGE(DataExp1.1!AH18:AH27)</f>
         <v>1.9167287224860321</v>
       </c>
       <c r="L48" s="22">
-        <f>AVERAGE(DataExp1!AI18:AI27)</f>
+        <f>AVERAGE(DataExp1.1!AI18:AI27)</f>
         <v>0.473754446095489</v>
       </c>
       <c r="M48" s="22">
@@ -5655,24 +5677,24 @@
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="65"/>
-      <c r="B49" s="66">
+      <c r="A49" s="49"/>
+      <c r="B49" s="38">
         <v>10</v>
       </c>
       <c r="C49" s="51"/>
       <c r="D49" s="51"/>
       <c r="E49" s="51"/>
-      <c r="F49" s="55"/>
+      <c r="F49" s="54"/>
       <c r="G49" s="51"/>
       <c r="H49" s="51"/>
       <c r="I49" s="51"/>
       <c r="J49" s="51"/>
       <c r="K49" s="22">
-        <f>AVERAGE(DataExp1!AK18:AK27)</f>
+        <f>AVERAGE(DataExp1.1!AK18:AK27)</f>
         <v>1.9152230126798291</v>
       </c>
       <c r="L49" s="22">
-        <f>AVERAGE(DataExp1!AL18:AL27)</f>
+        <f>AVERAGE(DataExp1.1!AL18:AL27)</f>
         <v>0.473754446095489</v>
       </c>
       <c r="M49" s="22">
@@ -5686,14 +5708,14 @@
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="65"/>
-      <c r="B50" s="66">
+      <c r="A50" s="49"/>
+      <c r="B50" s="38">
         <v>20</v>
       </c>
       <c r="C50" s="51"/>
       <c r="D50" s="51"/>
       <c r="E50" s="51"/>
-      <c r="F50" s="55"/>
+      <c r="F50" s="54"/>
       <c r="G50" s="51"/>
       <c r="H50" s="51"/>
       <c r="I50" s="51"/>
@@ -5705,14 +5727,14 @@
       <c r="O50" s="22"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="65"/>
-      <c r="B51" s="66">
+      <c r="A51" s="49"/>
+      <c r="B51" s="38">
         <v>50</v>
       </c>
       <c r="C51" s="51"/>
       <c r="D51" s="51"/>
       <c r="E51" s="51"/>
-      <c r="F51" s="55"/>
+      <c r="F51" s="54"/>
       <c r="G51" s="51"/>
       <c r="H51" s="51"/>
       <c r="I51" s="51"/>
@@ -5724,14 +5746,14 @@
       <c r="O51" s="22"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="65"/>
-      <c r="B52" s="66">
+      <c r="A52" s="49"/>
+      <c r="B52" s="38">
         <v>100</v>
       </c>
       <c r="C52" s="51"/>
       <c r="D52" s="51"/>
       <c r="E52" s="51"/>
-      <c r="F52" s="55"/>
+      <c r="F52" s="54"/>
       <c r="G52" s="51"/>
       <c r="H52" s="51"/>
       <c r="I52" s="51"/>
@@ -5743,7 +5765,7 @@
       <c r="O52" s="32"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="56" t="s">
+      <c r="A53" s="48" t="s">
         <v>15</v>
       </c>
       <c r="B53" s="9">
@@ -5752,17 +5774,17 @@
       <c r="C53" s="51"/>
       <c r="D53" s="51"/>
       <c r="E53" s="51"/>
-      <c r="F53" s="55"/>
+      <c r="F53" s="54"/>
       <c r="G53" s="51"/>
       <c r="H53" s="51"/>
       <c r="I53" s="51"/>
       <c r="J53" s="51"/>
       <c r="K53" s="14">
-        <f>AVERAGE(DataExp1!AO18:AO27)</f>
+        <f>AVERAGE(DataExp1.1!AO18:AO27)</f>
         <v>59.79535904859479</v>
       </c>
       <c r="L53" s="14">
-        <f>AVERAGE(DataExp1!AP18:AP27)</f>
+        <f>AVERAGE(DataExp1.1!AP18:AP27)</f>
         <v>5.6632343066267472</v>
       </c>
       <c r="M53" s="14">
@@ -5776,24 +5798,24 @@
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="56"/>
+      <c r="A54" s="48"/>
       <c r="B54" s="9">
         <v>3</v>
       </c>
       <c r="C54" s="51"/>
       <c r="D54" s="51"/>
       <c r="E54" s="51"/>
-      <c r="F54" s="55"/>
+      <c r="F54" s="54"/>
       <c r="G54" s="51"/>
       <c r="H54" s="51"/>
       <c r="I54" s="51"/>
       <c r="J54" s="51"/>
       <c r="K54" s="14">
-        <f>AVERAGE(DataExp1!AR18:AR27)</f>
+        <f>AVERAGE(DataExp1.1!AR18:AR27)</f>
         <v>4.1994209587286191</v>
       </c>
       <c r="L54" s="14">
-        <f>AVERAGE(DataExp1!AS18:AS27)</f>
+        <f>AVERAGE(DataExp1.1!AS18:AS27)</f>
         <v>0.76532657737815013</v>
       </c>
       <c r="M54" s="14">
@@ -5807,24 +5829,24 @@
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="56"/>
+      <c r="A55" s="48"/>
       <c r="B55" s="9">
         <v>5</v>
       </c>
       <c r="C55" s="51"/>
       <c r="D55" s="51"/>
       <c r="E55" s="51"/>
-      <c r="F55" s="55"/>
+      <c r="F55" s="54"/>
       <c r="G55" s="51"/>
       <c r="H55" s="51"/>
       <c r="I55" s="51"/>
       <c r="J55" s="51"/>
       <c r="K55" s="14">
-        <f>AVERAGE(DataExp1!AU18:AU27)</f>
+        <f>AVERAGE(DataExp1.1!AU18:AU27)</f>
         <v>4.4246201292478027</v>
       </c>
       <c r="L55" s="14">
-        <f>AVERAGE(DataExp1!AV18:AV27)</f>
+        <f>AVERAGE(DataExp1.1!AV18:AV27)</f>
         <v>0.76976707295684066</v>
       </c>
       <c r="M55" s="14">
@@ -5838,24 +5860,24 @@
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="56"/>
+      <c r="A56" s="48"/>
       <c r="B56" s="9">
         <v>10</v>
       </c>
       <c r="C56" s="51"/>
       <c r="D56" s="51"/>
       <c r="E56" s="51"/>
-      <c r="F56" s="55"/>
+      <c r="F56" s="54"/>
       <c r="G56" s="51"/>
       <c r="H56" s="51"/>
       <c r="I56" s="51"/>
       <c r="J56" s="51"/>
       <c r="K56" s="14">
-        <f>AVERAGE(DataExp1!AX18:AX27)</f>
+        <f>AVERAGE(DataExp1.1!AX18:AX27)</f>
         <v>4.1938757256751718</v>
       </c>
       <c r="L56" s="14">
-        <f>AVERAGE(DataExp1!AY18:AY27)</f>
+        <f>AVERAGE(DataExp1.1!AY18:AY27)</f>
         <v>0.76280764413276991</v>
       </c>
       <c r="M56" s="14">
@@ -5869,14 +5891,14 @@
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="56"/>
+      <c r="A57" s="48"/>
       <c r="B57" s="9">
         <v>20</v>
       </c>
       <c r="C57" s="51"/>
       <c r="D57" s="51"/>
       <c r="E57" s="51"/>
-      <c r="F57" s="55"/>
+      <c r="F57" s="54"/>
       <c r="G57" s="51"/>
       <c r="H57" s="51"/>
       <c r="I57" s="51"/>
@@ -5888,14 +5910,14 @@
       <c r="O57" s="14"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="56"/>
+      <c r="A58" s="48"/>
       <c r="B58" s="9">
         <v>50</v>
       </c>
       <c r="C58" s="51"/>
       <c r="D58" s="51"/>
       <c r="E58" s="51"/>
-      <c r="F58" s="55"/>
+      <c r="F58" s="54"/>
       <c r="G58" s="51"/>
       <c r="H58" s="51"/>
       <c r="I58" s="51"/>
@@ -5907,14 +5929,14 @@
       <c r="O58" s="14"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="56"/>
+      <c r="A59" s="48"/>
       <c r="B59" s="9">
         <v>100</v>
       </c>
       <c r="C59" s="51"/>
       <c r="D59" s="51"/>
       <c r="E59" s="51"/>
-      <c r="F59" s="53"/>
+      <c r="F59" s="50"/>
       <c r="G59" s="51"/>
       <c r="H59" s="51"/>
       <c r="I59" s="51"/>
@@ -5927,6 +5949,17 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="C4:C31"/>
+    <mergeCell ref="D4:D31"/>
+    <mergeCell ref="E4:E31"/>
+    <mergeCell ref="G4:G31"/>
+    <mergeCell ref="H4:H31"/>
+    <mergeCell ref="F4:F31"/>
     <mergeCell ref="A39:A45"/>
     <mergeCell ref="A46:A52"/>
     <mergeCell ref="A53:A59"/>
@@ -5941,17 +5974,6 @@
     <mergeCell ref="I32:I59"/>
     <mergeCell ref="J32:J59"/>
     <mergeCell ref="F32:F59"/>
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="C4:C31"/>
-    <mergeCell ref="D4:D31"/>
-    <mergeCell ref="E4:E31"/>
-    <mergeCell ref="G4:G31"/>
-    <mergeCell ref="H4:H31"/>
-    <mergeCell ref="F4:F31"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5960,39 +5982,1694 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0591575D-E9A4-466E-9459-9B52AEDB3DA6}">
+  <dimension ref="B1:V55"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B1" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="21"/>
+    </row>
+    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B2" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="41"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="44"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2" s="46"/>
+      <c r="V2" s="46"/>
+    </row>
+    <row r="3" spans="2:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="V3" s="25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B4" s="4">
+        <v>1422.6486110266001</v>
+      </c>
+      <c r="C4" s="4">
+        <v>45.929811909532802</v>
+      </c>
+      <c r="D4" s="4">
+        <v>11.247503519058199</v>
+      </c>
+      <c r="E4" s="5">
+        <v>705.57961533727905</v>
+      </c>
+      <c r="F4" s="5">
+        <v>23.691616665916101</v>
+      </c>
+      <c r="G4" s="5">
+        <v>11.5416815280914</v>
+      </c>
+      <c r="H4" s="4">
+        <v>445.21466785689103</v>
+      </c>
+      <c r="I4" s="4">
+        <v>15.6372913539942</v>
+      </c>
+      <c r="J4" s="4">
+        <v>11.7682547569274</v>
+      </c>
+      <c r="K4" s="5">
+        <v>13.3974143910746</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2.8155392856069898</v>
+      </c>
+      <c r="M4" s="5">
+        <v>11.6075575351715</v>
+      </c>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
+        <v>1294.61056839975</v>
+      </c>
+      <c r="C5" s="4">
+        <v>41.8406649909926</v>
+      </c>
+      <c r="D5" s="4">
+        <v>11.650307893753</v>
+      </c>
+      <c r="E5" s="5">
+        <v>670.93315278182297</v>
+      </c>
+      <c r="F5" s="5">
+        <v>23.104074526056401</v>
+      </c>
+      <c r="G5" s="5">
+        <v>11.5775046348571</v>
+      </c>
+      <c r="H5" s="4">
+        <v>452.90528389016202</v>
+      </c>
+      <c r="I5" s="4">
+        <v>15.0143822234905</v>
+      </c>
+      <c r="J5" s="4">
+        <v>11.707543134689301</v>
+      </c>
+      <c r="K5" s="5">
+        <v>12.057505130767799</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2.5488516330603002</v>
+      </c>
+      <c r="M5" s="5">
+        <v>12.1058855056762</v>
+      </c>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
+        <v>1289.0184630184999</v>
+      </c>
+      <c r="C6" s="4">
+        <v>41.622930606020802</v>
+      </c>
+      <c r="D6" s="4">
+        <v>11.7906243801116</v>
+      </c>
+      <c r="E6" s="5">
+        <v>671.16566533489095</v>
+      </c>
+      <c r="F6" s="5">
+        <v>23.600132749285098</v>
+      </c>
+      <c r="G6" s="5">
+        <v>11.659604072570801</v>
+      </c>
+      <c r="H6" s="4">
+        <v>382.52379452736102</v>
+      </c>
+      <c r="I6" s="4">
+        <v>14.509195905931101</v>
+      </c>
+      <c r="J6" s="4">
+        <v>11.6776049137115</v>
+      </c>
+      <c r="K6" s="5">
+        <v>7.5331515490260204</v>
+      </c>
+      <c r="L6" s="5">
+        <v>2.3080679106657098</v>
+      </c>
+      <c r="M6" s="5">
+        <v>11.7908341884613</v>
+      </c>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B7" s="4">
+        <v>1296.2356591640801</v>
+      </c>
+      <c r="C7" s="4">
+        <v>41.8761359103909</v>
+      </c>
+      <c r="D7" s="4">
+        <v>11.498032569885201</v>
+      </c>
+      <c r="E7" s="5">
+        <v>708.34939001939097</v>
+      </c>
+      <c r="F7" s="5">
+        <v>24.184761438753998</v>
+      </c>
+      <c r="G7" s="5">
+        <v>11.661856651306101</v>
+      </c>
+      <c r="H7" s="4">
+        <v>447.07443383220698</v>
+      </c>
+      <c r="I7" s="4">
+        <v>15.6069913344946</v>
+      </c>
+      <c r="J7" s="4">
+        <v>11.606946945190399</v>
+      </c>
+      <c r="K7" s="5">
+        <v>9.4122964525554504</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0.97370814509023795</v>
+      </c>
+      <c r="M7" s="5">
+        <v>11.7539100646972</v>
+      </c>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
+        <v>1289.0184630184999</v>
+      </c>
+      <c r="C8" s="4">
+        <v>41.622930606020802</v>
+      </c>
+      <c r="D8" s="4">
+        <v>11.680851459503099</v>
+      </c>
+      <c r="E8" s="5">
+        <v>11.661856651306101</v>
+      </c>
+      <c r="F8" s="5">
+        <v>23.650421254514399</v>
+      </c>
+      <c r="G8" s="5">
+        <v>11.6667003631591</v>
+      </c>
+      <c r="H8" s="4">
+        <v>442.05657317955303</v>
+      </c>
+      <c r="I8" s="4">
+        <v>15.161364429356199</v>
+      </c>
+      <c r="J8" s="4">
+        <v>11.557378768920801</v>
+      </c>
+      <c r="K8" s="5">
+        <v>11.7908341884613</v>
+      </c>
+      <c r="L8" s="5">
+        <v>2.0911466787725699</v>
+      </c>
+      <c r="M8" s="5">
+        <v>11.981241464614801</v>
+      </c>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B15" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="21"/>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B16" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="41"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="44"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" s="46"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="O16" s="46"/>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="R16" s="46"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="U16" s="46"/>
+      <c r="V16" s="46"/>
+    </row>
+    <row r="17" spans="2:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M17" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="P17" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="S17" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="T17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="U17" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="V17" s="25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B18" s="4">
+        <v>3148.1656097576601</v>
+      </c>
+      <c r="C18" s="4">
+        <v>101.370852177266</v>
+      </c>
+      <c r="D18" s="4">
+        <v>11.349320650100699</v>
+      </c>
+      <c r="E18" s="5">
+        <v>59.939718548351003</v>
+      </c>
+      <c r="F18" s="5">
+        <v>2.8714548974467702</v>
+      </c>
+      <c r="G18" s="5">
+        <v>11.4287197589874</v>
+      </c>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="5">
+        <v>93.0897561041469</v>
+      </c>
+      <c r="L18" s="5">
+        <v>3.30219451723107</v>
+      </c>
+      <c r="M18" s="5">
+        <v>11.680633068084701</v>
+      </c>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B19" s="4">
+        <v>3136.4726416762201</v>
+      </c>
+      <c r="C19" s="4">
+        <v>101.013057142517</v>
+      </c>
+      <c r="D19" s="4">
+        <v>11.4921865463256</v>
+      </c>
+      <c r="E19" s="5">
+        <v>117.17191609744501</v>
+      </c>
+      <c r="F19" s="5">
+        <v>4.4313448497848</v>
+      </c>
+      <c r="G19" s="5">
+        <v>11.4343502521514</v>
+      </c>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B20" s="4">
+        <v>3223.9336295605399</v>
+      </c>
+      <c r="C20" s="4">
+        <v>103.784368659451</v>
+      </c>
+      <c r="D20" s="4">
+        <v>11.4146075248718</v>
+      </c>
+      <c r="E20" s="5">
+        <v>59.934697645427597</v>
+      </c>
+      <c r="F20" s="5">
+        <v>2.85980873415342</v>
+      </c>
+      <c r="G20" s="5">
+        <v>11.333469867706199</v>
+      </c>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B21" s="4">
+        <v>3176.5909950571599</v>
+      </c>
+      <c r="C21" s="4">
+        <v>102.31930338011099</v>
+      </c>
+      <c r="D21" s="4">
+        <v>11.3907375335693</v>
+      </c>
+      <c r="E21" s="5">
+        <v>90.807082499348098</v>
+      </c>
+      <c r="F21" s="5">
+        <v>3.33094641325548</v>
+      </c>
+      <c r="G21" s="5">
+        <v>11.471031188964799</v>
+      </c>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B22" s="4">
+        <v>3205.8088725635798</v>
+      </c>
+      <c r="C22" s="4">
+        <v>103.23590755927199</v>
+      </c>
+      <c r="D22" s="4">
+        <v>11.27503657341</v>
+      </c>
+      <c r="E22" s="5">
+        <v>50.5762968786741</v>
+      </c>
+      <c r="F22" s="5">
+        <v>2.2407280618843299</v>
+      </c>
+      <c r="G22" s="5">
+        <v>11.491828918456999</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
+      <c r="V25" s="5"/>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+      <c r="V26" s="5"/>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B29" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="47"/>
+      <c r="M29" s="21"/>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B30" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="41"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="41"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="44"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="L30" s="46"/>
+      <c r="M30" s="46"/>
+      <c r="N30" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="O30" s="46"/>
+      <c r="P30" s="46"/>
+      <c r="Q30" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="R30" s="46"/>
+      <c r="S30" s="46"/>
+      <c r="T30" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="U30" s="46"/>
+      <c r="V30" s="46"/>
+    </row>
+    <row r="31" spans="2:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G31" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M31" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="N31" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O31" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="P31" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q31" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="R31" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="S31" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="T31" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="U31" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="V31" s="25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="5">
+        <v>93.0897561041469</v>
+      </c>
+      <c r="L32" s="5">
+        <v>3.30219451723107</v>
+      </c>
+      <c r="M32" s="5">
+        <v>11.680633068084701</v>
+      </c>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+      <c r="U34" s="5"/>
+      <c r="V34" s="5"/>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
+    </row>
+    <row r="38" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="5"/>
+      <c r="U40" s="5"/>
+      <c r="V40" s="5"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="5"/>
+      <c r="T41" s="5"/>
+      <c r="U41" s="5"/>
+      <c r="V41" s="5"/>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B43" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" s="47"/>
+      <c r="D43" s="47"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="47"/>
+      <c r="G43" s="47"/>
+      <c r="H43" s="47"/>
+      <c r="I43" s="47"/>
+      <c r="J43" s="47"/>
+      <c r="K43" s="47"/>
+      <c r="L43" s="47"/>
+      <c r="M43" s="21"/>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B44" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" s="41"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F44" s="41"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" s="44"/>
+      <c r="J44" s="45"/>
+      <c r="K44" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="L44" s="46"/>
+      <c r="M44" s="46"/>
+      <c r="N44" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="O44" s="46"/>
+      <c r="P44" s="46"/>
+      <c r="Q44" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="R44" s="46"/>
+      <c r="S44" s="46"/>
+      <c r="T44" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="U44" s="46"/>
+      <c r="V44" s="46"/>
+    </row>
+    <row r="45" spans="2:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J45" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="M45" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="N45" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O45" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="P45" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q45" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="R45" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="S45" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="T45" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="U45" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="V45" s="25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="5">
+        <v>93.0897561041469</v>
+      </c>
+      <c r="L46" s="5">
+        <v>3.30219451723107</v>
+      </c>
+      <c r="M46" s="5">
+        <v>11.680633068084701</v>
+      </c>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="5"/>
+      <c r="S46" s="5"/>
+      <c r="T46" s="5"/>
+      <c r="U46" s="5"/>
+      <c r="V46" s="5"/>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="5"/>
+      <c r="R47" s="5"/>
+      <c r="S47" s="5"/>
+      <c r="T47" s="5"/>
+      <c r="U47" s="5"/>
+      <c r="V47" s="5"/>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="5"/>
+      <c r="R48" s="5"/>
+      <c r="S48" s="5"/>
+      <c r="T48" s="5"/>
+      <c r="U48" s="5"/>
+      <c r="V48" s="5"/>
+    </row>
+    <row r="49" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="5"/>
+      <c r="R49" s="5"/>
+      <c r="S49" s="5"/>
+      <c r="T49" s="5"/>
+      <c r="U49" s="5"/>
+      <c r="V49" s="5"/>
+    </row>
+    <row r="50" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="5"/>
+      <c r="R50" s="5"/>
+      <c r="S50" s="5"/>
+      <c r="T50" s="5"/>
+      <c r="U50" s="5"/>
+      <c r="V50" s="5"/>
+    </row>
+    <row r="51" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="5"/>
+      <c r="R51" s="5"/>
+      <c r="S51" s="5"/>
+      <c r="T51" s="5"/>
+      <c r="U51" s="5"/>
+      <c r="V51" s="5"/>
+    </row>
+    <row r="52" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="5"/>
+      <c r="R52" s="5"/>
+      <c r="S52" s="5"/>
+      <c r="T52" s="5"/>
+      <c r="U52" s="5"/>
+      <c r="V52" s="5"/>
+    </row>
+    <row r="53" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="5"/>
+      <c r="R53" s="5"/>
+      <c r="S53" s="5"/>
+      <c r="T53" s="5"/>
+      <c r="U53" s="5"/>
+      <c r="V53" s="5"/>
+    </row>
+    <row r="54" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="5"/>
+      <c r="R54" s="5"/>
+      <c r="S54" s="5"/>
+      <c r="T54" s="5"/>
+      <c r="U54" s="5"/>
+      <c r="V54" s="5"/>
+    </row>
+    <row r="55" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="5"/>
+      <c r="Q55" s="5"/>
+      <c r="R55" s="5"/>
+      <c r="S55" s="5"/>
+      <c r="T55" s="5"/>
+      <c r="U55" s="5"/>
+      <c r="V55" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="T30:V30"/>
+    <mergeCell ref="B43:L43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="Q44:S44"/>
+    <mergeCell ref="T44:V44"/>
+    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="B29:L29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="K30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CACBC33-D91B-42B9-AA21-9BA30A2BE58A}">
   <dimension ref="A1:Z31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="48"/>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="48"/>
-      <c r="W1" s="48"/>
-      <c r="X1" s="48"/>
-      <c r="Y1" s="48"/>
-      <c r="Z1" s="48"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
     </row>
     <row r="3" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -6042,160 +7719,122 @@
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="57" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="53" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="53">
-        <v>66</v>
-      </c>
-      <c r="E4" s="53">
-        <v>66</v>
-      </c>
-      <c r="F4" s="54">
-        <v>13000</v>
-      </c>
-      <c r="G4" s="53">
-        <v>1</v>
-      </c>
-      <c r="H4" s="53">
-        <v>1</v>
-      </c>
-      <c r="I4" s="53">
-        <v>66</v>
-      </c>
-      <c r="J4" s="53">
-        <v>66</v>
-      </c>
-      <c r="K4" s="5">
-        <f>AVERAGE(DataExp1!B4:B13)</f>
-        <v>23.838309041284862</v>
-      </c>
-      <c r="L4" s="5">
-        <f>AVERAGE(DataExp1!C4:C13)</f>
-        <v>3.2827532251076272</v>
-      </c>
+      <c r="C4" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="50">
+        <v>1025</v>
+      </c>
+      <c r="E4" s="50">
+        <v>1025</v>
+      </c>
+      <c r="F4" s="60"/>
+      <c r="G4" s="50">
+        <v>8</v>
+      </c>
+      <c r="H4" s="50">
+        <v>8</v>
+      </c>
+      <c r="I4" s="50">
+        <v>128</v>
+      </c>
+      <c r="J4" s="50">
+        <v>128</v>
+      </c>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
       <c r="M4" s="5">
-        <v>280.77705301382201</v>
+        <v>1031.6912470326899</v>
       </c>
       <c r="N4" s="17">
-        <v>1.24324175218449E-3</v>
-      </c>
-      <c r="O4" s="14">
-        <f>AVERAGE(DataExp1!D4:D13)</f>
-        <v>1.6688517570495538</v>
-      </c>
+        <v>1.07046421020007E-2</v>
+      </c>
+      <c r="O4" s="14"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="50"/>
+      <c r="A5" s="58"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
       <c r="C5" s="51"/>
       <c r="D5" s="51"/>
       <c r="E5" s="51"/>
-      <c r="F5" s="55"/>
+      <c r="F5" s="54"/>
       <c r="G5" s="51"/>
       <c r="H5" s="51"/>
       <c r="I5" s="51"/>
       <c r="J5" s="51"/>
-      <c r="K5" s="5">
-        <f>AVERAGE(DataExp1!E4:E13)</f>
-        <v>11.070752653739017</v>
-      </c>
-      <c r="L5" s="5">
-        <f>AVERAGE(DataExp1!F4:F13)</f>
-        <v>1.6712838772969871</v>
-      </c>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
       <c r="M5" s="5">
-        <v>391.23075904146799</v>
+        <v>2037.9507810980799</v>
       </c>
       <c r="N5" s="17">
-        <v>1.8368430572894799E-3</v>
-      </c>
-      <c r="O5" s="14">
-        <f>AVERAGE(DataExp1!G4:G13)</f>
-        <v>1.6848387241363478</v>
-      </c>
+        <v>2.0295988771096798E-2</v>
+      </c>
+      <c r="O5" s="14"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="50"/>
+      <c r="A6" s="58"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
       <c r="C6" s="51"/>
       <c r="D6" s="51"/>
       <c r="E6" s="51"/>
-      <c r="F6" s="55"/>
+      <c r="F6" s="54"/>
       <c r="G6" s="51"/>
       <c r="H6" s="51"/>
       <c r="I6" s="51"/>
       <c r="J6" s="51"/>
-      <c r="K6" s="5">
-        <f>AVERAGE(DataExp1!H4:H13)</f>
-        <v>4.7480516396353174</v>
-      </c>
-      <c r="L6" s="5">
-        <f>AVERAGE(DataExp1!I4:I13)</f>
-        <v>0.82681097952909732</v>
-      </c>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
       <c r="M6" s="5">
-        <v>417.59086506911302</v>
+        <v>2541.3986197788599</v>
       </c>
       <c r="N6" s="17">
-        <v>1.8680991323063701E-3</v>
-      </c>
-      <c r="O6" s="14">
-        <f>AVERAGE(DataExp1!J4:J13)</f>
-        <v>1.7160061359405478</v>
-      </c>
+        <v>2.4744345044931799E-2</v>
+      </c>
+      <c r="O6" s="14"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="50"/>
+      <c r="A7" s="58"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
       <c r="C7" s="51"/>
       <c r="D7" s="51"/>
       <c r="E7" s="51"/>
-      <c r="F7" s="55"/>
+      <c r="F7" s="54"/>
       <c r="G7" s="51"/>
       <c r="H7" s="51"/>
       <c r="I7" s="51"/>
       <c r="J7" s="51"/>
-      <c r="K7" s="5">
-        <f>AVERAGE(DataExp1!K4:K13)</f>
-        <v>0.84932664663156276</v>
-      </c>
-      <c r="L7" s="5">
-        <f>AVERAGE(DataExp1!L4:L13)</f>
-        <v>0.24563346801399702</v>
-      </c>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
       <c r="M7" s="5">
-        <v>427.43972841419099</v>
+        <v>2261.5467674711599</v>
       </c>
       <c r="N7" s="17">
-        <v>1.90857404909223E-3</v>
-      </c>
-      <c r="O7" s="14">
-        <f>AVERAGE(DataExp1!M1:M10)</f>
-        <v>1.740799522399898</v>
-      </c>
+        <v>2.1991732115827198E-2</v>
+      </c>
+      <c r="O7" s="14"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="50"/>
+      <c r="A8" s="58"/>
       <c r="B8" s="6">
         <v>20</v>
       </c>
       <c r="C8" s="51"/>
       <c r="D8" s="51"/>
       <c r="E8" s="51"/>
-      <c r="F8" s="55"/>
+      <c r="F8" s="54"/>
       <c r="G8" s="51"/>
       <c r="H8" s="51"/>
       <c r="I8" s="51"/>
@@ -6207,14 +7846,14 @@
       <c r="O8" s="14"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="50"/>
+      <c r="A9" s="58"/>
       <c r="B9" s="6">
         <v>50</v>
       </c>
       <c r="C9" s="51"/>
       <c r="D9" s="51"/>
       <c r="E9" s="51"/>
-      <c r="F9" s="55"/>
+      <c r="F9" s="54"/>
       <c r="G9" s="51"/>
       <c r="H9" s="51"/>
       <c r="I9" s="51"/>
@@ -6226,14 +7865,14 @@
       <c r="O9" s="14"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="50"/>
+      <c r="A10" s="58"/>
       <c r="B10" s="6">
         <v>100</v>
       </c>
       <c r="C10" s="51"/>
       <c r="D10" s="51"/>
       <c r="E10" s="51"/>
-      <c r="F10" s="55"/>
+      <c r="F10" s="54"/>
       <c r="G10" s="51"/>
       <c r="H10" s="51"/>
       <c r="I10" s="51"/>
@@ -6254,29 +7893,20 @@
       <c r="C11" s="51"/>
       <c r="D11" s="51"/>
       <c r="E11" s="51"/>
-      <c r="F11" s="55"/>
+      <c r="F11" s="54"/>
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
       <c r="I11" s="51"/>
       <c r="J11" s="51"/>
-      <c r="K11" s="4">
-        <f>AVERAGE(DataExp1!O4:O13)</f>
-        <v>49.821904185231844</v>
-      </c>
-      <c r="L11" s="4">
-        <f>AVERAGE(DataExp1!P4:P13)</f>
-        <v>6.6901005257882433</v>
-      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
       <c r="M11" s="4">
-        <v>38.8018530138228</v>
+        <v>142.35263472500199</v>
       </c>
       <c r="N11" s="18">
-        <v>1.8341564911519399E-2</v>
-      </c>
-      <c r="O11" s="4">
-        <f>AVERAGE(DataExp1!Q4:Q13)</f>
-        <v>1.6223374366760202</v>
-      </c>
+        <v>0.15901865598749301</v>
+      </c>
+      <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="51"/>
@@ -6286,29 +7916,20 @@
       <c r="C12" s="51"/>
       <c r="D12" s="51"/>
       <c r="E12" s="51"/>
-      <c r="F12" s="55"/>
+      <c r="F12" s="54"/>
       <c r="G12" s="51"/>
       <c r="H12" s="51"/>
       <c r="I12" s="51"/>
       <c r="J12" s="51"/>
-      <c r="K12" s="4">
-        <f>AVERAGE(DataExp1!R4:R13)</f>
-        <v>2.2585080679270888</v>
-      </c>
-      <c r="L12" s="4">
-        <f>AVERAGE(DataExp1!S4:S13)</f>
-        <v>0.46312458447019578</v>
-      </c>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
       <c r="M12" s="4">
-        <v>73.281259041468303</v>
+        <v>469.98055340577702</v>
       </c>
       <c r="N12" s="18">
-        <v>3.8957965924184199E-2</v>
-      </c>
-      <c r="O12" s="4">
-        <f>AVERAGE(DataExp1!T4:T13)</f>
-        <v>1.6586509227752639</v>
-      </c>
+        <v>0.56156655781067499</v>
+      </c>
+      <c r="O12" s="4"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="51"/>
@@ -6318,29 +7939,16 @@
       <c r="C13" s="51"/>
       <c r="D13" s="51"/>
       <c r="E13" s="51"/>
-      <c r="F13" s="55"/>
+      <c r="F13" s="54"/>
       <c r="G13" s="51"/>
       <c r="H13" s="51"/>
       <c r="I13" s="51"/>
       <c r="J13" s="51"/>
-      <c r="K13" s="4">
-        <f>AVERAGE(DataExp1!U4:U13)</f>
-        <v>2.4443213833989064</v>
-      </c>
-      <c r="L13" s="4">
-        <f>AVERAGE(DataExp1!V4:V13)</f>
-        <v>0.67972664412295081</v>
-      </c>
-      <c r="M13" s="4">
-        <v>77.092715069113893</v>
-      </c>
-      <c r="N13" s="18">
-        <v>4.1758142847234302E-2</v>
-      </c>
-      <c r="O13" s="4">
-        <f>AVERAGE(DataExp1!W4:W13)</f>
-        <v>1.7100264072418159</v>
-      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="4"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="51"/>
@@ -6350,29 +7958,20 @@
       <c r="C14" s="51"/>
       <c r="D14" s="51"/>
       <c r="E14" s="51"/>
-      <c r="F14" s="55"/>
+      <c r="F14" s="54"/>
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
       <c r="I14" s="51"/>
       <c r="J14" s="51"/>
-      <c r="K14" s="4">
-        <f>AVERAGE(DataExp1!X4:X13)</f>
-        <v>2.0470536852897636</v>
-      </c>
-      <c r="L14" s="4">
-        <f>AVERAGE(DataExp1!Y4:Y13)</f>
-        <v>0.42174105651815957</v>
-      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
       <c r="M14" s="4">
-        <v>76.300224110581993</v>
+        <v>480.725983020287</v>
       </c>
       <c r="N14" s="18">
-        <v>4.0673431385843499E-2</v>
-      </c>
-      <c r="O14" s="4">
-        <f>AVERAGE(DataExp1!Z4:Z13)</f>
-        <v>1.7285686492919858</v>
-      </c>
+        <v>0.57873323315457403</v>
+      </c>
+      <c r="O14" s="4"/>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="51"/>
@@ -6382,7 +7981,7 @@
       <c r="C15" s="51"/>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
-      <c r="F15" s="55"/>
+      <c r="F15" s="54"/>
       <c r="G15" s="51"/>
       <c r="H15" s="51"/>
       <c r="I15" s="51"/>
@@ -6401,7 +8000,7 @@
       <c r="C16" s="51"/>
       <c r="D16" s="51"/>
       <c r="E16" s="51"/>
-      <c r="F16" s="55"/>
+      <c r="F16" s="54"/>
       <c r="G16" s="51"/>
       <c r="H16" s="51"/>
       <c r="I16" s="51"/>
@@ -6420,7 +8019,7 @@
       <c r="C17" s="51"/>
       <c r="D17" s="51"/>
       <c r="E17" s="51"/>
-      <c r="F17" s="55"/>
+      <c r="F17" s="54"/>
       <c r="G17" s="51"/>
       <c r="H17" s="51"/>
       <c r="I17" s="51"/>
@@ -6432,191 +8031,139 @@
       <c r="O17" s="4"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="32">
+      <c r="B18" s="9">
         <v>1</v>
       </c>
       <c r="C18" s="51"/>
       <c r="D18" s="51"/>
       <c r="E18" s="51"/>
-      <c r="F18" s="55"/>
+      <c r="F18" s="54"/>
       <c r="G18" s="51"/>
       <c r="H18" s="51"/>
       <c r="I18" s="51"/>
       <c r="J18" s="51"/>
-      <c r="K18" s="22">
-        <f>AVERAGE(DataExp1!AB4:AB13)</f>
-        <v>2.0194039548285878</v>
-      </c>
-      <c r="L18" s="22">
-        <f>AVERAGE(DataExp1!AC4:AC13)</f>
-        <v>0.37754673426285007</v>
-      </c>
-      <c r="M18" s="22">
-        <v>4.4845012962678503E-2</v>
-      </c>
-      <c r="N18" s="23">
-        <v>1.32241661098872E-4</v>
-      </c>
-      <c r="O18" s="22">
-        <f>AVERAGE(DataExp1!AD4:AD13)</f>
-        <v>0.14992039203643773</v>
-      </c>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="14"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="52"/>
-      <c r="B19" s="32">
+      <c r="A19" s="48"/>
+      <c r="B19" s="9">
         <v>3</v>
       </c>
       <c r="C19" s="51"/>
       <c r="D19" s="51"/>
       <c r="E19" s="51"/>
-      <c r="F19" s="55"/>
+      <c r="F19" s="54"/>
       <c r="G19" s="51"/>
       <c r="H19" s="51"/>
       <c r="I19" s="51"/>
       <c r="J19" s="51"/>
-      <c r="K19" s="22">
-        <f>AVERAGE(DataExp1!AE4:AE13)</f>
-        <v>3.0323916470832399</v>
-      </c>
-      <c r="L19" s="22">
-        <f>AVERAGE(DataExp1!AF4:AF13)</f>
-        <v>0.65287517616761293</v>
-      </c>
-      <c r="M19" s="22">
-        <v>4.4845012962678503E-2</v>
-      </c>
-      <c r="N19" s="23">
-        <v>1.3223489288371801E-4</v>
-      </c>
-      <c r="O19" s="22">
-        <f>AVERAGE(DataExp1!AG4:AG13)</f>
-        <v>0.15916876792907658</v>
-      </c>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="14"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="52"/>
-      <c r="B20" s="32">
+      <c r="A20" s="48"/>
+      <c r="B20" s="9">
         <v>5</v>
       </c>
       <c r="C20" s="51"/>
       <c r="D20" s="51"/>
       <c r="E20" s="51"/>
-      <c r="F20" s="55"/>
+      <c r="F20" s="54"/>
       <c r="G20" s="51"/>
       <c r="H20" s="51"/>
       <c r="I20" s="51"/>
       <c r="J20" s="51"/>
-      <c r="K20" s="22">
-        <f>AVERAGE(DataExp1!AH4:AH13)</f>
-        <v>3.0970657292831891</v>
-      </c>
-      <c r="L20" s="22">
-        <f>AVERAGE(DataExp1!AI4:AI13)</f>
-        <v>0.65291309034907874</v>
-      </c>
-      <c r="M20" s="22">
-        <v>4.78425388880356E-2</v>
-      </c>
-      <c r="N20" s="23">
-        <v>1.33917051049755E-4</v>
-      </c>
-      <c r="O20" s="22">
-        <f>AVERAGE(DataExp1!AJ4:AJ13)</f>
-        <v>0.18022336959838842</v>
-      </c>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="14"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="52"/>
-      <c r="B21" s="32">
+      <c r="A21" s="48"/>
+      <c r="B21" s="9">
         <v>10</v>
       </c>
       <c r="C21" s="51"/>
       <c r="D21" s="51"/>
       <c r="E21" s="51"/>
-      <c r="F21" s="55"/>
+      <c r="F21" s="54"/>
       <c r="G21" s="51"/>
       <c r="H21" s="51"/>
       <c r="I21" s="51"/>
       <c r="J21" s="51"/>
-      <c r="K21" s="22">
-        <f>AVERAGE(DataExp1!AK4:AK13)</f>
-        <v>3.0304601968108664</v>
-      </c>
-      <c r="L21" s="22">
-        <f>AVERAGE(DataExp1!AL4:AL13)</f>
-        <v>0.65218430526407922</v>
-      </c>
-      <c r="M21" s="22">
-        <v>4.7875038888035598E-2</v>
-      </c>
-      <c r="N21" s="23">
-        <v>1.33921911090507E-4</v>
-      </c>
-      <c r="O21" s="22">
-        <f>AVERAGE(DataExp1!AM4:AM13)</f>
-        <v>0.1679047107696528</v>
-      </c>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="14"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="52"/>
-      <c r="B22" s="32">
+      <c r="A22" s="48"/>
+      <c r="B22" s="9">
         <v>20</v>
       </c>
       <c r="C22" s="51"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
-      <c r="F22" s="55"/>
+      <c r="F22" s="54"/>
       <c r="G22" s="51"/>
       <c r="H22" s="51"/>
       <c r="I22" s="51"/>
       <c r="J22" s="51"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="22"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="14"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="52"/>
-      <c r="B23" s="32">
+      <c r="A23" s="48"/>
+      <c r="B23" s="9">
         <v>50</v>
       </c>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
       <c r="E23" s="51"/>
-      <c r="F23" s="55"/>
+      <c r="F23" s="54"/>
       <c r="G23" s="51"/>
       <c r="H23" s="51"/>
       <c r="I23" s="51"/>
       <c r="J23" s="51"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="22"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="14"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="52"/>
-      <c r="B24" s="32">
+      <c r="A24" s="48"/>
+      <c r="B24" s="9">
         <v>100</v>
       </c>
       <c r="C24" s="51"/>
       <c r="D24" s="51"/>
       <c r="E24" s="51"/>
-      <c r="F24" s="55"/>
+      <c r="F24" s="54"/>
       <c r="G24" s="51"/>
       <c r="H24" s="51"/>
       <c r="I24" s="51"/>
       <c r="J24" s="51"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="22"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="22"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="14"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="51" t="s">
@@ -6628,29 +8175,16 @@
       <c r="C25" s="51"/>
       <c r="D25" s="51"/>
       <c r="E25" s="51"/>
-      <c r="F25" s="55"/>
+      <c r="F25" s="54"/>
       <c r="G25" s="51"/>
       <c r="H25" s="51"/>
       <c r="I25" s="51"/>
       <c r="J25" s="51"/>
-      <c r="K25" s="4">
-        <f>AVERAGE(DataExp1!AO4:AO13)</f>
-        <v>34.552311810658352</v>
-      </c>
-      <c r="L25" s="4">
-        <f>AVERAGE(DataExp1!AP4:AP13)</f>
-        <v>4.575032042937762</v>
-      </c>
-      <c r="M25" s="4">
-        <v>6.2164238822761397E-2</v>
-      </c>
-      <c r="N25" s="18">
-        <v>1.8093373899484099E-5</v>
-      </c>
-      <c r="O25" s="4">
-        <f>AVERAGE(DataExp1!AQ4:AQ13)</f>
-        <v>1.6018030881881669</v>
-      </c>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="4"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="51"/>
@@ -6660,29 +8194,16 @@
       <c r="C26" s="51"/>
       <c r="D26" s="51"/>
       <c r="E26" s="51"/>
-      <c r="F26" s="55"/>
+      <c r="F26" s="54"/>
       <c r="G26" s="51"/>
       <c r="H26" s="51"/>
       <c r="I26" s="51"/>
       <c r="J26" s="51"/>
-      <c r="K26" s="4">
-        <f>AVERAGE(DataExp1!AR4:AR14)</f>
-        <v>1.8560190453181431</v>
-      </c>
-      <c r="L26" s="4">
-        <f>AVERAGE(DataExp1!AS4:AS14)</f>
-        <v>0.34311024868513884</v>
-      </c>
-      <c r="M26" s="4">
-        <v>8.8175866468285097E-2</v>
-      </c>
-      <c r="N26" s="18">
-        <v>2.79669169855113E-5</v>
-      </c>
-      <c r="O26" s="4">
-        <f>AVERAGE(DataExp1!AT4:AT13)</f>
-        <v>1.6889492511749222</v>
-      </c>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="4"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="51"/>
@@ -6692,29 +8213,16 @@
       <c r="C27" s="51"/>
       <c r="D27" s="51"/>
       <c r="E27" s="51"/>
-      <c r="F27" s="55"/>
+      <c r="F27" s="54"/>
       <c r="G27" s="51"/>
       <c r="H27" s="51"/>
       <c r="I27" s="51"/>
       <c r="J27" s="51"/>
-      <c r="K27" s="4">
-        <f>AVERAGE(DataExp1!AU4:AU13)</f>
-        <v>1.9127433590347436</v>
-      </c>
-      <c r="L27" s="4">
-        <f>AVERAGE(DataExp1!AV4:AV13)</f>
-        <v>0.35326132701310653</v>
-      </c>
-      <c r="M27" s="4">
-        <v>8.8376119113808799E-2</v>
-      </c>
-      <c r="N27" s="18">
-        <v>2.8023187480955202E-5</v>
-      </c>
-      <c r="O27" s="4">
-        <f>AVERAGE(DataExp1!AW4:AW13)</f>
-        <v>1.7003351620265386</v>
-      </c>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="4"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="51"/>
@@ -6724,29 +8232,16 @@
       <c r="C28" s="51"/>
       <c r="D28" s="51"/>
       <c r="E28" s="51"/>
-      <c r="F28" s="55"/>
+      <c r="F28" s="54"/>
       <c r="G28" s="51"/>
       <c r="H28" s="51"/>
       <c r="I28" s="51"/>
       <c r="J28" s="51"/>
-      <c r="K28" s="4">
-        <f>AVERAGE(DataExp1!AX4:AX13)</f>
-        <v>1.9259347567178799</v>
-      </c>
-      <c r="L28" s="4">
-        <f>AVERAGE(DataExp1!AY4:AY13)</f>
-        <v>0.35326486945372448</v>
-      </c>
-      <c r="M28" s="4">
-        <v>8.81585941138084E-2</v>
-      </c>
-      <c r="N28" s="18">
-        <v>2.7971865110220399E-5</v>
-      </c>
-      <c r="O28" s="4">
-        <f>AVERAGE(DataExp1!AZ4:AZ13)</f>
-        <v>1.6923342704772899</v>
-      </c>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="4"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="51"/>
@@ -6756,7 +8251,7 @@
       <c r="C29" s="51"/>
       <c r="D29" s="51"/>
       <c r="E29" s="51"/>
-      <c r="F29" s="55"/>
+      <c r="F29" s="54"/>
       <c r="G29" s="51"/>
       <c r="H29" s="51"/>
       <c r="I29" s="51"/>
@@ -6775,7 +8270,7 @@
       <c r="C30" s="51"/>
       <c r="D30" s="51"/>
       <c r="E30" s="51"/>
-      <c r="F30" s="55"/>
+      <c r="F30" s="54"/>
       <c r="G30" s="51"/>
       <c r="H30" s="51"/>
       <c r="I30" s="51"/>
@@ -6794,7 +8289,7 @@
       <c r="C31" s="51"/>
       <c r="D31" s="51"/>
       <c r="E31" s="51"/>
-      <c r="F31" s="53"/>
+      <c r="F31" s="50"/>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
       <c r="I31" s="51"/>
@@ -6825,7 +8320,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E02A095-16D7-4FBB-B206-8C2A6F2CFB60}">
   <dimension ref="B1:BM16"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6844,164 +8339,164 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:65" x14ac:dyDescent="0.25">
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
       <c r="M1" s="21"/>
-      <c r="R1" s="46" t="s">
+      <c r="R1" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="46"/>
-      <c r="AB1" s="46"/>
-      <c r="AI1" s="46" t="s">
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
+      <c r="AA1" s="39"/>
+      <c r="AB1" s="39"/>
+      <c r="AI1" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="AJ1" s="46"/>
-      <c r="AK1" s="46"/>
-      <c r="AL1" s="46"/>
-      <c r="AM1" s="46"/>
-      <c r="AN1" s="46"/>
-      <c r="AO1" s="46"/>
-      <c r="AP1" s="46"/>
-      <c r="AQ1" s="46"/>
-      <c r="AR1" s="38"/>
-      <c r="AS1" s="38"/>
+      <c r="AJ1" s="39"/>
+      <c r="AK1" s="39"/>
+      <c r="AL1" s="39"/>
+      <c r="AM1" s="39"/>
+      <c r="AN1" s="39"/>
+      <c r="AO1" s="39"/>
+      <c r="AP1" s="39"/>
+      <c r="AQ1" s="39"/>
+      <c r="AR1" s="47"/>
+      <c r="AS1" s="47"/>
       <c r="AT1" s="21"/>
-      <c r="AY1" s="46" t="s">
+      <c r="AY1" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AZ1" s="46"/>
-      <c r="BA1" s="46"/>
-      <c r="BB1" s="46"/>
-      <c r="BC1" s="46"/>
-      <c r="BD1" s="46"/>
-      <c r="BE1" s="46"/>
-      <c r="BF1" s="46"/>
-      <c r="BG1" s="46"/>
-      <c r="BH1" s="38"/>
-      <c r="BI1" s="38"/>
+      <c r="AZ1" s="39"/>
+      <c r="BA1" s="39"/>
+      <c r="BB1" s="39"/>
+      <c r="BC1" s="39"/>
+      <c r="BD1" s="39"/>
+      <c r="BE1" s="39"/>
+      <c r="BF1" s="39"/>
+      <c r="BG1" s="39"/>
+      <c r="BH1" s="47"/>
+      <c r="BI1" s="47"/>
     </row>
     <row r="2" spans="2:65" x14ac:dyDescent="0.25">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="39" t="s">
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="40"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="42" t="s">
+      <c r="F2" s="41"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="43"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="45" t="s">
+      <c r="I2" s="44"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45" t="s">
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="R2" s="39" t="s">
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="R2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="40"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="39" t="s">
+      <c r="S2" s="41"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="40"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="42" t="s">
+      <c r="V2" s="41"/>
+      <c r="W2" s="42"/>
+      <c r="X2" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="44"/>
-      <c r="AA2" s="45" t="s">
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="AB2" s="45"/>
-      <c r="AC2" s="45"/>
-      <c r="AD2" s="45" t="s">
+      <c r="AB2" s="46"/>
+      <c r="AC2" s="46"/>
+      <c r="AD2" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="AE2" s="45"/>
-      <c r="AF2" s="45"/>
+      <c r="AE2" s="46"/>
+      <c r="AF2" s="46"/>
       <c r="AG2" s="21"/>
       <c r="AH2" s="21"/>
-      <c r="AI2" s="39" t="s">
+      <c r="AI2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="AJ2" s="40"/>
-      <c r="AK2" s="41"/>
-      <c r="AL2" s="39" t="s">
+      <c r="AJ2" s="41"/>
+      <c r="AK2" s="42"/>
+      <c r="AL2" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="AM2" s="40"/>
-      <c r="AN2" s="41"/>
-      <c r="AO2" s="42" t="s">
+      <c r="AM2" s="41"/>
+      <c r="AN2" s="42"/>
+      <c r="AO2" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="AP2" s="43"/>
-      <c r="AQ2" s="44"/>
-      <c r="AR2" s="45" t="s">
+      <c r="AP2" s="44"/>
+      <c r="AQ2" s="45"/>
+      <c r="AR2" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="AS2" s="45"/>
-      <c r="AT2" s="45"/>
-      <c r="AU2" s="45" t="s">
+      <c r="AS2" s="46"/>
+      <c r="AT2" s="46"/>
+      <c r="AU2" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="AV2" s="45"/>
-      <c r="AW2" s="45"/>
-      <c r="AY2" s="39" t="s">
+      <c r="AV2" s="46"/>
+      <c r="AW2" s="46"/>
+      <c r="AY2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="AZ2" s="40"/>
-      <c r="BA2" s="41"/>
-      <c r="BB2" s="39" t="s">
+      <c r="AZ2" s="41"/>
+      <c r="BA2" s="42"/>
+      <c r="BB2" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="BC2" s="40"/>
-      <c r="BD2" s="41"/>
-      <c r="BE2" s="42" t="s">
+      <c r="BC2" s="41"/>
+      <c r="BD2" s="42"/>
+      <c r="BE2" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="BF2" s="43"/>
-      <c r="BG2" s="44"/>
-      <c r="BH2" s="45" t="s">
+      <c r="BF2" s="44"/>
+      <c r="BG2" s="45"/>
+      <c r="BH2" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="BI2" s="45"/>
-      <c r="BJ2" s="45"/>
-      <c r="BK2" s="45" t="s">
+      <c r="BI2" s="46"/>
+      <c r="BJ2" s="46"/>
+      <c r="BK2" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="BL2" s="45"/>
-      <c r="BM2" s="45"/>
+      <c r="BL2" s="46"/>
+      <c r="BM2" s="46"/>
     </row>
     <row r="3" spans="2:65" ht="45" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -8139,6 +9634,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BH2:BJ2"/>
     <mergeCell ref="AY1:BI1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
@@ -8155,51 +9658,43 @@
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="AI2:AK2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BH2:BJ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E80E6C9-07DF-4341-ACF2-5E614276889D}">
   <dimension ref="A1:AA23"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:27" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="48"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="48"/>
-      <c r="P1" s="48"/>
-      <c r="Q1" s="48"/>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="48"/>
-      <c r="W1" s="48"/>
-      <c r="X1" s="48"/>
-      <c r="Y1" s="48"/>
-      <c r="Z1" s="48"/>
-      <c r="AA1" s="48"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
+      <c r="AA1" s="56"/>
     </row>
     <row r="3" spans="1:27" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -8243,7 +9738,7 @@
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="58" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="6">
@@ -8258,7 +9753,7 @@
       <c r="E4" s="51">
         <v>66</v>
       </c>
-      <c r="F4" s="60"/>
+      <c r="F4" s="62"/>
       <c r="G4" s="51">
         <v>1</v>
       </c>
@@ -8285,14 +9780,14 @@
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="50"/>
+      <c r="A5" s="58"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
       <c r="C5" s="51"/>
       <c r="D5" s="51"/>
       <c r="E5" s="51"/>
-      <c r="F5" s="61"/>
+      <c r="F5" s="63"/>
       <c r="G5" s="51"/>
       <c r="H5" s="51"/>
       <c r="I5" s="51"/>
@@ -8311,14 +9806,14 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="50"/>
+      <c r="A6" s="58"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
       <c r="C6" s="51"/>
       <c r="D6" s="51"/>
       <c r="E6" s="51"/>
-      <c r="F6" s="61"/>
+      <c r="F6" s="63"/>
       <c r="G6" s="51"/>
       <c r="H6" s="51"/>
       <c r="I6" s="51"/>
@@ -8337,14 +9832,14 @@
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="50"/>
+      <c r="A7" s="58"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
       <c r="C7" s="51"/>
       <c r="D7" s="51"/>
       <c r="E7" s="51"/>
-      <c r="F7" s="61"/>
+      <c r="F7" s="63"/>
       <c r="G7" s="51"/>
       <c r="H7" s="51"/>
       <c r="I7" s="51"/>
@@ -8363,14 +9858,14 @@
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="50"/>
+      <c r="A8" s="58"/>
       <c r="B8" s="6">
         <v>1000</v>
       </c>
       <c r="C8" s="51"/>
       <c r="D8" s="51"/>
       <c r="E8" s="51"/>
-      <c r="F8" s="61"/>
+      <c r="F8" s="63"/>
       <c r="G8" s="51"/>
       <c r="H8" s="51"/>
       <c r="I8" s="51"/>
@@ -8398,7 +9893,7 @@
       <c r="C9" s="51"/>
       <c r="D9" s="51"/>
       <c r="E9" s="51"/>
-      <c r="F9" s="61"/>
+      <c r="F9" s="63"/>
       <c r="G9" s="51"/>
       <c r="H9" s="51"/>
       <c r="I9" s="51"/>
@@ -8424,7 +9919,7 @@
       <c r="C10" s="51"/>
       <c r="D10" s="51"/>
       <c r="E10" s="51"/>
-      <c r="F10" s="61"/>
+      <c r="F10" s="63"/>
       <c r="G10" s="51"/>
       <c r="H10" s="51"/>
       <c r="I10" s="51"/>
@@ -8450,7 +9945,7 @@
       <c r="C11" s="51"/>
       <c r="D11" s="51"/>
       <c r="E11" s="51"/>
-      <c r="F11" s="61"/>
+      <c r="F11" s="63"/>
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
       <c r="I11" s="51"/>
@@ -8476,7 +9971,7 @@
       <c r="C12" s="51"/>
       <c r="D12" s="51"/>
       <c r="E12" s="51"/>
-      <c r="F12" s="61"/>
+      <c r="F12" s="63"/>
       <c r="G12" s="51"/>
       <c r="H12" s="51"/>
       <c r="I12" s="51"/>
@@ -8502,7 +9997,7 @@
       <c r="C13" s="51"/>
       <c r="D13" s="51"/>
       <c r="E13" s="51"/>
-      <c r="F13" s="61"/>
+      <c r="F13" s="63"/>
       <c r="G13" s="51"/>
       <c r="H13" s="51"/>
       <c r="I13" s="51"/>
@@ -8521,7 +10016,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
+      <c r="A14" s="58" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="6">
@@ -8530,7 +10025,7 @@
       <c r="C14" s="51"/>
       <c r="D14" s="51"/>
       <c r="E14" s="51"/>
-      <c r="F14" s="61"/>
+      <c r="F14" s="63"/>
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
       <c r="I14" s="51"/>
@@ -8549,14 +10044,14 @@
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="50"/>
+      <c r="A15" s="58"/>
       <c r="B15" s="6">
         <v>3</v>
       </c>
       <c r="C15" s="51"/>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
-      <c r="F15" s="61"/>
+      <c r="F15" s="63"/>
       <c r="G15" s="51"/>
       <c r="H15" s="51"/>
       <c r="I15" s="51"/>
@@ -8575,14 +10070,14 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="50"/>
+      <c r="A16" s="58"/>
       <c r="B16" s="6">
         <v>5</v>
       </c>
       <c r="C16" s="51"/>
       <c r="D16" s="51"/>
       <c r="E16" s="51"/>
-      <c r="F16" s="61"/>
+      <c r="F16" s="63"/>
       <c r="G16" s="51"/>
       <c r="H16" s="51"/>
       <c r="I16" s="51"/>
@@ -8601,14 +10096,14 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="50"/>
+      <c r="A17" s="58"/>
       <c r="B17" s="6">
         <v>10</v>
       </c>
       <c r="C17" s="51"/>
       <c r="D17" s="51"/>
       <c r="E17" s="51"/>
-      <c r="F17" s="61"/>
+      <c r="F17" s="63"/>
       <c r="G17" s="51"/>
       <c r="H17" s="51"/>
       <c r="I17" s="51"/>
@@ -8627,14 +10122,14 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="50"/>
+      <c r="A18" s="58"/>
       <c r="B18" s="6">
         <v>1000</v>
       </c>
       <c r="C18" s="51"/>
       <c r="D18" s="51"/>
       <c r="E18" s="51"/>
-      <c r="F18" s="61"/>
+      <c r="F18" s="63"/>
       <c r="G18" s="51"/>
       <c r="H18" s="51"/>
       <c r="I18" s="51"/>
@@ -8662,7 +10157,7 @@
       <c r="C19" s="51"/>
       <c r="D19" s="51"/>
       <c r="E19" s="51"/>
-      <c r="F19" s="61"/>
+      <c r="F19" s="63"/>
       <c r="G19" s="51"/>
       <c r="H19" s="51"/>
       <c r="I19" s="51"/>
@@ -8688,7 +10183,7 @@
       <c r="C20" s="51"/>
       <c r="D20" s="51"/>
       <c r="E20" s="51"/>
-      <c r="F20" s="61"/>
+      <c r="F20" s="63"/>
       <c r="G20" s="51"/>
       <c r="H20" s="51"/>
       <c r="I20" s="51"/>
@@ -8714,7 +10209,7 @@
       <c r="C21" s="51"/>
       <c r="D21" s="51"/>
       <c r="E21" s="51"/>
-      <c r="F21" s="61"/>
+      <c r="F21" s="63"/>
       <c r="G21" s="51"/>
       <c r="H21" s="51"/>
       <c r="I21" s="51"/>
@@ -8733,18 +10228,18 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="58"/>
+      <c r="A22" s="53"/>
       <c r="B22" s="10">
         <v>10</v>
       </c>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
       <c r="K22" s="31">
         <f>AVERAGE(DataExp2!BH4:BH8)</f>
         <v>2.6552692879772497</v>
@@ -8759,18 +10254,18 @@
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="59"/>
+      <c r="A23" s="61"/>
       <c r="B23" s="30">
         <v>1000</v>
       </c>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="61"/>
       <c r="K23" s="29">
         <f>AVERAGE(DataExp2!BK4:BK8)</f>
         <v>2.6966735043782979</v>
@@ -8804,7 +10299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{109AAA12-50B0-4DB2-B0E7-B06F76284A15}">
   <dimension ref="A2:L22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8851,7 +10346,7 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="65" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="6">
@@ -8866,7 +10361,7 @@
       <c r="E3" s="51">
         <v>66</v>
       </c>
-      <c r="F3" s="45"/>
+      <c r="F3" s="46"/>
       <c r="G3" s="51">
         <v>1</v>
       </c>
@@ -8887,14 +10382,14 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="64"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="6">
         <v>3</v>
       </c>
       <c r="C4" s="51"/>
       <c r="D4" s="51"/>
       <c r="E4" s="51"/>
-      <c r="F4" s="45"/>
+      <c r="F4" s="46"/>
       <c r="G4" s="51"/>
       <c r="H4" s="51"/>
       <c r="I4" s="51"/>
@@ -8907,14 +10402,14 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="64"/>
+      <c r="A5" s="66"/>
       <c r="B5" s="6">
         <v>5</v>
       </c>
       <c r="C5" s="51"/>
       <c r="D5" s="51"/>
       <c r="E5" s="51"/>
-      <c r="F5" s="45"/>
+      <c r="F5" s="46"/>
       <c r="G5" s="51"/>
       <c r="H5" s="51"/>
       <c r="I5" s="51"/>
@@ -8927,14 +10422,14 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="64"/>
+      <c r="A6" s="66"/>
       <c r="B6" s="6">
         <v>10</v>
       </c>
       <c r="C6" s="51"/>
       <c r="D6" s="51"/>
       <c r="E6" s="51"/>
-      <c r="F6" s="45"/>
+      <c r="F6" s="46"/>
       <c r="G6" s="51"/>
       <c r="H6" s="51"/>
       <c r="I6" s="51"/>
@@ -8947,14 +10442,14 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="49"/>
+      <c r="A7" s="57"/>
       <c r="B7" s="6">
         <v>100</v>
       </c>
       <c r="C7" s="51"/>
       <c r="D7" s="51"/>
       <c r="E7" s="51"/>
-      <c r="F7" s="45"/>
+      <c r="F7" s="46"/>
       <c r="G7" s="51"/>
       <c r="H7" s="51"/>
       <c r="I7" s="51"/>
@@ -8967,7 +10462,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="53" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="3">
@@ -8976,7 +10471,7 @@
       <c r="C8" s="51"/>
       <c r="D8" s="51"/>
       <c r="E8" s="51"/>
-      <c r="F8" s="45"/>
+      <c r="F8" s="46"/>
       <c r="G8" s="51"/>
       <c r="H8" s="51"/>
       <c r="I8" s="51"/>
@@ -8989,14 +10484,14 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="55"/>
+      <c r="A9" s="54"/>
       <c r="B9" s="3">
         <v>3</v>
       </c>
       <c r="C9" s="51"/>
       <c r="D9" s="51"/>
       <c r="E9" s="51"/>
-      <c r="F9" s="45"/>
+      <c r="F9" s="46"/>
       <c r="G9" s="51"/>
       <c r="H9" s="51"/>
       <c r="I9" s="51"/>
@@ -9009,14 +10504,14 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="55"/>
+      <c r="A10" s="54"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
       <c r="C10" s="51"/>
       <c r="D10" s="51"/>
       <c r="E10" s="51"/>
-      <c r="F10" s="45"/>
+      <c r="F10" s="46"/>
       <c r="G10" s="51"/>
       <c r="H10" s="51"/>
       <c r="I10" s="51"/>
@@ -9029,14 +10524,14 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="55"/>
+      <c r="A11" s="54"/>
       <c r="B11" s="3">
         <v>10</v>
       </c>
       <c r="C11" s="51"/>
       <c r="D11" s="51"/>
       <c r="E11" s="51"/>
-      <c r="F11" s="45"/>
+      <c r="F11" s="46"/>
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
       <c r="I11" s="51"/>
@@ -9049,14 +10544,14 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="53"/>
+      <c r="A12" s="50"/>
       <c r="B12" s="3">
         <v>100</v>
       </c>
       <c r="C12" s="51"/>
       <c r="D12" s="51"/>
       <c r="E12" s="51"/>
-      <c r="F12" s="45"/>
+      <c r="F12" s="46"/>
       <c r="G12" s="51"/>
       <c r="H12" s="51"/>
       <c r="I12" s="51"/>
@@ -9069,7 +10564,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="63" t="s">
+      <c r="A13" s="65" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="6">
@@ -9078,7 +10573,7 @@
       <c r="C13" s="51"/>
       <c r="D13" s="51"/>
       <c r="E13" s="51"/>
-      <c r="F13" s="45"/>
+      <c r="F13" s="46"/>
       <c r="G13" s="51"/>
       <c r="H13" s="51"/>
       <c r="I13" s="51"/>
@@ -9091,14 +10586,14 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="64"/>
+      <c r="A14" s="66"/>
       <c r="B14" s="6">
         <v>3</v>
       </c>
       <c r="C14" s="51"/>
       <c r="D14" s="51"/>
       <c r="E14" s="51"/>
-      <c r="F14" s="45"/>
+      <c r="F14" s="46"/>
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
       <c r="I14" s="51"/>
@@ -9111,14 +10606,14 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="64"/>
+      <c r="A15" s="66"/>
       <c r="B15" s="6">
         <v>5</v>
       </c>
       <c r="C15" s="51"/>
       <c r="D15" s="51"/>
       <c r="E15" s="51"/>
-      <c r="F15" s="45"/>
+      <c r="F15" s="46"/>
       <c r="G15" s="51"/>
       <c r="H15" s="51"/>
       <c r="I15" s="51"/>
@@ -9131,14 +10626,14 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="64"/>
+      <c r="A16" s="66"/>
       <c r="B16" s="6">
         <v>10</v>
       </c>
       <c r="C16" s="51"/>
       <c r="D16" s="51"/>
       <c r="E16" s="51"/>
-      <c r="F16" s="45"/>
+      <c r="F16" s="46"/>
       <c r="G16" s="51"/>
       <c r="H16" s="51"/>
       <c r="I16" s="51"/>
@@ -9151,14 +10646,14 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="49"/>
+      <c r="A17" s="57"/>
       <c r="B17" s="6">
         <v>100</v>
       </c>
       <c r="C17" s="51"/>
       <c r="D17" s="51"/>
       <c r="E17" s="51"/>
-      <c r="F17" s="45"/>
+      <c r="F17" s="46"/>
       <c r="G17" s="51"/>
       <c r="H17" s="51"/>
       <c r="I17" s="51"/>
@@ -9180,7 +10675,7 @@
       <c r="C18" s="51"/>
       <c r="D18" s="51"/>
       <c r="E18" s="51"/>
-      <c r="F18" s="45"/>
+      <c r="F18" s="46"/>
       <c r="G18" s="51"/>
       <c r="H18" s="51"/>
       <c r="I18" s="51"/>
@@ -9200,7 +10695,7 @@
       <c r="C19" s="51"/>
       <c r="D19" s="51"/>
       <c r="E19" s="51"/>
-      <c r="F19" s="45"/>
+      <c r="F19" s="46"/>
       <c r="G19" s="51"/>
       <c r="H19" s="51"/>
       <c r="I19" s="51"/>
@@ -9220,7 +10715,7 @@
       <c r="C20" s="51"/>
       <c r="D20" s="51"/>
       <c r="E20" s="51"/>
-      <c r="F20" s="45"/>
+      <c r="F20" s="46"/>
       <c r="G20" s="51"/>
       <c r="H20" s="51"/>
       <c r="I20" s="51"/>
@@ -9233,14 +10728,14 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="58"/>
+      <c r="A21" s="53"/>
       <c r="B21" s="10">
         <v>10</v>
       </c>
       <c r="C21" s="51"/>
       <c r="D21" s="51"/>
       <c r="E21" s="51"/>
-      <c r="F21" s="45"/>
+      <c r="F21" s="46"/>
       <c r="G21" s="51"/>
       <c r="H21" s="51"/>
       <c r="I21" s="51"/>
@@ -9253,14 +10748,14 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59"/>
+      <c r="A22" s="61"/>
       <c r="B22" s="30">
         <v>100</v>
       </c>
       <c r="C22" s="51"/>
       <c r="D22" s="51"/>
       <c r="E22" s="51"/>
-      <c r="F22" s="45"/>
+      <c r="F22" s="46"/>
       <c r="G22" s="51"/>
       <c r="H22" s="51"/>
       <c r="I22" s="51"/>
@@ -9292,7 +10787,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88CF955-8A08-4606-BED9-523AEA531233}">
   <dimension ref="B1:BC21"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9310,148 +10805,148 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:55" x14ac:dyDescent="0.25">
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
       <c r="M1" s="21"/>
-      <c r="R1" s="46" t="s">
+      <c r="R1" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
-      <c r="Z1" s="46"/>
-      <c r="AA1" s="46"/>
-      <c r="AB1" s="46"/>
-      <c r="AE1" s="46" t="s">
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
+      <c r="AA1" s="39"/>
+      <c r="AB1" s="39"/>
+      <c r="AE1" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" s="46"/>
-      <c r="AG1" s="46"/>
-      <c r="AH1" s="46"/>
-      <c r="AI1" s="46"/>
-      <c r="AJ1" s="46"/>
-      <c r="AK1" s="46"/>
-      <c r="AL1" s="46"/>
-      <c r="AM1" s="46"/>
-      <c r="AN1" s="38"/>
-      <c r="AO1" s="38"/>
+      <c r="AF1" s="39"/>
+      <c r="AG1" s="39"/>
+      <c r="AH1" s="39"/>
+      <c r="AI1" s="39"/>
+      <c r="AJ1" s="39"/>
+      <c r="AK1" s="39"/>
+      <c r="AL1" s="39"/>
+      <c r="AM1" s="39"/>
+      <c r="AN1" s="47"/>
+      <c r="AO1" s="47"/>
       <c r="AP1" s="21"/>
-      <c r="AR1" s="46" t="s">
+      <c r="AR1" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AS1" s="46"/>
-      <c r="AT1" s="46"/>
-      <c r="AU1" s="46"/>
-      <c r="AV1" s="46"/>
-      <c r="AW1" s="46"/>
-      <c r="AX1" s="46"/>
-      <c r="AY1" s="46"/>
-      <c r="AZ1" s="46"/>
-      <c r="BA1" s="38"/>
-      <c r="BB1" s="38"/>
+      <c r="AS1" s="39"/>
+      <c r="AT1" s="39"/>
+      <c r="AU1" s="39"/>
+      <c r="AV1" s="39"/>
+      <c r="AW1" s="39"/>
+      <c r="AX1" s="39"/>
+      <c r="AY1" s="39"/>
+      <c r="AZ1" s="39"/>
+      <c r="BA1" s="47"/>
+      <c r="BB1" s="47"/>
     </row>
     <row r="2" spans="2:55" x14ac:dyDescent="0.25">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="39" t="s">
+      <c r="C2" s="41"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="40"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="42" t="s">
+      <c r="F2" s="41"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="43"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="45" t="s">
+      <c r="I2" s="44"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45" t="s">
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="R2" s="39" t="s">
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="R2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="40"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="39" t="s">
+      <c r="S2" s="41"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="40"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="42" t="s">
+      <c r="V2" s="41"/>
+      <c r="W2" s="42"/>
+      <c r="X2" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="44"/>
-      <c r="AA2" s="45" t="s">
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="AB2" s="45"/>
-      <c r="AC2" s="45"/>
+      <c r="AB2" s="46"/>
+      <c r="AC2" s="46"/>
       <c r="AD2" s="21"/>
-      <c r="AE2" s="39" t="s">
+      <c r="AE2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="AF2" s="40"/>
-      <c r="AG2" s="41"/>
-      <c r="AH2" s="39" t="s">
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="42"/>
+      <c r="AH2" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="AI2" s="40"/>
-      <c r="AJ2" s="41"/>
-      <c r="AK2" s="42" t="s">
+      <c r="AI2" s="41"/>
+      <c r="AJ2" s="42"/>
+      <c r="AK2" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="AL2" s="43"/>
-      <c r="AM2" s="44"/>
-      <c r="AN2" s="45" t="s">
+      <c r="AL2" s="44"/>
+      <c r="AM2" s="45"/>
+      <c r="AN2" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="AO2" s="45"/>
-      <c r="AP2" s="45"/>
-      <c r="AR2" s="39" t="s">
+      <c r="AO2" s="46"/>
+      <c r="AP2" s="46"/>
+      <c r="AR2" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="AS2" s="40"/>
-      <c r="AT2" s="41"/>
-      <c r="AU2" s="39" t="s">
+      <c r="AS2" s="41"/>
+      <c r="AT2" s="42"/>
+      <c r="AU2" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="AV2" s="40"/>
-      <c r="AW2" s="41"/>
-      <c r="AX2" s="42" t="s">
+      <c r="AV2" s="41"/>
+      <c r="AW2" s="42"/>
+      <c r="AX2" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="AY2" s="43"/>
-      <c r="AZ2" s="44"/>
-      <c r="BA2" s="45" t="s">
+      <c r="AY2" s="44"/>
+      <c r="AZ2" s="45"/>
+      <c r="BA2" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="BB2" s="45"/>
-      <c r="BC2" s="45"/>
+      <c r="BB2" s="46"/>
+      <c r="BC2" s="46"/>
     </row>
     <row r="3" spans="2:55" ht="45" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -10181,6 +11676,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="AN2:AP2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
     <mergeCell ref="AK2:AM2"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="R1:AB1"/>
@@ -10197,31 +11697,26 @@
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AE2:AG2"/>
     <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AN2:AP2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10450,6 +11945,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58C277AC-42DD-4338-BD2A-AF7ECB0689E8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -10462,14 +11965,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/documents/ExperimentData.xlsx
+++ b/documents/ExperimentData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1b2bcfbbb34c0c/Documents/GitHub/meliso/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1943" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDC8AC79-796B-4BCF-B7F0-9A80331168E2}"/>
+  <xr:revisionPtr revIDLastSave="2154" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{823E71BB-C26D-4C1B-9EEC-0DE850420BDB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
   </bookViews>
   <sheets>
     <sheet name="DataExp1.1" sheetId="2" r:id="rId1"/>
@@ -511,7 +511,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -535,29 +535,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -571,10 +550,31 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -949,60 +949,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
       <c r="M1" s="21"/>
-      <c r="O1" s="39" t="s">
+      <c r="O1" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="AB1" s="39" t="s">
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="AB1" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="AC1" s="39"/>
-      <c r="AD1" s="39"/>
-      <c r="AE1" s="39"/>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="39"/>
-      <c r="AH1" s="39"/>
-      <c r="AI1" s="39"/>
-      <c r="AJ1" s="39"/>
-      <c r="AK1" s="47"/>
-      <c r="AL1" s="47"/>
+      <c r="AC1" s="47"/>
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="47"/>
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="47"/>
+      <c r="AJ1" s="47"/>
+      <c r="AK1" s="39"/>
+      <c r="AL1" s="39"/>
       <c r="AM1" s="21"/>
-      <c r="AO1" s="39" t="s">
+      <c r="AO1" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="AP1" s="39"/>
-      <c r="AQ1" s="39"/>
-      <c r="AR1" s="39"/>
-      <c r="AS1" s="39"/>
-      <c r="AT1" s="39"/>
-      <c r="AU1" s="39"/>
-      <c r="AV1" s="39"/>
-      <c r="AW1" s="39"/>
-      <c r="AX1" s="47"/>
-      <c r="AY1" s="47"/>
+      <c r="AP1" s="47"/>
+      <c r="AQ1" s="47"/>
+      <c r="AR1" s="47"/>
+      <c r="AS1" s="47"/>
+      <c r="AT1" s="47"/>
+      <c r="AU1" s="47"/>
+      <c r="AV1" s="47"/>
+      <c r="AW1" s="47"/>
+      <c r="AX1" s="39"/>
+      <c r="AY1" s="39"/>
     </row>
     <row r="2" spans="2:52" x14ac:dyDescent="0.25">
       <c r="B2" s="40" t="s">
@@ -2574,60 +2574,60 @@
       <c r="D14" s="7"/>
     </row>
     <row r="15" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
       <c r="M15" s="21"/>
-      <c r="O15" s="39" t="s">
+      <c r="O15" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="39"/>
-      <c r="R15" s="39"/>
-      <c r="S15" s="39"/>
-      <c r="T15" s="39"/>
-      <c r="U15" s="39"/>
-      <c r="V15" s="39"/>
-      <c r="W15" s="39"/>
-      <c r="X15" s="39"/>
-      <c r="Y15" s="39"/>
-      <c r="AB15" s="39" t="s">
+      <c r="P15" s="47"/>
+      <c r="Q15" s="47"/>
+      <c r="R15" s="47"/>
+      <c r="S15" s="47"/>
+      <c r="T15" s="47"/>
+      <c r="U15" s="47"/>
+      <c r="V15" s="47"/>
+      <c r="W15" s="47"/>
+      <c r="X15" s="47"/>
+      <c r="Y15" s="47"/>
+      <c r="AB15" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="AC15" s="39"/>
-      <c r="AD15" s="39"/>
-      <c r="AE15" s="39"/>
-      <c r="AF15" s="39"/>
-      <c r="AG15" s="39"/>
-      <c r="AH15" s="39"/>
-      <c r="AI15" s="39"/>
-      <c r="AJ15" s="39"/>
-      <c r="AK15" s="39"/>
-      <c r="AL15" s="39"/>
+      <c r="AC15" s="47"/>
+      <c r="AD15" s="47"/>
+      <c r="AE15" s="47"/>
+      <c r="AF15" s="47"/>
+      <c r="AG15" s="47"/>
+      <c r="AH15" s="47"/>
+      <c r="AI15" s="47"/>
+      <c r="AJ15" s="47"/>
+      <c r="AK15" s="47"/>
+      <c r="AL15" s="47"/>
       <c r="AM15" s="21"/>
-      <c r="AO15" s="39" t="s">
+      <c r="AO15" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="AP15" s="39"/>
-      <c r="AQ15" s="39"/>
-      <c r="AR15" s="39"/>
-      <c r="AS15" s="39"/>
-      <c r="AT15" s="39"/>
-      <c r="AU15" s="39"/>
-      <c r="AV15" s="39"/>
-      <c r="AW15" s="39"/>
-      <c r="AX15" s="39"/>
-      <c r="AY15" s="39"/>
+      <c r="AP15" s="47"/>
+      <c r="AQ15" s="47"/>
+      <c r="AR15" s="47"/>
+      <c r="AS15" s="47"/>
+      <c r="AT15" s="47"/>
+      <c r="AU15" s="47"/>
+      <c r="AV15" s="47"/>
+      <c r="AW15" s="47"/>
+      <c r="AX15" s="47"/>
+      <c r="AY15" s="47"/>
     </row>
     <row r="16" spans="2:52" x14ac:dyDescent="0.25">
       <c r="B16" s="40" t="s">
@@ -4026,46 +4026,46 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="AB15:AL15"/>
+    <mergeCell ref="AB16:AD16"/>
+    <mergeCell ref="AE16:AG16"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AK16:AM16"/>
+    <mergeCell ref="AO15:AY15"/>
+    <mergeCell ref="AO16:AQ16"/>
+    <mergeCell ref="AR16:AT16"/>
+    <mergeCell ref="AU16:AW16"/>
+    <mergeCell ref="AX16:AZ16"/>
+    <mergeCell ref="O15:Y15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="U16:W16"/>
+    <mergeCell ref="X16:Z16"/>
+    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="AO1:AY1"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="AB1:AL1"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AK2:AM2"/>
+    <mergeCell ref="O1:Y1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="O1:Y1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AB1:AL1"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AK2:AM2"/>
-    <mergeCell ref="AO1:AY1"/>
-    <mergeCell ref="AO2:AQ2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="B15:L15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="O15:Y15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="U16:W16"/>
-    <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="AO15:AY15"/>
-    <mergeCell ref="AO16:AQ16"/>
-    <mergeCell ref="AR16:AT16"/>
-    <mergeCell ref="AU16:AW16"/>
-    <mergeCell ref="AX16:AZ16"/>
-    <mergeCell ref="AB15:AL15"/>
-    <mergeCell ref="AB16:AD16"/>
-    <mergeCell ref="AE16:AG16"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AK16:AM16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4101,34 +4101,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="24" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="56"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
     </row>
     <row r="2" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M2" s="12"/>
@@ -4190,34 +4190,34 @@
       <c r="W3" s="36"/>
     </row>
     <row r="4" spans="1:26" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="50" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="50">
+      <c r="D4" s="54">
         <v>66</v>
       </c>
-      <c r="E4" s="50">
+      <c r="E4" s="54">
         <v>66</v>
       </c>
-      <c r="F4" s="60">
+      <c r="F4" s="55">
         <v>13000</v>
       </c>
-      <c r="G4" s="50">
+      <c r="G4" s="54">
         <v>1</v>
       </c>
-      <c r="H4" s="50">
+      <c r="H4" s="54">
         <v>1</v>
       </c>
-      <c r="I4" s="50">
+      <c r="I4" s="54">
         <v>66</v>
       </c>
-      <c r="J4" s="50">
+      <c r="J4" s="54">
         <v>66</v>
       </c>
       <c r="K4" s="5">
@@ -4261,18 +4261,18 @@
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="58"/>
+      <c r="A5" s="51"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
       <c r="K5" s="5">
         <f>AVERAGE(DataExp1.1!E4:E13)</f>
         <v>11.070752653739017</v>
@@ -4320,18 +4320,18 @@
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="58"/>
+      <c r="A6" s="51"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
       <c r="K6" s="5">
         <f>AVERAGE(DataExp1.1!H4:H13)</f>
         <v>4.7480516396353174</v>
@@ -4379,18 +4379,18 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="58"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
       <c r="K7" s="5">
         <f>AVERAGE(DataExp1.1!K4:K13)</f>
         <v>0.84932664663156276</v>
@@ -4416,18 +4416,18 @@
       <c r="W7" s="35"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="58"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="6">
         <v>20</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
@@ -4440,18 +4440,18 @@
       <c r="W8" s="35"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="58"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="6">
         <v>50</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -4464,18 +4464,18 @@
       <c r="W9" s="35"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="58"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="6">
         <v>100</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
@@ -4510,20 +4510,20 @@
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="51" t="s">
+      <c r="A11" s="52" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
       <c r="K11" s="4">
         <f>AVERAGE(DataExp1.1!O4:O13)</f>
         <v>49.821904185231844</v>
@@ -4544,18 +4544,18 @@
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="51"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="3">
         <v>3</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
       <c r="K12" s="4">
         <f>AVERAGE(DataExp1.1!R4:R13)</f>
         <v>2.2585080679270888</v>
@@ -4576,18 +4576,18 @@
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="51"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="3">
         <v>5</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
       <c r="K13" s="4">
         <f>AVERAGE(DataExp1.1!U4:U13)</f>
         <v>2.4443213833989064</v>
@@ -4608,18 +4608,18 @@
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="51"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="3">
         <v>10</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
       <c r="K14" s="4">
         <f>AVERAGE(DataExp1.1!X4:X13)</f>
         <v>2.0470536852897636</v>
@@ -4640,18 +4640,18 @@
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="51"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="3">
         <v>20</v>
       </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="52"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -4659,18 +4659,18 @@
       <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="51"/>
+      <c r="A16" s="52"/>
       <c r="B16" s="3">
         <v>50</v>
       </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="52"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -4678,18 +4678,18 @@
       <c r="O16" s="4"/>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="51"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="3">
         <v>100</v>
       </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -4709,20 +4709,20 @@
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="59" t="s">
+      <c r="A18" s="53" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="32">
         <v>1</v>
       </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
       <c r="K18" s="22">
         <f>AVERAGE(DataExp1.1!AB4:AB13)</f>
         <v>2.0194039548285878</v>
@@ -4758,18 +4758,18 @@
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="59"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="32">
         <v>3</v>
       </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
       <c r="K19" s="22">
         <f>AVERAGE(DataExp1.1!AE4:AE13)</f>
         <v>3.0323916470832399</v>
@@ -4805,18 +4805,18 @@
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A20" s="59"/>
+      <c r="A20" s="53"/>
       <c r="B20" s="32">
         <v>5</v>
       </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="52"/>
       <c r="K20" s="22">
         <f>AVERAGE(DataExp1.1!AH4:AH13)</f>
         <v>3.0970657292831891</v>
@@ -4852,18 +4852,18 @@
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A21" s="59"/>
+      <c r="A21" s="53"/>
       <c r="B21" s="32">
         <v>10</v>
       </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
       <c r="K21" s="22">
         <f>AVERAGE(DataExp1.1!AK4:AK13)</f>
         <v>3.0304601968108664</v>
@@ -4884,18 +4884,18 @@
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="59"/>
+      <c r="A22" s="53"/>
       <c r="B22" s="32">
         <v>20</v>
       </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="52"/>
       <c r="K22" s="22"/>
       <c r="L22" s="22"/>
       <c r="M22" s="22"/>
@@ -4903,18 +4903,18 @@
       <c r="O22" s="22"/>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" s="59"/>
+      <c r="A23" s="53"/>
       <c r="B23" s="32">
         <v>50</v>
       </c>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="52"/>
       <c r="K23" s="22"/>
       <c r="L23" s="22"/>
       <c r="M23" s="22"/>
@@ -4922,18 +4922,18 @@
       <c r="O23" s="22"/>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" s="59"/>
+      <c r="A24" s="53"/>
       <c r="B24" s="32">
         <v>100</v>
       </c>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="51"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="52"/>
       <c r="K24" s="22"/>
       <c r="L24" s="22"/>
       <c r="M24" s="22"/>
@@ -4956,20 +4956,20 @@
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A25" s="51" t="s">
+      <c r="A25" s="52" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="3">
         <v>1</v>
       </c>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="51"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="52"/>
       <c r="K25" s="4">
         <f>AVERAGE(DataExp1.1!AO4:AO13)</f>
         <v>34.552311810658352</v>
@@ -4990,18 +4990,18 @@
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A26" s="51"/>
+      <c r="A26" s="52"/>
       <c r="B26" s="3">
         <v>3</v>
       </c>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="51"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="52"/>
       <c r="K26" s="4">
         <f>AVERAGE(DataExp1.1!AR4:AR14)</f>
         <v>1.8560190453181431</v>
@@ -5022,18 +5022,18 @@
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A27" s="51"/>
+      <c r="A27" s="52"/>
       <c r="B27" s="3">
         <v>5</v>
       </c>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="51"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
       <c r="K27" s="4">
         <f>AVERAGE(DataExp1.1!AU4:AU13)</f>
         <v>1.9127433590347436</v>
@@ -5054,18 +5054,18 @@
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A28" s="51"/>
+      <c r="A28" s="52"/>
       <c r="B28" s="3">
         <v>10</v>
       </c>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="51"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="52"/>
       <c r="K28" s="4">
         <f>AVERAGE(DataExp1.1!AX4:AX13)</f>
         <v>1.9259347567178799</v>
@@ -5086,18 +5086,18 @@
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A29" s="51"/>
+      <c r="A29" s="52"/>
       <c r="B29" s="3">
         <v>20</v>
       </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="52"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -5105,18 +5105,18 @@
       <c r="O29" s="4"/>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A30" s="51"/>
+      <c r="A30" s="52"/>
       <c r="B30" s="3">
         <v>50</v>
       </c>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -5124,18 +5124,18 @@
       <c r="O30" s="4"/>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A31" s="51"/>
+      <c r="A31" s="52"/>
       <c r="B31" s="3">
         <v>100</v>
       </c>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="52"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -5143,34 +5143,34 @@
       <c r="O31" s="4"/>
     </row>
     <row r="32" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="52" t="s">
+      <c r="A32" s="59" t="s">
         <v>12</v>
       </c>
       <c r="B32" s="3">
         <v>1</v>
       </c>
-      <c r="C32" s="51" t="s">
+      <c r="C32" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="51">
+      <c r="D32" s="52">
         <v>128</v>
       </c>
-      <c r="E32" s="51">
+      <c r="E32" s="52">
         <v>128</v>
       </c>
-      <c r="F32" s="53">
+      <c r="F32" s="60">
         <v>1.1200000000000001</v>
       </c>
-      <c r="G32" s="51">
+      <c r="G32" s="52">
         <v>1</v>
       </c>
-      <c r="H32" s="51">
+      <c r="H32" s="52">
         <v>1</v>
       </c>
-      <c r="I32" s="51">
+      <c r="I32" s="52">
         <v>128</v>
       </c>
-      <c r="J32" s="51">
+      <c r="J32" s="52">
         <v>128</v>
       </c>
       <c r="K32" s="3">
@@ -5213,18 +5213,18 @@
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A33" s="52"/>
+      <c r="A33" s="59"/>
       <c r="B33" s="3">
         <v>3</v>
       </c>
-      <c r="C33" s="51"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="51"/>
-      <c r="J33" s="51"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="52"/>
       <c r="K33" s="3">
         <f>AVERAGE(DataExp1.1!E18:E27)</f>
         <v>38.626208042487967</v>
@@ -5252,18 +5252,18 @@
       <c r="W33" s="35"/>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A34" s="52"/>
+      <c r="A34" s="59"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="54"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="51"/>
-      <c r="I34" s="51"/>
-      <c r="J34" s="51"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
       <c r="K34" s="3">
         <f>AVERAGE(DataExp1.1!H18:H27)</f>
         <v>19.080341123339618</v>
@@ -5291,18 +5291,18 @@
       <c r="W34" s="35"/>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A35" s="52"/>
+      <c r="A35" s="59"/>
       <c r="B35" s="3">
         <v>10</v>
       </c>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="54"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
-      <c r="J35" s="51"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
       <c r="K35" s="3">
         <f>AVERAGE(DataExp1.1!K18:K27)</f>
         <v>4.4322830974230261</v>
@@ -5327,18 +5327,18 @@
       <c r="W35" s="35"/>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A36" s="52"/>
+      <c r="A36" s="59"/>
       <c r="B36" s="3">
         <v>20</v>
       </c>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
-      <c r="J36" s="51"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="52"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="4"/>
@@ -5351,18 +5351,18 @@
       <c r="W36" s="35"/>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A37" s="52"/>
+      <c r="A37" s="59"/>
       <c r="B37" s="3">
         <v>50</v>
       </c>
-      <c r="C37" s="51"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="52"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="4"/>
@@ -5375,18 +5375,18 @@
       <c r="W37" s="35"/>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="52"/>
+      <c r="A38" s="59"/>
       <c r="B38" s="3">
         <v>100</v>
       </c>
-      <c r="C38" s="51"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="51"/>
-      <c r="J38" s="51"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="4"/>
@@ -5399,20 +5399,20 @@
       <c r="W38" s="35"/>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A39" s="48" t="s">
+      <c r="A39" s="57" t="s">
         <v>13</v>
       </c>
       <c r="B39" s="9">
         <v>1</v>
       </c>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="54"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="51"/>
-      <c r="J39" s="51"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="52"/>
       <c r="K39" s="9">
         <f>AVERAGE(DataExp1.1!O18:O27)</f>
         <v>157.51141235842792</v>
@@ -5432,18 +5432,18 @@
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A40" s="48"/>
+      <c r="A40" s="57"/>
       <c r="B40" s="9">
         <v>3</v>
       </c>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="54"/>
-      <c r="G40" s="51"/>
-      <c r="H40" s="51"/>
-      <c r="I40" s="51"/>
-      <c r="J40" s="51"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
       <c r="K40" s="9">
         <f>AVERAGE(DataExp1.1!R18:R27)</f>
         <v>5.370568162007002</v>
@@ -5463,18 +5463,18 @@
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A41" s="48"/>
+      <c r="A41" s="57"/>
       <c r="B41" s="9">
         <v>5</v>
       </c>
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="51"/>
-      <c r="H41" s="51"/>
-      <c r="I41" s="51"/>
-      <c r="J41" s="51"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="52"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="52"/>
       <c r="K41" s="9">
         <f>AVERAGE(DataExp1.1!U18:U27)</f>
         <v>6.130019567236074</v>
@@ -5494,18 +5494,18 @@
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A42" s="48"/>
+      <c r="A42" s="57"/>
       <c r="B42" s="9">
         <v>10</v>
       </c>
-      <c r="C42" s="51"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="54"/>
-      <c r="G42" s="51"/>
-      <c r="H42" s="51"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="51"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
       <c r="K42" s="9">
         <f>AVERAGE(DataExp1.1!X18:X27)</f>
         <v>6.2926813963615427</v>
@@ -5525,18 +5525,18 @@
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A43" s="48"/>
+      <c r="A43" s="57"/>
       <c r="B43" s="9">
         <v>20</v>
       </c>
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="54"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="51"/>
-      <c r="I43" s="51"/>
-      <c r="J43" s="51"/>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="52"/>
+      <c r="H43" s="52"/>
+      <c r="I43" s="52"/>
+      <c r="J43" s="52"/>
       <c r="K43" s="9"/>
       <c r="L43" s="9"/>
       <c r="M43" s="14"/>
@@ -5544,18 +5544,18 @@
       <c r="O43" s="14"/>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A44" s="48"/>
+      <c r="A44" s="57"/>
       <c r="B44" s="9">
         <v>50</v>
       </c>
-      <c r="C44" s="51"/>
-      <c r="D44" s="51"/>
-      <c r="E44" s="51"/>
-      <c r="F44" s="54"/>
-      <c r="G44" s="51"/>
-      <c r="H44" s="51"/>
-      <c r="I44" s="51"/>
-      <c r="J44" s="51"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="52"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
       <c r="K44" s="9"/>
       <c r="L44" s="9"/>
       <c r="M44" s="14"/>
@@ -5563,18 +5563,18 @@
       <c r="O44" s="14"/>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A45" s="48"/>
+      <c r="A45" s="57"/>
       <c r="B45" s="9">
         <v>100</v>
       </c>
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="54"/>
-      <c r="G45" s="51"/>
-      <c r="H45" s="51"/>
-      <c r="I45" s="51"/>
-      <c r="J45" s="51"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="52"/>
+      <c r="H45" s="52"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="52"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
       <c r="M45" s="14"/>
@@ -5582,20 +5582,20 @@
       <c r="O45" s="9"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A46" s="49" t="s">
+      <c r="A46" s="58" t="s">
         <v>14</v>
       </c>
       <c r="B46" s="32">
         <v>1</v>
       </c>
-      <c r="C46" s="51"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="51"/>
-      <c r="F46" s="54"/>
-      <c r="G46" s="51"/>
-      <c r="H46" s="51"/>
-      <c r="I46" s="51"/>
-      <c r="J46" s="51"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
       <c r="K46" s="22">
         <f>AVERAGE(DataExp1.1!AB18:AB27)</f>
         <v>13.2679396369752</v>
@@ -5615,18 +5615,18 @@
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A47" s="49"/>
+      <c r="A47" s="58"/>
       <c r="B47" s="32">
         <v>3</v>
       </c>
-      <c r="C47" s="51"/>
-      <c r="D47" s="51"/>
-      <c r="E47" s="51"/>
-      <c r="F47" s="54"/>
-      <c r="G47" s="51"/>
-      <c r="H47" s="51"/>
-      <c r="I47" s="51"/>
-      <c r="J47" s="51"/>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="56"/>
+      <c r="G47" s="52"/>
+      <c r="H47" s="52"/>
+      <c r="I47" s="52"/>
+      <c r="J47" s="52"/>
       <c r="K47" s="22">
         <f>AVERAGE(DataExp1.1!AE18:AE27)</f>
         <v>1.8847515193214188</v>
@@ -5646,18 +5646,18 @@
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="49"/>
+      <c r="A48" s="58"/>
       <c r="B48" s="32">
         <v>5</v>
       </c>
-      <c r="C48" s="51"/>
-      <c r="D48" s="51"/>
-      <c r="E48" s="51"/>
-      <c r="F48" s="54"/>
-      <c r="G48" s="51"/>
-      <c r="H48" s="51"/>
-      <c r="I48" s="51"/>
-      <c r="J48" s="51"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="52"/>
+      <c r="H48" s="52"/>
+      <c r="I48" s="52"/>
+      <c r="J48" s="52"/>
       <c r="K48" s="22">
         <f>AVERAGE(DataExp1.1!AH18:AH27)</f>
         <v>1.9167287224860321</v>
@@ -5677,18 +5677,18 @@
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="49"/>
+      <c r="A49" s="58"/>
       <c r="B49" s="38">
         <v>10</v>
       </c>
-      <c r="C49" s="51"/>
-      <c r="D49" s="51"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="54"/>
-      <c r="G49" s="51"/>
-      <c r="H49" s="51"/>
-      <c r="I49" s="51"/>
-      <c r="J49" s="51"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="52"/>
+      <c r="H49" s="52"/>
+      <c r="I49" s="52"/>
+      <c r="J49" s="52"/>
       <c r="K49" s="22">
         <f>AVERAGE(DataExp1.1!AK18:AK27)</f>
         <v>1.9152230126798291</v>
@@ -5708,18 +5708,18 @@
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="49"/>
+      <c r="A50" s="58"/>
       <c r="B50" s="38">
         <v>20</v>
       </c>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="54"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="51"/>
-      <c r="I50" s="51"/>
-      <c r="J50" s="51"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="56"/>
+      <c r="G50" s="52"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="52"/>
+      <c r="J50" s="52"/>
       <c r="K50" s="22"/>
       <c r="L50" s="22"/>
       <c r="M50" s="22"/>
@@ -5727,18 +5727,18 @@
       <c r="O50" s="22"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="49"/>
+      <c r="A51" s="58"/>
       <c r="B51" s="38">
         <v>50</v>
       </c>
-      <c r="C51" s="51"/>
-      <c r="D51" s="51"/>
-      <c r="E51" s="51"/>
-      <c r="F51" s="54"/>
-      <c r="G51" s="51"/>
-      <c r="H51" s="51"/>
-      <c r="I51" s="51"/>
-      <c r="J51" s="51"/>
+      <c r="C51" s="52"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="52"/>
+      <c r="H51" s="52"/>
+      <c r="I51" s="52"/>
+      <c r="J51" s="52"/>
       <c r="K51" s="22"/>
       <c r="L51" s="22"/>
       <c r="M51" s="22"/>
@@ -5746,18 +5746,18 @@
       <c r="O51" s="22"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="49"/>
+      <c r="A52" s="58"/>
       <c r="B52" s="38">
         <v>100</v>
       </c>
-      <c r="C52" s="51"/>
-      <c r="D52" s="51"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="54"/>
-      <c r="G52" s="51"/>
-      <c r="H52" s="51"/>
-      <c r="I52" s="51"/>
-      <c r="J52" s="51"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="56"/>
+      <c r="G52" s="52"/>
+      <c r="H52" s="52"/>
+      <c r="I52" s="52"/>
+      <c r="J52" s="52"/>
       <c r="K52" s="32"/>
       <c r="L52" s="32"/>
       <c r="M52" s="22"/>
@@ -5765,20 +5765,20 @@
       <c r="O52" s="32"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="48" t="s">
+      <c r="A53" s="57" t="s">
         <v>15</v>
       </c>
       <c r="B53" s="9">
         <v>1</v>
       </c>
-      <c r="C53" s="51"/>
-      <c r="D53" s="51"/>
-      <c r="E53" s="51"/>
-      <c r="F53" s="54"/>
-      <c r="G53" s="51"/>
-      <c r="H53" s="51"/>
-      <c r="I53" s="51"/>
-      <c r="J53" s="51"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="52"/>
+      <c r="E53" s="52"/>
+      <c r="F53" s="56"/>
+      <c r="G53" s="52"/>
+      <c r="H53" s="52"/>
+      <c r="I53" s="52"/>
+      <c r="J53" s="52"/>
       <c r="K53" s="14">
         <f>AVERAGE(DataExp1.1!AO18:AO27)</f>
         <v>59.79535904859479</v>
@@ -5798,18 +5798,18 @@
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="48"/>
+      <c r="A54" s="57"/>
       <c r="B54" s="9">
         <v>3</v>
       </c>
-      <c r="C54" s="51"/>
-      <c r="D54" s="51"/>
-      <c r="E54" s="51"/>
-      <c r="F54" s="54"/>
-      <c r="G54" s="51"/>
-      <c r="H54" s="51"/>
-      <c r="I54" s="51"/>
-      <c r="J54" s="51"/>
+      <c r="C54" s="52"/>
+      <c r="D54" s="52"/>
+      <c r="E54" s="52"/>
+      <c r="F54" s="56"/>
+      <c r="G54" s="52"/>
+      <c r="H54" s="52"/>
+      <c r="I54" s="52"/>
+      <c r="J54" s="52"/>
       <c r="K54" s="14">
         <f>AVERAGE(DataExp1.1!AR18:AR27)</f>
         <v>4.1994209587286191</v>
@@ -5829,18 +5829,18 @@
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="48"/>
+      <c r="A55" s="57"/>
       <c r="B55" s="9">
         <v>5</v>
       </c>
-      <c r="C55" s="51"/>
-      <c r="D55" s="51"/>
-      <c r="E55" s="51"/>
-      <c r="F55" s="54"/>
-      <c r="G55" s="51"/>
-      <c r="H55" s="51"/>
-      <c r="I55" s="51"/>
-      <c r="J55" s="51"/>
+      <c r="C55" s="52"/>
+      <c r="D55" s="52"/>
+      <c r="E55" s="52"/>
+      <c r="F55" s="56"/>
+      <c r="G55" s="52"/>
+      <c r="H55" s="52"/>
+      <c r="I55" s="52"/>
+      <c r="J55" s="52"/>
       <c r="K55" s="14">
         <f>AVERAGE(DataExp1.1!AU18:AU27)</f>
         <v>4.4246201292478027</v>
@@ -5860,18 +5860,18 @@
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="48"/>
+      <c r="A56" s="57"/>
       <c r="B56" s="9">
         <v>10</v>
       </c>
-      <c r="C56" s="51"/>
-      <c r="D56" s="51"/>
-      <c r="E56" s="51"/>
-      <c r="F56" s="54"/>
-      <c r="G56" s="51"/>
-      <c r="H56" s="51"/>
-      <c r="I56" s="51"/>
-      <c r="J56" s="51"/>
+      <c r="C56" s="52"/>
+      <c r="D56" s="52"/>
+      <c r="E56" s="52"/>
+      <c r="F56" s="56"/>
+      <c r="G56" s="52"/>
+      <c r="H56" s="52"/>
+      <c r="I56" s="52"/>
+      <c r="J56" s="52"/>
       <c r="K56" s="14">
         <f>AVERAGE(DataExp1.1!AX18:AX27)</f>
         <v>4.1938757256751718</v>
@@ -5891,18 +5891,18 @@
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="48"/>
+      <c r="A57" s="57"/>
       <c r="B57" s="9">
         <v>20</v>
       </c>
-      <c r="C57" s="51"/>
-      <c r="D57" s="51"/>
-      <c r="E57" s="51"/>
-      <c r="F57" s="54"/>
-      <c r="G57" s="51"/>
-      <c r="H57" s="51"/>
-      <c r="I57" s="51"/>
-      <c r="J57" s="51"/>
+      <c r="C57" s="52"/>
+      <c r="D57" s="52"/>
+      <c r="E57" s="52"/>
+      <c r="F57" s="56"/>
+      <c r="G57" s="52"/>
+      <c r="H57" s="52"/>
+      <c r="I57" s="52"/>
+      <c r="J57" s="52"/>
       <c r="K57" s="14"/>
       <c r="L57" s="14"/>
       <c r="M57" s="14"/>
@@ -5910,18 +5910,18 @@
       <c r="O57" s="14"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="48"/>
+      <c r="A58" s="57"/>
       <c r="B58" s="9">
         <v>50</v>
       </c>
-      <c r="C58" s="51"/>
-      <c r="D58" s="51"/>
-      <c r="E58" s="51"/>
-      <c r="F58" s="54"/>
-      <c r="G58" s="51"/>
-      <c r="H58" s="51"/>
-      <c r="I58" s="51"/>
-      <c r="J58" s="51"/>
+      <c r="C58" s="52"/>
+      <c r="D58" s="52"/>
+      <c r="E58" s="52"/>
+      <c r="F58" s="56"/>
+      <c r="G58" s="52"/>
+      <c r="H58" s="52"/>
+      <c r="I58" s="52"/>
+      <c r="J58" s="52"/>
       <c r="K58" s="14"/>
       <c r="L58" s="14"/>
       <c r="M58" s="14"/>
@@ -5929,18 +5929,18 @@
       <c r="O58" s="14"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="48"/>
+      <c r="A59" s="57"/>
       <c r="B59" s="9">
         <v>100</v>
       </c>
-      <c r="C59" s="51"/>
-      <c r="D59" s="51"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="50"/>
-      <c r="G59" s="51"/>
-      <c r="H59" s="51"/>
-      <c r="I59" s="51"/>
-      <c r="J59" s="51"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="52"/>
+      <c r="E59" s="52"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="52"/>
+      <c r="H59" s="52"/>
+      <c r="I59" s="52"/>
+      <c r="J59" s="52"/>
       <c r="K59" s="9"/>
       <c r="L59" s="9"/>
       <c r="M59" s="14"/>
@@ -5949,17 +5949,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="C4:C31"/>
-    <mergeCell ref="D4:D31"/>
-    <mergeCell ref="E4:E31"/>
-    <mergeCell ref="G4:G31"/>
-    <mergeCell ref="H4:H31"/>
-    <mergeCell ref="F4:F31"/>
     <mergeCell ref="A39:A45"/>
     <mergeCell ref="A46:A52"/>
     <mergeCell ref="A53:A59"/>
@@ -5974,6 +5963,17 @@
     <mergeCell ref="I32:I59"/>
     <mergeCell ref="J32:J59"/>
     <mergeCell ref="F32:F59"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="C4:C31"/>
+    <mergeCell ref="D4:D31"/>
+    <mergeCell ref="E4:E31"/>
+    <mergeCell ref="G4:G31"/>
+    <mergeCell ref="H4:H31"/>
+    <mergeCell ref="F4:F31"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5993,23 +5993,25 @@
     <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
       <c r="M1" s="21"/>
     </row>
     <row r="2" spans="2:22" x14ac:dyDescent="0.25">
@@ -6151,9 +6153,15 @@
       <c r="M4" s="5">
         <v>11.6075575351715</v>
       </c>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
+      <c r="N4" s="5">
+        <v>6.3181789085846596</v>
+      </c>
+      <c r="O4" s="5">
+        <v>2.08095050376079</v>
+      </c>
+      <c r="P4" s="5">
+        <v>12.9025807380676</v>
+      </c>
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
@@ -6198,9 +6206,15 @@
       <c r="M5" s="5">
         <v>12.1058855056762</v>
       </c>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
+      <c r="N5" s="5">
+        <v>8.6164836784218899</v>
+      </c>
+      <c r="O5" s="5">
+        <v>2.39237663692712</v>
+      </c>
+      <c r="P5" s="5">
+        <v>12.5410010814666</v>
+      </c>
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
@@ -6245,9 +6259,15 @@
       <c r="M6" s="5">
         <v>11.7908341884613</v>
       </c>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
+      <c r="N6" s="5">
+        <v>9.3580003831549003</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1.8491858103760901</v>
+      </c>
+      <c r="P6" s="5">
+        <v>12.6727230548858</v>
+      </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
@@ -6292,9 +6312,15 @@
       <c r="M7" s="5">
         <v>11.7539100646972</v>
       </c>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
+      <c r="N7" s="5">
+        <v>6.6513361881346897</v>
+      </c>
+      <c r="O7" s="5">
+        <v>2.4394343379781098</v>
+      </c>
+      <c r="P7" s="5">
+        <v>12.7637286186218</v>
+      </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="5"/>
@@ -6339,9 +6365,15 @@
       <c r="M8" s="5">
         <v>11.981241464614801</v>
       </c>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
+      <c r="N8" s="5">
+        <v>8.5318505891228398</v>
+      </c>
+      <c r="O8" s="5">
+        <v>2.2158730862496099</v>
+      </c>
+      <c r="P8" s="5">
+        <v>12.6539177894592</v>
+      </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
       <c r="S8" s="5"/>
@@ -6470,19 +6502,19 @@
       <c r="D14" s="7"/>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
       <c r="M15" s="21"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.25">
@@ -6606,21 +6638,33 @@
       <c r="G18" s="5">
         <v>11.4287197589874</v>
       </c>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
+      <c r="H18" s="4">
+        <v>10.325995288497399</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1.55053510934903</v>
+      </c>
+      <c r="J18" s="4">
+        <v>11.8249926567077</v>
+      </c>
       <c r="K18" s="5">
-        <v>93.0897561041469</v>
+        <v>119.256302244765</v>
       </c>
       <c r="L18" s="5">
-        <v>3.30219451723107</v>
+        <v>4.0501513115032699</v>
       </c>
       <c r="M18" s="5">
-        <v>11.680633068084701</v>
-      </c>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
+        <v>11.631165742874099</v>
+      </c>
+      <c r="N18" s="5">
+        <v>109.057293766711</v>
+      </c>
+      <c r="O18" s="5">
+        <v>4.2055400842948201</v>
+      </c>
+      <c r="P18" s="5">
+        <v>11.652021408081</v>
+      </c>
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
       <c r="S18" s="5"/>
@@ -6647,12 +6691,24 @@
       <c r="G19" s="5">
         <v>11.4343502521514</v>
       </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
+      <c r="H19" s="4">
+        <v>53.787521585037098</v>
+      </c>
+      <c r="I19" s="4">
+        <v>2.5686537043532498</v>
+      </c>
+      <c r="J19" s="4">
+        <v>11.736212730407701</v>
+      </c>
+      <c r="K19" s="5">
+        <v>91.182858257015695</v>
+      </c>
+      <c r="L19" s="5">
+        <v>3.3550519300816402</v>
+      </c>
+      <c r="M19" s="5">
+        <v>11.7357194423675</v>
+      </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
@@ -6682,12 +6738,24 @@
       <c r="G20" s="5">
         <v>11.333469867706199</v>
       </c>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
+      <c r="H20" s="4">
+        <v>96.3021034335286</v>
+      </c>
+      <c r="I20" s="4">
+        <v>3.4612446777092001</v>
+      </c>
+      <c r="J20" s="4">
+        <v>11.661410093307399</v>
+      </c>
+      <c r="K20" s="5">
+        <v>97.9758719182107</v>
+      </c>
+      <c r="L20" s="5">
+        <v>3.4788745442326801</v>
+      </c>
+      <c r="M20" s="5">
+        <v>11.722119808197</v>
+      </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
@@ -6717,12 +6785,24 @@
       <c r="G21" s="5">
         <v>11.471031188964799</v>
       </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
+      <c r="H21" s="4">
+        <v>91.015108259858593</v>
+      </c>
+      <c r="I21" s="4">
+        <v>3.4548550407023599</v>
+      </c>
+      <c r="J21" s="4">
+        <v>11.6886942386627</v>
+      </c>
+      <c r="K21" s="5">
+        <v>93.182364217165599</v>
+      </c>
+      <c r="L21" s="5">
+        <v>3.3661628055310602</v>
+      </c>
+      <c r="M21" s="5">
+        <v>11.7503917217254</v>
+      </c>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
@@ -6752,12 +6832,24 @@
       <c r="G22" s="5">
         <v>11.491828918456999</v>
       </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
+      <c r="H22" s="4">
+        <v>88.995976238619207</v>
+      </c>
+      <c r="I22" s="4">
+        <v>3.3984125362167399</v>
+      </c>
+      <c r="J22" s="4">
+        <v>11.668272495269701</v>
+      </c>
+      <c r="K22" s="5">
+        <v>98.761617243212299</v>
+      </c>
+      <c r="L22" s="5">
+        <v>3.5556758317575898</v>
+      </c>
+      <c r="M22" s="5">
+        <v>11.8244853019714</v>
+      </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
@@ -6775,12 +6867,24 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
+      <c r="H23" s="4">
+        <v>112.84872236471</v>
+      </c>
+      <c r="I23" s="4">
+        <v>4.2898188841504901</v>
+      </c>
+      <c r="J23" s="4">
+        <v>11.5611891746521</v>
+      </c>
+      <c r="K23" s="5">
+        <v>78.319907660454604</v>
+      </c>
+      <c r="L23" s="5">
+        <v>3.4998823088996298</v>
+      </c>
+      <c r="M23" s="5">
+        <v>11.871711730956999</v>
+      </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
@@ -6801,9 +6905,15 @@
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
+      <c r="K24" s="5">
+        <v>91.214004593635707</v>
+      </c>
+      <c r="L24" s="5">
+        <v>3.7516547356340801</v>
+      </c>
+      <c r="M24" s="5">
+        <v>11.7090663909912</v>
+      </c>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
       <c r="P24" s="5"/>
@@ -6884,19 +6994,19 @@
       <c r="V27" s="5"/>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="39"/>
       <c r="M29" s="21"/>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.25">
@@ -7002,23 +7112,41 @@
       </c>
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
+      <c r="B32" s="4">
+        <v>345.21337319137598</v>
+      </c>
+      <c r="C32" s="4">
+        <v>11.1560754052009</v>
+      </c>
+      <c r="D32" s="4">
+        <v>11.377435445785499</v>
+      </c>
+      <c r="E32" s="5">
+        <v>38.513262923581003</v>
+      </c>
+      <c r="F32" s="5">
+        <v>1.63046856597419</v>
+      </c>
+      <c r="G32" s="5">
+        <v>11.498995065689</v>
+      </c>
+      <c r="H32" s="4">
+        <v>38.875082820136598</v>
+      </c>
+      <c r="I32" s="4">
+        <v>1.67226589223227</v>
+      </c>
+      <c r="J32" s="4">
+        <v>11.604145526885899</v>
+      </c>
       <c r="K32" s="5">
-        <v>93.0897561041469</v>
+        <v>36.9453749198764</v>
       </c>
       <c r="L32" s="5">
-        <v>3.30219451723107</v>
+        <v>1.5478539695145099</v>
       </c>
       <c r="M32" s="5">
-        <v>11.680633068084701</v>
+        <v>11.7257986068725</v>
       </c>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
@@ -7031,18 +7159,42 @@
       <c r="V32" s="5"/>
     </row>
     <row r="33" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
+      <c r="B33" s="4">
+        <v>345.14754238117803</v>
+      </c>
+      <c r="C33" s="4">
+        <v>11.256697300114</v>
+      </c>
+      <c r="D33" s="4">
+        <v>11.487327337265</v>
+      </c>
+      <c r="E33" s="5">
+        <v>39.154638611102001</v>
+      </c>
+      <c r="F33" s="5">
+        <v>1.6396369165567799</v>
+      </c>
+      <c r="G33" s="5">
+        <v>11.6167652606964</v>
+      </c>
+      <c r="H33" s="4">
+        <v>36.967245682120897</v>
+      </c>
+      <c r="I33" s="4">
+        <v>1.55166069803561</v>
+      </c>
+      <c r="J33" s="4">
+        <v>11.7412493228912</v>
+      </c>
+      <c r="K33" s="5">
+        <v>37.639439251880802</v>
+      </c>
+      <c r="L33" s="5">
+        <v>1.5486966628866801</v>
+      </c>
+      <c r="M33" s="5">
+        <v>11.6624176502227</v>
+      </c>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
@@ -7054,18 +7206,42 @@
       <c r="V33" s="5"/>
     </row>
     <row r="34" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
+      <c r="B34" s="4">
+        <v>345.21337319137598</v>
+      </c>
+      <c r="C34" s="4">
+        <v>11.1560754052009</v>
+      </c>
+      <c r="D34" s="4">
+        <v>11.3636291027069</v>
+      </c>
+      <c r="E34" s="5">
+        <v>38.934354523328601</v>
+      </c>
+      <c r="F34" s="5">
+        <v>1.63853373966854</v>
+      </c>
+      <c r="G34" s="5">
+        <v>11.6858246326446</v>
+      </c>
+      <c r="H34" s="4">
+        <v>38.916233541762502</v>
+      </c>
+      <c r="I34" s="4">
+        <v>1.66423116261605</v>
+      </c>
+      <c r="J34" s="4">
+        <v>11.1895191669464</v>
+      </c>
+      <c r="K34" s="5">
+        <v>36.841168542412099</v>
+      </c>
+      <c r="L34" s="5">
+        <v>1.5521355529224199</v>
+      </c>
+      <c r="M34" s="5">
+        <v>11.729650735855101</v>
+      </c>
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
@@ -7077,18 +7253,42 @@
       <c r="V34" s="5"/>
     </row>
     <row r="35" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
+      <c r="B35" s="4">
+        <v>345.21337319137598</v>
+      </c>
+      <c r="C35" s="4">
+        <v>11.1560754052009</v>
+      </c>
+      <c r="D35" s="4">
+        <v>11.343361377716001</v>
+      </c>
+      <c r="E35" s="5">
+        <v>38.918840343166103</v>
+      </c>
+      <c r="F35" s="5">
+        <v>1.6604856638437699</v>
+      </c>
+      <c r="G35" s="5">
+        <v>11.5199015140533</v>
+      </c>
+      <c r="H35" s="4">
+        <v>38.622678793867102</v>
+      </c>
+      <c r="I35" s="4">
+        <v>1.5938949908242499</v>
+      </c>
+      <c r="J35" s="4">
+        <v>11.554682016372601</v>
+      </c>
+      <c r="K35" s="5">
+        <v>38.984238559721</v>
+      </c>
+      <c r="L35" s="5">
+        <v>1.54911046425938</v>
+      </c>
+      <c r="M35" s="5">
+        <v>11.653014421463</v>
+      </c>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
@@ -7100,18 +7300,42 @@
       <c r="V35" s="5"/>
     </row>
     <row r="36" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
+      <c r="B36" s="4">
+        <v>345.14754238117803</v>
+      </c>
+      <c r="C36" s="4">
+        <v>11.256697300114</v>
+      </c>
+      <c r="D36" s="4">
+        <v>11.3606398105621</v>
+      </c>
+      <c r="E36" s="5">
+        <v>39.0871757822323</v>
+      </c>
+      <c r="F36" s="5">
+        <v>1.55831707509211</v>
+      </c>
+      <c r="G36" s="5">
+        <v>11.5858001708984</v>
+      </c>
+      <c r="H36" s="4">
+        <v>39.015266694157901</v>
+      </c>
+      <c r="I36" s="4">
+        <v>1.6742726763459299</v>
+      </c>
+      <c r="J36" s="4">
+        <v>11.6733767986297</v>
+      </c>
+      <c r="K36" s="5">
+        <v>38.893643657267297</v>
+      </c>
+      <c r="L36" s="5">
+        <v>1.6642311586944201</v>
+      </c>
+      <c r="M36" s="5">
+        <v>11.7134552001953</v>
+      </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
@@ -7129,9 +7353,15 @@
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
+      <c r="H37" s="4">
+        <v>37.766138228678699</v>
+      </c>
+      <c r="I37" s="4">
+        <v>1.55007540837292</v>
+      </c>
+      <c r="J37" s="4">
+        <v>11.6366822719573</v>
+      </c>
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
@@ -7152,9 +7382,15 @@
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
+      <c r="H38" s="4">
+        <v>38.916233541762502</v>
+      </c>
+      <c r="I38" s="4">
+        <v>1.66423116261605</v>
+      </c>
+      <c r="J38" s="4">
+        <v>11.735893249511699</v>
+      </c>
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
@@ -7238,19 +7474,19 @@
       <c r="V41" s="5"/>
     </row>
     <row r="43" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B43" s="47" t="s">
+      <c r="B43" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="47"/>
-      <c r="I43" s="47"/>
-      <c r="J43" s="47"/>
-      <c r="K43" s="47"/>
-      <c r="L43" s="47"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="39"/>
+      <c r="H43" s="39"/>
+      <c r="I43" s="39"/>
+      <c r="J43" s="39"/>
+      <c r="K43" s="39"/>
+      <c r="L43" s="39"/>
       <c r="M43" s="21"/>
     </row>
     <row r="44" spans="2:22" x14ac:dyDescent="0.25">
@@ -7356,12 +7592,24 @@
       </c>
     </row>
     <row r="46" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
+      <c r="B46" s="4">
+        <v>1261.44296531498</v>
+      </c>
+      <c r="C46" s="4">
+        <v>41.440515677445802</v>
+      </c>
+      <c r="D46" s="4">
+        <v>11.526838302612299</v>
+      </c>
+      <c r="E46" s="5">
+        <v>45.443276753298697</v>
+      </c>
+      <c r="F46" s="5">
+        <v>2.8643923142918002</v>
+      </c>
+      <c r="G46" s="5">
+        <v>11.5067465305328</v>
+      </c>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
@@ -7385,12 +7633,24 @@
       <c r="V46" s="5"/>
     </row>
     <row r="47" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
+      <c r="B47" s="4">
+        <v>1258.94720083937</v>
+      </c>
+      <c r="C47" s="4">
+        <v>41.457191832359001</v>
+      </c>
+      <c r="D47" s="4">
+        <v>11.3741781711578</v>
+      </c>
+      <c r="E47" s="5">
+        <v>40.326313836370403</v>
+      </c>
+      <c r="F47" s="5">
+        <v>2.8997169176335298</v>
+      </c>
+      <c r="G47" s="5">
+        <v>11.515213727951</v>
+      </c>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
@@ -7408,12 +7668,24 @@
       <c r="V47" s="5"/>
     </row>
     <row r="48" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
+      <c r="B48" s="4">
+        <v>1272.84100087765</v>
+      </c>
+      <c r="C48" s="4">
+        <v>41.667283778004297</v>
+      </c>
+      <c r="D48" s="4">
+        <v>11.502956390380801</v>
+      </c>
+      <c r="E48" s="5">
+        <v>36.314017141862998</v>
+      </c>
+      <c r="F48" s="5">
+        <v>2.71538576301338</v>
+      </c>
+      <c r="G48" s="5">
+        <v>11.661873579025199</v>
+      </c>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
@@ -7431,12 +7703,24 @@
       <c r="V48" s="5"/>
     </row>
     <row r="49" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
+      <c r="B49" s="4">
+        <v>1262.32532809241</v>
+      </c>
+      <c r="C49" s="4">
+        <v>41.564492786032702</v>
+      </c>
+      <c r="D49" s="4">
+        <v>11.48459815979</v>
+      </c>
+      <c r="E49" s="5">
+        <v>45.442735532121198</v>
+      </c>
+      <c r="F49" s="5">
+        <v>2.8642774224038798</v>
+      </c>
+      <c r="G49" s="5">
+        <v>11.4730393886566</v>
+      </c>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
@@ -7454,12 +7738,24 @@
       <c r="V49" s="5"/>
     </row>
     <row r="50" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
+      <c r="B50" s="4">
+        <v>1257.69151891614</v>
+      </c>
+      <c r="C50" s="4">
+        <v>41.435255079969203</v>
+      </c>
+      <c r="D50" s="4">
+        <v>11.409185409545801</v>
+      </c>
+      <c r="E50" s="5">
+        <v>40.324952635694501</v>
+      </c>
+      <c r="F50" s="5">
+        <v>2.8998394693043799</v>
+      </c>
+      <c r="G50" s="5">
+        <v>11.6635522842407</v>
+      </c>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
@@ -7593,6 +7889,23 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="B29:L29"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="T30:V30"/>
     <mergeCell ref="B43:L43"/>
@@ -7603,28 +7916,11 @@
     <mergeCell ref="N44:P44"/>
     <mergeCell ref="Q44:S44"/>
     <mergeCell ref="T44:V44"/>
-    <mergeCell ref="B15:L15"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="T16:V16"/>
-    <mergeCell ref="B29:L29"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="E30:G30"/>
     <mergeCell ref="H30:J30"/>
     <mergeCell ref="K30:M30"/>
     <mergeCell ref="N30:P30"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7637,39 +7933,40 @@
   <cols>
     <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="56"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
     </row>
     <row r="3" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -7719,36 +8016,42 @@
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="50" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="50">
+      <c r="D4" s="54">
         <v>1025</v>
       </c>
-      <c r="E4" s="50">
+      <c r="E4" s="54">
         <v>1025</v>
       </c>
-      <c r="F4" s="60"/>
-      <c r="G4" s="50">
+      <c r="F4" s="55"/>
+      <c r="G4" s="54">
         <v>8</v>
       </c>
-      <c r="H4" s="50">
+      <c r="H4" s="54">
         <v>8</v>
       </c>
-      <c r="I4" s="50">
+      <c r="I4" s="54">
         <v>128</v>
       </c>
-      <c r="J4" s="50">
+      <c r="J4" s="54">
         <v>128</v>
       </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
+      <c r="K4" s="5">
+        <f>AVERAGE(DataExp1.2!B4:B13)</f>
+        <v>1318.3063529254857</v>
+      </c>
+      <c r="L4" s="5">
+        <f>AVERAGE(DataExp1.2!C4:C13)</f>
+        <v>42.578494804591585</v>
+      </c>
       <c r="M4" s="5">
         <v>1031.6912470326899</v>
       </c>
@@ -7758,20 +8061,26 @@
       <c r="O4" s="14"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="58"/>
+      <c r="A5" s="51"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="5">
+        <f>AVERAGE(DataExp1.2!E4:E13)</f>
+        <v>553.53793602493806</v>
+      </c>
+      <c r="L5" s="5">
+        <f>AVERAGE(DataExp1.2!F4:F13)</f>
+        <v>23.646201326905199</v>
+      </c>
       <c r="M5" s="5">
         <v>2037.9507810980799</v>
       </c>
@@ -7781,20 +8090,26 @@
       <c r="O5" s="14"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="58"/>
+      <c r="A6" s="51"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="5">
+        <f>AVERAGE(DataExp1.2!H4:H13)</f>
+        <v>433.9549506572348</v>
+      </c>
+      <c r="L6" s="5">
+        <f>AVERAGE(DataExp1.2!I4:I13)</f>
+        <v>15.18584504945332</v>
+      </c>
       <c r="M6" s="5">
         <v>2541.3986197788599</v>
       </c>
@@ -7804,20 +8119,26 @@
       <c r="O6" s="14"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="58"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="5">
+        <f>AVERAGE(DataExp1.2!K4:K13)</f>
+        <v>10.838240342377034</v>
+      </c>
+      <c r="L7" s="5">
+        <f>AVERAGE(DataExp1.2!L4:L13)</f>
+        <v>2.1474627306391616</v>
+      </c>
       <c r="M7" s="5">
         <v>2261.5467674711599</v>
       </c>
@@ -7827,37 +8148,47 @@
       <c r="O7" s="14"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="58"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="6">
         <v>20</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="17"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
+      <c r="K8" s="5">
+        <f>AVERAGE(DataExp1.2!N4:N13)</f>
+        <v>7.8951699494837957</v>
+      </c>
+      <c r="L8" s="5">
+        <f>AVERAGE(DataExp1.2!O4:O13)</f>
+        <v>2.1955640750583441</v>
+      </c>
+      <c r="M8" s="5">
+        <v>2901.56320216106</v>
+      </c>
+      <c r="N8" s="17">
+        <v>2.7777792550588001E-2</v>
+      </c>
       <c r="O8" s="14"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="58"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="6">
         <v>50</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -7865,18 +8196,18 @@
       <c r="O9" s="14"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="58"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="6">
         <v>100</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
@@ -7884,22 +8215,28 @@
       <c r="O10" s="14"/>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="51" t="s">
+      <c r="A11" s="52" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
+      <c r="K11" s="4">
+        <f>AVERAGE(DataExp1.2!B18:B27)</f>
+        <v>3178.1943497230322</v>
+      </c>
+      <c r="L11" s="4">
+        <f>AVERAGE(DataExp1.2!C18:C27)</f>
+        <v>102.34469778372339</v>
+      </c>
       <c r="M11" s="4">
         <v>142.35263472500199</v>
       </c>
@@ -7909,20 +8246,26 @@
       <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="51"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="3">
         <v>3</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="4">
+        <f>AVERAGE(DataExp1.2!E18:E27)</f>
+        <v>75.685942333849169</v>
+      </c>
+      <c r="L12" s="4">
+        <f>AVERAGE(DataExp1.2!F18:F27)</f>
+        <v>3.1468565913049598</v>
+      </c>
       <c r="M12" s="4">
         <v>469.98055340577702</v>
       </c>
@@ -7932,39 +8275,55 @@
       <c r="O12" s="4"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="51"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="3">
         <v>5</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="18"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="4">
+        <f>AVERAGE(DataExp1.2!H18:H27)</f>
+        <v>75.545904528375146</v>
+      </c>
+      <c r="L13" s="4">
+        <f>AVERAGE(DataExp1.2!I18:I27)</f>
+        <v>3.1205866587468449</v>
+      </c>
+      <c r="M13" s="4">
+        <v>477.62379095227902</v>
+      </c>
+      <c r="N13" s="18">
+        <v>0.57532111708419298</v>
+      </c>
       <c r="O13" s="4"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="51"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="3">
         <v>10</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="4">
+        <f>AVERAGE(DataExp1.2!K18:K27)</f>
+        <v>95.698989447779951</v>
+      </c>
+      <c r="L14" s="4">
+        <f>AVERAGE(DataExp1.2!L18:L27)</f>
+        <v>3.57963620966285</v>
+      </c>
       <c r="M14" s="4">
         <v>480.725983020287</v>
       </c>
@@ -7974,37 +8333,41 @@
       <c r="O14" s="4"/>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="51"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="3">
         <v>20</v>
       </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="52"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="18"/>
+      <c r="M15" s="4">
+        <v>479.01929800970601</v>
+      </c>
+      <c r="N15" s="18">
+        <v>0.57817838930787602</v>
+      </c>
       <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="51"/>
+      <c r="A16" s="52"/>
       <c r="B16" s="3">
         <v>50</v>
       </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="52"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -8012,18 +8375,18 @@
       <c r="O16" s="4"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="51"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="3">
         <v>100</v>
       </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -8031,58 +8394,78 @@
       <c r="O17" s="4"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="48" t="s">
+      <c r="A18" s="57" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="9">
         <v>1</v>
       </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="19"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="14">
+        <f>AVERAGE(DataExp1.2!B32:B41)</f>
+        <v>345.18704086729679</v>
+      </c>
+      <c r="L18" s="14">
+        <f>AVERAGE(DataExp1.2!C32:C41)</f>
+        <v>11.196324163166141</v>
+      </c>
+      <c r="M18" s="14">
+        <v>45.632296109617997</v>
+      </c>
+      <c r="N18" s="19">
+        <v>0.38384376025911399</v>
+      </c>
       <c r="O18" s="14"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="48"/>
+      <c r="A19" s="57"/>
       <c r="B19" s="9">
         <v>3</v>
       </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="19"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="14">
+        <f>AVERAGE(DataExp1.2!E32:E41)</f>
+        <v>38.921654436682005</v>
+      </c>
+      <c r="L19" s="14">
+        <f>AVERAGE(DataExp1.2!F32:F41)</f>
+        <v>1.6254883922270777</v>
+      </c>
+      <c r="M19" s="14">
+        <v>54.454426636546202</v>
+      </c>
+      <c r="N19" s="19">
+        <v>0.42563632754408898</v>
+      </c>
       <c r="O19" s="14"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="48"/>
+      <c r="A20" s="57"/>
       <c r="B20" s="9">
         <v>5</v>
       </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="52"/>
       <c r="K20" s="14"/>
       <c r="L20" s="14"/>
       <c r="M20" s="14"/>
@@ -8090,18 +8473,18 @@
       <c r="O20" s="14"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
+      <c r="A21" s="57"/>
       <c r="B21" s="9">
         <v>10</v>
       </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
       <c r="K21" s="14"/>
       <c r="L21" s="14"/>
       <c r="M21" s="14"/>
@@ -8109,18 +8492,18 @@
       <c r="O21" s="14"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="48"/>
+      <c r="A22" s="57"/>
       <c r="B22" s="9">
         <v>20</v>
       </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="52"/>
       <c r="K22" s="14"/>
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
@@ -8128,18 +8511,18 @@
       <c r="O22" s="14"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="48"/>
+      <c r="A23" s="57"/>
       <c r="B23" s="9">
         <v>50</v>
       </c>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="52"/>
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
@@ -8147,18 +8530,18 @@
       <c r="O23" s="14"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="48"/>
+      <c r="A24" s="57"/>
       <c r="B24" s="9">
         <v>100</v>
       </c>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="51"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="52"/>
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
@@ -8166,58 +8549,66 @@
       <c r="O24" s="14"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="51" t="s">
+      <c r="A25" s="52" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="3">
         <v>1</v>
       </c>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="51"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="52"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="18"/>
+      <c r="M25" s="4">
+        <v>0.22804703269489901</v>
+      </c>
+      <c r="N25" s="18">
+        <v>1.6157759423183701E-4</v>
+      </c>
       <c r="O25" s="4"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="51"/>
+      <c r="A26" s="52"/>
       <c r="B26" s="3">
         <v>3</v>
       </c>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="51"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="52"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="18"/>
+      <c r="M26" s="4">
+        <v>0.41259237346931399</v>
+      </c>
+      <c r="N26" s="18">
+        <v>2.92730512989791E-4</v>
+      </c>
       <c r="O26" s="4"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="51"/>
+      <c r="A27" s="52"/>
       <c r="B27" s="3">
         <v>5</v>
       </c>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="51"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -8225,18 +8616,18 @@
       <c r="O27" s="4"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="51"/>
+      <c r="A28" s="52"/>
       <c r="B28" s="3">
         <v>10</v>
       </c>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="51"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="52"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -8244,18 +8635,18 @@
       <c r="O28" s="4"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="51"/>
+      <c r="A29" s="52"/>
       <c r="B29" s="3">
         <v>20</v>
       </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="52"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -8263,18 +8654,18 @@
       <c r="O29" s="4"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="51"/>
+      <c r="A30" s="52"/>
       <c r="B30" s="3">
         <v>50</v>
       </c>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -8282,18 +8673,18 @@
       <c r="O30" s="4"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="51"/>
+      <c r="A31" s="52"/>
       <c r="B31" s="3">
         <v>100</v>
       </c>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="52"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -8339,60 +8730,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:65" x14ac:dyDescent="0.25">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
       <c r="M1" s="21"/>
-      <c r="R1" s="39" t="s">
+      <c r="R1" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="39"/>
-      <c r="AB1" s="39"/>
-      <c r="AI1" s="39" t="s">
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="47"/>
+      <c r="AI1" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="AJ1" s="39"/>
-      <c r="AK1" s="39"/>
-      <c r="AL1" s="39"/>
-      <c r="AM1" s="39"/>
-      <c r="AN1" s="39"/>
-      <c r="AO1" s="39"/>
-      <c r="AP1" s="39"/>
-      <c r="AQ1" s="39"/>
-      <c r="AR1" s="47"/>
-      <c r="AS1" s="47"/>
+      <c r="AJ1" s="47"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
+      <c r="AM1" s="47"/>
+      <c r="AN1" s="47"/>
+      <c r="AO1" s="47"/>
+      <c r="AP1" s="47"/>
+      <c r="AQ1" s="47"/>
+      <c r="AR1" s="39"/>
+      <c r="AS1" s="39"/>
       <c r="AT1" s="21"/>
-      <c r="AY1" s="39" t="s">
+      <c r="AY1" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="AZ1" s="39"/>
-      <c r="BA1" s="39"/>
-      <c r="BB1" s="39"/>
-      <c r="BC1" s="39"/>
-      <c r="BD1" s="39"/>
-      <c r="BE1" s="39"/>
-      <c r="BF1" s="39"/>
-      <c r="BG1" s="39"/>
-      <c r="BH1" s="47"/>
-      <c r="BI1" s="47"/>
+      <c r="AZ1" s="47"/>
+      <c r="BA1" s="47"/>
+      <c r="BB1" s="47"/>
+      <c r="BC1" s="47"/>
+      <c r="BD1" s="47"/>
+      <c r="BE1" s="47"/>
+      <c r="BF1" s="47"/>
+      <c r="BG1" s="47"/>
+      <c r="BH1" s="39"/>
+      <c r="BI1" s="39"/>
     </row>
     <row r="2" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B2" s="40" t="s">
@@ -9634,14 +10025,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="AI2:AK2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BH2:BJ2"/>
     <mergeCell ref="AY1:BI1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
@@ -9658,6 +10041,14 @@
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BH2:BJ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9669,32 +10060,32 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:27" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="55" t="s">
+      <c r="D1" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="56"/>
-      <c r="AA1" s="56"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
     </row>
     <row r="3" spans="1:27" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -9738,32 +10129,32 @@
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="51" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="6">
         <v>1</v>
       </c>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="51">
+      <c r="D4" s="52">
         <v>66</v>
       </c>
-      <c r="E4" s="51">
+      <c r="E4" s="52">
         <v>66</v>
       </c>
       <c r="F4" s="62"/>
-      <c r="G4" s="51">
+      <c r="G4" s="52">
         <v>1</v>
       </c>
-      <c r="H4" s="51">
+      <c r="H4" s="52">
         <v>1</v>
       </c>
-      <c r="I4" s="51">
+      <c r="I4" s="52">
         <v>66</v>
       </c>
-      <c r="J4" s="51">
+      <c r="J4" s="52">
         <v>66</v>
       </c>
       <c r="K4" s="5">
@@ -9780,18 +10171,18 @@
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="58"/>
+      <c r="A5" s="51"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
       <c r="F5" s="63"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
       <c r="K5" s="5">
         <f>AVERAGE(DataExp2!E4:E8)</f>
         <v>6.7273250931611468</v>
@@ -9806,18 +10197,18 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="58"/>
+      <c r="A6" s="51"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
       <c r="F6" s="63"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
       <c r="K6" s="5">
         <f>AVERAGE(DataExp2!H4:H8)</f>
         <v>2.8757780700062598</v>
@@ -9832,18 +10223,18 @@
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="58"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
       <c r="F7" s="63"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
       <c r="K7" s="5">
         <f>AVERAGE(DataExp2!K4:K8)</f>
         <v>2.5245777936554679</v>
@@ -9858,18 +10249,18 @@
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="58"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="6">
         <v>1000</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
       <c r="F8" s="63"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
       <c r="K8" s="5">
         <f>AVERAGE(DataExp2!N4:N8)</f>
         <v>2.6210229749569218</v>
@@ -9884,20 +10275,20 @@
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="51" t="s">
+      <c r="A9" s="52" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
       <c r="F9" s="63"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
       <c r="K9" s="4">
         <f>AVERAGE(DataExp2!R4:R8)</f>
         <v>25.122901453825698</v>
@@ -9912,18 +10303,18 @@
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="3">
         <v>3</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
       <c r="F10" s="63"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
       <c r="K10" s="4">
         <f>AVERAGE(DataExp2!U4:U8)</f>
         <v>1.1978887514698182</v>
@@ -9938,18 +10329,18 @@
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="51"/>
+      <c r="A11" s="52"/>
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
       <c r="F11" s="63"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
       <c r="K11" s="4">
         <f>AVERAGE(DataExp2!X4:X8)</f>
         <v>2.7398509444970598</v>
@@ -9964,18 +10355,18 @@
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="51"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="3">
         <v>10</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
       <c r="F12" s="63"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
       <c r="K12" s="4">
         <f>AVERAGE(DataExp2!AA4:AA8)</f>
         <v>2.3904188069590249</v>
@@ -9990,18 +10381,18 @@
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="51"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="3">
         <v>1000</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
       <c r="F13" s="63"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
       <c r="K13" s="4">
         <f>AVERAGE(DataExp2!AD4:AD8)</f>
         <v>3.118010443300594</v>
@@ -10016,20 +10407,20 @@
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="58" t="s">
+      <c r="A14" s="51" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="6">
         <v>1</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
       <c r="F14" s="63"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
       <c r="K14" s="14">
         <f>AVERAGE(DataExp2!AI4:AI8)</f>
         <v>2.018042671934988</v>
@@ -10044,18 +10435,18 @@
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="58"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="6">
         <v>3</v>
       </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
       <c r="F15" s="63"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="52"/>
       <c r="K15" s="14">
         <f>AVERAGE(DataExp2!AL4:AL8)</f>
         <v>2.9999089103706797</v>
@@ -10070,18 +10461,18 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="58"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="6">
         <v>5</v>
       </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
       <c r="F16" s="63"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="52"/>
       <c r="K16" s="14">
         <f>AVERAGE(DataExp2!AO4:AO8)</f>
         <v>3.0887572192386399</v>
@@ -10096,18 +10487,18 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="58"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="6">
         <v>10</v>
       </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
       <c r="F17" s="63"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
       <c r="K17" s="14">
         <f>AVERAGE(DataExp2!AR4:AR8)</f>
         <v>3.0147786188702144</v>
@@ -10122,18 +10513,18 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="58"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="6">
         <v>1000</v>
       </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
       <c r="F18" s="63"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
       <c r="K18" s="14">
         <f>AVERAGE(DataExp2!AU4:AU8)</f>
         <v>3.1022309678357018</v>
@@ -10148,20 +10539,20 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="51" t="s">
+      <c r="A19" s="52" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="3">
         <v>1</v>
       </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
       <c r="F19" s="63"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
       <c r="K19" s="4">
         <f>AVERAGE(DataExp2!AY4:AY8)</f>
         <v>23.17734266838546</v>
@@ -10176,18 +10567,18 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="51"/>
+      <c r="A20" s="52"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
       <c r="F20" s="63"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="52"/>
       <c r="K20" s="4">
         <f>AVERAGE(DataExp2!BB4:BB8)</f>
         <v>2.7741290185543344</v>
@@ -10202,18 +10593,18 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="51"/>
+      <c r="A21" s="52"/>
       <c r="B21" s="3">
         <v>5</v>
       </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
       <c r="F21" s="63"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
       <c r="K21" s="4">
         <f>AVERAGE(DataExp2!BE4:BE8)</f>
         <v>2.776927957976338</v>
@@ -10228,18 +10619,18 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="53"/>
+      <c r="A22" s="60"/>
       <c r="B22" s="10">
         <v>10</v>
       </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
       <c r="F22" s="63"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="60"/>
       <c r="K22" s="31">
         <f>AVERAGE(DataExp2!BH4:BH8)</f>
         <v>2.6552692879772497</v>
@@ -10352,26 +10743,26 @@
       <c r="B3" s="6">
         <v>1</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="51">
+      <c r="D3" s="52">
         <v>66</v>
       </c>
-      <c r="E3" s="51">
+      <c r="E3" s="52">
         <v>66</v>
       </c>
       <c r="F3" s="46"/>
-      <c r="G3" s="51">
+      <c r="G3" s="52">
         <v>1</v>
       </c>
-      <c r="H3" s="51">
+      <c r="H3" s="52">
         <v>1</v>
       </c>
-      <c r="I3" s="51">
+      <c r="I3" s="52">
         <v>66</v>
       </c>
-      <c r="J3" s="51">
+      <c r="J3" s="52">
         <v>66</v>
       </c>
       <c r="K3" s="9">
@@ -10386,14 +10777,14 @@
       <c r="B4" s="6">
         <v>3</v>
       </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
       <c r="F4" s="46"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
       <c r="K4" s="14">
         <v>10.596633070539401</v>
       </c>
@@ -10406,14 +10797,14 @@
       <c r="B5" s="6">
         <v>5</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
       <c r="F5" s="46"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
       <c r="K5" s="14">
         <v>4.5624707313509596</v>
       </c>
@@ -10426,14 +10817,14 @@
       <c r="B6" s="6">
         <v>10</v>
       </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
       <c r="F6" s="46"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
       <c r="K6" s="14">
         <v>0.610171518579538</v>
       </c>
@@ -10442,18 +10833,18 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="57"/>
+      <c r="A7" s="50"/>
       <c r="B7" s="6">
         <v>100</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
       <c r="F7" s="46"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
       <c r="K7" s="9">
         <v>0.56361848551125004</v>
       </c>
@@ -10462,20 +10853,20 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="60" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
       <c r="F8" s="46"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
       <c r="K8" s="4">
         <v>51.3708858392826</v>
       </c>
@@ -10484,18 +10875,18 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="54"/>
+      <c r="A9" s="56"/>
       <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
       <c r="F9" s="46"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
       <c r="K9" s="4">
         <v>2.1067016984413098</v>
       </c>
@@ -10504,18 +10895,18 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="54"/>
+      <c r="A10" s="56"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
       <c r="F10" s="46"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
       <c r="K10" s="4">
         <v>2.8064566058312099</v>
       </c>
@@ -10524,18 +10915,18 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="54"/>
+      <c r="A11" s="56"/>
       <c r="B11" s="3">
         <v>10</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
       <c r="F11" s="46"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
       <c r="K11" s="4">
         <v>1.8870454425238199</v>
       </c>
@@ -10544,18 +10935,18 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="50"/>
+      <c r="A12" s="54"/>
       <c r="B12" s="3">
         <v>100</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
       <c r="F12" s="46"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
       <c r="K12" s="4">
         <v>1.6795645399372201</v>
       </c>
@@ -10570,14 +10961,14 @@
       <c r="B13" s="6">
         <v>1</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
       <c r="F13" s="46"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
       <c r="K13" s="14">
         <v>1.97796965575553</v>
       </c>
@@ -10590,14 +10981,14 @@
       <c r="B14" s="6">
         <v>3</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
       <c r="F14" s="46"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
       <c r="K14" s="14">
         <v>3.1862607049915099</v>
       </c>
@@ -10610,14 +11001,14 @@
       <c r="B15" s="6">
         <v>5</v>
       </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
       <c r="F15" s="46"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="52"/>
       <c r="K15" s="14">
         <v>3.1662124268938201</v>
       </c>
@@ -10630,14 +11021,14 @@
       <c r="B16" s="6">
         <v>10</v>
       </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
       <c r="F16" s="46"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="52"/>
       <c r="K16" s="14">
         <v>3.0769912027266599</v>
       </c>
@@ -10646,18 +11037,18 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="57"/>
+      <c r="A17" s="50"/>
       <c r="B17" s="6">
         <v>100</v>
       </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
       <c r="F17" s="46"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
       <c r="K17" s="14">
         <v>3.1294599319079799</v>
       </c>
@@ -10666,20 +11057,20 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="52" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
       </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
       <c r="F18" s="46"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
       <c r="K18">
         <v>34.454845100484</v>
       </c>
@@ -10688,18 +11079,18 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="51"/>
+      <c r="A19" s="52"/>
       <c r="B19" s="3">
         <v>3</v>
       </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
       <c r="F19" s="46"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
       <c r="K19" s="4">
         <v>1.9521931441214699</v>
       </c>
@@ -10708,18 +11099,18 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="51"/>
+      <c r="A20" s="52"/>
       <c r="B20" s="3">
         <v>5</v>
       </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
       <c r="F20" s="46"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="52"/>
       <c r="K20" s="3">
         <v>2.0043440401661101</v>
       </c>
@@ -10728,18 +11119,18 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="53"/>
+      <c r="A21" s="60"/>
       <c r="B21" s="10">
         <v>10</v>
       </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
       <c r="F21" s="46"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
       <c r="K21" s="3">
         <v>2.0041611367035599</v>
       </c>
@@ -10752,14 +11143,14 @@
       <c r="B22" s="30">
         <v>100</v>
       </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
       <c r="F22" s="46"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="52"/>
       <c r="K22" s="3">
         <v>2.0126023888751998</v>
       </c>
@@ -10805,60 +11196,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:55" x14ac:dyDescent="0.25">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
       <c r="M1" s="21"/>
-      <c r="R1" s="39" t="s">
+      <c r="R1" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="39"/>
-      <c r="AB1" s="39"/>
-      <c r="AE1" s="39" t="s">
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="47"/>
+      <c r="AE1" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="39"/>
-      <c r="AH1" s="39"/>
-      <c r="AI1" s="39"/>
-      <c r="AJ1" s="39"/>
-      <c r="AK1" s="39"/>
-      <c r="AL1" s="39"/>
-      <c r="AM1" s="39"/>
-      <c r="AN1" s="47"/>
-      <c r="AO1" s="47"/>
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="47"/>
+      <c r="AJ1" s="47"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
+      <c r="AM1" s="47"/>
+      <c r="AN1" s="39"/>
+      <c r="AO1" s="39"/>
       <c r="AP1" s="21"/>
-      <c r="AR1" s="39" t="s">
+      <c r="AR1" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="AS1" s="39"/>
-      <c r="AT1" s="39"/>
-      <c r="AU1" s="39"/>
-      <c r="AV1" s="39"/>
-      <c r="AW1" s="39"/>
-      <c r="AX1" s="39"/>
-      <c r="AY1" s="39"/>
-      <c r="AZ1" s="39"/>
-      <c r="BA1" s="47"/>
-      <c r="BB1" s="47"/>
+      <c r="AS1" s="47"/>
+      <c r="AT1" s="47"/>
+      <c r="AU1" s="47"/>
+      <c r="AV1" s="47"/>
+      <c r="AW1" s="47"/>
+      <c r="AX1" s="47"/>
+      <c r="AY1" s="47"/>
+      <c r="AZ1" s="47"/>
+      <c r="BA1" s="39"/>
+      <c r="BB1" s="39"/>
     </row>
     <row r="2" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B2" s="40" t="s">
@@ -11676,11 +12067,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="AN2:AP2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
     <mergeCell ref="AK2:AM2"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="R1:AB1"/>
@@ -11697,26 +12083,31 @@
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AE2:AG2"/>
     <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AN2:AP2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11945,14 +12336,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58C277AC-42DD-4338-BD2A-AF7ECB0689E8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -11965,6 +12348,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/documents/ExperimentData.xlsx
+++ b/documents/ExperimentData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1b2bcfbbb34c0c/Documents/GitHub/meliso/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2154" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{823E71BB-C26D-4C1B-9EEC-0DE850420BDB}"/>
+  <xr:revisionPtr revIDLastSave="2159" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D2AE75C-F4EC-4F3C-BA84-02BC01E5B4CA}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="1" activeTab="3" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
   </bookViews>
   <sheets>
     <sheet name="DataExp1.1" sheetId="2" r:id="rId1"/>
@@ -511,7 +511,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -535,8 +535,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -550,31 +571,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -949,60 +949,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
       <c r="M1" s="21"/>
-      <c r="O1" s="47" t="s">
+      <c r="O1" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
-      <c r="X1" s="47"/>
-      <c r="Y1" s="47"/>
-      <c r="AB1" s="47" t="s">
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="AB1" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="47"/>
-      <c r="AH1" s="47"/>
-      <c r="AI1" s="47"/>
-      <c r="AJ1" s="47"/>
-      <c r="AK1" s="39"/>
-      <c r="AL1" s="39"/>
+      <c r="AC1" s="39"/>
+      <c r="AD1" s="39"/>
+      <c r="AE1" s="39"/>
+      <c r="AF1" s="39"/>
+      <c r="AG1" s="39"/>
+      <c r="AH1" s="39"/>
+      <c r="AI1" s="39"/>
+      <c r="AJ1" s="39"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
       <c r="AM1" s="21"/>
-      <c r="AO1" s="47" t="s">
+      <c r="AO1" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AP1" s="47"/>
-      <c r="AQ1" s="47"/>
-      <c r="AR1" s="47"/>
-      <c r="AS1" s="47"/>
-      <c r="AT1" s="47"/>
-      <c r="AU1" s="47"/>
-      <c r="AV1" s="47"/>
-      <c r="AW1" s="47"/>
-      <c r="AX1" s="39"/>
-      <c r="AY1" s="39"/>
+      <c r="AP1" s="39"/>
+      <c r="AQ1" s="39"/>
+      <c r="AR1" s="39"/>
+      <c r="AS1" s="39"/>
+      <c r="AT1" s="39"/>
+      <c r="AU1" s="39"/>
+      <c r="AV1" s="39"/>
+      <c r="AW1" s="39"/>
+      <c r="AX1" s="47"/>
+      <c r="AY1" s="47"/>
     </row>
     <row r="2" spans="2:52" x14ac:dyDescent="0.25">
       <c r="B2" s="40" t="s">
@@ -2574,60 +2574,60 @@
       <c r="D14" s="7"/>
     </row>
     <row r="15" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
       <c r="M15" s="21"/>
-      <c r="O15" s="47" t="s">
+      <c r="O15" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="47"/>
-      <c r="S15" s="47"/>
-      <c r="T15" s="47"/>
-      <c r="U15" s="47"/>
-      <c r="V15" s="47"/>
-      <c r="W15" s="47"/>
-      <c r="X15" s="47"/>
-      <c r="Y15" s="47"/>
-      <c r="AB15" s="47" t="s">
+      <c r="P15" s="39"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="39"/>
+      <c r="S15" s="39"/>
+      <c r="T15" s="39"/>
+      <c r="U15" s="39"/>
+      <c r="V15" s="39"/>
+      <c r="W15" s="39"/>
+      <c r="X15" s="39"/>
+      <c r="Y15" s="39"/>
+      <c r="AB15" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="AC15" s="47"/>
-      <c r="AD15" s="47"/>
-      <c r="AE15" s="47"/>
-      <c r="AF15" s="47"/>
-      <c r="AG15" s="47"/>
-      <c r="AH15" s="47"/>
-      <c r="AI15" s="47"/>
-      <c r="AJ15" s="47"/>
-      <c r="AK15" s="47"/>
-      <c r="AL15" s="47"/>
+      <c r="AC15" s="39"/>
+      <c r="AD15" s="39"/>
+      <c r="AE15" s="39"/>
+      <c r="AF15" s="39"/>
+      <c r="AG15" s="39"/>
+      <c r="AH15" s="39"/>
+      <c r="AI15" s="39"/>
+      <c r="AJ15" s="39"/>
+      <c r="AK15" s="39"/>
+      <c r="AL15" s="39"/>
       <c r="AM15" s="21"/>
-      <c r="AO15" s="47" t="s">
+      <c r="AO15" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="AP15" s="47"/>
-      <c r="AQ15" s="47"/>
-      <c r="AR15" s="47"/>
-      <c r="AS15" s="47"/>
-      <c r="AT15" s="47"/>
-      <c r="AU15" s="47"/>
-      <c r="AV15" s="47"/>
-      <c r="AW15" s="47"/>
-      <c r="AX15" s="47"/>
-      <c r="AY15" s="47"/>
+      <c r="AP15" s="39"/>
+      <c r="AQ15" s="39"/>
+      <c r="AR15" s="39"/>
+      <c r="AS15" s="39"/>
+      <c r="AT15" s="39"/>
+      <c r="AU15" s="39"/>
+      <c r="AV15" s="39"/>
+      <c r="AW15" s="39"/>
+      <c r="AX15" s="39"/>
+      <c r="AY15" s="39"/>
     </row>
     <row r="16" spans="2:52" x14ac:dyDescent="0.25">
       <c r="B16" s="40" t="s">
@@ -4026,46 +4026,46 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="O1:Y1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AB1:AL1"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AK2:AM2"/>
+    <mergeCell ref="AO1:AY1"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="O15:Y15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="U16:W16"/>
+    <mergeCell ref="X16:Z16"/>
+    <mergeCell ref="AO15:AY15"/>
+    <mergeCell ref="AO16:AQ16"/>
+    <mergeCell ref="AR16:AT16"/>
+    <mergeCell ref="AU16:AW16"/>
+    <mergeCell ref="AX16:AZ16"/>
     <mergeCell ref="AB15:AL15"/>
     <mergeCell ref="AB16:AD16"/>
     <mergeCell ref="AE16:AG16"/>
     <mergeCell ref="AH16:AJ16"/>
     <mergeCell ref="AK16:AM16"/>
-    <mergeCell ref="AO15:AY15"/>
-    <mergeCell ref="AO16:AQ16"/>
-    <mergeCell ref="AR16:AT16"/>
-    <mergeCell ref="AU16:AW16"/>
-    <mergeCell ref="AX16:AZ16"/>
-    <mergeCell ref="O15:Y15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="U16:W16"/>
-    <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="B15:L15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="AO1:AY1"/>
-    <mergeCell ref="AO2:AQ2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="AB1:AL1"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AK2:AM2"/>
-    <mergeCell ref="O1:Y1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4101,34 +4101,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="24" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
     </row>
     <row r="2" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M2" s="12"/>
@@ -4190,34 +4190,34 @@
       <c r="W3" s="36"/>
     </row>
     <row r="4" spans="1:26" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="57" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="54">
+      <c r="D4" s="50">
         <v>66</v>
       </c>
-      <c r="E4" s="54">
+      <c r="E4" s="50">
         <v>66</v>
       </c>
-      <c r="F4" s="55">
+      <c r="F4" s="60">
         <v>13000</v>
       </c>
-      <c r="G4" s="54">
+      <c r="G4" s="50">
         <v>1</v>
       </c>
-      <c r="H4" s="54">
+      <c r="H4" s="50">
         <v>1</v>
       </c>
-      <c r="I4" s="54">
+      <c r="I4" s="50">
         <v>66</v>
       </c>
-      <c r="J4" s="54">
+      <c r="J4" s="50">
         <v>66</v>
       </c>
       <c r="K4" s="5">
@@ -4261,18 +4261,18 @@
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="51"/>
+      <c r="A5" s="58"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
       <c r="K5" s="5">
         <f>AVERAGE(DataExp1.1!E4:E13)</f>
         <v>11.070752653739017</v>
@@ -4320,18 +4320,18 @@
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
+      <c r="A6" s="58"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
       <c r="K6" s="5">
         <f>AVERAGE(DataExp1.1!H4:H13)</f>
         <v>4.7480516396353174</v>
@@ -4379,18 +4379,18 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
+      <c r="A7" s="58"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
       <c r="K7" s="5">
         <f>AVERAGE(DataExp1.1!K4:K13)</f>
         <v>0.84932664663156276</v>
@@ -4416,18 +4416,18 @@
       <c r="W7" s="35"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
+      <c r="A8" s="58"/>
       <c r="B8" s="6">
         <v>20</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
@@ -4440,18 +4440,18 @@
       <c r="W8" s="35"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="51"/>
+      <c r="A9" s="58"/>
       <c r="B9" s="6">
         <v>50</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -4464,18 +4464,18 @@
       <c r="W9" s="35"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
+      <c r="A10" s="58"/>
       <c r="B10" s="6">
         <v>100</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
@@ -4510,20 +4510,20 @@
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="51" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
       <c r="K11" s="4">
         <f>AVERAGE(DataExp1.1!O4:O13)</f>
         <v>49.821904185231844</v>
@@ -4544,18 +4544,18 @@
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="52"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="3">
         <v>3</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
       <c r="K12" s="4">
         <f>AVERAGE(DataExp1.1!R4:R13)</f>
         <v>2.2585080679270888</v>
@@ -4576,18 +4576,18 @@
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="52"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="3">
         <v>5</v>
       </c>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
       <c r="K13" s="4">
         <f>AVERAGE(DataExp1.1!U4:U13)</f>
         <v>2.4443213833989064</v>
@@ -4608,18 +4608,18 @@
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="52"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="3">
         <v>10</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
       <c r="K14" s="4">
         <f>AVERAGE(DataExp1.1!X4:X13)</f>
         <v>2.0470536852897636</v>
@@ -4640,18 +4640,18 @@
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="52"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="3">
         <v>20</v>
       </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="52"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -4659,18 +4659,18 @@
       <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="52"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="3">
         <v>50</v>
       </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="52"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -4678,18 +4678,18 @@
       <c r="O16" s="4"/>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="52"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="3">
         <v>100</v>
       </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -4709,20 +4709,20 @@
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="53" t="s">
+      <c r="A18" s="59" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="32">
         <v>1</v>
       </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
       <c r="K18" s="22">
         <f>AVERAGE(DataExp1.1!AB4:AB13)</f>
         <v>2.0194039548285878</v>
@@ -4758,18 +4758,18 @@
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="53"/>
+      <c r="A19" s="59"/>
       <c r="B19" s="32">
         <v>3</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
       <c r="K19" s="22">
         <f>AVERAGE(DataExp1.1!AE4:AE13)</f>
         <v>3.0323916470832399</v>
@@ -4805,18 +4805,18 @@
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A20" s="53"/>
+      <c r="A20" s="59"/>
       <c r="B20" s="32">
         <v>5</v>
       </c>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="52"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
       <c r="K20" s="22">
         <f>AVERAGE(DataExp1.1!AH4:AH13)</f>
         <v>3.0970657292831891</v>
@@ -4852,18 +4852,18 @@
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A21" s="53"/>
+      <c r="A21" s="59"/>
       <c r="B21" s="32">
         <v>10</v>
       </c>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
       <c r="K21" s="22">
         <f>AVERAGE(DataExp1.1!AK4:AK13)</f>
         <v>3.0304601968108664</v>
@@ -4884,18 +4884,18 @@
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="53"/>
+      <c r="A22" s="59"/>
       <c r="B22" s="32">
         <v>20</v>
       </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="52"/>
-      <c r="J22" s="52"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
       <c r="K22" s="22"/>
       <c r="L22" s="22"/>
       <c r="M22" s="22"/>
@@ -4903,18 +4903,18 @@
       <c r="O22" s="22"/>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" s="53"/>
+      <c r="A23" s="59"/>
       <c r="B23" s="32">
         <v>50</v>
       </c>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="52"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
       <c r="K23" s="22"/>
       <c r="L23" s="22"/>
       <c r="M23" s="22"/>
@@ -4922,18 +4922,18 @@
       <c r="O23" s="22"/>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" s="53"/>
+      <c r="A24" s="59"/>
       <c r="B24" s="32">
         <v>100</v>
       </c>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="52"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="51"/>
       <c r="K24" s="22"/>
       <c r="L24" s="22"/>
       <c r="M24" s="22"/>
@@ -4956,20 +4956,20 @@
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A25" s="52" t="s">
+      <c r="A25" s="51" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="3">
         <v>1</v>
       </c>
-      <c r="C25" s="52"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="52"/>
-      <c r="J25" s="52"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="51"/>
       <c r="K25" s="4">
         <f>AVERAGE(DataExp1.1!AO4:AO13)</f>
         <v>34.552311810658352</v>
@@ -4990,18 +4990,18 @@
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A26" s="52"/>
+      <c r="A26" s="51"/>
       <c r="B26" s="3">
         <v>3</v>
       </c>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="52"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
       <c r="K26" s="4">
         <f>AVERAGE(DataExp1.1!AR4:AR14)</f>
         <v>1.8560190453181431</v>
@@ -5022,18 +5022,18 @@
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A27" s="52"/>
+      <c r="A27" s="51"/>
       <c r="B27" s="3">
         <v>5</v>
       </c>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="52"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
       <c r="K27" s="4">
         <f>AVERAGE(DataExp1.1!AU4:AU13)</f>
         <v>1.9127433590347436</v>
@@ -5054,18 +5054,18 @@
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A28" s="52"/>
+      <c r="A28" s="51"/>
       <c r="B28" s="3">
         <v>10</v>
       </c>
-      <c r="C28" s="52"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="52"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="52"/>
-      <c r="J28" s="52"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="51"/>
       <c r="K28" s="4">
         <f>AVERAGE(DataExp1.1!AX4:AX13)</f>
         <v>1.9259347567178799</v>
@@ -5086,18 +5086,18 @@
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A29" s="52"/>
+      <c r="A29" s="51"/>
       <c r="B29" s="3">
         <v>20</v>
       </c>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="52"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="51"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -5105,18 +5105,18 @@
       <c r="O29" s="4"/>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A30" s="52"/>
+      <c r="A30" s="51"/>
       <c r="B30" s="3">
         <v>50</v>
       </c>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -5124,18 +5124,18 @@
       <c r="O30" s="4"/>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A31" s="52"/>
+      <c r="A31" s="51"/>
       <c r="B31" s="3">
         <v>100</v>
       </c>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="52"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -5143,34 +5143,34 @@
       <c r="O31" s="4"/>
     </row>
     <row r="32" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="59" t="s">
+      <c r="A32" s="52" t="s">
         <v>12</v>
       </c>
       <c r="B32" s="3">
         <v>1</v>
       </c>
-      <c r="C32" s="52" t="s">
+      <c r="C32" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="52">
+      <c r="D32" s="51">
         <v>128</v>
       </c>
-      <c r="E32" s="52">
+      <c r="E32" s="51">
         <v>128</v>
       </c>
-      <c r="F32" s="60">
+      <c r="F32" s="53">
         <v>1.1200000000000001</v>
       </c>
-      <c r="G32" s="52">
+      <c r="G32" s="51">
         <v>1</v>
       </c>
-      <c r="H32" s="52">
+      <c r="H32" s="51">
         <v>1</v>
       </c>
-      <c r="I32" s="52">
+      <c r="I32" s="51">
         <v>128</v>
       </c>
-      <c r="J32" s="52">
+      <c r="J32" s="51">
         <v>128</v>
       </c>
       <c r="K32" s="3">
@@ -5213,18 +5213,18 @@
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A33" s="59"/>
+      <c r="A33" s="52"/>
       <c r="B33" s="3">
         <v>3</v>
       </c>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="52"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="52"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="51"/>
       <c r="K33" s="3">
         <f>AVERAGE(DataExp1.1!E18:E27)</f>
         <v>38.626208042487967</v>
@@ -5252,18 +5252,18 @@
       <c r="W33" s="35"/>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A34" s="59"/>
+      <c r="A34" s="52"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="56"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="51"/>
+      <c r="I34" s="51"/>
+      <c r="J34" s="51"/>
       <c r="K34" s="3">
         <f>AVERAGE(DataExp1.1!H18:H27)</f>
         <v>19.080341123339618</v>
@@ -5291,18 +5291,18 @@
       <c r="W34" s="35"/>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A35" s="59"/>
+      <c r="A35" s="52"/>
       <c r="B35" s="3">
         <v>10</v>
       </c>
-      <c r="C35" s="52"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
+      <c r="J35" s="51"/>
       <c r="K35" s="3">
         <f>AVERAGE(DataExp1.1!K18:K27)</f>
         <v>4.4322830974230261</v>
@@ -5327,18 +5327,18 @@
       <c r="W35" s="35"/>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A36" s="59"/>
+      <c r="A36" s="52"/>
       <c r="B36" s="3">
         <v>20</v>
       </c>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="52"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
+      <c r="J36" s="51"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="4"/>
@@ -5351,18 +5351,18 @@
       <c r="W36" s="35"/>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A37" s="59"/>
+      <c r="A37" s="52"/>
       <c r="B37" s="3">
         <v>50</v>
       </c>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="56"/>
-      <c r="G37" s="52"/>
-      <c r="H37" s="52"/>
-      <c r="I37" s="52"/>
-      <c r="J37" s="52"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="54"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="51"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="4"/>
@@ -5375,18 +5375,18 @@
       <c r="W37" s="35"/>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="59"/>
+      <c r="A38" s="52"/>
       <c r="B38" s="3">
         <v>100</v>
       </c>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="51"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="4"/>
@@ -5399,20 +5399,20 @@
       <c r="W38" s="35"/>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A39" s="57" t="s">
+      <c r="A39" s="48" t="s">
         <v>13</v>
       </c>
       <c r="B39" s="9">
         <v>1</v>
       </c>
-      <c r="C39" s="52"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="56"/>
-      <c r="G39" s="52"/>
-      <c r="H39" s="52"/>
-      <c r="I39" s="52"/>
-      <c r="J39" s="52"/>
+      <c r="C39" s="51"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="51"/>
+      <c r="J39" s="51"/>
       <c r="K39" s="9">
         <f>AVERAGE(DataExp1.1!O18:O27)</f>
         <v>157.51141235842792</v>
@@ -5432,18 +5432,18 @@
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A40" s="57"/>
+      <c r="A40" s="48"/>
       <c r="B40" s="9">
         <v>3</v>
       </c>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
+      <c r="C40" s="51"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="51"/>
+      <c r="I40" s="51"/>
+      <c r="J40" s="51"/>
       <c r="K40" s="9">
         <f>AVERAGE(DataExp1.1!R18:R27)</f>
         <v>5.370568162007002</v>
@@ -5463,18 +5463,18 @@
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A41" s="57"/>
+      <c r="A41" s="48"/>
       <c r="B41" s="9">
         <v>5</v>
       </c>
-      <c r="C41" s="52"/>
-      <c r="D41" s="52"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="52"/>
-      <c r="H41" s="52"/>
-      <c r="I41" s="52"/>
-      <c r="J41" s="52"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="51"/>
       <c r="K41" s="9">
         <f>AVERAGE(DataExp1.1!U18:U27)</f>
         <v>6.130019567236074</v>
@@ -5494,18 +5494,18 @@
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A42" s="57"/>
+      <c r="A42" s="48"/>
       <c r="B42" s="9">
         <v>10</v>
       </c>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="52"/>
+      <c r="C42" s="51"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="51"/>
+      <c r="H42" s="51"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="51"/>
       <c r="K42" s="9">
         <f>AVERAGE(DataExp1.1!X18:X27)</f>
         <v>6.2926813963615427</v>
@@ -5525,18 +5525,18 @@
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A43" s="57"/>
+      <c r="A43" s="48"/>
       <c r="B43" s="9">
         <v>20</v>
       </c>
-      <c r="C43" s="52"/>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="52"/>
-      <c r="H43" s="52"/>
-      <c r="I43" s="52"/>
-      <c r="J43" s="52"/>
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="51"/>
+      <c r="J43" s="51"/>
       <c r="K43" s="9"/>
       <c r="L43" s="9"/>
       <c r="M43" s="14"/>
@@ -5544,18 +5544,18 @@
       <c r="O43" s="14"/>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A44" s="57"/>
+      <c r="A44" s="48"/>
       <c r="B44" s="9">
         <v>50</v>
       </c>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="56"/>
-      <c r="G44" s="52"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="54"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="51"/>
+      <c r="I44" s="51"/>
+      <c r="J44" s="51"/>
       <c r="K44" s="9"/>
       <c r="L44" s="9"/>
       <c r="M44" s="14"/>
@@ -5563,18 +5563,18 @@
       <c r="O44" s="14"/>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A45" s="57"/>
+      <c r="A45" s="48"/>
       <c r="B45" s="9">
         <v>100</v>
       </c>
-      <c r="C45" s="52"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="56"/>
-      <c r="G45" s="52"/>
-      <c r="H45" s="52"/>
-      <c r="I45" s="52"/>
-      <c r="J45" s="52"/>
+      <c r="C45" s="51"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="51"/>
+      <c r="H45" s="51"/>
+      <c r="I45" s="51"/>
+      <c r="J45" s="51"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
       <c r="M45" s="14"/>
@@ -5582,20 +5582,20 @@
       <c r="O45" s="9"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A46" s="58" t="s">
+      <c r="A46" s="49" t="s">
         <v>14</v>
       </c>
       <c r="B46" s="32">
         <v>1</v>
       </c>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="56"/>
-      <c r="G46" s="52"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="52"/>
+      <c r="C46" s="51"/>
+      <c r="D46" s="51"/>
+      <c r="E46" s="51"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="51"/>
+      <c r="I46" s="51"/>
+      <c r="J46" s="51"/>
       <c r="K46" s="22">
         <f>AVERAGE(DataExp1.1!AB18:AB27)</f>
         <v>13.2679396369752</v>
@@ -5615,18 +5615,18 @@
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A47" s="58"/>
+      <c r="A47" s="49"/>
       <c r="B47" s="32">
         <v>3</v>
       </c>
-      <c r="C47" s="52"/>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="56"/>
-      <c r="G47" s="52"/>
-      <c r="H47" s="52"/>
-      <c r="I47" s="52"/>
-      <c r="J47" s="52"/>
+      <c r="C47" s="51"/>
+      <c r="D47" s="51"/>
+      <c r="E47" s="51"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="51"/>
+      <c r="H47" s="51"/>
+      <c r="I47" s="51"/>
+      <c r="J47" s="51"/>
       <c r="K47" s="22">
         <f>AVERAGE(DataExp1.1!AE18:AE27)</f>
         <v>1.8847515193214188</v>
@@ -5646,18 +5646,18 @@
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="58"/>
+      <c r="A48" s="49"/>
       <c r="B48" s="32">
         <v>5</v>
       </c>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="56"/>
-      <c r="G48" s="52"/>
-      <c r="H48" s="52"/>
-      <c r="I48" s="52"/>
-      <c r="J48" s="52"/>
+      <c r="C48" s="51"/>
+      <c r="D48" s="51"/>
+      <c r="E48" s="51"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="51"/>
+      <c r="H48" s="51"/>
+      <c r="I48" s="51"/>
+      <c r="J48" s="51"/>
       <c r="K48" s="22">
         <f>AVERAGE(DataExp1.1!AH18:AH27)</f>
         <v>1.9167287224860321</v>
@@ -5677,18 +5677,18 @@
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="58"/>
+      <c r="A49" s="49"/>
       <c r="B49" s="38">
         <v>10</v>
       </c>
-      <c r="C49" s="52"/>
-      <c r="D49" s="52"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="56"/>
-      <c r="G49" s="52"/>
-      <c r="H49" s="52"/>
-      <c r="I49" s="52"/>
-      <c r="J49" s="52"/>
+      <c r="C49" s="51"/>
+      <c r="D49" s="51"/>
+      <c r="E49" s="51"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="51"/>
+      <c r="H49" s="51"/>
+      <c r="I49" s="51"/>
+      <c r="J49" s="51"/>
       <c r="K49" s="22">
         <f>AVERAGE(DataExp1.1!AK18:AK27)</f>
         <v>1.9152230126798291</v>
@@ -5708,18 +5708,18 @@
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="58"/>
+      <c r="A50" s="49"/>
       <c r="B50" s="38">
         <v>20</v>
       </c>
-      <c r="C50" s="52"/>
-      <c r="D50" s="52"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="56"/>
-      <c r="G50" s="52"/>
-      <c r="H50" s="52"/>
-      <c r="I50" s="52"/>
-      <c r="J50" s="52"/>
+      <c r="C50" s="51"/>
+      <c r="D50" s="51"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="51"/>
+      <c r="H50" s="51"/>
+      <c r="I50" s="51"/>
+      <c r="J50" s="51"/>
       <c r="K50" s="22"/>
       <c r="L50" s="22"/>
       <c r="M50" s="22"/>
@@ -5727,18 +5727,18 @@
       <c r="O50" s="22"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="58"/>
+      <c r="A51" s="49"/>
       <c r="B51" s="38">
         <v>50</v>
       </c>
-      <c r="C51" s="52"/>
-      <c r="D51" s="52"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="56"/>
-      <c r="G51" s="52"/>
-      <c r="H51" s="52"/>
-      <c r="I51" s="52"/>
-      <c r="J51" s="52"/>
+      <c r="C51" s="51"/>
+      <c r="D51" s="51"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="51"/>
+      <c r="H51" s="51"/>
+      <c r="I51" s="51"/>
+      <c r="J51" s="51"/>
       <c r="K51" s="22"/>
       <c r="L51" s="22"/>
       <c r="M51" s="22"/>
@@ -5746,18 +5746,18 @@
       <c r="O51" s="22"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="58"/>
+      <c r="A52" s="49"/>
       <c r="B52" s="38">
         <v>100</v>
       </c>
-      <c r="C52" s="52"/>
-      <c r="D52" s="52"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="56"/>
-      <c r="G52" s="52"/>
-      <c r="H52" s="52"/>
-      <c r="I52" s="52"/>
-      <c r="J52" s="52"/>
+      <c r="C52" s="51"/>
+      <c r="D52" s="51"/>
+      <c r="E52" s="51"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="51"/>
+      <c r="H52" s="51"/>
+      <c r="I52" s="51"/>
+      <c r="J52" s="51"/>
       <c r="K52" s="32"/>
       <c r="L52" s="32"/>
       <c r="M52" s="22"/>
@@ -5765,20 +5765,20 @@
       <c r="O52" s="32"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="57" t="s">
+      <c r="A53" s="48" t="s">
         <v>15</v>
       </c>
       <c r="B53" s="9">
         <v>1</v>
       </c>
-      <c r="C53" s="52"/>
-      <c r="D53" s="52"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="56"/>
-      <c r="G53" s="52"/>
-      <c r="H53" s="52"/>
-      <c r="I53" s="52"/>
-      <c r="J53" s="52"/>
+      <c r="C53" s="51"/>
+      <c r="D53" s="51"/>
+      <c r="E53" s="51"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="51"/>
+      <c r="H53" s="51"/>
+      <c r="I53" s="51"/>
+      <c r="J53" s="51"/>
       <c r="K53" s="14">
         <f>AVERAGE(DataExp1.1!AO18:AO27)</f>
         <v>59.79535904859479</v>
@@ -5798,18 +5798,18 @@
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="57"/>
+      <c r="A54" s="48"/>
       <c r="B54" s="9">
         <v>3</v>
       </c>
-      <c r="C54" s="52"/>
-      <c r="D54" s="52"/>
-      <c r="E54" s="52"/>
-      <c r="F54" s="56"/>
-      <c r="G54" s="52"/>
-      <c r="H54" s="52"/>
-      <c r="I54" s="52"/>
-      <c r="J54" s="52"/>
+      <c r="C54" s="51"/>
+      <c r="D54" s="51"/>
+      <c r="E54" s="51"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="51"/>
+      <c r="H54" s="51"/>
+      <c r="I54" s="51"/>
+      <c r="J54" s="51"/>
       <c r="K54" s="14">
         <f>AVERAGE(DataExp1.1!AR18:AR27)</f>
         <v>4.1994209587286191</v>
@@ -5829,18 +5829,18 @@
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="57"/>
+      <c r="A55" s="48"/>
       <c r="B55" s="9">
         <v>5</v>
       </c>
-      <c r="C55" s="52"/>
-      <c r="D55" s="52"/>
-      <c r="E55" s="52"/>
-      <c r="F55" s="56"/>
-      <c r="G55" s="52"/>
-      <c r="H55" s="52"/>
-      <c r="I55" s="52"/>
-      <c r="J55" s="52"/>
+      <c r="C55" s="51"/>
+      <c r="D55" s="51"/>
+      <c r="E55" s="51"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="51"/>
+      <c r="H55" s="51"/>
+      <c r="I55" s="51"/>
+      <c r="J55" s="51"/>
       <c r="K55" s="14">
         <f>AVERAGE(DataExp1.1!AU18:AU27)</f>
         <v>4.4246201292478027</v>
@@ -5860,18 +5860,18 @@
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="57"/>
+      <c r="A56" s="48"/>
       <c r="B56" s="9">
         <v>10</v>
       </c>
-      <c r="C56" s="52"/>
-      <c r="D56" s="52"/>
-      <c r="E56" s="52"/>
-      <c r="F56" s="56"/>
-      <c r="G56" s="52"/>
-      <c r="H56" s="52"/>
-      <c r="I56" s="52"/>
-      <c r="J56" s="52"/>
+      <c r="C56" s="51"/>
+      <c r="D56" s="51"/>
+      <c r="E56" s="51"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="51"/>
+      <c r="H56" s="51"/>
+      <c r="I56" s="51"/>
+      <c r="J56" s="51"/>
       <c r="K56" s="14">
         <f>AVERAGE(DataExp1.1!AX18:AX27)</f>
         <v>4.1938757256751718</v>
@@ -5891,18 +5891,18 @@
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="57"/>
+      <c r="A57" s="48"/>
       <c r="B57" s="9">
         <v>20</v>
       </c>
-      <c r="C57" s="52"/>
-      <c r="D57" s="52"/>
-      <c r="E57" s="52"/>
-      <c r="F57" s="56"/>
-      <c r="G57" s="52"/>
-      <c r="H57" s="52"/>
-      <c r="I57" s="52"/>
-      <c r="J57" s="52"/>
+      <c r="C57" s="51"/>
+      <c r="D57" s="51"/>
+      <c r="E57" s="51"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="51"/>
+      <c r="H57" s="51"/>
+      <c r="I57" s="51"/>
+      <c r="J57" s="51"/>
       <c r="K57" s="14"/>
       <c r="L57" s="14"/>
       <c r="M57" s="14"/>
@@ -5910,18 +5910,18 @@
       <c r="O57" s="14"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="57"/>
+      <c r="A58" s="48"/>
       <c r="B58" s="9">
         <v>50</v>
       </c>
-      <c r="C58" s="52"/>
-      <c r="D58" s="52"/>
-      <c r="E58" s="52"/>
-      <c r="F58" s="56"/>
-      <c r="G58" s="52"/>
-      <c r="H58" s="52"/>
-      <c r="I58" s="52"/>
-      <c r="J58" s="52"/>
+      <c r="C58" s="51"/>
+      <c r="D58" s="51"/>
+      <c r="E58" s="51"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="51"/>
+      <c r="H58" s="51"/>
+      <c r="I58" s="51"/>
+      <c r="J58" s="51"/>
       <c r="K58" s="14"/>
       <c r="L58" s="14"/>
       <c r="M58" s="14"/>
@@ -5929,18 +5929,18 @@
       <c r="O58" s="14"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="57"/>
+      <c r="A59" s="48"/>
       <c r="B59" s="9">
         <v>100</v>
       </c>
-      <c r="C59" s="52"/>
-      <c r="D59" s="52"/>
-      <c r="E59" s="52"/>
-      <c r="F59" s="54"/>
-      <c r="G59" s="52"/>
-      <c r="H59" s="52"/>
-      <c r="I59" s="52"/>
-      <c r="J59" s="52"/>
+      <c r="C59" s="51"/>
+      <c r="D59" s="51"/>
+      <c r="E59" s="51"/>
+      <c r="F59" s="50"/>
+      <c r="G59" s="51"/>
+      <c r="H59" s="51"/>
+      <c r="I59" s="51"/>
+      <c r="J59" s="51"/>
       <c r="K59" s="9"/>
       <c r="L59" s="9"/>
       <c r="M59" s="14"/>
@@ -5949,6 +5949,17 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="C4:C31"/>
+    <mergeCell ref="D4:D31"/>
+    <mergeCell ref="E4:E31"/>
+    <mergeCell ref="G4:G31"/>
+    <mergeCell ref="H4:H31"/>
+    <mergeCell ref="F4:F31"/>
     <mergeCell ref="A39:A45"/>
     <mergeCell ref="A46:A52"/>
     <mergeCell ref="A53:A59"/>
@@ -5963,17 +5974,6 @@
     <mergeCell ref="I32:I59"/>
     <mergeCell ref="J32:J59"/>
     <mergeCell ref="F32:F59"/>
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="C4:C31"/>
-    <mergeCell ref="D4:D31"/>
-    <mergeCell ref="E4:E31"/>
-    <mergeCell ref="G4:G31"/>
-    <mergeCell ref="H4:H31"/>
-    <mergeCell ref="F4:F31"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5999,19 +5999,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
       <c r="M1" s="21"/>
     </row>
     <row r="2" spans="2:22" x14ac:dyDescent="0.25">
@@ -6502,19 +6502,19 @@
       <c r="D14" s="7"/>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
       <c r="M15" s="21"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.25">
@@ -6994,19 +6994,19 @@
       <c r="V27" s="5"/>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="39"/>
-      <c r="K29" s="39"/>
-      <c r="L29" s="39"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="47"/>
       <c r="M29" s="21"/>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.25">
@@ -7474,19 +7474,19 @@
       <c r="V41" s="5"/>
     </row>
     <row r="43" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B43" s="39" t="s">
+      <c r="B43" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="C43" s="39"/>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="39"/>
-      <c r="H43" s="39"/>
-      <c r="I43" s="39"/>
-      <c r="J43" s="39"/>
-      <c r="K43" s="39"/>
-      <c r="L43" s="39"/>
+      <c r="C43" s="47"/>
+      <c r="D43" s="47"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="47"/>
+      <c r="G43" s="47"/>
+      <c r="H43" s="47"/>
+      <c r="I43" s="47"/>
+      <c r="J43" s="47"/>
+      <c r="K43" s="47"/>
+      <c r="L43" s="47"/>
       <c r="M43" s="21"/>
     </row>
     <row r="44" spans="2:22" x14ac:dyDescent="0.25">
@@ -7889,22 +7889,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="B15:L15"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="T16:V16"/>
     <mergeCell ref="B29:L29"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="T30:V30"/>
@@ -7921,6 +7905,22 @@
     <mergeCell ref="H30:J30"/>
     <mergeCell ref="K30:M30"/>
     <mergeCell ref="N30:P30"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7939,34 +7939,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
     </row>
     <row r="3" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -8016,32 +8016,32 @@
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="57" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="54">
+      <c r="D4" s="50">
         <v>1025</v>
       </c>
-      <c r="E4" s="54">
+      <c r="E4" s="50">
         <v>1025</v>
       </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="54">
+      <c r="F4" s="60"/>
+      <c r="G4" s="50">
         <v>8</v>
       </c>
-      <c r="H4" s="54">
+      <c r="H4" s="50">
         <v>8</v>
       </c>
-      <c r="I4" s="54">
+      <c r="I4" s="50">
         <v>128</v>
       </c>
-      <c r="J4" s="54">
+      <c r="J4" s="50">
         <v>128</v>
       </c>
       <c r="K4" s="5">
@@ -8061,18 +8061,18 @@
       <c r="O4" s="14"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="51"/>
+      <c r="A5" s="58"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
       <c r="K5" s="5">
         <f>AVERAGE(DataExp1.2!E4:E13)</f>
         <v>553.53793602493806</v>
@@ -8090,18 +8090,18 @@
       <c r="O5" s="14"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
+      <c r="A6" s="58"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
       <c r="K6" s="5">
         <f>AVERAGE(DataExp1.2!H4:H13)</f>
         <v>433.9549506572348</v>
@@ -8119,18 +8119,18 @@
       <c r="O6" s="14"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
+      <c r="A7" s="58"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
       <c r="K7" s="5">
         <f>AVERAGE(DataExp1.2!K4:K13)</f>
         <v>10.838240342377034</v>
@@ -8148,18 +8148,18 @@
       <c r="O7" s="14"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
+      <c r="A8" s="58"/>
       <c r="B8" s="6">
         <v>20</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
       <c r="K8" s="5">
         <f>AVERAGE(DataExp1.2!N4:N13)</f>
         <v>7.8951699494837957</v>
@@ -8177,18 +8177,18 @@
       <c r="O8" s="14"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="51"/>
+      <c r="A9" s="58"/>
       <c r="B9" s="6">
         <v>50</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -8196,18 +8196,18 @@
       <c r="O9" s="14"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
+      <c r="A10" s="58"/>
       <c r="B10" s="6">
         <v>100</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
@@ -8215,20 +8215,20 @@
       <c r="O10" s="14"/>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="51" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
       <c r="K11" s="4">
         <f>AVERAGE(DataExp1.2!B18:B27)</f>
         <v>3178.1943497230322</v>
@@ -8246,18 +8246,18 @@
       <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="52"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="3">
         <v>3</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
       <c r="K12" s="4">
         <f>AVERAGE(DataExp1.2!E18:E27)</f>
         <v>75.685942333849169</v>
@@ -8275,18 +8275,18 @@
       <c r="O12" s="4"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="52"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="3">
         <v>5</v>
       </c>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
       <c r="K13" s="4">
         <f>AVERAGE(DataExp1.2!H18:H27)</f>
         <v>75.545904528375146</v>
@@ -8304,18 +8304,18 @@
       <c r="O13" s="4"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="52"/>
+      <c r="A14" s="51"/>
       <c r="B14" s="3">
         <v>10</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
       <c r="K14" s="4">
         <f>AVERAGE(DataExp1.2!K18:K27)</f>
         <v>95.698989447779951</v>
@@ -8333,18 +8333,18 @@
       <c r="O14" s="4"/>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="52"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="3">
         <v>20</v>
       </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="52"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4">
@@ -8356,18 +8356,18 @@
       <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="52"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="3">
         <v>50</v>
       </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="52"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -8375,18 +8375,18 @@
       <c r="O16" s="4"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="52"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="3">
         <v>100</v>
       </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -8394,20 +8394,20 @@
       <c r="O17" s="4"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="57" t="s">
+      <c r="A18" s="48" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="9">
         <v>1</v>
       </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
       <c r="K18" s="14">
         <f>AVERAGE(DataExp1.2!B32:B41)</f>
         <v>345.18704086729679</v>
@@ -8425,18 +8425,18 @@
       <c r="O18" s="14"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="57"/>
+      <c r="A19" s="48"/>
       <c r="B19" s="9">
         <v>3</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
       <c r="K19" s="14">
         <f>AVERAGE(DataExp1.2!E32:E41)</f>
         <v>38.921654436682005</v>
@@ -8454,18 +8454,18 @@
       <c r="O19" s="14"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="57"/>
+      <c r="A20" s="48"/>
       <c r="B20" s="9">
         <v>5</v>
       </c>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="52"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
       <c r="K20" s="14"/>
       <c r="L20" s="14"/>
       <c r="M20" s="14"/>
@@ -8473,18 +8473,18 @@
       <c r="O20" s="14"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="57"/>
+      <c r="A21" s="48"/>
       <c r="B21" s="9">
         <v>10</v>
       </c>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
       <c r="K21" s="14"/>
       <c r="L21" s="14"/>
       <c r="M21" s="14"/>
@@ -8492,18 +8492,18 @@
       <c r="O21" s="14"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="57"/>
+      <c r="A22" s="48"/>
       <c r="B22" s="9">
         <v>20</v>
       </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="52"/>
-      <c r="J22" s="52"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
       <c r="K22" s="14"/>
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
@@ -8511,18 +8511,18 @@
       <c r="O22" s="14"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="57"/>
+      <c r="A23" s="48"/>
       <c r="B23" s="9">
         <v>50</v>
       </c>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="52"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
@@ -8530,18 +8530,18 @@
       <c r="O23" s="14"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="57"/>
+      <c r="A24" s="48"/>
       <c r="B24" s="9">
         <v>100</v>
       </c>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="52"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="51"/>
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
@@ -8549,22 +8549,28 @@
       <c r="O24" s="14"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="52" t="s">
+      <c r="A25" s="51" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="3">
         <v>1</v>
       </c>
-      <c r="C25" s="52"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="56"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="52"/>
-      <c r="J25" s="52"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="4">
+        <f>AVERAGE(DataExp1.2!B46:B55)</f>
+        <v>1262.6496028081101</v>
+      </c>
+      <c r="L25" s="4">
+        <f>AVERAGE(DataExp1.2!C46:C55)</f>
+        <v>41.512947830762201</v>
+      </c>
       <c r="M25" s="4">
         <v>0.22804703269489901</v>
       </c>
@@ -8574,20 +8580,26 @@
       <c r="O25" s="4"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="52"/>
+      <c r="A26" s="51"/>
       <c r="B26" s="3">
         <v>3</v>
       </c>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="52"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="4">
+        <f>AVERAGE(DataExp1.2!E46:E55)</f>
+        <v>41.570259179869552</v>
+      </c>
+      <c r="L26" s="4">
+        <f>AVERAGE(DataExp1.2!F46:F55)</f>
+        <v>2.8487223773293939</v>
+      </c>
       <c r="M26" s="4">
         <v>0.41259237346931399</v>
       </c>
@@ -8597,18 +8609,18 @@
       <c r="O26" s="4"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="52"/>
+      <c r="A27" s="51"/>
       <c r="B27" s="3">
         <v>5</v>
       </c>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="52"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -8616,18 +8628,18 @@
       <c r="O27" s="4"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="52"/>
+      <c r="A28" s="51"/>
       <c r="B28" s="3">
         <v>10</v>
       </c>
-      <c r="C28" s="52"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="52"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="52"/>
-      <c r="J28" s="52"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="54"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="51"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -8635,18 +8647,18 @@
       <c r="O28" s="4"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="52"/>
+      <c r="A29" s="51"/>
       <c r="B29" s="3">
         <v>20</v>
       </c>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="52"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="51"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -8654,18 +8666,18 @@
       <c r="O29" s="4"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="52"/>
+      <c r="A30" s="51"/>
       <c r="B30" s="3">
         <v>50</v>
       </c>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -8673,18 +8685,18 @@
       <c r="O30" s="4"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="52"/>
+      <c r="A31" s="51"/>
       <c r="B31" s="3">
         <v>100</v>
       </c>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="52"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -8730,60 +8742,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:65" x14ac:dyDescent="0.25">
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
       <c r="M1" s="21"/>
-      <c r="R1" s="47" t="s">
+      <c r="R1" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
-      <c r="X1" s="47"/>
-      <c r="Y1" s="47"/>
-      <c r="Z1" s="47"/>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AI1" s="47" t="s">
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
+      <c r="AA1" s="39"/>
+      <c r="AB1" s="39"/>
+      <c r="AI1" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="AJ1" s="47"/>
-      <c r="AK1" s="47"/>
-      <c r="AL1" s="47"/>
-      <c r="AM1" s="47"/>
-      <c r="AN1" s="47"/>
-      <c r="AO1" s="47"/>
-      <c r="AP1" s="47"/>
-      <c r="AQ1" s="47"/>
-      <c r="AR1" s="39"/>
-      <c r="AS1" s="39"/>
+      <c r="AJ1" s="39"/>
+      <c r="AK1" s="39"/>
+      <c r="AL1" s="39"/>
+      <c r="AM1" s="39"/>
+      <c r="AN1" s="39"/>
+      <c r="AO1" s="39"/>
+      <c r="AP1" s="39"/>
+      <c r="AQ1" s="39"/>
+      <c r="AR1" s="47"/>
+      <c r="AS1" s="47"/>
       <c r="AT1" s="21"/>
-      <c r="AY1" s="47" t="s">
+      <c r="AY1" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AZ1" s="47"/>
-      <c r="BA1" s="47"/>
-      <c r="BB1" s="47"/>
-      <c r="BC1" s="47"/>
-      <c r="BD1" s="47"/>
-      <c r="BE1" s="47"/>
-      <c r="BF1" s="47"/>
-      <c r="BG1" s="47"/>
-      <c r="BH1" s="39"/>
-      <c r="BI1" s="39"/>
+      <c r="AZ1" s="39"/>
+      <c r="BA1" s="39"/>
+      <c r="BB1" s="39"/>
+      <c r="BC1" s="39"/>
+      <c r="BD1" s="39"/>
+      <c r="BE1" s="39"/>
+      <c r="BF1" s="39"/>
+      <c r="BG1" s="39"/>
+      <c r="BH1" s="47"/>
+      <c r="BI1" s="47"/>
     </row>
     <row r="2" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B2" s="40" t="s">
@@ -10025,6 +10037,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BH2:BJ2"/>
     <mergeCell ref="AY1:BI1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
@@ -10041,14 +10061,6 @@
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="AI2:AK2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BH2:BJ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10060,32 +10072,32 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:27" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="48" t="s">
+      <c r="D1" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
-      <c r="T1" s="49"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="49"/>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
+      <c r="AA1" s="56"/>
     </row>
     <row r="3" spans="1:27" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -10129,32 +10141,32 @@
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="58" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="6">
         <v>1</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="52">
+      <c r="D4" s="51">
         <v>66</v>
       </c>
-      <c r="E4" s="52">
+      <c r="E4" s="51">
         <v>66</v>
       </c>
       <c r="F4" s="62"/>
-      <c r="G4" s="52">
+      <c r="G4" s="51">
         <v>1</v>
       </c>
-      <c r="H4" s="52">
+      <c r="H4" s="51">
         <v>1</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4" s="51">
         <v>66</v>
       </c>
-      <c r="J4" s="52">
+      <c r="J4" s="51">
         <v>66</v>
       </c>
       <c r="K4" s="5">
@@ -10171,18 +10183,18 @@
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="51"/>
+      <c r="A5" s="58"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
       <c r="F5" s="63"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
       <c r="K5" s="5">
         <f>AVERAGE(DataExp2!E4:E8)</f>
         <v>6.7273250931611468</v>
@@ -10197,18 +10209,18 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
+      <c r="A6" s="58"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
       <c r="F6" s="63"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
       <c r="K6" s="5">
         <f>AVERAGE(DataExp2!H4:H8)</f>
         <v>2.8757780700062598</v>
@@ -10223,18 +10235,18 @@
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
+      <c r="A7" s="58"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
       <c r="F7" s="63"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
       <c r="K7" s="5">
         <f>AVERAGE(DataExp2!K4:K8)</f>
         <v>2.5245777936554679</v>
@@ -10249,18 +10261,18 @@
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
+      <c r="A8" s="58"/>
       <c r="B8" s="6">
         <v>1000</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
       <c r="F8" s="63"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
       <c r="K8" s="5">
         <f>AVERAGE(DataExp2!N4:N8)</f>
         <v>2.6210229749569218</v>
@@ -10275,20 +10287,20 @@
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="51" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
       <c r="F9" s="63"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
       <c r="K9" s="4">
         <f>AVERAGE(DataExp2!R4:R8)</f>
         <v>25.122901453825698</v>
@@ -10303,18 +10315,18 @@
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="52"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="3">
         <v>3</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
       <c r="F10" s="63"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
       <c r="K10" s="4">
         <f>AVERAGE(DataExp2!U4:U8)</f>
         <v>1.1978887514698182</v>
@@ -10329,18 +10341,18 @@
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="52"/>
+      <c r="A11" s="51"/>
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
       <c r="F11" s="63"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
       <c r="K11" s="4">
         <f>AVERAGE(DataExp2!X4:X8)</f>
         <v>2.7398509444970598</v>
@@ -10355,18 +10367,18 @@
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="52"/>
+      <c r="A12" s="51"/>
       <c r="B12" s="3">
         <v>10</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
       <c r="F12" s="63"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
       <c r="K12" s="4">
         <f>AVERAGE(DataExp2!AA4:AA8)</f>
         <v>2.3904188069590249</v>
@@ -10381,18 +10393,18 @@
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="52"/>
+      <c r="A13" s="51"/>
       <c r="B13" s="3">
         <v>1000</v>
       </c>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
       <c r="F13" s="63"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
       <c r="K13" s="4">
         <f>AVERAGE(DataExp2!AD4:AD8)</f>
         <v>3.118010443300594</v>
@@ -10407,20 +10419,20 @@
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="58" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="6">
         <v>1</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
       <c r="F14" s="63"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
       <c r="K14" s="14">
         <f>AVERAGE(DataExp2!AI4:AI8)</f>
         <v>2.018042671934988</v>
@@ -10435,18 +10447,18 @@
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="51"/>
+      <c r="A15" s="58"/>
       <c r="B15" s="6">
         <v>3</v>
       </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
       <c r="F15" s="63"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="52"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
       <c r="K15" s="14">
         <f>AVERAGE(DataExp2!AL4:AL8)</f>
         <v>2.9999089103706797</v>
@@ -10461,18 +10473,18 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="51"/>
+      <c r="A16" s="58"/>
       <c r="B16" s="6">
         <v>5</v>
       </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
       <c r="F16" s="63"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="52"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
       <c r="K16" s="14">
         <f>AVERAGE(DataExp2!AO4:AO8)</f>
         <v>3.0887572192386399</v>
@@ -10487,18 +10499,18 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="51"/>
+      <c r="A17" s="58"/>
       <c r="B17" s="6">
         <v>10</v>
       </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
       <c r="F17" s="63"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
       <c r="K17" s="14">
         <f>AVERAGE(DataExp2!AR4:AR8)</f>
         <v>3.0147786188702144</v>
@@ -10513,18 +10525,18 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="51"/>
+      <c r="A18" s="58"/>
       <c r="B18" s="6">
         <v>1000</v>
       </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
       <c r="F18" s="63"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
       <c r="K18" s="14">
         <f>AVERAGE(DataExp2!AU4:AU8)</f>
         <v>3.1022309678357018</v>
@@ -10539,20 +10551,20 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="52" t="s">
+      <c r="A19" s="51" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="3">
         <v>1</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
       <c r="F19" s="63"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
       <c r="K19" s="4">
         <f>AVERAGE(DataExp2!AY4:AY8)</f>
         <v>23.17734266838546</v>
@@ -10567,18 +10579,18 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="52"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
       <c r="F20" s="63"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="52"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
       <c r="K20" s="4">
         <f>AVERAGE(DataExp2!BB4:BB8)</f>
         <v>2.7741290185543344</v>
@@ -10593,18 +10605,18 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="52"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="3">
         <v>5</v>
       </c>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
       <c r="F21" s="63"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
       <c r="K21" s="4">
         <f>AVERAGE(DataExp2!BE4:BE8)</f>
         <v>2.776927957976338</v>
@@ -10619,18 +10631,18 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="60"/>
+      <c r="A22" s="53"/>
       <c r="B22" s="10">
         <v>10</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
       <c r="F22" s="63"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="53"/>
       <c r="K22" s="31">
         <f>AVERAGE(DataExp2!BH4:BH8)</f>
         <v>2.6552692879772497</v>
@@ -10743,26 +10755,26 @@
       <c r="B3" s="6">
         <v>1</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="52">
+      <c r="D3" s="51">
         <v>66</v>
       </c>
-      <c r="E3" s="52">
+      <c r="E3" s="51">
         <v>66</v>
       </c>
       <c r="F3" s="46"/>
-      <c r="G3" s="52">
+      <c r="G3" s="51">
         <v>1</v>
       </c>
-      <c r="H3" s="52">
+      <c r="H3" s="51">
         <v>1</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3" s="51">
         <v>66</v>
       </c>
-      <c r="J3" s="52">
+      <c r="J3" s="51">
         <v>66</v>
       </c>
       <c r="K3" s="9">
@@ -10777,14 +10789,14 @@
       <c r="B4" s="6">
         <v>3</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
       <c r="F4" s="46"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
       <c r="K4" s="14">
         <v>10.596633070539401</v>
       </c>
@@ -10797,14 +10809,14 @@
       <c r="B5" s="6">
         <v>5</v>
       </c>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
       <c r="F5" s="46"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
       <c r="K5" s="14">
         <v>4.5624707313509596</v>
       </c>
@@ -10817,14 +10829,14 @@
       <c r="B6" s="6">
         <v>10</v>
       </c>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
       <c r="F6" s="46"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
       <c r="K6" s="14">
         <v>0.610171518579538</v>
       </c>
@@ -10833,18 +10845,18 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="50"/>
+      <c r="A7" s="57"/>
       <c r="B7" s="6">
         <v>100</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
       <c r="F7" s="46"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
       <c r="K7" s="9">
         <v>0.56361848551125004</v>
       </c>
@@ -10853,20 +10865,20 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="60" t="s">
+      <c r="A8" s="53" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
       <c r="F8" s="46"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
       <c r="K8" s="4">
         <v>51.3708858392826</v>
       </c>
@@ -10875,18 +10887,18 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="56"/>
+      <c r="A9" s="54"/>
       <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
       <c r="F9" s="46"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
-      <c r="I9" s="52"/>
-      <c r="J9" s="52"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
       <c r="K9" s="4">
         <v>2.1067016984413098</v>
       </c>
@@ -10895,18 +10907,18 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="56"/>
+      <c r="A10" s="54"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
       <c r="F10" s="46"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
       <c r="K10" s="4">
         <v>2.8064566058312099</v>
       </c>
@@ -10915,18 +10927,18 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="56"/>
+      <c r="A11" s="54"/>
       <c r="B11" s="3">
         <v>10</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
       <c r="F11" s="46"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
       <c r="K11" s="4">
         <v>1.8870454425238199</v>
       </c>
@@ -10935,18 +10947,18 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="54"/>
+      <c r="A12" s="50"/>
       <c r="B12" s="3">
         <v>100</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
       <c r="F12" s="46"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
       <c r="K12" s="4">
         <v>1.6795645399372201</v>
       </c>
@@ -10961,14 +10973,14 @@
       <c r="B13" s="6">
         <v>1</v>
       </c>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
       <c r="F13" s="46"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
       <c r="K13" s="14">
         <v>1.97796965575553</v>
       </c>
@@ -10981,14 +10993,14 @@
       <c r="B14" s="6">
         <v>3</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
       <c r="F14" s="46"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
       <c r="K14" s="14">
         <v>3.1862607049915099</v>
       </c>
@@ -11001,14 +11013,14 @@
       <c r="B15" s="6">
         <v>5</v>
       </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
       <c r="F15" s="46"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="52"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
       <c r="K15" s="14">
         <v>3.1662124268938201</v>
       </c>
@@ -11021,14 +11033,14 @@
       <c r="B16" s="6">
         <v>10</v>
       </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
       <c r="F16" s="46"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="52"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
       <c r="K16" s="14">
         <v>3.0769912027266599</v>
       </c>
@@ -11037,18 +11049,18 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="50"/>
+      <c r="A17" s="57"/>
       <c r="B17" s="6">
         <v>100</v>
       </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
       <c r="F17" s="46"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="52"/>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
       <c r="K17" s="14">
         <v>3.1294599319079799</v>
       </c>
@@ -11057,20 +11069,20 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="51" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
       </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
       <c r="F18" s="46"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
       <c r="K18">
         <v>34.454845100484</v>
       </c>
@@ -11079,18 +11091,18 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="52"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="3">
         <v>3</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
       <c r="F19" s="46"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
       <c r="K19" s="4">
         <v>1.9521931441214699</v>
       </c>
@@ -11099,18 +11111,18 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="52"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="3">
         <v>5</v>
       </c>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
       <c r="F20" s="46"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="52"/>
-      <c r="J20" s="52"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
       <c r="K20" s="3">
         <v>2.0043440401661101</v>
       </c>
@@ -11119,18 +11131,18 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="60"/>
+      <c r="A21" s="53"/>
       <c r="B21" s="10">
         <v>10</v>
       </c>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
       <c r="F21" s="46"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="52"/>
-      <c r="J21" s="52"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
       <c r="K21" s="3">
         <v>2.0041611367035599</v>
       </c>
@@ -11143,14 +11155,14 @@
       <c r="B22" s="30">
         <v>100</v>
       </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
       <c r="F22" s="46"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="52"/>
-      <c r="J22" s="52"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
       <c r="K22" s="3">
         <v>2.0126023888751998</v>
       </c>
@@ -11196,60 +11208,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:55" x14ac:dyDescent="0.25">
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
       <c r="M1" s="21"/>
-      <c r="R1" s="47" t="s">
+      <c r="R1" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
-      <c r="X1" s="47"/>
-      <c r="Y1" s="47"/>
-      <c r="Z1" s="47"/>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="47"/>
-      <c r="AE1" s="47" t="s">
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
+      <c r="AA1" s="39"/>
+      <c r="AB1" s="39"/>
+      <c r="AE1" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="47"/>
-      <c r="AH1" s="47"/>
-      <c r="AI1" s="47"/>
-      <c r="AJ1" s="47"/>
-      <c r="AK1" s="47"/>
-      <c r="AL1" s="47"/>
-      <c r="AM1" s="47"/>
-      <c r="AN1" s="39"/>
-      <c r="AO1" s="39"/>
+      <c r="AF1" s="39"/>
+      <c r="AG1" s="39"/>
+      <c r="AH1" s="39"/>
+      <c r="AI1" s="39"/>
+      <c r="AJ1" s="39"/>
+      <c r="AK1" s="39"/>
+      <c r="AL1" s="39"/>
+      <c r="AM1" s="39"/>
+      <c r="AN1" s="47"/>
+      <c r="AO1" s="47"/>
       <c r="AP1" s="21"/>
-      <c r="AR1" s="47" t="s">
+      <c r="AR1" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="AS1" s="47"/>
-      <c r="AT1" s="47"/>
-      <c r="AU1" s="47"/>
-      <c r="AV1" s="47"/>
-      <c r="AW1" s="47"/>
-      <c r="AX1" s="47"/>
-      <c r="AY1" s="47"/>
-      <c r="AZ1" s="47"/>
-      <c r="BA1" s="39"/>
-      <c r="BB1" s="39"/>
+      <c r="AS1" s="39"/>
+      <c r="AT1" s="39"/>
+      <c r="AU1" s="39"/>
+      <c r="AV1" s="39"/>
+      <c r="AW1" s="39"/>
+      <c r="AX1" s="39"/>
+      <c r="AY1" s="39"/>
+      <c r="AZ1" s="39"/>
+      <c r="BA1" s="47"/>
+      <c r="BB1" s="47"/>
     </row>
     <row r="2" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B2" s="40" t="s">
@@ -12067,6 +12079,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="AN2:AP2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
     <mergeCell ref="AK2:AM2"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="R1:AB1"/>
@@ -12083,31 +12100,26 @@
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AE2:AG2"/>
     <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AN2:AP2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12336,6 +12348,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58C277AC-42DD-4338-BD2A-AF7ECB0689E8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -12348,14 +12368,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/documents/ExperimentData.xlsx
+++ b/documents/ExperimentData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1b2bcfbbb34c0c/Documents/GitHub/meliso/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2159" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D2AE75C-F4EC-4F3C-BA84-02BC01E5B4CA}"/>
+  <xr:revisionPtr revIDLastSave="2160" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DCBB456-E2A8-4269-BFE3-D7AD4C827807}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
   </bookViews>
@@ -511,7 +511,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -535,29 +535,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -571,10 +550,31 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -610,10 +610,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -949,60 +945,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
       <c r="M1" s="21"/>
-      <c r="O1" s="39" t="s">
+      <c r="O1" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="AB1" s="39" t="s">
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="AB1" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="AC1" s="39"/>
-      <c r="AD1" s="39"/>
-      <c r="AE1" s="39"/>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="39"/>
-      <c r="AH1" s="39"/>
-      <c r="AI1" s="39"/>
-      <c r="AJ1" s="39"/>
-      <c r="AK1" s="47"/>
-      <c r="AL1" s="47"/>
+      <c r="AC1" s="47"/>
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="47"/>
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="47"/>
+      <c r="AJ1" s="47"/>
+      <c r="AK1" s="39"/>
+      <c r="AL1" s="39"/>
       <c r="AM1" s="21"/>
-      <c r="AO1" s="39" t="s">
+      <c r="AO1" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="AP1" s="39"/>
-      <c r="AQ1" s="39"/>
-      <c r="AR1" s="39"/>
-      <c r="AS1" s="39"/>
-      <c r="AT1" s="39"/>
-      <c r="AU1" s="39"/>
-      <c r="AV1" s="39"/>
-      <c r="AW1" s="39"/>
-      <c r="AX1" s="47"/>
-      <c r="AY1" s="47"/>
+      <c r="AP1" s="47"/>
+      <c r="AQ1" s="47"/>
+      <c r="AR1" s="47"/>
+      <c r="AS1" s="47"/>
+      <c r="AT1" s="47"/>
+      <c r="AU1" s="47"/>
+      <c r="AV1" s="47"/>
+      <c r="AW1" s="47"/>
+      <c r="AX1" s="39"/>
+      <c r="AY1" s="39"/>
     </row>
     <row r="2" spans="2:52" x14ac:dyDescent="0.25">
       <c r="B2" s="40" t="s">
@@ -2574,60 +2570,60 @@
       <c r="D14" s="7"/>
     </row>
     <row r="15" spans="2:52" x14ac:dyDescent="0.25">
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
       <c r="M15" s="21"/>
-      <c r="O15" s="39" t="s">
+      <c r="O15" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="39"/>
-      <c r="R15" s="39"/>
-      <c r="S15" s="39"/>
-      <c r="T15" s="39"/>
-      <c r="U15" s="39"/>
-      <c r="V15" s="39"/>
-      <c r="W15" s="39"/>
-      <c r="X15" s="39"/>
-      <c r="Y15" s="39"/>
-      <c r="AB15" s="39" t="s">
+      <c r="P15" s="47"/>
+      <c r="Q15" s="47"/>
+      <c r="R15" s="47"/>
+      <c r="S15" s="47"/>
+      <c r="T15" s="47"/>
+      <c r="U15" s="47"/>
+      <c r="V15" s="47"/>
+      <c r="W15" s="47"/>
+      <c r="X15" s="47"/>
+      <c r="Y15" s="47"/>
+      <c r="AB15" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="AC15" s="39"/>
-      <c r="AD15" s="39"/>
-      <c r="AE15" s="39"/>
-      <c r="AF15" s="39"/>
-      <c r="AG15" s="39"/>
-      <c r="AH15" s="39"/>
-      <c r="AI15" s="39"/>
-      <c r="AJ15" s="39"/>
-      <c r="AK15" s="39"/>
-      <c r="AL15" s="39"/>
+      <c r="AC15" s="47"/>
+      <c r="AD15" s="47"/>
+      <c r="AE15" s="47"/>
+      <c r="AF15" s="47"/>
+      <c r="AG15" s="47"/>
+      <c r="AH15" s="47"/>
+      <c r="AI15" s="47"/>
+      <c r="AJ15" s="47"/>
+      <c r="AK15" s="47"/>
+      <c r="AL15" s="47"/>
       <c r="AM15" s="21"/>
-      <c r="AO15" s="39" t="s">
+      <c r="AO15" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="AP15" s="39"/>
-      <c r="AQ15" s="39"/>
-      <c r="AR15" s="39"/>
-      <c r="AS15" s="39"/>
-      <c r="AT15" s="39"/>
-      <c r="AU15" s="39"/>
-      <c r="AV15" s="39"/>
-      <c r="AW15" s="39"/>
-      <c r="AX15" s="39"/>
-      <c r="AY15" s="39"/>
+      <c r="AP15" s="47"/>
+      <c r="AQ15" s="47"/>
+      <c r="AR15" s="47"/>
+      <c r="AS15" s="47"/>
+      <c r="AT15" s="47"/>
+      <c r="AU15" s="47"/>
+      <c r="AV15" s="47"/>
+      <c r="AW15" s="47"/>
+      <c r="AX15" s="47"/>
+      <c r="AY15" s="47"/>
     </row>
     <row r="16" spans="2:52" x14ac:dyDescent="0.25">
       <c r="B16" s="40" t="s">
@@ -4026,46 +4022,46 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="AB15:AL15"/>
+    <mergeCell ref="AB16:AD16"/>
+    <mergeCell ref="AE16:AG16"/>
+    <mergeCell ref="AH16:AJ16"/>
+    <mergeCell ref="AK16:AM16"/>
+    <mergeCell ref="AO15:AY15"/>
+    <mergeCell ref="AO16:AQ16"/>
+    <mergeCell ref="AR16:AT16"/>
+    <mergeCell ref="AU16:AW16"/>
+    <mergeCell ref="AX16:AZ16"/>
+    <mergeCell ref="O15:Y15"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="U16:W16"/>
+    <mergeCell ref="X16:Z16"/>
+    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="AO1:AY1"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="AB1:AL1"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AK2:AM2"/>
+    <mergeCell ref="O1:Y1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="O1:Y1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AB1:AL1"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AK2:AM2"/>
-    <mergeCell ref="AO1:AY1"/>
-    <mergeCell ref="AO2:AQ2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="B15:L15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="O15:Y15"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="U16:W16"/>
-    <mergeCell ref="X16:Z16"/>
-    <mergeCell ref="AO15:AY15"/>
-    <mergeCell ref="AO16:AQ16"/>
-    <mergeCell ref="AR16:AT16"/>
-    <mergeCell ref="AU16:AW16"/>
-    <mergeCell ref="AX16:AZ16"/>
-    <mergeCell ref="AB15:AL15"/>
-    <mergeCell ref="AB16:AD16"/>
-    <mergeCell ref="AE16:AG16"/>
-    <mergeCell ref="AH16:AJ16"/>
-    <mergeCell ref="AK16:AM16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4096,39 +4092,39 @@
     <col min="19" max="19" width="10" style="35" customWidth="1"/>
     <col min="20" max="20" width="16.42578125" customWidth="1"/>
     <col min="21" max="21" width="16.7109375" customWidth="1"/>
-    <col min="22" max="22" width="15.5703125" customWidth="1"/>
+    <col min="22" max="22" width="15.42578125" customWidth="1"/>
     <col min="23" max="23" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="24" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="56"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
     </row>
     <row r="2" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M2" s="12"/>
@@ -4190,34 +4186,34 @@
       <c r="W3" s="36"/>
     </row>
     <row r="4" spans="1:26" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="50" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="50">
+      <c r="D4" s="54">
         <v>66</v>
       </c>
-      <c r="E4" s="50">
+      <c r="E4" s="54">
         <v>66</v>
       </c>
-      <c r="F4" s="60">
+      <c r="F4" s="55">
         <v>13000</v>
       </c>
-      <c r="G4" s="50">
+      <c r="G4" s="54">
         <v>1</v>
       </c>
-      <c r="H4" s="50">
+      <c r="H4" s="54">
         <v>1</v>
       </c>
-      <c r="I4" s="50">
+      <c r="I4" s="54">
         <v>66</v>
       </c>
-      <c r="J4" s="50">
+      <c r="J4" s="54">
         <v>66</v>
       </c>
       <c r="K4" s="5">
@@ -4261,18 +4257,18 @@
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="58"/>
+      <c r="A5" s="51"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
       <c r="K5" s="5">
         <f>AVERAGE(DataExp1.1!E4:E13)</f>
         <v>11.070752653739017</v>
@@ -4320,18 +4316,18 @@
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="58"/>
+      <c r="A6" s="51"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
       <c r="K6" s="5">
         <f>AVERAGE(DataExp1.1!H4:H13)</f>
         <v>4.7480516396353174</v>
@@ -4379,18 +4375,18 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="58"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
       <c r="K7" s="5">
         <f>AVERAGE(DataExp1.1!K4:K13)</f>
         <v>0.84932664663156276</v>
@@ -4416,18 +4412,18 @@
       <c r="W7" s="35"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="58"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="6">
         <v>20</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
@@ -4440,18 +4436,18 @@
       <c r="W8" s="35"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="58"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="6">
         <v>50</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -4464,18 +4460,18 @@
       <c r="W9" s="35"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="58"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="6">
         <v>100</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
@@ -4510,20 +4506,20 @@
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="51" t="s">
+      <c r="A11" s="52" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
       <c r="K11" s="4">
         <f>AVERAGE(DataExp1.1!O4:O13)</f>
         <v>49.821904185231844</v>
@@ -4544,18 +4540,18 @@
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="51"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="3">
         <v>3</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
       <c r="K12" s="4">
         <f>AVERAGE(DataExp1.1!R4:R13)</f>
         <v>2.2585080679270888</v>
@@ -4576,18 +4572,18 @@
       </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="51"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="3">
         <v>5</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
       <c r="K13" s="4">
         <f>AVERAGE(DataExp1.1!U4:U13)</f>
         <v>2.4443213833989064</v>
@@ -4608,18 +4604,18 @@
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="51"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="3">
         <v>10</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
       <c r="K14" s="4">
         <f>AVERAGE(DataExp1.1!X4:X13)</f>
         <v>2.0470536852897636</v>
@@ -4640,18 +4636,18 @@
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="51"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="3">
         <v>20</v>
       </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="52"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -4659,18 +4655,18 @@
       <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="51"/>
+      <c r="A16" s="52"/>
       <c r="B16" s="3">
         <v>50</v>
       </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="52"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -4678,18 +4674,18 @@
       <c r="O16" s="4"/>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="51"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="3">
         <v>100</v>
       </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -4709,20 +4705,20 @@
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" s="59" t="s">
+      <c r="A18" s="53" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="32">
         <v>1</v>
       </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
       <c r="K18" s="22">
         <f>AVERAGE(DataExp1.1!AB4:AB13)</f>
         <v>2.0194039548285878</v>
@@ -4758,18 +4754,18 @@
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" s="59"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="32">
         <v>3</v>
       </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
       <c r="K19" s="22">
         <f>AVERAGE(DataExp1.1!AE4:AE13)</f>
         <v>3.0323916470832399</v>
@@ -4805,18 +4801,18 @@
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A20" s="59"/>
+      <c r="A20" s="53"/>
       <c r="B20" s="32">
         <v>5</v>
       </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="52"/>
       <c r="K20" s="22">
         <f>AVERAGE(DataExp1.1!AH4:AH13)</f>
         <v>3.0970657292831891</v>
@@ -4852,18 +4848,18 @@
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A21" s="59"/>
+      <c r="A21" s="53"/>
       <c r="B21" s="32">
         <v>10</v>
       </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
       <c r="K21" s="22">
         <f>AVERAGE(DataExp1.1!AK4:AK13)</f>
         <v>3.0304601968108664</v>
@@ -4884,18 +4880,18 @@
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" s="59"/>
+      <c r="A22" s="53"/>
       <c r="B22" s="32">
         <v>20</v>
       </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="52"/>
       <c r="K22" s="22"/>
       <c r="L22" s="22"/>
       <c r="M22" s="22"/>
@@ -4903,18 +4899,18 @@
       <c r="O22" s="22"/>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" s="59"/>
+      <c r="A23" s="53"/>
       <c r="B23" s="32">
         <v>50</v>
       </c>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="52"/>
       <c r="K23" s="22"/>
       <c r="L23" s="22"/>
       <c r="M23" s="22"/>
@@ -4922,18 +4918,18 @@
       <c r="O23" s="22"/>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" s="59"/>
+      <c r="A24" s="53"/>
       <c r="B24" s="32">
         <v>100</v>
       </c>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="51"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="52"/>
       <c r="K24" s="22"/>
       <c r="L24" s="22"/>
       <c r="M24" s="22"/>
@@ -4956,20 +4952,20 @@
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A25" s="51" t="s">
+      <c r="A25" s="52" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="3">
         <v>1</v>
       </c>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="51"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="52"/>
       <c r="K25" s="4">
         <f>AVERAGE(DataExp1.1!AO4:AO13)</f>
         <v>34.552311810658352</v>
@@ -4990,18 +4986,18 @@
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A26" s="51"/>
+      <c r="A26" s="52"/>
       <c r="B26" s="3">
         <v>3</v>
       </c>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="51"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="52"/>
       <c r="K26" s="4">
         <f>AVERAGE(DataExp1.1!AR4:AR14)</f>
         <v>1.8560190453181431</v>
@@ -5022,18 +5018,18 @@
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A27" s="51"/>
+      <c r="A27" s="52"/>
       <c r="B27" s="3">
         <v>5</v>
       </c>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="51"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
       <c r="K27" s="4">
         <f>AVERAGE(DataExp1.1!AU4:AU13)</f>
         <v>1.9127433590347436</v>
@@ -5054,18 +5050,18 @@
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A28" s="51"/>
+      <c r="A28" s="52"/>
       <c r="B28" s="3">
         <v>10</v>
       </c>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="51"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="52"/>
       <c r="K28" s="4">
         <f>AVERAGE(DataExp1.1!AX4:AX13)</f>
         <v>1.9259347567178799</v>
@@ -5086,18 +5082,18 @@
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A29" s="51"/>
+      <c r="A29" s="52"/>
       <c r="B29" s="3">
         <v>20</v>
       </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="52"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -5105,18 +5101,18 @@
       <c r="O29" s="4"/>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A30" s="51"/>
+      <c r="A30" s="52"/>
       <c r="B30" s="3">
         <v>50</v>
       </c>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -5124,18 +5120,18 @@
       <c r="O30" s="4"/>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A31" s="51"/>
+      <c r="A31" s="52"/>
       <c r="B31" s="3">
         <v>100</v>
       </c>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="52"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -5143,34 +5139,34 @@
       <c r="O31" s="4"/>
     </row>
     <row r="32" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="52" t="s">
+      <c r="A32" s="59" t="s">
         <v>12</v>
       </c>
       <c r="B32" s="3">
         <v>1</v>
       </c>
-      <c r="C32" s="51" t="s">
+      <c r="C32" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="51">
+      <c r="D32" s="52">
         <v>128</v>
       </c>
-      <c r="E32" s="51">
+      <c r="E32" s="52">
         <v>128</v>
       </c>
-      <c r="F32" s="53">
+      <c r="F32" s="60">
         <v>1.1200000000000001</v>
       </c>
-      <c r="G32" s="51">
+      <c r="G32" s="52">
         <v>1</v>
       </c>
-      <c r="H32" s="51">
+      <c r="H32" s="52">
         <v>1</v>
       </c>
-      <c r="I32" s="51">
+      <c r="I32" s="52">
         <v>128</v>
       </c>
-      <c r="J32" s="51">
+      <c r="J32" s="52">
         <v>128</v>
       </c>
       <c r="K32" s="3">
@@ -5213,18 +5209,18 @@
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A33" s="52"/>
+      <c r="A33" s="59"/>
       <c r="B33" s="3">
         <v>3</v>
       </c>
-      <c r="C33" s="51"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="51"/>
-      <c r="J33" s="51"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="52"/>
       <c r="K33" s="3">
         <f>AVERAGE(DataExp1.1!E18:E27)</f>
         <v>38.626208042487967</v>
@@ -5252,18 +5248,18 @@
       <c r="W33" s="35"/>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A34" s="52"/>
+      <c r="A34" s="59"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="54"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="51"/>
-      <c r="I34" s="51"/>
-      <c r="J34" s="51"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="56"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
       <c r="K34" s="3">
         <f>AVERAGE(DataExp1.1!H18:H27)</f>
         <v>19.080341123339618</v>
@@ -5291,18 +5287,18 @@
       <c r="W34" s="35"/>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A35" s="52"/>
+      <c r="A35" s="59"/>
       <c r="B35" s="3">
         <v>10</v>
       </c>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="54"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="51"/>
-      <c r="J35" s="51"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
       <c r="K35" s="3">
         <f>AVERAGE(DataExp1.1!K18:K27)</f>
         <v>4.4322830974230261</v>
@@ -5327,18 +5323,18 @@
       <c r="W35" s="35"/>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A36" s="52"/>
+      <c r="A36" s="59"/>
       <c r="B36" s="3">
         <v>20</v>
       </c>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
-      <c r="J36" s="51"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="52"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="4"/>
@@ -5351,18 +5347,18 @@
       <c r="W36" s="35"/>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A37" s="52"/>
+      <c r="A37" s="59"/>
       <c r="B37" s="3">
         <v>50</v>
       </c>
-      <c r="C37" s="51"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="52"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="4"/>
@@ -5375,18 +5371,18 @@
       <c r="W37" s="35"/>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A38" s="52"/>
+      <c r="A38" s="59"/>
       <c r="B38" s="3">
         <v>100</v>
       </c>
-      <c r="C38" s="51"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="51"/>
-      <c r="J38" s="51"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="4"/>
@@ -5399,20 +5395,20 @@
       <c r="W38" s="35"/>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A39" s="48" t="s">
+      <c r="A39" s="57" t="s">
         <v>13</v>
       </c>
       <c r="B39" s="9">
         <v>1</v>
       </c>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="54"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="51"/>
-      <c r="J39" s="51"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="52"/>
       <c r="K39" s="9">
         <f>AVERAGE(DataExp1.1!O18:O27)</f>
         <v>157.51141235842792</v>
@@ -5432,18 +5428,18 @@
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A40" s="48"/>
+      <c r="A40" s="57"/>
       <c r="B40" s="9">
         <v>3</v>
       </c>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="54"/>
-      <c r="G40" s="51"/>
-      <c r="H40" s="51"/>
-      <c r="I40" s="51"/>
-      <c r="J40" s="51"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
       <c r="K40" s="9">
         <f>AVERAGE(DataExp1.1!R18:R27)</f>
         <v>5.370568162007002</v>
@@ -5463,18 +5459,18 @@
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A41" s="48"/>
+      <c r="A41" s="57"/>
       <c r="B41" s="9">
         <v>5</v>
       </c>
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="51"/>
-      <c r="H41" s="51"/>
-      <c r="I41" s="51"/>
-      <c r="J41" s="51"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="52"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="52"/>
       <c r="K41" s="9">
         <f>AVERAGE(DataExp1.1!U18:U27)</f>
         <v>6.130019567236074</v>
@@ -5494,18 +5490,18 @@
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A42" s="48"/>
+      <c r="A42" s="57"/>
       <c r="B42" s="9">
         <v>10</v>
       </c>
-      <c r="C42" s="51"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="54"/>
-      <c r="G42" s="51"/>
-      <c r="H42" s="51"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="51"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
       <c r="K42" s="9">
         <f>AVERAGE(DataExp1.1!X18:X27)</f>
         <v>6.2926813963615427</v>
@@ -5525,18 +5521,18 @@
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A43" s="48"/>
+      <c r="A43" s="57"/>
       <c r="B43" s="9">
         <v>20</v>
       </c>
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="54"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="51"/>
-      <c r="I43" s="51"/>
-      <c r="J43" s="51"/>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="52"/>
+      <c r="H43" s="52"/>
+      <c r="I43" s="52"/>
+      <c r="J43" s="52"/>
       <c r="K43" s="9"/>
       <c r="L43" s="9"/>
       <c r="M43" s="14"/>
@@ -5544,18 +5540,18 @@
       <c r="O43" s="14"/>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A44" s="48"/>
+      <c r="A44" s="57"/>
       <c r="B44" s="9">
         <v>50</v>
       </c>
-      <c r="C44" s="51"/>
-      <c r="D44" s="51"/>
-      <c r="E44" s="51"/>
-      <c r="F44" s="54"/>
-      <c r="G44" s="51"/>
-      <c r="H44" s="51"/>
-      <c r="I44" s="51"/>
-      <c r="J44" s="51"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="52"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
       <c r="K44" s="9"/>
       <c r="L44" s="9"/>
       <c r="M44" s="14"/>
@@ -5563,18 +5559,18 @@
       <c r="O44" s="14"/>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A45" s="48"/>
+      <c r="A45" s="57"/>
       <c r="B45" s="9">
         <v>100</v>
       </c>
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="54"/>
-      <c r="G45" s="51"/>
-      <c r="H45" s="51"/>
-      <c r="I45" s="51"/>
-      <c r="J45" s="51"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="52"/>
+      <c r="H45" s="52"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="52"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
       <c r="M45" s="14"/>
@@ -5582,20 +5578,20 @@
       <c r="O45" s="9"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A46" s="49" t="s">
+      <c r="A46" s="58" t="s">
         <v>14</v>
       </c>
       <c r="B46" s="32">
         <v>1</v>
       </c>
-      <c r="C46" s="51"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="51"/>
-      <c r="F46" s="54"/>
-      <c r="G46" s="51"/>
-      <c r="H46" s="51"/>
-      <c r="I46" s="51"/>
-      <c r="J46" s="51"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
       <c r="K46" s="22">
         <f>AVERAGE(DataExp1.1!AB18:AB27)</f>
         <v>13.2679396369752</v>
@@ -5615,18 +5611,18 @@
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A47" s="49"/>
+      <c r="A47" s="58"/>
       <c r="B47" s="32">
         <v>3</v>
       </c>
-      <c r="C47" s="51"/>
-      <c r="D47" s="51"/>
-      <c r="E47" s="51"/>
-      <c r="F47" s="54"/>
-      <c r="G47" s="51"/>
-      <c r="H47" s="51"/>
-      <c r="I47" s="51"/>
-      <c r="J47" s="51"/>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="56"/>
+      <c r="G47" s="52"/>
+      <c r="H47" s="52"/>
+      <c r="I47" s="52"/>
+      <c r="J47" s="52"/>
       <c r="K47" s="22">
         <f>AVERAGE(DataExp1.1!AE18:AE27)</f>
         <v>1.8847515193214188</v>
@@ -5646,18 +5642,18 @@
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A48" s="49"/>
+      <c r="A48" s="58"/>
       <c r="B48" s="32">
         <v>5</v>
       </c>
-      <c r="C48" s="51"/>
-      <c r="D48" s="51"/>
-      <c r="E48" s="51"/>
-      <c r="F48" s="54"/>
-      <c r="G48" s="51"/>
-      <c r="H48" s="51"/>
-      <c r="I48" s="51"/>
-      <c r="J48" s="51"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="56"/>
+      <c r="G48" s="52"/>
+      <c r="H48" s="52"/>
+      <c r="I48" s="52"/>
+      <c r="J48" s="52"/>
       <c r="K48" s="22">
         <f>AVERAGE(DataExp1.1!AH18:AH27)</f>
         <v>1.9167287224860321</v>
@@ -5677,18 +5673,18 @@
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="49"/>
+      <c r="A49" s="58"/>
       <c r="B49" s="38">
         <v>10</v>
       </c>
-      <c r="C49" s="51"/>
-      <c r="D49" s="51"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="54"/>
-      <c r="G49" s="51"/>
-      <c r="H49" s="51"/>
-      <c r="I49" s="51"/>
-      <c r="J49" s="51"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="52"/>
+      <c r="H49" s="52"/>
+      <c r="I49" s="52"/>
+      <c r="J49" s="52"/>
       <c r="K49" s="22">
         <f>AVERAGE(DataExp1.1!AK18:AK27)</f>
         <v>1.9152230126798291</v>
@@ -5708,18 +5704,18 @@
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="49"/>
+      <c r="A50" s="58"/>
       <c r="B50" s="38">
         <v>20</v>
       </c>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="54"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="51"/>
-      <c r="I50" s="51"/>
-      <c r="J50" s="51"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="56"/>
+      <c r="G50" s="52"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="52"/>
+      <c r="J50" s="52"/>
       <c r="K50" s="22"/>
       <c r="L50" s="22"/>
       <c r="M50" s="22"/>
@@ -5727,18 +5723,18 @@
       <c r="O50" s="22"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="49"/>
+      <c r="A51" s="58"/>
       <c r="B51" s="38">
         <v>50</v>
       </c>
-      <c r="C51" s="51"/>
-      <c r="D51" s="51"/>
-      <c r="E51" s="51"/>
-      <c r="F51" s="54"/>
-      <c r="G51" s="51"/>
-      <c r="H51" s="51"/>
-      <c r="I51" s="51"/>
-      <c r="J51" s="51"/>
+      <c r="C51" s="52"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="52"/>
+      <c r="H51" s="52"/>
+      <c r="I51" s="52"/>
+      <c r="J51" s="52"/>
       <c r="K51" s="22"/>
       <c r="L51" s="22"/>
       <c r="M51" s="22"/>
@@ -5746,18 +5742,18 @@
       <c r="O51" s="22"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="49"/>
+      <c r="A52" s="58"/>
       <c r="B52" s="38">
         <v>100</v>
       </c>
-      <c r="C52" s="51"/>
-      <c r="D52" s="51"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="54"/>
-      <c r="G52" s="51"/>
-      <c r="H52" s="51"/>
-      <c r="I52" s="51"/>
-      <c r="J52" s="51"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="56"/>
+      <c r="G52" s="52"/>
+      <c r="H52" s="52"/>
+      <c r="I52" s="52"/>
+      <c r="J52" s="52"/>
       <c r="K52" s="32"/>
       <c r="L52" s="32"/>
       <c r="M52" s="22"/>
@@ -5765,20 +5761,20 @@
       <c r="O52" s="32"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="48" t="s">
+      <c r="A53" s="57" t="s">
         <v>15</v>
       </c>
       <c r="B53" s="9">
         <v>1</v>
       </c>
-      <c r="C53" s="51"/>
-      <c r="D53" s="51"/>
-      <c r="E53" s="51"/>
-      <c r="F53" s="54"/>
-      <c r="G53" s="51"/>
-      <c r="H53" s="51"/>
-      <c r="I53" s="51"/>
-      <c r="J53" s="51"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="52"/>
+      <c r="E53" s="52"/>
+      <c r="F53" s="56"/>
+      <c r="G53" s="52"/>
+      <c r="H53" s="52"/>
+      <c r="I53" s="52"/>
+      <c r="J53" s="52"/>
       <c r="K53" s="14">
         <f>AVERAGE(DataExp1.1!AO18:AO27)</f>
         <v>59.79535904859479</v>
@@ -5798,18 +5794,18 @@
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="48"/>
+      <c r="A54" s="57"/>
       <c r="B54" s="9">
         <v>3</v>
       </c>
-      <c r="C54" s="51"/>
-      <c r="D54" s="51"/>
-      <c r="E54" s="51"/>
-      <c r="F54" s="54"/>
-      <c r="G54" s="51"/>
-      <c r="H54" s="51"/>
-      <c r="I54" s="51"/>
-      <c r="J54" s="51"/>
+      <c r="C54" s="52"/>
+      <c r="D54" s="52"/>
+      <c r="E54" s="52"/>
+      <c r="F54" s="56"/>
+      <c r="G54" s="52"/>
+      <c r="H54" s="52"/>
+      <c r="I54" s="52"/>
+      <c r="J54" s="52"/>
       <c r="K54" s="14">
         <f>AVERAGE(DataExp1.1!AR18:AR27)</f>
         <v>4.1994209587286191</v>
@@ -5829,18 +5825,18 @@
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="48"/>
+      <c r="A55" s="57"/>
       <c r="B55" s="9">
         <v>5</v>
       </c>
-      <c r="C55" s="51"/>
-      <c r="D55" s="51"/>
-      <c r="E55" s="51"/>
-      <c r="F55" s="54"/>
-      <c r="G55" s="51"/>
-      <c r="H55" s="51"/>
-      <c r="I55" s="51"/>
-      <c r="J55" s="51"/>
+      <c r="C55" s="52"/>
+      <c r="D55" s="52"/>
+      <c r="E55" s="52"/>
+      <c r="F55" s="56"/>
+      <c r="G55" s="52"/>
+      <c r="H55" s="52"/>
+      <c r="I55" s="52"/>
+      <c r="J55" s="52"/>
       <c r="K55" s="14">
         <f>AVERAGE(DataExp1.1!AU18:AU27)</f>
         <v>4.4246201292478027</v>
@@ -5860,18 +5856,18 @@
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="48"/>
+      <c r="A56" s="57"/>
       <c r="B56" s="9">
         <v>10</v>
       </c>
-      <c r="C56" s="51"/>
-      <c r="D56" s="51"/>
-      <c r="E56" s="51"/>
-      <c r="F56" s="54"/>
-      <c r="G56" s="51"/>
-      <c r="H56" s="51"/>
-      <c r="I56" s="51"/>
-      <c r="J56" s="51"/>
+      <c r="C56" s="52"/>
+      <c r="D56" s="52"/>
+      <c r="E56" s="52"/>
+      <c r="F56" s="56"/>
+      <c r="G56" s="52"/>
+      <c r="H56" s="52"/>
+      <c r="I56" s="52"/>
+      <c r="J56" s="52"/>
       <c r="K56" s="14">
         <f>AVERAGE(DataExp1.1!AX18:AX27)</f>
         <v>4.1938757256751718</v>
@@ -5891,18 +5887,18 @@
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="48"/>
+      <c r="A57" s="57"/>
       <c r="B57" s="9">
         <v>20</v>
       </c>
-      <c r="C57" s="51"/>
-      <c r="D57" s="51"/>
-      <c r="E57" s="51"/>
-      <c r="F57" s="54"/>
-      <c r="G57" s="51"/>
-      <c r="H57" s="51"/>
-      <c r="I57" s="51"/>
-      <c r="J57" s="51"/>
+      <c r="C57" s="52"/>
+      <c r="D57" s="52"/>
+      <c r="E57" s="52"/>
+      <c r="F57" s="56"/>
+      <c r="G57" s="52"/>
+      <c r="H57" s="52"/>
+      <c r="I57" s="52"/>
+      <c r="J57" s="52"/>
       <c r="K57" s="14"/>
       <c r="L57" s="14"/>
       <c r="M57" s="14"/>
@@ -5910,18 +5906,18 @@
       <c r="O57" s="14"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="48"/>
+      <c r="A58" s="57"/>
       <c r="B58" s="9">
         <v>50</v>
       </c>
-      <c r="C58" s="51"/>
-      <c r="D58" s="51"/>
-      <c r="E58" s="51"/>
-      <c r="F58" s="54"/>
-      <c r="G58" s="51"/>
-      <c r="H58" s="51"/>
-      <c r="I58" s="51"/>
-      <c r="J58" s="51"/>
+      <c r="C58" s="52"/>
+      <c r="D58" s="52"/>
+      <c r="E58" s="52"/>
+      <c r="F58" s="56"/>
+      <c r="G58" s="52"/>
+      <c r="H58" s="52"/>
+      <c r="I58" s="52"/>
+      <c r="J58" s="52"/>
       <c r="K58" s="14"/>
       <c r="L58" s="14"/>
       <c r="M58" s="14"/>
@@ -5929,18 +5925,18 @@
       <c r="O58" s="14"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="48"/>
+      <c r="A59" s="57"/>
       <c r="B59" s="9">
         <v>100</v>
       </c>
-      <c r="C59" s="51"/>
-      <c r="D59" s="51"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="50"/>
-      <c r="G59" s="51"/>
-      <c r="H59" s="51"/>
-      <c r="I59" s="51"/>
-      <c r="J59" s="51"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="52"/>
+      <c r="E59" s="52"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="52"/>
+      <c r="H59" s="52"/>
+      <c r="I59" s="52"/>
+      <c r="J59" s="52"/>
       <c r="K59" s="9"/>
       <c r="L59" s="9"/>
       <c r="M59" s="14"/>
@@ -5949,17 +5945,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="C4:C31"/>
-    <mergeCell ref="D4:D31"/>
-    <mergeCell ref="E4:E31"/>
-    <mergeCell ref="G4:G31"/>
-    <mergeCell ref="H4:H31"/>
-    <mergeCell ref="F4:F31"/>
     <mergeCell ref="A39:A45"/>
     <mergeCell ref="A46:A52"/>
     <mergeCell ref="A53:A59"/>
@@ -5974,6 +5959,17 @@
     <mergeCell ref="I32:I59"/>
     <mergeCell ref="J32:J59"/>
     <mergeCell ref="F32:F59"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="C4:C31"/>
+    <mergeCell ref="D4:D31"/>
+    <mergeCell ref="E4:E31"/>
+    <mergeCell ref="G4:G31"/>
+    <mergeCell ref="H4:H31"/>
+    <mergeCell ref="F4:F31"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5999,19 +5995,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
       <c r="M1" s="21"/>
     </row>
     <row r="2" spans="2:22" x14ac:dyDescent="0.25">
@@ -6502,19 +6498,19 @@
       <c r="D14" s="7"/>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
       <c r="M15" s="21"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.25">
@@ -6994,19 +6990,19 @@
       <c r="V27" s="5"/>
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="39"/>
       <c r="M29" s="21"/>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.25">
@@ -7474,19 +7470,19 @@
       <c r="V41" s="5"/>
     </row>
     <row r="43" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B43" s="47" t="s">
+      <c r="B43" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="47"/>
-      <c r="I43" s="47"/>
-      <c r="J43" s="47"/>
-      <c r="K43" s="47"/>
-      <c r="L43" s="47"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="39"/>
+      <c r="F43" s="39"/>
+      <c r="G43" s="39"/>
+      <c r="H43" s="39"/>
+      <c r="I43" s="39"/>
+      <c r="J43" s="39"/>
+      <c r="K43" s="39"/>
+      <c r="L43" s="39"/>
       <c r="M43" s="21"/>
     </row>
     <row r="44" spans="2:22" x14ac:dyDescent="0.25">
@@ -7889,6 +7885,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="T16:V16"/>
     <mergeCell ref="B29:L29"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="T30:V30"/>
@@ -7905,22 +7917,6 @@
     <mergeCell ref="H30:J30"/>
     <mergeCell ref="K30:M30"/>
     <mergeCell ref="N30:P30"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="B15:L15"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="T16:V16"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7929,44 +7925,45 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CACBC33-D91B-42B9-AA21-9BA30A2BE58A}">
   <dimension ref="A1:Z31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="56"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
     </row>
     <row r="3" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -8016,32 +8013,32 @@
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="50" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="50">
-        <v>1025</v>
-      </c>
-      <c r="E4" s="50">
-        <v>1025</v>
-      </c>
-      <c r="F4" s="60"/>
-      <c r="G4" s="50">
+      <c r="D4" s="54">
+        <v>1005</v>
+      </c>
+      <c r="E4" s="54">
+        <v>1005</v>
+      </c>
+      <c r="F4" s="55"/>
+      <c r="G4" s="54">
         <v>8</v>
       </c>
-      <c r="H4" s="50">
+      <c r="H4" s="54">
         <v>8</v>
       </c>
-      <c r="I4" s="50">
+      <c r="I4" s="54">
         <v>128</v>
       </c>
-      <c r="J4" s="50">
+      <c r="J4" s="54">
         <v>128</v>
       </c>
       <c r="K4" s="5">
@@ -8061,18 +8058,18 @@
       <c r="O4" s="14"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="58"/>
+      <c r="A5" s="51"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="54"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
       <c r="K5" s="5">
         <f>AVERAGE(DataExp1.2!E4:E13)</f>
         <v>553.53793602493806</v>
@@ -8090,18 +8087,18 @@
       <c r="O5" s="14"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="58"/>
+      <c r="A6" s="51"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
       <c r="K6" s="5">
         <f>AVERAGE(DataExp1.2!H4:H13)</f>
         <v>433.9549506572348</v>
@@ -8119,18 +8116,18 @@
       <c r="O6" s="14"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="58"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="54"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
       <c r="K7" s="5">
         <f>AVERAGE(DataExp1.2!K4:K13)</f>
         <v>10.838240342377034</v>
@@ -8148,18 +8145,18 @@
       <c r="O7" s="14"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="58"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="6">
         <v>20</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
       <c r="K8" s="5">
         <f>AVERAGE(DataExp1.2!N4:N13)</f>
         <v>7.8951699494837957</v>
@@ -8177,18 +8174,18 @@
       <c r="O8" s="14"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="58"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="6">
         <v>50</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -8196,18 +8193,18 @@
       <c r="O9" s="14"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="58"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="6">
         <v>100</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
@@ -8215,20 +8212,20 @@
       <c r="O10" s="14"/>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="51" t="s">
+      <c r="A11" s="52" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
       <c r="K11" s="4">
         <f>AVERAGE(DataExp1.2!B18:B27)</f>
         <v>3178.1943497230322</v>
@@ -8246,18 +8243,18 @@
       <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="51"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="3">
         <v>3</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
       <c r="K12" s="4">
         <f>AVERAGE(DataExp1.2!E18:E27)</f>
         <v>75.685942333849169</v>
@@ -8275,18 +8272,18 @@
       <c r="O12" s="4"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="51"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="3">
         <v>5</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
       <c r="K13" s="4">
         <f>AVERAGE(DataExp1.2!H18:H27)</f>
         <v>75.545904528375146</v>
@@ -8304,18 +8301,18 @@
       <c r="O13" s="4"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="51"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="3">
         <v>10</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
       <c r="K14" s="4">
         <f>AVERAGE(DataExp1.2!K18:K27)</f>
         <v>95.698989447779951</v>
@@ -8333,18 +8330,18 @@
       <c r="O14" s="4"/>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="51"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="3">
         <v>20</v>
       </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="52"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4">
@@ -8356,18 +8353,18 @@
       <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="51"/>
+      <c r="A16" s="52"/>
       <c r="B16" s="3">
         <v>50</v>
       </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="52"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -8375,18 +8372,18 @@
       <c r="O16" s="4"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="51"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="3">
         <v>100</v>
       </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -8394,20 +8391,20 @@
       <c r="O17" s="4"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="48" t="s">
+      <c r="A18" s="57" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="9">
         <v>1</v>
       </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
       <c r="K18" s="14">
         <f>AVERAGE(DataExp1.2!B32:B41)</f>
         <v>345.18704086729679</v>
@@ -8425,18 +8422,18 @@
       <c r="O18" s="14"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="48"/>
+      <c r="A19" s="57"/>
       <c r="B19" s="9">
         <v>3</v>
       </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
       <c r="K19" s="14">
         <f>AVERAGE(DataExp1.2!E32:E41)</f>
         <v>38.921654436682005</v>
@@ -8454,18 +8451,18 @@
       <c r="O19" s="14"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="48"/>
+      <c r="A20" s="57"/>
       <c r="B20" s="9">
         <v>5</v>
       </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="52"/>
       <c r="K20" s="14"/>
       <c r="L20" s="14"/>
       <c r="M20" s="14"/>
@@ -8473,18 +8470,18 @@
       <c r="O20" s="14"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
+      <c r="A21" s="57"/>
       <c r="B21" s="9">
         <v>10</v>
       </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
       <c r="K21" s="14"/>
       <c r="L21" s="14"/>
       <c r="M21" s="14"/>
@@ -8492,18 +8489,18 @@
       <c r="O21" s="14"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="48"/>
+      <c r="A22" s="57"/>
       <c r="B22" s="9">
         <v>20</v>
       </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="52"/>
       <c r="K22" s="14"/>
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
@@ -8511,18 +8508,18 @@
       <c r="O22" s="14"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="48"/>
+      <c r="A23" s="57"/>
       <c r="B23" s="9">
         <v>50</v>
       </c>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="52"/>
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
@@ -8530,18 +8527,18 @@
       <c r="O23" s="14"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="48"/>
+      <c r="A24" s="57"/>
       <c r="B24" s="9">
         <v>100</v>
       </c>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="51"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="52"/>
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
@@ -8549,28 +8546,22 @@
       <c r="O24" s="14"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="51" t="s">
+      <c r="A25" s="52" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="3">
         <v>1</v>
       </c>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="51"/>
-      <c r="K25" s="4">
-        <f>AVERAGE(DataExp1.2!B46:B55)</f>
-        <v>1262.6496028081101</v>
-      </c>
-      <c r="L25" s="4">
-        <f>AVERAGE(DataExp1.2!C46:C55)</f>
-        <v>41.512947830762201</v>
-      </c>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
       <c r="M25" s="4">
         <v>0.22804703269489901</v>
       </c>
@@ -8580,26 +8571,20 @@
       <c r="O25" s="4"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="51"/>
+      <c r="A26" s="52"/>
       <c r="B26" s="3">
         <v>3</v>
       </c>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="51"/>
-      <c r="K26" s="4">
-        <f>AVERAGE(DataExp1.2!E46:E55)</f>
-        <v>41.570259179869552</v>
-      </c>
-      <c r="L26" s="4">
-        <f>AVERAGE(DataExp1.2!F46:F55)</f>
-        <v>2.8487223773293939</v>
-      </c>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
       <c r="M26" s="4">
         <v>0.41259237346931399</v>
       </c>
@@ -8609,18 +8594,18 @@
       <c r="O26" s="4"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="51"/>
+      <c r="A27" s="52"/>
       <c r="B27" s="3">
         <v>5</v>
       </c>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="51"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="51"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -8628,18 +8613,18 @@
       <c r="O27" s="4"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="51"/>
+      <c r="A28" s="52"/>
       <c r="B28" s="3">
         <v>10</v>
       </c>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="51"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="52"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -8647,18 +8632,18 @@
       <c r="O28" s="4"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="51"/>
+      <c r="A29" s="52"/>
       <c r="B29" s="3">
         <v>20</v>
       </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="54"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="52"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -8666,18 +8651,18 @@
       <c r="O29" s="4"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="51"/>
+      <c r="A30" s="52"/>
       <c r="B30" s="3">
         <v>50</v>
       </c>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -8685,18 +8670,18 @@
       <c r="O30" s="4"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="51"/>
+      <c r="A31" s="52"/>
       <c r="B31" s="3">
         <v>100</v>
       </c>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="52"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -8742,60 +8727,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:65" x14ac:dyDescent="0.25">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
       <c r="M1" s="21"/>
-      <c r="R1" s="39" t="s">
+      <c r="R1" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="39"/>
-      <c r="AB1" s="39"/>
-      <c r="AI1" s="39" t="s">
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="47"/>
+      <c r="AI1" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="AJ1" s="39"/>
-      <c r="AK1" s="39"/>
-      <c r="AL1" s="39"/>
-      <c r="AM1" s="39"/>
-      <c r="AN1" s="39"/>
-      <c r="AO1" s="39"/>
-      <c r="AP1" s="39"/>
-      <c r="AQ1" s="39"/>
-      <c r="AR1" s="47"/>
-      <c r="AS1" s="47"/>
+      <c r="AJ1" s="47"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
+      <c r="AM1" s="47"/>
+      <c r="AN1" s="47"/>
+      <c r="AO1" s="47"/>
+      <c r="AP1" s="47"/>
+      <c r="AQ1" s="47"/>
+      <c r="AR1" s="39"/>
+      <c r="AS1" s="39"/>
       <c r="AT1" s="21"/>
-      <c r="AY1" s="39" t="s">
+      <c r="AY1" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="AZ1" s="39"/>
-      <c r="BA1" s="39"/>
-      <c r="BB1" s="39"/>
-      <c r="BC1" s="39"/>
-      <c r="BD1" s="39"/>
-      <c r="BE1" s="39"/>
-      <c r="BF1" s="39"/>
-      <c r="BG1" s="39"/>
-      <c r="BH1" s="47"/>
-      <c r="BI1" s="47"/>
+      <c r="AZ1" s="47"/>
+      <c r="BA1" s="47"/>
+      <c r="BB1" s="47"/>
+      <c r="BC1" s="47"/>
+      <c r="BD1" s="47"/>
+      <c r="BE1" s="47"/>
+      <c r="BF1" s="47"/>
+      <c r="BG1" s="47"/>
+      <c r="BH1" s="39"/>
+      <c r="BI1" s="39"/>
     </row>
     <row r="2" spans="2:65" x14ac:dyDescent="0.25">
       <c r="B2" s="40" t="s">
@@ -10037,14 +10022,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="AI2:AK2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BH2:BJ2"/>
     <mergeCell ref="AY1:BI1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
@@ -10061,6 +10038,14 @@
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BH2:BJ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10072,32 +10057,32 @@
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:27" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="55" t="s">
+      <c r="D1" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="56"/>
-      <c r="AA1" s="56"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="49"/>
+      <c r="P1" s="49"/>
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
+      <c r="Y1" s="49"/>
+      <c r="Z1" s="49"/>
+      <c r="AA1" s="49"/>
     </row>
     <row r="3" spans="1:27" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -10141,32 +10126,32 @@
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="51" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="6">
         <v>1</v>
       </c>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="51">
+      <c r="D4" s="52">
         <v>66</v>
       </c>
-      <c r="E4" s="51">
+      <c r="E4" s="52">
         <v>66</v>
       </c>
       <c r="F4" s="62"/>
-      <c r="G4" s="51">
+      <c r="G4" s="52">
         <v>1</v>
       </c>
-      <c r="H4" s="51">
+      <c r="H4" s="52">
         <v>1</v>
       </c>
-      <c r="I4" s="51">
+      <c r="I4" s="52">
         <v>66</v>
       </c>
-      <c r="J4" s="51">
+      <c r="J4" s="52">
         <v>66</v>
       </c>
       <c r="K4" s="5">
@@ -10183,18 +10168,18 @@
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="58"/>
+      <c r="A5" s="51"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
       <c r="F5" s="63"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
       <c r="K5" s="5">
         <f>AVERAGE(DataExp2!E4:E8)</f>
         <v>6.7273250931611468</v>
@@ -10209,18 +10194,18 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="58"/>
+      <c r="A6" s="51"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
       <c r="F6" s="63"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
       <c r="K6" s="5">
         <f>AVERAGE(DataExp2!H4:H8)</f>
         <v>2.8757780700062598</v>
@@ -10235,18 +10220,18 @@
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="58"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
       <c r="F7" s="63"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
       <c r="K7" s="5">
         <f>AVERAGE(DataExp2!K4:K8)</f>
         <v>2.5245777936554679</v>
@@ -10261,18 +10246,18 @@
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="58"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="6">
         <v>1000</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
       <c r="F8" s="63"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
       <c r="K8" s="5">
         <f>AVERAGE(DataExp2!N4:N8)</f>
         <v>2.6210229749569218</v>
@@ -10287,20 +10272,20 @@
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="51" t="s">
+      <c r="A9" s="52" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
       <c r="F9" s="63"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
       <c r="K9" s="4">
         <f>AVERAGE(DataExp2!R4:R8)</f>
         <v>25.122901453825698</v>
@@ -10315,18 +10300,18 @@
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="3">
         <v>3</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
       <c r="F10" s="63"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
       <c r="K10" s="4">
         <f>AVERAGE(DataExp2!U4:U8)</f>
         <v>1.1978887514698182</v>
@@ -10341,18 +10326,18 @@
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="51"/>
+      <c r="A11" s="52"/>
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
       <c r="F11" s="63"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
       <c r="K11" s="4">
         <f>AVERAGE(DataExp2!X4:X8)</f>
         <v>2.7398509444970598</v>
@@ -10367,18 +10352,18 @@
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="51"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="3">
         <v>10</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
       <c r="F12" s="63"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
       <c r="K12" s="4">
         <f>AVERAGE(DataExp2!AA4:AA8)</f>
         <v>2.3904188069590249</v>
@@ -10393,18 +10378,18 @@
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="51"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="3">
         <v>1000</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
       <c r="F13" s="63"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
       <c r="K13" s="4">
         <f>AVERAGE(DataExp2!AD4:AD8)</f>
         <v>3.118010443300594</v>
@@ -10419,20 +10404,20 @@
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="58" t="s">
+      <c r="A14" s="51" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="6">
         <v>1</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
       <c r="F14" s="63"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
       <c r="K14" s="14">
         <f>AVERAGE(DataExp2!AI4:AI8)</f>
         <v>2.018042671934988</v>
@@ -10447,18 +10432,18 @@
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="58"/>
+      <c r="A15" s="51"/>
       <c r="B15" s="6">
         <v>3</v>
       </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
       <c r="F15" s="63"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="52"/>
       <c r="K15" s="14">
         <f>AVERAGE(DataExp2!AL4:AL8)</f>
         <v>2.9999089103706797</v>
@@ -10473,18 +10458,18 @@
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="58"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="6">
         <v>5</v>
       </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
       <c r="F16" s="63"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="52"/>
       <c r="K16" s="14">
         <f>AVERAGE(DataExp2!AO4:AO8)</f>
         <v>3.0887572192386399</v>
@@ -10499,18 +10484,18 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="58"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="6">
         <v>10</v>
       </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
       <c r="F17" s="63"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
       <c r="K17" s="14">
         <f>AVERAGE(DataExp2!AR4:AR8)</f>
         <v>3.0147786188702144</v>
@@ -10525,18 +10510,18 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="58"/>
+      <c r="A18" s="51"/>
       <c r="B18" s="6">
         <v>1000</v>
       </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
       <c r="F18" s="63"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
       <c r="K18" s="14">
         <f>AVERAGE(DataExp2!AU4:AU8)</f>
         <v>3.1022309678357018</v>
@@ -10551,20 +10536,20 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="51" t="s">
+      <c r="A19" s="52" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="3">
         <v>1</v>
       </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
       <c r="F19" s="63"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
       <c r="K19" s="4">
         <f>AVERAGE(DataExp2!AY4:AY8)</f>
         <v>23.17734266838546</v>
@@ -10579,18 +10564,18 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="51"/>
+      <c r="A20" s="52"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
       <c r="F20" s="63"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="52"/>
       <c r="K20" s="4">
         <f>AVERAGE(DataExp2!BB4:BB8)</f>
         <v>2.7741290185543344</v>
@@ -10605,18 +10590,18 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="51"/>
+      <c r="A21" s="52"/>
       <c r="B21" s="3">
         <v>5</v>
       </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
       <c r="F21" s="63"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
       <c r="K21" s="4">
         <f>AVERAGE(DataExp2!BE4:BE8)</f>
         <v>2.776927957976338</v>
@@ -10631,18 +10616,18 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="53"/>
+      <c r="A22" s="60"/>
       <c r="B22" s="10">
         <v>10</v>
       </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
       <c r="F22" s="63"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="60"/>
       <c r="K22" s="31">
         <f>AVERAGE(DataExp2!BH4:BH8)</f>
         <v>2.6552692879772497</v>
@@ -10705,9 +10690,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{109AAA12-50B0-4DB2-B0E7-B06F76284A15}">
   <dimension ref="A2:L22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" ht="60" x14ac:dyDescent="0.25">
@@ -10755,26 +10740,26 @@
       <c r="B3" s="6">
         <v>1</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="51">
+      <c r="D3" s="52">
         <v>66</v>
       </c>
-      <c r="E3" s="51">
+      <c r="E3" s="52">
         <v>66</v>
       </c>
       <c r="F3" s="46"/>
-      <c r="G3" s="51">
+      <c r="G3" s="52">
         <v>1</v>
       </c>
-      <c r="H3" s="51">
+      <c r="H3" s="52">
         <v>1</v>
       </c>
-      <c r="I3" s="51">
+      <c r="I3" s="52">
         <v>66</v>
       </c>
-      <c r="J3" s="51">
+      <c r="J3" s="52">
         <v>66</v>
       </c>
       <c r="K3" s="9">
@@ -10789,14 +10774,14 @@
       <c r="B4" s="6">
         <v>3</v>
       </c>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
       <c r="F4" s="46"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
       <c r="K4" s="14">
         <v>10.596633070539401</v>
       </c>
@@ -10809,14 +10794,14 @@
       <c r="B5" s="6">
         <v>5</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
       <c r="F5" s="46"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
       <c r="K5" s="14">
         <v>4.5624707313509596</v>
       </c>
@@ -10829,14 +10814,14 @@
       <c r="B6" s="6">
         <v>10</v>
       </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
       <c r="F6" s="46"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
       <c r="K6" s="14">
         <v>0.610171518579538</v>
       </c>
@@ -10845,18 +10830,18 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="57"/>
+      <c r="A7" s="50"/>
       <c r="B7" s="6">
         <v>100</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
       <c r="F7" s="46"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
       <c r="K7" s="9">
         <v>0.56361848551125004</v>
       </c>
@@ -10865,20 +10850,20 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="60" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
       </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
       <c r="F8" s="46"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="52"/>
       <c r="K8" s="4">
         <v>51.3708858392826</v>
       </c>
@@ -10887,18 +10872,18 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="54"/>
+      <c r="A9" s="56"/>
       <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
       <c r="F9" s="46"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
+      <c r="J9" s="52"/>
       <c r="K9" s="4">
         <v>2.1067016984413098</v>
       </c>
@@ -10907,18 +10892,18 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="54"/>
+      <c r="A10" s="56"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
       <c r="F10" s="46"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
       <c r="K10" s="4">
         <v>2.8064566058312099</v>
       </c>
@@ -10927,18 +10912,18 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="54"/>
+      <c r="A11" s="56"/>
       <c r="B11" s="3">
         <v>10</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
       <c r="F11" s="46"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
       <c r="K11" s="4">
         <v>1.8870454425238199</v>
       </c>
@@ -10947,18 +10932,18 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="50"/>
+      <c r="A12" s="54"/>
       <c r="B12" s="3">
         <v>100</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
       <c r="F12" s="46"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
       <c r="K12" s="4">
         <v>1.6795645399372201</v>
       </c>
@@ -10973,14 +10958,14 @@
       <c r="B13" s="6">
         <v>1</v>
       </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
       <c r="F13" s="46"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
       <c r="K13" s="14">
         <v>1.97796965575553</v>
       </c>
@@ -10993,14 +10978,14 @@
       <c r="B14" s="6">
         <v>3</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
       <c r="F14" s="46"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
       <c r="K14" s="14">
         <v>3.1862607049915099</v>
       </c>
@@ -11013,14 +10998,14 @@
       <c r="B15" s="6">
         <v>5</v>
       </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
       <c r="F15" s="46"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="52"/>
       <c r="K15" s="14">
         <v>3.1662124268938201</v>
       </c>
@@ -11033,14 +11018,14 @@
       <c r="B16" s="6">
         <v>10</v>
       </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
       <c r="F16" s="46"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="52"/>
+      <c r="I16" s="52"/>
+      <c r="J16" s="52"/>
       <c r="K16" s="14">
         <v>3.0769912027266599</v>
       </c>
@@ -11049,18 +11034,18 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="57"/>
+      <c r="A17" s="50"/>
       <c r="B17" s="6">
         <v>100</v>
       </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
       <c r="F17" s="46"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
       <c r="K17" s="14">
         <v>3.1294599319079799</v>
       </c>
@@ -11069,20 +11054,20 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="52" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
       </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
       <c r="F18" s="46"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
       <c r="K18">
         <v>34.454845100484</v>
       </c>
@@ -11091,18 +11076,18 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="51"/>
+      <c r="A19" s="52"/>
       <c r="B19" s="3">
         <v>3</v>
       </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
       <c r="F19" s="46"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
       <c r="K19" s="4">
         <v>1.9521931441214699</v>
       </c>
@@ -11111,18 +11096,18 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="51"/>
+      <c r="A20" s="52"/>
       <c r="B20" s="3">
         <v>5</v>
       </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
       <c r="F20" s="46"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="51"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52"/>
+      <c r="J20" s="52"/>
       <c r="K20" s="3">
         <v>2.0043440401661101</v>
       </c>
@@ -11131,18 +11116,18 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="53"/>
+      <c r="A21" s="60"/>
       <c r="B21" s="10">
         <v>10</v>
       </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
       <c r="F21" s="46"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
       <c r="K21" s="3">
         <v>2.0041611367035599</v>
       </c>
@@ -11155,14 +11140,14 @@
       <c r="B22" s="30">
         <v>100</v>
       </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
       <c r="F22" s="46"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="52"/>
       <c r="K22" s="3">
         <v>2.0126023888751998</v>
       </c>
@@ -11208,60 +11193,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:55" x14ac:dyDescent="0.25">
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
       <c r="M1" s="21"/>
-      <c r="R1" s="39" t="s">
+      <c r="R1" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
-      <c r="AA1" s="39"/>
-      <c r="AB1" s="39"/>
-      <c r="AE1" s="39" t="s">
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="47"/>
+      <c r="X1" s="47"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="47"/>
+      <c r="AE1" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" s="39"/>
-      <c r="AG1" s="39"/>
-      <c r="AH1" s="39"/>
-      <c r="AI1" s="39"/>
-      <c r="AJ1" s="39"/>
-      <c r="AK1" s="39"/>
-      <c r="AL1" s="39"/>
-      <c r="AM1" s="39"/>
-      <c r="AN1" s="47"/>
-      <c r="AO1" s="47"/>
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="47"/>
+      <c r="AJ1" s="47"/>
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="47"/>
+      <c r="AM1" s="47"/>
+      <c r="AN1" s="39"/>
+      <c r="AO1" s="39"/>
       <c r="AP1" s="21"/>
-      <c r="AR1" s="39" t="s">
+      <c r="AR1" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="AS1" s="39"/>
-      <c r="AT1" s="39"/>
-      <c r="AU1" s="39"/>
-      <c r="AV1" s="39"/>
-      <c r="AW1" s="39"/>
-      <c r="AX1" s="39"/>
-      <c r="AY1" s="39"/>
-      <c r="AZ1" s="39"/>
-      <c r="BA1" s="47"/>
-      <c r="BB1" s="47"/>
+      <c r="AS1" s="47"/>
+      <c r="AT1" s="47"/>
+      <c r="AU1" s="47"/>
+      <c r="AV1" s="47"/>
+      <c r="AW1" s="47"/>
+      <c r="AX1" s="47"/>
+      <c r="AY1" s="47"/>
+      <c r="AZ1" s="47"/>
+      <c r="BA1" s="39"/>
+      <c r="BB1" s="39"/>
     </row>
     <row r="2" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B2" s="40" t="s">
@@ -12079,11 +12064,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="AN2:AP2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
     <mergeCell ref="AK2:AM2"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="R1:AB1"/>
@@ -12100,29 +12080,17 @@
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AE2:AG2"/>
     <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AN2:AP2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A16C87A6682E6E4295773DFF29EAB41B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a3213889016ec1ec7c5b45183b07d2a5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xmlns:ns4="c7f849e2-0a63-4d53-be53-fb9d39becd19" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39cf848dedf08b05fa72a945c282372c" ns3:_="" ns4:_="">
     <xsd:import namespace="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
@@ -12347,10 +12315,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
+    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12373,20 +12369,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA4F14C9-5422-45B5-82B0-09F318512608}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3"/>
-    <ds:schemaRef ds:uri="c7f849e2-0a63-4d53-be53-fb9d39becd19"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/documents/ExperimentData.xlsx
+++ b/documents/ExperimentData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1b2bcfbbb34c0c/Documents/GitHub/meliso/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3170" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB2C3DD6-C857-4775-B584-DA7AE8FAD1FB}"/>
+  <xr:revisionPtr revIDLastSave="3254" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1DC357F-1086-E442-A908-3719514C9EA6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="15720" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
   </bookViews>
   <sheets>
     <sheet name="DataExp1.1" sheetId="2" r:id="rId1"/>
@@ -195,7 +195,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.0000E+00"/>
+    <numFmt numFmtId="165" formatCode="0.0000E+00"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -391,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -446,7 +446,23 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -458,6 +474,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -467,11 +492,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -485,32 +534,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -530,60 +564,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -599,6 +579,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -919,36 +903,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB6579EC-3EC3-439D-9B94-319298E6C78E}">
   <dimension ref="B1:AN35"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="63" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="35" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="63" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.140625" customWidth="1"/>
-    <col min="12" max="12" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="63" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" style="63" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="8.140625" customWidth="1"/>
-    <col min="24" max="24" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.5703125" style="63" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="8.140625" customWidth="1"/>
-    <col min="29" max="29" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.5703125" style="63" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="10.140625" customWidth="1"/>
-    <col min="32" max="33" width="8.85546875" customWidth="1"/>
-    <col min="34" max="34" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.5703125" style="63" bestFit="1" customWidth="1"/>
-    <col min="36" max="39" width="8.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" style="35" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.1640625" customWidth="1"/>
+    <col min="12" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5" style="35" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5" style="35" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="8.1640625" customWidth="1"/>
+    <col min="24" max="24" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.5" style="35" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="8.1640625" customWidth="1"/>
+    <col min="29" max="29" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.5" style="35" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.1640625" customWidth="1"/>
+    <col min="32" max="33" width="8.83203125" customWidth="1"/>
+    <col min="34" max="34" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.5" style="35" bestFit="1" customWidth="1"/>
+    <col min="36" max="39" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B1" s="40" t="s">
         <v>25</v>
       </c>
@@ -987,59 +971,59 @@
       <c r="AI1" s="40"/>
       <c r="AJ1" s="40"/>
     </row>
-    <row r="2" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="B2" s="33" t="s">
+    <row r="2" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="70" t="s">
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="36" t="s">
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="75" t="s">
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="67" t="s">
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="W2" s="68"/>
-      <c r="X2" s="68"/>
-      <c r="Y2" s="68"/>
-      <c r="Z2" s="69"/>
-      <c r="AA2" s="75" t="s">
+      <c r="W2" s="48"/>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AB2" s="76"/>
-      <c r="AC2" s="76"/>
-      <c r="AD2" s="76"/>
-      <c r="AE2" s="77"/>
-      <c r="AF2" s="67" t="s">
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="51"/>
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="68"/>
-      <c r="AJ2" s="69"/>
+      <c r="AG2" s="48"/>
+      <c r="AH2" s="48"/>
+      <c r="AI2" s="48"/>
+      <c r="AJ2" s="49"/>
       <c r="AN2" s="21"/>
     </row>
-    <row r="3" spans="2:40" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:40" ht="64" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
@@ -1049,25 +1033,25 @@
       <c r="D3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="60" t="s">
+      <c r="E3" s="32" t="s">
         <v>23</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="73" t="s">
+      <c r="G3" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="73" t="s">
+      <c r="H3" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="74" t="s">
+      <c r="I3" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="81" t="s">
+      <c r="J3" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="73" t="s">
+      <c r="K3" s="36" t="s">
         <v>26</v>
       </c>
       <c r="L3" s="2" t="s">
@@ -1079,75 +1063,75 @@
       <c r="N3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="60" t="s">
+      <c r="O3" s="32" t="s">
         <v>23</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="Q3" s="73" t="s">
+      <c r="Q3" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="73" t="s">
+      <c r="R3" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="S3" s="74" t="s">
+      <c r="S3" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="T3" s="81" t="s">
+      <c r="T3" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="U3" s="73" t="s">
+      <c r="U3" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="V3" s="64" t="s">
+      <c r="V3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="64" t="s">
+      <c r="W3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="X3" s="65" t="s">
+      <c r="X3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="Y3" s="79" t="s">
+      <c r="Y3" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="Z3" s="64" t="s">
+      <c r="Z3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AA3" s="73" t="s">
+      <c r="AA3" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="AB3" s="73" t="s">
+      <c r="AB3" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="AC3" s="74" t="s">
+      <c r="AC3" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="AD3" s="81" t="s">
+      <c r="AD3" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="AE3" s="73" t="s">
+      <c r="AE3" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="AF3" s="64" t="s">
+      <c r="AF3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AG3" s="64" t="s">
+      <c r="AG3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AH3" s="65" t="s">
+      <c r="AH3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AI3" s="79" t="s">
+      <c r="AI3" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="AJ3" s="64" t="s">
+      <c r="AJ3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="AN3" s="26"/>
     </row>
-    <row r="4" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B4" s="4">
         <v>48.405375675691097</v>
       </c>
@@ -1157,7 +1141,7 @@
       <c r="D4" s="3">
         <v>280.77705301382201</v>
       </c>
-      <c r="E4" s="61">
+      <c r="E4" s="33">
         <v>1.2426647422269399E-3</v>
       </c>
       <c r="F4" s="4">
@@ -1172,7 +1156,7 @@
       <c r="I4" s="14">
         <v>390.73335904146597</v>
       </c>
-      <c r="J4" s="62">
+      <c r="J4" s="34">
         <v>1.832339402181E-3</v>
       </c>
       <c r="K4" s="14">
@@ -1187,7 +1171,7 @@
       <c r="N4" s="3">
         <v>429.57061506911401</v>
       </c>
-      <c r="O4" s="61">
+      <c r="O4" s="33">
         <v>2.0074486690417098E-3</v>
       </c>
       <c r="P4" s="4">
@@ -1202,25 +1186,25 @@
       <c r="S4" s="14">
         <v>445.815930138228</v>
       </c>
-      <c r="T4" s="62">
+      <c r="T4" s="34">
         <v>2.0439141245455999E-3</v>
       </c>
       <c r="U4" s="14">
         <v>2.48293805122375</v>
       </c>
-      <c r="V4" s="66">
+      <c r="V4" s="4">
         <v>1.1829448733229999</v>
       </c>
-      <c r="W4" s="66">
+      <c r="W4" s="4">
         <v>0.399074998842888</v>
       </c>
-      <c r="X4" s="66">
+      <c r="X4" s="4">
         <v>455.82186027645298</v>
       </c>
-      <c r="Y4" s="80">
+      <c r="Y4" s="33">
         <v>2.0637462472429401E-3</v>
       </c>
-      <c r="Z4" s="66">
+      <c r="Z4" s="4">
         <v>2.5318367481231601</v>
       </c>
       <c r="AA4" s="14">
@@ -1232,29 +1216,29 @@
       <c r="AC4" s="14">
         <v>460.27455069113802</v>
       </c>
-      <c r="AD4" s="62">
+      <c r="AD4" s="34">
         <v>2.0913029695989599E-3</v>
       </c>
       <c r="AE4" s="14">
         <v>3.1150028705596902</v>
       </c>
-      <c r="AF4" s="66">
+      <c r="AF4" s="4">
         <v>1.16738408109867</v>
       </c>
-      <c r="AG4" s="66">
+      <c r="AG4" s="4">
         <v>0.35890658938874798</v>
       </c>
-      <c r="AH4" s="66">
+      <c r="AH4" s="4">
         <v>458.095951382274</v>
       </c>
-      <c r="AI4" s="80">
+      <c r="AI4" s="33">
         <v>2.1146609841073698E-3</v>
       </c>
-      <c r="AJ4" s="66">
+      <c r="AJ4" s="4">
         <v>4.3998079299926696</v>
       </c>
     </row>
-    <row r="5" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B5" s="4">
         <v>48.544182751545002</v>
       </c>
@@ -1264,7 +1248,7 @@
       <c r="D5" s="3">
         <v>280.77705301382201</v>
       </c>
-      <c r="E5" s="61">
+      <c r="E5" s="33">
         <v>1.2423680427653E-3</v>
       </c>
       <c r="F5" s="4">
@@ -1279,7 +1263,7 @@
       <c r="I5" s="14">
         <v>391.11195904146803</v>
       </c>
-      <c r="J5" s="62">
+      <c r="J5" s="34">
         <v>1.8332875869532599E-3</v>
       </c>
       <c r="K5" s="14">
@@ -1294,7 +1278,7 @@
       <c r="N5" s="3">
         <v>429.74971506911402</v>
       </c>
-      <c r="O5" s="61">
+      <c r="O5" s="33">
         <v>2.0082558212510199E-3</v>
       </c>
       <c r="P5" s="4">
@@ -1309,25 +1293,25 @@
       <c r="S5" s="14">
         <v>456.20403013822698</v>
       </c>
-      <c r="T5" s="62">
+      <c r="T5" s="34">
         <v>2.0599180774274199E-3</v>
       </c>
       <c r="U5" s="14">
         <v>2.3609910011291499</v>
       </c>
-      <c r="V5" s="66">
+      <c r="V5" s="4">
         <v>1.1341129117536199</v>
       </c>
-      <c r="W5" s="66">
+      <c r="W5" s="4">
         <v>0.38645738940860103</v>
       </c>
-      <c r="X5" s="66">
+      <c r="X5" s="4">
         <v>445.07466027645501</v>
       </c>
-      <c r="Y5" s="80">
+      <c r="Y5" s="33">
         <v>2.0497697482144599E-3</v>
       </c>
-      <c r="Z5" s="66">
+      <c r="Z5" s="4">
         <v>2.5911741256713801</v>
       </c>
       <c r="AA5" s="14">
@@ -1339,29 +1323,29 @@
       <c r="AC5" s="14">
         <v>449.302950691136</v>
       </c>
-      <c r="AD5" s="62">
+      <c r="AD5" s="34">
         <v>2.0859871857910901E-3</v>
       </c>
       <c r="AE5" s="14">
         <v>3.10551762580871</v>
       </c>
-      <c r="AF5" s="66">
+      <c r="AF5" s="4">
         <v>1.0903015325565799</v>
       </c>
-      <c r="AG5" s="66">
+      <c r="AG5" s="4">
         <v>0.373692923687102</v>
       </c>
-      <c r="AH5" s="66">
+      <c r="AH5" s="4">
         <v>453.036001382275</v>
       </c>
-      <c r="AI5" s="80">
+      <c r="AI5" s="33">
         <v>2.0849598628704499E-3</v>
       </c>
-      <c r="AJ5" s="66">
+      <c r="AJ5" s="4">
         <v>4.2901444435119602</v>
       </c>
     </row>
-    <row r="6" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B6" s="4">
         <v>49.038547006529797</v>
       </c>
@@ -1371,7 +1355,7 @@
       <c r="D6" s="3">
         <v>280.77705301382201</v>
       </c>
-      <c r="E6" s="61">
+      <c r="E6" s="33">
         <v>1.2444118717866101E-3</v>
       </c>
       <c r="F6" s="4">
@@ -1386,7 +1370,7 @@
       <c r="I6" s="14">
         <v>393.00405904146697</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="34">
         <v>1.8425506799710999E-3</v>
       </c>
       <c r="K6" s="14">
@@ -1401,7 +1385,7 @@
       <c r="N6" s="3">
         <v>428.942865069113</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="33">
         <v>2.0055728581899399E-3</v>
       </c>
       <c r="P6" s="4">
@@ -1416,25 +1400,25 @@
       <c r="S6" s="14">
         <v>452.44893013822798</v>
       </c>
-      <c r="T6" s="62">
+      <c r="T6" s="34">
         <v>2.0656273401431198E-3</v>
       </c>
       <c r="U6" s="14">
         <v>2.21172642707824</v>
       </c>
-      <c r="V6" s="66">
+      <c r="V6" s="4">
         <v>1.17934098569572</v>
       </c>
-      <c r="W6" s="66">
+      <c r="W6" s="4">
         <v>0.33143758702708198</v>
       </c>
-      <c r="X6" s="66">
+      <c r="X6" s="4">
         <v>456.26781027645302</v>
       </c>
-      <c r="Y6" s="80">
+      <c r="Y6" s="33">
         <v>2.0669548454960102E-3</v>
       </c>
-      <c r="Z6" s="66">
+      <c r="Z6" s="4">
         <v>2.4619610309600799</v>
       </c>
       <c r="AA6" s="14">
@@ -1446,29 +1430,29 @@
       <c r="AC6" s="14">
         <v>459.053700691139</v>
       </c>
-      <c r="AD6" s="62">
+      <c r="AD6" s="34">
         <v>2.0826490536814202E-3</v>
       </c>
       <c r="AE6" s="14">
         <v>2.9935326576232901</v>
       </c>
-      <c r="AF6" s="66">
+      <c r="AF6" s="4">
         <v>1.18071296472814</v>
       </c>
-      <c r="AG6" s="66">
+      <c r="AG6" s="4">
         <v>0.36546240200688701</v>
       </c>
-      <c r="AH6" s="66">
+      <c r="AH6" s="4">
         <v>451.871851382275</v>
       </c>
-      <c r="AI6" s="80">
+      <c r="AI6" s="33">
         <v>2.0796577274464099E-3</v>
       </c>
-      <c r="AJ6" s="66">
+      <c r="AJ6" s="4">
         <v>3.93764972686767</v>
       </c>
     </row>
-    <row r="7" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B7" s="4">
         <v>43.487215227182297</v>
       </c>
@@ -1478,7 +1462,7 @@
       <c r="D7" s="3">
         <v>280.77705301382201</v>
       </c>
-      <c r="E7" s="61">
+      <c r="E7" s="33">
         <v>1.24177464384202E-3</v>
       </c>
       <c r="F7" s="4">
@@ -1493,7 +1477,7 @@
       <c r="I7" s="14">
         <v>390.03645904146703</v>
       </c>
-      <c r="J7" s="62">
+      <c r="J7" s="34">
         <v>1.82915892433048E-3</v>
       </c>
       <c r="K7" s="14">
@@ -1508,7 +1492,7 @@
       <c r="N7" s="3">
         <v>429.54931506911299</v>
       </c>
-      <c r="O7" s="61">
+      <c r="O7" s="33">
         <v>2.0109965585241199E-3</v>
       </c>
       <c r="P7" s="4">
@@ -1523,25 +1507,25 @@
       <c r="S7" s="14">
         <v>446.15463013822603</v>
       </c>
-      <c r="T7" s="62">
+      <c r="T7" s="34">
         <v>2.0458236362095299E-3</v>
       </c>
       <c r="U7" s="14">
         <v>2.19571828842163</v>
       </c>
-      <c r="V7" s="66">
+      <c r="V7" s="4">
         <v>1.1135811439341801</v>
       </c>
-      <c r="W7" s="66">
+      <c r="W7" s="4">
         <v>0.33484981320993101</v>
       </c>
-      <c r="X7" s="66">
+      <c r="X7" s="4">
         <v>463.96941027645499</v>
       </c>
-      <c r="Y7" s="80">
+      <c r="Y7" s="33">
         <v>2.06742927060437E-3</v>
       </c>
-      <c r="Z7" s="66">
+      <c r="Z7" s="4">
         <v>2.72619199752807</v>
       </c>
       <c r="AA7" s="14">
@@ -1553,29 +1537,29 @@
       <c r="AC7" s="14">
         <v>445.01160069113701</v>
       </c>
-      <c r="AD7" s="62">
+      <c r="AD7" s="34">
         <v>2.0738130715497699E-3</v>
       </c>
       <c r="AE7" s="14">
         <v>3.0592045783996502</v>
       </c>
-      <c r="AF7" s="66">
+      <c r="AF7" s="4">
         <v>1.1272064624118801</v>
       </c>
-      <c r="AG7" s="66">
+      <c r="AG7" s="4">
         <v>0.39454568341471902</v>
       </c>
-      <c r="AH7" s="66">
+      <c r="AH7" s="4">
         <v>452.23890138227802</v>
       </c>
-      <c r="AI7" s="80">
+      <c r="AI7" s="33">
         <v>2.08246416787376E-3</v>
       </c>
-      <c r="AJ7" s="66">
+      <c r="AJ7" s="4">
         <v>3.89451599121093</v>
       </c>
     </row>
-    <row r="8" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B8" s="4">
         <v>48.887283245854697</v>
       </c>
@@ -1585,7 +1569,7 @@
       <c r="D8" s="3">
         <v>280.77705301382201</v>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="33">
         <v>1.24147794438038E-3</v>
       </c>
       <c r="F8" s="4">
@@ -1600,7 +1584,7 @@
       <c r="I8" s="14">
         <v>390.73335904146597</v>
       </c>
-      <c r="J8" s="62">
+      <c r="J8" s="34">
         <v>1.83232660308975E-3</v>
       </c>
       <c r="K8" s="14">
@@ -1615,7 +1599,7 @@
       <c r="N8" s="3">
         <v>429.57061506911401</v>
       </c>
-      <c r="O8" s="61">
+      <c r="O8" s="33">
         <v>2.0074786582290598E-3</v>
       </c>
       <c r="P8" s="4">
@@ -1630,25 +1614,25 @@
       <c r="S8" s="14">
         <v>441.88533013822598</v>
       </c>
-      <c r="T8" s="62">
+      <c r="T8" s="34">
         <v>2.0443423165018202E-3</v>
       </c>
       <c r="U8" s="14">
         <v>2.12239217758178</v>
       </c>
-      <c r="V8" s="66">
+      <c r="V8" s="4">
         <v>1.2980958898952599</v>
       </c>
-      <c r="W8" s="66">
+      <c r="W8" s="4">
         <v>0.37077353542543101</v>
       </c>
-      <c r="X8" s="66">
+      <c r="X8" s="4">
         <v>464.41806027645498</v>
       </c>
-      <c r="Y8" s="80">
+      <c r="Y8" s="33">
         <v>2.06916063412581E-3</v>
       </c>
-      <c r="Z8" s="66">
+      <c r="Z8" s="4">
         <v>2.48653817176818</v>
       </c>
       <c r="AA8" s="14">
@@ -1660,35 +1644,35 @@
       <c r="AC8" s="14">
         <v>451.057800691137</v>
       </c>
-      <c r="AD8" s="62">
+      <c r="AD8" s="34">
         <v>2.0726876850760399E-3</v>
       </c>
       <c r="AE8" s="14">
         <v>2.8059625625610298</v>
       </c>
-      <c r="AF8" s="66">
+      <c r="AF8" s="4">
         <v>1.2381096128108899</v>
       </c>
-      <c r="AG8" s="66">
+      <c r="AG8" s="4">
         <v>0.34792243681192703</v>
       </c>
-      <c r="AH8" s="66">
+      <c r="AH8" s="4">
         <v>464.89035138227399</v>
       </c>
-      <c r="AI8" s="80">
+      <c r="AI8" s="33">
         <v>2.1306026601287699E-3</v>
       </c>
-      <c r="AJ8" s="66">
+      <c r="AJ8" s="4">
         <v>3.9945855140686</v>
       </c>
     </row>
-    <row r="9" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B10" s="40" t="s">
         <v>27</v>
       </c>
@@ -1727,58 +1711,58 @@
       <c r="AI10" s="40"/>
       <c r="AJ10" s="40"/>
     </row>
-    <row r="11" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="B11" s="33" t="s">
+    <row r="11" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="B11" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="70" t="s">
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="36" t="s">
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="75" t="s">
+      <c r="M11" s="48"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="48"/>
+      <c r="P11" s="49"/>
+      <c r="Q11" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="R11" s="76"/>
-      <c r="S11" s="76"/>
-      <c r="T11" s="76"/>
-      <c r="U11" s="77"/>
-      <c r="V11" s="67" t="s">
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+      <c r="T11" s="51"/>
+      <c r="U11" s="52"/>
+      <c r="V11" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="W11" s="68"/>
-      <c r="X11" s="68"/>
-      <c r="Y11" s="68"/>
-      <c r="Z11" s="69"/>
-      <c r="AA11" s="75" t="s">
+      <c r="W11" s="48"/>
+      <c r="X11" s="48"/>
+      <c r="Y11" s="48"/>
+      <c r="Z11" s="49"/>
+      <c r="AA11" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AB11" s="76"/>
-      <c r="AC11" s="76"/>
-      <c r="AD11" s="76"/>
-      <c r="AE11" s="77"/>
-      <c r="AF11" s="67" t="s">
+      <c r="AB11" s="51"/>
+      <c r="AC11" s="51"/>
+      <c r="AD11" s="51"/>
+      <c r="AE11" s="52"/>
+      <c r="AF11" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="AG11" s="68"/>
-      <c r="AH11" s="68"/>
-      <c r="AI11" s="68"/>
-      <c r="AJ11" s="69"/>
-    </row>
-    <row r="12" spans="2:40" ht="60" x14ac:dyDescent="0.25">
+      <c r="AG11" s="48"/>
+      <c r="AH11" s="48"/>
+      <c r="AI11" s="48"/>
+      <c r="AJ11" s="49"/>
+    </row>
+    <row r="12" spans="2:40" ht="64" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
@@ -1788,25 +1772,25 @@
       <c r="D12" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="60" t="s">
+      <c r="E12" s="32" t="s">
         <v>23</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="73" t="s">
+      <c r="G12" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="73" t="s">
+      <c r="H12" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="74" t="s">
+      <c r="I12" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="J12" s="81" t="s">
+      <c r="J12" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="K12" s="73" t="s">
+      <c r="K12" s="36" t="s">
         <v>26</v>
       </c>
       <c r="L12" s="2" t="s">
@@ -1818,74 +1802,74 @@
       <c r="N12" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="O12" s="60" t="s">
+      <c r="O12" s="32" t="s">
         <v>23</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="Q12" s="73" t="s">
+      <c r="Q12" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="R12" s="73" t="s">
+      <c r="R12" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="S12" s="74" t="s">
+      <c r="S12" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="T12" s="81" t="s">
+      <c r="T12" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="U12" s="73" t="s">
+      <c r="U12" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="V12" s="64" t="s">
+      <c r="V12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W12" s="64" t="s">
+      <c r="W12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="X12" s="65" t="s">
+      <c r="X12" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="Y12" s="79" t="s">
+      <c r="Y12" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="Z12" s="64" t="s">
+      <c r="Z12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AA12" s="73" t="s">
+      <c r="AA12" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="AB12" s="73" t="s">
+      <c r="AB12" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="AC12" s="74" t="s">
+      <c r="AC12" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="AD12" s="81" t="s">
+      <c r="AD12" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="AE12" s="73" t="s">
+      <c r="AE12" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="AF12" s="64" t="s">
+      <c r="AF12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AG12" s="64" t="s">
+      <c r="AG12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AH12" s="65" t="s">
+      <c r="AH12" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AI12" s="79" t="s">
+      <c r="AI12" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="AJ12" s="64" t="s">
+      <c r="AJ12" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B13" s="4">
         <v>97.996820764793895</v>
       </c>
@@ -1895,7 +1879,7 @@
       <c r="D13" s="3">
         <v>38.8018530138228</v>
       </c>
-      <c r="E13" s="61">
+      <c r="E13" s="33">
         <v>1.8313175473446699E-2</v>
       </c>
       <c r="F13" s="4">
@@ -1910,7 +1894,7 @@
       <c r="I13" s="14">
         <v>73.284409041468194</v>
       </c>
-      <c r="J13" s="62">
+      <c r="J13" s="34">
         <v>3.8994966839365201E-2</v>
       </c>
       <c r="K13" s="14">
@@ -1925,7 +1909,7 @@
       <c r="N13" s="3">
         <v>75.286565069113806</v>
       </c>
-      <c r="O13" s="61">
+      <c r="O13" s="33">
         <v>4.0256479690962001E-2</v>
       </c>
       <c r="P13" s="4">
@@ -1940,25 +1924,25 @@
       <c r="S13" s="14">
         <v>75.545080138227704</v>
       </c>
-      <c r="T13" s="62">
+      <c r="T13" s="34">
         <v>4.0608116963391901E-2</v>
       </c>
       <c r="U13" s="14">
         <v>2.44974660873413</v>
       </c>
-      <c r="V13" s="66">
+      <c r="V13" s="4">
         <v>4.8169352248984696</v>
       </c>
-      <c r="W13" s="66">
+      <c r="W13" s="4">
         <v>1.03204958653325</v>
       </c>
-      <c r="X13" s="66">
+      <c r="X13" s="4">
         <v>75.608660276455197</v>
       </c>
-      <c r="Y13" s="80">
+      <c r="Y13" s="33">
         <v>4.0527248269369903E-2</v>
       </c>
-      <c r="Z13" s="66">
+      <c r="Z13" s="4">
         <v>2.56579136848449</v>
       </c>
       <c r="AA13" s="14">
@@ -1970,29 +1954,29 @@
       <c r="AC13" s="14">
         <v>75.365400691138404</v>
       </c>
-      <c r="AD13" s="62">
+      <c r="AD13" s="34">
         <v>4.0554784230403498E-2</v>
       </c>
       <c r="AE13" s="14">
         <v>3.10210061073303</v>
       </c>
-      <c r="AF13" s="66">
+      <c r="AF13" s="4">
         <v>6.6956419073976097</v>
       </c>
-      <c r="AG13" s="66">
+      <c r="AG13" s="4">
         <v>1.35440971359411</v>
       </c>
-      <c r="AH13" s="66">
+      <c r="AH13" s="4">
         <v>77.501151382277001</v>
       </c>
-      <c r="AI13" s="80">
+      <c r="AI13" s="33">
         <v>4.2091459109702398E-2</v>
       </c>
-      <c r="AJ13" s="66">
+      <c r="AJ13" s="4">
         <v>4.2037107944488499</v>
       </c>
     </row>
-    <row r="14" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B14" s="4">
         <v>94.688350920336305</v>
       </c>
@@ -2002,7 +1986,7 @@
       <c r="D14" s="3">
         <v>38.8018530138228</v>
       </c>
-      <c r="E14" s="61">
+      <c r="E14" s="33">
         <v>1.8313175473446699E-2</v>
       </c>
       <c r="F14" s="3">
@@ -2017,7 +2001,7 @@
       <c r="I14" s="14">
         <v>71.477009041468307</v>
       </c>
-      <c r="J14" s="62">
+      <c r="J14" s="34">
         <v>3.7265885633866097E-2</v>
       </c>
       <c r="K14" s="14">
@@ -2032,7 +2016,7 @@
       <c r="N14" s="3">
         <v>75.602615069113796</v>
       </c>
-      <c r="O14" s="61">
+      <c r="O14" s="33">
         <v>4.0260067261321697E-2</v>
       </c>
       <c r="P14" s="4">
@@ -2047,25 +2031,25 @@
       <c r="S14" s="14">
         <v>77.550730138227493</v>
       </c>
-      <c r="T14" s="62">
+      <c r="T14" s="34">
         <v>4.2152379579014798E-2</v>
       </c>
       <c r="U14" s="14">
         <v>2.4255056381225502</v>
       </c>
-      <c r="V14" s="66">
+      <c r="V14" s="4">
         <v>4.6786404700233302</v>
       </c>
-      <c r="W14" s="66">
+      <c r="W14" s="4">
         <v>0.94171616841057904</v>
       </c>
-      <c r="X14" s="66">
+      <c r="X14" s="4">
         <v>75.518510276455203</v>
       </c>
-      <c r="Y14" s="80">
+      <c r="Y14" s="33">
         <v>4.0606052261504703E-2</v>
       </c>
-      <c r="Z14" s="66">
+      <c r="Z14" s="4">
         <v>2.6950168609619101</v>
       </c>
       <c r="AA14" s="14">
@@ -2077,29 +2061,29 @@
       <c r="AC14" s="14">
         <v>75.518600691138104</v>
       </c>
-      <c r="AD14" s="62">
+      <c r="AD14" s="34">
         <v>4.0606176453202102E-2</v>
       </c>
       <c r="AE14" s="14">
         <v>3.0403451919555602</v>
       </c>
-      <c r="AF14" s="66">
+      <c r="AF14" s="4">
         <v>2.8470669593498599</v>
       </c>
-      <c r="AG14" s="66">
+      <c r="AG14" s="4">
         <v>0.76356066113789101</v>
       </c>
-      <c r="AH14" s="66">
+      <c r="AH14" s="4">
         <v>75.219351382276898</v>
       </c>
-      <c r="AI14" s="80">
+      <c r="AI14" s="33">
         <v>4.0552802966253597E-2</v>
       </c>
-      <c r="AJ14" s="66">
+      <c r="AJ14" s="4">
         <v>4.0056276321411097</v>
       </c>
     </row>
-    <row r="15" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B15" s="4">
         <v>100.739848146935</v>
       </c>
@@ -2109,7 +2093,7 @@
       <c r="D15" s="3">
         <v>38.8018530138228</v>
       </c>
-      <c r="E15" s="61">
+      <c r="E15" s="33">
         <v>1.8313175473446699E-2</v>
       </c>
       <c r="F15" s="4">
@@ -2124,7 +2108,7 @@
       <c r="I15" s="14">
         <v>73.102359041468205</v>
       </c>
-      <c r="J15" s="62">
+      <c r="J15" s="34">
         <v>3.8879755317166302E-2</v>
       </c>
       <c r="K15" s="14">
@@ -2139,7 +2123,7 @@
       <c r="N15" s="3">
         <v>76.178365069113795</v>
       </c>
-      <c r="O15" s="61">
+      <c r="O15" s="33">
         <v>4.1812025192735802E-2</v>
       </c>
       <c r="P15" s="4">
@@ -2154,25 +2138,25 @@
       <c r="S15" s="14">
         <v>77.5008801382277</v>
       </c>
-      <c r="T15" s="62">
+      <c r="T15" s="34">
         <v>4.2090951595853798E-2</v>
       </c>
       <c r="U15" s="14">
         <v>2.3199012279510498</v>
       </c>
-      <c r="V15" s="66">
+      <c r="V15" s="4">
         <v>2.6889884781940498</v>
       </c>
-      <c r="W15" s="66">
+      <c r="W15" s="4">
         <v>0.63557734866359805</v>
       </c>
-      <c r="X15" s="66">
+      <c r="X15" s="4">
         <v>75.219110276455297</v>
       </c>
-      <c r="Y15" s="80">
+      <c r="Y15" s="33">
         <v>4.0551775193704502E-2</v>
       </c>
-      <c r="Z15" s="66">
+      <c r="Z15" s="4">
         <v>2.6627848148345898</v>
       </c>
       <c r="AA15" s="14">
@@ -2184,29 +2168,29 @@
       <c r="AC15" s="14">
         <v>75.421250691138397</v>
       </c>
-      <c r="AD15" s="62">
+      <c r="AD15" s="34">
         <v>4.0647351826981801E-2</v>
       </c>
       <c r="AE15" s="14">
         <v>3.2617387771606401</v>
       </c>
-      <c r="AF15" s="66">
+      <c r="AF15" s="4">
         <v>2.3307098937042299</v>
       </c>
-      <c r="AG15" s="66">
+      <c r="AG15" s="4">
         <v>0.49352867320587601</v>
       </c>
-      <c r="AH15" s="66">
+      <c r="AH15" s="4">
         <v>75.588301382276796</v>
       </c>
-      <c r="AI15" s="80">
+      <c r="AI15" s="33">
         <v>4.0547277265625799E-2</v>
       </c>
-      <c r="AJ15" s="66">
+      <c r="AJ15" s="4">
         <v>4.0872819423675502</v>
       </c>
     </row>
-    <row r="16" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B16" s="4">
         <v>100.378122212953</v>
       </c>
@@ -2216,7 +2200,7 @@
       <c r="D16" s="3">
         <v>38.8018530138228</v>
       </c>
-      <c r="E16" s="61">
+      <c r="E16" s="33">
         <v>1.8313175473446699E-2</v>
       </c>
       <c r="F16" s="4">
@@ -2231,7 +2215,7 @@
       <c r="I16" s="14">
         <v>73.280859041468304</v>
       </c>
-      <c r="J16" s="62">
+      <c r="J16" s="34">
         <v>3.9008239383358602E-2</v>
       </c>
       <c r="K16" s="14">
@@ -2246,7 +2230,7 @@
       <c r="N16" s="3">
         <v>75.110315069113597</v>
       </c>
-      <c r="O16" s="61">
+      <c r="O16" s="33">
         <v>4.02723006679667E-2</v>
       </c>
       <c r="P16" s="4">
@@ -2261,25 +2245,25 @@
       <c r="S16" s="14">
         <v>75.365280138227803</v>
       </c>
-      <c r="T16" s="62">
+      <c r="T16" s="34">
         <v>4.0554723193938401E-2</v>
       </c>
       <c r="U16" s="14">
         <v>2.0072596073150599</v>
       </c>
-      <c r="V16" s="66">
+      <c r="V16" s="4">
         <v>6.79324640747922</v>
       </c>
-      <c r="W16" s="66">
+      <c r="W16" s="4">
         <v>1.29311290195033</v>
       </c>
-      <c r="X16" s="66">
+      <c r="X16" s="4">
         <v>76.692960276455196</v>
       </c>
-      <c r="Y16" s="80">
+      <c r="Y16" s="33">
         <v>4.2155793795345002E-2</v>
       </c>
-      <c r="Z16" s="66">
+      <c r="Z16" s="4">
         <v>2.5493519306182799</v>
       </c>
       <c r="AA16" s="14">
@@ -2291,29 +2275,29 @@
       <c r="AC16" s="14">
         <v>75.219200691138596</v>
       </c>
-      <c r="AD16" s="62">
+      <c r="AD16" s="34">
         <v>4.0552262788175801E-2</v>
       </c>
       <c r="AE16" s="14">
         <v>3.1742980480193999</v>
       </c>
-      <c r="AF16" s="66">
+      <c r="AF16" s="4">
         <v>3.3416006381902501</v>
       </c>
-      <c r="AG16" s="66">
+      <c r="AG16" s="4">
         <v>0.83163335252466497</v>
       </c>
-      <c r="AH16" s="66">
+      <c r="AH16" s="4">
         <v>75.272551382276802</v>
       </c>
-      <c r="AI16" s="80">
+      <c r="AI16" s="33">
         <v>4.0573162213819701E-2</v>
       </c>
-      <c r="AJ16" s="66">
+      <c r="AJ16" s="4">
         <v>3.9984769821166899</v>
       </c>
     </row>
-    <row r="17" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B17" s="4">
         <v>98.816185006612301</v>
       </c>
@@ -2323,7 +2307,7 @@
       <c r="D17" s="3">
         <v>38.8018530138228</v>
       </c>
-      <c r="E17" s="61">
+      <c r="E17" s="33">
         <v>1.8313175473446699E-2</v>
       </c>
       <c r="F17" s="4">
@@ -2338,7 +2322,7 @@
       <c r="I17" s="14">
         <v>73.238509041468106</v>
       </c>
-      <c r="J17" s="62">
+      <c r="J17" s="34">
         <v>3.8928413203425098E-2</v>
       </c>
       <c r="K17" s="14">
@@ -2353,7 +2337,7 @@
       <c r="N17" s="3">
         <v>74.950415069113703</v>
       </c>
-      <c r="O17" s="61">
+      <c r="O17" s="33">
         <v>4.0250393754105003E-2</v>
       </c>
       <c r="P17" s="4">
@@ -2368,25 +2352,25 @@
       <c r="S17" s="14">
         <v>75.219080138227596</v>
       </c>
-      <c r="T17" s="62">
+      <c r="T17" s="34">
         <v>4.0551569502204801E-2</v>
       </c>
       <c r="U17" s="14">
         <v>2.3707435131072998</v>
       </c>
-      <c r="V17" s="66">
+      <c r="V17" s="4">
         <v>4.71324269565946</v>
       </c>
-      <c r="W17" s="66">
+      <c r="W17" s="4">
         <v>0.94392780050690905</v>
       </c>
-      <c r="X17" s="66">
+      <c r="X17" s="4">
         <v>75.545110276455205</v>
       </c>
-      <c r="Y17" s="80">
+      <c r="Y17" s="33">
         <v>4.0608270349277102E-2</v>
       </c>
-      <c r="Z17" s="66">
+      <c r="Z17" s="4">
         <v>2.6408619880676198</v>
       </c>
       <c r="AA17" s="14">
@@ -2398,29 +2382,29 @@
       <c r="AC17" s="14">
         <v>75.715150691138405</v>
       </c>
-      <c r="AD17" s="62">
+      <c r="AD17" s="34">
         <v>4.0532794778183598E-2</v>
       </c>
       <c r="AE17" s="14">
         <v>3.0870699882507302</v>
       </c>
-      <c r="AF17" s="66">
+      <c r="AF17" s="4">
         <v>5.0719053064671904</v>
       </c>
-      <c r="AG17" s="66">
+      <c r="AG17" s="4">
         <v>1.0501216484814899</v>
       </c>
-      <c r="AH17" s="66">
+      <c r="AH17" s="4">
         <v>76.011051382276705</v>
       </c>
-      <c r="AI17" s="80">
+      <c r="AI17" s="33">
         <v>4.0587721329767297E-2</v>
       </c>
-      <c r="AJ17" s="66">
+      <c r="AJ17" s="4">
         <v>4.2727708816528303</v>
       </c>
     </row>
-    <row r="19" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B19" s="40" t="s">
         <v>28</v>
       </c>
@@ -2459,58 +2443,58 @@
       <c r="AI19" s="40"/>
       <c r="AJ19" s="40"/>
     </row>
-    <row r="20" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B20" s="33" t="s">
+    <row r="20" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B20" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="70" t="s">
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="H20" s="71"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="72"/>
-      <c r="L20" s="36" t="s">
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="75" t="s">
+      <c r="M20" s="48"/>
+      <c r="N20" s="48"/>
+      <c r="O20" s="48"/>
+      <c r="P20" s="49"/>
+      <c r="Q20" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="R20" s="76"/>
-      <c r="S20" s="76"/>
-      <c r="T20" s="76"/>
-      <c r="U20" s="77"/>
-      <c r="V20" s="67" t="s">
+      <c r="R20" s="51"/>
+      <c r="S20" s="51"/>
+      <c r="T20" s="51"/>
+      <c r="U20" s="52"/>
+      <c r="V20" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="W20" s="68"/>
-      <c r="X20" s="68"/>
-      <c r="Y20" s="68"/>
-      <c r="Z20" s="69"/>
-      <c r="AA20" s="75" t="s">
+      <c r="W20" s="48"/>
+      <c r="X20" s="48"/>
+      <c r="Y20" s="48"/>
+      <c r="Z20" s="49"/>
+      <c r="AA20" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AB20" s="76"/>
-      <c r="AC20" s="76"/>
-      <c r="AD20" s="76"/>
-      <c r="AE20" s="77"/>
-      <c r="AF20" s="67" t="s">
+      <c r="AB20" s="51"/>
+      <c r="AC20" s="51"/>
+      <c r="AD20" s="51"/>
+      <c r="AE20" s="52"/>
+      <c r="AF20" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="AG20" s="68"/>
-      <c r="AH20" s="68"/>
-      <c r="AI20" s="68"/>
-      <c r="AJ20" s="69"/>
-    </row>
-    <row r="21" spans="2:36" ht="60" x14ac:dyDescent="0.25">
+      <c r="AG20" s="48"/>
+      <c r="AH20" s="48"/>
+      <c r="AI20" s="48"/>
+      <c r="AJ20" s="49"/>
+    </row>
+    <row r="21" spans="2:36" ht="64" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>20</v>
       </c>
@@ -2520,25 +2504,25 @@
       <c r="D21" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="60" t="s">
+      <c r="E21" s="32" t="s">
         <v>23</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G21" s="73" t="s">
+      <c r="G21" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="73" t="s">
+      <c r="H21" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I21" s="74" t="s">
+      <c r="I21" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="J21" s="81" t="s">
+      <c r="J21" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="K21" s="73" t="s">
+      <c r="K21" s="36" t="s">
         <v>26</v>
       </c>
       <c r="L21" s="2" t="s">
@@ -2550,74 +2534,74 @@
       <c r="N21" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="O21" s="60" t="s">
+      <c r="O21" s="32" t="s">
         <v>23</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="Q21" s="73" t="s">
+      <c r="Q21" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="R21" s="73" t="s">
+      <c r="R21" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="S21" s="74" t="s">
+      <c r="S21" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="T21" s="81" t="s">
+      <c r="T21" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="U21" s="73" t="s">
+      <c r="U21" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="V21" s="64" t="s">
+      <c r="V21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W21" s="64" t="s">
+      <c r="W21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="X21" s="65" t="s">
+      <c r="X21" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="Y21" s="79" t="s">
+      <c r="Y21" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="Z21" s="64" t="s">
+      <c r="Z21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AA21" s="73" t="s">
+      <c r="AA21" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="AB21" s="73" t="s">
+      <c r="AB21" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="AC21" s="74" t="s">
+      <c r="AC21" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="AD21" s="81" t="s">
+      <c r="AD21" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="AE21" s="73" t="s">
+      <c r="AE21" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="AF21" s="64" t="s">
+      <c r="AF21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AG21" s="64" t="s">
+      <c r="AG21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AH21" s="65" t="s">
+      <c r="AH21" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AI21" s="79" t="s">
+      <c r="AI21" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="AJ21" s="64" t="s">
+      <c r="AJ21" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B22" s="4">
         <v>4.5673914929329396</v>
       </c>
@@ -2627,44 +2611,64 @@
       <c r="D22" s="3">
         <v>4.4845012962678503E-2</v>
       </c>
-      <c r="E22" s="61">
+      <c r="E22" s="33">
         <v>1.3224448728735801E-4</v>
       </c>
       <c r="F22" s="4">
         <v>0.21188092231750399</v>
       </c>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="61"/>
-      <c r="P22" s="4"/>
+      <c r="G22" s="9">
+        <v>5.2461342255167303</v>
+      </c>
+      <c r="H22" s="9">
+        <v>0.87969942139475399</v>
+      </c>
+      <c r="I22" s="9">
+        <v>4.7820025925357099E-2</v>
+      </c>
+      <c r="J22" s="9">
+        <v>1.33908772236417E-4</v>
+      </c>
+      <c r="K22" s="9">
+        <v>0.242220878601074</v>
+      </c>
+      <c r="L22">
+        <v>5.0655324504313803</v>
+      </c>
+      <c r="M22">
+        <v>0.855346508320174</v>
+      </c>
+      <c r="N22">
+        <v>4.78425388880356E-2</v>
+      </c>
+      <c r="O22">
+        <v>1.33915733272207E-4</v>
+      </c>
+      <c r="P22">
+        <v>0.24848961830139099</v>
+      </c>
       <c r="Q22" s="14"/>
       <c r="R22" s="14"/>
       <c r="S22" s="14"/>
-      <c r="T22" s="62"/>
+      <c r="T22" s="34"/>
       <c r="U22" s="14"/>
-      <c r="V22" s="66"/>
-      <c r="W22" s="66"/>
-      <c r="X22" s="66"/>
-      <c r="Y22" s="80"/>
-      <c r="Z22" s="66"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="33"/>
+      <c r="Z22" s="4"/>
       <c r="AA22" s="14"/>
       <c r="AB22" s="14"/>
       <c r="AC22" s="14"/>
-      <c r="AD22" s="62"/>
+      <c r="AD22" s="34"/>
       <c r="AE22" s="14"/>
-      <c r="AF22" s="66"/>
-      <c r="AG22" s="66"/>
-      <c r="AH22" s="66"/>
-      <c r="AI22" s="80"/>
-      <c r="AJ22" s="66"/>
-    </row>
-    <row r="23" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="AF22" s="4"/>
+      <c r="AG22" s="4"/>
+      <c r="AH22" s="4"/>
+      <c r="AI22" s="33"/>
+      <c r="AJ22" s="4"/>
+    </row>
+    <row r="23" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B23" s="4">
         <v>4.5033926098328001</v>
       </c>
@@ -2674,44 +2678,64 @@
       <c r="D23" s="3">
         <v>4.4845012962678503E-2</v>
       </c>
-      <c r="E23" s="61">
+      <c r="E23" s="33">
         <v>1.3223692425413101E-4</v>
       </c>
       <c r="F23" s="3">
         <v>0.21985816955566401</v>
       </c>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="61"/>
-      <c r="P23" s="4"/>
+      <c r="G23" s="9">
+        <v>4.8659135500447901</v>
+      </c>
+      <c r="H23" s="9">
+        <v>0.80604506674792997</v>
+      </c>
+      <c r="I23" s="9">
+        <v>4.7850025925356997E-2</v>
+      </c>
+      <c r="J23" s="9">
+        <v>1.3391539425830799E-4</v>
+      </c>
+      <c r="K23" s="9">
+        <v>0.222387790679931</v>
+      </c>
+      <c r="L23">
+        <v>5.4064631513318799</v>
+      </c>
+      <c r="M23">
+        <v>0.87969942139475399</v>
+      </c>
+      <c r="N23">
+        <v>4.79325388880356E-2</v>
+      </c>
+      <c r="O23">
+        <v>1.33935670807651E-4</v>
+      </c>
+      <c r="P23">
+        <v>0.24995470046997001</v>
+      </c>
       <c r="Q23" s="14"/>
       <c r="R23" s="14"/>
       <c r="S23" s="14"/>
-      <c r="T23" s="62"/>
+      <c r="T23" s="34"/>
       <c r="U23" s="14"/>
-      <c r="V23" s="66"/>
-      <c r="W23" s="66"/>
-      <c r="X23" s="66"/>
-      <c r="Y23" s="80"/>
-      <c r="Z23" s="66"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="33"/>
+      <c r="Z23" s="4"/>
       <c r="AA23" s="14"/>
       <c r="AB23" s="14"/>
       <c r="AC23" s="14"/>
-      <c r="AD23" s="62"/>
+      <c r="AD23" s="34"/>
       <c r="AE23" s="14"/>
-      <c r="AF23" s="66"/>
-      <c r="AG23" s="66"/>
-      <c r="AH23" s="66"/>
-      <c r="AI23" s="80"/>
-      <c r="AJ23" s="66"/>
-    </row>
-    <row r="24" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="AF23" s="4"/>
+      <c r="AG23" s="4"/>
+      <c r="AH23" s="4"/>
+      <c r="AI23" s="33"/>
+      <c r="AJ23" s="4"/>
+    </row>
+    <row r="24" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B24" s="4">
         <v>4.5673914929329396</v>
       </c>
@@ -2721,44 +2745,64 @@
       <c r="D24" s="3">
         <v>4.4845012962678503E-2</v>
       </c>
-      <c r="E24" s="61">
+      <c r="E24" s="33">
         <v>1.32229361220904E-4</v>
       </c>
       <c r="F24" s="4">
         <v>0.20500302314758301</v>
       </c>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="61"/>
-      <c r="P24" s="4"/>
+      <c r="G24" s="9">
+        <v>4.8519449972323798</v>
+      </c>
+      <c r="H24" s="9">
+        <v>0.80579230553816195</v>
+      </c>
+      <c r="I24" s="9">
+        <v>4.7850025925356997E-2</v>
+      </c>
+      <c r="J24" s="9">
+        <v>1.3391514061268501E-4</v>
+      </c>
+      <c r="K24" s="9">
+        <v>0.22048783302307101</v>
+      </c>
+      <c r="L24">
+        <v>4.8532425752229802</v>
+      </c>
+      <c r="M24">
+        <v>0.80579230553816195</v>
+      </c>
+      <c r="N24">
+        <v>4.7847538888035598E-2</v>
+      </c>
+      <c r="O24">
+        <v>1.33917231857661E-4</v>
+      </c>
+      <c r="P24">
+        <v>0.22810745239257799</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
-      <c r="T24" s="62"/>
+      <c r="T24" s="34"/>
       <c r="U24" s="14"/>
-      <c r="V24" s="66"/>
-      <c r="W24" s="66"/>
-      <c r="X24" s="66"/>
-      <c r="Y24" s="80"/>
-      <c r="Z24" s="66"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="33"/>
+      <c r="Z24" s="4"/>
       <c r="AA24" s="14"/>
       <c r="AB24" s="14"/>
       <c r="AC24" s="14"/>
-      <c r="AD24" s="62"/>
+      <c r="AD24" s="34"/>
       <c r="AE24" s="14"/>
-      <c r="AF24" s="66"/>
-      <c r="AG24" s="66"/>
-      <c r="AH24" s="66"/>
-      <c r="AI24" s="80"/>
-      <c r="AJ24" s="66"/>
-    </row>
-    <row r="25" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="AF24" s="4"/>
+      <c r="AG24" s="4"/>
+      <c r="AH24" s="4"/>
+      <c r="AI24" s="33"/>
+      <c r="AJ24" s="4"/>
+    </row>
+    <row r="25" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B25" s="4">
         <v>4.5673914929329396</v>
       </c>
@@ -2768,44 +2812,64 @@
       <c r="D25" s="3">
         <v>4.4845012962678503E-2</v>
       </c>
-      <c r="E25" s="61">
+      <c r="E25" s="33">
         <v>1.32221798187677E-4</v>
       </c>
       <c r="F25" s="4">
         <v>0.211128234863281</v>
       </c>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="61"/>
-      <c r="P25" s="4"/>
+      <c r="G25" s="9">
+        <v>4.88457126512131</v>
+      </c>
+      <c r="H25" s="9">
+        <v>0.80604506674792997</v>
+      </c>
+      <c r="I25" s="9">
+        <v>4.7832525925357097E-2</v>
+      </c>
+      <c r="J25" s="9">
+        <v>1.33917557641819E-4</v>
+      </c>
+      <c r="K25" s="9">
+        <v>0.22298312187194799</v>
+      </c>
+      <c r="L25">
+        <v>5.2461342255167303</v>
+      </c>
+      <c r="M25">
+        <v>0.87969942139475399</v>
+      </c>
+      <c r="N25">
+        <v>4.7840038888035598E-2</v>
+      </c>
+      <c r="O25">
+        <v>1.33915989395852E-4</v>
+      </c>
+      <c r="P25">
+        <v>0.26530623435974099</v>
+      </c>
       <c r="Q25" s="14"/>
       <c r="R25" s="14"/>
       <c r="S25" s="14"/>
-      <c r="T25" s="62"/>
+      <c r="T25" s="34"/>
       <c r="U25" s="14"/>
-      <c r="V25" s="66"/>
-      <c r="W25" s="66"/>
-      <c r="X25" s="66"/>
-      <c r="Y25" s="80"/>
-      <c r="Z25" s="66"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="4"/>
       <c r="AA25" s="14"/>
       <c r="AB25" s="14"/>
       <c r="AC25" s="14"/>
-      <c r="AD25" s="62"/>
+      <c r="AD25" s="34"/>
       <c r="AE25" s="14"/>
-      <c r="AF25" s="66"/>
-      <c r="AG25" s="66"/>
-      <c r="AH25" s="66"/>
-      <c r="AI25" s="80"/>
-      <c r="AJ25" s="66"/>
-    </row>
-    <row r="26" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="AF25" s="4"/>
+      <c r="AG25" s="4"/>
+      <c r="AH25" s="4"/>
+      <c r="AI25" s="33"/>
+      <c r="AJ25" s="4"/>
+    </row>
+    <row r="26" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B26" s="4">
         <v>4.5201319803780304</v>
       </c>
@@ -2815,44 +2879,64 @@
       <c r="D26" s="3">
         <v>4.4845012962678503E-2</v>
       </c>
-      <c r="E26" s="61">
+      <c r="E26" s="33">
         <v>1.3221423515444999E-4</v>
       </c>
       <c r="F26" s="4">
         <v>0.24598479270935</v>
       </c>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="61"/>
-      <c r="P26" s="4"/>
+      <c r="G26" s="9">
+        <v>5.1555631562407296</v>
+      </c>
+      <c r="H26" s="9">
+        <v>0.87969942139475399</v>
+      </c>
+      <c r="I26" s="9">
+        <v>4.7847525925357098E-2</v>
+      </c>
+      <c r="J26" s="9">
+        <v>1.3391368999417599E-4</v>
+      </c>
+      <c r="K26" s="9">
+        <v>0.23683762550354001</v>
+      </c>
+      <c r="L26">
+        <v>5.1889066736848903</v>
+      </c>
+      <c r="M26">
+        <v>0.87969942139475399</v>
+      </c>
+      <c r="N26">
+        <v>4.7850038888035601E-2</v>
+      </c>
+      <c r="O26">
+        <v>1.3391669926256E-4</v>
+      </c>
+      <c r="P26">
+        <v>0.23890328407287501</v>
+      </c>
       <c r="Q26" s="14"/>
       <c r="R26" s="14"/>
       <c r="S26" s="14"/>
-      <c r="T26" s="62"/>
+      <c r="T26" s="34"/>
       <c r="U26" s="14"/>
-      <c r="V26" s="66"/>
-      <c r="W26" s="66"/>
-      <c r="X26" s="66"/>
-      <c r="Y26" s="80"/>
-      <c r="Z26" s="66"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="4"/>
       <c r="AA26" s="14"/>
       <c r="AB26" s="14"/>
       <c r="AC26" s="14"/>
-      <c r="AD26" s="62"/>
+      <c r="AD26" s="34"/>
       <c r="AE26" s="14"/>
-      <c r="AF26" s="66"/>
-      <c r="AG26" s="66"/>
-      <c r="AH26" s="66"/>
-      <c r="AI26" s="80"/>
-      <c r="AJ26" s="66"/>
-    </row>
-    <row r="28" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="AF26" s="4"/>
+      <c r="AG26" s="4"/>
+      <c r="AH26" s="4"/>
+      <c r="AI26" s="33"/>
+      <c r="AJ26" s="4"/>
+    </row>
+    <row r="28" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B28" s="40" t="s">
         <v>44</v>
       </c>
@@ -2891,58 +2975,58 @@
       <c r="AI28" s="40"/>
       <c r="AJ28" s="40"/>
     </row>
-    <row r="29" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B29" s="33" t="s">
+    <row r="29" spans="2:36" x14ac:dyDescent="0.2">
+      <c r="B29" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="70" t="s">
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="H29" s="71"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="71"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="36" t="s">
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="46"/>
+      <c r="L29" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="M29" s="37"/>
-      <c r="N29" s="37"/>
-      <c r="O29" s="37"/>
-      <c r="P29" s="38"/>
-      <c r="Q29" s="75" t="s">
+      <c r="M29" s="48"/>
+      <c r="N29" s="48"/>
+      <c r="O29" s="48"/>
+      <c r="P29" s="49"/>
+      <c r="Q29" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="R29" s="76"/>
-      <c r="S29" s="76"/>
-      <c r="T29" s="76"/>
-      <c r="U29" s="77"/>
-      <c r="V29" s="67" t="s">
+      <c r="R29" s="51"/>
+      <c r="S29" s="51"/>
+      <c r="T29" s="51"/>
+      <c r="U29" s="52"/>
+      <c r="V29" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="W29" s="68"/>
-      <c r="X29" s="68"/>
-      <c r="Y29" s="68"/>
-      <c r="Z29" s="69"/>
-      <c r="AA29" s="75" t="s">
+      <c r="W29" s="48"/>
+      <c r="X29" s="48"/>
+      <c r="Y29" s="48"/>
+      <c r="Z29" s="49"/>
+      <c r="AA29" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AB29" s="76"/>
-      <c r="AC29" s="76"/>
-      <c r="AD29" s="76"/>
-      <c r="AE29" s="77"/>
-      <c r="AF29" s="67" t="s">
+      <c r="AB29" s="51"/>
+      <c r="AC29" s="51"/>
+      <c r="AD29" s="51"/>
+      <c r="AE29" s="52"/>
+      <c r="AF29" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="AG29" s="68"/>
-      <c r="AH29" s="68"/>
-      <c r="AI29" s="68"/>
-      <c r="AJ29" s="69"/>
-    </row>
-    <row r="30" spans="2:36" ht="60" x14ac:dyDescent="0.25">
+      <c r="AG29" s="48"/>
+      <c r="AH29" s="48"/>
+      <c r="AI29" s="48"/>
+      <c r="AJ29" s="49"/>
+    </row>
+    <row r="30" spans="2:36" ht="64" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>20</v>
       </c>
@@ -2952,25 +3036,25 @@
       <c r="D30" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E30" s="60" t="s">
+      <c r="E30" s="32" t="s">
         <v>23</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G30" s="73" t="s">
+      <c r="G30" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="H30" s="73" t="s">
+      <c r="H30" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I30" s="74" t="s">
+      <c r="I30" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="J30" s="81" t="s">
+      <c r="J30" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="K30" s="73" t="s">
+      <c r="K30" s="36" t="s">
         <v>26</v>
       </c>
       <c r="L30" s="2" t="s">
@@ -2982,74 +3066,74 @@
       <c r="N30" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="O30" s="60" t="s">
+      <c r="O30" s="32" t="s">
         <v>23</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="Q30" s="73" t="s">
+      <c r="Q30" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="R30" s="73" t="s">
+      <c r="R30" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="S30" s="74" t="s">
+      <c r="S30" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="T30" s="81" t="s">
+      <c r="T30" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="U30" s="73" t="s">
+      <c r="U30" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="V30" s="64" t="s">
+      <c r="V30" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="W30" s="64" t="s">
+      <c r="W30" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="X30" s="65" t="s">
+      <c r="X30" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="Y30" s="79" t="s">
+      <c r="Y30" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="Z30" s="64" t="s">
+      <c r="Z30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AA30" s="73" t="s">
+      <c r="AA30" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="AB30" s="73" t="s">
+      <c r="AB30" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="AC30" s="74" t="s">
+      <c r="AC30" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="AD30" s="81" t="s">
+      <c r="AD30" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="AE30" s="73" t="s">
+      <c r="AE30" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="AF30" s="64" t="s">
+      <c r="AF30" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AG30" s="64" t="s">
+      <c r="AG30" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AH30" s="65" t="s">
+      <c r="AH30" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AI30" s="79" t="s">
+      <c r="AI30" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="AJ30" s="64" t="s">
+      <c r="AJ30" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B31" s="4">
         <v>69.401945813401099</v>
       </c>
@@ -3059,7 +3143,7 @@
       <c r="D31" s="3">
         <v>6.2164238822761397E-2</v>
       </c>
-      <c r="E31" s="61">
+      <c r="E31" s="33">
         <v>1.8113523540713401E-5</v>
       </c>
       <c r="F31" s="4">
@@ -3074,7 +3158,7 @@
       <c r="I31" s="14">
         <v>8.8056366468285296E-2</v>
       </c>
-      <c r="J31" s="62">
+      <c r="J31" s="34">
         <v>2.79096427281892E-5</v>
       </c>
       <c r="K31" s="14">
@@ -3089,7 +3173,7 @@
       <c r="N31" s="3">
         <v>8.8401044113808502E-2</v>
       </c>
-      <c r="O31" s="61">
+      <c r="O31" s="33">
         <v>2.80358393491259E-5</v>
       </c>
       <c r="P31" s="4">
@@ -3104,25 +3188,25 @@
       <c r="S31" s="14">
         <v>8.8616788227617399E-2</v>
       </c>
-      <c r="T31" s="62">
+      <c r="T31" s="34">
         <v>2.81752679425879E-5</v>
       </c>
       <c r="U31" s="14">
         <v>2.3361291885375901</v>
       </c>
-      <c r="V31" s="66">
+      <c r="V31" s="4">
         <v>3.8181739439976101</v>
       </c>
-      <c r="W31" s="66">
+      <c r="W31" s="4">
         <v>0.69893563754981602</v>
       </c>
-      <c r="X31" s="66">
+      <c r="X31" s="4">
         <v>8.8446251455234798E-2</v>
       </c>
-      <c r="Y31" s="80">
+      <c r="Y31" s="33">
         <v>2.8157871987388801E-5</v>
       </c>
-      <c r="Z31" s="66">
+      <c r="Z31" s="4">
         <v>2.6465549468994101</v>
       </c>
       <c r="AA31" s="14">
@@ -3134,29 +3218,29 @@
       <c r="AC31" s="14">
         <v>8.8203191138086501E-2</v>
       </c>
-      <c r="AD31" s="62">
+      <c r="AD31" s="34">
         <v>2.83035368819735E-5</v>
       </c>
       <c r="AE31" s="14">
         <v>3.06500816345214</v>
       </c>
-      <c r="AF31" s="66">
+      <c r="AF31" s="4">
         <v>3.8354882494398801</v>
       </c>
-      <c r="AG31" s="66">
+      <c r="AG31" s="4">
         <v>0.70595755176693498</v>
       </c>
-      <c r="AH31" s="66">
+      <c r="AH31" s="4">
         <v>8.8415207276172497E-2</v>
       </c>
-      <c r="AI31" s="80">
+      <c r="AI31" s="33">
         <v>2.8776972045180201E-5</v>
       </c>
-      <c r="AJ31" s="66">
+      <c r="AJ31" s="4">
         <v>3.9523067474365199</v>
       </c>
     </row>
-    <row r="32" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B32" s="4">
         <v>68.916185153514803</v>
       </c>
@@ -3166,7 +3250,7 @@
       <c r="D32" s="3">
         <v>6.2164238822761397E-2</v>
       </c>
-      <c r="E32" s="61">
+      <c r="E32" s="33">
         <v>1.80867406639186E-5</v>
       </c>
       <c r="F32" s="3">
@@ -3175,13 +3259,13 @@
       <c r="G32" s="14">
         <v>3.92157571097757</v>
       </c>
-      <c r="H32" s="78">
+      <c r="H32" s="38">
         <v>0.70745833035179795</v>
       </c>
       <c r="I32" s="14">
         <v>8.8056366468285296E-2</v>
       </c>
-      <c r="J32" s="62">
+      <c r="J32" s="34">
         <v>2.79165756357338E-5</v>
       </c>
       <c r="K32" s="14">
@@ -3196,7 +3280,7 @@
       <c r="N32" s="3">
         <v>8.85403441138089E-2</v>
       </c>
-      <c r="O32" s="61">
+      <c r="O32" s="33">
         <v>2.8099163570296E-5</v>
       </c>
       <c r="P32" s="4">
@@ -3211,25 +3295,25 @@
       <c r="S32" s="14">
         <v>8.8391188227616796E-2</v>
       </c>
-      <c r="T32" s="62">
+      <c r="T32" s="34">
         <v>2.8078570440168501E-5</v>
       </c>
       <c r="U32" s="14">
         <v>2.4931118488311701</v>
       </c>
-      <c r="V32" s="66">
+      <c r="V32" s="4">
         <v>3.8006592263743402</v>
       </c>
-      <c r="W32" s="66">
+      <c r="W32" s="4">
         <v>0.69891181163915606</v>
       </c>
-      <c r="X32" s="66">
+      <c r="X32" s="4">
         <v>8.8456201455234806E-2</v>
       </c>
-      <c r="Y32" s="80">
+      <c r="Y32" s="33">
         <v>2.81696465383705E-5</v>
       </c>
-      <c r="Z32" s="66">
+      <c r="Z32" s="4">
         <v>2.28475618362426</v>
       </c>
       <c r="AA32" s="14">
@@ -3241,29 +3325,29 @@
       <c r="AC32" s="14">
         <v>8.8511741138086297E-2</v>
       </c>
-      <c r="AD32" s="62">
+      <c r="AD32" s="34">
         <v>2.8413531592332301E-5</v>
       </c>
       <c r="AE32" s="14">
         <v>3.03480005264282</v>
       </c>
-      <c r="AF32" s="66">
+      <c r="AF32" s="4">
         <v>3.92702068981834</v>
       </c>
-      <c r="AG32" s="66">
+      <c r="AG32" s="4">
         <v>0.72441696782635001</v>
       </c>
-      <c r="AH32" s="66">
+      <c r="AH32" s="4">
         <v>8.8353882276172899E-2</v>
       </c>
-      <c r="AI32" s="80">
+      <c r="AI32" s="33">
         <v>2.8740707252570802E-5</v>
       </c>
-      <c r="AJ32" s="66">
+      <c r="AJ32" s="4">
         <v>4.0790760517120299</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B33" s="4">
         <v>68.964609212397804</v>
       </c>
@@ -3273,7 +3357,7 @@
       <c r="D33" s="3">
         <v>6.2164238822761397E-2</v>
       </c>
-      <c r="E33" s="61">
+      <c r="E33" s="33">
         <v>1.8099707152006E-5</v>
       </c>
       <c r="F33" s="4">
@@ -3288,7 +3372,7 @@
       <c r="I33" s="14">
         <v>8.8273741468284997E-2</v>
       </c>
-      <c r="J33" s="62">
+      <c r="J33" s="34">
         <v>2.79946164319667E-5</v>
       </c>
       <c r="K33" s="14">
@@ -3303,7 +3387,7 @@
       <c r="N33" s="3">
         <v>8.8307994113808796E-2</v>
       </c>
-      <c r="O33" s="61">
+      <c r="O33" s="33">
         <v>2.80145273619772E-5</v>
       </c>
       <c r="P33" s="4">
@@ -3318,25 +3402,25 @@
       <c r="S33" s="14">
         <v>8.8323063227617099E-2</v>
       </c>
-      <c r="T33" s="62">
+      <c r="T33" s="34">
         <v>2.80588246584969E-5</v>
       </c>
       <c r="U33" s="14">
         <v>2.14797663688659</v>
       </c>
-      <c r="V33" s="66">
+      <c r="V33" s="4">
         <v>3.9457577664771999</v>
       </c>
-      <c r="W33" s="66">
+      <c r="W33" s="4">
         <v>0.71548445965802898</v>
       </c>
-      <c r="X33" s="66">
+      <c r="X33" s="4">
         <v>8.8446251455234701E-2</v>
       </c>
-      <c r="Y33" s="80">
+      <c r="Y33" s="33">
         <v>2.8164523725942199E-5</v>
       </c>
-      <c r="Z33" s="66">
+      <c r="Z33" s="4">
         <v>2.5861542224884002</v>
       </c>
       <c r="AA33" s="14">
@@ -3348,29 +3432,29 @@
       <c r="AC33" s="14">
         <v>8.8443616138086198E-2</v>
       </c>
-      <c r="AD33" s="62">
+      <c r="AD33" s="34">
         <v>2.8409425784168799E-5</v>
       </c>
       <c r="AE33" s="14">
         <v>3.10672783851623</v>
       </c>
-      <c r="AF33" s="66">
+      <c r="AF33" s="4">
         <v>3.8184299570617402</v>
       </c>
-      <c r="AG33" s="66">
+      <c r="AG33" s="4">
         <v>0.69896723257465598</v>
       </c>
-      <c r="AH33" s="66">
+      <c r="AH33" s="4">
         <v>8.8687357276172801E-2</v>
       </c>
-      <c r="AI33" s="80">
+      <c r="AI33" s="33">
         <v>2.8858936560529499E-5</v>
       </c>
-      <c r="AJ33" s="66">
+      <c r="AJ33" s="4">
         <v>4.2503848075866699</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B34" s="4">
         <v>69.172551685058906</v>
       </c>
@@ -3380,7 +3464,7 @@
       <c r="D34" s="3">
         <v>6.2164238822761397E-2</v>
       </c>
-      <c r="E34" s="61">
+      <c r="E34" s="33">
         <v>1.8033174910329E-5</v>
       </c>
       <c r="F34" s="4">
@@ -3395,7 +3479,7 @@
       <c r="I34" s="14">
         <v>8.8273741468284997E-2</v>
       </c>
-      <c r="J34" s="62">
+      <c r="J34" s="34">
         <v>2.80154346836361E-5</v>
       </c>
       <c r="K34" s="14">
@@ -3410,7 +3494,7 @@
       <c r="N34" s="3">
         <v>8.8254894113808297E-2</v>
       </c>
-      <c r="O34" s="61">
+      <c r="O34" s="33">
         <v>2.8002209630401E-5</v>
       </c>
       <c r="P34" s="4">
@@ -3425,25 +3509,25 @@
       <c r="S34" s="14">
         <v>8.8143963227617098E-2</v>
       </c>
-      <c r="T34" s="62">
+      <c r="T34" s="34">
         <v>2.7991991491029802E-5</v>
       </c>
       <c r="U34" s="14">
         <v>2.5393826961517298</v>
       </c>
-      <c r="V34" s="66">
+      <c r="V34" s="4">
         <v>3.7290937930123</v>
       </c>
-      <c r="W34" s="66">
+      <c r="W34" s="4">
         <v>0.69918828192124105</v>
       </c>
-      <c r="X34" s="66">
+      <c r="X34" s="4">
         <v>8.8353201455234606E-2</v>
       </c>
-      <c r="Y34" s="80">
+      <c r="Y34" s="33">
         <v>2.8151395378405799E-5</v>
       </c>
-      <c r="Z34" s="66">
+      <c r="Z34" s="4">
         <v>2.5232589244842498</v>
       </c>
       <c r="AA34" s="14">
@@ -3455,29 +3539,29 @@
       <c r="AC34" s="14">
         <v>8.8390516138086503E-2</v>
       </c>
-      <c r="AD34" s="62">
+      <c r="AD34" s="34">
         <v>2.83951462158457E-5</v>
       </c>
       <c r="AE34" s="14">
         <v>3.0574562549590998</v>
       </c>
-      <c r="AF34" s="66">
+      <c r="AF34" s="4">
         <v>4.1305605019934903</v>
       </c>
-      <c r="AG34" s="66">
+      <c r="AG34" s="4">
         <v>0.74397459185471204</v>
       </c>
-      <c r="AH34" s="66">
+      <c r="AH34" s="4">
         <v>8.8718832276172804E-2</v>
       </c>
-      <c r="AI34" s="80">
+      <c r="AI34" s="33">
         <v>2.88892419446415E-5</v>
       </c>
-      <c r="AJ34" s="66">
+      <c r="AJ34" s="4">
         <v>3.9828605651855402</v>
       </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B35" s="4">
         <v>69.139874543880694</v>
       </c>
@@ -3487,7 +3571,7 @@
       <c r="D35" s="3">
         <v>6.2164238822761397E-2</v>
       </c>
-      <c r="E35" s="61">
+      <c r="E35" s="33">
         <v>1.8006392033534199E-5</v>
       </c>
       <c r="F35" s="4">
@@ -3502,7 +3586,7 @@
       <c r="I35" s="14">
         <v>8.8292016468285106E-2</v>
       </c>
-      <c r="J35" s="62">
+      <c r="J35" s="34">
         <v>2.7991976836474499E-5</v>
       </c>
       <c r="K35" s="14">
@@ -3517,7 +3601,7 @@
       <c r="N35" s="3">
         <v>8.8128894113808406E-2</v>
       </c>
-      <c r="O35" s="61">
+      <c r="O35" s="33">
         <v>2.7956683894845301E-5</v>
       </c>
       <c r="P35" s="4">
@@ -3532,25 +3616,25 @@
       <c r="S35" s="14">
         <v>8.8565363227617599E-2</v>
       </c>
-      <c r="T35" s="62">
+      <c r="T35" s="34">
         <v>2.8148309439684399E-5</v>
       </c>
       <c r="U35" s="14">
         <v>2.1721127033233598</v>
       </c>
-      <c r="V35" s="66">
+      <c r="V35" s="4">
         <v>3.8079109139982701</v>
       </c>
-      <c r="W35" s="66">
+      <c r="W35" s="4">
         <v>0.70885640099114799</v>
       </c>
-      <c r="X35" s="66">
+      <c r="X35" s="4">
         <v>8.8203801455234501E-2</v>
       </c>
-      <c r="Y35" s="80">
+      <c r="Y35" s="33">
         <v>2.8106798485124302E-5</v>
       </c>
-      <c r="Z35" s="66">
+      <c r="Z35" s="4">
         <v>2.48196053504943</v>
       </c>
       <c r="AA35" s="14">
@@ -3562,38 +3646,39 @@
       <c r="AC35" s="14">
         <v>8.8294216138086398E-2</v>
       </c>
-      <c r="AD35" s="62">
+      <c r="AD35" s="34">
         <v>2.83683693983857E-5</v>
       </c>
       <c r="AE35" s="14">
         <v>3.0213196277618399</v>
       </c>
-      <c r="AF35" s="66">
+      <c r="AF35" s="4">
         <v>3.9283256783666101</v>
       </c>
-      <c r="AG35" s="66">
+      <c r="AG35" s="4">
         <v>0.71459088090707101</v>
       </c>
-      <c r="AH35" s="66">
+      <c r="AH35" s="4">
         <v>8.8391857276173103E-2</v>
       </c>
-      <c r="AI35" s="80">
+      <c r="AI35" s="33">
         <v>2.8784333993172201E-5</v>
       </c>
-      <c r="AJ35" s="66">
+      <c r="AJ35" s="4">
         <v>4.0355627536773602</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B28:AJ28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="G29:K29"/>
-    <mergeCell ref="L29:P29"/>
-    <mergeCell ref="Q29:U29"/>
-    <mergeCell ref="V29:Z29"/>
-    <mergeCell ref="AA29:AE29"/>
-    <mergeCell ref="AF29:AJ29"/>
+    <mergeCell ref="AF2:AJ2"/>
+    <mergeCell ref="V2:Z2"/>
+    <mergeCell ref="AA2:AE2"/>
+    <mergeCell ref="B1:AJ1"/>
+    <mergeCell ref="B10:AJ10"/>
+    <mergeCell ref="Q2:U2"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="L2:P2"/>
+    <mergeCell ref="G2:K2"/>
     <mergeCell ref="V11:Z11"/>
     <mergeCell ref="AA11:AE11"/>
     <mergeCell ref="AF11:AJ11"/>
@@ -3605,19 +3690,18 @@
     <mergeCell ref="V20:Z20"/>
     <mergeCell ref="AA20:AE20"/>
     <mergeCell ref="AF20:AJ20"/>
-    <mergeCell ref="AF2:AJ2"/>
-    <mergeCell ref="V2:Z2"/>
-    <mergeCell ref="AA2:AE2"/>
-    <mergeCell ref="B1:AJ1"/>
-    <mergeCell ref="B10:AJ10"/>
     <mergeCell ref="Q11:U11"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="G11:K11"/>
     <mergeCell ref="L11:P11"/>
-    <mergeCell ref="Q2:U2"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="B28:AJ28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="G29:K29"/>
+    <mergeCell ref="L29:P29"/>
+    <mergeCell ref="Q29:U29"/>
+    <mergeCell ref="V29:Z29"/>
+    <mergeCell ref="AA29:AE29"/>
+    <mergeCell ref="AF29:AJ29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3626,53 +3710,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB2F127C-15E6-41A0-94B0-FA50F057125C}">
   <dimension ref="A1:S59"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.140625" style="20" customWidth="1"/>
+    <col min="13" max="13" width="17.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.1640625" style="20" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="24" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:19" s="24" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-    </row>
-    <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+    </row>
+    <row r="2" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="M2" s="12"/>
       <c r="N2" s="15"/>
     </row>
-    <row r="3" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -3719,35 +3803,35 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" s="62" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="47">
+      <c r="D4" s="55">
         <v>66</v>
       </c>
-      <c r="E4" s="47">
+      <c r="E4" s="55">
         <v>66</v>
       </c>
-      <c r="F4" s="48">
+      <c r="F4" s="65">
         <v>13000</v>
       </c>
-      <c r="G4" s="47">
+      <c r="G4" s="55">
         <v>1</v>
       </c>
-      <c r="H4" s="47">
+      <c r="H4" s="55">
         <v>1</v>
       </c>
-      <c r="I4" s="47">
+      <c r="I4" s="55">
         <v>66</v>
       </c>
-      <c r="J4" s="47">
+      <c r="J4" s="55">
         <v>66</v>
       </c>
       <c r="K4" s="5">
@@ -3771,19 +3855,19 @@
         <v>2.15042877197265</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="44"/>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" s="63"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
       <c r="K5" s="5">
         <f>AVERAGE(DataExp1.1!G4:G8)</f>
         <v>21.856551751247018</v>
@@ -3805,19 +3889,19 @@
         <v>2.1786093235015822</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" s="63"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
       <c r="K6" s="5">
         <f>AVERAGE(DataExp1.1!L4:L8)</f>
         <v>11.98984802681626</v>
@@ -3839,19 +3923,19 @@
         <v>2.3205418109893743</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="44"/>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" s="63"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
       <c r="K7" s="5">
         <f>AVERAGE(DataExp1.1!Q4:Q8)</f>
         <v>1.5875226457050842</v>
@@ -3873,19 +3957,19 @@
         <v>2.2747531890869097</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" s="63"/>
       <c r="B8" s="6">
         <v>20</v>
       </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
       <c r="K8" s="5">
         <f>AVERAGE(DataExp1.1!V4:V8)</f>
         <v>1.1816151609203558</v>
@@ -3907,19 +3991,19 @@
         <v>2.5595404148101739</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="44"/>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9" s="63"/>
       <c r="B9" s="6">
         <v>50</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
       <c r="K9" s="5">
         <f>AVERAGE(DataExp1.1!AA4:AA8)</f>
         <v>1.6919275836893182</v>
@@ -3941,19 +4025,19 @@
         <v>3.0158440589904738</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="44"/>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10" s="63"/>
       <c r="B10" s="6">
         <v>100</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
       <c r="K10" s="5">
         <f>AVERAGE(DataExp1.1!AF4:AF8)</f>
         <v>1.1607429307212318</v>
@@ -3975,21 +4059,21 @@
         <v>4.1033407211303663</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="45" t="s">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11" s="56" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="56"/>
       <c r="K11" s="4">
         <f>AVERAGE(DataExp1.1!B13:B17)</f>
         <v>98.52386541032611</v>
@@ -4011,19 +4095,19 @@
         <v>2.0277222156524619</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="45"/>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12" s="56"/>
       <c r="B12" s="3">
         <v>3</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="56"/>
       <c r="K12" s="4">
         <f>AVERAGE(DataExp1.1!G13:G17)</f>
         <v>3.5894588009443735</v>
@@ -4045,19 +4129,19 @@
         <v>2.2956936836242638</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="45"/>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13" s="56"/>
       <c r="B13" s="3">
         <v>5</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
       <c r="K13" s="4">
         <f>AVERAGE(DataExp1.1!L13:L17)</f>
         <v>4.6885991481999643</v>
@@ -4079,19 +4163,19 @@
         <v>2.1628134727477986</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="45"/>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A14" s="56"/>
       <c r="B14" s="3">
         <v>10</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
       <c r="K14" s="4">
         <f>AVERAGE(DataExp1.1!Q13:Q17)</f>
         <v>4.6542904797370337</v>
@@ -4113,19 +4197,19 @@
         <v>2.3146313190460179</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="45"/>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15" s="56"/>
       <c r="B15" s="3">
         <v>20</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
       <c r="K15" s="4">
         <f>AVERAGE(DataExp1.1!V13:V17)</f>
         <v>4.7382106552509056</v>
@@ -4147,19 +4231,19 @@
         <v>2.6227613925933779</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="45"/>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A16" s="56"/>
       <c r="B16" s="3">
         <v>50</v>
       </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
       <c r="K16" s="4">
         <f>AVERAGE(DataExp1.1!AA13:AA17)</f>
         <v>3.5014269837011178</v>
@@ -4181,19 +4265,19 @@
         <v>3.1331105232238721</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="45"/>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17" s="56"/>
       <c r="B17" s="3">
         <v>100</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="56"/>
       <c r="K17" s="4">
         <f>AVERAGE(DataExp1.1!AF13:AF17)</f>
         <v>4.0573849410218283</v>
@@ -4215,156 +4299,201 @@
         <v>4.1135736465454062</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="46" t="s">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18" s="64" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="30">
         <v>1</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="22"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="46"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
+      <c r="K18" s="22">
+        <f>AVERAGE(DataExp1.1!B22:B26)</f>
+        <v>4.5451398138019297</v>
+      </c>
+      <c r="L18" s="22">
+        <f>AVERAGE(DataExp1.1!C22:C26)</f>
+        <v>0.75511641042661903</v>
+      </c>
+      <c r="M18" s="22">
+        <f>AVERAGE(DataExp1.1!D22:D26)</f>
+        <v>4.4845012962678503E-2</v>
+      </c>
+      <c r="N18" s="22">
+        <f>AVERAGE(DataExp1.1!E22:E26)</f>
+        <v>1.32229361220904E-4</v>
+      </c>
+      <c r="O18" s="22">
+        <f>AVERAGE(DataExp1.1!F22:F26)</f>
+        <v>0.21877102851867641</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A19" s="64"/>
       <c r="B19" s="30">
         <v>3</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="22"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="22"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="46"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="56"/>
+      <c r="K19" s="22">
+        <f>AVERAGE(DataExp1.1!G22:G26)</f>
+        <v>5.0008254388311881</v>
+      </c>
+      <c r="L19" s="22">
+        <f>AVERAGE(DataExp1.1!H22:H26)</f>
+        <v>0.83545625636470588</v>
+      </c>
+      <c r="M19" s="22">
+        <f>AVERAGE(DataExp1.1!I22:I26)</f>
+        <v>4.7840025925357063E-2</v>
+      </c>
+      <c r="N19" s="22">
+        <f>AVERAGE(DataExp1.1!J22:J26)</f>
+        <v>1.3391411094868099E-4</v>
+      </c>
+      <c r="O19" s="22">
+        <f>AVERAGE(DataExp1.1!K22:K26)</f>
+        <v>0.22898344993591283</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A20" s="64"/>
       <c r="B20" s="30">
         <v>5</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="22"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="46"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="56"/>
+      <c r="K20" s="22">
+        <f>AVERAGE(DataExp1.1!L22:L26)</f>
+        <v>5.1520558152375724</v>
+      </c>
+      <c r="L20" s="22">
+        <f>AVERAGE(DataExp1.1!M22:M26)</f>
+        <v>0.86004741560851961</v>
+      </c>
+      <c r="M20" s="22">
+        <f>AVERAGE(DataExp1.1!N22:N26)</f>
+        <v>4.78625388880356E-2</v>
+      </c>
+      <c r="N20" s="22">
+        <f>AVERAGE(DataExp1.1!O22:O26)</f>
+        <v>1.3392026491918619E-4</v>
+      </c>
+      <c r="O20" s="22">
+        <f>AVERAGE(DataExp1.1!P22:P26)</f>
+        <v>0.246152257919311</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21" s="64"/>
       <c r="B21" s="30">
         <v>10</v>
       </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
       <c r="K21" s="22"/>
       <c r="L21" s="22"/>
       <c r="M21" s="22"/>
       <c r="N21" s="23"/>
       <c r="O21" s="22"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="46"/>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22" s="64"/>
       <c r="B22" s="30">
         <v>20</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
       <c r="K22" s="22"/>
       <c r="L22" s="22"/>
       <c r="M22" s="22"/>
       <c r="N22" s="23"/>
       <c r="O22" s="22"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="46"/>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23" s="64"/>
       <c r="B23" s="30">
         <v>50</v>
       </c>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="56"/>
       <c r="K23" s="22"/>
       <c r="L23" s="22"/>
       <c r="M23" s="22"/>
       <c r="N23" s="23"/>
       <c r="O23" s="22"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="46"/>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A24" s="64"/>
       <c r="B24" s="30">
         <v>100</v>
       </c>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="56"/>
       <c r="K24" s="22"/>
       <c r="L24" s="22"/>
       <c r="M24" s="22"/>
       <c r="N24" s="23"/>
       <c r="O24" s="22"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="45" t="s">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A25" s="56" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="3">
         <v>1</v>
       </c>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="56"/>
       <c r="K25" s="4">
         <f>AVERAGE(DataExp1.1!B31:B35)</f>
         <v>69.119033281650658</v>
@@ -4386,188 +4515,239 @@
         <v>2.0296193599700878</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="45"/>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A26" s="56"/>
       <c r="B26" s="3">
         <v>3</v>
       </c>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="4" t="e">
-        <f>AVERAGE(DataExp1.1!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L26" s="4" t="e">
-        <f>AVERAGE(DataExp1.1!#REF!)</f>
-        <v>#REF!</v>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="56"/>
+      <c r="K26" s="4">
+        <f>AVERAGE(DataExp1.1!G31:G35)</f>
+        <v>3.8112034677615521</v>
+      </c>
+      <c r="L26" s="4">
+        <f>AVERAGE(DataExp1.1!H31:H35)</f>
+        <v>0.69516313804590357</v>
       </c>
       <c r="M26" s="4">
-        <v>8.8175866468285097E-2</v>
-      </c>
-      <c r="N26" s="18">
-        <v>2.79669169855113E-5</v>
-      </c>
-      <c r="O26" s="4" t="e">
-        <f>AVERAGE(DataExp1.1!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="45"/>
+        <f>AVERAGE(DataExp1.1!I31:I35)</f>
+        <v>8.8190446468285139E-2</v>
+      </c>
+      <c r="N26" s="4">
+        <f>AVERAGE(DataExp1.1!J31:J35)</f>
+        <v>2.7965649263200062E-5</v>
+      </c>
+      <c r="O26" s="4">
+        <f>AVERAGE(DataExp1.1!K31:K35)</f>
+        <v>2.2586493492126438</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A27" s="56"/>
       <c r="B27" s="3">
         <v>5</v>
       </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="4" t="e">
-        <f>AVERAGE(DataExp1.1!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L27" s="4" t="e">
-        <f>AVERAGE(DataExp1.1!#REF!)</f>
-        <v>#REF!</v>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="56"/>
+      <c r="K27" s="4">
+        <f>AVERAGE(DataExp1.1!L31:L35)</f>
+        <v>3.794055612529962</v>
+      </c>
+      <c r="L27" s="4">
+        <f>AVERAGE(DataExp1.1!M31:M35)</f>
+        <v>0.70219775458629363</v>
       </c>
       <c r="M27" s="4">
-        <v>8.8376119113808799E-2</v>
-      </c>
-      <c r="N27" s="18">
-        <v>2.8023187480955202E-5</v>
-      </c>
-      <c r="O27" s="4" t="e">
-        <f>AVERAGE(DataExp1.1!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="45"/>
+        <f>AVERAGE(DataExp1.1!N31:N35)</f>
+        <v>8.8326634113808589E-2</v>
+      </c>
+      <c r="N27" s="4">
+        <f>AVERAGE(DataExp1.1!O31:O35)</f>
+        <v>2.8021684761329082E-5</v>
+      </c>
+      <c r="O27" s="4">
+        <f>AVERAGE(DataExp1.1!P31:P35)</f>
+        <v>2.2439172267913761</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28" s="56"/>
       <c r="B28" s="3">
         <v>10</v>
       </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="4" t="e">
-        <f>AVERAGE(DataExp1.1!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L28" s="4" t="e">
-        <f>AVERAGE(DataExp1.1!#REF!)</f>
-        <v>#REF!</v>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="4">
+        <f>AVERAGE(DataExp1.1!Q31:Q35)</f>
+        <v>3.8227770814034598</v>
+      </c>
+      <c r="L28" s="4">
+        <f>AVERAGE(DataExp1.1!R31:R35)</f>
+        <v>0.71134642701416584</v>
       </c>
       <c r="M28" s="4">
-        <v>8.81585941138084E-2</v>
-      </c>
-      <c r="N28" s="18">
-        <v>2.7971865110220399E-5</v>
-      </c>
-      <c r="O28" s="4" t="e">
-        <f>AVERAGE(DataExp1.1!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="45"/>
+        <f>AVERAGE(DataExp1.1!S31:S35)</f>
+        <v>8.8408073227617207E-2</v>
+      </c>
+      <c r="N28" s="4">
+        <f>AVERAGE(DataExp1.1!T31:T35)</f>
+        <v>2.8090592794393498E-5</v>
+      </c>
+      <c r="O28" s="4">
+        <f>AVERAGE(DataExp1.1!U31:U35)</f>
+        <v>2.3377426147460882</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29" s="56"/>
       <c r="B29" s="3">
         <v>20</v>
       </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="49"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="45"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="4"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="45"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="56"/>
+      <c r="K29" s="4">
+        <f>AVERAGE(DataExp1.1!V31:V35)</f>
+        <v>3.8203191287719442</v>
+      </c>
+      <c r="L29" s="4">
+        <f>AVERAGE(DataExp1.1!W31:W35)</f>
+        <v>0.70427531835187795</v>
+      </c>
+      <c r="M29" s="4">
+        <f>AVERAGE(DataExp1.1!X31:X35)</f>
+        <v>8.838114145523468E-2</v>
+      </c>
+      <c r="N29" s="4">
+        <f>AVERAGE(DataExp1.1!Y31:Y35)</f>
+        <v>2.8150047223046325E-5</v>
+      </c>
+      <c r="O29" s="4">
+        <f>AVERAGE(DataExp1.1!Z31:Z35)</f>
+        <v>2.50453696250915</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A30" s="56"/>
       <c r="B30" s="3">
         <v>50</v>
       </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="18"/>
-      <c r="O30" s="4"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="45"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="4">
+        <f>AVERAGE(DataExp1.1!AA31:AA35)</f>
+        <v>3.7894569132805862</v>
+      </c>
+      <c r="L30" s="4">
+        <f>AVERAGE(DataExp1.1!AB31:AB35)</f>
+        <v>0.70514874222061896</v>
+      </c>
+      <c r="M30" s="4">
+        <f>AVERAGE(DataExp1.1!AC31:AC35)</f>
+        <v>8.8368656138086393E-2</v>
+      </c>
+      <c r="N30" s="4">
+        <f>AVERAGE(DataExp1.1!AD31:AD35)</f>
+        <v>2.8378001974541202E-5</v>
+      </c>
+      <c r="O30" s="4">
+        <f>AVERAGE(DataExp1.1!AE31:AE35)</f>
+        <v>3.0570623874664258</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A31" s="56"/>
       <c r="B31" s="3">
         <v>100</v>
       </c>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="45"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="18"/>
-      <c r="O31" s="4"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32" s="52" t="s">
+      <c r="C31" s="56"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="56"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="56"/>
+      <c r="K31" s="4">
+        <f>AVERAGE(DataExp1.1!AF31:AF35)</f>
+        <v>3.9279650153360124</v>
+      </c>
+      <c r="L31" s="4">
+        <f>AVERAGE(DataExp1.1!AG31:AG35)</f>
+        <v>0.71758144498594478</v>
+      </c>
+      <c r="M31" s="4">
+        <f>AVERAGE(DataExp1.1!AH31:AH35)</f>
+        <v>8.8513427276172826E-2</v>
+      </c>
+      <c r="N31" s="4">
+        <f>AVERAGE(DataExp1.1!AI31:AI35)</f>
+        <v>2.881003835921884E-5</v>
+      </c>
+      <c r="O31" s="4">
+        <f>AVERAGE(DataExp1.1!AJ31:AJ35)</f>
+        <v>4.0600381851196241</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A32" s="57" t="s">
         <v>12</v>
       </c>
       <c r="B32" s="3">
         <v>1</v>
       </c>
-      <c r="C32" s="45" t="s">
+      <c r="C32" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="45">
+      <c r="D32" s="56">
         <v>128</v>
       </c>
-      <c r="E32" s="45">
+      <c r="E32" s="56">
         <v>128</v>
       </c>
-      <c r="F32" s="53">
+      <c r="F32" s="58">
         <v>1.1200000000000001</v>
       </c>
-      <c r="G32" s="45">
+      <c r="G32" s="56">
         <v>1</v>
       </c>
-      <c r="H32" s="45">
+      <c r="H32" s="56">
         <v>1</v>
       </c>
-      <c r="I32" s="45">
+      <c r="I32" s="56">
         <v>128</v>
       </c>
-      <c r="J32" s="45">
+      <c r="J32" s="56">
         <v>128</v>
       </c>
       <c r="K32" s="3" t="e">
@@ -4588,19 +4768,19 @@
         <v>12.759822845458901</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="52"/>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A33" s="57"/>
       <c r="B33" s="3">
         <v>3</v>
       </c>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="56"/>
       <c r="K33" s="3" t="e">
         <f>AVERAGE(DataExp1.1!#REF!)</f>
         <v>#REF!</v>
@@ -4619,19 +4799,19 @@
         <v>12.8247382640838</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="52"/>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A34" s="57"/>
       <c r="B34" s="3">
         <v>5</v>
       </c>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="45"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="45"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="56"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="56"/>
       <c r="K34" s="3" t="e">
         <f>AVERAGE(DataExp1.1!#REF!)</f>
         <v>#REF!</v>
@@ -4650,19 +4830,19 @@
         <v>12.9234986305236</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="52"/>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A35" s="57"/>
       <c r="B35" s="3">
         <v>10</v>
       </c>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="45"/>
-      <c r="H35" s="45"/>
-      <c r="I35" s="45"/>
-      <c r="J35" s="45"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
       <c r="K35" s="3" t="e">
         <f>AVERAGE(DataExp1.1!#REF!)</f>
         <v>#REF!</v>
@@ -4681,78 +4861,78 @@
         <v>14.266155481338499</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="52"/>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A36" s="57"/>
       <c r="B36" s="3">
         <v>20</v>
       </c>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
-      <c r="I36" s="45"/>
-      <c r="J36" s="45"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="56"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="4"/>
       <c r="N36" s="18"/>
       <c r="O36" s="4"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="52"/>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A37" s="57"/>
       <c r="B37" s="3">
         <v>50</v>
       </c>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="49"/>
-      <c r="G37" s="45"/>
-      <c r="H37" s="45"/>
-      <c r="I37" s="45"/>
-      <c r="J37" s="45"/>
+      <c r="C37" s="56"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="56"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="4"/>
       <c r="N37" s="18"/>
       <c r="O37" s="4"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="52"/>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A38" s="57"/>
       <c r="B38" s="3">
         <v>100</v>
       </c>
-      <c r="C38" s="45"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="45"/>
-      <c r="F38" s="49"/>
-      <c r="G38" s="45"/>
-      <c r="H38" s="45"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="45"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="56"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="4"/>
       <c r="N38" s="18"/>
       <c r="O38" s="4"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="50" t="s">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A39" s="53" t="s">
         <v>13</v>
       </c>
       <c r="B39" s="9">
         <v>1</v>
       </c>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="49"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="45"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="59"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="56"/>
       <c r="K39" s="9" t="e">
         <f>AVERAGE(DataExp1.1!#REF!)</f>
         <v>#REF!</v>
@@ -4771,19 +4951,19 @@
         <v>12.795346260070801</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="50"/>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A40" s="53"/>
       <c r="B40" s="9">
         <v>3</v>
       </c>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="49"/>
-      <c r="G40" s="45"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="45"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
       <c r="K40" s="9" t="e">
         <f>AVERAGE(DataExp1.1!#REF!)</f>
         <v>#REF!</v>
@@ -4802,19 +4982,19 @@
         <v>12.8078730106353</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="50"/>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A41" s="53"/>
       <c r="B41" s="9">
         <v>5</v>
       </c>
-      <c r="C41" s="45"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="45"/>
-      <c r="F41" s="49"/>
-      <c r="G41" s="45"/>
-      <c r="H41" s="45"/>
-      <c r="I41" s="45"/>
-      <c r="J41" s="45"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="56"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="56"/>
+      <c r="J41" s="56"/>
       <c r="K41" s="9" t="e">
         <f>AVERAGE(DataExp1.1!#REF!)</f>
         <v>#REF!</v>
@@ -4833,19 +5013,19 @@
         <v>26.1628239154815</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="50"/>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A42" s="53"/>
       <c r="B42" s="9">
         <v>10</v>
       </c>
-      <c r="C42" s="45"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="49"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="45"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="45"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="56"/>
+      <c r="J42" s="56"/>
       <c r="K42" s="9" t="e">
         <f>AVERAGE(DataExp1.1!#REF!)</f>
         <v>#REF!</v>
@@ -4864,78 +5044,78 @@
         <v>26.592686176299999</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="50"/>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A43" s="53"/>
       <c r="B43" s="9">
         <v>20</v>
       </c>
-      <c r="C43" s="45"/>
-      <c r="D43" s="45"/>
-      <c r="E43" s="45"/>
-      <c r="F43" s="49"/>
-      <c r="G43" s="45"/>
-      <c r="H43" s="45"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="45"/>
+      <c r="C43" s="56"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="56"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="56"/>
+      <c r="J43" s="56"/>
       <c r="K43" s="9"/>
       <c r="L43" s="9"/>
       <c r="M43" s="14"/>
       <c r="N43" s="19"/>
       <c r="O43" s="14"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="50"/>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A44" s="53"/>
       <c r="B44" s="9">
         <v>50</v>
       </c>
-      <c r="C44" s="45"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="45"/>
-      <c r="F44" s="49"/>
-      <c r="G44" s="45"/>
-      <c r="H44" s="45"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="45"/>
+      <c r="C44" s="56"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="56"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="56"/>
+      <c r="J44" s="56"/>
       <c r="K44" s="9"/>
       <c r="L44" s="9"/>
       <c r="M44" s="14"/>
       <c r="N44" s="19"/>
       <c r="O44" s="14"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="50"/>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A45" s="53"/>
       <c r="B45" s="9">
         <v>100</v>
       </c>
-      <c r="C45" s="45"/>
-      <c r="D45" s="45"/>
-      <c r="E45" s="45"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="45"/>
-      <c r="H45" s="45"/>
-      <c r="I45" s="45"/>
-      <c r="J45" s="45"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="56"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="56"/>
+      <c r="J45" s="56"/>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
       <c r="M45" s="14"/>
       <c r="N45" s="19"/>
       <c r="O45" s="9"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="51" t="s">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A46" s="54" t="s">
         <v>14</v>
       </c>
       <c r="B46" s="30">
         <v>1</v>
       </c>
-      <c r="C46" s="45"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="45"/>
-      <c r="F46" s="49"/>
-      <c r="G46" s="45"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45"/>
-      <c r="J46" s="45"/>
+      <c r="C46" s="56"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="59"/>
+      <c r="G46" s="56"/>
+      <c r="H46" s="56"/>
+      <c r="I46" s="56"/>
+      <c r="J46" s="56"/>
       <c r="K46" s="22" t="e">
         <f>AVERAGE(DataExp1.1!#REF!)</f>
         <v>#REF!</v>
@@ -4954,19 +5134,19 @@
         <v>0.30750107765197698</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" s="51"/>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A47" s="54"/>
       <c r="B47" s="30">
         <v>3</v>
       </c>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45"/>
-      <c r="E47" s="45"/>
-      <c r="F47" s="49"/>
-      <c r="G47" s="45"/>
-      <c r="H47" s="45"/>
-      <c r="I47" s="45"/>
-      <c r="J47" s="45"/>
+      <c r="C47" s="56"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56"/>
+      <c r="F47" s="59"/>
+      <c r="G47" s="56"/>
+      <c r="H47" s="56"/>
+      <c r="I47" s="56"/>
+      <c r="J47" s="56"/>
       <c r="K47" s="22" t="e">
         <f>AVERAGE(DataExp1.1!#REF!)</f>
         <v>#REF!</v>
@@ -4985,19 +5165,19 @@
         <v>0.36651349067687899</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" s="51"/>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A48" s="54"/>
       <c r="B48" s="30">
         <v>5</v>
       </c>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
-      <c r="E48" s="45"/>
-      <c r="F48" s="49"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="45"/>
+      <c r="C48" s="56"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="56"/>
+      <c r="F48" s="59"/>
+      <c r="G48" s="56"/>
+      <c r="H48" s="56"/>
+      <c r="I48" s="56"/>
+      <c r="J48" s="56"/>
       <c r="K48" s="22" t="e">
         <f>AVERAGE(DataExp1.1!#REF!)</f>
         <v>#REF!</v>
@@ -5016,19 +5196,19 @@
         <v>0.397212743759155</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A49" s="51"/>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A49" s="54"/>
       <c r="B49" s="31">
         <v>10</v>
       </c>
-      <c r="C49" s="45"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="45"/>
-      <c r="F49" s="49"/>
-      <c r="G49" s="45"/>
-      <c r="H49" s="45"/>
-      <c r="I49" s="45"/>
-      <c r="J49" s="45"/>
+      <c r="C49" s="56"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="59"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="56"/>
+      <c r="J49" s="56"/>
       <c r="K49" s="22" t="e">
         <f>AVERAGE(DataExp1.1!#REF!)</f>
         <v>#REF!</v>
@@ -5047,78 +5227,78 @@
         <v>0.36162972450256298</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" s="51"/>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A50" s="54"/>
       <c r="B50" s="31">
         <v>20</v>
       </c>
-      <c r="C50" s="45"/>
-      <c r="D50" s="45"/>
-      <c r="E50" s="45"/>
-      <c r="F50" s="49"/>
-      <c r="G50" s="45"/>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="45"/>
+      <c r="C50" s="56"/>
+      <c r="D50" s="56"/>
+      <c r="E50" s="56"/>
+      <c r="F50" s="59"/>
+      <c r="G50" s="56"/>
+      <c r="H50" s="56"/>
+      <c r="I50" s="56"/>
+      <c r="J50" s="56"/>
       <c r="K50" s="22"/>
       <c r="L50" s="22"/>
       <c r="M50" s="22"/>
       <c r="N50" s="23"/>
       <c r="O50" s="22"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" s="51"/>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A51" s="54"/>
       <c r="B51" s="31">
         <v>50</v>
       </c>
-      <c r="C51" s="45"/>
-      <c r="D51" s="45"/>
-      <c r="E51" s="45"/>
-      <c r="F51" s="49"/>
-      <c r="G51" s="45"/>
-      <c r="H51" s="45"/>
-      <c r="I51" s="45"/>
-      <c r="J51" s="45"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="59"/>
+      <c r="G51" s="56"/>
+      <c r="H51" s="56"/>
+      <c r="I51" s="56"/>
+      <c r="J51" s="56"/>
       <c r="K51" s="22"/>
       <c r="L51" s="22"/>
       <c r="M51" s="22"/>
       <c r="N51" s="23"/>
       <c r="O51" s="22"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="51"/>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A52" s="54"/>
       <c r="B52" s="31">
         <v>100</v>
       </c>
-      <c r="C52" s="45"/>
-      <c r="D52" s="45"/>
-      <c r="E52" s="45"/>
-      <c r="F52" s="49"/>
-      <c r="G52" s="45"/>
-      <c r="H52" s="45"/>
-      <c r="I52" s="45"/>
-      <c r="J52" s="45"/>
+      <c r="C52" s="56"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="56"/>
+      <c r="F52" s="59"/>
+      <c r="G52" s="56"/>
+      <c r="H52" s="56"/>
+      <c r="I52" s="56"/>
+      <c r="J52" s="56"/>
       <c r="K52" s="30"/>
       <c r="L52" s="30"/>
       <c r="M52" s="22"/>
       <c r="N52" s="23"/>
       <c r="O52" s="30"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" s="50" t="s">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A53" s="53" t="s">
         <v>15</v>
       </c>
       <c r="B53" s="9">
         <v>1</v>
       </c>
-      <c r="C53" s="45"/>
-      <c r="D53" s="45"/>
-      <c r="E53" s="45"/>
-      <c r="F53" s="49"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="45"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="45"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="59"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="56"/>
+      <c r="I53" s="56"/>
+      <c r="J53" s="56"/>
       <c r="K53" s="14" t="e">
         <f>AVERAGE(DataExp1.1!#REF!)</f>
         <v>#REF!</v>
@@ -5137,19 +5317,19 @@
         <v>12.858536243438699</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" s="50"/>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A54" s="53"/>
       <c r="B54" s="9">
         <v>3</v>
       </c>
-      <c r="C54" s="45"/>
-      <c r="D54" s="45"/>
-      <c r="E54" s="45"/>
-      <c r="F54" s="49"/>
-      <c r="G54" s="45"/>
-      <c r="H54" s="45"/>
-      <c r="I54" s="45"/>
-      <c r="J54" s="45"/>
+      <c r="C54" s="56"/>
+      <c r="D54" s="56"/>
+      <c r="E54" s="56"/>
+      <c r="F54" s="59"/>
+      <c r="G54" s="56"/>
+      <c r="H54" s="56"/>
+      <c r="I54" s="56"/>
+      <c r="J54" s="56"/>
       <c r="K54" s="14" t="e">
         <f>AVERAGE(DataExp1.1!#REF!)</f>
         <v>#REF!</v>
@@ -5168,19 +5348,19 @@
         <v>12.8858025074005</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="50"/>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A55" s="53"/>
       <c r="B55" s="9">
         <v>5</v>
       </c>
-      <c r="C55" s="45"/>
-      <c r="D55" s="45"/>
-      <c r="E55" s="45"/>
-      <c r="F55" s="49"/>
-      <c r="G55" s="45"/>
-      <c r="H55" s="45"/>
-      <c r="I55" s="45"/>
-      <c r="J55" s="45"/>
+      <c r="C55" s="56"/>
+      <c r="D55" s="56"/>
+      <c r="E55" s="56"/>
+      <c r="F55" s="59"/>
+      <c r="G55" s="56"/>
+      <c r="H55" s="56"/>
+      <c r="I55" s="56"/>
+      <c r="J55" s="56"/>
       <c r="K55" s="14" t="e">
         <f>AVERAGE(DataExp1.1!#REF!)</f>
         <v>#REF!</v>
@@ -5199,19 +5379,19 @@
         <v>13.6702349185943</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="50"/>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A56" s="53"/>
       <c r="B56" s="9">
         <v>10</v>
       </c>
-      <c r="C56" s="45"/>
-      <c r="D56" s="45"/>
-      <c r="E56" s="45"/>
-      <c r="F56" s="49"/>
-      <c r="G56" s="45"/>
-      <c r="H56" s="45"/>
-      <c r="I56" s="45"/>
-      <c r="J56" s="45"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="56"/>
+      <c r="E56" s="56"/>
+      <c r="F56" s="59"/>
+      <c r="G56" s="56"/>
+      <c r="H56" s="56"/>
+      <c r="I56" s="56"/>
+      <c r="J56" s="56"/>
       <c r="K56" s="14" t="e">
         <f>AVERAGE(DataExp1.1!#REF!)</f>
         <v>#REF!</v>
@@ -5230,57 +5410,57 @@
         <v>35.664546728134098</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="50"/>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A57" s="53"/>
       <c r="B57" s="9">
         <v>20</v>
       </c>
-      <c r="C57" s="45"/>
-      <c r="D57" s="45"/>
-      <c r="E57" s="45"/>
-      <c r="F57" s="49"/>
-      <c r="G57" s="45"/>
-      <c r="H57" s="45"/>
-      <c r="I57" s="45"/>
-      <c r="J57" s="45"/>
+      <c r="C57" s="56"/>
+      <c r="D57" s="56"/>
+      <c r="E57" s="56"/>
+      <c r="F57" s="59"/>
+      <c r="G57" s="56"/>
+      <c r="H57" s="56"/>
+      <c r="I57" s="56"/>
+      <c r="J57" s="56"/>
       <c r="K57" s="14"/>
       <c r="L57" s="14"/>
       <c r="M57" s="14"/>
       <c r="N57" s="19"/>
       <c r="O57" s="14"/>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="50"/>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A58" s="53"/>
       <c r="B58" s="9">
         <v>50</v>
       </c>
-      <c r="C58" s="45"/>
-      <c r="D58" s="45"/>
-      <c r="E58" s="45"/>
-      <c r="F58" s="49"/>
-      <c r="G58" s="45"/>
-      <c r="H58" s="45"/>
-      <c r="I58" s="45"/>
-      <c r="J58" s="45"/>
+      <c r="C58" s="56"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="56"/>
+      <c r="F58" s="59"/>
+      <c r="G58" s="56"/>
+      <c r="H58" s="56"/>
+      <c r="I58" s="56"/>
+      <c r="J58" s="56"/>
       <c r="K58" s="14"/>
       <c r="L58" s="14"/>
       <c r="M58" s="14"/>
       <c r="N58" s="19"/>
       <c r="O58" s="14"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="50"/>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A59" s="53"/>
       <c r="B59" s="9">
         <v>100</v>
       </c>
-      <c r="C59" s="45"/>
-      <c r="D59" s="45"/>
-      <c r="E59" s="45"/>
-      <c r="F59" s="47"/>
-      <c r="G59" s="45"/>
-      <c r="H59" s="45"/>
-      <c r="I59" s="45"/>
-      <c r="J59" s="45"/>
+      <c r="C59" s="56"/>
+      <c r="D59" s="56"/>
+      <c r="E59" s="56"/>
+      <c r="F59" s="55"/>
+      <c r="G59" s="56"/>
+      <c r="H59" s="56"/>
+      <c r="I59" s="56"/>
+      <c r="J59" s="56"/>
       <c r="K59" s="9"/>
       <c r="L59" s="9"/>
       <c r="M59" s="14"/>
@@ -5289,6 +5469,17 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="C4:C31"/>
+    <mergeCell ref="D4:D31"/>
+    <mergeCell ref="E4:E31"/>
+    <mergeCell ref="G4:G31"/>
+    <mergeCell ref="H4:H31"/>
+    <mergeCell ref="F4:F31"/>
     <mergeCell ref="A39:A45"/>
     <mergeCell ref="A46:A52"/>
     <mergeCell ref="A53:A59"/>
@@ -5303,17 +5494,6 @@
     <mergeCell ref="I32:I59"/>
     <mergeCell ref="J32:J59"/>
     <mergeCell ref="F32:F59"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="C4:C31"/>
-    <mergeCell ref="D4:D31"/>
-    <mergeCell ref="E4:E31"/>
-    <mergeCell ref="G4:G31"/>
-    <mergeCell ref="H4:H31"/>
-    <mergeCell ref="F4:F31"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5324,74 +5504,74 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0591575D-E9A4-466E-9459-9B52AEDB3DA6}">
   <dimension ref="B1:V55"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B1" s="32" t="s">
+    <row r="1" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B1" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
       <c r="M1" s="21"/>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B2" s="33" t="s">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="33" t="s">
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="34"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="36" t="s">
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="37"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="39" t="s">
+      <c r="I2" s="48"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39" t="s">
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39" t="s">
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39" t="s">
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="U2" s="39"/>
-      <c r="V2" s="39"/>
-    </row>
-    <row r="3" spans="2:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+    </row>
+    <row r="3" spans="2:22" ht="48" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
@@ -5456,7 +5636,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B4" s="4">
         <v>1422.6486110266001</v>
       </c>
@@ -5509,7 +5689,7 @@
       <c r="U4" s="5"/>
       <c r="V4" s="5"/>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B5" s="4">
         <v>1294.61056839975</v>
       </c>
@@ -5562,7 +5742,7 @@
       <c r="U5" s="5"/>
       <c r="V5" s="5"/>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B6" s="4">
         <v>1289.0184630184999</v>
       </c>
@@ -5615,7 +5795,7 @@
       <c r="U6" s="5"/>
       <c r="V6" s="5"/>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B7" s="4">
         <v>1296.2356591640801</v>
       </c>
@@ -5668,7 +5848,7 @@
       <c r="U7" s="5"/>
       <c r="V7" s="5"/>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B8" s="4">
         <v>1289.0184630184999</v>
       </c>
@@ -5721,7 +5901,7 @@
       <c r="U8" s="5"/>
       <c r="V8" s="5"/>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -5744,7 +5924,7 @@
       <c r="U9" s="5"/>
       <c r="V9" s="5"/>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -5767,7 +5947,7 @@
       <c r="U10" s="5"/>
       <c r="V10" s="5"/>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -5790,7 +5970,7 @@
       <c r="U11" s="5"/>
       <c r="V11" s="5"/>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -5813,7 +5993,7 @@
       <c r="U12" s="5"/>
       <c r="V12" s="5"/>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -5836,65 +6016,65 @@
       <c r="U13" s="5"/>
       <c r="V13" s="5"/>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B15" s="32" t="s">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B15" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="66"/>
       <c r="M15" s="21"/>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B16" s="33" t="s">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B16" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="34"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="33" t="s">
+      <c r="C16" s="42"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="36" t="s">
+      <c r="F16" s="42"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="I16" s="37"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="39" t="s">
+      <c r="I16" s="48"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39" t="s">
+      <c r="L16" s="67"/>
+      <c r="M16" s="67"/>
+      <c r="N16" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="O16" s="39"/>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="39" t="s">
+      <c r="O16" s="67"/>
+      <c r="P16" s="67"/>
+      <c r="Q16" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="R16" s="39"/>
-      <c r="S16" s="39"/>
-      <c r="T16" s="39" t="s">
+      <c r="R16" s="67"/>
+      <c r="S16" s="67"/>
+      <c r="T16" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="U16" s="39"/>
-      <c r="V16" s="39"/>
-    </row>
-    <row r="17" spans="2:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="U16" s="67"/>
+      <c r="V16" s="67"/>
+    </row>
+    <row r="17" spans="2:22" ht="48" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>20</v>
       </c>
@@ -5959,7 +6139,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B18" s="4">
         <v>3148.1656097576601</v>
       </c>
@@ -6012,7 +6192,7 @@
       <c r="U18" s="5"/>
       <c r="V18" s="5"/>
     </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B19" s="4">
         <v>3136.4726416762201</v>
       </c>
@@ -6059,7 +6239,7 @@
       <c r="U19" s="5"/>
       <c r="V19" s="5"/>
     </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B20" s="4">
         <v>3223.9336295605399</v>
       </c>
@@ -6106,7 +6286,7 @@
       <c r="U20" s="5"/>
       <c r="V20" s="5"/>
     </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B21" s="4">
         <v>3176.5909950571599</v>
       </c>
@@ -6153,7 +6333,7 @@
       <c r="U21" s="5"/>
       <c r="V21" s="5"/>
     </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B22" s="4">
         <v>3205.8088725635798</v>
       </c>
@@ -6200,7 +6380,7 @@
       <c r="U22" s="5"/>
       <c r="V22" s="5"/>
     </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -6235,7 +6415,7 @@
       <c r="U23" s="5"/>
       <c r="V23" s="5"/>
     </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -6264,7 +6444,7 @@
       <c r="U24" s="5"/>
       <c r="V24" s="5"/>
     </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -6287,7 +6467,7 @@
       <c r="U25" s="5"/>
       <c r="V25" s="5"/>
     </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -6310,7 +6490,7 @@
       <c r="U26" s="5"/>
       <c r="V26" s="5"/>
     </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -6333,60 +6513,60 @@
       <c r="U27" s="5"/>
       <c r="V27" s="5"/>
     </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B29" s="32" t="s">
+    <row r="29" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B29" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
+      <c r="C29" s="66"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="66"/>
+      <c r="G29" s="66"/>
+      <c r="H29" s="66"/>
+      <c r="I29" s="66"/>
+      <c r="J29" s="66"/>
+      <c r="K29" s="66"/>
+      <c r="L29" s="66"/>
       <c r="M29" s="21"/>
     </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B30" s="33" t="s">
+    <row r="30" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B30" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="34"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="33" t="s">
+      <c r="C30" s="42"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="34"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="36" t="s">
+      <c r="F30" s="42"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="I30" s="37"/>
-      <c r="J30" s="38"/>
-      <c r="K30" s="39" t="s">
+      <c r="I30" s="48"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="L30" s="39"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39" t="s">
+      <c r="L30" s="67"/>
+      <c r="M30" s="67"/>
+      <c r="N30" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="O30" s="39"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="39" t="s">
+      <c r="O30" s="67"/>
+      <c r="P30" s="67"/>
+      <c r="Q30" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="R30" s="39"/>
-      <c r="S30" s="39"/>
-      <c r="T30" s="39" t="s">
+      <c r="R30" s="67"/>
+      <c r="S30" s="67"/>
+      <c r="T30" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="U30" s="39"/>
-      <c r="V30" s="39"/>
-    </row>
-    <row r="31" spans="2:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="U30" s="67"/>
+      <c r="V30" s="67"/>
+    </row>
+    <row r="31" spans="2:22" ht="48" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>20</v>
       </c>
@@ -6451,7 +6631,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B32" s="4">
         <v>345.21337319137598</v>
       </c>
@@ -6498,7 +6678,7 @@
       <c r="U32" s="5"/>
       <c r="V32" s="5"/>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B33" s="4">
         <v>345.14754238117803</v>
       </c>
@@ -6545,7 +6725,7 @@
       <c r="U33" s="5"/>
       <c r="V33" s="5"/>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B34" s="4">
         <v>345.21337319137598</v>
       </c>
@@ -6592,7 +6772,7 @@
       <c r="U34" s="5"/>
       <c r="V34" s="5"/>
     </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B35" s="4">
         <v>345.21337319137598</v>
       </c>
@@ -6639,7 +6819,7 @@
       <c r="U35" s="5"/>
       <c r="V35" s="5"/>
     </row>
-    <row r="36" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B36" s="4">
         <v>345.14754238117803</v>
       </c>
@@ -6686,7 +6866,7 @@
       <c r="U36" s="5"/>
       <c r="V36" s="5"/>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -6715,7 +6895,7 @@
       <c r="U37" s="5"/>
       <c r="V37" s="5"/>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -6744,7 +6924,7 @@
       <c r="U38" s="5"/>
       <c r="V38" s="5"/>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -6767,7 +6947,7 @@
       <c r="U39" s="5"/>
       <c r="V39" s="5"/>
     </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -6790,7 +6970,7 @@
       <c r="U40" s="5"/>
       <c r="V40" s="5"/>
     </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -6813,60 +6993,60 @@
       <c r="U41" s="5"/>
       <c r="V41" s="5"/>
     </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B43" s="32" t="s">
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B43" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="32"/>
-      <c r="L43" s="32"/>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="66"/>
+      <c r="K43" s="66"/>
+      <c r="L43" s="66"/>
       <c r="M43" s="21"/>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B44" s="33" t="s">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B44" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="34"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="33" t="s">
+      <c r="C44" s="42"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="F44" s="34"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="36" t="s">
+      <c r="F44" s="42"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="I44" s="37"/>
-      <c r="J44" s="38"/>
-      <c r="K44" s="39" t="s">
+      <c r="I44" s="48"/>
+      <c r="J44" s="49"/>
+      <c r="K44" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="L44" s="39"/>
-      <c r="M44" s="39"/>
-      <c r="N44" s="39" t="s">
+      <c r="L44" s="67"/>
+      <c r="M44" s="67"/>
+      <c r="N44" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="O44" s="39"/>
-      <c r="P44" s="39"/>
-      <c r="Q44" s="39" t="s">
+      <c r="O44" s="67"/>
+      <c r="P44" s="67"/>
+      <c r="Q44" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="R44" s="39"/>
-      <c r="S44" s="39"/>
-      <c r="T44" s="39" t="s">
+      <c r="R44" s="67"/>
+      <c r="S44" s="67"/>
+      <c r="T44" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="U44" s="39"/>
-      <c r="V44" s="39"/>
-    </row>
-    <row r="45" spans="2:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="U44" s="67"/>
+      <c r="V44" s="67"/>
+    </row>
+    <row r="45" spans="2:22" ht="48" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
         <v>20</v>
       </c>
@@ -6931,7 +7111,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B46" s="4">
         <v>1261.44296531498</v>
       </c>
@@ -6972,7 +7152,7 @@
       <c r="U46" s="5"/>
       <c r="V46" s="5"/>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B47" s="4">
         <v>1258.94720083937</v>
       </c>
@@ -7007,7 +7187,7 @@
       <c r="U47" s="5"/>
       <c r="V47" s="5"/>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B48" s="4">
         <v>1272.84100087765</v>
       </c>
@@ -7042,7 +7222,7 @@
       <c r="U48" s="5"/>
       <c r="V48" s="5"/>
     </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B49" s="4">
         <v>1262.32532809241</v>
       </c>
@@ -7077,7 +7257,7 @@
       <c r="U49" s="5"/>
       <c r="V49" s="5"/>
     </row>
-    <row r="50" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B50" s="4">
         <v>1257.69151891614</v>
       </c>
@@ -7112,7 +7292,7 @@
       <c r="U50" s="5"/>
       <c r="V50" s="5"/>
     </row>
-    <row r="51" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -7135,7 +7315,7 @@
       <c r="U51" s="5"/>
       <c r="V51" s="5"/>
     </row>
-    <row r="52" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
@@ -7158,7 +7338,7 @@
       <c r="U52" s="5"/>
       <c r="V52" s="5"/>
     </row>
-    <row r="53" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
@@ -7181,7 +7361,7 @@
       <c r="U53" s="5"/>
       <c r="V53" s="5"/>
     </row>
-    <row r="54" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
@@ -7204,7 +7384,7 @@
       <c r="U54" s="5"/>
       <c r="V54" s="5"/>
     </row>
-    <row r="55" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
@@ -7229,22 +7409,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="B15:L15"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="T16:V16"/>
     <mergeCell ref="B29:L29"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="T30:V30"/>
@@ -7261,6 +7425,22 @@
     <mergeCell ref="H30:J30"/>
     <mergeCell ref="K30:M30"/>
     <mergeCell ref="N30:P30"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7269,46 +7449,46 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CACBC33-D91B-42B9-AA21-9BA30A2BE58A}">
   <dimension ref="A1:Z31"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:26" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="42"/>
-      <c r="W1" s="42"/>
-      <c r="X1" s="42"/>
-      <c r="Y1" s="42"/>
-      <c r="Z1" s="42"/>
-    </row>
-    <row r="3" spans="1:26" ht="60" x14ac:dyDescent="0.25">
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="61"/>
+      <c r="V1" s="61"/>
+      <c r="W1" s="61"/>
+      <c r="X1" s="61"/>
+      <c r="Y1" s="61"/>
+      <c r="Z1" s="61"/>
+    </row>
+    <row r="3" spans="1:26" ht="64" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -7355,33 +7535,33 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A4" s="62" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="47">
+      <c r="D4" s="55">
         <v>1005</v>
       </c>
-      <c r="E4" s="47">
+      <c r="E4" s="55">
         <v>1005</v>
       </c>
-      <c r="F4" s="48"/>
-      <c r="G4" s="47">
+      <c r="F4" s="65"/>
+      <c r="G4" s="55">
         <v>8</v>
       </c>
-      <c r="H4" s="47">
+      <c r="H4" s="55">
         <v>8</v>
       </c>
-      <c r="I4" s="47">
+      <c r="I4" s="55">
         <v>128</v>
       </c>
-      <c r="J4" s="47">
+      <c r="J4" s="55">
         <v>128</v>
       </c>
       <c r="K4" s="5">
@@ -7400,19 +7580,19 @@
       </c>
       <c r="O4" s="14"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="44"/>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A5" s="63"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
       <c r="K5" s="5">
         <f>AVERAGE(DataExp1.2!E4:E13)</f>
         <v>553.53793602493806</v>
@@ -7429,19 +7609,19 @@
       </c>
       <c r="O5" s="14"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A6" s="63"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
       <c r="K6" s="5">
         <f>AVERAGE(DataExp1.2!H4:H13)</f>
         <v>433.9549506572348</v>
@@ -7458,19 +7638,19 @@
       </c>
       <c r="O6" s="14"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="44"/>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A7" s="63"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
       <c r="K7" s="5">
         <f>AVERAGE(DataExp1.2!K4:K13)</f>
         <v>10.838240342377034</v>
@@ -7487,19 +7667,19 @@
       </c>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A8" s="63"/>
       <c r="B8" s="6">
         <v>20</v>
       </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
       <c r="K8" s="5">
         <f>AVERAGE(DataExp1.2!N4:N13)</f>
         <v>7.8951699494837957</v>
@@ -7516,59 +7696,59 @@
       </c>
       <c r="O8" s="14"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="44"/>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A9" s="63"/>
       <c r="B9" s="6">
         <v>50</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
       <c r="N9" s="17"/>
       <c r="O9" s="14"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="44"/>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A10" s="63"/>
       <c r="B10" s="6">
         <v>100</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="17"/>
       <c r="O10" s="14"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="45" t="s">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A11" s="56" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="56"/>
       <c r="K11" s="4">
         <f>AVERAGE(DataExp1.2!B18:B27)</f>
         <v>3178.1943497230322</v>
@@ -7585,19 +7765,19 @@
       </c>
       <c r="O11" s="4"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="45"/>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A12" s="56"/>
       <c r="B12" s="3">
         <v>3</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="56"/>
       <c r="K12" s="4">
         <f>AVERAGE(DataExp1.2!E18:E27)</f>
         <v>75.685942333849169</v>
@@ -7614,19 +7794,19 @@
       </c>
       <c r="O12" s="4"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="45"/>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A13" s="56"/>
       <c r="B13" s="3">
         <v>5</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
       <c r="K13" s="4">
         <f>AVERAGE(DataExp1.2!H18:H27)</f>
         <v>75.545904528375146</v>
@@ -7643,19 +7823,19 @@
       </c>
       <c r="O13" s="4"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="45"/>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A14" s="56"/>
       <c r="B14" s="3">
         <v>10</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
       <c r="K14" s="4">
         <f>AVERAGE(DataExp1.2!K18:K27)</f>
         <v>95.698989447779951</v>
@@ -7672,19 +7852,19 @@
       </c>
       <c r="O14" s="4"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="45"/>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A15" s="56"/>
       <c r="B15" s="3">
         <v>20</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4">
@@ -7695,59 +7875,59 @@
       </c>
       <c r="O15" s="4"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="45"/>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A16" s="56"/>
       <c r="B16" s="3">
         <v>50</v>
       </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="18"/>
       <c r="O16" s="4"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="45"/>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17" s="56"/>
       <c r="B17" s="3">
         <v>100</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="56"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="18"/>
       <c r="O17" s="4"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="50" t="s">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18" s="53" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="9">
         <v>1</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
       <c r="K18" s="14">
         <f>AVERAGE(DataExp1.2!B32:B41)</f>
         <v>345.18704086729679</v>
@@ -7764,19 +7944,19 @@
       </c>
       <c r="O18" s="14"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="50"/>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A19" s="53"/>
       <c r="B19" s="9">
         <v>3</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="56"/>
       <c r="K19" s="14">
         <f>AVERAGE(DataExp1.2!E32:E41)</f>
         <v>38.921654436682005</v>
@@ -7793,116 +7973,116 @@
       </c>
       <c r="O19" s="14"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="50"/>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A20" s="53"/>
       <c r="B20" s="9">
         <v>5</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="56"/>
       <c r="K20" s="14"/>
       <c r="L20" s="14"/>
       <c r="M20" s="14"/>
       <c r="N20" s="19"/>
       <c r="O20" s="14"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="50"/>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21" s="53"/>
       <c r="B21" s="9">
         <v>10</v>
       </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
       <c r="K21" s="14"/>
       <c r="L21" s="14"/>
       <c r="M21" s="14"/>
       <c r="N21" s="19"/>
       <c r="O21" s="14"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="50"/>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22" s="53"/>
       <c r="B22" s="9">
         <v>20</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
       <c r="K22" s="14"/>
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
       <c r="N22" s="19"/>
       <c r="O22" s="14"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="50"/>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23" s="53"/>
       <c r="B23" s="9">
         <v>50</v>
       </c>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="56"/>
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
       <c r="N23" s="19"/>
       <c r="O23" s="14"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="50"/>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A24" s="53"/>
       <c r="B24" s="9">
         <v>100</v>
       </c>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="56"/>
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
       <c r="N24" s="19"/>
       <c r="O24" s="14"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="45" t="s">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A25" s="56" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="3">
         <v>1</v>
       </c>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="56"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4">
@@ -7913,19 +8093,19 @@
       </c>
       <c r="O25" s="4"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="45"/>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A26" s="56"/>
       <c r="B26" s="3">
         <v>3</v>
       </c>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="56"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4">
@@ -7936,95 +8116,95 @@
       </c>
       <c r="O26" s="4"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="45"/>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A27" s="56"/>
       <c r="B27" s="3">
         <v>5</v>
       </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="45"/>
-      <c r="J27" s="45"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="56"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
       <c r="N27" s="18"/>
       <c r="O27" s="4"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="45"/>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28" s="56"/>
       <c r="B28" s="3">
         <v>10</v>
       </c>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="45"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
       <c r="N28" s="18"/>
       <c r="O28" s="4"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="45"/>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29" s="56"/>
       <c r="B29" s="3">
         <v>20</v>
       </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="49"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="45"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="56"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
       <c r="N29" s="18"/>
       <c r="O29" s="4"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="45"/>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A30" s="56"/>
       <c r="B30" s="3">
         <v>50</v>
       </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="56"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
       <c r="N30" s="18"/>
       <c r="O30" s="4"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="45"/>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A31" s="56"/>
       <c r="B31" s="3">
         <v>100</v>
       </c>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="45"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="56"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="56"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -8054,35 +8234,35 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E02A095-16D7-4FBB-B206-8C2A6F2CFB60}">
   <dimension ref="B1:BM16"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:65" x14ac:dyDescent="0.25">
-      <c r="B1" s="32" t="s">
+    <row r="1" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="B1" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
       <c r="M1" s="21"/>
       <c r="R1" s="40" t="s">
         <v>27</v>
@@ -8108,8 +8288,8 @@
       <c r="AO1" s="40"/>
       <c r="AP1" s="40"/>
       <c r="AQ1" s="40"/>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="32"/>
+      <c r="AR1" s="66"/>
+      <c r="AS1" s="66"/>
       <c r="AT1" s="21"/>
       <c r="AY1" s="40" t="s">
         <v>15</v>
@@ -8122,114 +8302,114 @@
       <c r="BE1" s="40"/>
       <c r="BF1" s="40"/>
       <c r="BG1" s="40"/>
-      <c r="BH1" s="32"/>
-      <c r="BI1" s="32"/>
-    </row>
-    <row r="2" spans="2:65" x14ac:dyDescent="0.25">
-      <c r="B2" s="33" t="s">
+      <c r="BH1" s="66"/>
+      <c r="BI1" s="66"/>
+    </row>
+    <row r="2" spans="2:65" x14ac:dyDescent="0.2">
+      <c r="B2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="33" t="s">
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="34"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="36" t="s">
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="37"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="39" t="s">
+      <c r="I2" s="48"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39" t="s">
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="R2" s="33" t="s">
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="R2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="34"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="33" t="s">
+      <c r="S2" s="42"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="34"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="36" t="s">
+      <c r="V2" s="42"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="39" t="s">
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="AB2" s="39"/>
-      <c r="AC2" s="39"/>
-      <c r="AD2" s="39" t="s">
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="AE2" s="39"/>
-      <c r="AF2" s="39"/>
+      <c r="AE2" s="67"/>
+      <c r="AF2" s="67"/>
       <c r="AG2" s="21"/>
       <c r="AH2" s="21"/>
-      <c r="AI2" s="33" t="s">
+      <c r="AI2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="AJ2" s="34"/>
-      <c r="AK2" s="35"/>
-      <c r="AL2" s="33" t="s">
+      <c r="AJ2" s="42"/>
+      <c r="AK2" s="43"/>
+      <c r="AL2" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="AM2" s="34"/>
-      <c r="AN2" s="35"/>
-      <c r="AO2" s="36" t="s">
+      <c r="AM2" s="42"/>
+      <c r="AN2" s="43"/>
+      <c r="AO2" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="AP2" s="37"/>
-      <c r="AQ2" s="38"/>
-      <c r="AR2" s="39" t="s">
+      <c r="AP2" s="48"/>
+      <c r="AQ2" s="49"/>
+      <c r="AR2" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="AS2" s="39"/>
-      <c r="AT2" s="39"/>
-      <c r="AU2" s="39" t="s">
+      <c r="AS2" s="67"/>
+      <c r="AT2" s="67"/>
+      <c r="AU2" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="AV2" s="39"/>
-      <c r="AW2" s="39"/>
-      <c r="AY2" s="33" t="s">
+      <c r="AV2" s="67"/>
+      <c r="AW2" s="67"/>
+      <c r="AY2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="AZ2" s="34"/>
-      <c r="BA2" s="35"/>
-      <c r="BB2" s="33" t="s">
+      <c r="AZ2" s="42"/>
+      <c r="BA2" s="43"/>
+      <c r="BB2" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="BC2" s="34"/>
-      <c r="BD2" s="35"/>
-      <c r="BE2" s="36" t="s">
+      <c r="BC2" s="42"/>
+      <c r="BD2" s="43"/>
+      <c r="BE2" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="BF2" s="37"/>
-      <c r="BG2" s="38"/>
-      <c r="BH2" s="39" t="s">
+      <c r="BF2" s="48"/>
+      <c r="BG2" s="49"/>
+      <c r="BH2" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="BI2" s="39"/>
-      <c r="BJ2" s="39"/>
-      <c r="BK2" s="39" t="s">
+      <c r="BI2" s="67"/>
+      <c r="BJ2" s="67"/>
+      <c r="BK2" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="BL2" s="39"/>
-      <c r="BM2" s="39"/>
-    </row>
-    <row r="3" spans="2:65" ht="45" x14ac:dyDescent="0.25">
+      <c r="BL2" s="67"/>
+      <c r="BM2" s="67"/>
+    </row>
+    <row r="3" spans="2:65" ht="48" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
@@ -8413,7 +8593,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="2:65" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B4" s="4">
         <v>12.3683837862365</v>
       </c>
@@ -8595,7 +8775,7 @@
         <v>0.15600681304931599</v>
       </c>
     </row>
-    <row r="5" spans="2:65" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B5" s="4">
         <v>13.2415117006289</v>
       </c>
@@ -8777,7 +8957,7 @@
         <v>0.15285587310790999</v>
       </c>
     </row>
-    <row r="6" spans="2:65" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B6" s="4">
         <v>12.7295497384731</v>
       </c>
@@ -8959,7 +9139,7 @@
         <v>0.15261030197143499</v>
       </c>
     </row>
-    <row r="7" spans="2:65" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B7" s="4">
         <v>12.5389865562673</v>
       </c>
@@ -9141,7 +9321,7 @@
         <v>0.155811786651611</v>
       </c>
     </row>
-    <row r="8" spans="2:65" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B8" s="4">
         <v>13.397439157339299</v>
       </c>
@@ -9323,48 +9503,56 @@
         <v>0.15216517448425201</v>
       </c>
     </row>
-    <row r="9" spans="2:65" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
     </row>
-    <row r="10" spans="2:65" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="2:65" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
     </row>
-    <row r="12" spans="2:65" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
     </row>
-    <row r="13" spans="2:65" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
     </row>
-    <row r="14" spans="2:65" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
     </row>
-    <row r="15" spans="2:65" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
     </row>
-    <row r="16" spans="2:65" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:65" x14ac:dyDescent="0.2">
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BH2:BJ2"/>
     <mergeCell ref="AY1:BI1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
@@ -9381,14 +9569,6 @@
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="AI2:AK2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BH2:BJ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9397,37 +9577,37 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E80E6C9-07DF-4341-ACF2-5E614276889D}">
   <dimension ref="A1:AA23"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D1" s="41" t="s">
+    <row r="1" spans="1:27" ht="57.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D1" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="42"/>
-      <c r="W1" s="42"/>
-      <c r="X1" s="42"/>
-      <c r="Y1" s="42"/>
-      <c r="Z1" s="42"/>
-      <c r="AA1" s="42"/>
-    </row>
-    <row r="3" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="61"/>
+      <c r="V1" s="61"/>
+      <c r="W1" s="61"/>
+      <c r="X1" s="61"/>
+      <c r="Y1" s="61"/>
+      <c r="Z1" s="61"/>
+      <c r="AA1" s="61"/>
+    </row>
+    <row r="3" spans="1:27" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -9468,33 +9648,33 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="44" t="s">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A4" s="63" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="6">
         <v>1</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="45">
+      <c r="D4" s="56">
         <v>66</v>
       </c>
-      <c r="E4" s="45">
+      <c r="E4" s="56">
         <v>66</v>
       </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="45">
+      <c r="F4" s="69"/>
+      <c r="G4" s="56">
         <v>1</v>
       </c>
-      <c r="H4" s="45">
+      <c r="H4" s="56">
         <v>1</v>
       </c>
-      <c r="I4" s="45">
+      <c r="I4" s="56">
         <v>66</v>
       </c>
-      <c r="J4" s="45">
+      <c r="J4" s="56">
         <v>66</v>
       </c>
       <c r="K4" s="5">
@@ -9510,19 +9690,19 @@
         <v>0.19700231552123962</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="44"/>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A5" s="63"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
       <c r="K5" s="5">
         <f>AVERAGE(DataExp2!E4:E8)</f>
         <v>6.7273250931611468</v>
@@ -9536,19 +9716,19 @@
         <v>0.2107465267181392</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A6" s="63"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
       <c r="K6" s="5">
         <f>AVERAGE(DataExp2!H4:H8)</f>
         <v>2.8757780700062598</v>
@@ -9562,19 +9742,19 @@
         <v>0.15662469863891562</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="44"/>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A7" s="63"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
       <c r="K7" s="5">
         <f>AVERAGE(DataExp2!K4:K8)</f>
         <v>2.5245777936554679</v>
@@ -9588,19 +9768,19 @@
         <v>0.1676195144653318</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A8" s="63"/>
       <c r="B8" s="6">
         <v>1000</v>
       </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
       <c r="K8" s="5">
         <f>AVERAGE(DataExp2!N4:N8)</f>
         <v>2.6210229749569218</v>
@@ -9614,21 +9794,21 @@
         <v>0.17717275619506781</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="45" t="s">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A9" s="56" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
       <c r="K9" s="4">
         <f>AVERAGE(DataExp2!R4:R8)</f>
         <v>25.122901453825698</v>
@@ -9642,19 +9822,19 @@
         <v>0.19828023910522422</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="45"/>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A10" s="56"/>
       <c r="B10" s="3">
         <v>3</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
       <c r="K10" s="4">
         <f>AVERAGE(DataExp2!U4:U8)</f>
         <v>1.1978887514698182</v>
@@ -9668,19 +9848,19 @@
         <v>0.15119447708129818</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="45"/>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A11" s="56"/>
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="56"/>
       <c r="K11" s="4">
         <f>AVERAGE(DataExp2!X4:X8)</f>
         <v>2.7398509444970598</v>
@@ -9694,19 +9874,19 @@
         <v>0.15588712692260681</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="45"/>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A12" s="56"/>
       <c r="B12" s="3">
         <v>10</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="56"/>
       <c r="K12" s="4">
         <f>AVERAGE(DataExp2!AA4:AA8)</f>
         <v>2.3904188069590249</v>
@@ -9720,19 +9900,19 @@
         <v>0.1640295982360836</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="45"/>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A13" s="56"/>
       <c r="B13" s="3">
         <v>1000</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
       <c r="K13" s="4">
         <f>AVERAGE(DataExp2!AD4:AD8)</f>
         <v>3.118010443300594</v>
@@ -9746,21 +9926,21 @@
         <v>0.1643743038177484</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="44" t="s">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A14" s="63" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="6">
         <v>1</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="70"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
       <c r="K14" s="14">
         <f>AVERAGE(DataExp2!AI4:AI8)</f>
         <v>2.018042671934988</v>
@@ -9774,19 +9954,19 @@
         <v>0.1502608299255368</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="44"/>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A15" s="63"/>
       <c r="B15" s="6">
         <v>3</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
       <c r="K15" s="14">
         <f>AVERAGE(DataExp2!AL4:AL8)</f>
         <v>2.9999089103706797</v>
@@ -9800,19 +9980,19 @@
         <v>0.15916876792907658</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="44"/>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A16" s="63"/>
       <c r="B16" s="6">
         <v>5</v>
       </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
       <c r="K16" s="14">
         <f>AVERAGE(DataExp2!AO4:AO8)</f>
         <v>3.0887572192386399</v>
@@ -9826,19 +10006,19 @@
         <v>0.18022336959838842</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="44"/>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="63"/>
       <c r="B17" s="6">
         <v>10</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="56"/>
       <c r="K17" s="14">
         <f>AVERAGE(DataExp2!AR4:AR8)</f>
         <v>3.0147786188702144</v>
@@ -9852,19 +10032,19 @@
         <v>0.1679047107696528</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="44"/>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="63"/>
       <c r="B18" s="6">
         <v>1000</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
       <c r="K18" s="14">
         <f>AVERAGE(DataExp2!AU4:AU8)</f>
         <v>3.1022309678357018</v>
@@ -9878,21 +10058,21 @@
         <v>0.1547142028808588</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="45" t="s">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="56" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="3">
         <v>1</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="56"/>
       <c r="K19" s="4">
         <f>AVERAGE(DataExp2!AY4:AY8)</f>
         <v>23.17734266838546</v>
@@ -9906,19 +10086,19 @@
         <v>0.19334774017333919</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="45"/>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="56"/>
       <c r="B20" s="3">
         <v>3</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="56"/>
       <c r="K20" s="4">
         <f>AVERAGE(DataExp2!BB4:BB8)</f>
         <v>2.7741290185543344</v>
@@ -9932,19 +10112,19 @@
         <v>0.19868965148925719</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="45"/>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="56"/>
       <c r="B21" s="3">
         <v>5</v>
       </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
       <c r="K21" s="4">
         <f>AVERAGE(DataExp2!BE4:BE8)</f>
         <v>2.776927957976338</v>
@@ -9958,19 +10138,19 @@
         <v>0.15434794425964279</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="53"/>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="58"/>
       <c r="B22" s="10">
         <v>10</v>
       </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="58"/>
       <c r="K22" s="29">
         <f>AVERAGE(DataExp2!BH4:BH8)</f>
         <v>2.6552692879772497</v>
@@ -9984,19 +10164,19 @@
         <v>0.1542748928070064</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="54"/>
+    <row r="23" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="68"/>
       <c r="B23" s="28">
         <v>1000</v>
       </c>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
       <c r="K23" s="27">
         <f>AVERAGE(DataExp2!BK4:BK8)</f>
         <v>2.6966735043782979</v>
@@ -10033,12 +10213,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{109AAA12-50B0-4DB2-B0E7-B06F76284A15}">
   <dimension ref="A2:L22"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -10076,33 +10256,33 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="72" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="6">
         <v>1</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="45">
+      <c r="D3" s="56">
         <v>66</v>
       </c>
-      <c r="E3" s="45">
+      <c r="E3" s="56">
         <v>66</v>
       </c>
-      <c r="F3" s="39"/>
-      <c r="G3" s="45">
+      <c r="F3" s="67"/>
+      <c r="G3" s="56">
         <v>1</v>
       </c>
-      <c r="H3" s="45">
+      <c r="H3" s="56">
         <v>1</v>
       </c>
-      <c r="I3" s="45">
+      <c r="I3" s="56">
         <v>66</v>
       </c>
-      <c r="J3" s="45">
+      <c r="J3" s="56">
         <v>66</v>
       </c>
       <c r="K3" s="9">
@@ -10112,19 +10292,19 @@
         <v>3.3054398403598002</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="59"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="73"/>
       <c r="B4" s="6">
         <v>3</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
       <c r="K4" s="14">
         <v>10.596633070539401</v>
       </c>
@@ -10132,19 +10312,19 @@
         <v>1.5955635877966901</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="59"/>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="73"/>
       <c r="B5" s="6">
         <v>5</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
       <c r="K5" s="14">
         <v>4.5624707313509596</v>
       </c>
@@ -10152,19 +10332,19 @@
         <v>0.80189414157007399</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="59"/>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="73"/>
       <c r="B6" s="6">
         <v>10</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
       <c r="K6" s="14">
         <v>0.610171518579538</v>
       </c>
@@ -10172,19 +10352,19 @@
         <v>0.18817509888984599</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="43"/>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="62"/>
       <c r="B7" s="6">
         <v>100</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
       <c r="K7" s="9">
         <v>0.56361848551125004</v>
       </c>
@@ -10192,21 +10372,21 @@
         <v>0.197282474192192</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="58" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
       </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
       <c r="K8" s="4">
         <v>51.3708858392826</v>
       </c>
@@ -10214,19 +10394,19 @@
         <v>6.6885950561924696</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="49"/>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="59"/>
       <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
       <c r="K9" s="4">
         <v>2.1067016984413098</v>
       </c>
@@ -10234,19 +10414,19 @@
         <v>0.40789971668138397</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="49"/>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="59"/>
       <c r="B10" s="3">
         <v>5</v>
       </c>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
       <c r="K10" s="4">
         <v>2.8064566058312099</v>
       </c>
@@ -10254,19 +10434,19 @@
         <v>0.67455402488281302</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="49"/>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="59"/>
       <c r="B11" s="3">
         <v>10</v>
       </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="56"/>
       <c r="K11" s="4">
         <v>1.8870454425238199</v>
       </c>
@@ -10274,19 +10454,19 @@
         <v>0.37616173059733798</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="47"/>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="55"/>
       <c r="B12" s="3">
         <v>100</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="56"/>
       <c r="K12" s="4">
         <v>1.6795645399372201</v>
       </c>
@@ -10294,21 +10474,21 @@
         <v>0.41984578161339797</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="58" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="72" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="6">
         <v>1</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
       <c r="K13" s="14">
         <v>1.97796965575553</v>
       </c>
@@ -10316,19 +10496,19 @@
         <v>0.37754673426285001</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="59"/>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="73"/>
       <c r="B14" s="6">
         <v>3</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
       <c r="K14" s="14">
         <v>3.1862607049915099</v>
       </c>
@@ -10336,19 +10516,19 @@
         <v>0.65565129784223597</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="59"/>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="73"/>
       <c r="B15" s="6">
         <v>5</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
       <c r="K15" s="14">
         <v>3.1662124268938201</v>
       </c>
@@ -10356,19 +10536,19 @@
         <v>0.65226013362701096</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="59"/>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="73"/>
       <c r="B16" s="6">
         <v>10</v>
       </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
-      <c r="J16" s="45"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
       <c r="K16" s="14">
         <v>3.0769912027266599</v>
       </c>
@@ -10376,19 +10556,19 @@
         <v>0.65226013362701096</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="43"/>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" s="62"/>
       <c r="B17" s="6">
         <v>100</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="56"/>
       <c r="K17" s="14">
         <v>3.1294599319079799</v>
       </c>
@@ -10396,21 +10576,21 @@
         <v>0.65226013362701096</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="45" t="s">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" s="56" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="3">
         <v>1</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="45"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
+      <c r="J18" s="56"/>
       <c r="K18">
         <v>34.454845100484</v>
       </c>
@@ -10418,19 +10598,19 @@
         <v>4.5813181927955497</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="45"/>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" s="56"/>
       <c r="B19" s="3">
         <v>3</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="56"/>
       <c r="K19" s="4">
         <v>1.9521931441214699</v>
       </c>
@@ -10438,19 +10618,19 @@
         <v>0.33857361093395399</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="45"/>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" s="56"/>
       <c r="B20" s="3">
         <v>5</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45"/>
-      <c r="J20" s="45"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="67"/>
+      <c r="G20" s="56"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="56"/>
+      <c r="J20" s="56"/>
       <c r="K20" s="3">
         <v>2.0043440401661101</v>
       </c>
@@ -10458,19 +10638,19 @@
         <v>0.34338396096988</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="53"/>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" s="58"/>
       <c r="B21" s="10">
         <v>10</v>
       </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="56"/>
       <c r="K21" s="3">
         <v>2.0041611367035599</v>
       </c>
@@ -10478,19 +10658,19 @@
         <v>2.0041611367035599</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="54"/>
+    <row r="22" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="68"/>
       <c r="B22" s="28">
         <v>100</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45"/>
-      <c r="J22" s="45"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="56"/>
       <c r="K22" s="3">
         <v>2.0126023888751998</v>
       </c>
@@ -10521,34 +10701,34 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B88CF955-8A08-4606-BED9-523AEA531233}">
   <dimension ref="B1:BC21"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:55" x14ac:dyDescent="0.25">
-      <c r="B1" s="32" t="s">
+    <row r="1" spans="2:55" x14ac:dyDescent="0.2">
+      <c r="B1" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
       <c r="M1" s="21"/>
       <c r="R1" s="40" t="s">
         <v>27</v>
@@ -10574,8 +10754,8 @@
       <c r="AK1" s="40"/>
       <c r="AL1" s="40"/>
       <c r="AM1" s="40"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
+      <c r="AN1" s="66"/>
+      <c r="AO1" s="66"/>
       <c r="AP1" s="21"/>
       <c r="AR1" s="40" t="s">
         <v>15</v>
@@ -10588,98 +10768,98 @@
       <c r="AX1" s="40"/>
       <c r="AY1" s="40"/>
       <c r="AZ1" s="40"/>
-      <c r="BA1" s="32"/>
-      <c r="BB1" s="32"/>
-    </row>
-    <row r="2" spans="2:55" x14ac:dyDescent="0.25">
-      <c r="B2" s="33" t="s">
+      <c r="BA1" s="66"/>
+      <c r="BB1" s="66"/>
+    </row>
+    <row r="2" spans="2:55" x14ac:dyDescent="0.2">
+      <c r="B2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="33" t="s">
+      <c r="C2" s="42"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="34"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="36" t="s">
+      <c r="F2" s="42"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="37"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="39" t="s">
+      <c r="I2" s="48"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39" t="s">
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="R2" s="33" t="s">
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="R2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="34"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="33" t="s">
+      <c r="S2" s="42"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="34"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="36" t="s">
+      <c r="V2" s="42"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="39" t="s">
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="AB2" s="39"/>
-      <c r="AC2" s="39"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
       <c r="AD2" s="21"/>
-      <c r="AE2" s="33" t="s">
+      <c r="AE2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="AF2" s="34"/>
-      <c r="AG2" s="35"/>
-      <c r="AH2" s="33" t="s">
+      <c r="AF2" s="42"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="AI2" s="34"/>
-      <c r="AJ2" s="35"/>
-      <c r="AK2" s="36" t="s">
+      <c r="AI2" s="42"/>
+      <c r="AJ2" s="43"/>
+      <c r="AK2" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="AL2" s="37"/>
-      <c r="AM2" s="38"/>
-      <c r="AN2" s="39" t="s">
+      <c r="AL2" s="48"/>
+      <c r="AM2" s="49"/>
+      <c r="AN2" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="AO2" s="39"/>
-      <c r="AP2" s="39"/>
-      <c r="AR2" s="33" t="s">
+      <c r="AO2" s="67"/>
+      <c r="AP2" s="67"/>
+      <c r="AR2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="AS2" s="34"/>
-      <c r="AT2" s="35"/>
-      <c r="AU2" s="33" t="s">
+      <c r="AS2" s="42"/>
+      <c r="AT2" s="43"/>
+      <c r="AU2" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="AV2" s="34"/>
-      <c r="AW2" s="35"/>
-      <c r="AX2" s="36" t="s">
+      <c r="AV2" s="42"/>
+      <c r="AW2" s="43"/>
+      <c r="AX2" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="AY2" s="37"/>
-      <c r="AZ2" s="38"/>
-      <c r="BA2" s="39" t="s">
+      <c r="AY2" s="48"/>
+      <c r="AZ2" s="49"/>
+      <c r="BA2" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="BB2" s="39"/>
-      <c r="BC2" s="39"/>
-    </row>
-    <row r="3" spans="2:55" ht="45" x14ac:dyDescent="0.25">
+      <c r="BB2" s="67"/>
+      <c r="BC2" s="67"/>
+    </row>
+    <row r="3" spans="2:55" ht="48" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
@@ -10835,7 +11015,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -10888,7 +11068,7 @@
       <c r="BB4" s="5"/>
       <c r="BC4" s="3"/>
     </row>
-    <row r="5" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -10941,7 +11121,7 @@
       <c r="BB5" s="5"/>
       <c r="BC5" s="3"/>
     </row>
-    <row r="6" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -10994,7 +11174,7 @@
       <c r="BB6" s="5"/>
       <c r="BC6" s="3"/>
     </row>
-    <row r="7" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -11047,7 +11227,7 @@
       <c r="BB7" s="5"/>
       <c r="BC7" s="3"/>
     </row>
-    <row r="8" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -11100,7 +11280,7 @@
       <c r="BB8" s="5"/>
       <c r="BC8" s="3"/>
     </row>
-    <row r="9" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -11153,7 +11333,7 @@
       <c r="BB9" s="5"/>
       <c r="BC9" s="3"/>
     </row>
-    <row r="10" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -11206,7 +11386,7 @@
       <c r="BB10" s="5"/>
       <c r="BC10" s="3"/>
     </row>
-    <row r="11" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -11259,7 +11439,7 @@
       <c r="BB11" s="5"/>
       <c r="BC11" s="3"/>
     </row>
-    <row r="12" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -11312,7 +11492,7 @@
       <c r="BB12" s="5"/>
       <c r="BC12" s="3"/>
     </row>
-    <row r="13" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -11365,48 +11545,53 @@
       <c r="BB13" s="5"/>
       <c r="BC13" s="3"/>
     </row>
-    <row r="14" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
     </row>
-    <row r="15" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
     </row>
-    <row r="16" spans="2:55" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:55" x14ac:dyDescent="0.2">
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="AN2:AP2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
     <mergeCell ref="AK2:AM2"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="R1:AB1"/>
@@ -11423,11 +11608,6 @@
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AE2:AG2"/>
     <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AN2:AP2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11659,20 +11839,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3025f3fe-b3fc-4756-a98b-aaebe57fb6e3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11695,6 +11875,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58C277AC-42DD-4338-BD2A-AF7ECB0689E8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -11709,12 +11897,4 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4150A870-1632-4D2D-B065-B299BA20F204}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/documents/ExperimentData.xlsx
+++ b/documents/ExperimentData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6A1B2BCFBBB34C0C/Documents/GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3954" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31F20057-FE73-4B81-96E6-8F30A3549847}"/>
+  <xr:revisionPtr revIDLastSave="3955" documentId="13_ncr:1_{4B21F078-1D86-7D42-975E-771B6217AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4A32372-C2A6-4290-8BDB-EB796B03D9C0}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11175" activeTab="2" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{3D929851-844D-4663-98AC-E560A272E6E8}"/>
   </bookViews>
   <sheets>
     <sheet name="DataExp1.0" sheetId="2" r:id="rId1"/>
@@ -497,24 +497,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -536,6 +518,66 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -545,6 +587,24 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -552,15 +612,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -581,62 +632,17 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -647,9 +653,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -659,10 +662,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1057,94 +1057,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="44"/>
-      <c r="AA1" s="44"/>
-      <c r="AB1" s="44"/>
-      <c r="AC1" s="44"/>
-      <c r="AD1" s="44"/>
-      <c r="AE1" s="44"/>
-      <c r="AF1" s="44"/>
-      <c r="AG1" s="44"/>
-      <c r="AH1" s="44"/>
-      <c r="AI1" s="44"/>
-      <c r="AJ1" s="44"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+      <c r="Z1" s="38"/>
+      <c r="AA1" s="38"/>
+      <c r="AB1" s="38"/>
+      <c r="AC1" s="38"/>
+      <c r="AD1" s="38"/>
+      <c r="AE1" s="38"/>
+      <c r="AF1" s="38"/>
+      <c r="AG1" s="38"/>
+      <c r="AH1" s="38"/>
+      <c r="AI1" s="38"/>
+      <c r="AJ1" s="38"/>
     </row>
     <row r="2" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48" t="s">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="38" t="s">
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="41" t="s">
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="38" t="s">
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W2" s="39"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="41" t="s">
+      <c r="W2" s="46"/>
+      <c r="X2" s="46"/>
+      <c r="Y2" s="46"/>
+      <c r="Z2" s="47"/>
+      <c r="AA2" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="AB2" s="42"/>
-      <c r="AC2" s="42"/>
-      <c r="AD2" s="42"/>
-      <c r="AE2" s="43"/>
-      <c r="AF2" s="38" t="s">
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="49"/>
+      <c r="AE2" s="50"/>
+      <c r="AF2" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="AG2" s="39"/>
-      <c r="AH2" s="39"/>
-      <c r="AI2" s="39"/>
-      <c r="AJ2" s="40"/>
+      <c r="AG2" s="46"/>
+      <c r="AH2" s="46"/>
+      <c r="AI2" s="46"/>
+      <c r="AJ2" s="47"/>
       <c r="AN2" s="27"/>
     </row>
     <row r="3" spans="2:40" ht="60" x14ac:dyDescent="0.25">
@@ -1791,94 +1791,94 @@
       </c>
     </row>
     <row r="10" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="44"/>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="44"/>
-      <c r="R10" s="44"/>
-      <c r="S10" s="44"/>
-      <c r="T10" s="44"/>
-      <c r="U10" s="44"/>
-      <c r="V10" s="44"/>
-      <c r="W10" s="44"/>
-      <c r="X10" s="44"/>
-      <c r="Y10" s="44"/>
-      <c r="Z10" s="44"/>
-      <c r="AA10" s="44"/>
-      <c r="AB10" s="44"/>
-      <c r="AC10" s="44"/>
-      <c r="AD10" s="44"/>
-      <c r="AE10" s="44"/>
-      <c r="AF10" s="44"/>
-      <c r="AG10" s="44"/>
-      <c r="AH10" s="44"/>
-      <c r="AI10" s="44"/>
-      <c r="AJ10" s="44"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="38"/>
+      <c r="Q10" s="38"/>
+      <c r="R10" s="38"/>
+      <c r="S10" s="38"/>
+      <c r="T10" s="38"/>
+      <c r="U10" s="38"/>
+      <c r="V10" s="38"/>
+      <c r="W10" s="38"/>
+      <c r="X10" s="38"/>
+      <c r="Y10" s="38"/>
+      <c r="Z10" s="38"/>
+      <c r="AA10" s="38"/>
+      <c r="AB10" s="38"/>
+      <c r="AC10" s="38"/>
+      <c r="AD10" s="38"/>
+      <c r="AE10" s="38"/>
+      <c r="AF10" s="38"/>
+      <c r="AG10" s="38"/>
+      <c r="AH10" s="38"/>
+      <c r="AI10" s="38"/>
+      <c r="AJ10" s="38"/>
     </row>
     <row r="11" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="48" t="s">
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="38" t="s">
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="41" t="s">
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="47"/>
+      <c r="Q11" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="R11" s="42"/>
-      <c r="S11" s="42"/>
-      <c r="T11" s="42"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="38" t="s">
+      <c r="R11" s="49"/>
+      <c r="S11" s="49"/>
+      <c r="T11" s="49"/>
+      <c r="U11" s="50"/>
+      <c r="V11" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W11" s="39"/>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="39"/>
-      <c r="Z11" s="40"/>
-      <c r="AA11" s="41" t="s">
+      <c r="W11" s="46"/>
+      <c r="X11" s="46"/>
+      <c r="Y11" s="46"/>
+      <c r="Z11" s="47"/>
+      <c r="AA11" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="AB11" s="42"/>
-      <c r="AC11" s="42"/>
-      <c r="AD11" s="42"/>
-      <c r="AE11" s="43"/>
-      <c r="AF11" s="38" t="s">
+      <c r="AB11" s="49"/>
+      <c r="AC11" s="49"/>
+      <c r="AD11" s="49"/>
+      <c r="AE11" s="50"/>
+      <c r="AF11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="AG11" s="39"/>
-      <c r="AH11" s="39"/>
-      <c r="AI11" s="39"/>
-      <c r="AJ11" s="40"/>
+      <c r="AG11" s="46"/>
+      <c r="AH11" s="46"/>
+      <c r="AI11" s="46"/>
+      <c r="AJ11" s="47"/>
     </row>
     <row r="12" spans="2:40" ht="60" x14ac:dyDescent="0.25">
       <c r="B12" s="13" t="s">
@@ -2523,94 +2523,94 @@
       </c>
     </row>
     <row r="19" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="44"/>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="44"/>
-      <c r="R19" s="44"/>
-      <c r="S19" s="44"/>
-      <c r="T19" s="44"/>
-      <c r="U19" s="44"/>
-      <c r="V19" s="44"/>
-      <c r="W19" s="44"/>
-      <c r="X19" s="44"/>
-      <c r="Y19" s="44"/>
-      <c r="Z19" s="44"/>
-      <c r="AA19" s="44"/>
-      <c r="AB19" s="44"/>
-      <c r="AC19" s="44"/>
-      <c r="AD19" s="44"/>
-      <c r="AE19" s="44"/>
-      <c r="AF19" s="44"/>
-      <c r="AG19" s="44"/>
-      <c r="AH19" s="44"/>
-      <c r="AI19" s="44"/>
-      <c r="AJ19" s="44"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="38"/>
+      <c r="T19" s="38"/>
+      <c r="U19" s="38"/>
+      <c r="V19" s="38"/>
+      <c r="W19" s="38"/>
+      <c r="X19" s="38"/>
+      <c r="Y19" s="38"/>
+      <c r="Z19" s="38"/>
+      <c r="AA19" s="38"/>
+      <c r="AB19" s="38"/>
+      <c r="AC19" s="38"/>
+      <c r="AD19" s="38"/>
+      <c r="AE19" s="38"/>
+      <c r="AF19" s="38"/>
+      <c r="AG19" s="38"/>
+      <c r="AH19" s="38"/>
+      <c r="AI19" s="38"/>
+      <c r="AJ19" s="38"/>
     </row>
     <row r="20" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="48" t="s">
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="38" t="s">
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="M20" s="39"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="39"/>
-      <c r="P20" s="40"/>
-      <c r="Q20" s="41" t="s">
+      <c r="M20" s="46"/>
+      <c r="N20" s="46"/>
+      <c r="O20" s="46"/>
+      <c r="P20" s="47"/>
+      <c r="Q20" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="R20" s="42"/>
-      <c r="S20" s="42"/>
-      <c r="T20" s="42"/>
-      <c r="U20" s="43"/>
-      <c r="V20" s="38" t="s">
+      <c r="R20" s="49"/>
+      <c r="S20" s="49"/>
+      <c r="T20" s="49"/>
+      <c r="U20" s="50"/>
+      <c r="V20" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W20" s="39"/>
-      <c r="X20" s="39"/>
-      <c r="Y20" s="39"/>
-      <c r="Z20" s="40"/>
-      <c r="AA20" s="41" t="s">
+      <c r="W20" s="46"/>
+      <c r="X20" s="46"/>
+      <c r="Y20" s="46"/>
+      <c r="Z20" s="47"/>
+      <c r="AA20" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="AB20" s="42"/>
-      <c r="AC20" s="42"/>
-      <c r="AD20" s="42"/>
-      <c r="AE20" s="43"/>
-      <c r="AF20" s="38" t="s">
+      <c r="AB20" s="49"/>
+      <c r="AC20" s="49"/>
+      <c r="AD20" s="49"/>
+      <c r="AE20" s="50"/>
+      <c r="AF20" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="AG20" s="39"/>
-      <c r="AH20" s="39"/>
-      <c r="AI20" s="39"/>
-      <c r="AJ20" s="40"/>
+      <c r="AG20" s="46"/>
+      <c r="AH20" s="46"/>
+      <c r="AI20" s="46"/>
+      <c r="AJ20" s="47"/>
     </row>
     <row r="21" spans="2:36" ht="60" x14ac:dyDescent="0.25">
       <c r="B21" s="13" t="s">
@@ -3255,94 +3255,94 @@
       </c>
     </row>
     <row r="28" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B28" s="44" t="s">
+      <c r="B28" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="44"/>
-      <c r="L28" s="44"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="44"/>
-      <c r="O28" s="44"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="44"/>
-      <c r="S28" s="44"/>
-      <c r="T28" s="44"/>
-      <c r="U28" s="44"/>
-      <c r="V28" s="44"/>
-      <c r="W28" s="44"/>
-      <c r="X28" s="44"/>
-      <c r="Y28" s="44"/>
-      <c r="Z28" s="44"/>
-      <c r="AA28" s="44"/>
-      <c r="AB28" s="44"/>
-      <c r="AC28" s="44"/>
-      <c r="AD28" s="44"/>
-      <c r="AE28" s="44"/>
-      <c r="AF28" s="44"/>
-      <c r="AG28" s="44"/>
-      <c r="AH28" s="44"/>
-      <c r="AI28" s="44"/>
-      <c r="AJ28" s="44"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="38"/>
+      <c r="M28" s="38"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="38"/>
+      <c r="Q28" s="38"/>
+      <c r="R28" s="38"/>
+      <c r="S28" s="38"/>
+      <c r="T28" s="38"/>
+      <c r="U28" s="38"/>
+      <c r="V28" s="38"/>
+      <c r="W28" s="38"/>
+      <c r="X28" s="38"/>
+      <c r="Y28" s="38"/>
+      <c r="Z28" s="38"/>
+      <c r="AA28" s="38"/>
+      <c r="AB28" s="38"/>
+      <c r="AC28" s="38"/>
+      <c r="AD28" s="38"/>
+      <c r="AE28" s="38"/>
+      <c r="AF28" s="38"/>
+      <c r="AG28" s="38"/>
+      <c r="AH28" s="38"/>
+      <c r="AI28" s="38"/>
+      <c r="AJ28" s="38"/>
     </row>
     <row r="29" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B29" s="45" t="s">
+      <c r="B29" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="46"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="48" t="s">
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="38" t="s">
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="41" t="s">
+      <c r="M29" s="46"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="46"/>
+      <c r="P29" s="47"/>
+      <c r="Q29" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="R29" s="42"/>
-      <c r="S29" s="42"/>
-      <c r="T29" s="42"/>
-      <c r="U29" s="43"/>
-      <c r="V29" s="38" t="s">
+      <c r="R29" s="49"/>
+      <c r="S29" s="49"/>
+      <c r="T29" s="49"/>
+      <c r="U29" s="50"/>
+      <c r="V29" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W29" s="39"/>
-      <c r="X29" s="39"/>
-      <c r="Y29" s="39"/>
-      <c r="Z29" s="40"/>
-      <c r="AA29" s="41" t="s">
+      <c r="W29" s="46"/>
+      <c r="X29" s="46"/>
+      <c r="Y29" s="46"/>
+      <c r="Z29" s="47"/>
+      <c r="AA29" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="AB29" s="42"/>
-      <c r="AC29" s="42"/>
-      <c r="AD29" s="42"/>
-      <c r="AE29" s="43"/>
-      <c r="AF29" s="38" t="s">
+      <c r="AB29" s="49"/>
+      <c r="AC29" s="49"/>
+      <c r="AD29" s="49"/>
+      <c r="AE29" s="50"/>
+      <c r="AF29" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="AG29" s="39"/>
-      <c r="AH29" s="39"/>
-      <c r="AI29" s="39"/>
-      <c r="AJ29" s="40"/>
+      <c r="AG29" s="46"/>
+      <c r="AH29" s="46"/>
+      <c r="AI29" s="46"/>
+      <c r="AJ29" s="47"/>
     </row>
     <row r="30" spans="2:36" ht="60" x14ac:dyDescent="0.25">
       <c r="B30" s="13" t="s">
@@ -3987,94 +3987,94 @@
       </c>
     </row>
     <row r="38" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B38" s="44" t="s">
+      <c r="B38" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="44"/>
-      <c r="D38" s="44"/>
-      <c r="E38" s="44"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="44"/>
-      <c r="H38" s="44"/>
-      <c r="I38" s="44"/>
-      <c r="J38" s="44"/>
-      <c r="K38" s="44"/>
-      <c r="L38" s="44"/>
-      <c r="M38" s="44"/>
-      <c r="N38" s="44"/>
-      <c r="O38" s="44"/>
-      <c r="P38" s="44"/>
-      <c r="Q38" s="44"/>
-      <c r="R38" s="44"/>
-      <c r="S38" s="44"/>
-      <c r="T38" s="44"/>
-      <c r="U38" s="44"/>
-      <c r="V38" s="44"/>
-      <c r="W38" s="44"/>
-      <c r="X38" s="44"/>
-      <c r="Y38" s="44"/>
-      <c r="Z38" s="44"/>
-      <c r="AA38" s="44"/>
-      <c r="AB38" s="44"/>
-      <c r="AC38" s="44"/>
-      <c r="AD38" s="44"/>
-      <c r="AE38" s="44"/>
-      <c r="AF38" s="44"/>
-      <c r="AG38" s="44"/>
-      <c r="AH38" s="44"/>
-      <c r="AI38" s="44"/>
-      <c r="AJ38" s="44"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="38"/>
+      <c r="J38" s="38"/>
+      <c r="K38" s="38"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="38"/>
+      <c r="O38" s="38"/>
+      <c r="P38" s="38"/>
+      <c r="Q38" s="38"/>
+      <c r="R38" s="38"/>
+      <c r="S38" s="38"/>
+      <c r="T38" s="38"/>
+      <c r="U38" s="38"/>
+      <c r="V38" s="38"/>
+      <c r="W38" s="38"/>
+      <c r="X38" s="38"/>
+      <c r="Y38" s="38"/>
+      <c r="Z38" s="38"/>
+      <c r="AA38" s="38"/>
+      <c r="AB38" s="38"/>
+      <c r="AC38" s="38"/>
+      <c r="AD38" s="38"/>
+      <c r="AE38" s="38"/>
+      <c r="AF38" s="38"/>
+      <c r="AG38" s="38"/>
+      <c r="AH38" s="38"/>
+      <c r="AI38" s="38"/>
+      <c r="AJ38" s="38"/>
     </row>
     <row r="39" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B39" s="45" t="s">
+      <c r="B39" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
-      <c r="E39" s="46"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="48" t="s">
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
-      <c r="K39" s="50"/>
-      <c r="L39" s="38" t="s">
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="44"/>
+      <c r="L39" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="M39" s="39"/>
-      <c r="N39" s="39"/>
-      <c r="O39" s="39"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="41" t="s">
+      <c r="M39" s="46"/>
+      <c r="N39" s="46"/>
+      <c r="O39" s="46"/>
+      <c r="P39" s="47"/>
+      <c r="Q39" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="R39" s="42"/>
-      <c r="S39" s="42"/>
-      <c r="T39" s="42"/>
-      <c r="U39" s="43"/>
-      <c r="V39" s="38" t="s">
+      <c r="R39" s="49"/>
+      <c r="S39" s="49"/>
+      <c r="T39" s="49"/>
+      <c r="U39" s="50"/>
+      <c r="V39" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W39" s="39"/>
-      <c r="X39" s="39"/>
-      <c r="Y39" s="39"/>
-      <c r="Z39" s="40"/>
-      <c r="AA39" s="41" t="s">
+      <c r="W39" s="46"/>
+      <c r="X39" s="46"/>
+      <c r="Y39" s="46"/>
+      <c r="Z39" s="47"/>
+      <c r="AA39" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
-      <c r="AD39" s="42"/>
-      <c r="AE39" s="43"/>
-      <c r="AF39" s="38" t="s">
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AE39" s="50"/>
+      <c r="AF39" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="AG39" s="39"/>
-      <c r="AH39" s="39"/>
-      <c r="AI39" s="39"/>
-      <c r="AJ39" s="40"/>
+      <c r="AG39" s="46"/>
+      <c r="AH39" s="46"/>
+      <c r="AI39" s="46"/>
+      <c r="AJ39" s="47"/>
     </row>
     <row r="40" spans="2:36" ht="60" x14ac:dyDescent="0.25">
       <c r="B40" s="13" t="s">
@@ -4719,94 +4719,94 @@
       </c>
     </row>
     <row r="47" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B47" s="44" t="s">
+      <c r="B47" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="C47" s="44"/>
-      <c r="D47" s="44"/>
-      <c r="E47" s="44"/>
-      <c r="F47" s="44"/>
-      <c r="G47" s="44"/>
-      <c r="H47" s="44"/>
-      <c r="I47" s="44"/>
-      <c r="J47" s="44"/>
-      <c r="K47" s="44"/>
-      <c r="L47" s="44"/>
-      <c r="M47" s="44"/>
-      <c r="N47" s="44"/>
-      <c r="O47" s="44"/>
-      <c r="P47" s="44"/>
-      <c r="Q47" s="44"/>
-      <c r="R47" s="44"/>
-      <c r="S47" s="44"/>
-      <c r="T47" s="44"/>
-      <c r="U47" s="44"/>
-      <c r="V47" s="44"/>
-      <c r="W47" s="44"/>
-      <c r="X47" s="44"/>
-      <c r="Y47" s="44"/>
-      <c r="Z47" s="44"/>
-      <c r="AA47" s="44"/>
-      <c r="AB47" s="44"/>
-      <c r="AC47" s="44"/>
-      <c r="AD47" s="44"/>
-      <c r="AE47" s="44"/>
-      <c r="AF47" s="44"/>
-      <c r="AG47" s="44"/>
-      <c r="AH47" s="44"/>
-      <c r="AI47" s="44"/>
-      <c r="AJ47" s="44"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="38"/>
+      <c r="I47" s="38"/>
+      <c r="J47" s="38"/>
+      <c r="K47" s="38"/>
+      <c r="L47" s="38"/>
+      <c r="M47" s="38"/>
+      <c r="N47" s="38"/>
+      <c r="O47" s="38"/>
+      <c r="P47" s="38"/>
+      <c r="Q47" s="38"/>
+      <c r="R47" s="38"/>
+      <c r="S47" s="38"/>
+      <c r="T47" s="38"/>
+      <c r="U47" s="38"/>
+      <c r="V47" s="38"/>
+      <c r="W47" s="38"/>
+      <c r="X47" s="38"/>
+      <c r="Y47" s="38"/>
+      <c r="Z47" s="38"/>
+      <c r="AA47" s="38"/>
+      <c r="AB47" s="38"/>
+      <c r="AC47" s="38"/>
+      <c r="AD47" s="38"/>
+      <c r="AE47" s="38"/>
+      <c r="AF47" s="38"/>
+      <c r="AG47" s="38"/>
+      <c r="AH47" s="38"/>
+      <c r="AI47" s="38"/>
+      <c r="AJ47" s="38"/>
     </row>
     <row r="48" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B48" s="45" t="s">
+      <c r="B48" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="46"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="48" t="s">
+      <c r="C48" s="40"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H48" s="49"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="49"/>
-      <c r="K48" s="50"/>
-      <c r="L48" s="38" t="s">
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="44"/>
+      <c r="L48" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="M48" s="39"/>
-      <c r="N48" s="39"/>
-      <c r="O48" s="39"/>
-      <c r="P48" s="40"/>
-      <c r="Q48" s="41" t="s">
+      <c r="M48" s="46"/>
+      <c r="N48" s="46"/>
+      <c r="O48" s="46"/>
+      <c r="P48" s="47"/>
+      <c r="Q48" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="R48" s="42"/>
-      <c r="S48" s="42"/>
-      <c r="T48" s="42"/>
-      <c r="U48" s="43"/>
-      <c r="V48" s="38" t="s">
+      <c r="R48" s="49"/>
+      <c r="S48" s="49"/>
+      <c r="T48" s="49"/>
+      <c r="U48" s="50"/>
+      <c r="V48" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W48" s="39"/>
-      <c r="X48" s="39"/>
-      <c r="Y48" s="39"/>
-      <c r="Z48" s="40"/>
-      <c r="AA48" s="41" t="s">
+      <c r="W48" s="46"/>
+      <c r="X48" s="46"/>
+      <c r="Y48" s="46"/>
+      <c r="Z48" s="47"/>
+      <c r="AA48" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AE48" s="43"/>
-      <c r="AF48" s="38" t="s">
+      <c r="AB48" s="49"/>
+      <c r="AC48" s="49"/>
+      <c r="AD48" s="49"/>
+      <c r="AE48" s="50"/>
+      <c r="AF48" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="AG48" s="39"/>
-      <c r="AH48" s="39"/>
-      <c r="AI48" s="39"/>
-      <c r="AJ48" s="40"/>
+      <c r="AG48" s="46"/>
+      <c r="AH48" s="46"/>
+      <c r="AI48" s="46"/>
+      <c r="AJ48" s="47"/>
     </row>
     <row r="49" spans="2:36" ht="60" x14ac:dyDescent="0.25">
       <c r="B49" s="13" t="s">
@@ -5451,94 +5451,94 @@
       </c>
     </row>
     <row r="56" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B56" s="44" t="s">
+      <c r="B56" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C56" s="44"/>
-      <c r="D56" s="44"/>
-      <c r="E56" s="44"/>
-      <c r="F56" s="44"/>
-      <c r="G56" s="44"/>
-      <c r="H56" s="44"/>
-      <c r="I56" s="44"/>
-      <c r="J56" s="44"/>
-      <c r="K56" s="44"/>
-      <c r="L56" s="44"/>
-      <c r="M56" s="44"/>
-      <c r="N56" s="44"/>
-      <c r="O56" s="44"/>
-      <c r="P56" s="44"/>
-      <c r="Q56" s="44"/>
-      <c r="R56" s="44"/>
-      <c r="S56" s="44"/>
-      <c r="T56" s="44"/>
-      <c r="U56" s="44"/>
-      <c r="V56" s="44"/>
-      <c r="W56" s="44"/>
-      <c r="X56" s="44"/>
-      <c r="Y56" s="44"/>
-      <c r="Z56" s="44"/>
-      <c r="AA56" s="44"/>
-      <c r="AB56" s="44"/>
-      <c r="AC56" s="44"/>
-      <c r="AD56" s="44"/>
-      <c r="AE56" s="44"/>
-      <c r="AF56" s="44"/>
-      <c r="AG56" s="44"/>
-      <c r="AH56" s="44"/>
-      <c r="AI56" s="44"/>
-      <c r="AJ56" s="44"/>
+      <c r="C56" s="38"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="38"/>
+      <c r="F56" s="38"/>
+      <c r="G56" s="38"/>
+      <c r="H56" s="38"/>
+      <c r="I56" s="38"/>
+      <c r="J56" s="38"/>
+      <c r="K56" s="38"/>
+      <c r="L56" s="38"/>
+      <c r="M56" s="38"/>
+      <c r="N56" s="38"/>
+      <c r="O56" s="38"/>
+      <c r="P56" s="38"/>
+      <c r="Q56" s="38"/>
+      <c r="R56" s="38"/>
+      <c r="S56" s="38"/>
+      <c r="T56" s="38"/>
+      <c r="U56" s="38"/>
+      <c r="V56" s="38"/>
+      <c r="W56" s="38"/>
+      <c r="X56" s="38"/>
+      <c r="Y56" s="38"/>
+      <c r="Z56" s="38"/>
+      <c r="AA56" s="38"/>
+      <c r="AB56" s="38"/>
+      <c r="AC56" s="38"/>
+      <c r="AD56" s="38"/>
+      <c r="AE56" s="38"/>
+      <c r="AF56" s="38"/>
+      <c r="AG56" s="38"/>
+      <c r="AH56" s="38"/>
+      <c r="AI56" s="38"/>
+      <c r="AJ56" s="38"/>
     </row>
     <row r="57" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B57" s="45" t="s">
+      <c r="B57" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="46"/>
-      <c r="D57" s="46"/>
-      <c r="E57" s="46"/>
-      <c r="F57" s="47"/>
-      <c r="G57" s="48" t="s">
+      <c r="C57" s="40"/>
+      <c r="D57" s="40"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="41"/>
+      <c r="G57" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H57" s="49"/>
-      <c r="I57" s="49"/>
-      <c r="J57" s="49"/>
-      <c r="K57" s="50"/>
-      <c r="L57" s="38" t="s">
+      <c r="H57" s="43"/>
+      <c r="I57" s="43"/>
+      <c r="J57" s="43"/>
+      <c r="K57" s="44"/>
+      <c r="L57" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="M57" s="39"/>
-      <c r="N57" s="39"/>
-      <c r="O57" s="39"/>
-      <c r="P57" s="40"/>
-      <c r="Q57" s="41" t="s">
+      <c r="M57" s="46"/>
+      <c r="N57" s="46"/>
+      <c r="O57" s="46"/>
+      <c r="P57" s="47"/>
+      <c r="Q57" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="R57" s="42"/>
-      <c r="S57" s="42"/>
-      <c r="T57" s="42"/>
-      <c r="U57" s="43"/>
-      <c r="V57" s="38" t="s">
+      <c r="R57" s="49"/>
+      <c r="S57" s="49"/>
+      <c r="T57" s="49"/>
+      <c r="U57" s="50"/>
+      <c r="V57" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W57" s="39"/>
-      <c r="X57" s="39"/>
-      <c r="Y57" s="39"/>
-      <c r="Z57" s="40"/>
-      <c r="AA57" s="41" t="s">
+      <c r="W57" s="46"/>
+      <c r="X57" s="46"/>
+      <c r="Y57" s="46"/>
+      <c r="Z57" s="47"/>
+      <c r="AA57" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="AB57" s="42"/>
-      <c r="AC57" s="42"/>
-      <c r="AD57" s="42"/>
-      <c r="AE57" s="43"/>
-      <c r="AF57" s="38" t="s">
+      <c r="AB57" s="49"/>
+      <c r="AC57" s="49"/>
+      <c r="AD57" s="49"/>
+      <c r="AE57" s="50"/>
+      <c r="AF57" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="AG57" s="39"/>
-      <c r="AH57" s="39"/>
-      <c r="AI57" s="39"/>
-      <c r="AJ57" s="40"/>
+      <c r="AG57" s="46"/>
+      <c r="AH57" s="46"/>
+      <c r="AI57" s="46"/>
+      <c r="AJ57" s="47"/>
     </row>
     <row r="58" spans="2:36" ht="60" x14ac:dyDescent="0.25">
       <c r="B58" s="13" t="s">
@@ -6183,94 +6183,94 @@
       </c>
     </row>
     <row r="65" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B65" s="44" t="s">
+      <c r="B65" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="C65" s="44"/>
-      <c r="D65" s="44"/>
-      <c r="E65" s="44"/>
-      <c r="F65" s="44"/>
-      <c r="G65" s="44"/>
-      <c r="H65" s="44"/>
-      <c r="I65" s="44"/>
-      <c r="J65" s="44"/>
-      <c r="K65" s="44"/>
-      <c r="L65" s="44"/>
-      <c r="M65" s="44"/>
-      <c r="N65" s="44"/>
-      <c r="O65" s="44"/>
-      <c r="P65" s="44"/>
-      <c r="Q65" s="44"/>
-      <c r="R65" s="44"/>
-      <c r="S65" s="44"/>
-      <c r="T65" s="44"/>
-      <c r="U65" s="44"/>
-      <c r="V65" s="44"/>
-      <c r="W65" s="44"/>
-      <c r="X65" s="44"/>
-      <c r="Y65" s="44"/>
-      <c r="Z65" s="44"/>
-      <c r="AA65" s="44"/>
-      <c r="AB65" s="44"/>
-      <c r="AC65" s="44"/>
-      <c r="AD65" s="44"/>
-      <c r="AE65" s="44"/>
-      <c r="AF65" s="44"/>
-      <c r="AG65" s="44"/>
-      <c r="AH65" s="44"/>
-      <c r="AI65" s="44"/>
-      <c r="AJ65" s="44"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="38"/>
+      <c r="E65" s="38"/>
+      <c r="F65" s="38"/>
+      <c r="G65" s="38"/>
+      <c r="H65" s="38"/>
+      <c r="I65" s="38"/>
+      <c r="J65" s="38"/>
+      <c r="K65" s="38"/>
+      <c r="L65" s="38"/>
+      <c r="M65" s="38"/>
+      <c r="N65" s="38"/>
+      <c r="O65" s="38"/>
+      <c r="P65" s="38"/>
+      <c r="Q65" s="38"/>
+      <c r="R65" s="38"/>
+      <c r="S65" s="38"/>
+      <c r="T65" s="38"/>
+      <c r="U65" s="38"/>
+      <c r="V65" s="38"/>
+      <c r="W65" s="38"/>
+      <c r="X65" s="38"/>
+      <c r="Y65" s="38"/>
+      <c r="Z65" s="38"/>
+      <c r="AA65" s="38"/>
+      <c r="AB65" s="38"/>
+      <c r="AC65" s="38"/>
+      <c r="AD65" s="38"/>
+      <c r="AE65" s="38"/>
+      <c r="AF65" s="38"/>
+      <c r="AG65" s="38"/>
+      <c r="AH65" s="38"/>
+      <c r="AI65" s="38"/>
+      <c r="AJ65" s="38"/>
     </row>
     <row r="66" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B66" s="45" t="s">
+      <c r="B66" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C66" s="46"/>
-      <c r="D66" s="46"/>
-      <c r="E66" s="46"/>
-      <c r="F66" s="47"/>
-      <c r="G66" s="48" t="s">
+      <c r="C66" s="40"/>
+      <c r="D66" s="40"/>
+      <c r="E66" s="40"/>
+      <c r="F66" s="41"/>
+      <c r="G66" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H66" s="49"/>
-      <c r="I66" s="49"/>
-      <c r="J66" s="49"/>
-      <c r="K66" s="50"/>
-      <c r="L66" s="38" t="s">
+      <c r="H66" s="43"/>
+      <c r="I66" s="43"/>
+      <c r="J66" s="43"/>
+      <c r="K66" s="44"/>
+      <c r="L66" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="M66" s="39"/>
-      <c r="N66" s="39"/>
-      <c r="O66" s="39"/>
-      <c r="P66" s="40"/>
-      <c r="Q66" s="41" t="s">
+      <c r="M66" s="46"/>
+      <c r="N66" s="46"/>
+      <c r="O66" s="46"/>
+      <c r="P66" s="47"/>
+      <c r="Q66" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="R66" s="42"/>
-      <c r="S66" s="42"/>
-      <c r="T66" s="42"/>
-      <c r="U66" s="43"/>
-      <c r="V66" s="38" t="s">
+      <c r="R66" s="49"/>
+      <c r="S66" s="49"/>
+      <c r="T66" s="49"/>
+      <c r="U66" s="50"/>
+      <c r="V66" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W66" s="39"/>
-      <c r="X66" s="39"/>
-      <c r="Y66" s="39"/>
-      <c r="Z66" s="40"/>
-      <c r="AA66" s="41" t="s">
+      <c r="W66" s="46"/>
+      <c r="X66" s="46"/>
+      <c r="Y66" s="46"/>
+      <c r="Z66" s="47"/>
+      <c r="AA66" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="AB66" s="42"/>
-      <c r="AC66" s="42"/>
-      <c r="AD66" s="42"/>
-      <c r="AE66" s="43"/>
-      <c r="AF66" s="38" t="s">
+      <c r="AB66" s="49"/>
+      <c r="AC66" s="49"/>
+      <c r="AD66" s="49"/>
+      <c r="AE66" s="50"/>
+      <c r="AF66" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="AG66" s="39"/>
-      <c r="AH66" s="39"/>
-      <c r="AI66" s="39"/>
-      <c r="AJ66" s="40"/>
+      <c r="AG66" s="46"/>
+      <c r="AH66" s="46"/>
+      <c r="AI66" s="46"/>
+      <c r="AJ66" s="47"/>
     </row>
     <row r="67" spans="2:36" ht="60" x14ac:dyDescent="0.25">
       <c r="B67" s="13" t="s">
@@ -6916,46 +6916,15 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="B65:AJ65"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="G66:K66"/>
-    <mergeCell ref="L66:P66"/>
-    <mergeCell ref="Q66:U66"/>
-    <mergeCell ref="V66:Z66"/>
-    <mergeCell ref="AA66:AE66"/>
-    <mergeCell ref="AF66:AJ66"/>
-    <mergeCell ref="B56:AJ56"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="G57:K57"/>
-    <mergeCell ref="L57:P57"/>
-    <mergeCell ref="Q57:U57"/>
-    <mergeCell ref="V57:Z57"/>
-    <mergeCell ref="AA57:AE57"/>
-    <mergeCell ref="AF57:AJ57"/>
-    <mergeCell ref="B47:AJ47"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="G48:K48"/>
-    <mergeCell ref="L48:P48"/>
-    <mergeCell ref="Q48:U48"/>
-    <mergeCell ref="V48:Z48"/>
-    <mergeCell ref="AA48:AE48"/>
-    <mergeCell ref="AF48:AJ48"/>
-    <mergeCell ref="B38:AJ38"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="G39:K39"/>
-    <mergeCell ref="L39:P39"/>
-    <mergeCell ref="Q39:U39"/>
-    <mergeCell ref="V39:Z39"/>
-    <mergeCell ref="AA39:AE39"/>
-    <mergeCell ref="AF39:AJ39"/>
-    <mergeCell ref="B28:AJ28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="G29:K29"/>
-    <mergeCell ref="L29:P29"/>
-    <mergeCell ref="Q29:U29"/>
-    <mergeCell ref="V29:Z29"/>
-    <mergeCell ref="AA29:AE29"/>
-    <mergeCell ref="AF29:AJ29"/>
+    <mergeCell ref="AF2:AJ2"/>
+    <mergeCell ref="V2:Z2"/>
+    <mergeCell ref="AA2:AE2"/>
+    <mergeCell ref="B1:AJ1"/>
+    <mergeCell ref="B10:AJ10"/>
+    <mergeCell ref="Q2:U2"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="L2:P2"/>
+    <mergeCell ref="G2:K2"/>
     <mergeCell ref="V11:Z11"/>
     <mergeCell ref="AA11:AE11"/>
     <mergeCell ref="AF11:AJ11"/>
@@ -6971,15 +6940,46 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="G11:K11"/>
     <mergeCell ref="L11:P11"/>
-    <mergeCell ref="AF2:AJ2"/>
-    <mergeCell ref="V2:Z2"/>
-    <mergeCell ref="AA2:AE2"/>
-    <mergeCell ref="B1:AJ1"/>
-    <mergeCell ref="B10:AJ10"/>
-    <mergeCell ref="Q2:U2"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="L2:P2"/>
-    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="B28:AJ28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="G29:K29"/>
+    <mergeCell ref="L29:P29"/>
+    <mergeCell ref="Q29:U29"/>
+    <mergeCell ref="V29:Z29"/>
+    <mergeCell ref="AA29:AE29"/>
+    <mergeCell ref="AF29:AJ29"/>
+    <mergeCell ref="B38:AJ38"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="L39:P39"/>
+    <mergeCell ref="Q39:U39"/>
+    <mergeCell ref="V39:Z39"/>
+    <mergeCell ref="AA39:AE39"/>
+    <mergeCell ref="AF39:AJ39"/>
+    <mergeCell ref="B47:AJ47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G48:K48"/>
+    <mergeCell ref="L48:P48"/>
+    <mergeCell ref="Q48:U48"/>
+    <mergeCell ref="V48:Z48"/>
+    <mergeCell ref="AA48:AE48"/>
+    <mergeCell ref="AF48:AJ48"/>
+    <mergeCell ref="B56:AJ56"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="G57:K57"/>
+    <mergeCell ref="L57:P57"/>
+    <mergeCell ref="Q57:U57"/>
+    <mergeCell ref="V57:Z57"/>
+    <mergeCell ref="AA57:AE57"/>
+    <mergeCell ref="AF57:AJ57"/>
+    <mergeCell ref="B65:AJ65"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="G66:K66"/>
+    <mergeCell ref="L66:P66"/>
+    <mergeCell ref="Q66:U66"/>
+    <mergeCell ref="V66:Z66"/>
+    <mergeCell ref="AA66:AE66"/>
+    <mergeCell ref="AF66:AJ66"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7011,29 +7011,29 @@
   </cols>
   <sheetData>
     <row r="6" spans="1:21" s="20" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="69" t="s">
+      <c r="A6" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="70"/>
-      <c r="S6" s="70"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="70"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="61"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="61"/>
+      <c r="U6" s="61"/>
     </row>
     <row r="7" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="L7" s="12"/>
@@ -7097,37 +7097,37 @@
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="62" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="11">
         <v>1</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="53">
         <v>66</v>
       </c>
-      <c r="E9" s="59">
+      <c r="E9" s="53">
         <v>66</v>
       </c>
-      <c r="F9" s="75">
+      <c r="F9" s="64">
         <v>13000</v>
       </c>
-      <c r="G9" s="59">
+      <c r="G9" s="53">
         <v>1</v>
       </c>
-      <c r="H9" s="59">
+      <c r="H9" s="53">
         <v>1</v>
       </c>
-      <c r="I9" s="59">
+      <c r="I9" s="53">
         <v>66</v>
       </c>
-      <c r="J9" s="59">
+      <c r="J9" s="53">
         <v>66</v>
       </c>
-      <c r="K9" s="51">
+      <c r="K9" s="65">
         <f>AVERAGE(DataExp1.0!B4:B8)</f>
         <v>47.672520781360575</v>
       </c>
@@ -7135,7 +7135,7 @@
         <f>AVERAGE(DataExp1.0!B4:B8)</f>
         <v>47.672520781360575</v>
       </c>
-      <c r="M9" s="76">
+      <c r="M9" s="68">
         <f>AVERAGE(DataExp1.0!C4:C8)</f>
         <v>6.570467981210955</v>
       </c>
@@ -7157,24 +7157,24 @@
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
+      <c r="A10" s="63"/>
       <c r="B10" s="6">
         <v>3</v>
       </c>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="73"/>
-      <c r="J10" s="73"/>
-      <c r="K10" s="52"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="66"/>
       <c r="L10" s="5">
         <f>AVERAGE(DataExp1.0!G4:G8)</f>
         <v>21.856551751247018</v>
       </c>
-      <c r="M10" s="77"/>
+      <c r="M10" s="69"/>
       <c r="N10" s="5">
         <f>AVERAGE(DataExp1.0!H4:H8)</f>
         <v>3.2246456912534418</v>
@@ -7193,24 +7193,24 @@
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
+      <c r="A11" s="63"/>
       <c r="B11" s="6">
         <v>5</v>
       </c>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="73"/>
-      <c r="J11" s="73"/>
-      <c r="K11" s="52"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="66"/>
       <c r="L11" s="5">
         <f>AVERAGE(DataExp1.0!L4:L8)</f>
         <v>11.98984802681626</v>
       </c>
-      <c r="M11" s="77"/>
+      <c r="M11" s="69"/>
       <c r="N11" s="5">
         <f>AVERAGE(DataExp1.0!M4:M8)</f>
         <v>2.0149346560221604</v>
@@ -7229,24 +7229,24 @@
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
+      <c r="A12" s="63"/>
       <c r="B12" s="6">
         <v>10</v>
       </c>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="73"/>
-      <c r="K12" s="52"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54"/>
+      <c r="K12" s="66"/>
       <c r="L12" s="5">
         <f>AVERAGE(DataExp1.0!Q4:Q8)</f>
         <v>1.5875226457050842</v>
       </c>
-      <c r="M12" s="77"/>
+      <c r="M12" s="69"/>
       <c r="N12" s="5">
         <f>AVERAGE(DataExp1.0!R4:R8)</f>
         <v>0.4703038834919574</v>
@@ -7265,24 +7265,24 @@
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="72"/>
+      <c r="A13" s="63"/>
       <c r="B13" s="6">
         <v>20</v>
       </c>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="73"/>
-      <c r="K13" s="52"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="66"/>
       <c r="L13" s="5">
         <f>AVERAGE(DataExp1.0!V4:V8)</f>
         <v>1.1816151609203558</v>
       </c>
-      <c r="M13" s="77"/>
+      <c r="M13" s="69"/>
       <c r="N13" s="5">
         <f>AVERAGE(DataExp1.0!W4:W8)</f>
         <v>0.36451866478278661</v>
@@ -7301,24 +7301,24 @@
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="72"/>
+      <c r="A14" s="63"/>
       <c r="B14" s="6">
         <v>50</v>
       </c>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="73"/>
-      <c r="K14" s="52"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="66"/>
       <c r="L14" s="5">
         <f>AVERAGE(DataExp1.0!AA4:AA8)</f>
         <v>1.6919275836893182</v>
       </c>
-      <c r="M14" s="77"/>
+      <c r="M14" s="69"/>
       <c r="N14" s="5">
         <f>AVERAGE(DataExp1.0!AB4:AB8)</f>
         <v>0.47056375966812097</v>
@@ -7337,24 +7337,24 @@
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="72"/>
+      <c r="A15" s="63"/>
       <c r="B15" s="6">
         <v>100</v>
       </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="73"/>
-      <c r="K15" s="53"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="54"/>
+      <c r="K15" s="67"/>
       <c r="L15" s="5">
         <f>AVERAGE(DataExp1.0!AF4:AF8)</f>
         <v>1.1607429307212318</v>
       </c>
-      <c r="M15" s="78"/>
+      <c r="M15" s="70"/>
       <c r="N15" s="5">
         <f>AVERAGE(DataExp1.0!AG4:AG8)</f>
         <v>0.36810600706187663</v>
@@ -7373,21 +7373,21 @@
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="73" t="s">
+      <c r="A16" s="54" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
       </c>
-      <c r="C16" s="73"/>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="73"/>
-      <c r="H16" s="73"/>
-      <c r="I16" s="73"/>
-      <c r="J16" s="73"/>
-      <c r="K16" s="57">
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="54"/>
+      <c r="K16" s="58">
         <f>AVERAGE(DataExp1.0!B13:B17)</f>
         <v>98.52386541032611</v>
       </c>
@@ -7395,7 +7395,7 @@
         <f>AVERAGE(DataExp1.0!B13:B17)</f>
         <v>98.52386541032611</v>
       </c>
-      <c r="M16" s="66">
+      <c r="M16" s="71">
         <f>AVERAGE(DataExp1.0!C13:C17)</f>
         <v>13.16799620264122</v>
       </c>
@@ -7417,24 +7417,24 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="73"/>
+      <c r="A17" s="54"/>
       <c r="B17" s="3">
         <v>3</v>
       </c>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="73"/>
-      <c r="H17" s="73"/>
-      <c r="I17" s="73"/>
-      <c r="J17" s="73"/>
-      <c r="K17" s="58"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="54"/>
+      <c r="K17" s="59"/>
       <c r="L17" s="4">
         <f>AVERAGE(DataExp1.0!G13:G17)</f>
         <v>3.5894588009443735</v>
       </c>
-      <c r="M17" s="67"/>
+      <c r="M17" s="72"/>
       <c r="N17" s="4">
         <f>AVERAGE(DataExp1.0!H13:H17)</f>
         <v>0.7271290796951515</v>
@@ -7453,24 +7453,24 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="73"/>
+      <c r="A18" s="54"/>
       <c r="B18" s="3">
         <v>5</v>
       </c>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="73"/>
-      <c r="J18" s="73"/>
-      <c r="K18" s="58"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="54"/>
+      <c r="K18" s="59"/>
       <c r="L18" s="4">
         <f>AVERAGE(DataExp1.0!L13:L17)</f>
         <v>4.6885991481999643</v>
       </c>
-      <c r="M18" s="67"/>
+      <c r="M18" s="72"/>
       <c r="N18" s="4">
         <f>AVERAGE(DataExp1.0!M13:M17)</f>
         <v>0.94745746549765697</v>
@@ -7489,24 +7489,24 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="73"/>
+      <c r="A19" s="54"/>
       <c r="B19" s="3">
         <v>10</v>
       </c>
-      <c r="C19" s="73"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="73"/>
-      <c r="J19" s="73"/>
-      <c r="K19" s="58"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="54"/>
+      <c r="K19" s="59"/>
       <c r="L19" s="4">
         <f>AVERAGE(DataExp1.0!Q13:Q17)</f>
         <v>4.6542904797370337</v>
       </c>
-      <c r="M19" s="67"/>
+      <c r="M19" s="72"/>
       <c r="N19" s="4">
         <f>AVERAGE(DataExp1.0!R13:R17)</f>
         <v>0.99628493667097506</v>
@@ -7525,24 +7525,24 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="73"/>
+      <c r="A20" s="54"/>
       <c r="B20" s="3">
         <v>20</v>
       </c>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="73"/>
-      <c r="J20" s="73"/>
-      <c r="K20" s="58"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
+      <c r="K20" s="59"/>
       <c r="L20" s="4">
         <f>AVERAGE(DataExp1.0!V13:V17)</f>
         <v>4.7382106552509056</v>
       </c>
-      <c r="M20" s="67"/>
+      <c r="M20" s="72"/>
       <c r="N20" s="4">
         <f>AVERAGE(DataExp1.0!W13:W17)</f>
         <v>0.96927676121293316</v>
@@ -7561,24 +7561,24 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="73"/>
+      <c r="A21" s="54"/>
       <c r="B21" s="3">
         <v>50</v>
       </c>
-      <c r="C21" s="73"/>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="73"/>
-      <c r="J21" s="73"/>
-      <c r="K21" s="58"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
+      <c r="K21" s="59"/>
       <c r="L21" s="4">
         <f>AVERAGE(DataExp1.0!AA13:AA17)</f>
         <v>3.5014269837011178</v>
       </c>
-      <c r="M21" s="67"/>
+      <c r="M21" s="72"/>
       <c r="N21" s="4">
         <f>AVERAGE(DataExp1.0!AB13:AB17)</f>
         <v>0.82194590388464606</v>
@@ -7597,24 +7597,24 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="73"/>
+      <c r="A22" s="54"/>
       <c r="B22" s="3">
         <v>100</v>
       </c>
-      <c r="C22" s="73"/>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="73"/>
-      <c r="J22" s="73"/>
-      <c r="K22" s="59"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="53"/>
       <c r="L22" s="4">
         <f>AVERAGE(DataExp1.0!AF13:AF17)</f>
         <v>4.0573849410218283</v>
       </c>
-      <c r="M22" s="68"/>
+      <c r="M22" s="73"/>
       <c r="N22" s="4">
         <f>AVERAGE(DataExp1.0!AG13:AG17)</f>
         <v>0.8986508097888064</v>
@@ -7633,21 +7633,21 @@
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="74" t="s">
+      <c r="A23" s="51" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="9">
         <v>1</v>
       </c>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="73"/>
-      <c r="K23" s="51">
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="65">
         <f>AVERAGE(DataExp1.0!B22:B26)</f>
         <v>4.5451398138019297</v>
       </c>
@@ -7655,7 +7655,7 @@
         <f>AVERAGE(DataExp1.0!B22:B26)</f>
         <v>4.5451398138019297</v>
       </c>
-      <c r="M23" s="54">
+      <c r="M23" s="74">
         <f>AVERAGE(DataExp1.0!C22:C26)</f>
         <v>0.75511641042661903</v>
       </c>
@@ -7677,24 +7677,24 @@
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="74"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="9">
         <v>3</v>
       </c>
-      <c r="C24" s="73"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="73"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="73"/>
-      <c r="J24" s="73"/>
-      <c r="K24" s="52"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="66"/>
       <c r="L24" s="14">
         <f>AVERAGE(DataExp1.0!G22:G26)</f>
         <v>5.0008254388311881</v>
       </c>
-      <c r="M24" s="55"/>
+      <c r="M24" s="75"/>
       <c r="N24" s="14">
         <f>AVERAGE(DataExp1.0!H22:H26)</f>
         <v>0.83545625636470588</v>
@@ -7713,24 +7713,24 @@
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="74"/>
+      <c r="A25" s="51"/>
       <c r="B25" s="9">
         <v>5</v>
       </c>
-      <c r="C25" s="73"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="73"/>
-      <c r="J25" s="73"/>
-      <c r="K25" s="52"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="54"/>
+      <c r="K25" s="66"/>
       <c r="L25" s="14">
         <f>AVERAGE(DataExp1.0!L22:L26)</f>
         <v>5.1520558152375724</v>
       </c>
-      <c r="M25" s="55"/>
+      <c r="M25" s="75"/>
       <c r="N25" s="14">
         <f>AVERAGE(DataExp1.0!M22:M26)</f>
         <v>0.86004741560851961</v>
@@ -7749,24 +7749,24 @@
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="74"/>
+      <c r="A26" s="51"/>
       <c r="B26" s="9">
         <v>10</v>
       </c>
-      <c r="C26" s="73"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="73"/>
-      <c r="J26" s="73"/>
-      <c r="K26" s="52"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
+      <c r="K26" s="66"/>
       <c r="L26" s="14">
         <f>AVERAGE(DataExp1.0!Q22:Q26)</f>
         <v>5.0638720407004723</v>
       </c>
-      <c r="M26" s="55"/>
+      <c r="M26" s="75"/>
       <c r="N26" s="14">
         <f>AVERAGE(DataExp1.0!R22:R26)</f>
         <v>0.84643462799769187</v>
@@ -7785,24 +7785,24 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="74"/>
+      <c r="A27" s="51"/>
       <c r="B27" s="9">
         <v>20</v>
       </c>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="73"/>
-      <c r="J27" s="73"/>
-      <c r="K27" s="52"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="54"/>
+      <c r="K27" s="66"/>
       <c r="L27" s="14">
         <f>AVERAGE(DataExp1.0!V22:V26)</f>
         <v>5.0919611857628801</v>
       </c>
-      <c r="M27" s="55"/>
+      <c r="M27" s="75"/>
       <c r="N27" s="14">
         <f>AVERAGE(DataExp1.0!W22:W26)</f>
         <v>0.85522738523555719</v>
@@ -7821,24 +7821,24 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="74"/>
+      <c r="A28" s="51"/>
       <c r="B28" s="9">
         <v>50</v>
       </c>
-      <c r="C28" s="73"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="73"/>
-      <c r="J28" s="73"/>
-      <c r="K28" s="52"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="54"/>
+      <c r="K28" s="66"/>
       <c r="L28" s="14">
         <f>AVERAGE(DataExp1.0!AA22:AA26)</f>
         <v>5.1348735027135763</v>
       </c>
-      <c r="M28" s="55"/>
+      <c r="M28" s="75"/>
       <c r="N28" s="14">
         <f>AVERAGE(DataExp1.0!AB22:AB26)</f>
         <v>0.85522738523555719</v>
@@ -7857,24 +7857,24 @@
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="74"/>
+      <c r="A29" s="51"/>
       <c r="B29" s="9">
         <v>100</v>
       </c>
-      <c r="C29" s="73"/>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="73"/>
-      <c r="J29" s="73"/>
-      <c r="K29" s="53"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="67"/>
       <c r="L29" s="14">
         <f>AVERAGE(DataExp1.0!AF22:AF26)</f>
         <v>5.1012116368683964</v>
       </c>
-      <c r="M29" s="56"/>
+      <c r="M29" s="76"/>
       <c r="N29" s="14">
         <f>AVERAGE(DataExp1.0!AG22:AG26)</f>
         <v>0.85522738523555719</v>
@@ -7893,21 +7893,21 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="73" t="s">
+      <c r="A30" s="54" t="s">
         <v>15</v>
       </c>
       <c r="B30" s="3">
         <v>1</v>
       </c>
-      <c r="C30" s="73"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
-      <c r="J30" s="73"/>
-      <c r="K30" s="57">
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="54"/>
+      <c r="K30" s="58">
         <f>AVERAGE(DataExp1.0!B31:B35)</f>
         <v>69.119033281650658</v>
       </c>
@@ -7915,7 +7915,7 @@
         <f>AVERAGE(DataExp1.0!B31:B35)</f>
         <v>69.119033281650658</v>
       </c>
-      <c r="M30" s="66">
+      <c r="M30" s="71">
         <f>AVERAGE(DataExp1.0!C31:C35)</f>
         <v>9.1400504790035715</v>
       </c>
@@ -7937,24 +7937,24 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="73"/>
+      <c r="A31" s="54"/>
       <c r="B31" s="3">
         <v>3</v>
       </c>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="73"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="73"/>
-      <c r="J31" s="73"/>
-      <c r="K31" s="58"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="59"/>
       <c r="L31" s="4">
         <f>AVERAGE(DataExp1.0!G31:G35)</f>
         <v>3.8112034677615521</v>
       </c>
-      <c r="M31" s="67"/>
+      <c r="M31" s="72"/>
       <c r="N31" s="4">
         <f>AVERAGE(DataExp1.0!H31:H35)</f>
         <v>0.69516313804590357</v>
@@ -7973,24 +7973,24 @@
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="73"/>
+      <c r="A32" s="54"/>
       <c r="B32" s="3">
         <v>5</v>
       </c>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="73"/>
-      <c r="H32" s="73"/>
-      <c r="I32" s="73"/>
-      <c r="J32" s="73"/>
-      <c r="K32" s="58"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="54"/>
+      <c r="K32" s="59"/>
       <c r="L32" s="4">
         <f>AVERAGE(DataExp1.0!L31:L35)</f>
         <v>3.794055612529962</v>
       </c>
-      <c r="M32" s="67"/>
+      <c r="M32" s="72"/>
       <c r="N32" s="4">
         <f>AVERAGE(DataExp1.0!M31:M35)</f>
         <v>0.70219775458629363</v>
@@ -8009,24 +8009,24 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="73"/>
+      <c r="A33" s="54"/>
       <c r="B33" s="3">
         <v>10</v>
       </c>
-      <c r="C33" s="73"/>
-      <c r="D33" s="73"/>
-      <c r="E33" s="73"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="73"/>
-      <c r="H33" s="73"/>
-      <c r="I33" s="73"/>
-      <c r="J33" s="73"/>
-      <c r="K33" s="58"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="54"/>
+      <c r="K33" s="59"/>
       <c r="L33" s="4">
         <f>AVERAGE(DataExp1.0!Q31:Q35)</f>
         <v>3.8227770814034598</v>
       </c>
-      <c r="M33" s="67"/>
+      <c r="M33" s="72"/>
       <c r="N33" s="4">
         <f>AVERAGE(DataExp1.0!R31:R35)</f>
         <v>0.71134642701416584</v>
@@ -8045,24 +8045,24 @@
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="73"/>
+      <c r="A34" s="54"/>
       <c r="B34" s="3">
         <v>20</v>
       </c>
-      <c r="C34" s="73"/>
-      <c r="D34" s="73"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="73"/>
-      <c r="H34" s="73"/>
-      <c r="I34" s="73"/>
-      <c r="J34" s="73"/>
-      <c r="K34" s="58"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="54"/>
+      <c r="K34" s="59"/>
       <c r="L34" s="4">
         <f>AVERAGE(DataExp1.0!V31:V35)</f>
         <v>3.8203191287719442</v>
       </c>
-      <c r="M34" s="67"/>
+      <c r="M34" s="72"/>
       <c r="N34" s="4">
         <f>AVERAGE(DataExp1.0!W31:W35)</f>
         <v>0.70427531835187795</v>
@@ -8081,24 +8081,24 @@
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" s="73"/>
+      <c r="A35" s="54"/>
       <c r="B35" s="3">
         <v>50</v>
       </c>
-      <c r="C35" s="73"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="73"/>
-      <c r="H35" s="73"/>
-      <c r="I35" s="73"/>
-      <c r="J35" s="73"/>
-      <c r="K35" s="58"/>
+      <c r="C35" s="54"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="59"/>
       <c r="L35" s="4">
         <f>AVERAGE(DataExp1.0!AA31:AA35)</f>
         <v>3.7894569132805862</v>
       </c>
-      <c r="M35" s="67"/>
+      <c r="M35" s="72"/>
       <c r="N35" s="4">
         <f>AVERAGE(DataExp1.0!AB31:AB35)</f>
         <v>0.70514874222061896</v>
@@ -8117,24 +8117,24 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="73"/>
+      <c r="A36" s="54"/>
       <c r="B36" s="3">
         <v>100</v>
       </c>
-      <c r="C36" s="73"/>
-      <c r="D36" s="73"/>
-      <c r="E36" s="73"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="73"/>
-      <c r="H36" s="73"/>
-      <c r="I36" s="73"/>
-      <c r="J36" s="73"/>
-      <c r="K36" s="59"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="54"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="54"/>
+      <c r="K36" s="53"/>
       <c r="L36" s="4">
         <f>AVERAGE(DataExp1.0!AF31:AF35)</f>
         <v>3.9279650153360124</v>
       </c>
-      <c r="M36" s="68"/>
+      <c r="M36" s="73"/>
       <c r="N36" s="4">
         <f>AVERAGE(DataExp1.0!AG31:AG35)</f>
         <v>0.71758144498594478</v>
@@ -8153,37 +8153,37 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="80" t="s">
+      <c r="A38" s="55" t="s">
         <v>12</v>
       </c>
       <c r="B38" s="3">
         <v>1</v>
       </c>
-      <c r="C38" s="73" t="s">
+      <c r="C38" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="D38" s="73">
+      <c r="D38" s="54">
         <v>128</v>
       </c>
-      <c r="E38" s="73">
+      <c r="E38" s="54">
         <v>128</v>
       </c>
-      <c r="F38" s="57">
+      <c r="F38" s="58">
         <v>1.1200000000000001</v>
       </c>
-      <c r="G38" s="73">
+      <c r="G38" s="54">
         <v>1</v>
       </c>
-      <c r="H38" s="73">
+      <c r="H38" s="54">
         <v>1</v>
       </c>
-      <c r="I38" s="73">
+      <c r="I38" s="54">
         <v>128</v>
       </c>
-      <c r="J38" s="73">
+      <c r="J38" s="54">
         <v>128</v>
       </c>
-      <c r="K38" s="57">
+      <c r="K38" s="58">
         <f>AVERAGE(DataExp1.0!B41:B45)</f>
         <v>49.109113664906239</v>
       </c>
@@ -8191,7 +8191,7 @@
         <f>AVERAGE(DataExp1.0!B41:B45)</f>
         <v>49.109113664906239</v>
       </c>
-      <c r="M38" s="66">
+      <c r="M38" s="71">
         <f>AVERAGE(DataExp1.0!C41:C45)</f>
         <v>7.1307054880345344</v>
       </c>
@@ -8213,24 +8213,24 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" s="81"/>
+      <c r="A39" s="56"/>
       <c r="B39" s="3">
         <v>3</v>
       </c>
-      <c r="C39" s="73"/>
-      <c r="D39" s="73"/>
-      <c r="E39" s="73"/>
-      <c r="F39" s="58"/>
-      <c r="G39" s="73"/>
-      <c r="H39" s="73"/>
-      <c r="I39" s="73"/>
-      <c r="J39" s="73"/>
-      <c r="K39" s="58"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="59"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="54"/>
+      <c r="K39" s="59"/>
       <c r="L39" s="4">
         <f>AVERAGE(DataExp1.0!G41:G45)</f>
         <v>29.353773127605098</v>
       </c>
-      <c r="M39" s="67"/>
+      <c r="M39" s="72"/>
       <c r="N39" s="4">
         <f>AVERAGE(DataExp1.0!H41:H45)</f>
         <v>4.4551993118062274</v>
@@ -8249,24 +8249,24 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" s="81"/>
+      <c r="A40" s="56"/>
       <c r="B40" s="3">
         <v>5</v>
       </c>
-      <c r="C40" s="73"/>
-      <c r="D40" s="73"/>
-      <c r="E40" s="73"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="73"/>
-      <c r="H40" s="73"/>
-      <c r="I40" s="73"/>
-      <c r="J40" s="73"/>
-      <c r="K40" s="58"/>
+      <c r="C40" s="54"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="54"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="54"/>
+      <c r="I40" s="54"/>
+      <c r="J40" s="54"/>
+      <c r="K40" s="59"/>
       <c r="L40" s="4">
         <f>AVERAGE(DataExp1.0!L41:L45)</f>
         <v>15.663362976697901</v>
       </c>
-      <c r="M40" s="67"/>
+      <c r="M40" s="72"/>
       <c r="N40" s="4">
         <f>AVERAGE(DataExp1.0!M41:M45)</f>
         <v>2.88709338804897</v>
@@ -8285,24 +8285,24 @@
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" s="81"/>
+      <c r="A41" s="56"/>
       <c r="B41" s="3">
         <v>10</v>
       </c>
-      <c r="C41" s="73"/>
-      <c r="D41" s="73"/>
-      <c r="E41" s="73"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="73"/>
-      <c r="H41" s="73"/>
-      <c r="I41" s="73"/>
-      <c r="J41" s="73"/>
-      <c r="K41" s="58"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="54"/>
+      <c r="J41" s="54"/>
+      <c r="K41" s="59"/>
       <c r="L41" s="4">
         <f>AVERAGE(DataExp1.0!Q41:Q45)</f>
         <v>2.6831688983529682</v>
       </c>
-      <c r="M41" s="67"/>
+      <c r="M41" s="72"/>
       <c r="N41" s="4">
         <f>AVERAGE(DataExp1.0!R41:R45)</f>
         <v>0.85955240456339899</v>
@@ -8321,24 +8321,24 @@
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="81"/>
+      <c r="A42" s="56"/>
       <c r="B42" s="3">
         <v>20</v>
       </c>
-      <c r="C42" s="73"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="73"/>
-      <c r="J42" s="73"/>
-      <c r="K42" s="58"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="54"/>
+      <c r="K42" s="59"/>
       <c r="L42" s="4">
         <f>AVERAGE(DataExp1.0!V41:V45)</f>
         <v>1.976742439773264</v>
       </c>
-      <c r="M42" s="67"/>
+      <c r="M42" s="72"/>
       <c r="N42" s="4">
         <f>AVERAGE(DataExp1.0!W41:W45)</f>
         <v>0.49921018725094479</v>
@@ -8357,24 +8357,24 @@
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="81"/>
+      <c r="A43" s="56"/>
       <c r="B43" s="3">
         <v>50</v>
       </c>
-      <c r="C43" s="73"/>
-      <c r="D43" s="73"/>
-      <c r="E43" s="73"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="73"/>
-      <c r="H43" s="73"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="73"/>
-      <c r="K43" s="58"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="54"/>
+      <c r="I43" s="54"/>
+      <c r="J43" s="54"/>
+      <c r="K43" s="59"/>
       <c r="L43" s="4">
         <f>AVERAGE(DataExp1.0!AA41:AA45)</f>
         <v>1.6365291135842757</v>
       </c>
-      <c r="M43" s="67"/>
+      <c r="M43" s="72"/>
       <c r="N43" s="4">
         <f>AVERAGE(DataExp1.0!AB41:AB45)</f>
         <v>0.51205840109109702</v>
@@ -8393,24 +8393,24 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="82"/>
+      <c r="A44" s="57"/>
       <c r="B44" s="3">
         <v>100</v>
       </c>
-      <c r="C44" s="73"/>
-      <c r="D44" s="73"/>
-      <c r="E44" s="73"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="73"/>
-      <c r="H44" s="73"/>
-      <c r="I44" s="73"/>
-      <c r="J44" s="73"/>
-      <c r="K44" s="59"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="54"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="54"/>
+      <c r="I44" s="54"/>
+      <c r="J44" s="54"/>
+      <c r="K44" s="53"/>
       <c r="L44" s="4">
         <f>AVERAGE(DataExp1.0!AF41:AF45)</f>
         <v>1.7066608066957361</v>
       </c>
-      <c r="M44" s="68"/>
+      <c r="M44" s="73"/>
       <c r="N44" s="4">
         <f>AVERAGE(DataExp1.0!AG41:AG45)</f>
         <v>0.41120745370947642</v>
@@ -8429,21 +8429,21 @@
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" s="74" t="s">
+      <c r="A45" s="51" t="s">
         <v>13</v>
       </c>
       <c r="B45" s="9">
         <v>1</v>
       </c>
-      <c r="C45" s="73"/>
-      <c r="D45" s="73"/>
-      <c r="E45" s="73"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="73"/>
-      <c r="H45" s="73"/>
-      <c r="I45" s="73"/>
-      <c r="J45" s="73"/>
-      <c r="K45" s="51">
+      <c r="C45" s="54"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="54"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="65">
         <f>AVERAGE(DataExp1.0!B50:B54)</f>
         <v>109.49437252943599</v>
       </c>
@@ -8451,7 +8451,7 @@
         <f>AVERAGE(DataExp1.0!B50:B54)</f>
         <v>109.49437252943599</v>
       </c>
-      <c r="M45" s="54">
+      <c r="M45" s="74">
         <f>AVERAGE(DataExp1.0!C50:C54)</f>
         <v>14.725215274084761</v>
       </c>
@@ -8473,24 +8473,24 @@
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="74"/>
+      <c r="A46" s="51"/>
       <c r="B46" s="9">
         <v>3</v>
       </c>
-      <c r="C46" s="73"/>
-      <c r="D46" s="73"/>
-      <c r="E46" s="73"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="73"/>
-      <c r="H46" s="73"/>
-      <c r="I46" s="73"/>
-      <c r="J46" s="73"/>
-      <c r="K46" s="52"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="59"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="54"/>
+      <c r="J46" s="54"/>
+      <c r="K46" s="66"/>
       <c r="L46" s="14">
         <f>AVERAGE(DataExp1.0!G50:G54)</f>
         <v>1.9585561928098438</v>
       </c>
-      <c r="M46" s="55"/>
+      <c r="M46" s="75"/>
       <c r="N46" s="14">
         <f>AVERAGE(DataExp1.0!H50:H54)</f>
         <v>0.49011707608867516</v>
@@ -8509,24 +8509,24 @@
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="74"/>
+      <c r="A47" s="51"/>
       <c r="B47" s="9">
         <v>5</v>
       </c>
-      <c r="C47" s="73"/>
-      <c r="D47" s="73"/>
-      <c r="E47" s="73"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="73"/>
-      <c r="H47" s="73"/>
-      <c r="I47" s="73"/>
-      <c r="J47" s="73"/>
-      <c r="K47" s="52"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
+      <c r="F47" s="59"/>
+      <c r="G47" s="54"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="54"/>
+      <c r="J47" s="54"/>
+      <c r="K47" s="66"/>
       <c r="L47" s="14">
         <f>AVERAGE(DataExp1.0!L50:L54)</f>
         <v>1.9859984774941259</v>
       </c>
-      <c r="M47" s="55"/>
+      <c r="M47" s="75"/>
       <c r="N47" s="14">
         <f>AVERAGE(DataExp1.0!M50:M54)</f>
         <v>0.42502141161115414</v>
@@ -8545,24 +8545,24 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="74"/>
+      <c r="A48" s="51"/>
       <c r="B48" s="9">
         <v>10</v>
       </c>
-      <c r="C48" s="73"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="73"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="73"/>
-      <c r="H48" s="73"/>
-      <c r="I48" s="73"/>
-      <c r="J48" s="73"/>
-      <c r="K48" s="52"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54"/>
+      <c r="F48" s="59"/>
+      <c r="G48" s="54"/>
+      <c r="H48" s="54"/>
+      <c r="I48" s="54"/>
+      <c r="J48" s="54"/>
+      <c r="K48" s="66"/>
       <c r="L48" s="14">
         <f>AVERAGE(DataExp1.0!Q50:Q54)</f>
         <v>1.7733344450645681</v>
       </c>
-      <c r="M48" s="55"/>
+      <c r="M48" s="75"/>
       <c r="N48" s="14">
         <f>AVERAGE(DataExp1.0!R50:R54)</f>
         <v>0.46339672866043857</v>
@@ -8581,24 +8581,24 @@
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="74"/>
+      <c r="A49" s="51"/>
       <c r="B49" s="9">
         <v>20</v>
       </c>
-      <c r="C49" s="73"/>
-      <c r="D49" s="73"/>
-      <c r="E49" s="73"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="73"/>
-      <c r="H49" s="73"/>
-      <c r="I49" s="73"/>
-      <c r="J49" s="73"/>
-      <c r="K49" s="52"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="59"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="54"/>
+      <c r="K49" s="66"/>
       <c r="L49" s="14">
         <f>AVERAGE(DataExp1.0!V50:V54)</f>
         <v>1.7733344450645681</v>
       </c>
-      <c r="M49" s="55"/>
+      <c r="M49" s="75"/>
       <c r="N49" s="14">
         <f>AVERAGE(DataExp1.0!W50:W54)</f>
         <v>0.46339672866043857</v>
@@ -8617,24 +8617,24 @@
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="74"/>
+      <c r="A50" s="51"/>
       <c r="B50" s="9">
         <v>50</v>
       </c>
-      <c r="C50" s="73"/>
-      <c r="D50" s="73"/>
-      <c r="E50" s="73"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="73"/>
-      <c r="H50" s="73"/>
-      <c r="I50" s="73"/>
-      <c r="J50" s="73"/>
-      <c r="K50" s="52"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="59"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54"/>
+      <c r="K50" s="66"/>
       <c r="L50" s="14">
         <f>AVERAGE(DataExp1.0!AA50:AA54)</f>
         <v>2.4184933787745742</v>
       </c>
-      <c r="M50" s="55"/>
+      <c r="M50" s="75"/>
       <c r="N50" s="14">
         <f>AVERAGE(DataExp1.0!AB50:AB54)</f>
         <v>0.59543539722803129</v>
@@ -8653,24 +8653,24 @@
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="74"/>
+      <c r="A51" s="51"/>
       <c r="B51" s="9">
         <v>100</v>
       </c>
-      <c r="C51" s="73"/>
-      <c r="D51" s="73"/>
-      <c r="E51" s="73"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="73"/>
-      <c r="H51" s="73"/>
-      <c r="I51" s="73"/>
-      <c r="J51" s="73"/>
-      <c r="K51" s="53"/>
+      <c r="C51" s="54"/>
+      <c r="D51" s="54"/>
+      <c r="E51" s="54"/>
+      <c r="F51" s="59"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="54"/>
+      <c r="I51" s="54"/>
+      <c r="J51" s="54"/>
+      <c r="K51" s="67"/>
       <c r="L51" s="14">
         <f>AVERAGE(DataExp1.0!AF50:AF54)</f>
         <v>1.7615966456598742</v>
       </c>
-      <c r="M51" s="56"/>
+      <c r="M51" s="76"/>
       <c r="N51" s="14">
         <f>AVERAGE(DataExp1.0!AG50:AG54)</f>
         <v>0.42629294842947418</v>
@@ -8689,21 +8689,21 @@
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A52" s="79" t="s">
+      <c r="A52" s="52" t="s">
         <v>14</v>
       </c>
       <c r="B52" s="3">
         <v>1</v>
       </c>
-      <c r="C52" s="73"/>
-      <c r="D52" s="73"/>
-      <c r="E52" s="73"/>
-      <c r="F52" s="58"/>
-      <c r="G52" s="73"/>
-      <c r="H52" s="73"/>
-      <c r="I52" s="73"/>
-      <c r="J52" s="73"/>
-      <c r="K52" s="57">
+      <c r="C52" s="54"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="54"/>
+      <c r="F52" s="59"/>
+      <c r="G52" s="54"/>
+      <c r="H52" s="54"/>
+      <c r="I52" s="54"/>
+      <c r="J52" s="54"/>
+      <c r="K52" s="58">
         <f>AVERAGE(DataExp1.0!B59:B63)</f>
         <v>11.563078744278901</v>
       </c>
@@ -8711,7 +8711,7 @@
         <f>AVERAGE(DataExp1.0!B59:B63)</f>
         <v>11.563078744278901</v>
       </c>
-      <c r="M52" s="60">
+      <c r="M52" s="77">
         <f>AVERAGE(DataExp1.0!C59:C63)</f>
         <v>1.5537107420088601</v>
       </c>
@@ -8733,24 +8733,24 @@
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="79"/>
+      <c r="A53" s="52"/>
       <c r="B53" s="3">
         <v>3</v>
       </c>
-      <c r="C53" s="73"/>
-      <c r="D53" s="73"/>
-      <c r="E53" s="73"/>
-      <c r="F53" s="58"/>
-      <c r="G53" s="73"/>
-      <c r="H53" s="73"/>
-      <c r="I53" s="73"/>
-      <c r="J53" s="73"/>
-      <c r="K53" s="58"/>
+      <c r="C53" s="54"/>
+      <c r="D53" s="54"/>
+      <c r="E53" s="54"/>
+      <c r="F53" s="59"/>
+      <c r="G53" s="54"/>
+      <c r="H53" s="54"/>
+      <c r="I53" s="54"/>
+      <c r="J53" s="54"/>
+      <c r="K53" s="59"/>
       <c r="L53" s="4">
         <f>AVERAGE(DataExp1.0!G59:G63)</f>
         <v>2.5097222256129199</v>
       </c>
-      <c r="M53" s="61"/>
+      <c r="M53" s="78"/>
       <c r="N53" s="4">
         <f>AVERAGE(DataExp1.0!H59:H63)</f>
         <v>0.34269894250306598</v>
@@ -8769,24 +8769,24 @@
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="79"/>
+      <c r="A54" s="52"/>
       <c r="B54" s="3">
         <v>5</v>
       </c>
-      <c r="C54" s="73"/>
-      <c r="D54" s="73"/>
-      <c r="E54" s="73"/>
-      <c r="F54" s="58"/>
-      <c r="G54" s="73"/>
-      <c r="H54" s="73"/>
-      <c r="I54" s="73"/>
-      <c r="J54" s="73"/>
-      <c r="K54" s="58"/>
+      <c r="C54" s="54"/>
+      <c r="D54" s="54"/>
+      <c r="E54" s="54"/>
+      <c r="F54" s="59"/>
+      <c r="G54" s="54"/>
+      <c r="H54" s="54"/>
+      <c r="I54" s="54"/>
+      <c r="J54" s="54"/>
+      <c r="K54" s="59"/>
       <c r="L54" s="4">
         <f>AVERAGE(DataExp1.0!L59:L63)</f>
         <v>2.50972029449454</v>
       </c>
-      <c r="M54" s="61"/>
+      <c r="M54" s="78"/>
       <c r="N54" s="4">
         <f>AVERAGE(DataExp1.0!M59:M63)</f>
         <v>0.34269894250306598</v>
@@ -8805,24 +8805,24 @@
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55" s="79"/>
+      <c r="A55" s="52"/>
       <c r="B55" s="10">
         <v>10</v>
       </c>
-      <c r="C55" s="73"/>
-      <c r="D55" s="73"/>
-      <c r="E55" s="73"/>
-      <c r="F55" s="58"/>
-      <c r="G55" s="73"/>
-      <c r="H55" s="73"/>
-      <c r="I55" s="73"/>
-      <c r="J55" s="73"/>
-      <c r="K55" s="58"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="59"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="54"/>
+      <c r="I55" s="54"/>
+      <c r="J55" s="54"/>
+      <c r="K55" s="59"/>
       <c r="L55" s="4">
         <f>AVERAGE(DataExp1.0!Q59:Q63)</f>
         <v>2.50972029449454</v>
       </c>
-      <c r="M55" s="61"/>
+      <c r="M55" s="78"/>
       <c r="N55" s="4">
         <f>AVERAGE(DataExp1.0!R59:R63)</f>
         <v>0.34269894250306598</v>
@@ -8841,24 +8841,24 @@
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="79"/>
+      <c r="A56" s="52"/>
       <c r="B56" s="10">
         <v>20</v>
       </c>
-      <c r="C56" s="73"/>
-      <c r="D56" s="73"/>
-      <c r="E56" s="73"/>
-      <c r="F56" s="58"/>
-      <c r="G56" s="73"/>
-      <c r="H56" s="73"/>
-      <c r="I56" s="73"/>
-      <c r="J56" s="73"/>
-      <c r="K56" s="58"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="59"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="54"/>
+      <c r="I56" s="54"/>
+      <c r="J56" s="54"/>
+      <c r="K56" s="59"/>
       <c r="L56" s="4">
         <f>AVERAGE(DataExp1.0!V59:V63)</f>
         <v>2.50972029449454</v>
       </c>
-      <c r="M56" s="61"/>
+      <c r="M56" s="78"/>
       <c r="N56" s="4">
         <f>AVERAGE(DataExp1.0!W59:W63)</f>
         <v>0.34269894250306598</v>
@@ -8877,24 +8877,24 @@
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="79"/>
+      <c r="A57" s="52"/>
       <c r="B57" s="10">
         <v>50</v>
       </c>
-      <c r="C57" s="73"/>
-      <c r="D57" s="73"/>
-      <c r="E57" s="73"/>
-      <c r="F57" s="58"/>
-      <c r="G57" s="73"/>
-      <c r="H57" s="73"/>
-      <c r="I57" s="73"/>
-      <c r="J57" s="73"/>
-      <c r="K57" s="58"/>
+      <c r="C57" s="54"/>
+      <c r="D57" s="54"/>
+      <c r="E57" s="54"/>
+      <c r="F57" s="59"/>
+      <c r="G57" s="54"/>
+      <c r="H57" s="54"/>
+      <c r="I57" s="54"/>
+      <c r="J57" s="54"/>
+      <c r="K57" s="59"/>
       <c r="L57" s="4">
         <f>AVERAGE(DataExp1.0!AA59:AA63)</f>
         <v>2.50972029449454</v>
       </c>
-      <c r="M57" s="61"/>
+      <c r="M57" s="78"/>
       <c r="N57" s="4">
         <f>AVERAGE(DataExp1.0!AB59:AB63)</f>
         <v>0.34269894250306598</v>
@@ -8913,24 +8913,24 @@
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58" s="79"/>
+      <c r="A58" s="52"/>
       <c r="B58" s="10">
         <v>100</v>
       </c>
-      <c r="C58" s="73"/>
-      <c r="D58" s="73"/>
-      <c r="E58" s="73"/>
-      <c r="F58" s="58"/>
-      <c r="G58" s="73"/>
-      <c r="H58" s="73"/>
-      <c r="I58" s="73"/>
-      <c r="J58" s="73"/>
-      <c r="K58" s="59"/>
+      <c r="C58" s="54"/>
+      <c r="D58" s="54"/>
+      <c r="E58" s="54"/>
+      <c r="F58" s="59"/>
+      <c r="G58" s="54"/>
+      <c r="H58" s="54"/>
+      <c r="I58" s="54"/>
+      <c r="J58" s="54"/>
+      <c r="K58" s="53"/>
       <c r="L58" s="4">
         <f>AVERAGE(DataExp1.0!AF59:AF63)</f>
         <v>2.50972029449454</v>
       </c>
-      <c r="M58" s="62"/>
+      <c r="M58" s="79"/>
       <c r="N58" s="4">
         <f>AVERAGE(DataExp1.0!AG59:AG63)</f>
         <v>0.34269894250306598</v>
@@ -8949,21 +8949,21 @@
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A59" s="74" t="s">
+      <c r="A59" s="51" t="s">
         <v>15</v>
       </c>
       <c r="B59" s="9">
         <v>1</v>
       </c>
-      <c r="C59" s="73"/>
-      <c r="D59" s="73"/>
-      <c r="E59" s="73"/>
-      <c r="F59" s="58"/>
-      <c r="G59" s="73"/>
-      <c r="H59" s="73"/>
-      <c r="I59" s="73"/>
-      <c r="J59" s="73"/>
-      <c r="K59" s="63">
+      <c r="C59" s="54"/>
+      <c r="D59" s="54"/>
+      <c r="E59" s="54"/>
+      <c r="F59" s="59"/>
+      <c r="G59" s="54"/>
+      <c r="H59" s="54"/>
+      <c r="I59" s="54"/>
+      <c r="J59" s="54"/>
+      <c r="K59" s="80">
         <f>AVERAGE(DataExp1.0!B68:B72)</f>
         <v>50.883996585062086</v>
       </c>
@@ -8971,7 +8971,7 @@
         <f>AVERAGE(DataExp1.0!B68:B72)</f>
         <v>50.883996585062086</v>
       </c>
-      <c r="M59" s="54">
+      <c r="M59" s="74">
         <f>AVERAGE(DataExp1.0!C68:C72)</f>
         <v>6.9682177433078207</v>
       </c>
@@ -8993,24 +8993,24 @@
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60" s="74"/>
+      <c r="A60" s="51"/>
       <c r="B60" s="9">
         <v>3</v>
       </c>
-      <c r="C60" s="73"/>
-      <c r="D60" s="73"/>
-      <c r="E60" s="73"/>
-      <c r="F60" s="58"/>
-      <c r="G60" s="73"/>
-      <c r="H60" s="73"/>
-      <c r="I60" s="73"/>
-      <c r="J60" s="73"/>
-      <c r="K60" s="64"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="54"/>
+      <c r="F60" s="59"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="54"/>
+      <c r="I60" s="54"/>
+      <c r="J60" s="54"/>
+      <c r="K60" s="81"/>
       <c r="L60" s="14">
         <f>AVERAGE(DataExp1.0!G68:G72)</f>
         <v>5.1526806673707641</v>
       </c>
-      <c r="M60" s="55"/>
+      <c r="M60" s="75"/>
       <c r="N60" s="14">
         <f>AVERAGE(DataExp1.0!H68:H72)</f>
         <v>1.64322334708934</v>
@@ -9029,24 +9029,24 @@
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A61" s="74"/>
+      <c r="A61" s="51"/>
       <c r="B61" s="9">
         <v>5</v>
       </c>
-      <c r="C61" s="73"/>
-      <c r="D61" s="73"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="58"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="73"/>
-      <c r="J61" s="73"/>
-      <c r="K61" s="64"/>
+      <c r="C61" s="54"/>
+      <c r="D61" s="54"/>
+      <c r="E61" s="54"/>
+      <c r="F61" s="59"/>
+      <c r="G61" s="54"/>
+      <c r="H61" s="54"/>
+      <c r="I61" s="54"/>
+      <c r="J61" s="54"/>
+      <c r="K61" s="81"/>
       <c r="L61" s="14">
         <f>AVERAGE(DataExp1.0!L68:L72)</f>
         <v>4.5663862222048444</v>
       </c>
-      <c r="M61" s="55"/>
+      <c r="M61" s="75"/>
       <c r="N61" s="14">
         <f>AVERAGE(DataExp1.0!M68:M72)</f>
         <v>1.4990279812301417</v>
@@ -9065,24 +9065,24 @@
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A62" s="74"/>
+      <c r="A62" s="51"/>
       <c r="B62" s="9">
         <v>10</v>
       </c>
-      <c r="C62" s="73"/>
-      <c r="D62" s="73"/>
-      <c r="E62" s="73"/>
-      <c r="F62" s="58"/>
-      <c r="G62" s="73"/>
-      <c r="H62" s="73"/>
-      <c r="I62" s="73"/>
-      <c r="J62" s="73"/>
-      <c r="K62" s="64"/>
+      <c r="C62" s="54"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="54"/>
+      <c r="F62" s="59"/>
+      <c r="G62" s="54"/>
+      <c r="H62" s="54"/>
+      <c r="I62" s="54"/>
+      <c r="J62" s="54"/>
+      <c r="K62" s="81"/>
       <c r="L62" s="14">
         <f>AVERAGE(DataExp1.0!Q68:Q72)</f>
         <v>4.8609510367857283</v>
       </c>
-      <c r="M62" s="55"/>
+      <c r="M62" s="75"/>
       <c r="N62" s="14">
         <f>AVERAGE(DataExp1.0!R68:R72)</f>
         <v>1.6425330183325961</v>
@@ -9101,24 +9101,24 @@
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A63" s="74"/>
+      <c r="A63" s="51"/>
       <c r="B63" s="9">
         <v>20</v>
       </c>
-      <c r="C63" s="73"/>
-      <c r="D63" s="73"/>
-      <c r="E63" s="73"/>
-      <c r="F63" s="58"/>
-      <c r="G63" s="73"/>
-      <c r="H63" s="73"/>
-      <c r="I63" s="73"/>
-      <c r="J63" s="73"/>
-      <c r="K63" s="64"/>
+      <c r="C63" s="54"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="59"/>
+      <c r="G63" s="54"/>
+      <c r="H63" s="54"/>
+      <c r="I63" s="54"/>
+      <c r="J63" s="54"/>
+      <c r="K63" s="81"/>
       <c r="L63" s="14">
         <f>AVERAGE(DataExp1.0!V68:V72)</f>
         <v>4.6108742283920376</v>
       </c>
-      <c r="M63" s="55"/>
+      <c r="M63" s="75"/>
       <c r="N63" s="14">
         <f>AVERAGE(DataExp1.0!W68:W72)</f>
         <v>1.6479351514602882</v>
@@ -9137,24 +9137,24 @@
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A64" s="74"/>
+      <c r="A64" s="51"/>
       <c r="B64" s="9">
         <v>50</v>
       </c>
-      <c r="C64" s="73"/>
-      <c r="D64" s="73"/>
-      <c r="E64" s="73"/>
-      <c r="F64" s="58"/>
-      <c r="G64" s="73"/>
-      <c r="H64" s="73"/>
-      <c r="I64" s="73"/>
-      <c r="J64" s="73"/>
-      <c r="K64" s="64"/>
+      <c r="C64" s="54"/>
+      <c r="D64" s="54"/>
+      <c r="E64" s="54"/>
+      <c r="F64" s="59"/>
+      <c r="G64" s="54"/>
+      <c r="H64" s="54"/>
+      <c r="I64" s="54"/>
+      <c r="J64" s="54"/>
+      <c r="K64" s="81"/>
       <c r="L64" s="14">
         <f>AVERAGE(DataExp1.0!AA68:AA72)</f>
         <v>4.3214484422064539</v>
       </c>
-      <c r="M64" s="55"/>
+      <c r="M64" s="75"/>
       <c r="N64" s="14">
         <f>AVERAGE(DataExp1.0!AB68:AB72)</f>
         <v>1.64558067160458</v>
@@ -9173,24 +9173,24 @@
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A65" s="74"/>
+      <c r="A65" s="51"/>
       <c r="B65" s="9">
         <v>100</v>
       </c>
-      <c r="C65" s="73"/>
-      <c r="D65" s="73"/>
-      <c r="E65" s="73"/>
-      <c r="F65" s="59"/>
-      <c r="G65" s="73"/>
-      <c r="H65" s="73"/>
-      <c r="I65" s="73"/>
-      <c r="J65" s="73"/>
-      <c r="K65" s="65"/>
+      <c r="C65" s="54"/>
+      <c r="D65" s="54"/>
+      <c r="E65" s="54"/>
+      <c r="F65" s="53"/>
+      <c r="G65" s="54"/>
+      <c r="H65" s="54"/>
+      <c r="I65" s="54"/>
+      <c r="J65" s="54"/>
+      <c r="K65" s="82"/>
       <c r="L65" s="14">
         <f>AVERAGE(DataExp1.0!AF68:AF72)</f>
         <v>4.45619340247758</v>
       </c>
-      <c r="M65" s="56"/>
+      <c r="M65" s="76"/>
       <c r="N65" s="14">
         <f>AVERAGE(DataExp1.0!AG68:AG72)</f>
         <v>1.6424059899405161</v>
@@ -9210,20 +9210,17 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A45:A51"/>
-    <mergeCell ref="A52:A58"/>
-    <mergeCell ref="A59:A65"/>
-    <mergeCell ref="I9:I36"/>
-    <mergeCell ref="J9:J36"/>
-    <mergeCell ref="A38:A44"/>
-    <mergeCell ref="C38:C65"/>
-    <mergeCell ref="D38:D65"/>
-    <mergeCell ref="E38:E65"/>
-    <mergeCell ref="G38:G65"/>
-    <mergeCell ref="H38:H65"/>
-    <mergeCell ref="I38:I65"/>
-    <mergeCell ref="J38:J65"/>
-    <mergeCell ref="F38:F65"/>
+    <mergeCell ref="K45:K51"/>
+    <mergeCell ref="M45:M51"/>
+    <mergeCell ref="K52:K58"/>
+    <mergeCell ref="M52:M58"/>
+    <mergeCell ref="K59:K65"/>
+    <mergeCell ref="M59:M65"/>
+    <mergeCell ref="M16:M22"/>
+    <mergeCell ref="M23:M29"/>
+    <mergeCell ref="M30:M36"/>
+    <mergeCell ref="K38:K44"/>
+    <mergeCell ref="M38:M44"/>
     <mergeCell ref="A6:U6"/>
     <mergeCell ref="A9:A15"/>
     <mergeCell ref="A16:A22"/>
@@ -9240,17 +9237,20 @@
     <mergeCell ref="K23:K29"/>
     <mergeCell ref="K30:K36"/>
     <mergeCell ref="M9:M15"/>
-    <mergeCell ref="M16:M22"/>
-    <mergeCell ref="M23:M29"/>
-    <mergeCell ref="M30:M36"/>
-    <mergeCell ref="K38:K44"/>
-    <mergeCell ref="M38:M44"/>
-    <mergeCell ref="K45:K51"/>
-    <mergeCell ref="M45:M51"/>
-    <mergeCell ref="K52:K58"/>
-    <mergeCell ref="M52:M58"/>
-    <mergeCell ref="K59:K65"/>
-    <mergeCell ref="M59:M65"/>
+    <mergeCell ref="A45:A51"/>
+    <mergeCell ref="A52:A58"/>
+    <mergeCell ref="A59:A65"/>
+    <mergeCell ref="I9:I36"/>
+    <mergeCell ref="J9:J36"/>
+    <mergeCell ref="A38:A44"/>
+    <mergeCell ref="C38:C65"/>
+    <mergeCell ref="D38:D65"/>
+    <mergeCell ref="E38:E65"/>
+    <mergeCell ref="G38:G65"/>
+    <mergeCell ref="H38:H65"/>
+    <mergeCell ref="I38:I65"/>
+    <mergeCell ref="J38:J65"/>
+    <mergeCell ref="F38:F65"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9295,94 +9295,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-      <c r="M1" s="44"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="44"/>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="44"/>
-      <c r="R1" s="44"/>
-      <c r="S1" s="44"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="44"/>
-      <c r="V1" s="44"/>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-      <c r="Z1" s="44"/>
-      <c r="AA1" s="44"/>
-      <c r="AB1" s="44"/>
-      <c r="AC1" s="44"/>
-      <c r="AD1" s="44"/>
-      <c r="AE1" s="44"/>
-      <c r="AF1" s="44"/>
-      <c r="AG1" s="44"/>
-      <c r="AH1" s="44"/>
-      <c r="AI1" s="44"/>
-      <c r="AJ1" s="44"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+      <c r="Z1" s="38"/>
+      <c r="AA1" s="38"/>
+      <c r="AB1" s="38"/>
+      <c r="AC1" s="38"/>
+      <c r="AD1" s="38"/>
+      <c r="AE1" s="38"/>
+      <c r="AF1" s="38"/>
+      <c r="AG1" s="38"/>
+      <c r="AH1" s="38"/>
+      <c r="AI1" s="38"/>
+      <c r="AJ1" s="38"/>
     </row>
     <row r="2" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48" t="s">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="38" t="s">
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="41" t="s">
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="38" t="s">
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W2" s="39"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="41" t="s">
+      <c r="W2" s="46"/>
+      <c r="X2" s="46"/>
+      <c r="Y2" s="46"/>
+      <c r="Z2" s="47"/>
+      <c r="AA2" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="AB2" s="42"/>
-      <c r="AC2" s="42"/>
-      <c r="AD2" s="42"/>
-      <c r="AE2" s="43"/>
-      <c r="AF2" s="38" t="s">
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="49"/>
+      <c r="AE2" s="50"/>
+      <c r="AF2" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="AG2" s="39"/>
-      <c r="AH2" s="39"/>
-      <c r="AI2" s="39"/>
-      <c r="AJ2" s="40"/>
+      <c r="AG2" s="46"/>
+      <c r="AH2" s="46"/>
+      <c r="AI2" s="46"/>
+      <c r="AJ2" s="47"/>
       <c r="AN2" s="27"/>
     </row>
     <row r="3" spans="2:40" ht="60" x14ac:dyDescent="0.25">
@@ -9679,94 +9679,94 @@
       <c r="AJ8" s="4"/>
     </row>
     <row r="10" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="44"/>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="44"/>
-      <c r="R10" s="44"/>
-      <c r="S10" s="44"/>
-      <c r="T10" s="44"/>
-      <c r="U10" s="44"/>
-      <c r="V10" s="44"/>
-      <c r="W10" s="44"/>
-      <c r="X10" s="44"/>
-      <c r="Y10" s="44"/>
-      <c r="Z10" s="44"/>
-      <c r="AA10" s="44"/>
-      <c r="AB10" s="44"/>
-      <c r="AC10" s="44"/>
-      <c r="AD10" s="44"/>
-      <c r="AE10" s="44"/>
-      <c r="AF10" s="44"/>
-      <c r="AG10" s="44"/>
-      <c r="AH10" s="44"/>
-      <c r="AI10" s="44"/>
-      <c r="AJ10" s="44"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="38"/>
+      <c r="Q10" s="38"/>
+      <c r="R10" s="38"/>
+      <c r="S10" s="38"/>
+      <c r="T10" s="38"/>
+      <c r="U10" s="38"/>
+      <c r="V10" s="38"/>
+      <c r="W10" s="38"/>
+      <c r="X10" s="38"/>
+      <c r="Y10" s="38"/>
+      <c r="Z10" s="38"/>
+      <c r="AA10" s="38"/>
+      <c r="AB10" s="38"/>
+      <c r="AC10" s="38"/>
+      <c r="AD10" s="38"/>
+      <c r="AE10" s="38"/>
+      <c r="AF10" s="38"/>
+      <c r="AG10" s="38"/>
+      <c r="AH10" s="38"/>
+      <c r="AI10" s="38"/>
+      <c r="AJ10" s="38"/>
     </row>
     <row r="11" spans="2:40" x14ac:dyDescent="0.25">
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="48" t="s">
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="38" t="s">
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="41" t="s">
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="47"/>
+      <c r="Q11" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="R11" s="42"/>
-      <c r="S11" s="42"/>
-      <c r="T11" s="42"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="38" t="s">
+      <c r="R11" s="49"/>
+      <c r="S11" s="49"/>
+      <c r="T11" s="49"/>
+      <c r="U11" s="50"/>
+      <c r="V11" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W11" s="39"/>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="39"/>
-      <c r="Z11" s="40"/>
-      <c r="AA11" s="41" t="s">
+      <c r="W11" s="46"/>
+      <c r="X11" s="46"/>
+      <c r="Y11" s="46"/>
+      <c r="Z11" s="47"/>
+      <c r="AA11" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="AB11" s="42"/>
-      <c r="AC11" s="42"/>
-      <c r="AD11" s="42"/>
-      <c r="AE11" s="43"/>
-      <c r="AF11" s="38" t="s">
+      <c r="AB11" s="49"/>
+      <c r="AC11" s="49"/>
+      <c r="AD11" s="49"/>
+      <c r="AE11" s="50"/>
+      <c r="AF11" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="AG11" s="39"/>
-      <c r="AH11" s="39"/>
-      <c r="AI11" s="39"/>
-      <c r="AJ11" s="40"/>
+      <c r="AG11" s="46"/>
+      <c r="AH11" s="46"/>
+      <c r="AI11" s="46"/>
+      <c r="AJ11" s="47"/>
     </row>
     <row r="12" spans="2:40" ht="60" x14ac:dyDescent="0.25">
       <c r="B12" s="13" t="s">
@@ -10061,94 +10061,94 @@
       <c r="AJ17" s="4"/>
     </row>
     <row r="19" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="44"/>
-      <c r="P19" s="44"/>
-      <c r="Q19" s="44"/>
-      <c r="R19" s="44"/>
-      <c r="S19" s="44"/>
-      <c r="T19" s="44"/>
-      <c r="U19" s="44"/>
-      <c r="V19" s="44"/>
-      <c r="W19" s="44"/>
-      <c r="X19" s="44"/>
-      <c r="Y19" s="44"/>
-      <c r="Z19" s="44"/>
-      <c r="AA19" s="44"/>
-      <c r="AB19" s="44"/>
-      <c r="AC19" s="44"/>
-      <c r="AD19" s="44"/>
-      <c r="AE19" s="44"/>
-      <c r="AF19" s="44"/>
-      <c r="AG19" s="44"/>
-      <c r="AH19" s="44"/>
-      <c r="AI19" s="44"/>
-      <c r="AJ19" s="44"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="38"/>
+      <c r="T19" s="38"/>
+      <c r="U19" s="38"/>
+      <c r="V19" s="38"/>
+      <c r="W19" s="38"/>
+      <c r="X19" s="38"/>
+      <c r="Y19" s="38"/>
+      <c r="Z19" s="38"/>
+      <c r="AA19" s="38"/>
+      <c r="AB19" s="38"/>
+      <c r="AC19" s="38"/>
+      <c r="AD19" s="38"/>
+      <c r="AE19" s="38"/>
+      <c r="AF19" s="38"/>
+      <c r="AG19" s="38"/>
+      <c r="AH19" s="38"/>
+      <c r="AI19" s="38"/>
+      <c r="AJ19" s="38"/>
     </row>
     <row r="20" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="48" t="s">
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="38" t="s">
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="M20" s="39"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="39"/>
-      <c r="P20" s="40"/>
-      <c r="Q20" s="41" t="s">
+      <c r="M20" s="46"/>
+      <c r="N20" s="46"/>
+      <c r="O20" s="46"/>
+      <c r="P20" s="47"/>
+      <c r="Q20" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="R20" s="42"/>
-      <c r="S20" s="42"/>
-      <c r="T20" s="42"/>
-      <c r="U20" s="43"/>
-      <c r="V20" s="38" t="s">
+      <c r="R20" s="49"/>
+      <c r="S20" s="49"/>
+      <c r="T20" s="49"/>
+      <c r="U20" s="50"/>
+      <c r="V20" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W20" s="39"/>
-      <c r="X20" s="39"/>
-      <c r="Y20" s="39"/>
-      <c r="Z20" s="40"/>
-      <c r="AA20" s="41" t="s">
+      <c r="W20" s="46"/>
+      <c r="X20" s="46"/>
+      <c r="Y20" s="46"/>
+      <c r="Z20" s="47"/>
+      <c r="AA20" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="AB20" s="42"/>
-      <c r="AC20" s="42"/>
-      <c r="AD20" s="42"/>
-      <c r="AE20" s="43"/>
-      <c r="AF20" s="38" t="s">
+      <c r="AB20" s="49"/>
+      <c r="AC20" s="49"/>
+      <c r="AD20" s="49"/>
+      <c r="AE20" s="50"/>
+      <c r="AF20" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="AG20" s="39"/>
-      <c r="AH20" s="39"/>
-      <c r="AI20" s="39"/>
-      <c r="AJ20" s="40"/>
+      <c r="AG20" s="46"/>
+      <c r="AH20" s="46"/>
+      <c r="AI20" s="46"/>
+      <c r="AJ20" s="47"/>
     </row>
     <row r="21" spans="2:36" ht="60" x14ac:dyDescent="0.25">
       <c r="B21" s="13" t="s">
@@ -10443,94 +10443,94 @@
       <c r="AJ26" s="4"/>
     </row>
     <row r="28" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B28" s="44" t="s">
+      <c r="B28" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="44"/>
-      <c r="L28" s="44"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="44"/>
-      <c r="O28" s="44"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="44"/>
-      <c r="S28" s="44"/>
-      <c r="T28" s="44"/>
-      <c r="U28" s="44"/>
-      <c r="V28" s="44"/>
-      <c r="W28" s="44"/>
-      <c r="X28" s="44"/>
-      <c r="Y28" s="44"/>
-      <c r="Z28" s="44"/>
-      <c r="AA28" s="44"/>
-      <c r="AB28" s="44"/>
-      <c r="AC28" s="44"/>
-      <c r="AD28" s="44"/>
-      <c r="AE28" s="44"/>
-      <c r="AF28" s="44"/>
-      <c r="AG28" s="44"/>
-      <c r="AH28" s="44"/>
-      <c r="AI28" s="44"/>
-      <c r="AJ28" s="44"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="38"/>
+      <c r="M28" s="38"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="38"/>
+      <c r="Q28" s="38"/>
+      <c r="R28" s="38"/>
+      <c r="S28" s="38"/>
+      <c r="T28" s="38"/>
+      <c r="U28" s="38"/>
+      <c r="V28" s="38"/>
+      <c r="W28" s="38"/>
+      <c r="X28" s="38"/>
+      <c r="Y28" s="38"/>
+      <c r="Z28" s="38"/>
+      <c r="AA28" s="38"/>
+      <c r="AB28" s="38"/>
+      <c r="AC28" s="38"/>
+      <c r="AD28" s="38"/>
+      <c r="AE28" s="38"/>
+      <c r="AF28" s="38"/>
+      <c r="AG28" s="38"/>
+      <c r="AH28" s="38"/>
+      <c r="AI28" s="38"/>
+      <c r="AJ28" s="38"/>
     </row>
     <row r="29" spans="2:36" x14ac:dyDescent="0.25">
-      <c r="B29" s="45" t="s">
+      <c r="B29" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="46"/>
-      <c r="D29" s="46"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="48" t="s">
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="38" t="s">
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="41" t="s">
+      <c r="M29" s="46"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="46"/>
+      <c r="P29" s="47"/>
+      <c r="Q29" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="R29" s="42"/>
-      <c r="S29" s="42"/>
-      <c r="T29" s="42"/>
-      <c r="U29" s="43"/>
-      <c r="V29" s="38" t="s">
+      <c r="R29" s="49"/>
+      <c r="S29" s="49"/>
+      <c r="T29" s="49"/>
+      <c r="U29" s="50"/>
+      <c r="V29" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="W29" s="39"/>
-      <c r="X29" s="39"/>
-      <c r="Y29" s="39"/>
-      <c r="Z29" s="40"/>
-      <c r="AA29" s="41" t="s">
+      <c r="W29" s="46"/>
+      <c r="X29" s="46"/>
+      <c r="Y29" s="46"/>
+      <c r="Z29" s="47"/>
+      <c r="AA29" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="AB29" s="42"/>
-      <c r="AC29" s="42"/>
-      <c r="AD29" s="42"/>
-      <c r="AE29" s="43"/>
-      <c r="AF29" s="38" t="s">
+      <c r="AB29" s="49"/>
+      <c r="AC29" s="49"/>
+      <c r="AD29" s="49"/>
+      <c r="AE29" s="50"/>
+      <c r="AF29" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="AG29" s="39"/>
-      <c r="AH29" s="39"/>
-      <c r="AI29" s="39"/>
-      <c r="AJ29" s="40"/>
+      <c r="AG29" s="46"/>
+      <c r="AH29" s="46"/>
+      <c r="AI29" s="46"/>
+      <c r="AJ29" s="47"/>
     </row>
     <row r="30" spans="2:36" ht="60" x14ac:dyDescent="0.25">
       <c r="B30" s="13" t="s">
@@ -10826,6 +10826,30 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B28:AJ28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="G29:K29"/>
+    <mergeCell ref="L29:P29"/>
+    <mergeCell ref="Q29:U29"/>
+    <mergeCell ref="V29:Z29"/>
+    <mergeCell ref="AA29:AE29"/>
+    <mergeCell ref="AF29:AJ29"/>
+    <mergeCell ref="B19:AJ19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="G20:K20"/>
+    <mergeCell ref="L20:P20"/>
+    <mergeCell ref="Q20:U20"/>
+    <mergeCell ref="V20:Z20"/>
+    <mergeCell ref="AA20:AE20"/>
+    <mergeCell ref="AF20:AJ20"/>
+    <mergeCell ref="B10:AJ10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="L11:P11"/>
+    <mergeCell ref="Q11:U11"/>
+    <mergeCell ref="V11:Z11"/>
+    <mergeCell ref="AA11:AE11"/>
+    <mergeCell ref="AF11:AJ11"/>
     <mergeCell ref="B1:AJ1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G2:K2"/>
@@ -10834,30 +10858,6 @@
     <mergeCell ref="V2:Z2"/>
     <mergeCell ref="AA2:AE2"/>
     <mergeCell ref="AF2:AJ2"/>
-    <mergeCell ref="B10:AJ10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="L11:P11"/>
-    <mergeCell ref="Q11:U11"/>
-    <mergeCell ref="V11:Z11"/>
-    <mergeCell ref="AA11:AE11"/>
-    <mergeCell ref="AF11:AJ11"/>
-    <mergeCell ref="B19:AJ19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="G20:K20"/>
-    <mergeCell ref="L20:P20"/>
-    <mergeCell ref="Q20:U20"/>
-    <mergeCell ref="V20:Z20"/>
-    <mergeCell ref="AA20:AE20"/>
-    <mergeCell ref="AF20:AJ20"/>
-    <mergeCell ref="B28:AJ28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="G29:K29"/>
-    <mergeCell ref="L29:P29"/>
-    <mergeCell ref="Q29:U29"/>
-    <mergeCell ref="V29:Z29"/>
-    <mergeCell ref="AA29:AE29"/>
-    <mergeCell ref="AF29:AJ29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10954,32 +10954,32 @@
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="62" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="59">
+      <c r="D4" s="53">
         <v>1005</v>
       </c>
-      <c r="E4" s="59">
+      <c r="E4" s="53">
         <v>1005</v>
       </c>
-      <c r="F4" s="75"/>
-      <c r="G4" s="59">
+      <c r="F4" s="64"/>
+      <c r="G4" s="53">
         <v>32</v>
       </c>
-      <c r="H4" s="59">
+      <c r="H4" s="53">
         <v>32</v>
       </c>
-      <c r="I4" s="59">
+      <c r="I4" s="53">
         <v>32</v>
       </c>
-      <c r="J4" s="59">
+      <c r="J4" s="53">
         <v>32</v>
       </c>
       <c r="K4" s="5"/>
@@ -10989,18 +10989,18 @@
       <c r="O4" s="14"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
+      <c r="A5" s="63"/>
       <c r="B5" s="6">
         <v>3</v>
       </c>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
@@ -11008,18 +11008,18 @@
       <c r="O5" s="14"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
+      <c r="A6" s="63"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="73"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
@@ -11027,18 +11027,18 @@
       <c r="O6" s="14"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
+      <c r="A7" s="63"/>
       <c r="B7" s="6">
         <v>10</v>
       </c>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
@@ -11046,18 +11046,18 @@
       <c r="O7" s="14"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
+      <c r="A8" s="63"/>
       <c r="B8" s="6">
         <v>20</v>
       </c>
-      <c r="C8" s="73"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="73"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
@@ -11065,18 +11065,18 @@
       <c r="O8" s="14"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="72"/>
+      <c r="A9" s="63"/>
       <c r="B9" s="6">
         <v>50</v>
       </c>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="73"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -11084,18 +11084,18 @@
       <c r="O9" s="14"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
+      <c r="A10" s="63"/>
       <c r="B10" s="6">
         <v>100</v>
       </c>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="73"/>
-      <c r="J10" s="73"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
@@ -11103,20 +11103,20 @@
       <c r="O10" s="14"/>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="73" t="s">
+      <c r="A11" s="54" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
       </c>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="73"/>
-      <c r="J11" s="73"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -11124,18 +11124,18 @@
       <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A12" s="73"/>
+      <c r="A12" s="54"/>
       <c r="B12" s="3">
         <v>3</v>
       </c>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="73"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -11143,18 +11143,18 @@
       <c r="O12" s="4"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A13" s="73"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="3">
         <v>5</v>
       </c>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="73"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
@@ -11162,18 +11162,18 @@
       <c r="O13" s="4"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A14" s="73"/>
+      <c r="A14" s="54"/>
       <c r="B14" s="3">
         <v>10</v>
       </c>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="73"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -11181,18 +11181,18 @@
       <c r="O14" s="4"/>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A15" s="73"/>
+      <c r="A15" s="54"/>
       <c r="B15" s="3">
         <v>20</v>
       </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="73"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="54"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -11200,18 +11200,18 @@
       <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A16" s="73"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="3">
         <v>50</v>
       </c>
-      <c r="C16" s="73"/>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="73"/>
-      <c r="H16" s="73"/>
-      <c r="I16" s="73"/>
-      <c r="J16" s="73"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="54"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -11219,18 +11219,18 @@
       <c r="O16" s="4"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="73"/>
+      <c r="A17" s="54"/>
       <c r="B17" s="3">
         <v>100</v>
       </c>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="73"/>
-      <c r="H17" s="73"/>
-      <c r="I17" s="73"/>
-      <c r="J17" s="73"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="54"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="54"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -11238,20 +11238,20 @@
       <c r="O17" s="4"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="74" t="s">
+      <c r="A18" s="51" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="9">
         <v>1</v>
       </c>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="73"/>
-      <c r="J18" s="73"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="54"/>
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
       <c r="M18" s="14"/>
@@ -11259,18 +11259,18 @@
       <c r="O18" s="14"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="74"/>
+      <c r="A19" s="51"/>
       <c r="B19" s="9">
         <v>3</v>
       </c>
-      <c r="C19" s="73"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="73"/>
-      <c r="J19" s="73"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="54"/>
       <c r="K19" s="14"/>
       <c r="L19" s="14"/>
       <c r="M19" s="14"/>
@@ -11278,18 +11278,18 @@
       <c r="O19" s="14"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="74"/>
+      <c r="A20" s="51"/>
       <c r="B20" s="9">
         <v>5</v>
       </c>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="73"/>
-      <c r="J20" s="73"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
       <c r="K20" s="14"/>
       <c r="L20" s="14"/>
       <c r="M20" s="14"/>
@@ -11297,18 +11297,18 @@
       <c r="O20" s="14"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="74"/>
+      <c r="A21" s="51"/>
       <c r="B21" s="9">
         <v>10</v>
       </c>
-      <c r="C21" s="73"/>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="73"/>
-      <c r="J21" s="73"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
       <c r="K21" s="14"/>
       <c r="L21" s="14"/>
       <c r="M21" s="14"/>
@@ -11316,18 +11316,18 @@
       <c r="O21" s="14"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="74"/>
+      <c r="A22" s="51"/>
       <c r="B22" s="9">
         <v>20</v>
       </c>
-      <c r="C22" s="73"/>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="73"/>
-      <c r="J22" s="73"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
       <c r="K22" s="14"/>
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
@@ -11335,18 +11335,18 @@
       <c r="O22" s="14"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="74"/>
+      <c r="A23" s="51"/>
       <c r="B23" s="9">
         <v>50</v>
       </c>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="73"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
@@ -11354,18 +11354,18 @@
       <c r="O23" s="14"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="74"/>
+      <c r="A24" s="51"/>
       <c r="B24" s="9">
         <v>100</v>
       </c>
-      <c r="C24" s="73"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="73"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="73"/>
-      <c r="J24" s="73"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
@@ -11373,20 +11373,20 @@
       <c r="O24" s="14"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="73" t="s">
+      <c r="A25" s="54" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="3">
         <v>1</v>
       </c>
-      <c r="C25" s="73"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="73"/>
-      <c r="J25" s="73"/>
+      <c r="C25" s="54"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="54"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="54"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="54"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -11394,18 +11394,18 @@
       <c r="O25" s="4"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="73"/>
+      <c r="A26" s="54"/>
       <c r="B26" s="3">
         <v>3</v>
       </c>
-      <c r="C26" s="73"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="73"/>
-      <c r="J26" s="73"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -11413,18 +11413,18 @@
       <c r="O26" s="4"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="73"/>
+      <c r="A27" s="54"/>
       <c r="B27" s="3">
         <v>5</v>
       </c>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="73"/>
-      <c r="J27" s="73"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="54"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -11432,18 +11432,18 @@
       <c r="O27" s="4"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28" s="73"/>
+      <c r="A28" s="54"/>
       <c r="B28" s="3">
         <v>10</v>
       </c>
-      <c r="C28" s="73"/>
-      <c r="D28" s="73"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="73"/>
-      <c r="J28" s="73"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="54"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -11451,18 +11451,18 @@
       <c r="O28" s="4"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="73"/>
+      <c r="A29" s="54"/>
       <c r="B29" s="3">
         <v>20</v>
       </c>
-      <c r="C29" s="73"/>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="73"/>
-      <c r="J29" s="73"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="54"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
@@ -11470,18 +11470,18 @@
       <c r="O29" s="4"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="73"/>
+      <c r="A30" s="54"/>
       <c r="B30" s="3">
         <v>50</v>
       </c>
-      <c r="C30" s="73"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
-      <c r="J30" s="73"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="54"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -11489,18 +11489,18 @@
       <c r="O30" s="4"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="73"/>
+      <c r="A31" s="54"/>
       <c r="B31" s="3">
         <v>100</v>
       </c>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="73"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="73"/>
-      <c r="J31" s="73"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="54"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -11555,32 +11555,32 @@
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="71" t="s">
+      <c r="A34" s="62" t="s">
         <v>12</v>
       </c>
       <c r="B34" s="11">
         <v>1</v>
       </c>
-      <c r="C34" s="59" t="s">
+      <c r="C34" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="D34" s="59">
+      <c r="D34" s="53">
         <v>1005</v>
       </c>
-      <c r="E34" s="59">
+      <c r="E34" s="53">
         <v>1005</v>
       </c>
-      <c r="F34" s="75"/>
-      <c r="G34" s="59">
+      <c r="F34" s="64"/>
+      <c r="G34" s="53">
         <v>16</v>
       </c>
-      <c r="H34" s="59">
+      <c r="H34" s="53">
         <v>16</v>
       </c>
-      <c r="I34" s="59">
+      <c r="I34" s="53">
         <v>64</v>
       </c>
-      <c r